--- a/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
+++ b/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WINDOWS\Desktop\dados planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCF72263-C789-4136-9288-A3008DE20595}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6722DB34-9A73-4C00-A039-919A88AC586C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="219">
   <si>
     <t>Funcionário</t>
   </si>
@@ -453,7 +453,7 @@
     <t>PHARMACEUTICA DISTRIBUIDORA DE MAT. E MED. HOSPITA</t>
   </si>
   <si>
-    <t>01005217.1BPBPBP</t>
+    <t>01005217.1BPBPBPBP</t>
   </si>
   <si>
     <t>BR MEDICAMENTOS LTDA</t>
@@ -552,85 +552,76 @@
     <t>00191154200000860000000003473568000003128917</t>
   </si>
   <si>
-    <t>PLENA DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>01006787.1</t>
-  </si>
-  <si>
-    <t>70799154300000875250001121205064100656762096</t>
+    <t>01006753.5</t>
+  </si>
+  <si>
+    <t>00197154900000860000000003473568000003129017</t>
+  </si>
+  <si>
+    <t>01006941.2</t>
+  </si>
+  <si>
+    <t>00195154900002818370000003473568000003141117</t>
+  </si>
+  <si>
+    <t>REALMED COMERCIO DE PRODUTOS MEDICOS E HOSPITALARE</t>
+  </si>
+  <si>
+    <t>01006951.2</t>
+  </si>
+  <si>
+    <t>00194155000000787400000003473568000003141917</t>
+  </si>
+  <si>
+    <t>M. A. M COMERCIO E DISTRIBUIDORA DE MEDICAMENTOS L</t>
+  </si>
+  <si>
+    <t>01006872.3</t>
+  </si>
+  <si>
+    <t>70791155100003419960001121205064100656763565</t>
+  </si>
+  <si>
+    <t>JT COSTA COMERCIAL LTDA</t>
+  </si>
+  <si>
+    <t>01007005.1</t>
+  </si>
+  <si>
+    <t>00197155200018957860000003473568000003145817</t>
   </si>
   <si>
     <t>ATACAMED COMERCIO LTDA</t>
   </si>
   <si>
-    <t>01006816.3</t>
-  </si>
-  <si>
-    <t>00191154300002754000000003473568000003133117</t>
-  </si>
-  <si>
-    <t>MONTALVAO COMERCIAL LTDA</t>
-  </si>
-  <si>
-    <t>01006713.4</t>
-  </si>
-  <si>
-    <t>JMC</t>
-  </si>
-  <si>
-    <t>70791154800003300000001121205064100656761254</t>
-  </si>
-  <si>
-    <t>01006941.2</t>
-  </si>
-  <si>
-    <t>00195154900002818370000003473568000003141117</t>
-  </si>
-  <si>
-    <t>01006753.5</t>
-  </si>
-  <si>
-    <t>00197154900000860000000003473568000003129017</t>
-  </si>
-  <si>
-    <t>01006996.1</t>
-  </si>
-  <si>
-    <t>00197154900001366670000003473568000003144517</t>
-  </si>
-  <si>
-    <t>MULTIMAIS ATACADO LTDA</t>
-  </si>
-  <si>
-    <t>01006782.5</t>
-  </si>
-  <si>
-    <t>70799154900002400000001121205064100656762880</t>
-  </si>
-  <si>
-    <t>REALMED COMERCIO DE PRODUTOS MEDICOS E HOSPITALARE</t>
-  </si>
-  <si>
-    <t>01006951.2</t>
-  </si>
-  <si>
-    <t>00194155000000787400000003473568000003141917</t>
-  </si>
-  <si>
-    <t>M. A. M COMERCIO E DISTRIBUIDORA DE MEDICAMENTOS L</t>
-  </si>
-  <si>
-    <t>01006872.3</t>
-  </si>
-  <si>
-    <t>70791155100003419960001121205064100656763565</t>
-  </si>
-  <si>
-    <t>01007024.1</t>
-  </si>
-  <si>
-    <t>34195155100001836001090002607538120992717000</t>
+    <t>01006996.2</t>
+  </si>
+  <si>
+    <t>00191155600001366670000003473568000003144617</t>
+  </si>
+  <si>
+    <t>01006941.3</t>
+  </si>
+  <si>
+    <t>00191155600002818370000003473568000003141217</t>
+  </si>
+  <si>
+    <t>01007074.1</t>
+  </si>
+  <si>
+    <t>34195155700002930401090002611328120992717000</t>
+  </si>
+  <si>
+    <t>01006951.3</t>
+  </si>
+  <si>
+    <t>00191155700000787400000003473568000003142017</t>
+  </si>
+  <si>
+    <t>01006872.4</t>
+  </si>
+  <si>
+    <t>70799155800003419960001121205064100656763573</t>
   </si>
   <si>
     <t>KELLEN - MA</t>
@@ -639,97 +630,58 @@
     <t>RICCO FARMA DISTRIBUIDORA LTDA</t>
   </si>
   <si>
-    <t>01006870.2</t>
+    <t>01006741.3</t>
   </si>
   <si>
     <t>MA</t>
   </si>
   <si>
-    <t>00191155200013056000000003473568000003137717</t>
-  </si>
-  <si>
-    <t>CIRURGICA MONTEBELLO LTDA</t>
-  </si>
-  <si>
-    <t>01006958.3</t>
-  </si>
-  <si>
-    <t>70791155200023168600001121205064100656764068</t>
-  </si>
-  <si>
-    <t>JT COSTA COMERCIAL LTDA</t>
-  </si>
-  <si>
-    <t>01007005.1</t>
-  </si>
-  <si>
-    <t>00197155200018957860000003473568000003145817</t>
-  </si>
-  <si>
-    <t>01006787.2</t>
-  </si>
-  <si>
-    <t>70798155300000875250001121205064100656762104</t>
-  </si>
-  <si>
-    <t>DUO HOSPITALAR LTDA</t>
-  </si>
-  <si>
-    <t>01006612.6</t>
-  </si>
-  <si>
-    <t>00193155400004207500000003473568000003123017</t>
-  </si>
-  <si>
-    <t>01007034.1</t>
-  </si>
-  <si>
-    <t>70797155400003172800001121205064100656764589</t>
-  </si>
-  <si>
-    <t>ALINE CERBINO - PA</t>
-  </si>
-  <si>
-    <t>ALTAMED DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>01006932.1</t>
-  </si>
-  <si>
-    <t>PA</t>
-  </si>
-  <si>
-    <t>34196155400007424651090002603818120992717000</t>
-  </si>
-  <si>
-    <t>LEANDRA LUIZA SILVA - AM</t>
-  </si>
-  <si>
-    <t>MP COMERCIO DE PRODUTOS HOSPITALARES E ALIMENTICIO</t>
-  </si>
-  <si>
-    <t>01007016.1</t>
-  </si>
-  <si>
-    <t>AM</t>
-  </si>
-  <si>
-    <t>00193155400008166290000003473568000003148617</t>
-  </si>
-  <si>
-    <t>01007125.1</t>
-  </si>
-  <si>
-    <t>70799155500004320000001121205064100656765099</t>
-  </si>
-  <si>
-    <t>VITAL DISTRIBUIDORA LTDA</t>
-  </si>
-  <si>
-    <t>01006823.4</t>
-  </si>
-  <si>
-    <t>70791155500003530750001121205064100656763326</t>
+    <t>70795155800005352200001121205064100656762039</t>
+  </si>
+  <si>
+    <t>01006749.3</t>
+  </si>
+  <si>
+    <t>70798155800016880700001121205064100656762294</t>
+  </si>
+  <si>
+    <t>01006939.2</t>
+  </si>
+  <si>
+    <t>00196155800005860800000003473568000003140417</t>
+  </si>
+  <si>
+    <t>01007024.2</t>
+  </si>
+  <si>
+    <t>34199155800001836001090002607618120992717000</t>
+  </si>
+  <si>
+    <t>THIAGO RIBEIRO - RO</t>
+  </si>
+  <si>
+    <t>HOSPMED COMERCIO ATAC. E VAREJ. DE PROD. MED. E HO</t>
+  </si>
+  <si>
+    <t>01006647.2</t>
+  </si>
+  <si>
+    <t>RO</t>
+  </si>
+  <si>
+    <t>70799155800003492520001121205064100656761437</t>
+  </si>
+  <si>
+    <t>COBERMED COMERCIO DE MATERIAIS MEDICOS LTDA</t>
+  </si>
+  <si>
+    <t>01006877.2</t>
+  </si>
+  <si>
+    <t>BRADESCO</t>
+  </si>
+  <si>
+    <t>23792155800006265000435090000000110600304920</t>
   </si>
 </sst>
 </file>
@@ -1159,7 +1111,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K88"/>
+  <dimension ref="A1:K84"/>
   <sheetFormatPr defaultColWidth="12.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.28515625" style="1" customWidth="1"/>
@@ -1228,7 +1180,7 @@
         <v>9391.7800000000007</v>
       </c>
       <c r="F2" s="6">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>14</v>
@@ -1259,7 +1211,7 @@
         <v>5418</v>
       </c>
       <c r="F3" s="6">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>14</v>
@@ -1290,7 +1242,7 @@
         <v>1264.8699999999999</v>
       </c>
       <c r="F4" s="6">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>22</v>
@@ -1321,7 +1273,7 @@
         <v>5418</v>
       </c>
       <c r="F5" s="6">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>14</v>
@@ -1352,7 +1304,7 @@
         <v>384</v>
       </c>
       <c r="F6" s="6">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>22</v>
@@ -1383,7 +1335,7 @@
         <v>816</v>
       </c>
       <c r="F7" s="6">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>22</v>
@@ -1414,7 +1366,7 @@
         <v>816</v>
       </c>
       <c r="F8" s="6">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>22</v>
@@ -1445,7 +1397,7 @@
         <v>1674.52</v>
       </c>
       <c r="F9" s="6">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>14</v>
@@ -1476,7 +1428,7 @@
         <v>873.6</v>
       </c>
       <c r="F10" s="6">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>14</v>
@@ -1507,7 +1459,7 @@
         <v>873.6</v>
       </c>
       <c r="F11" s="6">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>14</v>
@@ -1538,7 +1490,7 @@
         <v>2000</v>
       </c>
       <c r="F12" s="6">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>14</v>
@@ -1569,7 +1521,7 @@
         <v>3204.34</v>
       </c>
       <c r="F13" s="6">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>14</v>
@@ -1600,7 +1552,7 @@
         <v>4439.8999999999996</v>
       </c>
       <c r="F14" s="6">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>14</v>
@@ -1631,7 +1583,7 @@
         <v>2000</v>
       </c>
       <c r="F15" s="6">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>14</v>
@@ -1662,7 +1614,7 @@
         <v>1216.8599999999999</v>
       </c>
       <c r="F16" s="6">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>14</v>
@@ -1693,7 +1645,7 @@
         <v>1843.87</v>
       </c>
       <c r="F17" s="6">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>14</v>
@@ -1724,7 +1676,7 @@
         <v>1216.8599999999999</v>
       </c>
       <c r="F18" s="6">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>14</v>
@@ -1755,7 +1707,7 @@
         <v>4439.8999999999996</v>
       </c>
       <c r="F19" s="6">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>14</v>
@@ -1786,7 +1738,7 @@
         <v>1843.88</v>
       </c>
       <c r="F20" s="6">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>14</v>
@@ -1817,7 +1769,7 @@
         <v>1118.4000000000001</v>
       </c>
       <c r="F21" s="6">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>14</v>
@@ -1848,7 +1800,7 @@
         <v>3296.8</v>
       </c>
       <c r="F22" s="6">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>14</v>
@@ -1879,7 +1831,7 @@
         <v>2330</v>
       </c>
       <c r="F23" s="6">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>14</v>
@@ -1910,7 +1862,7 @@
         <v>3296.8</v>
       </c>
       <c r="F24" s="6">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>14</v>
@@ -1941,7 +1893,7 @@
         <v>2541</v>
       </c>
       <c r="F25" s="6">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>22</v>
@@ -1972,7 +1924,7 @@
         <v>3296.8</v>
       </c>
       <c r="F26" s="6">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>14</v>
@@ -2003,7 +1955,7 @@
         <v>2541</v>
       </c>
       <c r="F27" s="6">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>22</v>
@@ -2034,7 +1986,7 @@
         <v>2541</v>
       </c>
       <c r="F28" s="6">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>22</v>
@@ -2065,7 +2017,7 @@
         <v>7562.78</v>
       </c>
       <c r="F29" s="6">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>14</v>
@@ -2096,7 +2048,7 @@
         <v>7562.78</v>
       </c>
       <c r="F30" s="6">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>14</v>
@@ -2127,7 +2079,7 @@
         <v>1154.56</v>
       </c>
       <c r="F31" s="6">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>14</v>
@@ -2158,7 +2110,7 @@
         <v>2541</v>
       </c>
       <c r="F32" s="6">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>22</v>
@@ -2189,7 +2141,7 @@
         <v>7562.78</v>
       </c>
       <c r="F33" s="6">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>14</v>
@@ -2220,7 +2172,7 @@
         <v>1154.56</v>
       </c>
       <c r="F34" s="6">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>14</v>
@@ -2251,7 +2203,7 @@
         <v>1154.56</v>
       </c>
       <c r="F35" s="6">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>14</v>
@@ -2282,7 +2234,7 @@
         <v>7562.76</v>
       </c>
       <c r="F36" s="6">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>14</v>
@@ -2313,7 +2265,7 @@
         <v>1154.56</v>
       </c>
       <c r="F37" s="6">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>14</v>
@@ -2344,7 +2296,7 @@
         <v>6169.53</v>
       </c>
       <c r="F38" s="6">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>14</v>
@@ -2375,7 +2327,7 @@
         <v>3850</v>
       </c>
       <c r="F39" s="6">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>14</v>
@@ -2406,7 +2358,7 @@
         <v>3850</v>
       </c>
       <c r="F40" s="6">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>14</v>
@@ -2437,7 +2389,7 @@
         <v>6089.41</v>
       </c>
       <c r="F41" s="6">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>14</v>
@@ -2468,7 +2420,7 @@
         <v>3800</v>
       </c>
       <c r="F42" s="6">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>14</v>
@@ -2499,7 +2451,7 @@
         <v>3800</v>
       </c>
       <c r="F43" s="6">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>14</v>
@@ -2530,7 +2482,7 @@
         <v>1143.54</v>
       </c>
       <c r="F44" s="6">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>22</v>
@@ -2561,7 +2513,7 @@
         <v>2287.06</v>
       </c>
       <c r="F45" s="6">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>22</v>
@@ -2592,7 +2544,7 @@
         <v>4572.62</v>
       </c>
       <c r="F46" s="6">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>22</v>
@@ -2623,7 +2575,7 @@
         <v>3663.84</v>
       </c>
       <c r="F47" s="6">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>22</v>
@@ -2654,7 +2606,7 @@
         <v>3663.84</v>
       </c>
       <c r="F48" s="6">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>22</v>
@@ -2685,7 +2637,7 @@
         <v>3867.34</v>
       </c>
       <c r="F49" s="6">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>22</v>
@@ -2716,7 +2668,7 @@
         <v>2144.59</v>
       </c>
       <c r="F50" s="6">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>22</v>
@@ -2747,7 +2699,7 @@
         <v>2144.59</v>
       </c>
       <c r="F51" s="6">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>22</v>
@@ -2778,7 +2730,7 @@
         <v>2144.59</v>
       </c>
       <c r="F52" s="6">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>22</v>
@@ -2806,10 +2758,10 @@
         <v>45980</v>
       </c>
       <c r="E53" s="5">
-        <v>38840.89</v>
+        <v>28666.44</v>
       </c>
       <c r="F53" s="6">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="G53" s="3"/>
       <c r="H53" s="3" t="s">
@@ -2836,7 +2788,7 @@
         <v>4480</v>
       </c>
       <c r="F54" s="6">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>22</v>
@@ -2867,7 +2819,7 @@
         <v>33844.160000000003</v>
       </c>
       <c r="F55" s="6">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="G55" s="3"/>
       <c r="H55" s="3" t="s">
@@ -2894,7 +2846,7 @@
         <v>3220</v>
       </c>
       <c r="F56" s="6">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="G56" s="3"/>
       <c r="H56" s="3" t="s">
@@ -2921,7 +2873,7 @@
         <v>14483.06</v>
       </c>
       <c r="F57" s="6">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="G57" s="3"/>
       <c r="H57" s="3" t="s">
@@ -2948,7 +2900,7 @@
         <v>806.34</v>
       </c>
       <c r="F58" s="6">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>22</v>
@@ -2979,7 +2931,7 @@
         <v>503.28</v>
       </c>
       <c r="F59" s="6">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>22</v>
@@ -3010,7 +2962,7 @@
         <v>503.28</v>
       </c>
       <c r="F60" s="6">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>22</v>
@@ -3041,7 +2993,7 @@
         <v>5466.66</v>
       </c>
       <c r="F61" s="6">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>14</v>
@@ -3072,7 +3024,7 @@
         <v>7494.53</v>
       </c>
       <c r="F62" s="6">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G62" s="3"/>
       <c r="H62" s="3" t="s">
@@ -3099,7 +3051,7 @@
         <v>4676.8500000000004</v>
       </c>
       <c r="F63" s="6">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G63" s="3"/>
       <c r="H63" s="3" t="s">
@@ -3126,7 +3078,7 @@
         <v>4676.8500000000004</v>
       </c>
       <c r="F64" s="6">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G64" s="3"/>
       <c r="H64" s="3" t="s">
@@ -3153,7 +3105,7 @@
         <v>31531.5</v>
       </c>
       <c r="F65" s="6">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G65" s="3" t="s">
         <v>14</v>
@@ -3184,7 +3136,7 @@
         <v>3516.48</v>
       </c>
       <c r="F66" s="6">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>166</v>
@@ -3215,7 +3167,7 @@
         <v>2818.37</v>
       </c>
       <c r="F67" s="6">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G67" s="3" t="s">
         <v>22</v>
@@ -3246,7 +3198,7 @@
         <v>860</v>
       </c>
       <c r="F68" s="6">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G68" s="3" t="s">
         <v>22</v>
@@ -3262,96 +3214,94 @@
     </row>
     <row r="69" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>41</v>
+        <v>168</v>
       </c>
       <c r="B69" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="C69" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="C69" s="3" t="s">
-        <v>176</v>
-      </c>
       <c r="D69" s="4">
-        <v>46253</v>
+        <v>46259</v>
       </c>
       <c r="E69" s="5">
-        <v>875.25</v>
+        <v>860</v>
       </c>
       <c r="F69" s="6">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>166</v>
+        <v>22</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>71</v>
+        <v>171</v>
       </c>
       <c r="I69" s="3"/>
       <c r="J69" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="K69" s="3"/>
     </row>
     <row r="70" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>19</v>
+        <v>168</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D70" s="4">
-        <v>46253</v>
+        <v>46259</v>
       </c>
       <c r="E70" s="5">
-        <v>2754</v>
+        <v>2818.37</v>
       </c>
       <c r="F70" s="6">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G70" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>67</v>
+        <v>171</v>
       </c>
       <c r="I70" s="3"/>
       <c r="J70" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="K70" s="3"/>
     </row>
     <row r="71" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="B71" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D71" s="4">
+        <v>46260</v>
+      </c>
+      <c r="E71" s="5">
+        <v>787.4</v>
+      </c>
+      <c r="F71" s="6">
+        <v>9</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I71" s="3"/>
+      <c r="J71" s="3" t="s">
         <v>181</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="D71" s="4">
-        <v>46258</v>
-      </c>
-      <c r="E71" s="5">
-        <v>3300</v>
-      </c>
-      <c r="F71" s="6">
-        <v>8</v>
-      </c>
-      <c r="G71" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H71" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I71" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="J71" s="3" t="s">
-        <v>184</v>
       </c>
       <c r="K71" s="3"/>
     </row>
@@ -3360,47 +3310,47 @@
         <v>168</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D72" s="4">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="E72" s="5">
-        <v>2818.37</v>
+        <v>3419.96</v>
       </c>
       <c r="F72" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>22</v>
+        <v>166</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>171</v>
       </c>
       <c r="I72" s="3"/>
       <c r="J72" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="K72" s="3"/>
     </row>
     <row r="73" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>168</v>
+        <v>11</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D73" s="4">
-        <v>46259</v>
+        <v>46262</v>
       </c>
       <c r="E73" s="5">
-        <v>860</v>
+        <v>18957.86</v>
       </c>
       <c r="F73" s="6">
         <v>7</v>
@@ -3409,11 +3359,11 @@
         <v>22</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>171</v>
+        <v>35</v>
       </c>
       <c r="I73" s="3"/>
       <c r="J73" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="K73" s="3"/>
     </row>
@@ -3422,19 +3372,19 @@
         <v>19</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>189</v>
       </c>
       <c r="D74" s="4">
-        <v>46259</v>
+        <v>46266</v>
       </c>
       <c r="E74" s="5">
         <v>1366.67</v>
       </c>
       <c r="F74" s="6">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>22</v>
@@ -3450,280 +3400,280 @@
     </row>
     <row r="75" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>41</v>
+        <v>168</v>
       </c>
       <c r="B75" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="C75" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="C75" s="3" t="s">
-        <v>192</v>
-      </c>
       <c r="D75" s="4">
-        <v>46259</v>
+        <v>46266</v>
       </c>
       <c r="E75" s="5">
-        <v>2400</v>
+        <v>2818.37</v>
       </c>
       <c r="F75" s="6">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>166</v>
+        <v>22</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>71</v>
+        <v>171</v>
       </c>
       <c r="I75" s="3"/>
       <c r="J75" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K75" s="3"/>
     </row>
     <row r="76" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>194</v>
+        <v>162</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D76" s="4">
-        <v>46260</v>
+        <v>46267</v>
       </c>
       <c r="E76" s="5">
-        <v>787.4</v>
+        <v>2930.4</v>
       </c>
       <c r="F76" s="6">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>67</v>
       </c>
       <c r="I76" s="3"/>
       <c r="J76" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="K76" s="3"/>
     </row>
     <row r="77" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>168</v>
+        <v>41</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D77" s="4">
-        <v>46261</v>
+        <v>46267</v>
       </c>
       <c r="E77" s="5">
-        <v>3419.96</v>
+        <v>787.4</v>
       </c>
       <c r="F77" s="6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>166</v>
+        <v>22</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>171</v>
+        <v>67</v>
       </c>
       <c r="I77" s="3"/>
       <c r="J77" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="K77" s="3"/>
     </row>
     <row r="78" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>19</v>
+        <v>168</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D78" s="4">
-        <v>46261</v>
+        <v>46268</v>
       </c>
       <c r="E78" s="5">
-        <v>1836</v>
+        <v>3419.96</v>
       </c>
       <c r="F78" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>14</v>
+        <v>166</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>67</v>
+        <v>171</v>
       </c>
       <c r="I78" s="3"/>
       <c r="J78" s="3" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="K78" s="3"/>
     </row>
     <row r="79" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D79" s="4">
+        <v>46268</v>
+      </c>
+      <c r="E79" s="5">
+        <v>5352.2</v>
+      </c>
+      <c r="F79" s="6">
+        <v>1</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H79" s="3" t="s">
         <v>202</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="D79" s="4">
-        <v>46262</v>
-      </c>
-      <c r="E79" s="5">
-        <v>13056</v>
-      </c>
-      <c r="F79" s="6">
-        <v>4</v>
-      </c>
-      <c r="G79" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H79" s="3" t="s">
-        <v>205</v>
       </c>
       <c r="I79" s="3"/>
       <c r="J79" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="K79" s="3"/>
     </row>
     <row r="80" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>41</v>
+        <v>199</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D80" s="4">
-        <v>46262</v>
+        <v>46268</v>
       </c>
       <c r="E80" s="5">
-        <v>23168.6</v>
+        <v>16880.7</v>
       </c>
       <c r="F80" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G80" s="3" t="s">
         <v>166</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>23</v>
+        <v>202</v>
       </c>
       <c r="I80" s="3"/>
       <c r="J80" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="K80" s="3"/>
     </row>
     <row r="81" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>210</v>
+        <v>162</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="D81" s="4">
-        <v>46262</v>
+        <v>46268</v>
       </c>
       <c r="E81" s="5">
-        <v>18957.86</v>
+        <v>5860.8</v>
       </c>
       <c r="F81" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="I81" s="3"/>
       <c r="J81" s="3" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="K81" s="3"/>
     </row>
     <row r="82" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="D82" s="4">
-        <v>46263</v>
+        <v>46268</v>
       </c>
       <c r="E82" s="5">
-        <v>875.25</v>
+        <v>1836</v>
       </c>
       <c r="F82" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>166</v>
+        <v>14</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="I82" s="3"/>
       <c r="J82" s="3" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="K82" s="3"/>
     </row>
     <row r="83" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>11</v>
+        <v>210</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="D83" s="4">
-        <v>46264</v>
+        <v>46268</v>
       </c>
       <c r="E83" s="5">
-        <v>4207.5</v>
+        <v>3492.52</v>
       </c>
       <c r="F83" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>22</v>
+        <v>166</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>15</v>
+        <v>213</v>
       </c>
       <c r="I83" s="3"/>
       <c r="J83" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="K83" s="3"/>
     </row>
@@ -3735,152 +3685,28 @@
         <v>215</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D84" s="4">
-        <v>46264</v>
+        <v>46268</v>
       </c>
       <c r="E84" s="5">
-        <v>3172.8</v>
+        <v>6265</v>
       </c>
       <c r="F84" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>166</v>
+        <v>217</v>
       </c>
       <c r="H84" s="3" t="s">
         <v>15</v>
       </c>
       <c r="I84" s="3"/>
       <c r="J84" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K84" s="3"/>
-    </row>
-    <row r="85" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="D85" s="4">
-        <v>46264</v>
-      </c>
-      <c r="E85" s="5">
-        <v>7424.65</v>
-      </c>
-      <c r="F85" s="6">
-        <v>2</v>
-      </c>
-      <c r="G85" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H85" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="I85" s="3"/>
-      <c r="J85" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="K85" s="3"/>
-    </row>
-    <row r="86" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="D86" s="4">
-        <v>46264</v>
-      </c>
-      <c r="E86" s="5">
-        <v>8166.29</v>
-      </c>
-      <c r="F86" s="6">
-        <v>2</v>
-      </c>
-      <c r="G86" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H86" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="I86" s="3"/>
-      <c r="J86" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="K86" s="3"/>
-    </row>
-    <row r="87" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="D87" s="4">
-        <v>46265</v>
-      </c>
-      <c r="E87" s="5">
-        <v>4320</v>
-      </c>
-      <c r="F87" s="6">
-        <v>1</v>
-      </c>
-      <c r="G87" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H87" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I87" s="3"/>
-      <c r="J87" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="K87" s="3"/>
-    </row>
-    <row r="88" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="B88" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="D88" s="4">
-        <v>46265</v>
-      </c>
-      <c r="E88" s="5">
-        <v>3530.75</v>
-      </c>
-      <c r="F88" s="6">
-        <v>1</v>
-      </c>
-      <c r="G88" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H88" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="I88" s="3"/>
-      <c r="J88" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="K88" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
+++ b/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WINDOWS\Desktop\dados planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB866648-A7A0-4F3B-AAB8-D246BD5D0F34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{599B15ED-0D5C-4E10-8CC9-49AC9BFB5493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="XLS_Grid_LANCAMENTO A RECEBER" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0" iterateCount="1"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="245">
   <si>
     <t>Dt.Emissão</t>
   </si>
@@ -48,6 +48,9 @@
     <t>Vr.Líquido</t>
   </si>
   <si>
+    <t>Dt.Baixa</t>
+  </si>
+  <si>
     <t>Dias Atraso</t>
   </si>
   <si>
@@ -546,19 +549,25 @@
     <t>ALIANCA DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
   </si>
   <si>
+    <t>01006753.4</t>
+  </si>
+  <si>
+    <t>PI</t>
+  </si>
+  <si>
+    <t>00191154200000860000000003473568000003128917</t>
+  </si>
+  <si>
     <t>01006941.1</t>
   </si>
   <si>
-    <t>PI</t>
-  </si>
-  <si>
     <t>00191154200002818370000003473568000003141017</t>
   </si>
   <si>
-    <t>01006753.4</t>
-  </si>
-  <si>
-    <t>00191154200000860000000003473568000003128917</t>
+    <t>01006941.2</t>
+  </si>
+  <si>
+    <t>00195154900002818370000003473568000003141117</t>
   </si>
   <si>
     <t>01006753.5</t>
@@ -567,217 +576,190 @@
     <t>00197154900000860000000003473568000003129017</t>
   </si>
   <si>
-    <t>01006941.2</t>
-  </si>
-  <si>
-    <t>00195154900002818370000003473568000003141117</t>
+    <t>JT COSTA COMERCIAL LTDA</t>
+  </si>
+  <si>
+    <t>01007005.1</t>
+  </si>
+  <si>
+    <t>00197155200018957860000003473568000003145817</t>
+  </si>
+  <si>
+    <t>01006941.3</t>
+  </si>
+  <si>
+    <t>00191155600002818370000003473568000003141217</t>
+  </si>
+  <si>
+    <t>ATACAMED COMERCIO LTDA</t>
+  </si>
+  <si>
+    <t>01007024.2</t>
+  </si>
+  <si>
+    <t>34199155800001836001090002607618120992717000</t>
+  </si>
+  <si>
+    <t>CIRURGICA MONTEBELLO LTDA</t>
+  </si>
+  <si>
+    <t>01006958.4</t>
+  </si>
+  <si>
+    <t>70791155900023168600001121205064100656764076</t>
+  </si>
+  <si>
+    <t>ALINE CERBINO - PA</t>
+  </si>
+  <si>
+    <t>CRISTALFARMA COMERCIO IMPORT E EXPORT LTDA</t>
+  </si>
+  <si>
+    <t>01006920.1</t>
+  </si>
+  <si>
+    <t>PA</t>
+  </si>
+  <si>
+    <t>70797156000011442870001121205064100656763979</t>
+  </si>
+  <si>
+    <t>01006976.1</t>
+  </si>
+  <si>
+    <t>BRADESCO</t>
+  </si>
+  <si>
+    <t>23791156200006389240435090000000114600304920</t>
+  </si>
+  <si>
+    <t>01007005.2</t>
+  </si>
+  <si>
+    <t>00193156200009716000000003473568000003145917</t>
+  </si>
+  <si>
+    <t>VITAL DISTRIBUIDORA LTDA</t>
+  </si>
+  <si>
+    <t>01006823.5</t>
+  </si>
+  <si>
+    <t>70798156200003530760001121205064100656763334</t>
+  </si>
+  <si>
+    <t>01006996.3</t>
+  </si>
+  <si>
+    <t>00199156300001366660000003473568000003144717</t>
+  </si>
+  <si>
+    <t>PLENA DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>01006922.1</t>
+  </si>
+  <si>
+    <t>70795156300011200000001121205064100656763870</t>
+  </si>
+  <si>
+    <t>01006941.4</t>
+  </si>
+  <si>
+    <t>00194156300002818370000003473568000003141317</t>
+  </si>
+  <si>
+    <t>01007187.1</t>
+  </si>
+  <si>
+    <t>70791156400010080000001121205064100656766188</t>
+  </si>
+  <si>
+    <t>RAMON ANTONIO NUNES DA SILVA</t>
+  </si>
+  <si>
+    <t>01006944.4</t>
+  </si>
+  <si>
+    <t>00196156500001803740000003473568000003142417</t>
   </si>
   <si>
     <t>M. A. M COMERCIO E DISTRIBUIDORA DE MEDICAMENTOS L</t>
   </si>
   <si>
-    <t>01006872.3</t>
-  </si>
-  <si>
-    <t>70791155100003419960001121205064100656763565</t>
-  </si>
-  <si>
-    <t>JT COSTA COMERCIAL LTDA</t>
-  </si>
-  <si>
-    <t>01007005.1</t>
-  </si>
-  <si>
-    <t>00197155200018957860000003473568000003145817</t>
-  </si>
-  <si>
-    <t>ATACAMED COMERCIO LTDA</t>
-  </si>
-  <si>
-    <t>01006996.2</t>
-  </si>
-  <si>
-    <t>00191155600001366670000003473568000003144617</t>
-  </si>
-  <si>
-    <t>01006941.3</t>
-  </si>
-  <si>
-    <t>00191155600002818370000003473568000003141217</t>
-  </si>
-  <si>
-    <t>01007024.2</t>
-  </si>
-  <si>
-    <t>34199155800001836001090002607618120992717000</t>
-  </si>
-  <si>
-    <t>01006872.4</t>
-  </si>
-  <si>
-    <t>70799155800003419960001121205064100656763573</t>
+    <t>01006872.5</t>
+  </si>
+  <si>
+    <t>70798156500003419960001121205064100656763581</t>
+  </si>
+  <si>
+    <t>01007024.3</t>
+  </si>
+  <si>
+    <t>34199156500001836001090002607798120992717000</t>
   </si>
   <si>
     <t>KELLEN - MA</t>
   </si>
   <si>
-    <t>RICCO FARMA DISTRIBUIDORA LTDA</t>
-  </si>
-  <si>
-    <t>01006741.3</t>
+    <t>DISTRIBUIDORA BELLFARMA LTDA</t>
+  </si>
+  <si>
+    <t>01007055.2</t>
   </si>
   <si>
     <t>MA</t>
   </si>
   <si>
-    <t>70795155800005352200001121205064100656762039</t>
-  </si>
-  <si>
-    <t>01006749.3</t>
-  </si>
-  <si>
-    <t>70798155800016880700001121205064100656762294</t>
-  </si>
-  <si>
-    <t>THIAGO RIBEIRO - RO</t>
-  </si>
-  <si>
-    <t>HOSPMED COMERCIO ATAC. E VAREJ. DE PROD. MED. E HO</t>
-  </si>
-  <si>
-    <t>01006647.2</t>
-  </si>
-  <si>
-    <t>RO</t>
-  </si>
-  <si>
-    <t>70799155800003492520001121205064100656761437</t>
-  </si>
-  <si>
-    <t>CIRURGICA MONTEBELLO LTDA</t>
-  </si>
-  <si>
-    <t>01006958.4</t>
-  </si>
-  <si>
-    <t>70791155900023168600001121205064100656764076</t>
-  </si>
-  <si>
-    <t>L G PRODUTOS HOSPITALARES LTDA</t>
-  </si>
-  <si>
-    <t>01007060.2</t>
-  </si>
-  <si>
-    <t>70794155900003837600001121205064100656764688</t>
+    <t>34193156600002970001090002610748120992717000</t>
+  </si>
+  <si>
+    <t>MEDICAL MERCANTIL DE APARELHAGEM MEDICA LTDA</t>
+  </si>
+  <si>
+    <t>01007303.1</t>
+  </si>
+  <si>
+    <t>70791156600021103000001121205064100656767509</t>
+  </si>
+  <si>
+    <t>01007316.1</t>
+  </si>
+  <si>
+    <t>23792156600005796000435090000000131500304920</t>
+  </si>
+  <si>
+    <t>NATAL CLEAN DISTRIBUIDORA LTDA</t>
+  </si>
+  <si>
+    <t>01007145.1</t>
+  </si>
+  <si>
+    <t>70793156600004791200001121205064100656765586</t>
   </si>
   <si>
     <t>MAIS SAUDE LTDA</t>
   </si>
   <si>
-    <t>01006873.4</t>
-  </si>
-  <si>
-    <t>34191155900009358701090002603328120992717000</t>
-  </si>
-  <si>
-    <t>PLENA DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>01006910.1</t>
-  </si>
-  <si>
-    <t>BRADESCO</t>
-  </si>
-  <si>
-    <t>23791156000005333330435090000000109600304920</t>
-  </si>
-  <si>
-    <t>ALINE CERBINO - PA</t>
-  </si>
-  <si>
-    <t>CRISTALFARMA COMERCIO IMPORT E EXPORT LTDA</t>
-  </si>
-  <si>
-    <t>01006920.1</t>
-  </si>
-  <si>
-    <t>PA</t>
-  </si>
-  <si>
-    <t>70797156000011442870001121205064100656763979</t>
-  </si>
-  <si>
-    <t>PROMED DIST. DE MEDIC E PROD. PARA SAUDE LTDA</t>
-  </si>
-  <si>
-    <t>01006640.1</t>
-  </si>
-  <si>
-    <t>23795156100004582760435090000000105600304920</t>
-  </si>
-  <si>
-    <t>01006976.1</t>
-  </si>
-  <si>
-    <t>23791156200006389240435090000000114600304920</t>
-  </si>
-  <si>
-    <t>VITAL DISTRIBUIDORA LTDA</t>
-  </si>
-  <si>
-    <t>01006823.5</t>
-  </si>
-  <si>
-    <t>70798156200003530760001121205064100656763334</t>
-  </si>
-  <si>
-    <t>01007005.2</t>
-  </si>
-  <si>
-    <t>00193156200009716000000003473568000003145917</t>
-  </si>
-  <si>
-    <t>01006922.1</t>
-  </si>
-  <si>
-    <t>70795156300011200000001121205064100656763870</t>
-  </si>
-  <si>
-    <t>01006941.4</t>
-  </si>
-  <si>
-    <t>00194156300002818370000003473568000003141317</t>
-  </si>
-  <si>
-    <t>01006996.3</t>
-  </si>
-  <si>
-    <t>00199156300001366660000003473568000003144717</t>
-  </si>
-  <si>
-    <t>ODONTOMED COMERCIO DE PRODUTOS MEDICO HOSPITALAR L</t>
-  </si>
-  <si>
-    <t>01007128.1</t>
-  </si>
-  <si>
-    <t>23791156300002161090435090000000120800304920</t>
-  </si>
-  <si>
-    <t>VIAMED LTDA</t>
-  </si>
-  <si>
-    <t>01006861.5</t>
-  </si>
-  <si>
-    <t>23793156300003151680435090000000108400304920</t>
-  </si>
-  <si>
-    <t>01006787.3</t>
-  </si>
-  <si>
-    <t>70793156300000875250001121205064100656762112</t>
+    <t>01006873.5</t>
+  </si>
+  <si>
+    <t>34194156600009358701090002603408120992717000</t>
+  </si>
+  <si>
+    <t>01006958.5</t>
+  </si>
+  <si>
+    <t>70799156600023168600001121205064100656764084</t>
+  </si>
+  <si>
+    <t>AMAZONIA HOSPITALAR LTDA</t>
+  </si>
+  <si>
+    <t>01006915.5</t>
+  </si>
+  <si>
+    <t>23799156600001760000435090000000110300304920</t>
   </si>
 </sst>
 </file>
@@ -797,13 +779,13 @@
       <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Segoe UI"/>
-      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1207,7 +1189,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N94"/>
+  <dimension ref="A1:O92"/>
   <sheetFormatPr defaultColWidth="12.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.85546875" style="1" customWidth="1"/>
@@ -1217,17 +1199,18 @@
     <col min="5" max="5" width="24.7109375" style="1" customWidth="1"/>
     <col min="6" max="6" width="9.140625" style="1" customWidth="1"/>
     <col min="7" max="7" width="27.28515625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="9.140625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="26.28515625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="3.7109375" style="1" customWidth="1"/>
-    <col min="11" max="11" width="43.42578125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="60.5703125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="26.28515625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="43.42578125" style="1" customWidth="1"/>
-    <col min="15" max="16384" width="12.140625" style="1"/>
+    <col min="8" max="8" width="28.140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="9.140625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="26.28515625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="3.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="43.42578125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="60.5703125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="26.28515625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="43.42578125" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="12.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1270,19 +1253,22 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>45296</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E2" s="3">
         <v>45326</v>
@@ -1293,34 +1279,35 @@
       <c r="G2" s="5">
         <v>9391.7800000000007</v>
       </c>
-      <c r="H2" s="6">
-        <v>948</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>17</v>
+      <c r="H2" s="3"/>
+      <c r="I2" s="6">
+        <v>953</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4" t="s">
+      <c r="K2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="M2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="N2" s="4"/>
-    </row>
-    <row r="3" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O2" s="4"/>
+    </row>
+    <row r="3" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>45296</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E3" s="3">
         <v>45346</v>
@@ -1331,34 +1318,35 @@
       <c r="G3" s="5">
         <v>5418</v>
       </c>
-      <c r="H3" s="6">
-        <v>928</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>17</v>
+      <c r="H3" s="3"/>
+      <c r="I3" s="6">
+        <v>933</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="M3" s="4"/>
+      <c r="K3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4" t="s">
+        <v>22</v>
+      </c>
       <c r="N3" s="4"/>
-    </row>
-    <row r="4" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O3" s="4"/>
+    </row>
+    <row r="4" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>45322</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E4" s="3">
         <v>45350</v>
@@ -1369,34 +1357,35 @@
       <c r="G4" s="5">
         <v>1264.8699999999999</v>
       </c>
-      <c r="H4" s="6">
-        <v>924</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>25</v>
+      <c r="H4" s="3"/>
+      <c r="I4" s="6">
+        <v>929</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4" t="s">
+      <c r="K4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="M4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4" t="s">
+        <v>28</v>
+      </c>
       <c r="N4" s="4"/>
-    </row>
-    <row r="5" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O4" s="4"/>
+    </row>
+    <row r="5" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>45296</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E5" s="3">
         <v>45356</v>
@@ -1407,34 +1396,35 @@
       <c r="G5" s="5">
         <v>5418</v>
       </c>
-      <c r="H5" s="6">
-        <v>918</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>17</v>
+      <c r="H5" s="3"/>
+      <c r="I5" s="6">
+        <v>923</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="M5" s="4"/>
+      <c r="K5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4" t="s">
+        <v>30</v>
+      </c>
       <c r="N5" s="4"/>
-    </row>
-    <row r="6" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O5" s="4"/>
+    </row>
+    <row r="6" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>45306</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E6" s="3">
         <v>45362</v>
@@ -1445,34 +1435,35 @@
       <c r="G6" s="5">
         <v>384</v>
       </c>
-      <c r="H6" s="6">
-        <v>912</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>25</v>
+      <c r="H6" s="3"/>
+      <c r="I6" s="6">
+        <v>917</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="M6" s="4"/>
+      <c r="K6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4" t="s">
+        <v>32</v>
+      </c>
       <c r="N6" s="4"/>
-    </row>
-    <row r="7" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O6" s="4"/>
+    </row>
+    <row r="7" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>45322</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E7" s="3">
         <v>45364</v>
@@ -1483,34 +1474,35 @@
       <c r="G7" s="5">
         <v>816</v>
       </c>
-      <c r="H7" s="6">
-        <v>910</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>25</v>
+      <c r="H7" s="3"/>
+      <c r="I7" s="6">
+        <v>915</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="M7" s="4"/>
+      <c r="K7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="N7" s="4"/>
-    </row>
-    <row r="8" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O7" s="4"/>
+    </row>
+    <row r="8" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>45322</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E8" s="3">
         <v>45378</v>
@@ -1521,34 +1513,35 @@
       <c r="G8" s="5">
         <v>816</v>
       </c>
-      <c r="H8" s="6">
-        <v>896</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>25</v>
+      <c r="H8" s="3"/>
+      <c r="I8" s="6">
+        <v>901</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="M8" s="4"/>
+      <c r="K8" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4" t="s">
+        <v>36</v>
+      </c>
       <c r="N8" s="4"/>
-    </row>
-    <row r="9" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O8" s="4"/>
+    </row>
+    <row r="9" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>45433</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E9" s="3">
         <v>45463</v>
@@ -1559,34 +1552,35 @@
       <c r="G9" s="5">
         <v>1674.52</v>
       </c>
-      <c r="H9" s="6">
-        <v>811</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>17</v>
+      <c r="H9" s="3"/>
+      <c r="I9" s="6">
+        <v>816</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K9" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="M9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4" t="s">
+        <v>40</v>
+      </c>
       <c r="N9" s="4"/>
-    </row>
-    <row r="10" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O9" s="4"/>
+    </row>
+    <row r="10" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>45433</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E10" s="3">
         <v>45493</v>
@@ -1597,34 +1591,35 @@
       <c r="G10" s="5">
         <v>873.6</v>
       </c>
-      <c r="H10" s="6">
-        <v>781</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>17</v>
+      <c r="H10" s="3"/>
+      <c r="I10" s="6">
+        <v>786</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="K10" s="4"/>
-      <c r="L10" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="M10" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="L10" s="4"/>
+      <c r="M10" s="4" t="s">
+        <v>42</v>
+      </c>
       <c r="N10" s="4"/>
-    </row>
-    <row r="11" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O10" s="4"/>
+    </row>
+    <row r="11" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>45433</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E11" s="3">
         <v>45523</v>
@@ -1635,34 +1630,35 @@
       <c r="G11" s="5">
         <v>873.6</v>
       </c>
-      <c r="H11" s="6">
-        <v>751</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>17</v>
+      <c r="H11" s="3"/>
+      <c r="I11" s="6">
+        <v>756</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="K11" s="4"/>
-      <c r="L11" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="M11" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4" t="s">
+        <v>44</v>
+      </c>
       <c r="N11" s="4"/>
-    </row>
-    <row r="12" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O11" s="4"/>
+    </row>
+    <row r="12" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>45558</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E12" s="3">
         <v>45600</v>
@@ -1673,34 +1669,35 @@
       <c r="G12" s="5">
         <v>2000</v>
       </c>
-      <c r="H12" s="6">
-        <v>674</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>17</v>
+      <c r="H12" s="3"/>
+      <c r="I12" s="6">
+        <v>679</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K12" s="4"/>
-      <c r="L12" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="M12" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L12" s="4"/>
+      <c r="M12" s="4" t="s">
+        <v>48</v>
+      </c>
       <c r="N12" s="4"/>
-    </row>
-    <row r="13" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O12" s="4"/>
+    </row>
+    <row r="13" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>45558</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E13" s="3">
         <v>45607</v>
@@ -1711,34 +1708,35 @@
       <c r="G13" s="5">
         <v>3204.34</v>
       </c>
-      <c r="H13" s="6">
-        <v>667</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>17</v>
+      <c r="H13" s="3"/>
+      <c r="I13" s="6">
+        <v>672</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="M13" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L13" s="4"/>
+      <c r="M13" s="4" t="s">
+        <v>50</v>
+      </c>
       <c r="N13" s="4"/>
-    </row>
-    <row r="14" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O13" s="4"/>
+    </row>
+    <row r="14" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>45552</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E14" s="3">
         <v>45608</v>
@@ -1749,34 +1747,35 @@
       <c r="G14" s="5">
         <v>4439.8999999999996</v>
       </c>
-      <c r="H14" s="6">
-        <v>666</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>17</v>
+      <c r="H14" s="3"/>
+      <c r="I14" s="6">
+        <v>671</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="K14" s="4"/>
-      <c r="L14" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K14" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="M14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="4" t="s">
+        <v>55</v>
+      </c>
       <c r="N14" s="4"/>
-    </row>
-    <row r="15" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O14" s="4"/>
+    </row>
+    <row r="15" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>45558</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E15" s="3">
         <v>45614</v>
@@ -1787,34 +1786,35 @@
       <c r="G15" s="5">
         <v>2000</v>
       </c>
-      <c r="H15" s="6">
-        <v>660</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>17</v>
+      <c r="H15" s="3"/>
+      <c r="I15" s="6">
+        <v>665</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K15" s="4"/>
-      <c r="L15" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="M15" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L15" s="4"/>
+      <c r="M15" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="N15" s="4"/>
-    </row>
-    <row r="16" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O15" s="4"/>
+    </row>
+    <row r="16" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>45546</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E16" s="3">
         <v>45615</v>
@@ -1825,34 +1825,35 @@
       <c r="G16" s="5">
         <v>1216.8599999999999</v>
       </c>
-      <c r="H16" s="6">
-        <v>659</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>17</v>
+      <c r="H16" s="3"/>
+      <c r="I16" s="6">
+        <v>664</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K16" s="4"/>
-      <c r="L16" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="M16" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L16" s="4"/>
+      <c r="M16" s="4" t="s">
+        <v>59</v>
+      </c>
       <c r="N16" s="4"/>
-    </row>
-    <row r="17" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O16" s="4"/>
+    </row>
+    <row r="17" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>45548</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E17" s="3">
         <v>45617</v>
@@ -1863,34 +1864,35 @@
       <c r="G17" s="5">
         <v>1843.87</v>
       </c>
-      <c r="H17" s="6">
-        <v>657</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>17</v>
+      <c r="H17" s="3"/>
+      <c r="I17" s="6">
+        <v>662</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K17" s="4"/>
-      <c r="L17" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="M17" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L17" s="4"/>
+      <c r="M17" s="4" t="s">
+        <v>61</v>
+      </c>
       <c r="N17" s="4"/>
-    </row>
-    <row r="18" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O17" s="4"/>
+    </row>
+    <row r="18" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>45546</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E18" s="3">
         <v>45622</v>
@@ -1901,34 +1903,35 @@
       <c r="G18" s="5">
         <v>1216.8599999999999</v>
       </c>
-      <c r="H18" s="6">
-        <v>652</v>
-      </c>
-      <c r="I18" s="4" t="s">
-        <v>17</v>
+      <c r="H18" s="3"/>
+      <c r="I18" s="6">
+        <v>657</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K18" s="4"/>
-      <c r="L18" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="M18" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L18" s="4"/>
+      <c r="M18" s="4" t="s">
+        <v>63</v>
+      </c>
       <c r="N18" s="4"/>
-    </row>
-    <row r="19" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O18" s="4"/>
+    </row>
+    <row r="19" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>45552</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E19" s="3">
         <v>45622</v>
@@ -1939,34 +1942,35 @@
       <c r="G19" s="5">
         <v>4439.8999999999996</v>
       </c>
-      <c r="H19" s="6">
-        <v>652</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>17</v>
+      <c r="H19" s="3"/>
+      <c r="I19" s="6">
+        <v>657</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="K19" s="4"/>
-      <c r="L19" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="M19" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="L19" s="4"/>
+      <c r="M19" s="4" t="s">
+        <v>65</v>
+      </c>
       <c r="N19" s="4"/>
-    </row>
-    <row r="20" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O19" s="4"/>
+    </row>
+    <row r="20" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>45548</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E20" s="3">
         <v>45624</v>
@@ -1977,34 +1981,35 @@
       <c r="G20" s="5">
         <v>1843.88</v>
       </c>
-      <c r="H20" s="6">
-        <v>650</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>17</v>
+      <c r="H20" s="3"/>
+      <c r="I20" s="6">
+        <v>655</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K20" s="4"/>
-      <c r="L20" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="M20" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L20" s="4"/>
+      <c r="M20" s="4" t="s">
+        <v>67</v>
+      </c>
       <c r="N20" s="4"/>
-    </row>
-    <row r="21" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O20" s="4"/>
+    </row>
+    <row r="21" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>45632</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E21" s="3">
         <v>45688</v>
@@ -2015,34 +2020,35 @@
       <c r="G21" s="5">
         <v>1118.4000000000001</v>
       </c>
-      <c r="H21" s="6">
-        <v>586</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>17</v>
+      <c r="H21" s="3"/>
+      <c r="I21" s="6">
+        <v>591</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="K21" s="4"/>
-      <c r="L21" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K21" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="M21" s="4"/>
+      <c r="L21" s="4"/>
+      <c r="M21" s="4" t="s">
+        <v>72</v>
+      </c>
       <c r="N21" s="4"/>
-    </row>
-    <row r="22" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O21" s="4"/>
+    </row>
+    <row r="22" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>45646</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E22" s="3">
         <v>45695</v>
@@ -2053,34 +2059,35 @@
       <c r="G22" s="5">
         <v>3296.8</v>
       </c>
-      <c r="H22" s="6">
-        <v>579</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>17</v>
+      <c r="H22" s="3"/>
+      <c r="I22" s="6">
+        <v>584</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="K22" s="4"/>
-      <c r="L22" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K22" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="M22" s="4"/>
+      <c r="L22" s="4"/>
+      <c r="M22" s="4" t="s">
+        <v>76</v>
+      </c>
       <c r="N22" s="4"/>
-    </row>
-    <row r="23" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O22" s="4"/>
+    </row>
+    <row r="23" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>45636</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E23" s="3">
         <v>45699</v>
@@ -2091,34 +2098,35 @@
       <c r="G23" s="5">
         <v>2330</v>
       </c>
-      <c r="H23" s="6">
-        <v>575</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>17</v>
+      <c r="H23" s="3"/>
+      <c r="I23" s="6">
+        <v>580</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="K23" s="4"/>
-      <c r="L23" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="M23" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="L23" s="4"/>
+      <c r="M23" s="4" t="s">
+        <v>78</v>
+      </c>
       <c r="N23" s="4"/>
-    </row>
-    <row r="24" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O23" s="4"/>
+    </row>
+    <row r="24" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>45646</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E24" s="3">
         <v>45702</v>
@@ -2129,34 +2137,35 @@
       <c r="G24" s="5">
         <v>3296.8</v>
       </c>
-      <c r="H24" s="6">
-        <v>572</v>
-      </c>
-      <c r="I24" s="4" t="s">
-        <v>17</v>
+      <c r="H24" s="3"/>
+      <c r="I24" s="6">
+        <v>577</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="K24" s="4"/>
-      <c r="L24" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="M24" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="L24" s="4"/>
+      <c r="M24" s="4" t="s">
+        <v>80</v>
+      </c>
       <c r="N24" s="4"/>
-    </row>
-    <row r="25" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O24" s="4"/>
+    </row>
+    <row r="25" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>45677</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E25" s="3">
         <v>45705</v>
@@ -2167,34 +2176,35 @@
       <c r="G25" s="5">
         <v>2541</v>
       </c>
-      <c r="H25" s="6">
-        <v>569</v>
-      </c>
-      <c r="I25" s="4" t="s">
-        <v>25</v>
+      <c r="H25" s="3"/>
+      <c r="I25" s="6">
+        <v>574</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="K25" s="4"/>
-      <c r="L25" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="M25" s="4"/>
+        <v>26</v>
+      </c>
+      <c r="K25" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="L25" s="4"/>
+      <c r="M25" s="4" t="s">
+        <v>82</v>
+      </c>
       <c r="N25" s="4"/>
-    </row>
-    <row r="26" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O25" s="4"/>
+    </row>
+    <row r="26" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>45646</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E26" s="3">
         <v>45709</v>
@@ -2205,34 +2215,35 @@
       <c r="G26" s="5">
         <v>3296.8</v>
       </c>
-      <c r="H26" s="6">
-        <v>565</v>
-      </c>
-      <c r="I26" s="4" t="s">
-        <v>17</v>
+      <c r="H26" s="3"/>
+      <c r="I26" s="6">
+        <v>570</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="K26" s="4"/>
-      <c r="L26" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="M26" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="K26" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="L26" s="4"/>
+      <c r="M26" s="4" t="s">
+        <v>84</v>
+      </c>
       <c r="N26" s="4"/>
-    </row>
-    <row r="27" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O26" s="4"/>
+    </row>
+    <row r="27" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>45677</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E27" s="3">
         <v>45712</v>
@@ -2243,34 +2254,35 @@
       <c r="G27" s="5">
         <v>2541</v>
       </c>
-      <c r="H27" s="6">
-        <v>562</v>
-      </c>
-      <c r="I27" s="4" t="s">
-        <v>25</v>
+      <c r="H27" s="3"/>
+      <c r="I27" s="6">
+        <v>567</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="K27" s="4"/>
-      <c r="L27" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="M27" s="4"/>
+        <v>26</v>
+      </c>
+      <c r="K27" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="L27" s="4"/>
+      <c r="M27" s="4" t="s">
+        <v>86</v>
+      </c>
       <c r="N27" s="4"/>
-    </row>
-    <row r="28" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O27" s="4"/>
+    </row>
+    <row r="28" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>45677</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E28" s="3">
         <v>45726</v>
@@ -2281,34 +2293,35 @@
       <c r="G28" s="5">
         <v>2541</v>
       </c>
-      <c r="H28" s="6">
-        <v>548</v>
-      </c>
-      <c r="I28" s="4" t="s">
-        <v>25</v>
+      <c r="H28" s="3"/>
+      <c r="I28" s="6">
+        <v>553</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="K28" s="4"/>
-      <c r="L28" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="M28" s="4"/>
+        <v>26</v>
+      </c>
+      <c r="K28" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="L28" s="4"/>
+      <c r="M28" s="4" t="s">
+        <v>88</v>
+      </c>
       <c r="N28" s="4"/>
-    </row>
-    <row r="29" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O28" s="4"/>
+    </row>
+    <row r="29" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>45699</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E29" s="3">
         <v>45727</v>
@@ -2319,34 +2332,35 @@
       <c r="G29" s="5">
         <v>7562.78</v>
       </c>
-      <c r="H29" s="6">
-        <v>547</v>
-      </c>
-      <c r="I29" s="4" t="s">
-        <v>17</v>
+      <c r="H29" s="3"/>
+      <c r="I29" s="6">
+        <v>552</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="K29" s="4"/>
-      <c r="L29" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="M29" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="K29" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="L29" s="4"/>
+      <c r="M29" s="4" t="s">
+        <v>90</v>
+      </c>
       <c r="N29" s="4"/>
-    </row>
-    <row r="30" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O29" s="4"/>
+    </row>
+    <row r="30" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>45699</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E30" s="3">
         <v>45734</v>
@@ -2357,34 +2371,35 @@
       <c r="G30" s="5">
         <v>7562.78</v>
       </c>
-      <c r="H30" s="6">
-        <v>540</v>
-      </c>
-      <c r="I30" s="4" t="s">
-        <v>17</v>
+      <c r="H30" s="3"/>
+      <c r="I30" s="6">
+        <v>545</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="K30" s="4"/>
-      <c r="L30" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="M30" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="K30" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="L30" s="4"/>
+      <c r="M30" s="4" t="s">
+        <v>92</v>
+      </c>
       <c r="N30" s="4"/>
-    </row>
-    <row r="31" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O30" s="4"/>
+    </row>
+    <row r="31" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>45699</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E31" s="3">
         <v>45734</v>
@@ -2395,34 +2410,35 @@
       <c r="G31" s="5">
         <v>1154.56</v>
       </c>
-      <c r="H31" s="6">
-        <v>540</v>
-      </c>
-      <c r="I31" s="4" t="s">
-        <v>17</v>
+      <c r="H31" s="3"/>
+      <c r="I31" s="6">
+        <v>545</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="K31" s="4"/>
-      <c r="L31" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="M31" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="K31" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="L31" s="4"/>
+      <c r="M31" s="4" t="s">
+        <v>95</v>
+      </c>
       <c r="N31" s="4"/>
-    </row>
-    <row r="32" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O31" s="4"/>
+    </row>
+    <row r="32" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>45677</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E32" s="3">
         <v>45740</v>
@@ -2433,34 +2449,35 @@
       <c r="G32" s="5">
         <v>2541</v>
       </c>
-      <c r="H32" s="6">
-        <v>534</v>
-      </c>
-      <c r="I32" s="4" t="s">
-        <v>25</v>
+      <c r="H32" s="3"/>
+      <c r="I32" s="6">
+        <v>539</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="K32" s="4"/>
-      <c r="L32" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="M32" s="4"/>
+        <v>26</v>
+      </c>
+      <c r="K32" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="L32" s="4"/>
+      <c r="M32" s="4" t="s">
+        <v>97</v>
+      </c>
       <c r="N32" s="4"/>
-    </row>
-    <row r="33" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O32" s="4"/>
+    </row>
+    <row r="33" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>45699</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E33" s="3">
         <v>45741</v>
@@ -2471,34 +2488,35 @@
       <c r="G33" s="5">
         <v>7562.78</v>
       </c>
-      <c r="H33" s="6">
-        <v>533</v>
-      </c>
-      <c r="I33" s="4" t="s">
-        <v>17</v>
+      <c r="H33" s="3"/>
+      <c r="I33" s="6">
+        <v>538</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="K33" s="4"/>
-      <c r="L33" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="M33" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="K33" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="L33" s="4"/>
+      <c r="M33" s="4" t="s">
+        <v>99</v>
+      </c>
       <c r="N33" s="4"/>
-    </row>
-    <row r="34" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O33" s="4"/>
+    </row>
+    <row r="34" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>45699</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E34" s="3">
         <v>45741</v>
@@ -2509,34 +2527,35 @@
       <c r="G34" s="5">
         <v>1154.56</v>
       </c>
-      <c r="H34" s="6">
-        <v>533</v>
-      </c>
-      <c r="I34" s="4" t="s">
-        <v>17</v>
+      <c r="H34" s="3"/>
+      <c r="I34" s="6">
+        <v>538</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="K34" s="4"/>
-      <c r="L34" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="M34" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="K34" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="L34" s="4"/>
+      <c r="M34" s="4" t="s">
+        <v>101</v>
+      </c>
       <c r="N34" s="4"/>
-    </row>
-    <row r="35" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O34" s="4"/>
+    </row>
+    <row r="35" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>45699</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E35" s="3">
         <v>45748</v>
@@ -2547,34 +2566,35 @@
       <c r="G35" s="5">
         <v>1154.56</v>
       </c>
-      <c r="H35" s="6">
-        <v>526</v>
-      </c>
-      <c r="I35" s="4" t="s">
-        <v>17</v>
+      <c r="H35" s="3"/>
+      <c r="I35" s="6">
+        <v>531</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="K35" s="4"/>
-      <c r="L35" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="M35" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="K35" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="L35" s="4"/>
+      <c r="M35" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="N35" s="4"/>
-    </row>
-    <row r="36" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O35" s="4"/>
+    </row>
+    <row r="36" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>45699</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E36" s="3">
         <v>45748</v>
@@ -2585,34 +2605,35 @@
       <c r="G36" s="5">
         <v>7562.76</v>
       </c>
-      <c r="H36" s="6">
-        <v>526</v>
-      </c>
-      <c r="I36" s="4" t="s">
-        <v>17</v>
+      <c r="H36" s="3"/>
+      <c r="I36" s="6">
+        <v>531</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="K36" s="4"/>
-      <c r="L36" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="M36" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="K36" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="L36" s="4"/>
+      <c r="M36" s="4" t="s">
+        <v>105</v>
+      </c>
       <c r="N36" s="4"/>
-    </row>
-    <row r="37" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O36" s="4"/>
+    </row>
+    <row r="37" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>45699</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E37" s="3">
         <v>45755</v>
@@ -2623,34 +2644,35 @@
       <c r="G37" s="5">
         <v>1154.56</v>
       </c>
-      <c r="H37" s="6">
-        <v>519</v>
-      </c>
-      <c r="I37" s="4" t="s">
-        <v>17</v>
+      <c r="H37" s="3"/>
+      <c r="I37" s="6">
+        <v>524</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="K37" s="4"/>
-      <c r="L37" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="M37" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="K37" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="L37" s="4"/>
+      <c r="M37" s="4" t="s">
+        <v>107</v>
+      </c>
       <c r="N37" s="4"/>
-    </row>
-    <row r="38" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O37" s="4"/>
+    </row>
+    <row r="38" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>45733</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E38" s="3">
         <v>45761</v>
@@ -2661,34 +2683,35 @@
       <c r="G38" s="5">
         <v>6169.53</v>
       </c>
-      <c r="H38" s="6">
-        <v>513</v>
-      </c>
-      <c r="I38" s="4" t="s">
-        <v>17</v>
+      <c r="H38" s="3"/>
+      <c r="I38" s="6">
+        <v>518</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="K38" s="4"/>
-      <c r="L38" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="M38" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="K38" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="L38" s="4"/>
+      <c r="M38" s="4" t="s">
+        <v>110</v>
+      </c>
       <c r="N38" s="4"/>
-    </row>
-    <row r="39" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O38" s="4"/>
+    </row>
+    <row r="39" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>45733</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E39" s="3">
         <v>45768</v>
@@ -2699,34 +2722,35 @@
       <c r="G39" s="5">
         <v>3850</v>
       </c>
-      <c r="H39" s="6">
-        <v>506</v>
-      </c>
-      <c r="I39" s="4" t="s">
-        <v>17</v>
+      <c r="H39" s="3"/>
+      <c r="I39" s="6">
+        <v>511</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="K39" s="4"/>
-      <c r="L39" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="M39" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="K39" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="L39" s="4"/>
+      <c r="M39" s="4" t="s">
+        <v>112</v>
+      </c>
       <c r="N39" s="4"/>
-    </row>
-    <row r="40" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O39" s="4"/>
+    </row>
+    <row r="40" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>45733</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E40" s="3">
         <v>45775</v>
@@ -2737,34 +2761,35 @@
       <c r="G40" s="5">
         <v>3850</v>
       </c>
-      <c r="H40" s="6">
-        <v>499</v>
-      </c>
-      <c r="I40" s="4" t="s">
-        <v>17</v>
+      <c r="H40" s="3"/>
+      <c r="I40" s="6">
+        <v>504</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="K40" s="4"/>
-      <c r="L40" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="M40" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="K40" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="L40" s="4"/>
+      <c r="M40" s="4" t="s">
+        <v>114</v>
+      </c>
       <c r="N40" s="4"/>
-    </row>
-    <row r="41" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O40" s="4"/>
+    </row>
+    <row r="41" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <v>45747</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E41" s="3">
         <v>45775</v>
@@ -2775,34 +2800,35 @@
       <c r="G41" s="5">
         <v>6089.41</v>
       </c>
-      <c r="H41" s="6">
-        <v>499</v>
-      </c>
-      <c r="I41" s="4" t="s">
-        <v>17</v>
+      <c r="H41" s="3"/>
+      <c r="I41" s="6">
+        <v>504</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="K41" s="4"/>
-      <c r="L41" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="M41" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="K41" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="L41" s="4"/>
+      <c r="M41" s="4" t="s">
+        <v>116</v>
+      </c>
       <c r="N41" s="4"/>
-    </row>
-    <row r="42" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O41" s="4"/>
+    </row>
+    <row r="42" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <v>45747</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E42" s="3">
         <v>45782</v>
@@ -2813,34 +2839,35 @@
       <c r="G42" s="5">
         <v>3800</v>
       </c>
-      <c r="H42" s="6">
-        <v>492</v>
-      </c>
-      <c r="I42" s="4" t="s">
-        <v>17</v>
+      <c r="H42" s="3"/>
+      <c r="I42" s="6">
+        <v>497</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="K42" s="4"/>
-      <c r="L42" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="M42" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="K42" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="L42" s="4"/>
+      <c r="M42" s="4" t="s">
+        <v>118</v>
+      </c>
       <c r="N42" s="4"/>
-    </row>
-    <row r="43" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O42" s="4"/>
+    </row>
+    <row r="43" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>45747</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E43" s="3">
         <v>45789</v>
@@ -2851,34 +2878,35 @@
       <c r="G43" s="5">
         <v>3800</v>
       </c>
-      <c r="H43" s="6">
-        <v>485</v>
-      </c>
-      <c r="I43" s="4" t="s">
-        <v>17</v>
+      <c r="H43" s="3"/>
+      <c r="I43" s="6">
+        <v>490</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="K43" s="4"/>
-      <c r="L43" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="M43" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="K43" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="L43" s="4"/>
+      <c r="M43" s="4" t="s">
+        <v>120</v>
+      </c>
       <c r="N43" s="4"/>
-    </row>
-    <row r="44" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O43" s="4"/>
+    </row>
+    <row r="44" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>45754</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E44" s="3">
         <v>45789</v>
@@ -2889,34 +2917,35 @@
       <c r="G44" s="5">
         <v>1143.54</v>
       </c>
-      <c r="H44" s="6">
-        <v>485</v>
-      </c>
-      <c r="I44" s="4" t="s">
-        <v>25</v>
+      <c r="H44" s="3"/>
+      <c r="I44" s="6">
+        <v>490</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="K44" s="4"/>
-      <c r="L44" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K44" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="M44" s="4"/>
+      <c r="L44" s="4"/>
+      <c r="M44" s="4" t="s">
+        <v>125</v>
+      </c>
       <c r="N44" s="4"/>
-    </row>
-    <row r="45" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O44" s="4"/>
+    </row>
+    <row r="45" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>45754</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E45" s="3">
         <v>45796</v>
@@ -2927,34 +2956,35 @@
       <c r="G45" s="5">
         <v>2287.06</v>
       </c>
-      <c r="H45" s="6">
-        <v>478</v>
-      </c>
-      <c r="I45" s="4" t="s">
-        <v>25</v>
+      <c r="H45" s="3"/>
+      <c r="I45" s="6">
+        <v>483</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="K45" s="4"/>
-      <c r="L45" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="M45" s="4"/>
+        <v>26</v>
+      </c>
+      <c r="K45" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="L45" s="4"/>
+      <c r="M45" s="4" t="s">
+        <v>127</v>
+      </c>
       <c r="N45" s="4"/>
-    </row>
-    <row r="46" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O45" s="4"/>
+    </row>
+    <row r="46" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>45868</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E46" s="3">
         <v>45896</v>
@@ -2965,34 +2995,35 @@
       <c r="G46" s="5">
         <v>4572.62</v>
       </c>
-      <c r="H46" s="6">
-        <v>378</v>
-      </c>
-      <c r="I46" s="4" t="s">
-        <v>25</v>
+      <c r="H46" s="3"/>
+      <c r="I46" s="6">
+        <v>383</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="K46" s="4"/>
-      <c r="L46" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="M46" s="4"/>
+        <v>26</v>
+      </c>
+      <c r="K46" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="L46" s="4"/>
+      <c r="M46" s="4" t="s">
+        <v>130</v>
+      </c>
       <c r="N46" s="4"/>
-    </row>
-    <row r="47" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O46" s="4"/>
+    </row>
+    <row r="47" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>45868</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E47" s="3">
         <v>45910</v>
@@ -3003,34 +3034,35 @@
       <c r="G47" s="5">
         <v>3663.84</v>
       </c>
-      <c r="H47" s="6">
-        <v>364</v>
-      </c>
-      <c r="I47" s="4" t="s">
-        <v>25</v>
+      <c r="H47" s="3"/>
+      <c r="I47" s="6">
+        <v>369</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="K47" s="4"/>
-      <c r="L47" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="M47" s="4"/>
+        <v>26</v>
+      </c>
+      <c r="K47" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="L47" s="4"/>
+      <c r="M47" s="4" t="s">
+        <v>132</v>
+      </c>
       <c r="N47" s="4"/>
-    </row>
-    <row r="48" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O47" s="4"/>
+    </row>
+    <row r="48" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>45868</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E48" s="3">
         <v>45924</v>
@@ -3041,34 +3073,35 @@
       <c r="G48" s="5">
         <v>3663.84</v>
       </c>
-      <c r="H48" s="6">
-        <v>350</v>
-      </c>
-      <c r="I48" s="4" t="s">
-        <v>25</v>
+      <c r="H48" s="3"/>
+      <c r="I48" s="6">
+        <v>355</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="K48" s="4"/>
-      <c r="L48" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="M48" s="4"/>
+        <v>26</v>
+      </c>
+      <c r="K48" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="L48" s="4"/>
+      <c r="M48" s="4" t="s">
+        <v>134</v>
+      </c>
       <c r="N48" s="4"/>
-    </row>
-    <row r="49" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O48" s="4"/>
+    </row>
+    <row r="49" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>45919</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E49" s="3">
         <v>45947</v>
@@ -3079,34 +3112,35 @@
       <c r="G49" s="5">
         <v>3867.34</v>
       </c>
-      <c r="H49" s="6">
-        <v>327</v>
-      </c>
-      <c r="I49" s="4" t="s">
-        <v>25</v>
+      <c r="H49" s="3"/>
+      <c r="I49" s="6">
+        <v>332</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="K49" s="4"/>
-      <c r="L49" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="M49" s="4"/>
+        <v>26</v>
+      </c>
+      <c r="K49" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="L49" s="4"/>
+      <c r="M49" s="4" t="s">
+        <v>138</v>
+      </c>
       <c r="N49" s="4"/>
-    </row>
-    <row r="50" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O49" s="4"/>
+    </row>
+    <row r="50" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <v>45919</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E50" s="3">
         <v>45954</v>
@@ -3117,34 +3151,35 @@
       <c r="G50" s="5">
         <v>2144.59</v>
       </c>
-      <c r="H50" s="6">
-        <v>320</v>
-      </c>
-      <c r="I50" s="4" t="s">
-        <v>25</v>
+      <c r="H50" s="3"/>
+      <c r="I50" s="6">
+        <v>325</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="K50" s="4"/>
-      <c r="L50" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="M50" s="4"/>
+        <v>26</v>
+      </c>
+      <c r="K50" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="L50" s="4"/>
+      <c r="M50" s="4" t="s">
+        <v>140</v>
+      </c>
       <c r="N50" s="4"/>
-    </row>
-    <row r="51" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O50" s="4"/>
+    </row>
+    <row r="51" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <v>45919</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E51" s="3">
         <v>45961</v>
@@ -3155,34 +3190,35 @@
       <c r="G51" s="5">
         <v>2144.59</v>
       </c>
-      <c r="H51" s="6">
-        <v>313</v>
-      </c>
-      <c r="I51" s="4" t="s">
-        <v>25</v>
+      <c r="H51" s="3"/>
+      <c r="I51" s="6">
+        <v>318</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="K51" s="4"/>
-      <c r="L51" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="M51" s="4"/>
+        <v>26</v>
+      </c>
+      <c r="K51" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="L51" s="4"/>
+      <c r="M51" s="4" t="s">
+        <v>142</v>
+      </c>
       <c r="N51" s="4"/>
-    </row>
-    <row r="52" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O51" s="4"/>
+    </row>
+    <row r="52" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <v>45919</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E52" s="3">
         <v>45968</v>
@@ -3193,34 +3229,35 @@
       <c r="G52" s="5">
         <v>2144.59</v>
       </c>
-      <c r="H52" s="6">
-        <v>306</v>
-      </c>
-      <c r="I52" s="4" t="s">
-        <v>25</v>
+      <c r="H52" s="3"/>
+      <c r="I52" s="6">
+        <v>311</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="K52" s="4"/>
-      <c r="L52" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="M52" s="4"/>
+        <v>26</v>
+      </c>
+      <c r="K52" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="L52" s="4"/>
+      <c r="M52" s="4" t="s">
+        <v>144</v>
+      </c>
       <c r="N52" s="4"/>
-    </row>
-    <row r="53" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O52" s="4"/>
+    </row>
+    <row r="53" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>45959</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E53" s="3">
         <v>45980</v>
@@ -3231,30 +3268,31 @@
       <c r="G53" s="5">
         <v>28666.44</v>
       </c>
-      <c r="H53" s="6">
-        <v>294</v>
-      </c>
-      <c r="I53" s="4"/>
-      <c r="J53" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="K53" s="4"/>
+      <c r="H53" s="3"/>
+      <c r="I53" s="6">
+        <v>299</v>
+      </c>
+      <c r="J53" s="4"/>
+      <c r="K53" s="4" t="s">
+        <v>54</v>
+      </c>
       <c r="L53" s="4"/>
       <c r="M53" s="4"/>
       <c r="N53" s="4"/>
-    </row>
-    <row r="54" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O53" s="4"/>
+    </row>
+    <row r="54" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <v>45938</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E54" s="3">
         <v>45980</v>
@@ -3265,34 +3303,35 @@
       <c r="G54" s="5">
         <v>4480</v>
       </c>
-      <c r="H54" s="6">
-        <v>294</v>
-      </c>
-      <c r="I54" s="4" t="s">
-        <v>25</v>
+      <c r="H54" s="3"/>
+      <c r="I54" s="6">
+        <v>299</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="K54" s="4"/>
-      <c r="L54" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="M54" s="4"/>
+        <v>26</v>
+      </c>
+      <c r="K54" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="L54" s="4"/>
+      <c r="M54" s="4" t="s">
+        <v>149</v>
+      </c>
       <c r="N54" s="4"/>
-    </row>
-    <row r="55" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O54" s="4"/>
+    </row>
+    <row r="55" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
         <v>45959</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E55" s="3">
         <v>45987</v>
@@ -3303,30 +3342,31 @@
       <c r="G55" s="5">
         <v>33844.160000000003</v>
       </c>
-      <c r="H55" s="6">
-        <v>287</v>
-      </c>
-      <c r="I55" s="4"/>
-      <c r="J55" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="K55" s="4"/>
+      <c r="H55" s="3"/>
+      <c r="I55" s="6">
+        <v>292</v>
+      </c>
+      <c r="J55" s="4"/>
+      <c r="K55" s="4" t="s">
+        <v>54</v>
+      </c>
       <c r="L55" s="4"/>
       <c r="M55" s="4"/>
       <c r="N55" s="4"/>
-    </row>
-    <row r="56" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O55" s="4"/>
+    </row>
+    <row r="56" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
         <v>45947</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E56" s="3">
         <v>45989</v>
@@ -3337,30 +3377,31 @@
       <c r="G56" s="5">
         <v>3220</v>
       </c>
-      <c r="H56" s="6">
-        <v>285</v>
-      </c>
-      <c r="I56" s="4"/>
-      <c r="J56" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="K56" s="4"/>
+      <c r="H56" s="3"/>
+      <c r="I56" s="6">
+        <v>290</v>
+      </c>
+      <c r="J56" s="4"/>
+      <c r="K56" s="4" t="s">
+        <v>124</v>
+      </c>
       <c r="L56" s="4"/>
       <c r="M56" s="4"/>
       <c r="N56" s="4"/>
-    </row>
-    <row r="57" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O56" s="4"/>
+    </row>
+    <row r="57" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
         <v>45959</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E57" s="3">
         <v>45994</v>
@@ -3371,30 +3412,31 @@
       <c r="G57" s="5">
         <v>14483.06</v>
       </c>
-      <c r="H57" s="6">
-        <v>280</v>
-      </c>
-      <c r="I57" s="4"/>
-      <c r="J57" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="K57" s="4"/>
+      <c r="H57" s="3"/>
+      <c r="I57" s="6">
+        <v>285</v>
+      </c>
+      <c r="J57" s="4"/>
+      <c r="K57" s="4" t="s">
+        <v>54</v>
+      </c>
       <c r="L57" s="4"/>
       <c r="M57" s="4"/>
       <c r="N57" s="4"/>
-    </row>
-    <row r="58" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O57" s="4"/>
+    </row>
+    <row r="58" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
         <v>46062</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E58" s="3">
         <v>46090</v>
@@ -3405,34 +3447,35 @@
       <c r="G58" s="5">
         <v>806.34</v>
       </c>
-      <c r="H58" s="6">
-        <v>184</v>
-      </c>
-      <c r="I58" s="4" t="s">
-        <v>25</v>
+      <c r="H58" s="3"/>
+      <c r="I58" s="6">
+        <v>189</v>
       </c>
       <c r="J58" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="K58" s="4"/>
-      <c r="L58" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="M58" s="4"/>
+      <c r="K58" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L58" s="4"/>
+      <c r="M58" s="4" t="s">
+        <v>155</v>
+      </c>
       <c r="N58" s="4"/>
-    </row>
-    <row r="59" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O58" s="4"/>
+    </row>
+    <row r="59" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
         <v>46062</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E59" s="3">
         <v>46097</v>
@@ -3443,34 +3486,35 @@
       <c r="G59" s="5">
         <v>503.28</v>
       </c>
-      <c r="H59" s="6">
-        <v>177</v>
-      </c>
-      <c r="I59" s="4" t="s">
-        <v>25</v>
+      <c r="H59" s="3"/>
+      <c r="I59" s="6">
+        <v>182</v>
       </c>
       <c r="J59" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="K59" s="4"/>
-      <c r="L59" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="M59" s="4"/>
+      <c r="K59" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L59" s="4"/>
+      <c r="M59" s="4" t="s">
+        <v>157</v>
+      </c>
       <c r="N59" s="4"/>
-    </row>
-    <row r="60" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O59" s="4"/>
+    </row>
+    <row r="60" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
         <v>46062</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E60" s="3">
         <v>46104</v>
@@ -3481,34 +3525,35 @@
       <c r="G60" s="5">
         <v>503.28</v>
       </c>
-      <c r="H60" s="6">
-        <v>170</v>
-      </c>
-      <c r="I60" s="4" t="s">
-        <v>25</v>
+      <c r="H60" s="3"/>
+      <c r="I60" s="6">
+        <v>175</v>
       </c>
       <c r="J60" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="K60" s="4"/>
-      <c r="L60" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="M60" s="4"/>
+      <c r="K60" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L60" s="4"/>
+      <c r="M60" s="4" t="s">
+        <v>159</v>
+      </c>
       <c r="N60" s="4"/>
-    </row>
-    <row r="61" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O60" s="4"/>
+    </row>
+    <row r="61" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
         <v>46045</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E61" s="3">
         <v>46105</v>
@@ -3519,34 +3564,35 @@
       <c r="G61" s="5">
         <v>5466.66</v>
       </c>
-      <c r="H61" s="6">
-        <v>169</v>
-      </c>
-      <c r="I61" s="4" t="s">
-        <v>17</v>
+      <c r="H61" s="3"/>
+      <c r="I61" s="6">
+        <v>174</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="K61" s="4"/>
-      <c r="L61" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="M61" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="K61" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="L61" s="4"/>
+      <c r="M61" s="4" t="s">
+        <v>162</v>
+      </c>
       <c r="N61" s="4"/>
-    </row>
-    <row r="62" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O61" s="4"/>
+    </row>
+    <row r="62" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
         <v>46171</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E62" s="3">
         <v>46192</v>
@@ -3557,30 +3603,31 @@
       <c r="G62" s="5">
         <v>7494.53</v>
       </c>
-      <c r="H62" s="6">
-        <v>82</v>
-      </c>
-      <c r="I62" s="4"/>
-      <c r="J62" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="K62" s="4"/>
+      <c r="H62" s="3"/>
+      <c r="I62" s="6">
+        <v>87</v>
+      </c>
+      <c r="J62" s="4"/>
+      <c r="K62" s="4" t="s">
+        <v>54</v>
+      </c>
       <c r="L62" s="4"/>
       <c r="M62" s="4"/>
       <c r="N62" s="4"/>
-    </row>
-    <row r="63" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O62" s="4"/>
+    </row>
+    <row r="63" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
         <v>46171</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E63" s="3">
         <v>46199</v>
@@ -3591,30 +3638,31 @@
       <c r="G63" s="5">
         <v>4676.8500000000004</v>
       </c>
-      <c r="H63" s="6">
-        <v>75</v>
-      </c>
-      <c r="I63" s="4"/>
-      <c r="J63" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="K63" s="4"/>
+      <c r="H63" s="3"/>
+      <c r="I63" s="6">
+        <v>80</v>
+      </c>
+      <c r="J63" s="4"/>
+      <c r="K63" s="4" t="s">
+        <v>54</v>
+      </c>
       <c r="L63" s="4"/>
       <c r="M63" s="4"/>
       <c r="N63" s="4"/>
-    </row>
-    <row r="64" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O63" s="4"/>
+    </row>
+    <row r="64" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
         <v>46171</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E64" s="3">
         <v>46206</v>
@@ -3625,30 +3673,31 @@
       <c r="G64" s="5">
         <v>4676.8500000000004</v>
       </c>
-      <c r="H64" s="6">
-        <v>68</v>
-      </c>
-      <c r="I64" s="4"/>
-      <c r="J64" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="K64" s="4"/>
+      <c r="H64" s="3"/>
+      <c r="I64" s="6">
+        <v>73</v>
+      </c>
+      <c r="J64" s="4"/>
+      <c r="K64" s="4" t="s">
+        <v>54</v>
+      </c>
       <c r="L64" s="4"/>
       <c r="M64" s="4"/>
       <c r="N64" s="4"/>
-    </row>
-    <row r="65" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O64" s="4"/>
+    </row>
+    <row r="65" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
         <v>46162</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E65" s="3">
         <v>46222</v>
@@ -3659,34 +3708,35 @@
       <c r="G65" s="5">
         <v>31531.5</v>
       </c>
-      <c r="H65" s="6">
-        <v>52</v>
-      </c>
-      <c r="I65" s="4" t="s">
-        <v>17</v>
+      <c r="H65" s="3"/>
+      <c r="I65" s="6">
+        <v>57</v>
       </c>
       <c r="J65" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="K65" s="4"/>
-      <c r="L65" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="M65" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="K65" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="L65" s="4"/>
+      <c r="M65" s="4" t="s">
+        <v>168</v>
+      </c>
       <c r="N65" s="4"/>
-    </row>
-    <row r="66" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O65" s="4"/>
+    </row>
+    <row r="66" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
         <v>46198</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E66" s="3">
         <v>46228</v>
@@ -3697,256 +3747,263 @@
       <c r="G66" s="5">
         <v>3516.48</v>
       </c>
-      <c r="H66" s="6">
-        <v>46</v>
-      </c>
-      <c r="I66" s="4" t="s">
-        <v>169</v>
+      <c r="H66" s="3"/>
+      <c r="I66" s="6">
+        <v>51</v>
       </c>
       <c r="J66" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="K66" s="4"/>
-      <c r="L66" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="M66" s="4"/>
+      <c r="K66" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="L66" s="4"/>
+      <c r="M66" s="4" t="s">
+        <v>171</v>
+      </c>
       <c r="N66" s="4"/>
-    </row>
-    <row r="67" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O66" s="4"/>
+    </row>
+    <row r="67" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
-        <v>46224</v>
+        <v>46203</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E67" s="3">
         <v>46252</v>
       </c>
       <c r="F67" s="5">
-        <v>2818.37</v>
+        <v>860</v>
       </c>
       <c r="G67" s="5">
-        <v>2818.37</v>
-      </c>
-      <c r="H67" s="6">
-        <v>22</v>
-      </c>
-      <c r="I67" s="4" t="s">
-        <v>25</v>
+        <v>860</v>
+      </c>
+      <c r="H67" s="3"/>
+      <c r="I67" s="6">
+        <v>27</v>
       </c>
       <c r="J67" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="K67" s="4"/>
-      <c r="L67" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K67" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="M67" s="4"/>
+      <c r="L67" s="4"/>
+      <c r="M67" s="4" t="s">
+        <v>176</v>
+      </c>
       <c r="N67" s="4"/>
-    </row>
-    <row r="68" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O67" s="4"/>
+    </row>
+    <row r="68" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
-        <v>46203</v>
+        <v>46224</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E68" s="3">
         <v>46252</v>
       </c>
       <c r="F68" s="5">
-        <v>860</v>
+        <v>2818.37</v>
       </c>
       <c r="G68" s="5">
-        <v>860</v>
-      </c>
-      <c r="H68" s="6">
-        <v>22</v>
-      </c>
-      <c r="I68" s="4" t="s">
-        <v>25</v>
+        <v>2818.37</v>
+      </c>
+      <c r="H68" s="3"/>
+      <c r="I68" s="6">
+        <v>27</v>
       </c>
       <c r="J68" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="K68" s="4"/>
-      <c r="L68" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="M68" s="4"/>
+        <v>26</v>
+      </c>
+      <c r="K68" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="L68" s="4"/>
+      <c r="M68" s="4" t="s">
+        <v>178</v>
+      </c>
       <c r="N68" s="4"/>
-    </row>
-    <row r="69" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O68" s="4"/>
+    </row>
+    <row r="69" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
-        <v>46203</v>
+        <v>46224</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E69" s="3">
         <v>46259</v>
       </c>
       <c r="F69" s="5">
-        <v>860</v>
+        <v>2818.37</v>
       </c>
       <c r="G69" s="5">
-        <v>860</v>
-      </c>
-      <c r="H69" s="6">
-        <v>15</v>
-      </c>
-      <c r="I69" s="4" t="s">
-        <v>25</v>
+        <v>2818.37</v>
+      </c>
+      <c r="H69" s="3"/>
+      <c r="I69" s="6">
+        <v>20</v>
       </c>
       <c r="J69" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="K69" s="4"/>
-      <c r="L69" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="M69" s="4"/>
+        <v>26</v>
+      </c>
+      <c r="K69" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="L69" s="4"/>
+      <c r="M69" s="4" t="s">
+        <v>180</v>
+      </c>
       <c r="N69" s="4"/>
-    </row>
-    <row r="70" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O69" s="4"/>
+    </row>
+    <row r="70" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
-        <v>46224</v>
+        <v>46203</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E70" s="3">
         <v>46259</v>
       </c>
       <c r="F70" s="5">
-        <v>2818.37</v>
+        <v>860</v>
       </c>
       <c r="G70" s="5">
-        <v>2818.37</v>
-      </c>
-      <c r="H70" s="6">
+        <v>860</v>
+      </c>
+      <c r="H70" s="3"/>
+      <c r="I70" s="6">
+        <v>20</v>
+      </c>
+      <c r="J70" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K70" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="L70" s="4"/>
+      <c r="M70" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="N70" s="4"/>
+      <c r="O70" s="4"/>
+    </row>
+    <row r="71" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="3">
+        <v>46232</v>
+      </c>
+      <c r="B71" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I70" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="J70" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="K70" s="4"/>
-      <c r="L70" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="M70" s="4"/>
-      <c r="N70" s="4"/>
-    </row>
-    <row r="71" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="3">
-        <v>46219</v>
-      </c>
-      <c r="B71" s="4" t="s">
-        <v>171</v>
-      </c>
       <c r="C71" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E71" s="3">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="F71" s="5">
-        <v>3419.96</v>
+        <v>9716</v>
       </c>
       <c r="G71" s="5">
-        <v>3419.96</v>
-      </c>
-      <c r="H71" s="6">
-        <v>13</v>
-      </c>
-      <c r="I71" s="4" t="s">
-        <v>169</v>
+        <v>18957.86</v>
+      </c>
+      <c r="H71" s="3"/>
+      <c r="I71" s="6">
+        <v>17</v>
       </c>
       <c r="J71" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="K71" s="4"/>
-      <c r="L71" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="M71" s="4"/>
+        <v>26</v>
+      </c>
+      <c r="K71" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="L71" s="4"/>
+      <c r="M71" s="4" t="s">
+        <v>185</v>
+      </c>
       <c r="N71" s="4"/>
-    </row>
-    <row r="72" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O71" s="4"/>
+    </row>
+    <row r="72" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
-        <v>46232</v>
+        <v>46224</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>14</v>
+        <v>172</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="D72" s="4" t="s">
         <v>186</v>
       </c>
       <c r="E72" s="3">
-        <v>46262</v>
+        <v>46266</v>
       </c>
       <c r="F72" s="5">
-        <v>9716</v>
+        <v>2818.37</v>
       </c>
       <c r="G72" s="5">
-        <v>18957.86</v>
-      </c>
-      <c r="H72" s="6">
-        <v>12</v>
-      </c>
-      <c r="I72" s="4" t="s">
-        <v>25</v>
+        <v>2818.37</v>
+      </c>
+      <c r="H72" s="3"/>
+      <c r="I72" s="6">
+        <v>13</v>
       </c>
       <c r="J72" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="K72" s="4"/>
-      <c r="L72" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K72" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="L72" s="4"/>
+      <c r="M72" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="M72" s="4"/>
       <c r="N72" s="4"/>
-    </row>
-    <row r="73" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O72" s="4"/>
+    </row>
+    <row r="73" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="3">
-        <v>46231</v>
+        <v>46233</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C73" s="4" t="s">
         <v>188</v>
@@ -3955,264 +4012,271 @@
         <v>189</v>
       </c>
       <c r="E73" s="3">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="F73" s="5">
-        <v>1366.67</v>
+        <v>1836</v>
       </c>
       <c r="G73" s="5">
-        <v>1366.67</v>
-      </c>
-      <c r="H73" s="6">
-        <v>8</v>
-      </c>
-      <c r="I73" s="4" t="s">
-        <v>25</v>
+        <v>1836</v>
+      </c>
+      <c r="H73" s="3"/>
+      <c r="I73" s="6">
+        <v>11</v>
       </c>
       <c r="J73" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="K73" s="4"/>
-      <c r="L73" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K73" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="L73" s="4"/>
+      <c r="M73" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="M73" s="4"/>
       <c r="N73" s="4"/>
-    </row>
-    <row r="74" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O73" s="4"/>
+    </row>
+    <row r="74" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="3">
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>171</v>
+        <v>45</v>
       </c>
       <c r="C74" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="E74" s="3">
+        <v>46269</v>
+      </c>
+      <c r="F74" s="5">
+        <v>23168.6</v>
+      </c>
+      <c r="G74" s="5">
+        <v>23168.6</v>
+      </c>
+      <c r="H74" s="3"/>
+      <c r="I74" s="6">
+        <v>10</v>
+      </c>
+      <c r="J74" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="K74" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L74" s="4"/>
+      <c r="M74" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="N74" s="4"/>
+      <c r="O74" s="4"/>
+    </row>
+    <row r="75" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="E75" s="3">
+        <v>46270</v>
+      </c>
+      <c r="F75" s="5">
+        <v>7551.88</v>
+      </c>
+      <c r="G75" s="5">
+        <v>11442.87</v>
+      </c>
+      <c r="H75" s="3"/>
+      <c r="I75" s="6">
+        <v>9</v>
+      </c>
+      <c r="J75" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="K75" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="L75" s="4"/>
+      <c r="M75" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="N75" s="4"/>
+      <c r="O75" s="4"/>
+    </row>
+    <row r="76" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="3">
+        <v>46227</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="E76" s="3">
+        <v>46272</v>
+      </c>
+      <c r="F76" s="5">
+        <v>4216.67</v>
+      </c>
+      <c r="G76" s="5">
+        <v>6389.24</v>
+      </c>
+      <c r="H76" s="3"/>
+      <c r="I76" s="6">
+        <v>7</v>
+      </c>
+      <c r="J76" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="K76" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="L76" s="4"/>
+      <c r="M76" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="N76" s="4"/>
+      <c r="O76" s="4"/>
+    </row>
+    <row r="77" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="3">
+        <v>46232</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="E77" s="3">
+        <v>46272</v>
+      </c>
+      <c r="F77" s="5">
+        <v>9716</v>
+      </c>
+      <c r="G77" s="5">
+        <v>9716</v>
+      </c>
+      <c r="H77" s="3"/>
+      <c r="I77" s="6">
+        <v>7</v>
+      </c>
+      <c r="J77" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K77" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="L77" s="4"/>
+      <c r="M77" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="N77" s="4"/>
+      <c r="O77" s="4"/>
+    </row>
+    <row r="78" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="3">
+        <v>46216</v>
+      </c>
+      <c r="B78" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="D74" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="E74" s="3">
-        <v>46266</v>
-      </c>
-      <c r="F74" s="5">
-        <v>2818.37</v>
-      </c>
-      <c r="G74" s="5">
-        <v>2818.37</v>
-      </c>
-      <c r="H74" s="6">
-        <v>8</v>
-      </c>
-      <c r="I74" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="J74" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="K74" s="4"/>
-      <c r="L74" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="M74" s="4"/>
-      <c r="N74" s="4"/>
-    </row>
-    <row r="75" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="3">
-        <v>46233</v>
-      </c>
-      <c r="B75" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C75" s="4" t="s">
+      <c r="C78" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="E78" s="3">
+        <v>46272</v>
+      </c>
+      <c r="F78" s="5">
+        <v>3530.76</v>
+      </c>
+      <c r="G78" s="5">
+        <v>3530.76</v>
+      </c>
+      <c r="H78" s="3"/>
+      <c r="I78" s="6">
+        <v>7</v>
+      </c>
+      <c r="J78" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="K78" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="L78" s="4"/>
+      <c r="M78" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="N78" s="4"/>
+      <c r="O78" s="4"/>
+    </row>
+    <row r="79" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="3">
+        <v>46231</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C79" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="D75" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="E75" s="3">
-        <v>46268</v>
-      </c>
-      <c r="F75" s="5">
-        <v>1836</v>
-      </c>
-      <c r="G75" s="5">
-        <v>1836</v>
-      </c>
-      <c r="H75" s="6">
+      <c r="D79" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="E79" s="3">
+        <v>46273</v>
+      </c>
+      <c r="F79" s="5">
+        <v>1366.66</v>
+      </c>
+      <c r="G79" s="5">
+        <v>1366.66</v>
+      </c>
+      <c r="H79" s="3"/>
+      <c r="I79" s="6">
         <v>6</v>
       </c>
-      <c r="I75" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J75" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="K75" s="4"/>
-      <c r="L75" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="M75" s="4"/>
-      <c r="N75" s="4"/>
-    </row>
-    <row r="76" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="3">
-        <v>46219</v>
-      </c>
-      <c r="B76" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="C76" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="D76" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="E76" s="3">
-        <v>46268</v>
-      </c>
-      <c r="F76" s="5">
-        <v>3419.96</v>
-      </c>
-      <c r="G76" s="5">
-        <v>3419.96</v>
-      </c>
-      <c r="H76" s="6">
-        <v>6</v>
-      </c>
-      <c r="I76" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="J76" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="K76" s="4"/>
-      <c r="L76" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="M76" s="4"/>
-      <c r="N76" s="4"/>
-    </row>
-    <row r="77" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="3">
-        <v>46203</v>
-      </c>
-      <c r="B77" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="C77" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="D77" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="E77" s="3">
-        <v>46268</v>
-      </c>
-      <c r="F77" s="5">
-        <v>5352.2</v>
-      </c>
-      <c r="G77" s="5">
-        <v>5352.2</v>
-      </c>
-      <c r="H77" s="6">
-        <v>6</v>
-      </c>
-      <c r="I77" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="J77" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="K77" s="4"/>
-      <c r="L77" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="M77" s="4"/>
-      <c r="N77" s="4"/>
-    </row>
-    <row r="78" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="3">
-        <v>46203</v>
-      </c>
-      <c r="B78" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="C78" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="D78" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="E78" s="3">
-        <v>46268</v>
-      </c>
-      <c r="F78" s="5">
-        <v>16880.7</v>
-      </c>
-      <c r="G78" s="5">
-        <v>16880.7</v>
-      </c>
-      <c r="H78" s="6">
-        <v>6</v>
-      </c>
-      <c r="I78" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="J78" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="K78" s="4"/>
-      <c r="L78" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="M78" s="4"/>
-      <c r="N78" s="4"/>
-    </row>
-    <row r="79" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="3">
-        <v>46198</v>
-      </c>
-      <c r="B79" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="C79" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="D79" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="E79" s="3">
-        <v>46268</v>
-      </c>
-      <c r="F79" s="5">
-        <v>3492.52</v>
-      </c>
-      <c r="G79" s="5">
-        <v>3492.52</v>
-      </c>
-      <c r="H79" s="6">
-        <v>6</v>
-      </c>
-      <c r="I79" s="4" t="s">
-        <v>169</v>
-      </c>
       <c r="J79" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="K79" s="4"/>
-      <c r="L79" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K79" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="L79" s="4"/>
+      <c r="M79" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="M79" s="4"/>
       <c r="N79" s="4"/>
-    </row>
-    <row r="80" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O79" s="4"/>
+    </row>
+    <row r="80" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="3">
-        <v>46227</v>
+        <v>46223</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C80" s="4" t="s">
         <v>209</v>
@@ -4221,561 +4285,498 @@
         <v>210</v>
       </c>
       <c r="E80" s="3">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="F80" s="5">
+        <v>11200</v>
+      </c>
+      <c r="G80" s="5">
+        <v>11200</v>
+      </c>
+      <c r="H80" s="3"/>
+      <c r="I80" s="6">
+        <v>6</v>
+      </c>
+      <c r="J80" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="K80" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L80" s="4"/>
+      <c r="M80" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="N80" s="4"/>
+      <c r="O80" s="4"/>
+    </row>
+    <row r="81" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="3">
+        <v>46224</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="E81" s="3">
+        <v>46273</v>
+      </c>
+      <c r="F81" s="5">
+        <v>2818.37</v>
+      </c>
+      <c r="G81" s="5">
+        <v>2818.37</v>
+      </c>
+      <c r="H81" s="3"/>
+      <c r="I81" s="6">
+        <v>6</v>
+      </c>
+      <c r="J81" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K81" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="L81" s="4"/>
+      <c r="M81" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="N81" s="4"/>
+      <c r="O81" s="4"/>
+    </row>
+    <row r="82" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="3">
+        <v>46253</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="E82" s="3">
+        <v>46274</v>
+      </c>
+      <c r="F82" s="5">
+        <v>10080</v>
+      </c>
+      <c r="G82" s="5">
+        <v>10080</v>
+      </c>
+      <c r="H82" s="3"/>
+      <c r="I82" s="6">
+        <v>5</v>
+      </c>
+      <c r="J82" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="K82" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L82" s="4"/>
+      <c r="M82" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="N82" s="4"/>
+      <c r="O82" s="4"/>
+    </row>
+    <row r="83" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="3">
+        <v>46226</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="E83" s="3">
+        <v>46275</v>
+      </c>
+      <c r="F83" s="5">
+        <v>1803.74</v>
+      </c>
+      <c r="G83" s="5">
+        <v>1803.74</v>
+      </c>
+      <c r="H83" s="3"/>
+      <c r="I83" s="6">
+        <v>4</v>
+      </c>
+      <c r="J83" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K83" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="L83" s="4"/>
+      <c r="M83" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="N83" s="4"/>
+      <c r="O83" s="4"/>
+    </row>
+    <row r="84" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="3">
+        <v>46219</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="E84" s="3">
+        <v>46275</v>
+      </c>
+      <c r="F84" s="5">
+        <v>3419.96</v>
+      </c>
+      <c r="G84" s="5">
+        <v>3419.96</v>
+      </c>
+      <c r="H84" s="3"/>
+      <c r="I84" s="6">
+        <v>4</v>
+      </c>
+      <c r="J84" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="K84" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="L84" s="4"/>
+      <c r="M84" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="N84" s="4"/>
+      <c r="O84" s="4"/>
+    </row>
+    <row r="85" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="3">
+        <v>46233</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="E85" s="3">
+        <v>46275</v>
+      </c>
+      <c r="F85" s="5">
+        <v>1836</v>
+      </c>
+      <c r="G85" s="5">
+        <v>1836</v>
+      </c>
+      <c r="H85" s="3"/>
+      <c r="I85" s="6">
+        <v>4</v>
+      </c>
+      <c r="J85" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K85" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="L85" s="4"/>
+      <c r="M85" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="N85" s="4"/>
+      <c r="O85" s="4"/>
+    </row>
+    <row r="86" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="3">
+        <v>46234</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="E86" s="3">
+        <v>46276</v>
+      </c>
+      <c r="F86" s="5">
+        <v>2970</v>
+      </c>
+      <c r="G86" s="5">
+        <v>2970</v>
+      </c>
+      <c r="H86" s="3"/>
+      <c r="I86" s="6">
+        <v>3</v>
+      </c>
+      <c r="J86" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K86" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="L86" s="4"/>
+      <c r="M86" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="N86" s="4"/>
+      <c r="O86" s="4"/>
+    </row>
+    <row r="87" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="3">
+        <v>46265</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="E87" s="3">
+        <v>46276</v>
+      </c>
+      <c r="F87" s="5">
+        <v>21103</v>
+      </c>
+      <c r="G87" s="5">
+        <v>21103</v>
+      </c>
+      <c r="H87" s="3"/>
+      <c r="I87" s="6">
+        <v>3</v>
+      </c>
+      <c r="J87" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="K87" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L87" s="4"/>
+      <c r="M87" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="N87" s="4"/>
+      <c r="O87" s="4"/>
+    </row>
+    <row r="88" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="3">
+        <v>46274</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="E88" s="3">
+        <v>46276</v>
+      </c>
+      <c r="F88" s="5">
+        <v>5796</v>
+      </c>
+      <c r="G88" s="5">
+        <v>5796</v>
+      </c>
+      <c r="H88" s="3"/>
+      <c r="I88" s="6">
+        <v>3</v>
+      </c>
+      <c r="J88" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="K88" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L88" s="4"/>
+      <c r="M88" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="N88" s="4"/>
+      <c r="O88" s="4"/>
+    </row>
+    <row r="89" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="3">
+        <v>46248</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="E89" s="3">
+        <v>46276</v>
+      </c>
+      <c r="F89" s="5">
+        <v>4791.2</v>
+      </c>
+      <c r="G89" s="5">
+        <v>4791.2</v>
+      </c>
+      <c r="H89" s="3"/>
+      <c r="I89" s="6">
+        <v>3</v>
+      </c>
+      <c r="J89" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="K89" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="L89" s="4"/>
+      <c r="M89" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="N89" s="4"/>
+      <c r="O89" s="4"/>
+    </row>
+    <row r="90" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="3">
+        <v>46220</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="E90" s="3">
+        <v>46276</v>
+      </c>
+      <c r="F90" s="5">
+        <v>9358.7000000000007</v>
+      </c>
+      <c r="G90" s="5">
+        <v>9358.7000000000007</v>
+      </c>
+      <c r="H90" s="3"/>
+      <c r="I90" s="6">
+        <v>3</v>
+      </c>
+      <c r="J90" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K90" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="L90" s="4"/>
+      <c r="M90" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="N90" s="4"/>
+      <c r="O90" s="4"/>
+    </row>
+    <row r="91" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="3">
+        <v>46227</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="E91" s="3">
+        <v>46276</v>
+      </c>
+      <c r="F91" s="5">
         <v>23168.6</v>
       </c>
-      <c r="G80" s="5">
+      <c r="G91" s="5">
         <v>23168.6</v>
       </c>
-      <c r="H80" s="6">
-        <v>5</v>
-      </c>
-      <c r="I80" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="J80" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K80" s="4"/>
-      <c r="L80" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="M80" s="4"/>
-      <c r="N80" s="4"/>
-    </row>
-    <row r="81" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="3">
-        <v>46234</v>
-      </c>
-      <c r="B81" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C81" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="D81" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="E81" s="3">
-        <v>46269</v>
-      </c>
-      <c r="F81" s="5">
-        <v>3837.6</v>
-      </c>
-      <c r="G81" s="5">
-        <v>3837.6</v>
-      </c>
-      <c r="H81" s="6">
-        <v>5</v>
-      </c>
-      <c r="I81" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="J81" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="K81" s="4"/>
-      <c r="L81" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="M81" s="4"/>
-      <c r="N81" s="4"/>
-    </row>
-    <row r="82" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="3">
+      <c r="H91" s="3"/>
+      <c r="I91" s="6">
+        <v>3</v>
+      </c>
+      <c r="J91" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="K91" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L91" s="4"/>
+      <c r="M91" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="N91" s="4"/>
+      <c r="O91" s="4"/>
+    </row>
+    <row r="92" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="3">
         <v>46220</v>
       </c>
-      <c r="B82" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="C82" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="D82" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="E82" s="3">
-        <v>46269</v>
-      </c>
-      <c r="F82" s="5">
-        <v>9358.7000000000007</v>
-      </c>
-      <c r="G82" s="5">
-        <v>9358.7000000000007</v>
-      </c>
-      <c r="H82" s="6">
-        <v>5</v>
-      </c>
-      <c r="I82" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J82" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="K82" s="4"/>
-      <c r="L82" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="M82" s="4"/>
-      <c r="N82" s="4"/>
-    </row>
-    <row r="83" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="3">
-        <v>46220</v>
-      </c>
-      <c r="B83" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C83" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="D83" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="E83" s="3">
-        <v>46270</v>
-      </c>
-      <c r="F83" s="5">
-        <v>5333.33</v>
-      </c>
-      <c r="G83" s="5">
-        <v>5333.33</v>
-      </c>
-      <c r="H83" s="6">
-        <v>4</v>
-      </c>
-      <c r="I83" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="J83" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="K83" s="4"/>
-      <c r="L83" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="M83" s="4"/>
-      <c r="N83" s="4"/>
-    </row>
-    <row r="84" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="3">
-        <v>46225</v>
-      </c>
-      <c r="B84" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="C84" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="D84" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="E84" s="3">
-        <v>46270</v>
-      </c>
-      <c r="F84" s="5">
-        <v>7551.88</v>
-      </c>
-      <c r="G84" s="5">
-        <v>11442.87</v>
-      </c>
-      <c r="H84" s="6">
-        <v>4</v>
-      </c>
-      <c r="I84" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="J84" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="K84" s="4"/>
-      <c r="L84" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="M84" s="4"/>
-      <c r="N84" s="4"/>
-    </row>
-    <row r="85" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="3">
-        <v>46189</v>
-      </c>
-      <c r="B85" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="C85" s="4" t="s">
+      <c r="B92" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="E92" s="3">
+        <v>46276</v>
+      </c>
+      <c r="F92" s="5">
+        <v>1760</v>
+      </c>
+      <c r="G92" s="5">
+        <v>1760</v>
+      </c>
+      <c r="H92" s="3"/>
+      <c r="I92" s="6">
+        <v>3</v>
+      </c>
+      <c r="J92" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="K92" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="D85" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="E85" s="3">
-        <v>46271</v>
-      </c>
-      <c r="F85" s="5">
-        <v>4582.76</v>
-      </c>
-      <c r="G85" s="5">
-        <v>4582.76</v>
-      </c>
-      <c r="H85" s="6">
-        <v>3</v>
-      </c>
-      <c r="I85" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="J85" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="K85" s="4"/>
-      <c r="L85" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="M85" s="4"/>
-      <c r="N85" s="4"/>
-    </row>
-    <row r="86" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="3">
-        <v>46227</v>
-      </c>
-      <c r="B86" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="C86" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="D86" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="E86" s="3">
-        <v>46272</v>
-      </c>
-      <c r="F86" s="5">
-        <v>4216.67</v>
-      </c>
-      <c r="G86" s="5">
-        <v>6389.24</v>
-      </c>
-      <c r="H86" s="6">
-        <v>2</v>
-      </c>
-      <c r="I86" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="J86" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="K86" s="4"/>
-      <c r="L86" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="M86" s="4"/>
-      <c r="N86" s="4"/>
-    </row>
-    <row r="87" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="3">
-        <v>46216</v>
-      </c>
-      <c r="B87" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="C87" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="D87" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="E87" s="3">
-        <v>46272</v>
-      </c>
-      <c r="F87" s="5">
-        <v>3530.76</v>
-      </c>
-      <c r="G87" s="5">
-        <v>3530.76</v>
-      </c>
-      <c r="H87" s="6">
-        <v>2</v>
-      </c>
-      <c r="I87" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="J87" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="K87" s="4"/>
-      <c r="L87" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="M87" s="4"/>
-      <c r="N87" s="4"/>
-    </row>
-    <row r="88" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="3">
-        <v>46232</v>
-      </c>
-      <c r="B88" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C88" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="D88" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="E88" s="3">
-        <v>46272</v>
-      </c>
-      <c r="F88" s="5">
-        <v>9716</v>
-      </c>
-      <c r="G88" s="5">
-        <v>9716</v>
-      </c>
-      <c r="H88" s="6">
-        <v>2</v>
-      </c>
-      <c r="I88" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="J88" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="K88" s="4"/>
-      <c r="L88" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="M88" s="4"/>
-      <c r="N88" s="4"/>
-    </row>
-    <row r="89" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="3">
-        <v>46223</v>
-      </c>
-      <c r="B89" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C89" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="D89" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="E89" s="3">
-        <v>46273</v>
-      </c>
-      <c r="F89" s="5">
-        <v>11200</v>
-      </c>
-      <c r="G89" s="5">
-        <v>11200</v>
-      </c>
-      <c r="H89" s="6">
-        <v>1</v>
-      </c>
-      <c r="I89" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="J89" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K89" s="4"/>
-      <c r="L89" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="M89" s="4"/>
-      <c r="N89" s="4"/>
-    </row>
-    <row r="90" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="3">
-        <v>46224</v>
-      </c>
-      <c r="B90" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="C90" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="D90" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="E90" s="3">
-        <v>46273</v>
-      </c>
-      <c r="F90" s="5">
-        <v>2818.37</v>
-      </c>
-      <c r="G90" s="5">
-        <v>2818.37</v>
-      </c>
-      <c r="H90" s="6">
-        <v>1</v>
-      </c>
-      <c r="I90" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="J90" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="K90" s="4"/>
-      <c r="L90" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="M90" s="4"/>
-      <c r="N90" s="4"/>
-    </row>
-    <row r="91" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="3">
-        <v>46231</v>
-      </c>
-      <c r="B91" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C91" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="D91" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="E91" s="3">
-        <v>46273</v>
-      </c>
-      <c r="F91" s="5">
-        <v>1366.66</v>
-      </c>
-      <c r="G91" s="5">
-        <v>1366.66</v>
-      </c>
-      <c r="H91" s="6">
-        <v>1</v>
-      </c>
-      <c r="I91" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="J91" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="K91" s="4"/>
-      <c r="L91" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="M91" s="4"/>
-      <c r="N91" s="4"/>
-    </row>
-    <row r="92" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="3">
-        <v>46245</v>
-      </c>
-      <c r="B92" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C92" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="D92" s="4" t="s">
+      <c r="L92" s="4"/>
+      <c r="M92" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="E92" s="3">
-        <v>46273</v>
-      </c>
-      <c r="F92" s="5">
-        <v>1624</v>
-      </c>
-      <c r="G92" s="5">
-        <v>2161.09</v>
-      </c>
-      <c r="H92" s="6">
-        <v>1</v>
-      </c>
-      <c r="I92" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="J92" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="K92" s="4"/>
-      <c r="L92" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="M92" s="4"/>
       <c r="N92" s="4"/>
-    </row>
-    <row r="93" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="3">
-        <v>46217</v>
-      </c>
-      <c r="B93" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C93" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="D93" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="E93" s="3">
-        <v>46273</v>
-      </c>
-      <c r="F93" s="5">
-        <v>3151.68</v>
-      </c>
-      <c r="G93" s="5">
-        <v>3151.68</v>
-      </c>
-      <c r="H93" s="6">
-        <v>1</v>
-      </c>
-      <c r="I93" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="J93" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="K93" s="4"/>
-      <c r="L93" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="M93" s="4"/>
-      <c r="N93" s="4"/>
-    </row>
-    <row r="94" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="3">
-        <v>46203</v>
-      </c>
-      <c r="B94" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C94" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="D94" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="E94" s="3">
-        <v>46273</v>
-      </c>
-      <c r="F94" s="5">
-        <v>875.25</v>
-      </c>
-      <c r="G94" s="5">
-        <v>875.25</v>
-      </c>
-      <c r="H94" s="6">
-        <v>1</v>
-      </c>
-      <c r="I94" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="J94" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="K94" s="4"/>
-      <c r="L94" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="M94" s="4"/>
-      <c r="N94" s="4"/>
+      <c r="O92" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
+++ b/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WINDOWS\Desktop\dados planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{599B15ED-0D5C-4E10-8CC9-49AC9BFB5493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13A32787-D520-48B3-ABE1-E0BA33938EFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="239">
   <si>
     <t>Dt.Emissão</t>
   </si>
@@ -462,21 +462,21 @@
     <t>00191125800002144590000003473568000002964317</t>
   </si>
   <si>
+    <t>BR MEDICAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>01005075.3</t>
+  </si>
+  <si>
+    <t>00195127000004480000000003473568000002981317</t>
+  </si>
+  <si>
     <t>PHARMACEUTICA DISTRIBUIDORA DE MAT. E MED. HOSPITA</t>
   </si>
   <si>
     <t>01005217.1BPBPBPBP</t>
   </si>
   <si>
-    <t>BR MEDICAMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>01005075.3</t>
-  </si>
-  <si>
-    <t>00195127000004480000000003473568000002981317</t>
-  </si>
-  <si>
     <t>01005217.2BP</t>
   </si>
   <si>
@@ -549,19 +549,13 @@
     <t>ALIANCA DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
   </si>
   <si>
-    <t>01006753.4</t>
+    <t>01006753.5</t>
   </si>
   <si>
     <t>PI</t>
   </si>
   <si>
-    <t>00191154200000860000000003473568000003128917</t>
-  </si>
-  <si>
-    <t>01006941.1</t>
-  </si>
-  <si>
-    <t>00191154200002818370000003473568000003141017</t>
+    <t>00197154900000860000000003473568000003129017</t>
   </si>
   <si>
     <t>01006941.2</t>
@@ -570,12 +564,6 @@
     <t>00195154900002818370000003473568000003141117</t>
   </si>
   <si>
-    <t>01006753.5</t>
-  </si>
-  <si>
-    <t>00197154900000860000000003473568000003129017</t>
-  </si>
-  <si>
     <t>JT COSTA COMERCIAL LTDA</t>
   </si>
   <si>
@@ -591,90 +579,81 @@
     <t>00191155600002818370000003473568000003141217</t>
   </si>
   <si>
+    <t>CIRURGICA MONTEBELLO LTDA</t>
+  </si>
+  <si>
+    <t>01006958.4</t>
+  </si>
+  <si>
+    <t>70791155900023168600001121205064100656764076</t>
+  </si>
+  <si>
+    <t>ALINE CERBINO - PA</t>
+  </si>
+  <si>
+    <t>CRISTALFARMA COMERCIO IMPORT E EXPORT LTDA</t>
+  </si>
+  <si>
+    <t>01006920.1</t>
+  </si>
+  <si>
+    <t>PA</t>
+  </si>
+  <si>
+    <t>70797156000011442870001121205064100656763979</t>
+  </si>
+  <si>
+    <t>01006976.1</t>
+  </si>
+  <si>
+    <t>BRADESCO</t>
+  </si>
+  <si>
+    <t>23791156200006389240435090000000114600304920</t>
+  </si>
+  <si>
+    <t>01007005.2</t>
+  </si>
+  <si>
+    <t>00193156200009716000000003473568000003145917</t>
+  </si>
+  <si>
+    <t>01006941.4</t>
+  </si>
+  <si>
+    <t>00194156300002818370000003473568000003141317</t>
+  </si>
+  <si>
+    <t>PLENA DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>01006922.1</t>
+  </si>
+  <si>
+    <t>70795156300011200000001121205064100656763870</t>
+  </si>
+  <si>
     <t>ATACAMED COMERCIO LTDA</t>
   </si>
   <si>
-    <t>01007024.2</t>
-  </si>
-  <si>
-    <t>34199155800001836001090002607618120992717000</t>
-  </si>
-  <si>
-    <t>CIRURGICA MONTEBELLO LTDA</t>
-  </si>
-  <si>
-    <t>01006958.4</t>
-  </si>
-  <si>
-    <t>70791155900023168600001121205064100656764076</t>
-  </si>
-  <si>
-    <t>ALINE CERBINO - PA</t>
-  </si>
-  <si>
-    <t>CRISTALFARMA COMERCIO IMPORT E EXPORT LTDA</t>
-  </si>
-  <si>
-    <t>01006920.1</t>
-  </si>
-  <si>
-    <t>PA</t>
-  </si>
-  <si>
-    <t>70797156000011442870001121205064100656763979</t>
-  </si>
-  <si>
-    <t>01006976.1</t>
-  </si>
-  <si>
-    <t>BRADESCO</t>
-  </si>
-  <si>
-    <t>23791156200006389240435090000000114600304920</t>
-  </si>
-  <si>
-    <t>01007005.2</t>
-  </si>
-  <si>
-    <t>00193156200009716000000003473568000003145917</t>
-  </si>
-  <si>
-    <t>VITAL DISTRIBUIDORA LTDA</t>
-  </si>
-  <si>
-    <t>01006823.5</t>
-  </si>
-  <si>
-    <t>70798156200003530760001121205064100656763334</t>
-  </si>
-  <si>
     <t>01006996.3</t>
   </si>
   <si>
     <t>00199156300001366660000003473568000003144717</t>
   </si>
   <si>
-    <t>PLENA DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>01006922.1</t>
-  </si>
-  <si>
-    <t>70795156300011200000001121205064100656763870</t>
-  </si>
-  <si>
-    <t>01006941.4</t>
-  </si>
-  <si>
-    <t>00194156300002818370000003473568000003141317</t>
-  </si>
-  <si>
     <t>01007187.1</t>
   </si>
   <si>
     <t>70791156400010080000001121205064100656766188</t>
   </si>
   <si>
+    <t>01007024.3</t>
+  </si>
+  <si>
+    <t>34199156500001836001090002607798120992717000</t>
+  </si>
+  <si>
     <t>RAMON ANTONIO NUNES DA SILVA</t>
   </si>
   <si>
@@ -684,82 +663,85 @@
     <t>00196156500001803740000003473568000003142417</t>
   </si>
   <si>
+    <t>01006958.5</t>
+  </si>
+  <si>
+    <t>70799156600023168600001121205064100656764084</t>
+  </si>
+  <si>
+    <t>01007023.1</t>
+  </si>
+  <si>
+    <t>70799156900005741360001121205064100656764415</t>
+  </si>
+  <si>
+    <t>AMAZONIA HOSPITALAR LTDA</t>
+  </si>
+  <si>
+    <t>01007105.1</t>
+  </si>
+  <si>
+    <t>MA</t>
+  </si>
+  <si>
+    <t>00194157000005443560000003473568000003154717</t>
+  </si>
+  <si>
+    <t>01006941.5</t>
+  </si>
+  <si>
+    <t>00191157000002818360000003473568000003141417</t>
+  </si>
+  <si>
+    <t>01007187.2</t>
+  </si>
+  <si>
+    <t>70791157100010080000001121205064100656766196</t>
+  </si>
+  <si>
+    <t>HOSPMED LTDA</t>
+  </si>
+  <si>
+    <t>01007167.1</t>
+  </si>
+  <si>
+    <t>34191157100001452601090002616868120992717000</t>
+  </si>
+  <si>
+    <t>01007005.3</t>
+  </si>
+  <si>
+    <t>00196157200009716000000003473568000003146017</t>
+  </si>
+  <si>
+    <t>ASPEN SERVICE COMERCIO LTDA</t>
+  </si>
+  <si>
+    <t>01006665.4</t>
+  </si>
+  <si>
+    <t>00192157200022750000000003473568000003126417</t>
+  </si>
+  <si>
+    <t>01007074.2</t>
+  </si>
+  <si>
+    <t>34192157200002930401090002611408120992717000</t>
+  </si>
+  <si>
+    <t>01007169.1</t>
+  </si>
+  <si>
+    <t>70794157200003809520001121205064100656765966</t>
+  </si>
+  <si>
     <t>M. A. M COMERCIO E DISTRIBUIDORA DE MEDICAMENTOS L</t>
   </si>
   <si>
-    <t>01006872.5</t>
-  </si>
-  <si>
-    <t>70798156500003419960001121205064100656763581</t>
-  </si>
-  <si>
-    <t>01007024.3</t>
-  </si>
-  <si>
-    <t>34199156500001836001090002607798120992717000</t>
-  </si>
-  <si>
-    <t>KELLEN - MA</t>
-  </si>
-  <si>
-    <t>DISTRIBUIDORA BELLFARMA LTDA</t>
-  </si>
-  <si>
-    <t>01007055.2</t>
-  </si>
-  <si>
-    <t>MA</t>
-  </si>
-  <si>
-    <t>34193156600002970001090002610748120992717000</t>
-  </si>
-  <si>
-    <t>MEDICAL MERCANTIL DE APARELHAGEM MEDICA LTDA</t>
-  </si>
-  <si>
-    <t>01007303.1</t>
-  </si>
-  <si>
-    <t>70791156600021103000001121205064100656767509</t>
-  </si>
-  <si>
-    <t>01007316.1</t>
-  </si>
-  <si>
-    <t>23792156600005796000435090000000131500304920</t>
-  </si>
-  <si>
-    <t>NATAL CLEAN DISTRIBUIDORA LTDA</t>
-  </si>
-  <si>
-    <t>01007145.1</t>
-  </si>
-  <si>
-    <t>70793156600004791200001121205064100656765586</t>
-  </si>
-  <si>
-    <t>MAIS SAUDE LTDA</t>
-  </si>
-  <si>
-    <t>01006873.5</t>
-  </si>
-  <si>
-    <t>34194156600009358701090002603408120992717000</t>
-  </si>
-  <si>
-    <t>01006958.5</t>
-  </si>
-  <si>
-    <t>70799156600023168600001121205064100656764084</t>
-  </si>
-  <si>
-    <t>AMAZONIA HOSPITALAR LTDA</t>
-  </si>
-  <si>
-    <t>01006915.5</t>
-  </si>
-  <si>
-    <t>23799156600001760000435090000000110300304920</t>
+    <t>01006872.6</t>
+  </si>
+  <si>
+    <t>70799157200003419960001121205064100656763599</t>
   </si>
 </sst>
 </file>
@@ -1189,7 +1171,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O92"/>
+  <dimension ref="A1:O91"/>
   <sheetFormatPr defaultColWidth="12.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.85546875" style="1" customWidth="1"/>
@@ -1281,7 +1263,7 @@
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="6">
-        <v>953</v>
+        <v>957</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>18</v>
@@ -1320,7 +1302,7 @@
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="6">
-        <v>933</v>
+        <v>937</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>18</v>
@@ -1359,7 +1341,7 @@
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="6">
-        <v>929</v>
+        <v>933</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>26</v>
@@ -1398,7 +1380,7 @@
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="6">
-        <v>923</v>
+        <v>927</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>18</v>
@@ -1437,7 +1419,7 @@
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="6">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>26</v>
@@ -1476,7 +1458,7 @@
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="6">
-        <v>915</v>
+        <v>919</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>26</v>
@@ -1515,7 +1497,7 @@
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="6">
-        <v>901</v>
+        <v>905</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>26</v>
@@ -1554,7 +1536,7 @@
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="6">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>18</v>
@@ -1593,7 +1575,7 @@
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="6">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>18</v>
@@ -1632,7 +1614,7 @@
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="6">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>18</v>
@@ -1671,7 +1653,7 @@
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="6">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>18</v>
@@ -1710,7 +1692,7 @@
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="6">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>18</v>
@@ -1749,7 +1731,7 @@
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="6">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>18</v>
@@ -1788,7 +1770,7 @@
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="6">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>18</v>
@@ -1827,7 +1809,7 @@
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="6">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>18</v>
@@ -1866,7 +1848,7 @@
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="6">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>18</v>
@@ -1905,7 +1887,7 @@
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="6">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>18</v>
@@ -1944,7 +1926,7 @@
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="6">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="J19" s="4" t="s">
         <v>18</v>
@@ -1983,7 +1965,7 @@
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="6">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>18</v>
@@ -2022,7 +2004,7 @@
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="6">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>18</v>
@@ -2061,7 +2043,7 @@
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="6">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="J22" s="4" t="s">
         <v>18</v>
@@ -2100,7 +2082,7 @@
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="6">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="J23" s="4" t="s">
         <v>18</v>
@@ -2139,7 +2121,7 @@
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="6">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="J24" s="4" t="s">
         <v>18</v>
@@ -2178,7 +2160,7 @@
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="6">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="J25" s="4" t="s">
         <v>26</v>
@@ -2217,7 +2199,7 @@
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="6">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="J26" s="4" t="s">
         <v>18</v>
@@ -2256,7 +2238,7 @@
       </c>
       <c r="H27" s="3"/>
       <c r="I27" s="6">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="J27" s="4" t="s">
         <v>26</v>
@@ -2295,7 +2277,7 @@
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="6">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="J28" s="4" t="s">
         <v>26</v>
@@ -2334,7 +2316,7 @@
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="6">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="J29" s="4" t="s">
         <v>18</v>
@@ -2373,7 +2355,7 @@
       </c>
       <c r="H30" s="3"/>
       <c r="I30" s="6">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="J30" s="4" t="s">
         <v>18</v>
@@ -2412,7 +2394,7 @@
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="6">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="J31" s="4" t="s">
         <v>18</v>
@@ -2451,7 +2433,7 @@
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="6">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="J32" s="4" t="s">
         <v>26</v>
@@ -2490,7 +2472,7 @@
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="6">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="J33" s="4" t="s">
         <v>18</v>
@@ -2529,7 +2511,7 @@
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="6">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="J34" s="4" t="s">
         <v>18</v>
@@ -2568,7 +2550,7 @@
       </c>
       <c r="H35" s="3"/>
       <c r="I35" s="6">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="J35" s="4" t="s">
         <v>18</v>
@@ -2607,7 +2589,7 @@
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="6">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="J36" s="4" t="s">
         <v>18</v>
@@ -2646,7 +2628,7 @@
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="6">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="J37" s="4" t="s">
         <v>18</v>
@@ -2685,7 +2667,7 @@
       </c>
       <c r="H38" s="3"/>
       <c r="I38" s="6">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="J38" s="4" t="s">
         <v>18</v>
@@ -2724,7 +2706,7 @@
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="6">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="J39" s="4" t="s">
         <v>18</v>
@@ -2763,7 +2745,7 @@
       </c>
       <c r="H40" s="3"/>
       <c r="I40" s="6">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="J40" s="4" t="s">
         <v>18</v>
@@ -2802,7 +2784,7 @@
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="6">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="J41" s="4" t="s">
         <v>18</v>
@@ -2841,7 +2823,7 @@
       </c>
       <c r="H42" s="3"/>
       <c r="I42" s="6">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="J42" s="4" t="s">
         <v>18</v>
@@ -2880,7 +2862,7 @@
       </c>
       <c r="H43" s="3"/>
       <c r="I43" s="6">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="J43" s="4" t="s">
         <v>18</v>
@@ -2919,7 +2901,7 @@
       </c>
       <c r="H44" s="3"/>
       <c r="I44" s="6">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="J44" s="4" t="s">
         <v>26</v>
@@ -2958,7 +2940,7 @@
       </c>
       <c r="H45" s="3"/>
       <c r="I45" s="6">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="J45" s="4" t="s">
         <v>26</v>
@@ -2997,7 +2979,7 @@
       </c>
       <c r="H46" s="3"/>
       <c r="I46" s="6">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="J46" s="4" t="s">
         <v>26</v>
@@ -3036,7 +3018,7 @@
       </c>
       <c r="H47" s="3"/>
       <c r="I47" s="6">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="J47" s="4" t="s">
         <v>26</v>
@@ -3075,7 +3057,7 @@
       </c>
       <c r="H48" s="3"/>
       <c r="I48" s="6">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="J48" s="4" t="s">
         <v>26</v>
@@ -3114,7 +3096,7 @@
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="6">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="J49" s="4" t="s">
         <v>26</v>
@@ -3153,7 +3135,7 @@
       </c>
       <c r="H50" s="3"/>
       <c r="I50" s="6">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="J50" s="4" t="s">
         <v>26</v>
@@ -3192,7 +3174,7 @@
       </c>
       <c r="H51" s="3"/>
       <c r="I51" s="6">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="J51" s="4" t="s">
         <v>26</v>
@@ -3231,7 +3213,7 @@
       </c>
       <c r="H52" s="3"/>
       <c r="I52" s="6">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="J52" s="4" t="s">
         <v>26</v>
@@ -3248,10 +3230,10 @@
     </row>
     <row r="53" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
-        <v>45959</v>
+        <v>45938</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>145</v>
@@ -3263,60 +3245,60 @@
         <v>45980</v>
       </c>
       <c r="F53" s="5">
-        <v>28666.44</v>
+        <v>4480</v>
       </c>
       <c r="G53" s="5">
-        <v>28666.44</v>
+        <v>4480</v>
       </c>
       <c r="H53" s="3"/>
       <c r="I53" s="6">
-        <v>299</v>
-      </c>
-      <c r="J53" s="4"/>
+        <v>303</v>
+      </c>
+      <c r="J53" s="4" t="s">
+        <v>26</v>
+      </c>
       <c r="K53" s="4" t="s">
-        <v>54</v>
+        <v>124</v>
       </c>
       <c r="L53" s="4"/>
-      <c r="M53" s="4"/>
+      <c r="M53" s="4" t="s">
+        <v>147</v>
+      </c>
       <c r="N53" s="4"/>
       <c r="O53" s="4"/>
     </row>
     <row r="54" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
-        <v>45938</v>
+        <v>45959</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E54" s="3">
         <v>45980</v>
       </c>
       <c r="F54" s="5">
-        <v>4480</v>
+        <v>28666.44</v>
       </c>
       <c r="G54" s="5">
-        <v>4480</v>
+        <v>28666.44</v>
       </c>
       <c r="H54" s="3"/>
       <c r="I54" s="6">
-        <v>299</v>
-      </c>
-      <c r="J54" s="4" t="s">
-        <v>26</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="J54" s="4"/>
       <c r="K54" s="4" t="s">
-        <v>124</v>
+        <v>54</v>
       </c>
       <c r="L54" s="4"/>
-      <c r="M54" s="4" t="s">
-        <v>149</v>
-      </c>
+      <c r="M54" s="4"/>
       <c r="N54" s="4"/>
       <c r="O54" s="4"/>
     </row>
@@ -3328,7 +3310,7 @@
         <v>135</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>150</v>
@@ -3344,7 +3326,7 @@
       </c>
       <c r="H55" s="3"/>
       <c r="I55" s="6">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="J55" s="4"/>
       <c r="K55" s="4" t="s">
@@ -3363,7 +3345,7 @@
         <v>121</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D56" s="4" t="s">
         <v>151</v>
@@ -3379,7 +3361,7 @@
       </c>
       <c r="H56" s="3"/>
       <c r="I56" s="6">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="J56" s="4"/>
       <c r="K56" s="4" t="s">
@@ -3398,7 +3380,7 @@
         <v>135</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>152</v>
@@ -3414,7 +3396,7 @@
       </c>
       <c r="H57" s="3"/>
       <c r="I57" s="6">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="J57" s="4"/>
       <c r="K57" s="4" t="s">
@@ -3449,7 +3431,7 @@
       </c>
       <c r="H58" s="3"/>
       <c r="I58" s="6">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="J58" s="4" t="s">
         <v>26</v>
@@ -3488,7 +3470,7 @@
       </c>
       <c r="H59" s="3"/>
       <c r="I59" s="6">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="J59" s="4" t="s">
         <v>26</v>
@@ -3527,7 +3509,7 @@
       </c>
       <c r="H60" s="3"/>
       <c r="I60" s="6">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="J60" s="4" t="s">
         <v>26</v>
@@ -3566,7 +3548,7 @@
       </c>
       <c r="H61" s="3"/>
       <c r="I61" s="6">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="J61" s="4" t="s">
         <v>18</v>
@@ -3589,7 +3571,7 @@
         <v>135</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>163</v>
@@ -3605,7 +3587,7 @@
       </c>
       <c r="H62" s="3"/>
       <c r="I62" s="6">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="J62" s="4"/>
       <c r="K62" s="4" t="s">
@@ -3624,7 +3606,7 @@
         <v>135</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D63" s="4" t="s">
         <v>164</v>
@@ -3640,7 +3622,7 @@
       </c>
       <c r="H63" s="3"/>
       <c r="I63" s="6">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="J63" s="4"/>
       <c r="K63" s="4" t="s">
@@ -3659,7 +3641,7 @@
         <v>135</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D64" s="4" t="s">
         <v>165</v>
@@ -3675,7 +3657,7 @@
       </c>
       <c r="H64" s="3"/>
       <c r="I64" s="6">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="J64" s="4"/>
       <c r="K64" s="4" t="s">
@@ -3710,7 +3692,7 @@
       </c>
       <c r="H65" s="3"/>
       <c r="I65" s="6">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="J65" s="4" t="s">
         <v>18</v>
@@ -3749,7 +3731,7 @@
       </c>
       <c r="H66" s="3"/>
       <c r="I66" s="6">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="J66" s="4" t="s">
         <v>170</v>
@@ -3778,7 +3760,7 @@
         <v>174</v>
       </c>
       <c r="E67" s="3">
-        <v>46252</v>
+        <v>46259</v>
       </c>
       <c r="F67" s="5">
         <v>860</v>
@@ -3788,7 +3770,7 @@
       </c>
       <c r="H67" s="3"/>
       <c r="I67" s="6">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J67" s="4" t="s">
         <v>26</v>
@@ -3817,7 +3799,7 @@
         <v>177</v>
       </c>
       <c r="E68" s="3">
-        <v>46252</v>
+        <v>46259</v>
       </c>
       <c r="F68" s="5">
         <v>2818.37</v>
@@ -3827,7 +3809,7 @@
       </c>
       <c r="H68" s="3"/>
       <c r="I68" s="6">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J68" s="4" t="s">
         <v>26</v>
@@ -3844,46 +3826,46 @@
     </row>
     <row r="69" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
-        <v>46224</v>
+        <v>46232</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>172</v>
+        <v>15</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E69" s="3">
-        <v>46259</v>
+        <v>46262</v>
       </c>
       <c r="F69" s="5">
-        <v>2818.37</v>
+        <v>9716</v>
       </c>
       <c r="G69" s="5">
-        <v>2818.37</v>
+        <v>18957.86</v>
       </c>
       <c r="H69" s="3"/>
       <c r="I69" s="6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J69" s="4" t="s">
         <v>26</v>
       </c>
       <c r="K69" s="4" t="s">
-        <v>175</v>
+        <v>39</v>
       </c>
       <c r="L69" s="4"/>
       <c r="M69" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N69" s="4"/>
       <c r="O69" s="4"/>
     </row>
     <row r="70" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
-        <v>46203</v>
+        <v>46224</v>
       </c>
       <c r="B70" s="4" t="s">
         <v>172</v>
@@ -3892,20 +3874,20 @@
         <v>173</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E70" s="3">
-        <v>46259</v>
+        <v>46266</v>
       </c>
       <c r="F70" s="5">
-        <v>860</v>
+        <v>2818.37</v>
       </c>
       <c r="G70" s="5">
-        <v>860</v>
+        <v>2818.37</v>
       </c>
       <c r="H70" s="3"/>
       <c r="I70" s="6">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J70" s="4" t="s">
         <v>26</v>
@@ -3915,198 +3897,198 @@
       </c>
       <c r="L70" s="4"/>
       <c r="M70" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N70" s="4"/>
       <c r="O70" s="4"/>
     </row>
     <row r="71" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3">
-        <v>46232</v>
+        <v>46227</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E71" s="3">
-        <v>46262</v>
+        <v>46269</v>
       </c>
       <c r="F71" s="5">
-        <v>9716</v>
+        <v>23168.6</v>
       </c>
       <c r="G71" s="5">
-        <v>18957.86</v>
+        <v>23168.6</v>
       </c>
       <c r="H71" s="3"/>
       <c r="I71" s="6">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J71" s="4" t="s">
-        <v>26</v>
+        <v>170</v>
       </c>
       <c r="K71" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="L71" s="4"/>
       <c r="M71" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N71" s="4"/>
       <c r="O71" s="4"/>
     </row>
     <row r="72" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="E72" s="3">
-        <v>46266</v>
+        <v>46270</v>
       </c>
       <c r="F72" s="5">
-        <v>2818.37</v>
+        <v>7551.88</v>
       </c>
       <c r="G72" s="5">
-        <v>2818.37</v>
+        <v>11442.87</v>
       </c>
       <c r="H72" s="3"/>
       <c r="I72" s="6">
         <v>13</v>
       </c>
       <c r="J72" s="4" t="s">
-        <v>26</v>
+        <v>170</v>
       </c>
       <c r="K72" s="4" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="L72" s="4"/>
       <c r="M72" s="4" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="N72" s="4"/>
       <c r="O72" s="4"/>
     </row>
     <row r="73" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="3">
-        <v>46233</v>
+        <v>46227</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>23</v>
+        <v>187</v>
       </c>
       <c r="C73" s="4" t="s">
         <v>188</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E73" s="3">
-        <v>46268</v>
+        <v>46272</v>
       </c>
       <c r="F73" s="5">
-        <v>1836</v>
+        <v>4216.67</v>
       </c>
       <c r="G73" s="5">
-        <v>1836</v>
+        <v>6389.24</v>
       </c>
       <c r="H73" s="3"/>
       <c r="I73" s="6">
         <v>11</v>
       </c>
       <c r="J73" s="4" t="s">
-        <v>18</v>
+        <v>193</v>
       </c>
       <c r="K73" s="4" t="s">
-        <v>71</v>
+        <v>190</v>
       </c>
       <c r="L73" s="4"/>
       <c r="M73" s="4" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="N73" s="4"/>
       <c r="O73" s="4"/>
     </row>
     <row r="74" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="3">
-        <v>46227</v>
+        <v>46232</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="E74" s="3">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="F74" s="5">
-        <v>23168.6</v>
+        <v>9716</v>
       </c>
       <c r="G74" s="5">
-        <v>23168.6</v>
+        <v>9716</v>
       </c>
       <c r="H74" s="3"/>
       <c r="I74" s="6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J74" s="4" t="s">
-        <v>170</v>
+        <v>26</v>
       </c>
       <c r="K74" s="4" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="L74" s="4"/>
       <c r="M74" s="4" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="N74" s="4"/>
       <c r="O74" s="4"/>
     </row>
     <row r="75" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="3">
-        <v>46225</v>
+        <v>46224</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>194</v>
+        <v>172</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>195</v>
+        <v>173</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E75" s="3">
-        <v>46270</v>
+        <v>46273</v>
       </c>
       <c r="F75" s="5">
-        <v>7551.88</v>
+        <v>2818.37</v>
       </c>
       <c r="G75" s="5">
-        <v>11442.87</v>
+        <v>2818.37</v>
       </c>
       <c r="H75" s="3"/>
       <c r="I75" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J75" s="4" t="s">
-        <v>170</v>
+        <v>26</v>
       </c>
       <c r="K75" s="4" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="L75" s="4"/>
       <c r="M75" s="4" t="s">
@@ -4117,35 +4099,35 @@
     </row>
     <row r="76" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="3">
-        <v>46227</v>
+        <v>46223</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>194</v>
+        <v>45</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E76" s="3">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="F76" s="5">
-        <v>4216.67</v>
+        <v>11200</v>
       </c>
       <c r="G76" s="5">
-        <v>6389.24</v>
+        <v>11200</v>
       </c>
       <c r="H76" s="3"/>
       <c r="I76" s="6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J76" s="4" t="s">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="K76" s="4" t="s">
-        <v>197</v>
+        <v>27</v>
       </c>
       <c r="L76" s="4"/>
       <c r="M76" s="4" t="s">
@@ -4156,74 +4138,74 @@
     </row>
     <row r="77" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="3">
-        <v>46232</v>
+        <v>46231</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>183</v>
+        <v>202</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E77" s="3">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="F77" s="5">
-        <v>9716</v>
+        <v>1366.66</v>
       </c>
       <c r="G77" s="5">
-        <v>9716</v>
+        <v>1366.66</v>
       </c>
       <c r="H77" s="3"/>
       <c r="I77" s="6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J77" s="4" t="s">
         <v>26</v>
       </c>
       <c r="K77" s="4" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="L77" s="4"/>
       <c r="M77" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N77" s="4"/>
       <c r="O77" s="4"/>
     </row>
     <row r="78" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="3">
-        <v>46216</v>
+        <v>46253</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>172</v>
+        <v>45</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
       <c r="D78" s="4" t="s">
         <v>205</v>
       </c>
       <c r="E78" s="3">
-        <v>46272</v>
+        <v>46274</v>
       </c>
       <c r="F78" s="5">
-        <v>3530.76</v>
+        <v>10080</v>
       </c>
       <c r="G78" s="5">
-        <v>3530.76</v>
+        <v>10080</v>
       </c>
       <c r="H78" s="3"/>
       <c r="I78" s="6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J78" s="4" t="s">
         <v>170</v>
       </c>
       <c r="K78" s="4" t="s">
-        <v>175</v>
+        <v>27</v>
       </c>
       <c r="L78" s="4"/>
       <c r="M78" s="4" t="s">
@@ -4234,32 +4216,32 @@
     </row>
     <row r="79" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="3">
-        <v>46231</v>
+        <v>46233</v>
       </c>
       <c r="B79" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="D79" s="4" t="s">
         <v>207</v>
       </c>
       <c r="E79" s="3">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="F79" s="5">
-        <v>1366.66</v>
+        <v>1836</v>
       </c>
       <c r="G79" s="5">
-        <v>1366.66</v>
+        <v>1836</v>
       </c>
       <c r="H79" s="3"/>
       <c r="I79" s="6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J79" s="4" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="K79" s="4" t="s">
         <v>71</v>
@@ -4273,10 +4255,10 @@
     </row>
     <row r="80" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="3">
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="C80" s="4" t="s">
         <v>209</v>
@@ -4285,23 +4267,23 @@
         <v>210</v>
       </c>
       <c r="E80" s="3">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="F80" s="5">
-        <v>11200</v>
+        <v>1803.74</v>
       </c>
       <c r="G80" s="5">
-        <v>11200</v>
+        <v>1803.74</v>
       </c>
       <c r="H80" s="3"/>
       <c r="I80" s="6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J80" s="4" t="s">
-        <v>170</v>
+        <v>26</v>
       </c>
       <c r="K80" s="4" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="L80" s="4"/>
       <c r="M80" s="4" t="s">
@@ -4312,35 +4294,35 @@
     </row>
     <row r="81" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="3">
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>172</v>
+        <v>45</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D81" s="4" t="s">
         <v>212</v>
       </c>
       <c r="E81" s="3">
-        <v>46273</v>
+        <v>46276</v>
       </c>
       <c r="F81" s="5">
-        <v>2818.37</v>
+        <v>23168.6</v>
       </c>
       <c r="G81" s="5">
-        <v>2818.37</v>
+        <v>23168.6</v>
       </c>
       <c r="H81" s="3"/>
       <c r="I81" s="6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J81" s="4" t="s">
-        <v>26</v>
+        <v>170</v>
       </c>
       <c r="K81" s="4" t="s">
-        <v>175</v>
+        <v>27</v>
       </c>
       <c r="L81" s="4"/>
       <c r="M81" s="4" t="s">
@@ -4351,35 +4333,35 @@
     </row>
     <row r="82" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3">
-        <v>46253</v>
+        <v>46234</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>45</v>
+        <v>187</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D82" s="4" t="s">
         <v>214</v>
       </c>
       <c r="E82" s="3">
-        <v>46274</v>
+        <v>46279</v>
       </c>
       <c r="F82" s="5">
-        <v>10080</v>
+        <v>3789.09</v>
       </c>
       <c r="G82" s="5">
-        <v>10080</v>
+        <v>5741.36</v>
       </c>
       <c r="H82" s="3"/>
       <c r="I82" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J82" s="4" t="s">
         <v>170</v>
       </c>
       <c r="K82" s="4" t="s">
-        <v>27</v>
+        <v>190</v>
       </c>
       <c r="L82" s="4"/>
       <c r="M82" s="4" t="s">
@@ -4390,10 +4372,10 @@
     </row>
     <row r="83" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="3">
-        <v>46226</v>
+        <v>46252</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>23</v>
+        <v>172</v>
       </c>
       <c r="C83" s="4" t="s">
         <v>216</v>
@@ -4402,59 +4384,59 @@
         <v>217</v>
       </c>
       <c r="E83" s="3">
-        <v>46275</v>
+        <v>46280</v>
       </c>
       <c r="F83" s="5">
-        <v>1803.74</v>
+        <v>5443.56</v>
       </c>
       <c r="G83" s="5">
-        <v>1803.74</v>
+        <v>5443.56</v>
       </c>
       <c r="H83" s="3"/>
       <c r="I83" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J83" s="4" t="s">
         <v>26</v>
       </c>
       <c r="K83" s="4" t="s">
-        <v>71</v>
+        <v>218</v>
       </c>
       <c r="L83" s="4"/>
       <c r="M83" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N83" s="4"/>
       <c r="O83" s="4"/>
     </row>
     <row r="84" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="3">
-        <v>46219</v>
+        <v>46224</v>
       </c>
       <c r="B84" s="4" t="s">
         <v>172</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>219</v>
+        <v>173</v>
       </c>
       <c r="D84" s="4" t="s">
         <v>220</v>
       </c>
       <c r="E84" s="3">
-        <v>46275</v>
+        <v>46280</v>
       </c>
       <c r="F84" s="5">
-        <v>3419.96</v>
+        <v>2818.36</v>
       </c>
       <c r="G84" s="5">
-        <v>3419.96</v>
+        <v>2818.36</v>
       </c>
       <c r="H84" s="3"/>
       <c r="I84" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J84" s="4" t="s">
-        <v>170</v>
+        <v>26</v>
       </c>
       <c r="K84" s="4" t="s">
         <v>175</v>
@@ -4468,35 +4450,35 @@
     </row>
     <row r="85" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="3">
-        <v>46233</v>
+        <v>46253</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D85" s="4" t="s">
         <v>222</v>
       </c>
       <c r="E85" s="3">
-        <v>46275</v>
+        <v>46281</v>
       </c>
       <c r="F85" s="5">
-        <v>1836</v>
+        <v>10080</v>
       </c>
       <c r="G85" s="5">
-        <v>1836</v>
+        <v>10080</v>
       </c>
       <c r="H85" s="3"/>
       <c r="I85" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J85" s="4" t="s">
-        <v>18</v>
+        <v>170</v>
       </c>
       <c r="K85" s="4" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="L85" s="4"/>
       <c r="M85" s="4" t="s">
@@ -4507,276 +4489,237 @@
     </row>
     <row r="86" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="3">
-        <v>46234</v>
+        <v>46253</v>
       </c>
       <c r="B86" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C86" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="C86" s="4" t="s">
+      <c r="D86" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="D86" s="4" t="s">
-        <v>226</v>
-      </c>
       <c r="E86" s="3">
-        <v>46276</v>
+        <v>46281</v>
       </c>
       <c r="F86" s="5">
-        <v>2970</v>
+        <v>1452.6</v>
       </c>
       <c r="G86" s="5">
-        <v>2970</v>
+        <v>1452.6</v>
       </c>
       <c r="H86" s="3"/>
       <c r="I86" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J86" s="4" t="s">
         <v>18</v>
       </c>
       <c r="K86" s="4" t="s">
-        <v>227</v>
+        <v>175</v>
       </c>
       <c r="L86" s="4"/>
       <c r="M86" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="N86" s="4"/>
       <c r="O86" s="4"/>
     </row>
     <row r="87" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="3">
-        <v>46265</v>
+        <v>46232</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>229</v>
+        <v>179</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E87" s="3">
-        <v>46276</v>
+        <v>46282</v>
       </c>
       <c r="F87" s="5">
-        <v>21103</v>
+        <v>9716</v>
       </c>
       <c r="G87" s="5">
-        <v>21103</v>
+        <v>9716</v>
       </c>
       <c r="H87" s="3"/>
       <c r="I87" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J87" s="4" t="s">
-        <v>170</v>
+        <v>26</v>
       </c>
       <c r="K87" s="4" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="L87" s="4"/>
       <c r="M87" s="4" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="N87" s="4"/>
       <c r="O87" s="4"/>
     </row>
     <row r="88" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="3">
-        <v>46274</v>
+        <v>46192</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="C88" s="4" t="s">
         <v>229</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E88" s="3">
-        <v>46276</v>
+        <v>46282</v>
       </c>
       <c r="F88" s="5">
-        <v>5796</v>
+        <v>22750</v>
       </c>
       <c r="G88" s="5">
-        <v>5796</v>
+        <v>22750</v>
       </c>
       <c r="H88" s="3"/>
       <c r="I88" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J88" s="4" t="s">
-        <v>200</v>
+        <v>26</v>
       </c>
       <c r="K88" s="4" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="L88" s="4"/>
       <c r="M88" s="4" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="N88" s="4"/>
       <c r="O88" s="4"/>
     </row>
     <row r="89" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="3">
-        <v>46248</v>
+        <v>46237</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>234</v>
+        <v>166</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="E89" s="3">
-        <v>46276</v>
+        <v>46282</v>
       </c>
       <c r="F89" s="5">
-        <v>4791.2</v>
+        <v>2930.4</v>
       </c>
       <c r="G89" s="5">
-        <v>4791.2</v>
+        <v>2930.4</v>
       </c>
       <c r="H89" s="3"/>
       <c r="I89" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J89" s="4" t="s">
-        <v>170</v>
+        <v>18</v>
       </c>
       <c r="K89" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="L89" s="4"/>
       <c r="M89" s="4" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="N89" s="4"/>
       <c r="O89" s="4"/>
     </row>
     <row r="90" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="3">
-        <v>46220</v>
+        <v>46252</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>172</v>
+        <v>23</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>237</v>
+        <v>166</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="E90" s="3">
-        <v>46276</v>
+        <v>46282</v>
       </c>
       <c r="F90" s="5">
-        <v>9358.7000000000007</v>
+        <v>3809.52</v>
       </c>
       <c r="G90" s="5">
-        <v>9358.7000000000007</v>
+        <v>3809.52</v>
       </c>
       <c r="H90" s="3"/>
       <c r="I90" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J90" s="4" t="s">
-        <v>18</v>
+        <v>170</v>
       </c>
       <c r="K90" s="4" t="s">
-        <v>175</v>
+        <v>71</v>
       </c>
       <c r="L90" s="4"/>
       <c r="M90" s="4" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="N90" s="4"/>
       <c r="O90" s="4"/>
     </row>
     <row r="91" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="3">
-        <v>46227</v>
+        <v>46219</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>45</v>
+        <v>172</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>191</v>
+        <v>236</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="E91" s="3">
-        <v>46276</v>
+        <v>46282</v>
       </c>
       <c r="F91" s="5">
-        <v>23168.6</v>
+        <v>3419.96</v>
       </c>
       <c r="G91" s="5">
-        <v>23168.6</v>
+        <v>3419.96</v>
       </c>
       <c r="H91" s="3"/>
       <c r="I91" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J91" s="4" t="s">
         <v>170</v>
       </c>
       <c r="K91" s="4" t="s">
-        <v>27</v>
+        <v>175</v>
       </c>
       <c r="L91" s="4"/>
       <c r="M91" s="4" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="N91" s="4"/>
       <c r="O91" s="4"/>
-    </row>
-    <row r="92" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="3">
-        <v>46220</v>
-      </c>
-      <c r="B92" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="C92" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="D92" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="E92" s="3">
-        <v>46276</v>
-      </c>
-      <c r="F92" s="5">
-        <v>1760</v>
-      </c>
-      <c r="G92" s="5">
-        <v>1760</v>
-      </c>
-      <c r="H92" s="3"/>
-      <c r="I92" s="6">
-        <v>3</v>
-      </c>
-      <c r="J92" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="K92" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="L92" s="4"/>
-      <c r="M92" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="N92" s="4"/>
-      <c r="O92" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
+++ b/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
@@ -1,31 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WINDOWS\Desktop\dados planilhas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13A32787-D520-48B3-ABE1-E0BA33938EFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView activeTab="0" showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true"/>
   </bookViews>
   <sheets>
     <sheet name="XLS_Grid_LANCAMENTO A RECEBER" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <calcPr refMode="A1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="259">
   <si>
     <t>Dt.Emissão</t>
   </si>
@@ -633,36 +621,12 @@
     <t>70795156300011200000001121205064100656763870</t>
   </si>
   <si>
-    <t>ATACAMED COMERCIO LTDA</t>
-  </si>
-  <si>
-    <t>01006996.3</t>
-  </si>
-  <si>
-    <t>00199156300001366660000003473568000003144717</t>
-  </si>
-  <si>
     <t>01007187.1</t>
   </si>
   <si>
     <t>70791156400010080000001121205064100656766188</t>
   </si>
   <si>
-    <t>01007024.3</t>
-  </si>
-  <si>
-    <t>34199156500001836001090002607798120992717000</t>
-  </si>
-  <si>
-    <t>RAMON ANTONIO NUNES DA SILVA</t>
-  </si>
-  <si>
-    <t>01006944.4</t>
-  </si>
-  <si>
-    <t>00196156500001803740000003473568000003142417</t>
-  </si>
-  <si>
     <t>01006958.5</t>
   </si>
   <si>
@@ -675,102 +639,187 @@
     <t>70799156900005741360001121205064100656764415</t>
   </si>
   <si>
+    <t>01006941.5</t>
+  </si>
+  <si>
+    <t>00191157000002818360000003473568000003141417</t>
+  </si>
+  <si>
+    <t>01007187.2</t>
+  </si>
+  <si>
+    <t>70791157100010080000001121205064100656766196</t>
+  </si>
+  <si>
+    <t>M. A. M COMERCIO E DISTRIBUIDORA DE MEDICAMENTOS L</t>
+  </si>
+  <si>
+    <t>01006872.6</t>
+  </si>
+  <si>
+    <t>70799157200003419960001121205064100656763599</t>
+  </si>
+  <si>
+    <t>01007005.3</t>
+  </si>
+  <si>
+    <t>00196157200009716000000003473568000003146017</t>
+  </si>
+  <si>
+    <t>ASPEN SERVICE COMERCIO LTDA</t>
+  </si>
+  <si>
+    <t>01006665.4</t>
+  </si>
+  <si>
+    <t>00192157200022750000000003473568000003126417</t>
+  </si>
+  <si>
+    <t>01006922.2</t>
+  </si>
+  <si>
+    <t>70792157300011200000001121205064100656763888</t>
+  </si>
+  <si>
+    <t>01006939.3</t>
+  </si>
+  <si>
+    <t>00194157300005860800000003473568000003140517</t>
+  </si>
+  <si>
+    <t>01007197.1</t>
+  </si>
+  <si>
+    <t>23791157300001172160435090000000124600304920</t>
+  </si>
+  <si>
+    <t>01006958.6</t>
+  </si>
+  <si>
+    <t>70798157300023168600001121205064100656764092</t>
+  </si>
+  <si>
+    <t>01006957.2</t>
+  </si>
+  <si>
+    <t>70792157400010666670001121205064100656763953</t>
+  </si>
+  <si>
+    <t>01006999.1</t>
+  </si>
+  <si>
+    <t>70799157400006500000001121205064100656764282</t>
+  </si>
+  <si>
+    <t>01007020.1</t>
+  </si>
+  <si>
+    <t>70799157400004950170001121205064100656764449</t>
+  </si>
+  <si>
+    <t>01006920.2</t>
+  </si>
+  <si>
+    <t>70794157500007551880001121205064100656763987</t>
+  </si>
+  <si>
+    <t>01007125.4</t>
+  </si>
+  <si>
+    <t>70791157600004320000001121205064100656765123</t>
+  </si>
+  <si>
+    <t>01007301.1</t>
+  </si>
+  <si>
+    <t>00192157700018600000000003473568000003161317</t>
+  </si>
+  <si>
     <t>AMAZONIA HOSPITALAR LTDA</t>
   </si>
   <si>
-    <t>01007105.1</t>
+    <t>01007105.2</t>
   </si>
   <si>
     <t>MA</t>
   </si>
   <si>
-    <t>00194157000005443560000003473568000003154717</t>
-  </si>
-  <si>
-    <t>01006941.5</t>
-  </si>
-  <si>
-    <t>00191157000002818360000003473568000003141417</t>
-  </si>
-  <si>
-    <t>01007187.2</t>
-  </si>
-  <si>
-    <t>70791157100010080000001121205064100656766196</t>
+    <t>00199157700005443560000003473568000003154817</t>
+  </si>
+  <si>
+    <t>01006976.2</t>
+  </si>
+  <si>
+    <t>23791157700004216670435090000000114700304920</t>
   </si>
   <si>
     <t>HOSPMED LTDA</t>
   </si>
   <si>
-    <t>01007167.1</t>
-  </si>
-  <si>
-    <t>34191157100001452601090002616868120992717000</t>
-  </si>
-  <si>
-    <t>01007005.3</t>
-  </si>
-  <si>
-    <t>00196157200009716000000003473568000003146017</t>
-  </si>
-  <si>
-    <t>ASPEN SERVICE COMERCIO LTDA</t>
-  </si>
-  <si>
-    <t>01006665.4</t>
-  </si>
-  <si>
-    <t>00192157200022750000000003473568000003126417</t>
-  </si>
-  <si>
-    <t>01007074.2</t>
-  </si>
-  <si>
-    <t>34192157200002930401090002611408120992717000</t>
-  </si>
-  <si>
-    <t>01007169.1</t>
-  </si>
-  <si>
-    <t>70794157200003809520001121205064100656765966</t>
-  </si>
-  <si>
-    <t>M. A. M COMERCIO E DISTRIBUIDORA DE MEDICAMENTOS L</t>
-  </si>
-  <si>
-    <t>01006872.6</t>
-  </si>
-  <si>
-    <t>70799157200003419960001121205064100656763599</t>
+    <t>01007167.2</t>
+  </si>
+  <si>
+    <t>34194157800001452601090002616948120992717000</t>
+  </si>
+  <si>
+    <t>01007187.3</t>
+  </si>
+  <si>
+    <t>70793157800010080000001121205064100656766204</t>
+  </si>
+  <si>
+    <t>DROGUISTA CEARENSE LTDA</t>
+  </si>
+  <si>
+    <t>01007171.2</t>
+  </si>
+  <si>
+    <t>70794157800003640000001121205064100656766162</t>
+  </si>
+  <si>
+    <t>01007175.2</t>
+  </si>
+  <si>
+    <t>34193157800001660331090002618768120992717000</t>
+  </si>
+  <si>
+    <t>COBERMED COMERCIO DE MATERIAIS MEDICOS LTDA</t>
+  </si>
+  <si>
+    <t>01007194.1</t>
+  </si>
+  <si>
+    <t>70797157900006265000001121205064100656766642</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="###,###,##0.00"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt formatCode="dd/MM/yyyy" numFmtId="164"/>
+    <numFmt formatCode="###,###,##0.00" numFmtId="165"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
       <charset val="1"/>
     </font>
     <font>
+      <color rgb="FF000000"/>
       <sz val="8"/>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
       <charset val="1"/>
     </font>
     <font>
+      <color rgb="FF000000"/>
       <sz val="8"/>
-      <color rgb="FF000000"/>
       <name val="Segoe UI"/>
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -789,8 +838,14 @@
         <bgColor rgb="FF7EA6D1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0F0F0"/>
+        <bgColor rgb="FFF0F0F0"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -813,386 +868,124 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFA0A0A0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFA0A0A0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFA0A0A0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFA0A0A0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFA0A0A0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFA0A0A0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFA0A0A0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFA0A0A0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+  <cellXfs count="11">
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" shrinkToFit="false" wrapText="false"/>
+      <protection hidden="false" locked="true"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="164" xfId="0">
+      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="165" xfId="0">
+      <alignment horizontal="right" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0">
+      <alignment horizontal="right" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="2" fillId="4" fontId="1" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="3" fillId="4" fontId="1" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="4" fontId="1" numFmtId="165" xfId="0">
+      <alignment horizontal="right" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="4" fillId="4" fontId="1" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-  </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="0E2841"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="156082"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="E97132"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="196B24"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="A02B93"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="4EA72E"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="467886"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="96607D"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O91"/>
-  <sheetFormatPr defaultColWidth="12.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="true" summaryRight="true"/>
+  </sheetPr>
+  <dimension ref="A1:O102"/>
+  <sheetFormatPr defaultColWidth="12.140625" customHeight="true" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.28515625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="30.28515625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="24.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="27.28515625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="28.140625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="9.140625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="26.28515625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="3.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="43.42578125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="60.5703125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="26.28515625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="43.42578125" style="1" customWidth="1"/>
-    <col min="16" max="16384" width="12.140625" style="1"/>
+    <col max="1" min="1" style="1" width="11.85546875" customWidth="true"/>
+    <col max="2" min="2" style="1" width="22.28515625" customWidth="true"/>
+    <col max="3" min="3" style="1" width="30.28515625" customWidth="true"/>
+    <col max="4" min="4" style="1" width="12.85546875" customWidth="true"/>
+    <col max="5" min="5" style="1" width="24.7109375" customWidth="true"/>
+    <col max="6" min="6" style="1" width="9.140625" customWidth="true"/>
+    <col max="7" min="7" style="1" width="27.28515625" customWidth="true"/>
+    <col max="8" min="8" style="1" width="28.140625" customWidth="true"/>
+    <col max="9" min="9" style="1" width="9.140625" customWidth="true"/>
+    <col max="10" min="10" style="1" width="26.28515625" customWidth="true"/>
+    <col max="11" min="11" style="1" width="3.7109375" customWidth="true"/>
+    <col max="12" min="12" style="1" width="43.42578125" customWidth="true"/>
+    <col max="13" min="13" style="1" width="60.5703125" customWidth="true"/>
+    <col max="14" min="14" style="1" width="26.28515625" customWidth="true"/>
+    <col max="15" min="15" style="1" width="43.42578125" customWidth="true"/>
+    <col max="16384" min="16" style="1" width="12.140625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" customHeight="true" ht="27" customFormat="true" s="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1239,8 +1032,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
+    <row r="2" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A2" s="3" t="n">
         <v>45296</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -1252,18 +1045,18 @@
       <c r="D2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="3" t="n">
         <v>45326</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2" s="5" t="n">
         <v>5418</v>
       </c>
-      <c r="G2" s="5">
-        <v>9391.7800000000007</v>
+      <c r="G2" s="5" t="n">
+        <v>9391.78</v>
       </c>
       <c r="H2" s="3"/>
-      <c r="I2" s="6">
-        <v>957</v>
+      <c r="I2" s="6" t="n">
+        <v>964</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>18</v>
@@ -1278,8 +1071,8 @@
       <c r="N2" s="4"/>
       <c r="O2" s="4"/>
     </row>
-    <row r="3" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3">
+    <row r="3" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A3" s="3" t="n">
         <v>45296</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -1291,18 +1084,18 @@
       <c r="D3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="3" t="n">
         <v>45346</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3" s="5" t="n">
         <v>5418</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="5" t="n">
         <v>5418</v>
       </c>
       <c r="H3" s="3"/>
-      <c r="I3" s="6">
-        <v>937</v>
+      <c r="I3" s="6" t="n">
+        <v>944</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>18</v>
@@ -1317,8 +1110,8 @@
       <c r="N3" s="4"/>
       <c r="O3" s="4"/>
     </row>
-    <row r="4" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
+    <row r="4" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A4" s="3" t="n">
         <v>45322</v>
       </c>
       <c r="B4" s="4" t="s">
@@ -1330,18 +1123,18 @@
       <c r="D4" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="3" t="n">
         <v>45350</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="5" t="n">
         <v>816</v>
       </c>
-      <c r="G4" s="5">
-        <v>1264.8699999999999</v>
+      <c r="G4" s="5" t="n">
+        <v>1264.87</v>
       </c>
       <c r="H4" s="3"/>
-      <c r="I4" s="6">
-        <v>933</v>
+      <c r="I4" s="6" t="n">
+        <v>940</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>26</v>
@@ -1356,8 +1149,8 @@
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
     </row>
-    <row r="5" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3">
+    <row r="5" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A5" s="3" t="n">
         <v>45296</v>
       </c>
       <c r="B5" s="4" t="s">
@@ -1369,18 +1162,18 @@
       <c r="D5" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="3" t="n">
         <v>45356</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="5" t="n">
         <v>5418</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="5" t="n">
         <v>5418</v>
       </c>
       <c r="H5" s="3"/>
-      <c r="I5" s="6">
-        <v>927</v>
+      <c r="I5" s="6" t="n">
+        <v>934</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>18</v>
@@ -1395,8 +1188,8 @@
       <c r="N5" s="4"/>
       <c r="O5" s="4"/>
     </row>
-    <row r="6" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3">
+    <row r="6" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A6" s="3" t="n">
         <v>45306</v>
       </c>
       <c r="B6" s="4" t="s">
@@ -1408,18 +1201,18 @@
       <c r="D6" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="3" t="n">
         <v>45362</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="5" t="n">
         <v>384</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="5" t="n">
         <v>384</v>
       </c>
       <c r="H6" s="3"/>
-      <c r="I6" s="6">
-        <v>921</v>
+      <c r="I6" s="6" t="n">
+        <v>928</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>26</v>
@@ -1434,8 +1227,8 @@
       <c r="N6" s="4"/>
       <c r="O6" s="4"/>
     </row>
-    <row r="7" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3">
+    <row r="7" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A7" s="3" t="n">
         <v>45322</v>
       </c>
       <c r="B7" s="4" t="s">
@@ -1447,18 +1240,18 @@
       <c r="D7" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="3" t="n">
         <v>45364</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="5" t="n">
         <v>816</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="5" t="n">
         <v>816</v>
       </c>
       <c r="H7" s="3"/>
-      <c r="I7" s="6">
-        <v>919</v>
+      <c r="I7" s="6" t="n">
+        <v>926</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>26</v>
@@ -1473,8 +1266,8 @@
       <c r="N7" s="4"/>
       <c r="O7" s="4"/>
     </row>
-    <row r="8" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3">
+    <row r="8" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A8" s="3" t="n">
         <v>45322</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -1486,18 +1279,18 @@
       <c r="D8" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="3" t="n">
         <v>45378</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8" s="5" t="n">
         <v>816</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G8" s="5" t="n">
         <v>816</v>
       </c>
       <c r="H8" s="3"/>
-      <c r="I8" s="6">
-        <v>905</v>
+      <c r="I8" s="6" t="n">
+        <v>912</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>26</v>
@@ -1512,8 +1305,8 @@
       <c r="N8" s="4"/>
       <c r="O8" s="4"/>
     </row>
-    <row r="9" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3">
+    <row r="9" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A9" s="3" t="n">
         <v>45433</v>
       </c>
       <c r="B9" s="4" t="s">
@@ -1525,18 +1318,18 @@
       <c r="D9" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="3" t="n">
         <v>45463</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9" s="5" t="n">
         <v>873.6</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G9" s="5" t="n">
         <v>1674.52</v>
       </c>
       <c r="H9" s="3"/>
-      <c r="I9" s="6">
-        <v>820</v>
+      <c r="I9" s="6" t="n">
+        <v>827</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>18</v>
@@ -1551,8 +1344,8 @@
       <c r="N9" s="4"/>
       <c r="O9" s="4"/>
     </row>
-    <row r="10" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3">
+    <row r="10" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A10" s="3" t="n">
         <v>45433</v>
       </c>
       <c r="B10" s="4" t="s">
@@ -1564,18 +1357,18 @@
       <c r="D10" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="3" t="n">
         <v>45493</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10" s="5" t="n">
         <v>873.6</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G10" s="5" t="n">
         <v>873.6</v>
       </c>
       <c r="H10" s="3"/>
-      <c r="I10" s="6">
-        <v>790</v>
+      <c r="I10" s="6" t="n">
+        <v>797</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>18</v>
@@ -1590,8 +1383,8 @@
       <c r="N10" s="4"/>
       <c r="O10" s="4"/>
     </row>
-    <row r="11" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="3">
+    <row r="11" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A11" s="3" t="n">
         <v>45433</v>
       </c>
       <c r="B11" s="4" t="s">
@@ -1603,18 +1396,18 @@
       <c r="D11" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="3" t="n">
         <v>45523</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F11" s="5" t="n">
         <v>873.6</v>
       </c>
-      <c r="G11" s="5">
+      <c r="G11" s="5" t="n">
         <v>873.6</v>
       </c>
       <c r="H11" s="3"/>
-      <c r="I11" s="6">
-        <v>760</v>
+      <c r="I11" s="6" t="n">
+        <v>767</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>18</v>
@@ -1629,8 +1422,8 @@
       <c r="N11" s="4"/>
       <c r="O11" s="4"/>
     </row>
-    <row r="12" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="3">
+    <row r="12" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A12" s="3" t="n">
         <v>45558</v>
       </c>
       <c r="B12" s="4" t="s">
@@ -1642,18 +1435,18 @@
       <c r="D12" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="3" t="n">
         <v>45600</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="5" t="n">
         <v>2000</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G12" s="5" t="n">
         <v>2000</v>
       </c>
       <c r="H12" s="3"/>
-      <c r="I12" s="6">
-        <v>683</v>
+      <c r="I12" s="6" t="n">
+        <v>690</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>18</v>
@@ -1668,8 +1461,8 @@
       <c r="N12" s="4"/>
       <c r="O12" s="4"/>
     </row>
-    <row r="13" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="3">
+    <row r="13" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A13" s="3" t="n">
         <v>45558</v>
       </c>
       <c r="B13" s="4" t="s">
@@ -1681,18 +1474,18 @@
       <c r="D13" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="3" t="n">
         <v>45607</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F13" s="5" t="n">
         <v>2000</v>
       </c>
-      <c r="G13" s="5">
+      <c r="G13" s="5" t="n">
         <v>3204.34</v>
       </c>
       <c r="H13" s="3"/>
-      <c r="I13" s="6">
-        <v>676</v>
+      <c r="I13" s="6" t="n">
+        <v>683</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>18</v>
@@ -1707,8 +1500,8 @@
       <c r="N13" s="4"/>
       <c r="O13" s="4"/>
     </row>
-    <row r="14" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3">
+    <row r="14" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A14" s="3" t="n">
         <v>45552</v>
       </c>
       <c r="B14" s="4" t="s">
@@ -1720,18 +1513,18 @@
       <c r="D14" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="n">
         <v>45608</v>
       </c>
-      <c r="F14" s="5">
-        <v>4439.8999999999996</v>
-      </c>
-      <c r="G14" s="5">
-        <v>4439.8999999999996</v>
+      <c r="F14" s="5" t="n">
+        <v>4439.9</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>4439.9</v>
       </c>
       <c r="H14" s="3"/>
-      <c r="I14" s="6">
-        <v>675</v>
+      <c r="I14" s="6" t="n">
+        <v>682</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>18</v>
@@ -1746,8 +1539,8 @@
       <c r="N14" s="4"/>
       <c r="O14" s="4"/>
     </row>
-    <row r="15" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3">
+    <row r="15" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A15" s="3" t="n">
         <v>45558</v>
       </c>
       <c r="B15" s="4" t="s">
@@ -1759,18 +1552,18 @@
       <c r="D15" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="3" t="n">
         <v>45614</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15" s="5" t="n">
         <v>2000</v>
       </c>
-      <c r="G15" s="5">
+      <c r="G15" s="5" t="n">
         <v>2000</v>
       </c>
       <c r="H15" s="3"/>
-      <c r="I15" s="6">
-        <v>669</v>
+      <c r="I15" s="6" t="n">
+        <v>676</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>18</v>
@@ -1785,8 +1578,8 @@
       <c r="N15" s="4"/>
       <c r="O15" s="4"/>
     </row>
-    <row r="16" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="3">
+    <row r="16" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A16" s="3" t="n">
         <v>45546</v>
       </c>
       <c r="B16" s="4" t="s">
@@ -1798,18 +1591,18 @@
       <c r="D16" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E16" s="3">
+      <c r="E16" s="3" t="n">
         <v>45615</v>
       </c>
-      <c r="F16" s="5">
-        <v>1216.8599999999999</v>
-      </c>
-      <c r="G16" s="5">
-        <v>1216.8599999999999</v>
+      <c r="F16" s="5" t="n">
+        <v>1216.86</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>1216.86</v>
       </c>
       <c r="H16" s="3"/>
-      <c r="I16" s="6">
-        <v>668</v>
+      <c r="I16" s="6" t="n">
+        <v>675</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>18</v>
@@ -1824,8 +1617,8 @@
       <c r="N16" s="4"/>
       <c r="O16" s="4"/>
     </row>
-    <row r="17" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="3">
+    <row r="17" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A17" s="3" t="n">
         <v>45548</v>
       </c>
       <c r="B17" s="4" t="s">
@@ -1837,18 +1630,18 @@
       <c r="D17" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E17" s="3">
+      <c r="E17" s="3" t="n">
         <v>45617</v>
       </c>
-      <c r="F17" s="5">
+      <c r="F17" s="5" t="n">
         <v>1843.87</v>
       </c>
-      <c r="G17" s="5">
+      <c r="G17" s="5" t="n">
         <v>1843.87</v>
       </c>
       <c r="H17" s="3"/>
-      <c r="I17" s="6">
-        <v>666</v>
+      <c r="I17" s="6" t="n">
+        <v>673</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>18</v>
@@ -1863,8 +1656,8 @@
       <c r="N17" s="4"/>
       <c r="O17" s="4"/>
     </row>
-    <row r="18" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="3">
+    <row r="18" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A18" s="3" t="n">
         <v>45546</v>
       </c>
       <c r="B18" s="4" t="s">
@@ -1876,18 +1669,18 @@
       <c r="D18" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18" s="3" t="n">
         <v>45622</v>
       </c>
-      <c r="F18" s="5">
-        <v>1216.8599999999999</v>
-      </c>
-      <c r="G18" s="5">
-        <v>1216.8599999999999</v>
+      <c r="F18" s="5" t="n">
+        <v>1216.86</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>1216.86</v>
       </c>
       <c r="H18" s="3"/>
-      <c r="I18" s="6">
-        <v>661</v>
+      <c r="I18" s="6" t="n">
+        <v>668</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>18</v>
@@ -1902,8 +1695,8 @@
       <c r="N18" s="4"/>
       <c r="O18" s="4"/>
     </row>
-    <row r="19" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="3">
+    <row r="19" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A19" s="3" t="n">
         <v>45552</v>
       </c>
       <c r="B19" s="4" t="s">
@@ -1915,18 +1708,18 @@
       <c r="D19" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="E19" s="3">
+      <c r="E19" s="3" t="n">
         <v>45622</v>
       </c>
-      <c r="F19" s="5">
-        <v>4439.8999999999996</v>
-      </c>
-      <c r="G19" s="5">
-        <v>4439.8999999999996</v>
+      <c r="F19" s="5" t="n">
+        <v>4439.9</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>4439.9</v>
       </c>
       <c r="H19" s="3"/>
-      <c r="I19" s="6">
-        <v>661</v>
+      <c r="I19" s="6" t="n">
+        <v>668</v>
       </c>
       <c r="J19" s="4" t="s">
         <v>18</v>
@@ -1941,8 +1734,8 @@
       <c r="N19" s="4"/>
       <c r="O19" s="4"/>
     </row>
-    <row r="20" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="3">
+    <row r="20" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A20" s="3" t="n">
         <v>45548</v>
       </c>
       <c r="B20" s="4" t="s">
@@ -1954,18 +1747,18 @@
       <c r="D20" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="3" t="n">
         <v>45624</v>
       </c>
-      <c r="F20" s="5">
+      <c r="F20" s="5" t="n">
         <v>1843.88</v>
       </c>
-      <c r="G20" s="5">
+      <c r="G20" s="5" t="n">
         <v>1843.88</v>
       </c>
       <c r="H20" s="3"/>
-      <c r="I20" s="6">
-        <v>659</v>
+      <c r="I20" s="6" t="n">
+        <v>666</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>18</v>
@@ -1980,8 +1773,8 @@
       <c r="N20" s="4"/>
       <c r="O20" s="4"/>
     </row>
-    <row r="21" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="3">
+    <row r="21" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A21" s="3" t="n">
         <v>45632</v>
       </c>
       <c r="B21" s="4" t="s">
@@ -1993,18 +1786,18 @@
       <c r="D21" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E21" s="3">
+      <c r="E21" s="3" t="n">
         <v>45688</v>
       </c>
-      <c r="F21" s="5">
-        <v>1118.4000000000001</v>
-      </c>
-      <c r="G21" s="5">
-        <v>1118.4000000000001</v>
+      <c r="F21" s="5" t="n">
+        <v>1118.4</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>1118.4</v>
       </c>
       <c r="H21" s="3"/>
-      <c r="I21" s="6">
-        <v>595</v>
+      <c r="I21" s="6" t="n">
+        <v>602</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>18</v>
@@ -2019,8 +1812,8 @@
       <c r="N21" s="4"/>
       <c r="O21" s="4"/>
     </row>
-    <row r="22" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="3">
+    <row r="22" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A22" s="3" t="n">
         <v>45646</v>
       </c>
       <c r="B22" s="4" t="s">
@@ -2032,18 +1825,18 @@
       <c r="D22" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="E22" s="3">
+      <c r="E22" s="3" t="n">
         <v>45695</v>
       </c>
-      <c r="F22" s="5">
+      <c r="F22" s="5" t="n">
         <v>3296.8</v>
       </c>
-      <c r="G22" s="5">
+      <c r="G22" s="5" t="n">
         <v>3296.8</v>
       </c>
       <c r="H22" s="3"/>
-      <c r="I22" s="6">
-        <v>588</v>
+      <c r="I22" s="6" t="n">
+        <v>595</v>
       </c>
       <c r="J22" s="4" t="s">
         <v>18</v>
@@ -2058,8 +1851,8 @@
       <c r="N22" s="4"/>
       <c r="O22" s="4"/>
     </row>
-    <row r="23" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="3">
+    <row r="23" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A23" s="3" t="n">
         <v>45636</v>
       </c>
       <c r="B23" s="4" t="s">
@@ -2071,18 +1864,18 @@
       <c r="D23" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="E23" s="3">
+      <c r="E23" s="3" t="n">
         <v>45699</v>
       </c>
-      <c r="F23" s="5">
+      <c r="F23" s="5" t="n">
         <v>2330</v>
       </c>
-      <c r="G23" s="5">
+      <c r="G23" s="5" t="n">
         <v>2330</v>
       </c>
       <c r="H23" s="3"/>
-      <c r="I23" s="6">
-        <v>584</v>
+      <c r="I23" s="6" t="n">
+        <v>591</v>
       </c>
       <c r="J23" s="4" t="s">
         <v>18</v>
@@ -2097,8 +1890,8 @@
       <c r="N23" s="4"/>
       <c r="O23" s="4"/>
     </row>
-    <row r="24" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="3">
+    <row r="24" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A24" s="3" t="n">
         <v>45646</v>
       </c>
       <c r="B24" s="4" t="s">
@@ -2110,18 +1903,18 @@
       <c r="D24" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="E24" s="3">
+      <c r="E24" s="3" t="n">
         <v>45702</v>
       </c>
-      <c r="F24" s="5">
+      <c r="F24" s="5" t="n">
         <v>3296.8</v>
       </c>
-      <c r="G24" s="5">
+      <c r="G24" s="5" t="n">
         <v>3296.8</v>
       </c>
       <c r="H24" s="3"/>
-      <c r="I24" s="6">
-        <v>581</v>
+      <c r="I24" s="6" t="n">
+        <v>588</v>
       </c>
       <c r="J24" s="4" t="s">
         <v>18</v>
@@ -2136,8 +1929,8 @@
       <c r="N24" s="4"/>
       <c r="O24" s="4"/>
     </row>
-    <row r="25" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="3">
+    <row r="25" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A25" s="3" t="n">
         <v>45677</v>
       </c>
       <c r="B25" s="4" t="s">
@@ -2149,18 +1942,18 @@
       <c r="D25" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="E25" s="3">
+      <c r="E25" s="3" t="n">
         <v>45705</v>
       </c>
-      <c r="F25" s="5">
+      <c r="F25" s="5" t="n">
         <v>2541</v>
       </c>
-      <c r="G25" s="5">
+      <c r="G25" s="5" t="n">
         <v>2541</v>
       </c>
       <c r="H25" s="3"/>
-      <c r="I25" s="6">
-        <v>578</v>
+      <c r="I25" s="6" t="n">
+        <v>585</v>
       </c>
       <c r="J25" s="4" t="s">
         <v>26</v>
@@ -2175,8 +1968,8 @@
       <c r="N25" s="4"/>
       <c r="O25" s="4"/>
     </row>
-    <row r="26" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="3">
+    <row r="26" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A26" s="3" t="n">
         <v>45646</v>
       </c>
       <c r="B26" s="4" t="s">
@@ -2188,18 +1981,18 @@
       <c r="D26" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="E26" s="3">
+      <c r="E26" s="3" t="n">
         <v>45709</v>
       </c>
-      <c r="F26" s="5">
+      <c r="F26" s="5" t="n">
         <v>3296.8</v>
       </c>
-      <c r="G26" s="5">
+      <c r="G26" s="5" t="n">
         <v>3296.8</v>
       </c>
       <c r="H26" s="3"/>
-      <c r="I26" s="6">
-        <v>574</v>
+      <c r="I26" s="6" t="n">
+        <v>581</v>
       </c>
       <c r="J26" s="4" t="s">
         <v>18</v>
@@ -2214,8 +2007,8 @@
       <c r="N26" s="4"/>
       <c r="O26" s="4"/>
     </row>
-    <row r="27" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="3">
+    <row r="27" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A27" s="3" t="n">
         <v>45677</v>
       </c>
       <c r="B27" s="4" t="s">
@@ -2227,18 +2020,18 @@
       <c r="D27" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="E27" s="3">
+      <c r="E27" s="3" t="n">
         <v>45712</v>
       </c>
-      <c r="F27" s="5">
+      <c r="F27" s="5" t="n">
         <v>2541</v>
       </c>
-      <c r="G27" s="5">
+      <c r="G27" s="5" t="n">
         <v>2541</v>
       </c>
       <c r="H27" s="3"/>
-      <c r="I27" s="6">
-        <v>571</v>
+      <c r="I27" s="6" t="n">
+        <v>578</v>
       </c>
       <c r="J27" s="4" t="s">
         <v>26</v>
@@ -2253,8 +2046,8 @@
       <c r="N27" s="4"/>
       <c r="O27" s="4"/>
     </row>
-    <row r="28" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="3">
+    <row r="28" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A28" s="3" t="n">
         <v>45677</v>
       </c>
       <c r="B28" s="4" t="s">
@@ -2266,18 +2059,18 @@
       <c r="D28" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="E28" s="3">
+      <c r="E28" s="3" t="n">
         <v>45726</v>
       </c>
-      <c r="F28" s="5">
+      <c r="F28" s="5" t="n">
         <v>2541</v>
       </c>
-      <c r="G28" s="5">
+      <c r="G28" s="5" t="n">
         <v>2541</v>
       </c>
       <c r="H28" s="3"/>
-      <c r="I28" s="6">
-        <v>557</v>
+      <c r="I28" s="6" t="n">
+        <v>564</v>
       </c>
       <c r="J28" s="4" t="s">
         <v>26</v>
@@ -2292,8 +2085,8 @@
       <c r="N28" s="4"/>
       <c r="O28" s="4"/>
     </row>
-    <row r="29" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="3">
+    <row r="29" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A29" s="3" t="n">
         <v>45699</v>
       </c>
       <c r="B29" s="4" t="s">
@@ -2305,18 +2098,18 @@
       <c r="D29" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="E29" s="3">
+      <c r="E29" s="3" t="n">
         <v>45727</v>
       </c>
-      <c r="F29" s="5">
+      <c r="F29" s="5" t="n">
         <v>7562.78</v>
       </c>
-      <c r="G29" s="5">
+      <c r="G29" s="5" t="n">
         <v>7562.78</v>
       </c>
       <c r="H29" s="3"/>
-      <c r="I29" s="6">
-        <v>556</v>
+      <c r="I29" s="6" t="n">
+        <v>563</v>
       </c>
       <c r="J29" s="4" t="s">
         <v>18</v>
@@ -2331,8 +2124,8 @@
       <c r="N29" s="4"/>
       <c r="O29" s="4"/>
     </row>
-    <row r="30" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="3">
+    <row r="30" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A30" s="3" t="n">
         <v>45699</v>
       </c>
       <c r="B30" s="4" t="s">
@@ -2344,18 +2137,18 @@
       <c r="D30" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="E30" s="3">
+      <c r="E30" s="3" t="n">
         <v>45734</v>
       </c>
-      <c r="F30" s="5">
+      <c r="F30" s="5" t="n">
         <v>7562.78</v>
       </c>
-      <c r="G30" s="5">
+      <c r="G30" s="5" t="n">
         <v>7562.78</v>
       </c>
       <c r="H30" s="3"/>
-      <c r="I30" s="6">
-        <v>549</v>
+      <c r="I30" s="6" t="n">
+        <v>556</v>
       </c>
       <c r="J30" s="4" t="s">
         <v>18</v>
@@ -2370,8 +2163,8 @@
       <c r="N30" s="4"/>
       <c r="O30" s="4"/>
     </row>
-    <row r="31" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="3">
+    <row r="31" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A31" s="3" t="n">
         <v>45699</v>
       </c>
       <c r="B31" s="4" t="s">
@@ -2383,18 +2176,18 @@
       <c r="D31" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="E31" s="3">
+      <c r="E31" s="3" t="n">
         <v>45734</v>
       </c>
-      <c r="F31" s="5">
+      <c r="F31" s="5" t="n">
         <v>1154.56</v>
       </c>
-      <c r="G31" s="5">
+      <c r="G31" s="5" t="n">
         <v>1154.56</v>
       </c>
       <c r="H31" s="3"/>
-      <c r="I31" s="6">
-        <v>549</v>
+      <c r="I31" s="6" t="n">
+        <v>556</v>
       </c>
       <c r="J31" s="4" t="s">
         <v>18</v>
@@ -2409,8 +2202,8 @@
       <c r="N31" s="4"/>
       <c r="O31" s="4"/>
     </row>
-    <row r="32" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="3">
+    <row r="32" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A32" s="3" t="n">
         <v>45677</v>
       </c>
       <c r="B32" s="4" t="s">
@@ -2422,18 +2215,18 @@
       <c r="D32" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="E32" s="3">
+      <c r="E32" s="3" t="n">
         <v>45740</v>
       </c>
-      <c r="F32" s="5">
+      <c r="F32" s="5" t="n">
         <v>2541</v>
       </c>
-      <c r="G32" s="5">
+      <c r="G32" s="5" t="n">
         <v>2541</v>
       </c>
       <c r="H32" s="3"/>
-      <c r="I32" s="6">
-        <v>543</v>
+      <c r="I32" s="6" t="n">
+        <v>550</v>
       </c>
       <c r="J32" s="4" t="s">
         <v>26</v>
@@ -2448,8 +2241,8 @@
       <c r="N32" s="4"/>
       <c r="O32" s="4"/>
     </row>
-    <row r="33" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="3">
+    <row r="33" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A33" s="3" t="n">
         <v>45699</v>
       </c>
       <c r="B33" s="4" t="s">
@@ -2461,18 +2254,18 @@
       <c r="D33" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="E33" s="3">
+      <c r="E33" s="3" t="n">
         <v>45741</v>
       </c>
-      <c r="F33" s="5">
+      <c r="F33" s="5" t="n">
         <v>7562.78</v>
       </c>
-      <c r="G33" s="5">
+      <c r="G33" s="5" t="n">
         <v>7562.78</v>
       </c>
       <c r="H33" s="3"/>
-      <c r="I33" s="6">
-        <v>542</v>
+      <c r="I33" s="6" t="n">
+        <v>549</v>
       </c>
       <c r="J33" s="4" t="s">
         <v>18</v>
@@ -2487,8 +2280,8 @@
       <c r="N33" s="4"/>
       <c r="O33" s="4"/>
     </row>
-    <row r="34" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="3">
+    <row r="34" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A34" s="3" t="n">
         <v>45699</v>
       </c>
       <c r="B34" s="4" t="s">
@@ -2500,18 +2293,18 @@
       <c r="D34" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="E34" s="3">
+      <c r="E34" s="3" t="n">
         <v>45741</v>
       </c>
-      <c r="F34" s="5">
+      <c r="F34" s="5" t="n">
         <v>1154.56</v>
       </c>
-      <c r="G34" s="5">
+      <c r="G34" s="5" t="n">
         <v>1154.56</v>
       </c>
       <c r="H34" s="3"/>
-      <c r="I34" s="6">
-        <v>542</v>
+      <c r="I34" s="6" t="n">
+        <v>549</v>
       </c>
       <c r="J34" s="4" t="s">
         <v>18</v>
@@ -2526,8 +2319,8 @@
       <c r="N34" s="4"/>
       <c r="O34" s="4"/>
     </row>
-    <row r="35" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="3">
+    <row r="35" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A35" s="3" t="n">
         <v>45699</v>
       </c>
       <c r="B35" s="4" t="s">
@@ -2539,18 +2332,18 @@
       <c r="D35" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="E35" s="3">
+      <c r="E35" s="3" t="n">
         <v>45748</v>
       </c>
-      <c r="F35" s="5">
+      <c r="F35" s="5" t="n">
         <v>1154.56</v>
       </c>
-      <c r="G35" s="5">
+      <c r="G35" s="5" t="n">
         <v>1154.56</v>
       </c>
       <c r="H35" s="3"/>
-      <c r="I35" s="6">
-        <v>535</v>
+      <c r="I35" s="6" t="n">
+        <v>542</v>
       </c>
       <c r="J35" s="4" t="s">
         <v>18</v>
@@ -2565,8 +2358,8 @@
       <c r="N35" s="4"/>
       <c r="O35" s="4"/>
     </row>
-    <row r="36" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="3">
+    <row r="36" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A36" s="3" t="n">
         <v>45699</v>
       </c>
       <c r="B36" s="4" t="s">
@@ -2578,18 +2371,18 @@
       <c r="D36" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E36" s="3">
+      <c r="E36" s="3" t="n">
         <v>45748</v>
       </c>
-      <c r="F36" s="5">
+      <c r="F36" s="5" t="n">
         <v>7562.76</v>
       </c>
-      <c r="G36" s="5">
+      <c r="G36" s="5" t="n">
         <v>7562.76</v>
       </c>
       <c r="H36" s="3"/>
-      <c r="I36" s="6">
-        <v>535</v>
+      <c r="I36" s="6" t="n">
+        <v>542</v>
       </c>
       <c r="J36" s="4" t="s">
         <v>18</v>
@@ -2604,8 +2397,8 @@
       <c r="N36" s="4"/>
       <c r="O36" s="4"/>
     </row>
-    <row r="37" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="3">
+    <row r="37" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A37" s="3" t="n">
         <v>45699</v>
       </c>
       <c r="B37" s="4" t="s">
@@ -2617,18 +2410,18 @@
       <c r="D37" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="E37" s="3">
+      <c r="E37" s="3" t="n">
         <v>45755</v>
       </c>
-      <c r="F37" s="5">
+      <c r="F37" s="5" t="n">
         <v>1154.56</v>
       </c>
-      <c r="G37" s="5">
+      <c r="G37" s="5" t="n">
         <v>1154.56</v>
       </c>
       <c r="H37" s="3"/>
-      <c r="I37" s="6">
-        <v>528</v>
+      <c r="I37" s="6" t="n">
+        <v>535</v>
       </c>
       <c r="J37" s="4" t="s">
         <v>18</v>
@@ -2643,8 +2436,8 @@
       <c r="N37" s="4"/>
       <c r="O37" s="4"/>
     </row>
-    <row r="38" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="3">
+    <row r="38" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A38" s="3" t="n">
         <v>45733</v>
       </c>
       <c r="B38" s="4" t="s">
@@ -2656,18 +2449,18 @@
       <c r="D38" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="E38" s="3">
+      <c r="E38" s="3" t="n">
         <v>45761</v>
       </c>
-      <c r="F38" s="5">
+      <c r="F38" s="5" t="n">
         <v>3850</v>
       </c>
-      <c r="G38" s="5">
+      <c r="G38" s="5" t="n">
         <v>6169.53</v>
       </c>
       <c r="H38" s="3"/>
-      <c r="I38" s="6">
-        <v>522</v>
+      <c r="I38" s="6" t="n">
+        <v>529</v>
       </c>
       <c r="J38" s="4" t="s">
         <v>18</v>
@@ -2682,8 +2475,8 @@
       <c r="N38" s="4"/>
       <c r="O38" s="4"/>
     </row>
-    <row r="39" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="3">
+    <row r="39" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A39" s="3" t="n">
         <v>45733</v>
       </c>
       <c r="B39" s="4" t="s">
@@ -2695,18 +2488,18 @@
       <c r="D39" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="E39" s="3">
+      <c r="E39" s="3" t="n">
         <v>45768</v>
       </c>
-      <c r="F39" s="5">
+      <c r="F39" s="5" t="n">
         <v>3850</v>
       </c>
-      <c r="G39" s="5">
+      <c r="G39" s="5" t="n">
         <v>3850</v>
       </c>
       <c r="H39" s="3"/>
-      <c r="I39" s="6">
-        <v>515</v>
+      <c r="I39" s="6" t="n">
+        <v>522</v>
       </c>
       <c r="J39" s="4" t="s">
         <v>18</v>
@@ -2721,8 +2514,8 @@
       <c r="N39" s="4"/>
       <c r="O39" s="4"/>
     </row>
-    <row r="40" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="3">
+    <row r="40" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A40" s="3" t="n">
         <v>45733</v>
       </c>
       <c r="B40" s="4" t="s">
@@ -2734,18 +2527,18 @@
       <c r="D40" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="E40" s="3">
+      <c r="E40" s="3" t="n">
         <v>45775</v>
       </c>
-      <c r="F40" s="5">
+      <c r="F40" s="5" t="n">
         <v>3850</v>
       </c>
-      <c r="G40" s="5">
+      <c r="G40" s="5" t="n">
         <v>3850</v>
       </c>
       <c r="H40" s="3"/>
-      <c r="I40" s="6">
-        <v>508</v>
+      <c r="I40" s="6" t="n">
+        <v>515</v>
       </c>
       <c r="J40" s="4" t="s">
         <v>18</v>
@@ -2760,8 +2553,8 @@
       <c r="N40" s="4"/>
       <c r="O40" s="4"/>
     </row>
-    <row r="41" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="3">
+    <row r="41" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A41" s="3" t="n">
         <v>45747</v>
       </c>
       <c r="B41" s="4" t="s">
@@ -2773,18 +2566,18 @@
       <c r="D41" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="E41" s="3">
+      <c r="E41" s="3" t="n">
         <v>45775</v>
       </c>
-      <c r="F41" s="5">
+      <c r="F41" s="5" t="n">
         <v>3800</v>
       </c>
-      <c r="G41" s="5">
+      <c r="G41" s="5" t="n">
         <v>6089.41</v>
       </c>
       <c r="H41" s="3"/>
-      <c r="I41" s="6">
-        <v>508</v>
+      <c r="I41" s="6" t="n">
+        <v>515</v>
       </c>
       <c r="J41" s="4" t="s">
         <v>18</v>
@@ -2799,8 +2592,8 @@
       <c r="N41" s="4"/>
       <c r="O41" s="4"/>
     </row>
-    <row r="42" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="3">
+    <row r="42" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A42" s="3" t="n">
         <v>45747</v>
       </c>
       <c r="B42" s="4" t="s">
@@ -2812,18 +2605,18 @@
       <c r="D42" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="E42" s="3">
+      <c r="E42" s="3" t="n">
         <v>45782</v>
       </c>
-      <c r="F42" s="5">
+      <c r="F42" s="5" t="n">
         <v>3800</v>
       </c>
-      <c r="G42" s="5">
+      <c r="G42" s="5" t="n">
         <v>3800</v>
       </c>
       <c r="H42" s="3"/>
-      <c r="I42" s="6">
-        <v>501</v>
+      <c r="I42" s="6" t="n">
+        <v>508</v>
       </c>
       <c r="J42" s="4" t="s">
         <v>18</v>
@@ -2838,8 +2631,8 @@
       <c r="N42" s="4"/>
       <c r="O42" s="4"/>
     </row>
-    <row r="43" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="3">
+    <row r="43" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A43" s="3" t="n">
         <v>45747</v>
       </c>
       <c r="B43" s="4" t="s">
@@ -2851,18 +2644,18 @@
       <c r="D43" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="E43" s="3">
+      <c r="E43" s="3" t="n">
         <v>45789</v>
       </c>
-      <c r="F43" s="5">
+      <c r="F43" s="5" t="n">
         <v>3800</v>
       </c>
-      <c r="G43" s="5">
+      <c r="G43" s="5" t="n">
         <v>3800</v>
       </c>
       <c r="H43" s="3"/>
-      <c r="I43" s="6">
-        <v>494</v>
+      <c r="I43" s="6" t="n">
+        <v>501</v>
       </c>
       <c r="J43" s="4" t="s">
         <v>18</v>
@@ -2877,8 +2670,8 @@
       <c r="N43" s="4"/>
       <c r="O43" s="4"/>
     </row>
-    <row r="44" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="3">
+    <row r="44" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A44" s="3" t="n">
         <v>45754</v>
       </c>
       <c r="B44" s="4" t="s">
@@ -2890,18 +2683,18 @@
       <c r="D44" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="E44" s="3">
+      <c r="E44" s="3" t="n">
         <v>45789</v>
       </c>
-      <c r="F44" s="5">
-        <v>2287.0700000000002</v>
-      </c>
-      <c r="G44" s="5">
+      <c r="F44" s="5" t="n">
+        <v>2287.07</v>
+      </c>
+      <c r="G44" s="5" t="n">
         <v>1143.54</v>
       </c>
       <c r="H44" s="3"/>
-      <c r="I44" s="6">
-        <v>494</v>
+      <c r="I44" s="6" t="n">
+        <v>501</v>
       </c>
       <c r="J44" s="4" t="s">
         <v>26</v>
@@ -2916,8 +2709,8 @@
       <c r="N44" s="4"/>
       <c r="O44" s="4"/>
     </row>
-    <row r="45" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="3">
+    <row r="45" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A45" s="3" t="n">
         <v>45754</v>
       </c>
       <c r="B45" s="4" t="s">
@@ -2929,18 +2722,18 @@
       <c r="D45" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="3" t="n">
         <v>45796</v>
       </c>
-      <c r="F45" s="5">
+      <c r="F45" s="5" t="n">
         <v>2287.06</v>
       </c>
-      <c r="G45" s="5">
+      <c r="G45" s="5" t="n">
         <v>2287.06</v>
       </c>
       <c r="H45" s="3"/>
-      <c r="I45" s="6">
-        <v>487</v>
+      <c r="I45" s="6" t="n">
+        <v>494</v>
       </c>
       <c r="J45" s="4" t="s">
         <v>26</v>
@@ -2955,8 +2748,8 @@
       <c r="N45" s="4"/>
       <c r="O45" s="4"/>
     </row>
-    <row r="46" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="3">
+    <row r="46" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A46" s="3" t="n">
         <v>45868</v>
       </c>
       <c r="B46" s="4" t="s">
@@ -2968,18 +2761,18 @@
       <c r="D46" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="E46" s="3">
+      <c r="E46" s="3" t="n">
         <v>45896</v>
       </c>
-      <c r="F46" s="5">
+      <c r="F46" s="5" t="n">
         <v>3663.84</v>
       </c>
-      <c r="G46" s="5">
+      <c r="G46" s="5" t="n">
         <v>4572.62</v>
       </c>
       <c r="H46" s="3"/>
-      <c r="I46" s="6">
-        <v>387</v>
+      <c r="I46" s="6" t="n">
+        <v>394</v>
       </c>
       <c r="J46" s="4" t="s">
         <v>26</v>
@@ -2994,8 +2787,8 @@
       <c r="N46" s="4"/>
       <c r="O46" s="4"/>
     </row>
-    <row r="47" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="3">
+    <row r="47" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A47" s="3" t="n">
         <v>45868</v>
       </c>
       <c r="B47" s="4" t="s">
@@ -3007,18 +2800,18 @@
       <c r="D47" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="E47" s="3">
+      <c r="E47" s="3" t="n">
         <v>45910</v>
       </c>
-      <c r="F47" s="5">
+      <c r="F47" s="5" t="n">
         <v>3663.84</v>
       </c>
-      <c r="G47" s="5">
+      <c r="G47" s="5" t="n">
         <v>3663.84</v>
       </c>
       <c r="H47" s="3"/>
-      <c r="I47" s="6">
-        <v>373</v>
+      <c r="I47" s="6" t="n">
+        <v>380</v>
       </c>
       <c r="J47" s="4" t="s">
         <v>26</v>
@@ -3033,8 +2826,8 @@
       <c r="N47" s="4"/>
       <c r="O47" s="4"/>
     </row>
-    <row r="48" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="3">
+    <row r="48" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A48" s="3" t="n">
         <v>45868</v>
       </c>
       <c r="B48" s="4" t="s">
@@ -3046,18 +2839,18 @@
       <c r="D48" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="E48" s="3">
+      <c r="E48" s="3" t="n">
         <v>45924</v>
       </c>
-      <c r="F48" s="5">
+      <c r="F48" s="5" t="n">
         <v>3663.84</v>
       </c>
-      <c r="G48" s="5">
+      <c r="G48" s="5" t="n">
         <v>3663.84</v>
       </c>
       <c r="H48" s="3"/>
-      <c r="I48" s="6">
-        <v>359</v>
+      <c r="I48" s="6" t="n">
+        <v>366</v>
       </c>
       <c r="J48" s="4" t="s">
         <v>26</v>
@@ -3072,8 +2865,8 @@
       <c r="N48" s="4"/>
       <c r="O48" s="4"/>
     </row>
-    <row r="49" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="3">
+    <row r="49" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A49" s="3" t="n">
         <v>45919</v>
       </c>
       <c r="B49" s="4" t="s">
@@ -3085,18 +2878,18 @@
       <c r="D49" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="E49" s="3">
+      <c r="E49" s="3" t="n">
         <v>45947</v>
       </c>
-      <c r="F49" s="5">
+      <c r="F49" s="5" t="n">
         <v>2144.59</v>
       </c>
-      <c r="G49" s="5">
+      <c r="G49" s="5" t="n">
         <v>3867.34</v>
       </c>
       <c r="H49" s="3"/>
-      <c r="I49" s="6">
-        <v>336</v>
+      <c r="I49" s="6" t="n">
+        <v>343</v>
       </c>
       <c r="J49" s="4" t="s">
         <v>26</v>
@@ -3111,8 +2904,8 @@
       <c r="N49" s="4"/>
       <c r="O49" s="4"/>
     </row>
-    <row r="50" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="3">
+    <row r="50" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A50" s="3" t="n">
         <v>45919</v>
       </c>
       <c r="B50" s="4" t="s">
@@ -3124,18 +2917,18 @@
       <c r="D50" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="E50" s="3">
+      <c r="E50" s="3" t="n">
         <v>45954</v>
       </c>
-      <c r="F50" s="5">
+      <c r="F50" s="5" t="n">
         <v>2144.59</v>
       </c>
-      <c r="G50" s="5">
+      <c r="G50" s="5" t="n">
         <v>2144.59</v>
       </c>
       <c r="H50" s="3"/>
-      <c r="I50" s="6">
-        <v>329</v>
+      <c r="I50" s="6" t="n">
+        <v>336</v>
       </c>
       <c r="J50" s="4" t="s">
         <v>26</v>
@@ -3150,8 +2943,8 @@
       <c r="N50" s="4"/>
       <c r="O50" s="4"/>
     </row>
-    <row r="51" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="3">
+    <row r="51" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A51" s="3" t="n">
         <v>45919</v>
       </c>
       <c r="B51" s="4" t="s">
@@ -3163,18 +2956,18 @@
       <c r="D51" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="E51" s="3">
+      <c r="E51" s="3" t="n">
         <v>45961</v>
       </c>
-      <c r="F51" s="5">
+      <c r="F51" s="5" t="n">
         <v>2144.59</v>
       </c>
-      <c r="G51" s="5">
+      <c r="G51" s="5" t="n">
         <v>2144.59</v>
       </c>
       <c r="H51" s="3"/>
-      <c r="I51" s="6">
-        <v>322</v>
+      <c r="I51" s="6" t="n">
+        <v>329</v>
       </c>
       <c r="J51" s="4" t="s">
         <v>26</v>
@@ -3189,8 +2982,8 @@
       <c r="N51" s="4"/>
       <c r="O51" s="4"/>
     </row>
-    <row r="52" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="3">
+    <row r="52" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A52" s="3" t="n">
         <v>45919</v>
       </c>
       <c r="B52" s="4" t="s">
@@ -3202,18 +2995,18 @@
       <c r="D52" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="E52" s="3">
+      <c r="E52" s="3" t="n">
         <v>45968</v>
       </c>
-      <c r="F52" s="5">
+      <c r="F52" s="5" t="n">
         <v>2144.59</v>
       </c>
-      <c r="G52" s="5">
+      <c r="G52" s="5" t="n">
         <v>2144.59</v>
       </c>
       <c r="H52" s="3"/>
-      <c r="I52" s="6">
-        <v>315</v>
+      <c r="I52" s="6" t="n">
+        <v>322</v>
       </c>
       <c r="J52" s="4" t="s">
         <v>26</v>
@@ -3228,8 +3021,8 @@
       <c r="N52" s="4"/>
       <c r="O52" s="4"/>
     </row>
-    <row r="53" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="3">
+    <row r="53" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A53" s="3" t="n">
         <v>45938</v>
       </c>
       <c r="B53" s="4" t="s">
@@ -3241,18 +3034,18 @@
       <c r="D53" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="E53" s="3">
+      <c r="E53" s="3" t="n">
         <v>45980</v>
       </c>
-      <c r="F53" s="5">
+      <c r="F53" s="5" t="n">
         <v>4480</v>
       </c>
-      <c r="G53" s="5">
+      <c r="G53" s="5" t="n">
         <v>4480</v>
       </c>
       <c r="H53" s="3"/>
-      <c r="I53" s="6">
-        <v>303</v>
+      <c r="I53" s="6" t="n">
+        <v>310</v>
       </c>
       <c r="J53" s="4" t="s">
         <v>26</v>
@@ -3267,8 +3060,8 @@
       <c r="N53" s="4"/>
       <c r="O53" s="4"/>
     </row>
-    <row r="54" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="3">
+    <row r="54" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A54" s="3" t="n">
         <v>45959</v>
       </c>
       <c r="B54" s="4" t="s">
@@ -3280,18 +3073,18 @@
       <c r="D54" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="E54" s="3">
+      <c r="E54" s="3" t="n">
         <v>45980</v>
       </c>
-      <c r="F54" s="5">
+      <c r="F54" s="5" t="n">
         <v>28666.44</v>
       </c>
-      <c r="G54" s="5">
+      <c r="G54" s="5" t="n">
         <v>28666.44</v>
       </c>
       <c r="H54" s="3"/>
-      <c r="I54" s="6">
-        <v>303</v>
+      <c r="I54" s="6" t="n">
+        <v>310</v>
       </c>
       <c r="J54" s="4"/>
       <c r="K54" s="4" t="s">
@@ -3302,8 +3095,8 @@
       <c r="N54" s="4"/>
       <c r="O54" s="4"/>
     </row>
-    <row r="55" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="3">
+    <row r="55" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A55" s="3" t="n">
         <v>45959</v>
       </c>
       <c r="B55" s="4" t="s">
@@ -3315,18 +3108,18 @@
       <c r="D55" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="E55" s="3">
+      <c r="E55" s="3" t="n">
         <v>45987</v>
       </c>
-      <c r="F55" s="5">
-        <v>33844.160000000003</v>
-      </c>
-      <c r="G55" s="5">
-        <v>33844.160000000003</v>
+      <c r="F55" s="5" t="n">
+        <v>33844.16</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>33844.16</v>
       </c>
       <c r="H55" s="3"/>
-      <c r="I55" s="6">
-        <v>296</v>
+      <c r="I55" s="6" t="n">
+        <v>303</v>
       </c>
       <c r="J55" s="4"/>
       <c r="K55" s="4" t="s">
@@ -3337,8 +3130,8 @@
       <c r="N55" s="4"/>
       <c r="O55" s="4"/>
     </row>
-    <row r="56" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="3">
+    <row r="56" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A56" s="3" t="n">
         <v>45947</v>
       </c>
       <c r="B56" s="4" t="s">
@@ -3350,18 +3143,18 @@
       <c r="D56" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="E56" s="3">
+      <c r="E56" s="3" t="n">
         <v>45989</v>
       </c>
-      <c r="F56" s="5">
+      <c r="F56" s="5" t="n">
         <v>3220</v>
       </c>
-      <c r="G56" s="5">
+      <c r="G56" s="5" t="n">
         <v>3220</v>
       </c>
       <c r="H56" s="3"/>
-      <c r="I56" s="6">
-        <v>294</v>
+      <c r="I56" s="6" t="n">
+        <v>301</v>
       </c>
       <c r="J56" s="4"/>
       <c r="K56" s="4" t="s">
@@ -3372,8 +3165,8 @@
       <c r="N56" s="4"/>
       <c r="O56" s="4"/>
     </row>
-    <row r="57" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="3">
+    <row r="57" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A57" s="3" t="n">
         <v>45959</v>
       </c>
       <c r="B57" s="4" t="s">
@@ -3385,18 +3178,18 @@
       <c r="D57" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="E57" s="3">
+      <c r="E57" s="3" t="n">
         <v>45994</v>
       </c>
-      <c r="F57" s="5">
+      <c r="F57" s="5" t="n">
         <v>14483.06</v>
       </c>
-      <c r="G57" s="5">
+      <c r="G57" s="5" t="n">
         <v>14483.06</v>
       </c>
       <c r="H57" s="3"/>
-      <c r="I57" s="6">
-        <v>289</v>
+      <c r="I57" s="6" t="n">
+        <v>296</v>
       </c>
       <c r="J57" s="4"/>
       <c r="K57" s="4" t="s">
@@ -3407,8 +3200,8 @@
       <c r="N57" s="4"/>
       <c r="O57" s="4"/>
     </row>
-    <row r="58" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="3">
+    <row r="58" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A58" s="3" t="n">
         <v>46062</v>
       </c>
       <c r="B58" s="4" t="s">
@@ -3420,18 +3213,18 @@
       <c r="D58" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="E58" s="3">
+      <c r="E58" s="3" t="n">
         <v>46090</v>
       </c>
-      <c r="F58" s="5">
+      <c r="F58" s="5" t="n">
         <v>503.28</v>
       </c>
-      <c r="G58" s="5">
+      <c r="G58" s="5" t="n">
         <v>806.34</v>
       </c>
       <c r="H58" s="3"/>
-      <c r="I58" s="6">
-        <v>193</v>
+      <c r="I58" s="6" t="n">
+        <v>200</v>
       </c>
       <c r="J58" s="4" t="s">
         <v>26</v>
@@ -3446,8 +3239,8 @@
       <c r="N58" s="4"/>
       <c r="O58" s="4"/>
     </row>
-    <row r="59" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="3">
+    <row r="59" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A59" s="3" t="n">
         <v>46062</v>
       </c>
       <c r="B59" s="4" t="s">
@@ -3459,18 +3252,18 @@
       <c r="D59" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="E59" s="3">
+      <c r="E59" s="3" t="n">
         <v>46097</v>
       </c>
-      <c r="F59" s="5">
+      <c r="F59" s="5" t="n">
         <v>503.28</v>
       </c>
-      <c r="G59" s="5">
+      <c r="G59" s="5" t="n">
         <v>503.28</v>
       </c>
       <c r="H59" s="3"/>
-      <c r="I59" s="6">
-        <v>186</v>
+      <c r="I59" s="6" t="n">
+        <v>193</v>
       </c>
       <c r="J59" s="4" t="s">
         <v>26</v>
@@ -3485,8 +3278,8 @@
       <c r="N59" s="4"/>
       <c r="O59" s="4"/>
     </row>
-    <row r="60" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="3">
+    <row r="60" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A60" s="3" t="n">
         <v>46062</v>
       </c>
       <c r="B60" s="4" t="s">
@@ -3498,18 +3291,18 @@
       <c r="D60" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="E60" s="3">
+      <c r="E60" s="3" t="n">
         <v>46104</v>
       </c>
-      <c r="F60" s="5">
+      <c r="F60" s="5" t="n">
         <v>503.28</v>
       </c>
-      <c r="G60" s="5">
+      <c r="G60" s="5" t="n">
         <v>503.28</v>
       </c>
       <c r="H60" s="3"/>
-      <c r="I60" s="6">
-        <v>179</v>
+      <c r="I60" s="6" t="n">
+        <v>186</v>
       </c>
       <c r="J60" s="4" t="s">
         <v>26</v>
@@ -3524,8 +3317,8 @@
       <c r="N60" s="4"/>
       <c r="O60" s="4"/>
     </row>
-    <row r="61" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="3">
+    <row r="61" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A61" s="3" t="n">
         <v>46045</v>
       </c>
       <c r="B61" s="4" t="s">
@@ -3537,18 +3330,18 @@
       <c r="D61" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="E61" s="3">
+      <c r="E61" s="3" t="n">
         <v>46105</v>
       </c>
-      <c r="F61" s="5">
+      <c r="F61" s="5" t="n">
         <v>5466.66</v>
       </c>
-      <c r="G61" s="5">
+      <c r="G61" s="5" t="n">
         <v>5466.66</v>
       </c>
       <c r="H61" s="3"/>
-      <c r="I61" s="6">
-        <v>178</v>
+      <c r="I61" s="6" t="n">
+        <v>185</v>
       </c>
       <c r="J61" s="4" t="s">
         <v>18</v>
@@ -3563,8 +3356,8 @@
       <c r="N61" s="4"/>
       <c r="O61" s="4"/>
     </row>
-    <row r="62" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="3">
+    <row r="62" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A62" s="3" t="n">
         <v>46171</v>
       </c>
       <c r="B62" s="4" t="s">
@@ -3576,18 +3369,18 @@
       <c r="D62" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="E62" s="3">
+      <c r="E62" s="3" t="n">
         <v>46192</v>
       </c>
-      <c r="F62" s="5">
-        <v>4676.8500000000004</v>
-      </c>
-      <c r="G62" s="5">
+      <c r="F62" s="5" t="n">
+        <v>4676.85</v>
+      </c>
+      <c r="G62" s="5" t="n">
         <v>7494.53</v>
       </c>
       <c r="H62" s="3"/>
-      <c r="I62" s="6">
-        <v>91</v>
+      <c r="I62" s="6" t="n">
+        <v>98</v>
       </c>
       <c r="J62" s="4"/>
       <c r="K62" s="4" t="s">
@@ -3598,8 +3391,8 @@
       <c r="N62" s="4"/>
       <c r="O62" s="4"/>
     </row>
-    <row r="63" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="3">
+    <row r="63" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A63" s="3" t="n">
         <v>46171</v>
       </c>
       <c r="B63" s="4" t="s">
@@ -3611,18 +3404,18 @@
       <c r="D63" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="E63" s="3">
+      <c r="E63" s="3" t="n">
         <v>46199</v>
       </c>
-      <c r="F63" s="5">
-        <v>4676.8500000000004</v>
-      </c>
-      <c r="G63" s="5">
-        <v>4676.8500000000004</v>
+      <c r="F63" s="5" t="n">
+        <v>4676.85</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>4676.85</v>
       </c>
       <c r="H63" s="3"/>
-      <c r="I63" s="6">
-        <v>84</v>
+      <c r="I63" s="6" t="n">
+        <v>91</v>
       </c>
       <c r="J63" s="4"/>
       <c r="K63" s="4" t="s">
@@ -3633,8 +3426,8 @@
       <c r="N63" s="4"/>
       <c r="O63" s="4"/>
     </row>
-    <row r="64" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="3">
+    <row r="64" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A64" s="3" t="n">
         <v>46171</v>
       </c>
       <c r="B64" s="4" t="s">
@@ -3646,18 +3439,18 @@
       <c r="D64" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="E64" s="3">
+      <c r="E64" s="3" t="n">
         <v>46206</v>
       </c>
-      <c r="F64" s="5">
-        <v>4676.8500000000004</v>
-      </c>
-      <c r="G64" s="5">
-        <v>4676.8500000000004</v>
+      <c r="F64" s="5" t="n">
+        <v>4676.85</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>4676.85</v>
       </c>
       <c r="H64" s="3"/>
-      <c r="I64" s="6">
-        <v>77</v>
+      <c r="I64" s="6" t="n">
+        <v>84</v>
       </c>
       <c r="J64" s="4"/>
       <c r="K64" s="4" t="s">
@@ -3668,8 +3461,8 @@
       <c r="N64" s="4"/>
       <c r="O64" s="4"/>
     </row>
-    <row r="65" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="3">
+    <row r="65" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A65" s="3" t="n">
         <v>46162</v>
       </c>
       <c r="B65" s="4" t="s">
@@ -3681,18 +3474,18 @@
       <c r="D65" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="E65" s="3">
+      <c r="E65" s="3" t="n">
         <v>46222</v>
       </c>
-      <c r="F65" s="5">
+      <c r="F65" s="5" t="n">
         <v>31531.5</v>
       </c>
-      <c r="G65" s="5">
+      <c r="G65" s="5" t="n">
         <v>31531.5</v>
       </c>
       <c r="H65" s="3"/>
-      <c r="I65" s="6">
-        <v>61</v>
+      <c r="I65" s="6" t="n">
+        <v>68</v>
       </c>
       <c r="J65" s="4" t="s">
         <v>18</v>
@@ -3707,8 +3500,8 @@
       <c r="N65" s="4"/>
       <c r="O65" s="4"/>
     </row>
-    <row r="66" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="3">
+    <row r="66" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A66" s="3" t="n">
         <v>46198</v>
       </c>
       <c r="B66" s="4" t="s">
@@ -3720,18 +3513,18 @@
       <c r="D66" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="E66" s="3">
+      <c r="E66" s="3" t="n">
         <v>46228</v>
       </c>
-      <c r="F66" s="5">
+      <c r="F66" s="5" t="n">
         <v>3516.48</v>
       </c>
-      <c r="G66" s="5">
+      <c r="G66" s="5" t="n">
         <v>3516.48</v>
       </c>
       <c r="H66" s="3"/>
-      <c r="I66" s="6">
-        <v>55</v>
+      <c r="I66" s="6" t="n">
+        <v>62</v>
       </c>
       <c r="J66" s="4" t="s">
         <v>170</v>
@@ -3746,8 +3539,8 @@
       <c r="N66" s="4"/>
       <c r="O66" s="4"/>
     </row>
-    <row r="67" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="3">
+    <row r="67" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A67" s="3" t="n">
         <v>46203</v>
       </c>
       <c r="B67" s="4" t="s">
@@ -3759,18 +3552,18 @@
       <c r="D67" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="E67" s="3">
+      <c r="E67" s="3" t="n">
         <v>46259</v>
       </c>
-      <c r="F67" s="5">
+      <c r="F67" s="5" t="n">
         <v>860</v>
       </c>
-      <c r="G67" s="5">
+      <c r="G67" s="5" t="n">
         <v>860</v>
       </c>
       <c r="H67" s="3"/>
-      <c r="I67" s="6">
-        <v>24</v>
+      <c r="I67" s="6" t="n">
+        <v>31</v>
       </c>
       <c r="J67" s="4" t="s">
         <v>26</v>
@@ -3785,8 +3578,8 @@
       <c r="N67" s="4"/>
       <c r="O67" s="4"/>
     </row>
-    <row r="68" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="3">
+    <row r="68" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A68" s="3" t="n">
         <v>46224</v>
       </c>
       <c r="B68" s="4" t="s">
@@ -3798,18 +3591,18 @@
       <c r="D68" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="E68" s="3">
+      <c r="E68" s="3" t="n">
         <v>46259</v>
       </c>
-      <c r="F68" s="5">
+      <c r="F68" s="5" t="n">
         <v>2818.37</v>
       </c>
-      <c r="G68" s="5">
+      <c r="G68" s="5" t="n">
         <v>2818.37</v>
       </c>
       <c r="H68" s="3"/>
-      <c r="I68" s="6">
-        <v>24</v>
+      <c r="I68" s="6" t="n">
+        <v>31</v>
       </c>
       <c r="J68" s="4" t="s">
         <v>26</v>
@@ -3824,8 +3617,8 @@
       <c r="N68" s="4"/>
       <c r="O68" s="4"/>
     </row>
-    <row r="69" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="3">
+    <row r="69" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A69" s="3" t="n">
         <v>46232</v>
       </c>
       <c r="B69" s="4" t="s">
@@ -3837,18 +3630,18 @@
       <c r="D69" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="E69" s="3">
+      <c r="E69" s="3" t="n">
         <v>46262</v>
       </c>
-      <c r="F69" s="5">
+      <c r="F69" s="5" t="n">
         <v>9716</v>
       </c>
-      <c r="G69" s="5">
+      <c r="G69" s="5" t="n">
         <v>18957.86</v>
       </c>
       <c r="H69" s="3"/>
-      <c r="I69" s="6">
-        <v>21</v>
+      <c r="I69" s="6" t="n">
+        <v>28</v>
       </c>
       <c r="J69" s="4" t="s">
         <v>26</v>
@@ -3863,8 +3656,8 @@
       <c r="N69" s="4"/>
       <c r="O69" s="4"/>
     </row>
-    <row r="70" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="3">
+    <row r="70" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A70" s="3" t="n">
         <v>46224</v>
       </c>
       <c r="B70" s="4" t="s">
@@ -3876,18 +3669,18 @@
       <c r="D70" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="E70" s="3">
+      <c r="E70" s="3" t="n">
         <v>46266</v>
       </c>
-      <c r="F70" s="5">
+      <c r="F70" s="5" t="n">
         <v>2818.37</v>
       </c>
-      <c r="G70" s="5">
+      <c r="G70" s="5" t="n">
         <v>2818.37</v>
       </c>
       <c r="H70" s="3"/>
-      <c r="I70" s="6">
-        <v>17</v>
+      <c r="I70" s="6" t="n">
+        <v>24</v>
       </c>
       <c r="J70" s="4" t="s">
         <v>26</v>
@@ -3902,8 +3695,8 @@
       <c r="N70" s="4"/>
       <c r="O70" s="4"/>
     </row>
-    <row r="71" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="3">
+    <row r="71" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A71" s="3" t="n">
         <v>46227</v>
       </c>
       <c r="B71" s="4" t="s">
@@ -3915,18 +3708,18 @@
       <c r="D71" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="E71" s="3">
+      <c r="E71" s="3" t="n">
         <v>46269</v>
       </c>
-      <c r="F71" s="5">
+      <c r="F71" s="5" t="n">
         <v>23168.6</v>
       </c>
-      <c r="G71" s="5">
+      <c r="G71" s="5" t="n">
         <v>23168.6</v>
       </c>
       <c r="H71" s="3"/>
-      <c r="I71" s="6">
-        <v>14</v>
+      <c r="I71" s="6" t="n">
+        <v>21</v>
       </c>
       <c r="J71" s="4" t="s">
         <v>170</v>
@@ -3941,8 +3734,8 @@
       <c r="N71" s="4"/>
       <c r="O71" s="4"/>
     </row>
-    <row r="72" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="3">
+    <row r="72" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A72" s="3" t="n">
         <v>46225</v>
       </c>
       <c r="B72" s="4" t="s">
@@ -3954,18 +3747,18 @@
       <c r="D72" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="E72" s="3">
+      <c r="E72" s="3" t="n">
         <v>46270</v>
       </c>
-      <c r="F72" s="5">
+      <c r="F72" s="5" t="n">
         <v>7551.88</v>
       </c>
-      <c r="G72" s="5">
+      <c r="G72" s="5" t="n">
         <v>11442.87</v>
       </c>
       <c r="H72" s="3"/>
-      <c r="I72" s="6">
-        <v>13</v>
+      <c r="I72" s="6" t="n">
+        <v>20</v>
       </c>
       <c r="J72" s="4" t="s">
         <v>170</v>
@@ -3980,8 +3773,8 @@
       <c r="N72" s="4"/>
       <c r="O72" s="4"/>
     </row>
-    <row r="73" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="3">
+    <row r="73" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A73" s="3" t="n">
         <v>46227</v>
       </c>
       <c r="B73" s="4" t="s">
@@ -3993,18 +3786,18 @@
       <c r="D73" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="E73" s="3">
+      <c r="E73" s="3" t="n">
         <v>46272</v>
       </c>
-      <c r="F73" s="5">
+      <c r="F73" s="5" t="n">
         <v>4216.67</v>
       </c>
-      <c r="G73" s="5">
+      <c r="G73" s="5" t="n">
         <v>6389.24</v>
       </c>
       <c r="H73" s="3"/>
-      <c r="I73" s="6">
-        <v>11</v>
+      <c r="I73" s="6" t="n">
+        <v>18</v>
       </c>
       <c r="J73" s="4" t="s">
         <v>193</v>
@@ -4019,8 +3812,8 @@
       <c r="N73" s="4"/>
       <c r="O73" s="4"/>
     </row>
-    <row r="74" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="3">
+    <row r="74" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A74" s="3" t="n">
         <v>46232</v>
       </c>
       <c r="B74" s="4" t="s">
@@ -4032,18 +3825,18 @@
       <c r="D74" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="E74" s="3">
+      <c r="E74" s="3" t="n">
         <v>46272</v>
       </c>
-      <c r="F74" s="5">
+      <c r="F74" s="5" t="n">
         <v>9716</v>
       </c>
-      <c r="G74" s="5">
+      <c r="G74" s="5" t="n">
         <v>9716</v>
       </c>
       <c r="H74" s="3"/>
-      <c r="I74" s="6">
-        <v>11</v>
+      <c r="I74" s="6" t="n">
+        <v>18</v>
       </c>
       <c r="J74" s="4" t="s">
         <v>26</v>
@@ -4058,8 +3851,8 @@
       <c r="N74" s="4"/>
       <c r="O74" s="4"/>
     </row>
-    <row r="75" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="3">
+    <row r="75" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A75" s="3" t="n">
         <v>46224</v>
       </c>
       <c r="B75" s="4" t="s">
@@ -4071,18 +3864,18 @@
       <c r="D75" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="E75" s="3">
+      <c r="E75" s="3" t="n">
         <v>46273</v>
       </c>
-      <c r="F75" s="5">
+      <c r="F75" s="5" t="n">
         <v>2818.37</v>
       </c>
-      <c r="G75" s="5">
+      <c r="G75" s="5" t="n">
         <v>2818.37</v>
       </c>
       <c r="H75" s="3"/>
-      <c r="I75" s="6">
-        <v>10</v>
+      <c r="I75" s="6" t="n">
+        <v>17</v>
       </c>
       <c r="J75" s="4" t="s">
         <v>26</v>
@@ -4097,8 +3890,8 @@
       <c r="N75" s="4"/>
       <c r="O75" s="4"/>
     </row>
-    <row r="76" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="3">
+    <row r="76" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A76" s="3" t="n">
         <v>46223</v>
       </c>
       <c r="B76" s="4" t="s">
@@ -4110,18 +3903,18 @@
       <c r="D76" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="E76" s="3" t="n">
         <v>46273</v>
       </c>
-      <c r="F76" s="5">
+      <c r="F76" s="5" t="n">
         <v>11200</v>
       </c>
-      <c r="G76" s="5">
+      <c r="G76" s="5" t="n">
         <v>11200</v>
       </c>
       <c r="H76" s="3"/>
-      <c r="I76" s="6">
-        <v>10</v>
+      <c r="I76" s="6" t="n">
+        <v>17</v>
       </c>
       <c r="J76" s="4" t="s">
         <v>170</v>
@@ -4136,48 +3929,48 @@
       <c r="N76" s="4"/>
       <c r="O76" s="4"/>
     </row>
-    <row r="77" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="3">
-        <v>46231</v>
+    <row r="77" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A77" s="3" t="n">
+        <v>46253</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="C77" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="D77" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="D77" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="E77" s="3">
-        <v>46273</v>
-      </c>
-      <c r="F77" s="5">
-        <v>1366.66</v>
-      </c>
-      <c r="G77" s="5">
-        <v>1366.66</v>
+      <c r="E77" s="3" t="n">
+        <v>46274</v>
+      </c>
+      <c r="F77" s="5" t="n">
+        <v>10080</v>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>10080</v>
       </c>
       <c r="H77" s="3"/>
-      <c r="I77" s="6">
-        <v>10</v>
+      <c r="I77" s="6" t="n">
+        <v>16</v>
       </c>
       <c r="J77" s="4" t="s">
-        <v>26</v>
+        <v>170</v>
       </c>
       <c r="K77" s="4" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="L77" s="4"/>
       <c r="M77" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="N77" s="4"/>
       <c r="O77" s="4"/>
     </row>
-    <row r="78" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="3">
-        <v>46253</v>
+    <row r="78" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A78" s="3" t="n">
+        <v>46227</v>
       </c>
       <c r="B78" s="4" t="s">
         <v>45</v>
@@ -4186,20 +3979,20 @@
         <v>184</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="E78" s="3">
-        <v>46274</v>
-      </c>
-      <c r="F78" s="5">
-        <v>10080</v>
-      </c>
-      <c r="G78" s="5">
-        <v>10080</v>
+        <v>204</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>46276</v>
+      </c>
+      <c r="F78" s="5" t="n">
+        <v>23168.6</v>
+      </c>
+      <c r="G78" s="5" t="n">
+        <v>23168.6</v>
       </c>
       <c r="H78" s="3"/>
-      <c r="I78" s="6">
-        <v>9</v>
+      <c r="I78" s="6" t="n">
+        <v>14</v>
       </c>
       <c r="J78" s="4" t="s">
         <v>170</v>
@@ -4209,92 +4002,92 @@
       </c>
       <c r="L78" s="4"/>
       <c r="M78" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="N78" s="4"/>
       <c r="O78" s="4"/>
     </row>
-    <row r="79" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="3">
-        <v>46233</v>
+    <row r="79" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A79" s="3" t="n">
+        <v>46234</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>23</v>
+        <v>187</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="E79" s="3">
-        <v>46275</v>
-      </c>
-      <c r="F79" s="5">
-        <v>1836</v>
-      </c>
-      <c r="G79" s="5">
-        <v>1836</v>
+        <v>206</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>46279</v>
+      </c>
+      <c r="F79" s="5" t="n">
+        <v>3789.09</v>
+      </c>
+      <c r="G79" s="5" t="n">
+        <v>5741.36</v>
       </c>
       <c r="H79" s="3"/>
-      <c r="I79" s="6">
-        <v>8</v>
+      <c r="I79" s="6" t="n">
+        <v>11</v>
       </c>
       <c r="J79" s="4" t="s">
-        <v>18</v>
+        <v>170</v>
       </c>
       <c r="K79" s="4" t="s">
-        <v>71</v>
+        <v>190</v>
       </c>
       <c r="L79" s="4"/>
       <c r="M79" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="N79" s="4"/>
       <c r="O79" s="4"/>
     </row>
-    <row r="80" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="3">
-        <v>46226</v>
+    <row r="80" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A80" s="3" t="n">
+        <v>46224</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>23</v>
+        <v>172</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>209</v>
+        <v>173</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="E80" s="3">
-        <v>46275</v>
-      </c>
-      <c r="F80" s="5">
-        <v>1803.74</v>
-      </c>
-      <c r="G80" s="5">
-        <v>1803.74</v>
+        <v>208</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F80" s="5" t="n">
+        <v>2818.36</v>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>2818.36</v>
       </c>
       <c r="H80" s="3"/>
-      <c r="I80" s="6">
-        <v>8</v>
+      <c r="I80" s="6" t="n">
+        <v>10</v>
       </c>
       <c r="J80" s="4" t="s">
         <v>26</v>
       </c>
       <c r="K80" s="4" t="s">
-        <v>71</v>
+        <v>175</v>
       </c>
       <c r="L80" s="4"/>
       <c r="M80" s="4" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="N80" s="4"/>
       <c r="O80" s="4"/>
     </row>
-    <row r="81" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="3">
-        <v>46227</v>
+    <row r="81" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A81" s="3" t="n">
+        <v>46253</v>
       </c>
       <c r="B81" s="4" t="s">
         <v>45</v>
@@ -4303,20 +4096,20 @@
         <v>184</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="E81" s="3">
-        <v>46276</v>
-      </c>
-      <c r="F81" s="5">
-        <v>23168.6</v>
-      </c>
-      <c r="G81" s="5">
-        <v>23168.6</v>
+        <v>210</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F81" s="5" t="n">
+        <v>10080</v>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>10080</v>
       </c>
       <c r="H81" s="3"/>
-      <c r="I81" s="6">
-        <v>7</v>
+      <c r="I81" s="6" t="n">
+        <v>9</v>
       </c>
       <c r="J81" s="4" t="s">
         <v>170</v>
@@ -4326,153 +4119,153 @@
       </c>
       <c r="L81" s="4"/>
       <c r="M81" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="N81" s="4"/>
       <c r="O81" s="4"/>
     </row>
-    <row r="82" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="3">
-        <v>46234</v>
+    <row r="82" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A82" s="3" t="n">
+        <v>46219</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>188</v>
+        <v>212</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="E82" s="3">
-        <v>46279</v>
-      </c>
-      <c r="F82" s="5">
-        <v>3789.09</v>
-      </c>
-      <c r="G82" s="5">
-        <v>5741.36</v>
+        <v>213</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F82" s="5" t="n">
+        <v>3419.96</v>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>3419.96</v>
       </c>
       <c r="H82" s="3"/>
-      <c r="I82" s="6">
-        <v>4</v>
+      <c r="I82" s="6" t="n">
+        <v>8</v>
       </c>
       <c r="J82" s="4" t="s">
         <v>170</v>
       </c>
       <c r="K82" s="4" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="L82" s="4"/>
       <c r="M82" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="N82" s="4"/>
       <c r="O82" s="4"/>
     </row>
-    <row r="83" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="3">
-        <v>46252</v>
+    <row r="83" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A83" s="3" t="n">
+        <v>46232</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>172</v>
+        <v>15</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>216</v>
+        <v>179</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="E83" s="3">
-        <v>46280</v>
-      </c>
-      <c r="F83" s="5">
-        <v>5443.56</v>
-      </c>
-      <c r="G83" s="5">
-        <v>5443.56</v>
+        <v>215</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F83" s="5" t="n">
+        <v>9716</v>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>9716</v>
       </c>
       <c r="H83" s="3"/>
-      <c r="I83" s="6">
-        <v>3</v>
+      <c r="I83" s="6" t="n">
+        <v>8</v>
       </c>
       <c r="J83" s="4" t="s">
         <v>26</v>
       </c>
       <c r="K83" s="4" t="s">
-        <v>218</v>
+        <v>39</v>
       </c>
       <c r="L83" s="4"/>
       <c r="M83" s="4" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="N83" s="4"/>
       <c r="O83" s="4"/>
     </row>
-    <row r="84" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="3">
-        <v>46224</v>
+    <row r="84" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A84" s="3" t="n">
+        <v>46192</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>172</v>
+        <v>15</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>173</v>
+        <v>217</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="E84" s="3">
-        <v>46280</v>
-      </c>
-      <c r="F84" s="5">
-        <v>2818.36</v>
-      </c>
-      <c r="G84" s="5">
-        <v>2818.36</v>
+        <v>218</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F84" s="5" t="n">
+        <v>22750</v>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>22750</v>
       </c>
       <c r="H84" s="3"/>
-      <c r="I84" s="6">
-        <v>3</v>
+      <c r="I84" s="6" t="n">
+        <v>8</v>
       </c>
       <c r="J84" s="4" t="s">
         <v>26</v>
       </c>
       <c r="K84" s="4" t="s">
-        <v>175</v>
+        <v>39</v>
       </c>
       <c r="L84" s="4"/>
       <c r="M84" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="N84" s="4"/>
       <c r="O84" s="4"/>
     </row>
-    <row r="85" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="3">
-        <v>46253</v>
+    <row r="85" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A85" s="3" t="n">
+        <v>46223</v>
       </c>
       <c r="B85" s="4" t="s">
         <v>45</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="E85" s="3">
-        <v>46281</v>
-      </c>
-      <c r="F85" s="5">
-        <v>10080</v>
-      </c>
-      <c r="G85" s="5">
-        <v>10080</v>
+        <v>220</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>11200</v>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>11200</v>
       </c>
       <c r="H85" s="3"/>
-      <c r="I85" s="6">
-        <v>2</v>
+      <c r="I85" s="6" t="n">
+        <v>7</v>
       </c>
       <c r="J85" s="4" t="s">
         <v>170</v>
@@ -4482,246 +4275,657 @@
       </c>
       <c r="L85" s="4"/>
       <c r="M85" s="4" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="N85" s="4"/>
       <c r="O85" s="4"/>
     </row>
-    <row r="86" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="3">
-        <v>46253</v>
+    <row r="86" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A86" s="3" t="n">
+        <v>46223</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>172</v>
+        <v>23</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>224</v>
+        <v>166</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="E86" s="3">
-        <v>46281</v>
-      </c>
-      <c r="F86" s="5">
-        <v>1452.6</v>
-      </c>
-      <c r="G86" s="5">
-        <v>1452.6</v>
+        <v>222</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F86" s="5" t="n">
+        <v>5860.8</v>
+      </c>
+      <c r="G86" s="5" t="n">
+        <v>5860.8</v>
       </c>
       <c r="H86" s="3"/>
-      <c r="I86" s="6">
-        <v>2</v>
+      <c r="I86" s="6" t="n">
+        <v>7</v>
       </c>
       <c r="J86" s="4" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="K86" s="4" t="s">
-        <v>175</v>
+        <v>71</v>
       </c>
       <c r="L86" s="4"/>
       <c r="M86" s="4" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="N86" s="4"/>
       <c r="O86" s="4"/>
     </row>
-    <row r="87" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="3">
-        <v>46232</v>
+    <row r="87" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A87" s="3" t="n">
+        <v>46253</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="E87" s="3">
-        <v>46282</v>
-      </c>
-      <c r="F87" s="5">
-        <v>9716</v>
-      </c>
-      <c r="G87" s="5">
-        <v>9716</v>
+        <v>224</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F87" s="5" t="n">
+        <v>1172.16</v>
+      </c>
+      <c r="G87" s="5" t="n">
+        <v>1172.16</v>
       </c>
       <c r="H87" s="3"/>
-      <c r="I87" s="6">
-        <v>1</v>
+      <c r="I87" s="6" t="n">
+        <v>7</v>
       </c>
       <c r="J87" s="4" t="s">
-        <v>26</v>
+        <v>193</v>
       </c>
       <c r="K87" s="4" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="L87" s="4"/>
       <c r="M87" s="4" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="N87" s="4"/>
       <c r="O87" s="4"/>
     </row>
-    <row r="88" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="3">
-        <v>46192</v>
+    <row r="88" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A88" s="3" t="n">
+        <v>46227</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>229</v>
+        <v>184</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="E88" s="3">
-        <v>46282</v>
-      </c>
-      <c r="F88" s="5">
-        <v>22750</v>
-      </c>
-      <c r="G88" s="5">
-        <v>22750</v>
+        <v>226</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F88" s="5" t="n">
+        <v>23168.6</v>
+      </c>
+      <c r="G88" s="5" t="n">
+        <v>23168.6</v>
       </c>
       <c r="H88" s="3"/>
-      <c r="I88" s="6">
-        <v>1</v>
+      <c r="I88" s="6" t="n">
+        <v>7</v>
       </c>
       <c r="J88" s="4" t="s">
-        <v>26</v>
+        <v>170</v>
       </c>
       <c r="K88" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="L88" s="4"/>
       <c r="M88" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="N88" s="4"/>
       <c r="O88" s="4"/>
     </row>
-    <row r="89" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="3">
-        <v>46237</v>
+    <row r="89" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A89" s="3" t="n">
+        <v>46224</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>166</v>
+        <v>199</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="E89" s="3">
-        <v>46282</v>
-      </c>
-      <c r="F89" s="5">
-        <v>2930.4</v>
-      </c>
-      <c r="G89" s="5">
-        <v>2930.4</v>
+        <v>228</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F89" s="5" t="n">
+        <v>10666.67</v>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>10666.67</v>
       </c>
       <c r="H89" s="3"/>
-      <c r="I89" s="6">
-        <v>1</v>
+      <c r="I89" s="6" t="n">
+        <v>6</v>
       </c>
       <c r="J89" s="4" t="s">
-        <v>18</v>
+        <v>170</v>
       </c>
       <c r="K89" s="4" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="L89" s="4"/>
       <c r="M89" s="4" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="N89" s="4"/>
       <c r="O89" s="4"/>
     </row>
-    <row r="90" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="3">
-        <v>46252</v>
+    <row r="90" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A90" s="3" t="n">
+        <v>46234</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>166</v>
+        <v>199</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="E90" s="3">
-        <v>46282</v>
-      </c>
-      <c r="F90" s="5">
-        <v>3809.52</v>
-      </c>
-      <c r="G90" s="5">
-        <v>3809.52</v>
+        <v>230</v>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F90" s="5" t="n">
+        <v>6500</v>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>6500</v>
       </c>
       <c r="H90" s="3"/>
-      <c r="I90" s="6">
-        <v>1</v>
+      <c r="I90" s="6" t="n">
+        <v>6</v>
       </c>
       <c r="J90" s="4" t="s">
         <v>170</v>
       </c>
       <c r="K90" s="4" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="L90" s="4"/>
       <c r="M90" s="4" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="N90" s="4"/>
       <c r="O90" s="4"/>
     </row>
-    <row r="91" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="3">
-        <v>46219</v>
+    <row r="91" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A91" s="3" t="n">
+        <v>46234</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>172</v>
+        <v>45</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>236</v>
+        <v>199</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="E91" s="3">
-        <v>46282</v>
-      </c>
-      <c r="F91" s="5">
-        <v>3419.96</v>
-      </c>
-      <c r="G91" s="5">
-        <v>3419.96</v>
+        <v>232</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F91" s="5" t="n">
+        <v>4950.17</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>4950.17</v>
       </c>
       <c r="H91" s="3"/>
-      <c r="I91" s="6">
-        <v>1</v>
+      <c r="I91" s="6" t="n">
+        <v>6</v>
       </c>
       <c r="J91" s="4" t="s">
         <v>170</v>
       </c>
       <c r="K91" s="4" t="s">
-        <v>175</v>
+        <v>27</v>
       </c>
       <c r="L91" s="4"/>
       <c r="M91" s="4" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="N91" s="4"/>
       <c r="O91" s="4"/>
     </row>
+    <row r="92" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A92" s="3" t="n">
+        <v>46225</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>46285</v>
+      </c>
+      <c r="F92" s="5" t="n">
+        <v>7551.88</v>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>7551.88</v>
+      </c>
+      <c r="H92" s="3"/>
+      <c r="I92" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J92" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="K92" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="L92" s="4"/>
+      <c r="M92" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="N92" s="4"/>
+      <c r="O92" s="4"/>
+    </row>
+    <row r="93" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A93" s="3" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>46286</v>
+      </c>
+      <c r="F93" s="5" t="n">
+        <v>4320</v>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>4320</v>
+      </c>
+      <c r="H93" s="3"/>
+      <c r="I93" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J93" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="K93" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L93" s="4"/>
+      <c r="M93" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="N93" s="4"/>
+      <c r="O93" s="4"/>
+    </row>
+    <row r="94" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A94" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="D94" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>46287</v>
+      </c>
+      <c r="F94" s="5" t="n">
+        <v>18600</v>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>18600</v>
+      </c>
+      <c r="H94" s="3"/>
+      <c r="I94" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J94" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K94" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L94" s="4"/>
+      <c r="M94" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="N94" s="4"/>
+      <c r="O94" s="4"/>
+    </row>
+    <row r="95" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A95" s="3" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>46287</v>
+      </c>
+      <c r="F95" s="5" t="n">
+        <v>5443.56</v>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>5443.56</v>
+      </c>
+      <c r="H95" s="3"/>
+      <c r="I95" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J95" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K95" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="L95" s="4"/>
+      <c r="M95" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="N95" s="4"/>
+      <c r="O95" s="4"/>
+    </row>
+    <row r="96" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A96" s="3" t="n">
+        <v>46227</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>46287</v>
+      </c>
+      <c r="F96" s="5" t="n">
+        <v>4216.67</v>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>4216.67</v>
+      </c>
+      <c r="H96" s="3"/>
+      <c r="I96" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J96" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="K96" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="L96" s="4"/>
+      <c r="M96" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="N96" s="4"/>
+      <c r="O96" s="4"/>
+    </row>
+    <row r="97" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A97" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="E97" s="3" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F97" s="5" t="n">
+        <v>1452.6</v>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>1452.6</v>
+      </c>
+      <c r="H97" s="3"/>
+      <c r="I97" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J97" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K97" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="L97" s="4"/>
+      <c r="M97" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="N97" s="4"/>
+      <c r="O97" s="4"/>
+    </row>
+    <row r="98" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A98" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="E98" s="3" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F98" s="5" t="n">
+        <v>10080</v>
+      </c>
+      <c r="G98" s="5" t="n">
+        <v>10080</v>
+      </c>
+      <c r="H98" s="3"/>
+      <c r="I98" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J98" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="K98" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L98" s="4"/>
+      <c r="M98" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="N98" s="4"/>
+      <c r="O98" s="4"/>
+    </row>
+    <row r="99" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A99" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F99" s="5" t="n">
+        <v>3640</v>
+      </c>
+      <c r="G99" s="5" t="n">
+        <v>3640</v>
+      </c>
+      <c r="H99" s="3"/>
+      <c r="I99" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J99" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="K99" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="L99" s="4"/>
+      <c r="M99" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="N99" s="4"/>
+      <c r="O99" s="4"/>
+    </row>
+    <row r="100" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A100" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="D100" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F100" s="5" t="n">
+        <v>1660.33</v>
+      </c>
+      <c r="G100" s="5" t="n">
+        <v>1660.33</v>
+      </c>
+      <c r="H100" s="3"/>
+      <c r="I100" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J100" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K100" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="L100" s="4"/>
+      <c r="M100" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="N100" s="4"/>
+      <c r="O100" s="4"/>
+    </row>
+    <row r="101" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A101" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="D101" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F101" s="5" t="n">
+        <v>6265</v>
+      </c>
+      <c r="G101" s="5" t="n">
+        <v>6265</v>
+      </c>
+      <c r="H101" s="3"/>
+      <c r="I101" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J101" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="K101" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="L101" s="4"/>
+      <c r="M101" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="N101" s="4"/>
+      <c r="O101" s="4"/>
+    </row>
+    <row r="102" customHeight="true" ht="13.5" customFormat="true" s="1">
+      <c r="A102" s="7"/>
+      <c r="B102" s="8"/>
+      <c r="C102" s="8"/>
+      <c r="D102" s="8"/>
+      <c r="E102" s="8"/>
+      <c r="F102" s="9" t="n">
+        <v>576377.62</v>
+      </c>
+      <c r="G102" s="9" t="n">
+        <v>609280.9</v>
+      </c>
+      <c r="H102" s="8"/>
+      <c r="I102" s="8"/>
+      <c r="J102" s="8"/>
+      <c r="K102" s="8"/>
+      <c r="L102" s="8"/>
+      <c r="M102" s="8"/>
+      <c r="N102" s="8"/>
+      <c r="O102" s="10"/>
+    </row>
   </sheetData>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup orientation="default" cellComments="none"/>
 </worksheet>
 </file>
--- a/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
+++ b/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
@@ -1,19 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WINDOWS\Desktop\dados planilhas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4441FE2C-9A11-40BB-B10C-EFCBF2BF743D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0" showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="XLS_Grid_LANCAMENTO A RECEBER" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr refMode="A1"/>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="297">
   <si>
     <t>Dt.Emissão</t>
   </si>
@@ -651,15 +663,6 @@
     <t>70791157100010080000001121205064100656766196</t>
   </si>
   <si>
-    <t>M. A. M COMERCIO E DISTRIBUIDORA DE MEDICAMENTOS L</t>
-  </si>
-  <si>
-    <t>01006872.6</t>
-  </si>
-  <si>
-    <t>70799157200003419960001121205064100656763599</t>
-  </si>
-  <si>
     <t>01007005.3</t>
   </si>
   <si>
@@ -681,12 +684,6 @@
     <t>70792157300011200000001121205064100656763888</t>
   </si>
   <si>
-    <t>01006939.3</t>
-  </si>
-  <si>
-    <t>00194157300005860800000003473568000003140517</t>
-  </si>
-  <si>
     <t>01007197.1</t>
   </si>
   <si>
@@ -790,36 +787,164 @@
   </si>
   <si>
     <t>70797157900006265000001121205064100656766642</t>
+  </si>
+  <si>
+    <t>FELIPE AQUINO - MT</t>
+  </si>
+  <si>
+    <t>FAMA DISTRIBUIDORA HOSPITALAR LTDA</t>
+  </si>
+  <si>
+    <t>01007265.1</t>
+  </si>
+  <si>
+    <t>MT</t>
+  </si>
+  <si>
+    <t>00198158000007694400000003473568000003158817</t>
+  </si>
+  <si>
+    <t>01007249.1</t>
+  </si>
+  <si>
+    <t>70793158000011660110001121205064100656766915</t>
+  </si>
+  <si>
+    <t>01007224.1</t>
+  </si>
+  <si>
+    <t>70795158000002992000001121205064100656766857</t>
+  </si>
+  <si>
+    <t>01006998.2</t>
+  </si>
+  <si>
+    <t>00191158100006500000000003473568000003144317</t>
+  </si>
+  <si>
+    <t>LEANDRA LUIZA SILVA - AM</t>
+  </si>
+  <si>
+    <t>JM COMERCIO DE PRODUTOS FARMACEUTICOS LTDA</t>
+  </si>
+  <si>
+    <t>01007186.1</t>
+  </si>
+  <si>
+    <t>AM</t>
+  </si>
+  <si>
+    <t>70796158200004689220001121205064100656766782</t>
+  </si>
+  <si>
+    <t>01007005.4</t>
+  </si>
+  <si>
+    <t>00197158200009716000000003473568000003146117</t>
+  </si>
+  <si>
+    <t>FERMATA LTDA</t>
+  </si>
+  <si>
+    <t>01006989.2</t>
+  </si>
+  <si>
+    <t>70795158200004082050001121205064100656764191</t>
+  </si>
+  <si>
+    <t>LICIMASTER DIST. DE MED. E PRODUTOS MEDICO</t>
+  </si>
+  <si>
+    <t>01007094.4</t>
+  </si>
+  <si>
+    <t>34191158300003599851090002612318120992717000</t>
+  </si>
+  <si>
+    <t>01006978.6</t>
+  </si>
+  <si>
+    <t>23796158300001513130435090000000116500304920</t>
+  </si>
+  <si>
+    <t>01006877.3</t>
+  </si>
+  <si>
+    <t>23797158300006265000435090000000110700304920</t>
+  </si>
+  <si>
+    <t>01007125.5</t>
+  </si>
+  <si>
+    <t>70799158300004320000001121205064100656765131</t>
+  </si>
+  <si>
+    <t>01006922.3</t>
+  </si>
+  <si>
+    <t>70798158300011200000001121205064100656763896</t>
+  </si>
+  <si>
+    <t>R5 SOLUCOES EM SAUDE LTDA</t>
+  </si>
+  <si>
+    <t>01007136.3</t>
+  </si>
+  <si>
+    <t>70795158300002521250001121205064100656765842</t>
+  </si>
+  <si>
+    <t>ATACAMED COMERCIO LTDA</t>
+  </si>
+  <si>
+    <t>01007274.1</t>
+  </si>
+  <si>
+    <t>34192158300001664001090002623468120992717000</t>
+  </si>
+  <si>
+    <t>01007117.1</t>
+  </si>
+  <si>
+    <t>70791158300023355330001121205064100656765669</t>
+  </si>
+  <si>
+    <t>OMNIELMASTER HEMOMED REPRESENTACAO</t>
+  </si>
+  <si>
+    <t>01007164.3</t>
+  </si>
+  <si>
+    <t>34199158300002070201090002615878120992717000</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt formatCode="dd/MM/yyyy" numFmtId="164"/>
-    <numFmt formatCode="###,###,##0.00" numFmtId="165"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="###,###,##0.00"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
       <charset val="1"/>
     </font>
     <font>
+      <sz val="8"/>
       <color rgb="FF000000"/>
-      <sz val="8"/>
       <name val="Arial"/>
       <charset val="1"/>
     </font>
     <font>
+      <sz val="8"/>
       <color rgb="FF000000"/>
-      <sz val="8"/>
       <name val="Segoe UI"/>
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -838,14 +963,8 @@
         <bgColor rgb="FF7EA6D1"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0F0F0"/>
-        <bgColor rgb="FFF0F0F0"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="5">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -868,124 +987,386 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFA0A0A0"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FFA0A0A0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFA0A0A0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFA0A0A0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFA0A0A0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFA0A0A0"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFA0A0A0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFA0A0A0"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" shrinkToFit="false" wrapText="false"/>
-      <protection hidden="false" locked="true"/>
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="164" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="165" xfId="0">
-      <alignment horizontal="right" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="right" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="2" fillId="4" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="3" fillId="4" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="4" fontId="1" numFmtId="165" xfId="0">
-      <alignment horizontal="right" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="4" fillId="4" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="true" summaryRight="true"/>
-  </sheetPr>
-  <dimension ref="A1:O102"/>
-  <sheetFormatPr defaultColWidth="12.140625" customHeight="true" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:O115"/>
+  <sheetFormatPr defaultColWidth="12.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col max="1" min="1" style="1" width="11.85546875" customWidth="true"/>
-    <col max="2" min="2" style="1" width="22.28515625" customWidth="true"/>
-    <col max="3" min="3" style="1" width="30.28515625" customWidth="true"/>
-    <col max="4" min="4" style="1" width="12.85546875" customWidth="true"/>
-    <col max="5" min="5" style="1" width="24.7109375" customWidth="true"/>
-    <col max="6" min="6" style="1" width="9.140625" customWidth="true"/>
-    <col max="7" min="7" style="1" width="27.28515625" customWidth="true"/>
-    <col max="8" min="8" style="1" width="28.140625" customWidth="true"/>
-    <col max="9" min="9" style="1" width="9.140625" customWidth="true"/>
-    <col max="10" min="10" style="1" width="26.28515625" customWidth="true"/>
-    <col max="11" min="11" style="1" width="3.7109375" customWidth="true"/>
-    <col max="12" min="12" style="1" width="43.42578125" customWidth="true"/>
-    <col max="13" min="13" style="1" width="60.5703125" customWidth="true"/>
-    <col max="14" min="14" style="1" width="26.28515625" customWidth="true"/>
-    <col max="15" min="15" style="1" width="43.42578125" customWidth="true"/>
-    <col max="16384" min="16" style="1" width="12.140625"/>
+    <col min="1" max="1" width="11.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="30.28515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="24.7109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="27.28515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="28.140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="9.140625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="26.28515625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="3.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="43.42578125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="60.5703125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="26.28515625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="43.42578125" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="12.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="true" ht="27" customFormat="true" s="1">
+    <row r="1" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1032,8 +1413,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A2" s="3" t="n">
+    <row r="2" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
         <v>45296</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -1045,18 +1426,18 @@
       <c r="D2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="3">
         <v>45326</v>
       </c>
-      <c r="F2" s="5" t="n">
+      <c r="F2" s="5">
         <v>5418</v>
       </c>
-      <c r="G2" s="5" t="n">
-        <v>9391.78</v>
+      <c r="G2" s="5">
+        <v>9391.7800000000007</v>
       </c>
       <c r="H2" s="3"/>
-      <c r="I2" s="6" t="n">
-        <v>964</v>
+      <c r="I2" s="6">
+        <v>968</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>18</v>
@@ -1071,8 +1452,8 @@
       <c r="N2" s="4"/>
       <c r="O2" s="4"/>
     </row>
-    <row r="3" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A3" s="3" t="n">
+    <row r="3" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
         <v>45296</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -1084,18 +1465,18 @@
       <c r="D3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="3">
         <v>45346</v>
       </c>
-      <c r="F3" s="5" t="n">
+      <c r="F3" s="5">
         <v>5418</v>
       </c>
-      <c r="G3" s="5" t="n">
+      <c r="G3" s="5">
         <v>5418</v>
       </c>
       <c r="H3" s="3"/>
-      <c r="I3" s="6" t="n">
-        <v>944</v>
+      <c r="I3" s="6">
+        <v>948</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>18</v>
@@ -1110,8 +1491,8 @@
       <c r="N3" s="4"/>
       <c r="O3" s="4"/>
     </row>
-    <row r="4" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A4" s="3" t="n">
+    <row r="4" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
         <v>45322</v>
       </c>
       <c r="B4" s="4" t="s">
@@ -1123,18 +1504,18 @@
       <c r="D4" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="3">
         <v>45350</v>
       </c>
-      <c r="F4" s="5" t="n">
+      <c r="F4" s="5">
         <v>816</v>
       </c>
-      <c r="G4" s="5" t="n">
-        <v>1264.87</v>
+      <c r="G4" s="5">
+        <v>1264.8699999999999</v>
       </c>
       <c r="H4" s="3"/>
-      <c r="I4" s="6" t="n">
-        <v>940</v>
+      <c r="I4" s="6">
+        <v>944</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>26</v>
@@ -1149,8 +1530,8 @@
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
     </row>
-    <row r="5" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A5" s="3" t="n">
+    <row r="5" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
         <v>45296</v>
       </c>
       <c r="B5" s="4" t="s">
@@ -1162,18 +1543,18 @@
       <c r="D5" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="3">
         <v>45356</v>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="F5" s="5">
         <v>5418</v>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="G5" s="5">
         <v>5418</v>
       </c>
       <c r="H5" s="3"/>
-      <c r="I5" s="6" t="n">
-        <v>934</v>
+      <c r="I5" s="6">
+        <v>938</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>18</v>
@@ -1188,8 +1569,8 @@
       <c r="N5" s="4"/>
       <c r="O5" s="4"/>
     </row>
-    <row r="6" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A6" s="3" t="n">
+    <row r="6" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
         <v>45306</v>
       </c>
       <c r="B6" s="4" t="s">
@@ -1201,18 +1582,18 @@
       <c r="D6" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="3">
         <v>45362</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="5">
         <v>384</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="G6" s="5">
         <v>384</v>
       </c>
       <c r="H6" s="3"/>
-      <c r="I6" s="6" t="n">
-        <v>928</v>
+      <c r="I6" s="6">
+        <v>932</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>26</v>
@@ -1227,8 +1608,8 @@
       <c r="N6" s="4"/>
       <c r="O6" s="4"/>
     </row>
-    <row r="7" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A7" s="3" t="n">
+    <row r="7" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
         <v>45322</v>
       </c>
       <c r="B7" s="4" t="s">
@@ -1240,18 +1621,18 @@
       <c r="D7" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="3">
         <v>45364</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F7" s="5">
         <v>816</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="G7" s="5">
         <v>816</v>
       </c>
       <c r="H7" s="3"/>
-      <c r="I7" s="6" t="n">
-        <v>926</v>
+      <c r="I7" s="6">
+        <v>930</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>26</v>
@@ -1266,8 +1647,8 @@
       <c r="N7" s="4"/>
       <c r="O7" s="4"/>
     </row>
-    <row r="8" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A8" s="3" t="n">
+    <row r="8" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
         <v>45322</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -1279,18 +1660,18 @@
       <c r="D8" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="3">
         <v>45378</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F8" s="5">
         <v>816</v>
       </c>
-      <c r="G8" s="5" t="n">
+      <c r="G8" s="5">
         <v>816</v>
       </c>
       <c r="H8" s="3"/>
-      <c r="I8" s="6" t="n">
-        <v>912</v>
+      <c r="I8" s="6">
+        <v>916</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>26</v>
@@ -1305,8 +1686,8 @@
       <c r="N8" s="4"/>
       <c r="O8" s="4"/>
     </row>
-    <row r="9" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A9" s="3" t="n">
+    <row r="9" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
         <v>45433</v>
       </c>
       <c r="B9" s="4" t="s">
@@ -1318,18 +1699,18 @@
       <c r="D9" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" s="3">
         <v>45463</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="F9" s="5">
         <v>873.6</v>
       </c>
-      <c r="G9" s="5" t="n">
+      <c r="G9" s="5">
         <v>1674.52</v>
       </c>
       <c r="H9" s="3"/>
-      <c r="I9" s="6" t="n">
-        <v>827</v>
+      <c r="I9" s="6">
+        <v>831</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>18</v>
@@ -1344,8 +1725,8 @@
       <c r="N9" s="4"/>
       <c r="O9" s="4"/>
     </row>
-    <row r="10" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A10" s="3" t="n">
+    <row r="10" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
         <v>45433</v>
       </c>
       <c r="B10" s="4" t="s">
@@ -1357,18 +1738,18 @@
       <c r="D10" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="E10" s="3">
         <v>45493</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="F10" s="5">
         <v>873.6</v>
       </c>
-      <c r="G10" s="5" t="n">
+      <c r="G10" s="5">
         <v>873.6</v>
       </c>
       <c r="H10" s="3"/>
-      <c r="I10" s="6" t="n">
-        <v>797</v>
+      <c r="I10" s="6">
+        <v>801</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>18</v>
@@ -1383,8 +1764,8 @@
       <c r="N10" s="4"/>
       <c r="O10" s="4"/>
     </row>
-    <row r="11" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A11" s="3" t="n">
+    <row r="11" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
         <v>45433</v>
       </c>
       <c r="B11" s="4" t="s">
@@ -1396,18 +1777,18 @@
       <c r="D11" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="E11" s="3">
         <v>45523</v>
       </c>
-      <c r="F11" s="5" t="n">
+      <c r="F11" s="5">
         <v>873.6</v>
       </c>
-      <c r="G11" s="5" t="n">
+      <c r="G11" s="5">
         <v>873.6</v>
       </c>
       <c r="H11" s="3"/>
-      <c r="I11" s="6" t="n">
-        <v>767</v>
+      <c r="I11" s="6">
+        <v>771</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>18</v>
@@ -1422,8 +1803,8 @@
       <c r="N11" s="4"/>
       <c r="O11" s="4"/>
     </row>
-    <row r="12" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A12" s="3" t="n">
+    <row r="12" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
         <v>45558</v>
       </c>
       <c r="B12" s="4" t="s">
@@ -1435,18 +1816,18 @@
       <c r="D12" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="E12" s="3">
         <v>45600</v>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="F12" s="5">
         <v>2000</v>
       </c>
-      <c r="G12" s="5" t="n">
+      <c r="G12" s="5">
         <v>2000</v>
       </c>
       <c r="H12" s="3"/>
-      <c r="I12" s="6" t="n">
-        <v>690</v>
+      <c r="I12" s="6">
+        <v>694</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>18</v>
@@ -1461,8 +1842,8 @@
       <c r="N12" s="4"/>
       <c r="O12" s="4"/>
     </row>
-    <row r="13" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A13" s="3" t="n">
+    <row r="13" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3">
         <v>45558</v>
       </c>
       <c r="B13" s="4" t="s">
@@ -1474,18 +1855,18 @@
       <c r="D13" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="E13" s="3">
         <v>45607</v>
       </c>
-      <c r="F13" s="5" t="n">
+      <c r="F13" s="5">
         <v>2000</v>
       </c>
-      <c r="G13" s="5" t="n">
+      <c r="G13" s="5">
         <v>3204.34</v>
       </c>
       <c r="H13" s="3"/>
-      <c r="I13" s="6" t="n">
-        <v>683</v>
+      <c r="I13" s="6">
+        <v>687</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>18</v>
@@ -1500,8 +1881,8 @@
       <c r="N13" s="4"/>
       <c r="O13" s="4"/>
     </row>
-    <row r="14" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A14" s="3" t="n">
+    <row r="14" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="3">
         <v>45552</v>
       </c>
       <c r="B14" s="4" t="s">
@@ -1513,18 +1894,18 @@
       <c r="D14" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="E14" s="3">
         <v>45608</v>
       </c>
-      <c r="F14" s="5" t="n">
-        <v>4439.9</v>
-      </c>
-      <c r="G14" s="5" t="n">
-        <v>4439.9</v>
+      <c r="F14" s="5">
+        <v>4439.8999999999996</v>
+      </c>
+      <c r="G14" s="5">
+        <v>4439.8999999999996</v>
       </c>
       <c r="H14" s="3"/>
-      <c r="I14" s="6" t="n">
-        <v>682</v>
+      <c r="I14" s="6">
+        <v>686</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>18</v>
@@ -1539,8 +1920,8 @@
       <c r="N14" s="4"/>
       <c r="O14" s="4"/>
     </row>
-    <row r="15" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A15" s="3" t="n">
+    <row r="15" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3">
         <v>45558</v>
       </c>
       <c r="B15" s="4" t="s">
@@ -1552,18 +1933,18 @@
       <c r="D15" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="E15" s="3">
         <v>45614</v>
       </c>
-      <c r="F15" s="5" t="n">
+      <c r="F15" s="5">
         <v>2000</v>
       </c>
-      <c r="G15" s="5" t="n">
+      <c r="G15" s="5">
         <v>2000</v>
       </c>
       <c r="H15" s="3"/>
-      <c r="I15" s="6" t="n">
-        <v>676</v>
+      <c r="I15" s="6">
+        <v>680</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>18</v>
@@ -1578,8 +1959,8 @@
       <c r="N15" s="4"/>
       <c r="O15" s="4"/>
     </row>
-    <row r="16" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A16" s="3" t="n">
+    <row r="16" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="3">
         <v>45546</v>
       </c>
       <c r="B16" s="4" t="s">
@@ -1591,18 +1972,18 @@
       <c r="D16" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="E16" s="3">
         <v>45615</v>
       </c>
-      <c r="F16" s="5" t="n">
-        <v>1216.86</v>
-      </c>
-      <c r="G16" s="5" t="n">
-        <v>1216.86</v>
+      <c r="F16" s="5">
+        <v>1216.8599999999999</v>
+      </c>
+      <c r="G16" s="5">
+        <v>1216.8599999999999</v>
       </c>
       <c r="H16" s="3"/>
-      <c r="I16" s="6" t="n">
-        <v>675</v>
+      <c r="I16" s="6">
+        <v>679</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>18</v>
@@ -1617,8 +1998,8 @@
       <c r="N16" s="4"/>
       <c r="O16" s="4"/>
     </row>
-    <row r="17" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A17" s="3" t="n">
+    <row r="17" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3">
         <v>45548</v>
       </c>
       <c r="B17" s="4" t="s">
@@ -1630,18 +2011,18 @@
       <c r="D17" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="E17" s="3">
         <v>45617</v>
       </c>
-      <c r="F17" s="5" t="n">
+      <c r="F17" s="5">
         <v>1843.87</v>
       </c>
-      <c r="G17" s="5" t="n">
+      <c r="G17" s="5">
         <v>1843.87</v>
       </c>
       <c r="H17" s="3"/>
-      <c r="I17" s="6" t="n">
-        <v>673</v>
+      <c r="I17" s="6">
+        <v>677</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>18</v>
@@ -1656,8 +2037,8 @@
       <c r="N17" s="4"/>
       <c r="O17" s="4"/>
     </row>
-    <row r="18" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A18" s="3" t="n">
+    <row r="18" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="3">
         <v>45546</v>
       </c>
       <c r="B18" s="4" t="s">
@@ -1669,18 +2050,18 @@
       <c r="D18" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="E18" s="3">
         <v>45622</v>
       </c>
-      <c r="F18" s="5" t="n">
-        <v>1216.86</v>
-      </c>
-      <c r="G18" s="5" t="n">
-        <v>1216.86</v>
+      <c r="F18" s="5">
+        <v>1216.8599999999999</v>
+      </c>
+      <c r="G18" s="5">
+        <v>1216.8599999999999</v>
       </c>
       <c r="H18" s="3"/>
-      <c r="I18" s="6" t="n">
-        <v>668</v>
+      <c r="I18" s="6">
+        <v>672</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>18</v>
@@ -1695,8 +2076,8 @@
       <c r="N18" s="4"/>
       <c r="O18" s="4"/>
     </row>
-    <row r="19" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A19" s="3" t="n">
+    <row r="19" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
         <v>45552</v>
       </c>
       <c r="B19" s="4" t="s">
@@ -1708,18 +2089,18 @@
       <c r="D19" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="E19" s="3">
         <v>45622</v>
       </c>
-      <c r="F19" s="5" t="n">
-        <v>4439.9</v>
-      </c>
-      <c r="G19" s="5" t="n">
-        <v>4439.9</v>
+      <c r="F19" s="5">
+        <v>4439.8999999999996</v>
+      </c>
+      <c r="G19" s="5">
+        <v>4439.8999999999996</v>
       </c>
       <c r="H19" s="3"/>
-      <c r="I19" s="6" t="n">
-        <v>668</v>
+      <c r="I19" s="6">
+        <v>672</v>
       </c>
       <c r="J19" s="4" t="s">
         <v>18</v>
@@ -1734,8 +2115,8 @@
       <c r="N19" s="4"/>
       <c r="O19" s="4"/>
     </row>
-    <row r="20" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A20" s="3" t="n">
+    <row r="20" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
         <v>45548</v>
       </c>
       <c r="B20" s="4" t="s">
@@ -1747,18 +2128,18 @@
       <c r="D20" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="E20" s="3">
         <v>45624</v>
       </c>
-      <c r="F20" s="5" t="n">
+      <c r="F20" s="5">
         <v>1843.88</v>
       </c>
-      <c r="G20" s="5" t="n">
+      <c r="G20" s="5">
         <v>1843.88</v>
       </c>
       <c r="H20" s="3"/>
-      <c r="I20" s="6" t="n">
-        <v>666</v>
+      <c r="I20" s="6">
+        <v>670</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>18</v>
@@ -1773,8 +2154,8 @@
       <c r="N20" s="4"/>
       <c r="O20" s="4"/>
     </row>
-    <row r="21" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A21" s="3" t="n">
+    <row r="21" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="3">
         <v>45632</v>
       </c>
       <c r="B21" s="4" t="s">
@@ -1786,18 +2167,18 @@
       <c r="D21" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="E21" s="3">
         <v>45688</v>
       </c>
-      <c r="F21" s="5" t="n">
-        <v>1118.4</v>
-      </c>
-      <c r="G21" s="5" t="n">
-        <v>1118.4</v>
+      <c r="F21" s="5">
+        <v>1118.4000000000001</v>
+      </c>
+      <c r="G21" s="5">
+        <v>1118.4000000000001</v>
       </c>
       <c r="H21" s="3"/>
-      <c r="I21" s="6" t="n">
-        <v>602</v>
+      <c r="I21" s="6">
+        <v>606</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>18</v>
@@ -1812,8 +2193,8 @@
       <c r="N21" s="4"/>
       <c r="O21" s="4"/>
     </row>
-    <row r="22" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A22" s="3" t="n">
+    <row r="22" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="3">
         <v>45646</v>
       </c>
       <c r="B22" s="4" t="s">
@@ -1825,18 +2206,18 @@
       <c r="D22" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="E22" s="3">
         <v>45695</v>
       </c>
-      <c r="F22" s="5" t="n">
+      <c r="F22" s="5">
         <v>3296.8</v>
       </c>
-      <c r="G22" s="5" t="n">
+      <c r="G22" s="5">
         <v>3296.8</v>
       </c>
       <c r="H22" s="3"/>
-      <c r="I22" s="6" t="n">
-        <v>595</v>
+      <c r="I22" s="6">
+        <v>599</v>
       </c>
       <c r="J22" s="4" t="s">
         <v>18</v>
@@ -1851,8 +2232,8 @@
       <c r="N22" s="4"/>
       <c r="O22" s="4"/>
     </row>
-    <row r="23" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A23" s="3" t="n">
+    <row r="23" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="3">
         <v>45636</v>
       </c>
       <c r="B23" s="4" t="s">
@@ -1864,18 +2245,18 @@
       <c r="D23" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="E23" s="3">
         <v>45699</v>
       </c>
-      <c r="F23" s="5" t="n">
+      <c r="F23" s="5">
         <v>2330</v>
       </c>
-      <c r="G23" s="5" t="n">
+      <c r="G23" s="5">
         <v>2330</v>
       </c>
       <c r="H23" s="3"/>
-      <c r="I23" s="6" t="n">
-        <v>591</v>
+      <c r="I23" s="6">
+        <v>595</v>
       </c>
       <c r="J23" s="4" t="s">
         <v>18</v>
@@ -1890,8 +2271,8 @@
       <c r="N23" s="4"/>
       <c r="O23" s="4"/>
     </row>
-    <row r="24" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A24" s="3" t="n">
+    <row r="24" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="3">
         <v>45646</v>
       </c>
       <c r="B24" s="4" t="s">
@@ -1903,18 +2284,18 @@
       <c r="D24" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="E24" s="3">
         <v>45702</v>
       </c>
-      <c r="F24" s="5" t="n">
+      <c r="F24" s="5">
         <v>3296.8</v>
       </c>
-      <c r="G24" s="5" t="n">
+      <c r="G24" s="5">
         <v>3296.8</v>
       </c>
       <c r="H24" s="3"/>
-      <c r="I24" s="6" t="n">
-        <v>588</v>
+      <c r="I24" s="6">
+        <v>592</v>
       </c>
       <c r="J24" s="4" t="s">
         <v>18</v>
@@ -1929,8 +2310,8 @@
       <c r="N24" s="4"/>
       <c r="O24" s="4"/>
     </row>
-    <row r="25" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A25" s="3" t="n">
+    <row r="25" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="3">
         <v>45677</v>
       </c>
       <c r="B25" s="4" t="s">
@@ -1942,18 +2323,18 @@
       <c r="D25" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="E25" s="3">
         <v>45705</v>
       </c>
-      <c r="F25" s="5" t="n">
+      <c r="F25" s="5">
         <v>2541</v>
       </c>
-      <c r="G25" s="5" t="n">
+      <c r="G25" s="5">
         <v>2541</v>
       </c>
       <c r="H25" s="3"/>
-      <c r="I25" s="6" t="n">
-        <v>585</v>
+      <c r="I25" s="6">
+        <v>589</v>
       </c>
       <c r="J25" s="4" t="s">
         <v>26</v>
@@ -1968,8 +2349,8 @@
       <c r="N25" s="4"/>
       <c r="O25" s="4"/>
     </row>
-    <row r="26" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A26" s="3" t="n">
+    <row r="26" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="3">
         <v>45646</v>
       </c>
       <c r="B26" s="4" t="s">
@@ -1981,18 +2362,18 @@
       <c r="D26" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="E26" s="3">
         <v>45709</v>
       </c>
-      <c r="F26" s="5" t="n">
+      <c r="F26" s="5">
         <v>3296.8</v>
       </c>
-      <c r="G26" s="5" t="n">
+      <c r="G26" s="5">
         <v>3296.8</v>
       </c>
       <c r="H26" s="3"/>
-      <c r="I26" s="6" t="n">
-        <v>581</v>
+      <c r="I26" s="6">
+        <v>585</v>
       </c>
       <c r="J26" s="4" t="s">
         <v>18</v>
@@ -2007,8 +2388,8 @@
       <c r="N26" s="4"/>
       <c r="O26" s="4"/>
     </row>
-    <row r="27" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A27" s="3" t="n">
+    <row r="27" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="3">
         <v>45677</v>
       </c>
       <c r="B27" s="4" t="s">
@@ -2020,18 +2401,18 @@
       <c r="D27" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="E27" s="3">
         <v>45712</v>
       </c>
-      <c r="F27" s="5" t="n">
+      <c r="F27" s="5">
         <v>2541</v>
       </c>
-      <c r="G27" s="5" t="n">
+      <c r="G27" s="5">
         <v>2541</v>
       </c>
       <c r="H27" s="3"/>
-      <c r="I27" s="6" t="n">
-        <v>578</v>
+      <c r="I27" s="6">
+        <v>582</v>
       </c>
       <c r="J27" s="4" t="s">
         <v>26</v>
@@ -2046,8 +2427,8 @@
       <c r="N27" s="4"/>
       <c r="O27" s="4"/>
     </row>
-    <row r="28" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A28" s="3" t="n">
+    <row r="28" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="3">
         <v>45677</v>
       </c>
       <c r="B28" s="4" t="s">
@@ -2059,18 +2440,18 @@
       <c r="D28" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="E28" s="3">
         <v>45726</v>
       </c>
-      <c r="F28" s="5" t="n">
+      <c r="F28" s="5">
         <v>2541</v>
       </c>
-      <c r="G28" s="5" t="n">
+      <c r="G28" s="5">
         <v>2541</v>
       </c>
       <c r="H28" s="3"/>
-      <c r="I28" s="6" t="n">
-        <v>564</v>
+      <c r="I28" s="6">
+        <v>568</v>
       </c>
       <c r="J28" s="4" t="s">
         <v>26</v>
@@ -2085,8 +2466,8 @@
       <c r="N28" s="4"/>
       <c r="O28" s="4"/>
     </row>
-    <row r="29" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A29" s="3" t="n">
+    <row r="29" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="3">
         <v>45699</v>
       </c>
       <c r="B29" s="4" t="s">
@@ -2098,18 +2479,18 @@
       <c r="D29" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="E29" s="3">
         <v>45727</v>
       </c>
-      <c r="F29" s="5" t="n">
+      <c r="F29" s="5">
         <v>7562.78</v>
       </c>
-      <c r="G29" s="5" t="n">
+      <c r="G29" s="5">
         <v>7562.78</v>
       </c>
       <c r="H29" s="3"/>
-      <c r="I29" s="6" t="n">
-        <v>563</v>
+      <c r="I29" s="6">
+        <v>567</v>
       </c>
       <c r="J29" s="4" t="s">
         <v>18</v>
@@ -2124,8 +2505,8 @@
       <c r="N29" s="4"/>
       <c r="O29" s="4"/>
     </row>
-    <row r="30" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A30" s="3" t="n">
+    <row r="30" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="3">
         <v>45699</v>
       </c>
       <c r="B30" s="4" t="s">
@@ -2137,18 +2518,18 @@
       <c r="D30" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="E30" s="3">
         <v>45734</v>
       </c>
-      <c r="F30" s="5" t="n">
+      <c r="F30" s="5">
         <v>7562.78</v>
       </c>
-      <c r="G30" s="5" t="n">
+      <c r="G30" s="5">
         <v>7562.78</v>
       </c>
       <c r="H30" s="3"/>
-      <c r="I30" s="6" t="n">
-        <v>556</v>
+      <c r="I30" s="6">
+        <v>560</v>
       </c>
       <c r="J30" s="4" t="s">
         <v>18</v>
@@ -2163,8 +2544,8 @@
       <c r="N30" s="4"/>
       <c r="O30" s="4"/>
     </row>
-    <row r="31" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A31" s="3" t="n">
+    <row r="31" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="3">
         <v>45699</v>
       </c>
       <c r="B31" s="4" t="s">
@@ -2176,18 +2557,18 @@
       <c r="D31" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="E31" s="3">
         <v>45734</v>
       </c>
-      <c r="F31" s="5" t="n">
+      <c r="F31" s="5">
         <v>1154.56</v>
       </c>
-      <c r="G31" s="5" t="n">
+      <c r="G31" s="5">
         <v>1154.56</v>
       </c>
       <c r="H31" s="3"/>
-      <c r="I31" s="6" t="n">
-        <v>556</v>
+      <c r="I31" s="6">
+        <v>560</v>
       </c>
       <c r="J31" s="4" t="s">
         <v>18</v>
@@ -2202,8 +2583,8 @@
       <c r="N31" s="4"/>
       <c r="O31" s="4"/>
     </row>
-    <row r="32" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A32" s="3" t="n">
+    <row r="32" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="3">
         <v>45677</v>
       </c>
       <c r="B32" s="4" t="s">
@@ -2215,18 +2596,18 @@
       <c r="D32" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="E32" s="3">
         <v>45740</v>
       </c>
-      <c r="F32" s="5" t="n">
+      <c r="F32" s="5">
         <v>2541</v>
       </c>
-      <c r="G32" s="5" t="n">
+      <c r="G32" s="5">
         <v>2541</v>
       </c>
       <c r="H32" s="3"/>
-      <c r="I32" s="6" t="n">
-        <v>550</v>
+      <c r="I32" s="6">
+        <v>554</v>
       </c>
       <c r="J32" s="4" t="s">
         <v>26</v>
@@ -2241,8 +2622,8 @@
       <c r="N32" s="4"/>
       <c r="O32" s="4"/>
     </row>
-    <row r="33" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A33" s="3" t="n">
+    <row r="33" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="3">
         <v>45699</v>
       </c>
       <c r="B33" s="4" t="s">
@@ -2254,18 +2635,18 @@
       <c r="D33" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="E33" s="3">
         <v>45741</v>
       </c>
-      <c r="F33" s="5" t="n">
+      <c r="F33" s="5">
         <v>7562.78</v>
       </c>
-      <c r="G33" s="5" t="n">
+      <c r="G33" s="5">
         <v>7562.78</v>
       </c>
       <c r="H33" s="3"/>
-      <c r="I33" s="6" t="n">
-        <v>549</v>
+      <c r="I33" s="6">
+        <v>553</v>
       </c>
       <c r="J33" s="4" t="s">
         <v>18</v>
@@ -2280,8 +2661,8 @@
       <c r="N33" s="4"/>
       <c r="O33" s="4"/>
     </row>
-    <row r="34" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A34" s="3" t="n">
+    <row r="34" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="3">
         <v>45699</v>
       </c>
       <c r="B34" s="4" t="s">
@@ -2293,18 +2674,18 @@
       <c r="D34" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="E34" s="3">
         <v>45741</v>
       </c>
-      <c r="F34" s="5" t="n">
+      <c r="F34" s="5">
         <v>1154.56</v>
       </c>
-      <c r="G34" s="5" t="n">
+      <c r="G34" s="5">
         <v>1154.56</v>
       </c>
       <c r="H34" s="3"/>
-      <c r="I34" s="6" t="n">
-        <v>549</v>
+      <c r="I34" s="6">
+        <v>553</v>
       </c>
       <c r="J34" s="4" t="s">
         <v>18</v>
@@ -2319,8 +2700,8 @@
       <c r="N34" s="4"/>
       <c r="O34" s="4"/>
     </row>
-    <row r="35" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A35" s="3" t="n">
+    <row r="35" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="3">
         <v>45699</v>
       </c>
       <c r="B35" s="4" t="s">
@@ -2332,18 +2713,18 @@
       <c r="D35" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="E35" s="3">
         <v>45748</v>
       </c>
-      <c r="F35" s="5" t="n">
+      <c r="F35" s="5">
         <v>1154.56</v>
       </c>
-      <c r="G35" s="5" t="n">
+      <c r="G35" s="5">
         <v>1154.56</v>
       </c>
       <c r="H35" s="3"/>
-      <c r="I35" s="6" t="n">
-        <v>542</v>
+      <c r="I35" s="6">
+        <v>546</v>
       </c>
       <c r="J35" s="4" t="s">
         <v>18</v>
@@ -2358,8 +2739,8 @@
       <c r="N35" s="4"/>
       <c r="O35" s="4"/>
     </row>
-    <row r="36" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A36" s="3" t="n">
+    <row r="36" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="3">
         <v>45699</v>
       </c>
       <c r="B36" s="4" t="s">
@@ -2371,18 +2752,18 @@
       <c r="D36" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="E36" s="3">
         <v>45748</v>
       </c>
-      <c r="F36" s="5" t="n">
+      <c r="F36" s="5">
         <v>7562.76</v>
       </c>
-      <c r="G36" s="5" t="n">
+      <c r="G36" s="5">
         <v>7562.76</v>
       </c>
       <c r="H36" s="3"/>
-      <c r="I36" s="6" t="n">
-        <v>542</v>
+      <c r="I36" s="6">
+        <v>546</v>
       </c>
       <c r="J36" s="4" t="s">
         <v>18</v>
@@ -2397,8 +2778,8 @@
       <c r="N36" s="4"/>
       <c r="O36" s="4"/>
     </row>
-    <row r="37" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A37" s="3" t="n">
+    <row r="37" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="3">
         <v>45699</v>
       </c>
       <c r="B37" s="4" t="s">
@@ -2410,18 +2791,18 @@
       <c r="D37" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="E37" s="3">
         <v>45755</v>
       </c>
-      <c r="F37" s="5" t="n">
+      <c r="F37" s="5">
         <v>1154.56</v>
       </c>
-      <c r="G37" s="5" t="n">
+      <c r="G37" s="5">
         <v>1154.56</v>
       </c>
       <c r="H37" s="3"/>
-      <c r="I37" s="6" t="n">
-        <v>535</v>
+      <c r="I37" s="6">
+        <v>539</v>
       </c>
       <c r="J37" s="4" t="s">
         <v>18</v>
@@ -2436,8 +2817,8 @@
       <c r="N37" s="4"/>
       <c r="O37" s="4"/>
     </row>
-    <row r="38" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A38" s="3" t="n">
+    <row r="38" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="3">
         <v>45733</v>
       </c>
       <c r="B38" s="4" t="s">
@@ -2449,18 +2830,18 @@
       <c r="D38" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="E38" s="3">
         <v>45761</v>
       </c>
-      <c r="F38" s="5" t="n">
+      <c r="F38" s="5">
         <v>3850</v>
       </c>
-      <c r="G38" s="5" t="n">
+      <c r="G38" s="5">
         <v>6169.53</v>
       </c>
       <c r="H38" s="3"/>
-      <c r="I38" s="6" t="n">
-        <v>529</v>
+      <c r="I38" s="6">
+        <v>533</v>
       </c>
       <c r="J38" s="4" t="s">
         <v>18</v>
@@ -2475,8 +2856,8 @@
       <c r="N38" s="4"/>
       <c r="O38" s="4"/>
     </row>
-    <row r="39" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A39" s="3" t="n">
+    <row r="39" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="3">
         <v>45733</v>
       </c>
       <c r="B39" s="4" t="s">
@@ -2488,18 +2869,18 @@
       <c r="D39" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="E39" s="3">
         <v>45768</v>
       </c>
-      <c r="F39" s="5" t="n">
+      <c r="F39" s="5">
         <v>3850</v>
       </c>
-      <c r="G39" s="5" t="n">
+      <c r="G39" s="5">
         <v>3850</v>
       </c>
       <c r="H39" s="3"/>
-      <c r="I39" s="6" t="n">
-        <v>522</v>
+      <c r="I39" s="6">
+        <v>526</v>
       </c>
       <c r="J39" s="4" t="s">
         <v>18</v>
@@ -2514,8 +2895,8 @@
       <c r="N39" s="4"/>
       <c r="O39" s="4"/>
     </row>
-    <row r="40" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A40" s="3" t="n">
+    <row r="40" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="3">
         <v>45733</v>
       </c>
       <c r="B40" s="4" t="s">
@@ -2527,18 +2908,18 @@
       <c r="D40" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="E40" s="3">
         <v>45775</v>
       </c>
-      <c r="F40" s="5" t="n">
+      <c r="F40" s="5">
         <v>3850</v>
       </c>
-      <c r="G40" s="5" t="n">
+      <c r="G40" s="5">
         <v>3850</v>
       </c>
       <c r="H40" s="3"/>
-      <c r="I40" s="6" t="n">
-        <v>515</v>
+      <c r="I40" s="6">
+        <v>519</v>
       </c>
       <c r="J40" s="4" t="s">
         <v>18</v>
@@ -2553,8 +2934,8 @@
       <c r="N40" s="4"/>
       <c r="O40" s="4"/>
     </row>
-    <row r="41" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A41" s="3" t="n">
+    <row r="41" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="3">
         <v>45747</v>
       </c>
       <c r="B41" s="4" t="s">
@@ -2566,18 +2947,18 @@
       <c r="D41" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="E41" s="3">
         <v>45775</v>
       </c>
-      <c r="F41" s="5" t="n">
+      <c r="F41" s="5">
         <v>3800</v>
       </c>
-      <c r="G41" s="5" t="n">
+      <c r="G41" s="5">
         <v>6089.41</v>
       </c>
       <c r="H41" s="3"/>
-      <c r="I41" s="6" t="n">
-        <v>515</v>
+      <c r="I41" s="6">
+        <v>519</v>
       </c>
       <c r="J41" s="4" t="s">
         <v>18</v>
@@ -2592,8 +2973,8 @@
       <c r="N41" s="4"/>
       <c r="O41" s="4"/>
     </row>
-    <row r="42" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A42" s="3" t="n">
+    <row r="42" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="3">
         <v>45747</v>
       </c>
       <c r="B42" s="4" t="s">
@@ -2605,18 +2986,18 @@
       <c r="D42" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="E42" s="3">
         <v>45782</v>
       </c>
-      <c r="F42" s="5" t="n">
+      <c r="F42" s="5">
         <v>3800</v>
       </c>
-      <c r="G42" s="5" t="n">
+      <c r="G42" s="5">
         <v>3800</v>
       </c>
       <c r="H42" s="3"/>
-      <c r="I42" s="6" t="n">
-        <v>508</v>
+      <c r="I42" s="6">
+        <v>512</v>
       </c>
       <c r="J42" s="4" t="s">
         <v>18</v>
@@ -2631,8 +3012,8 @@
       <c r="N42" s="4"/>
       <c r="O42" s="4"/>
     </row>
-    <row r="43" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A43" s="3" t="n">
+    <row r="43" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="3">
         <v>45747</v>
       </c>
       <c r="B43" s="4" t="s">
@@ -2644,18 +3025,18 @@
       <c r="D43" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="E43" s="3">
         <v>45789</v>
       </c>
-      <c r="F43" s="5" t="n">
+      <c r="F43" s="5">
         <v>3800</v>
       </c>
-      <c r="G43" s="5" t="n">
+      <c r="G43" s="5">
         <v>3800</v>
       </c>
       <c r="H43" s="3"/>
-      <c r="I43" s="6" t="n">
-        <v>501</v>
+      <c r="I43" s="6">
+        <v>505</v>
       </c>
       <c r="J43" s="4" t="s">
         <v>18</v>
@@ -2670,8 +3051,8 @@
       <c r="N43" s="4"/>
       <c r="O43" s="4"/>
     </row>
-    <row r="44" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A44" s="3" t="n">
+    <row r="44" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="3">
         <v>45754</v>
       </c>
       <c r="B44" s="4" t="s">
@@ -2683,18 +3064,18 @@
       <c r="D44" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="E44" s="3">
         <v>45789</v>
       </c>
-      <c r="F44" s="5" t="n">
-        <v>2287.07</v>
-      </c>
-      <c r="G44" s="5" t="n">
+      <c r="F44" s="5">
+        <v>2287.0700000000002</v>
+      </c>
+      <c r="G44" s="5">
         <v>1143.54</v>
       </c>
       <c r="H44" s="3"/>
-      <c r="I44" s="6" t="n">
-        <v>501</v>
+      <c r="I44" s="6">
+        <v>505</v>
       </c>
       <c r="J44" s="4" t="s">
         <v>26</v>
@@ -2709,8 +3090,8 @@
       <c r="N44" s="4"/>
       <c r="O44" s="4"/>
     </row>
-    <row r="45" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A45" s="3" t="n">
+    <row r="45" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="3">
         <v>45754</v>
       </c>
       <c r="B45" s="4" t="s">
@@ -2722,18 +3103,18 @@
       <c r="D45" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="E45" s="3">
         <v>45796</v>
       </c>
-      <c r="F45" s="5" t="n">
+      <c r="F45" s="5">
         <v>2287.06</v>
       </c>
-      <c r="G45" s="5" t="n">
+      <c r="G45" s="5">
         <v>2287.06</v>
       </c>
       <c r="H45" s="3"/>
-      <c r="I45" s="6" t="n">
-        <v>494</v>
+      <c r="I45" s="6">
+        <v>498</v>
       </c>
       <c r="J45" s="4" t="s">
         <v>26</v>
@@ -2748,8 +3129,8 @@
       <c r="N45" s="4"/>
       <c r="O45" s="4"/>
     </row>
-    <row r="46" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A46" s="3" t="n">
+    <row r="46" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="3">
         <v>45868</v>
       </c>
       <c r="B46" s="4" t="s">
@@ -2761,18 +3142,18 @@
       <c r="D46" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="E46" s="3">
         <v>45896</v>
       </c>
-      <c r="F46" s="5" t="n">
+      <c r="F46" s="5">
         <v>3663.84</v>
       </c>
-      <c r="G46" s="5" t="n">
+      <c r="G46" s="5">
         <v>4572.62</v>
       </c>
       <c r="H46" s="3"/>
-      <c r="I46" s="6" t="n">
-        <v>394</v>
+      <c r="I46" s="6">
+        <v>398</v>
       </c>
       <c r="J46" s="4" t="s">
         <v>26</v>
@@ -2787,8 +3168,8 @@
       <c r="N46" s="4"/>
       <c r="O46" s="4"/>
     </row>
-    <row r="47" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A47" s="3" t="n">
+    <row r="47" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="3">
         <v>45868</v>
       </c>
       <c r="B47" s="4" t="s">
@@ -2800,18 +3181,18 @@
       <c r="D47" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="E47" s="3" t="n">
+      <c r="E47" s="3">
         <v>45910</v>
       </c>
-      <c r="F47" s="5" t="n">
+      <c r="F47" s="5">
         <v>3663.84</v>
       </c>
-      <c r="G47" s="5" t="n">
+      <c r="G47" s="5">
         <v>3663.84</v>
       </c>
       <c r="H47" s="3"/>
-      <c r="I47" s="6" t="n">
-        <v>380</v>
+      <c r="I47" s="6">
+        <v>384</v>
       </c>
       <c r="J47" s="4" t="s">
         <v>26</v>
@@ -2826,8 +3207,8 @@
       <c r="N47" s="4"/>
       <c r="O47" s="4"/>
     </row>
-    <row r="48" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A48" s="3" t="n">
+    <row r="48" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="3">
         <v>45868</v>
       </c>
       <c r="B48" s="4" t="s">
@@ -2839,18 +3220,18 @@
       <c r="D48" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="E48" s="3" t="n">
+      <c r="E48" s="3">
         <v>45924</v>
       </c>
-      <c r="F48" s="5" t="n">
+      <c r="F48" s="5">
         <v>3663.84</v>
       </c>
-      <c r="G48" s="5" t="n">
+      <c r="G48" s="5">
         <v>3663.84</v>
       </c>
       <c r="H48" s="3"/>
-      <c r="I48" s="6" t="n">
-        <v>366</v>
+      <c r="I48" s="6">
+        <v>370</v>
       </c>
       <c r="J48" s="4" t="s">
         <v>26</v>
@@ -2865,8 +3246,8 @@
       <c r="N48" s="4"/>
       <c r="O48" s="4"/>
     </row>
-    <row r="49" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A49" s="3" t="n">
+    <row r="49" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="3">
         <v>45919</v>
       </c>
       <c r="B49" s="4" t="s">
@@ -2878,18 +3259,18 @@
       <c r="D49" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="E49" s="3" t="n">
+      <c r="E49" s="3">
         <v>45947</v>
       </c>
-      <c r="F49" s="5" t="n">
+      <c r="F49" s="5">
         <v>2144.59</v>
       </c>
-      <c r="G49" s="5" t="n">
+      <c r="G49" s="5">
         <v>3867.34</v>
       </c>
       <c r="H49" s="3"/>
-      <c r="I49" s="6" t="n">
-        <v>343</v>
+      <c r="I49" s="6">
+        <v>347</v>
       </c>
       <c r="J49" s="4" t="s">
         <v>26</v>
@@ -2904,8 +3285,8 @@
       <c r="N49" s="4"/>
       <c r="O49" s="4"/>
     </row>
-    <row r="50" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A50" s="3" t="n">
+    <row r="50" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="3">
         <v>45919</v>
       </c>
       <c r="B50" s="4" t="s">
@@ -2917,18 +3298,18 @@
       <c r="D50" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="E50" s="3" t="n">
+      <c r="E50" s="3">
         <v>45954</v>
       </c>
-      <c r="F50" s="5" t="n">
+      <c r="F50" s="5">
         <v>2144.59</v>
       </c>
-      <c r="G50" s="5" t="n">
+      <c r="G50" s="5">
         <v>2144.59</v>
       </c>
       <c r="H50" s="3"/>
-      <c r="I50" s="6" t="n">
-        <v>336</v>
+      <c r="I50" s="6">
+        <v>340</v>
       </c>
       <c r="J50" s="4" t="s">
         <v>26</v>
@@ -2943,8 +3324,8 @@
       <c r="N50" s="4"/>
       <c r="O50" s="4"/>
     </row>
-    <row r="51" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A51" s="3" t="n">
+    <row r="51" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="3">
         <v>45919</v>
       </c>
       <c r="B51" s="4" t="s">
@@ -2956,18 +3337,18 @@
       <c r="D51" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="E51" s="3" t="n">
+      <c r="E51" s="3">
         <v>45961</v>
       </c>
-      <c r="F51" s="5" t="n">
+      <c r="F51" s="5">
         <v>2144.59</v>
       </c>
-      <c r="G51" s="5" t="n">
+      <c r="G51" s="5">
         <v>2144.59</v>
       </c>
       <c r="H51" s="3"/>
-      <c r="I51" s="6" t="n">
-        <v>329</v>
+      <c r="I51" s="6">
+        <v>333</v>
       </c>
       <c r="J51" s="4" t="s">
         <v>26</v>
@@ -2982,8 +3363,8 @@
       <c r="N51" s="4"/>
       <c r="O51" s="4"/>
     </row>
-    <row r="52" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A52" s="3" t="n">
+    <row r="52" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="3">
         <v>45919</v>
       </c>
       <c r="B52" s="4" t="s">
@@ -2995,18 +3376,18 @@
       <c r="D52" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="E52" s="3" t="n">
+      <c r="E52" s="3">
         <v>45968</v>
       </c>
-      <c r="F52" s="5" t="n">
+      <c r="F52" s="5">
         <v>2144.59</v>
       </c>
-      <c r="G52" s="5" t="n">
+      <c r="G52" s="5">
         <v>2144.59</v>
       </c>
       <c r="H52" s="3"/>
-      <c r="I52" s="6" t="n">
-        <v>322</v>
+      <c r="I52" s="6">
+        <v>326</v>
       </c>
       <c r="J52" s="4" t="s">
         <v>26</v>
@@ -3021,8 +3402,8 @@
       <c r="N52" s="4"/>
       <c r="O52" s="4"/>
     </row>
-    <row r="53" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A53" s="3" t="n">
+    <row r="53" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="3">
         <v>45938</v>
       </c>
       <c r="B53" s="4" t="s">
@@ -3034,18 +3415,18 @@
       <c r="D53" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="E53" s="3" t="n">
+      <c r="E53" s="3">
         <v>45980</v>
       </c>
-      <c r="F53" s="5" t="n">
+      <c r="F53" s="5">
         <v>4480</v>
       </c>
-      <c r="G53" s="5" t="n">
+      <c r="G53" s="5">
         <v>4480</v>
       </c>
       <c r="H53" s="3"/>
-      <c r="I53" s="6" t="n">
-        <v>310</v>
+      <c r="I53" s="6">
+        <v>314</v>
       </c>
       <c r="J53" s="4" t="s">
         <v>26</v>
@@ -3060,8 +3441,8 @@
       <c r="N53" s="4"/>
       <c r="O53" s="4"/>
     </row>
-    <row r="54" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A54" s="3" t="n">
+    <row r="54" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="3">
         <v>45959</v>
       </c>
       <c r="B54" s="4" t="s">
@@ -3073,18 +3454,18 @@
       <c r="D54" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="E54" s="3" t="n">
+      <c r="E54" s="3">
         <v>45980</v>
       </c>
-      <c r="F54" s="5" t="n">
+      <c r="F54" s="5">
         <v>28666.44</v>
       </c>
-      <c r="G54" s="5" t="n">
+      <c r="G54" s="5">
         <v>28666.44</v>
       </c>
       <c r="H54" s="3"/>
-      <c r="I54" s="6" t="n">
-        <v>310</v>
+      <c r="I54" s="6">
+        <v>314</v>
       </c>
       <c r="J54" s="4"/>
       <c r="K54" s="4" t="s">
@@ -3095,8 +3476,8 @@
       <c r="N54" s="4"/>
       <c r="O54" s="4"/>
     </row>
-    <row r="55" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A55" s="3" t="n">
+    <row r="55" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="3">
         <v>45959</v>
       </c>
       <c r="B55" s="4" t="s">
@@ -3108,18 +3489,18 @@
       <c r="D55" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="E55" s="3" t="n">
+      <c r="E55" s="3">
         <v>45987</v>
       </c>
-      <c r="F55" s="5" t="n">
-        <v>33844.16</v>
-      </c>
-      <c r="G55" s="5" t="n">
-        <v>33844.16</v>
+      <c r="F55" s="5">
+        <v>33844.160000000003</v>
+      </c>
+      <c r="G55" s="5">
+        <v>33844.160000000003</v>
       </c>
       <c r="H55" s="3"/>
-      <c r="I55" s="6" t="n">
-        <v>303</v>
+      <c r="I55" s="6">
+        <v>307</v>
       </c>
       <c r="J55" s="4"/>
       <c r="K55" s="4" t="s">
@@ -3130,8 +3511,8 @@
       <c r="N55" s="4"/>
       <c r="O55" s="4"/>
     </row>
-    <row r="56" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A56" s="3" t="n">
+    <row r="56" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="3">
         <v>45947</v>
       </c>
       <c r="B56" s="4" t="s">
@@ -3143,18 +3524,18 @@
       <c r="D56" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="E56" s="3" t="n">
+      <c r="E56" s="3">
         <v>45989</v>
       </c>
-      <c r="F56" s="5" t="n">
+      <c r="F56" s="5">
         <v>3220</v>
       </c>
-      <c r="G56" s="5" t="n">
+      <c r="G56" s="5">
         <v>3220</v>
       </c>
       <c r="H56" s="3"/>
-      <c r="I56" s="6" t="n">
-        <v>301</v>
+      <c r="I56" s="6">
+        <v>305</v>
       </c>
       <c r="J56" s="4"/>
       <c r="K56" s="4" t="s">
@@ -3165,8 +3546,8 @@
       <c r="N56" s="4"/>
       <c r="O56" s="4"/>
     </row>
-    <row r="57" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A57" s="3" t="n">
+    <row r="57" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="3">
         <v>45959</v>
       </c>
       <c r="B57" s="4" t="s">
@@ -3178,18 +3559,18 @@
       <c r="D57" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="E57" s="3" t="n">
+      <c r="E57" s="3">
         <v>45994</v>
       </c>
-      <c r="F57" s="5" t="n">
+      <c r="F57" s="5">
         <v>14483.06</v>
       </c>
-      <c r="G57" s="5" t="n">
+      <c r="G57" s="5">
         <v>14483.06</v>
       </c>
       <c r="H57" s="3"/>
-      <c r="I57" s="6" t="n">
-        <v>296</v>
+      <c r="I57" s="6">
+        <v>300</v>
       </c>
       <c r="J57" s="4"/>
       <c r="K57" s="4" t="s">
@@ -3200,8 +3581,8 @@
       <c r="N57" s="4"/>
       <c r="O57" s="4"/>
     </row>
-    <row r="58" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A58" s="3" t="n">
+    <row r="58" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="3">
         <v>46062</v>
       </c>
       <c r="B58" s="4" t="s">
@@ -3213,18 +3594,18 @@
       <c r="D58" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="E58" s="3" t="n">
+      <c r="E58" s="3">
         <v>46090</v>
       </c>
-      <c r="F58" s="5" t="n">
+      <c r="F58" s="5">
         <v>503.28</v>
       </c>
-      <c r="G58" s="5" t="n">
+      <c r="G58" s="5">
         <v>806.34</v>
       </c>
       <c r="H58" s="3"/>
-      <c r="I58" s="6" t="n">
-        <v>200</v>
+      <c r="I58" s="6">
+        <v>204</v>
       </c>
       <c r="J58" s="4" t="s">
         <v>26</v>
@@ -3239,8 +3620,8 @@
       <c r="N58" s="4"/>
       <c r="O58" s="4"/>
     </row>
-    <row r="59" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A59" s="3" t="n">
+    <row r="59" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="3">
         <v>46062</v>
       </c>
       <c r="B59" s="4" t="s">
@@ -3252,18 +3633,18 @@
       <c r="D59" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="E59" s="3" t="n">
+      <c r="E59" s="3">
         <v>46097</v>
       </c>
-      <c r="F59" s="5" t="n">
+      <c r="F59" s="5">
         <v>503.28</v>
       </c>
-      <c r="G59" s="5" t="n">
+      <c r="G59" s="5">
         <v>503.28</v>
       </c>
       <c r="H59" s="3"/>
-      <c r="I59" s="6" t="n">
-        <v>193</v>
+      <c r="I59" s="6">
+        <v>197</v>
       </c>
       <c r="J59" s="4" t="s">
         <v>26</v>
@@ -3278,8 +3659,8 @@
       <c r="N59" s="4"/>
       <c r="O59" s="4"/>
     </row>
-    <row r="60" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A60" s="3" t="n">
+    <row r="60" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="3">
         <v>46062</v>
       </c>
       <c r="B60" s="4" t="s">
@@ -3291,18 +3672,18 @@
       <c r="D60" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="E60" s="3" t="n">
+      <c r="E60" s="3">
         <v>46104</v>
       </c>
-      <c r="F60" s="5" t="n">
+      <c r="F60" s="5">
         <v>503.28</v>
       </c>
-      <c r="G60" s="5" t="n">
+      <c r="G60" s="5">
         <v>503.28</v>
       </c>
       <c r="H60" s="3"/>
-      <c r="I60" s="6" t="n">
-        <v>186</v>
+      <c r="I60" s="6">
+        <v>190</v>
       </c>
       <c r="J60" s="4" t="s">
         <v>26</v>
@@ -3317,8 +3698,8 @@
       <c r="N60" s="4"/>
       <c r="O60" s="4"/>
     </row>
-    <row r="61" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A61" s="3" t="n">
+    <row r="61" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="3">
         <v>46045</v>
       </c>
       <c r="B61" s="4" t="s">
@@ -3330,18 +3711,18 @@
       <c r="D61" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="E61" s="3" t="n">
+      <c r="E61" s="3">
         <v>46105</v>
       </c>
-      <c r="F61" s="5" t="n">
+      <c r="F61" s="5">
         <v>5466.66</v>
       </c>
-      <c r="G61" s="5" t="n">
+      <c r="G61" s="5">
         <v>5466.66</v>
       </c>
       <c r="H61" s="3"/>
-      <c r="I61" s="6" t="n">
-        <v>185</v>
+      <c r="I61" s="6">
+        <v>189</v>
       </c>
       <c r="J61" s="4" t="s">
         <v>18</v>
@@ -3356,8 +3737,8 @@
       <c r="N61" s="4"/>
       <c r="O61" s="4"/>
     </row>
-    <row r="62" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A62" s="3" t="n">
+    <row r="62" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="3">
         <v>46171</v>
       </c>
       <c r="B62" s="4" t="s">
@@ -3369,18 +3750,18 @@
       <c r="D62" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="E62" s="3" t="n">
+      <c r="E62" s="3">
         <v>46192</v>
       </c>
-      <c r="F62" s="5" t="n">
-        <v>4676.85</v>
-      </c>
-      <c r="G62" s="5" t="n">
+      <c r="F62" s="5">
+        <v>4676.8500000000004</v>
+      </c>
+      <c r="G62" s="5">
         <v>7494.53</v>
       </c>
       <c r="H62" s="3"/>
-      <c r="I62" s="6" t="n">
-        <v>98</v>
+      <c r="I62" s="6">
+        <v>102</v>
       </c>
       <c r="J62" s="4"/>
       <c r="K62" s="4" t="s">
@@ -3391,8 +3772,8 @@
       <c r="N62" s="4"/>
       <c r="O62" s="4"/>
     </row>
-    <row r="63" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A63" s="3" t="n">
+    <row r="63" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="3">
         <v>46171</v>
       </c>
       <c r="B63" s="4" t="s">
@@ -3404,18 +3785,18 @@
       <c r="D63" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="E63" s="3" t="n">
+      <c r="E63" s="3">
         <v>46199</v>
       </c>
-      <c r="F63" s="5" t="n">
-        <v>4676.85</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>4676.85</v>
+      <c r="F63" s="5">
+        <v>4676.8500000000004</v>
+      </c>
+      <c r="G63" s="5">
+        <v>4676.8500000000004</v>
       </c>
       <c r="H63" s="3"/>
-      <c r="I63" s="6" t="n">
-        <v>91</v>
+      <c r="I63" s="6">
+        <v>95</v>
       </c>
       <c r="J63" s="4"/>
       <c r="K63" s="4" t="s">
@@ -3426,8 +3807,8 @@
       <c r="N63" s="4"/>
       <c r="O63" s="4"/>
     </row>
-    <row r="64" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A64" s="3" t="n">
+    <row r="64" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="3">
         <v>46171</v>
       </c>
       <c r="B64" s="4" t="s">
@@ -3439,18 +3820,18 @@
       <c r="D64" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="E64" s="3" t="n">
+      <c r="E64" s="3">
         <v>46206</v>
       </c>
-      <c r="F64" s="5" t="n">
-        <v>4676.85</v>
-      </c>
-      <c r="G64" s="5" t="n">
-        <v>4676.85</v>
+      <c r="F64" s="5">
+        <v>4676.8500000000004</v>
+      </c>
+      <c r="G64" s="5">
+        <v>4676.8500000000004</v>
       </c>
       <c r="H64" s="3"/>
-      <c r="I64" s="6" t="n">
-        <v>84</v>
+      <c r="I64" s="6">
+        <v>88</v>
       </c>
       <c r="J64" s="4"/>
       <c r="K64" s="4" t="s">
@@ -3461,8 +3842,8 @@
       <c r="N64" s="4"/>
       <c r="O64" s="4"/>
     </row>
-    <row r="65" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A65" s="3" t="n">
+    <row r="65" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="3">
         <v>46162</v>
       </c>
       <c r="B65" s="4" t="s">
@@ -3474,18 +3855,18 @@
       <c r="D65" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="E65" s="3" t="n">
+      <c r="E65" s="3">
         <v>46222</v>
       </c>
-      <c r="F65" s="5" t="n">
+      <c r="F65" s="5">
         <v>31531.5</v>
       </c>
-      <c r="G65" s="5" t="n">
+      <c r="G65" s="5">
         <v>31531.5</v>
       </c>
       <c r="H65" s="3"/>
-      <c r="I65" s="6" t="n">
-        <v>68</v>
+      <c r="I65" s="6">
+        <v>72</v>
       </c>
       <c r="J65" s="4" t="s">
         <v>18</v>
@@ -3500,8 +3881,8 @@
       <c r="N65" s="4"/>
       <c r="O65" s="4"/>
     </row>
-    <row r="66" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A66" s="3" t="n">
+    <row r="66" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="3">
         <v>46198</v>
       </c>
       <c r="B66" s="4" t="s">
@@ -3513,18 +3894,18 @@
       <c r="D66" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="E66" s="3" t="n">
+      <c r="E66" s="3">
         <v>46228</v>
       </c>
-      <c r="F66" s="5" t="n">
+      <c r="F66" s="5">
         <v>3516.48</v>
       </c>
-      <c r="G66" s="5" t="n">
+      <c r="G66" s="5">
         <v>3516.48</v>
       </c>
       <c r="H66" s="3"/>
-      <c r="I66" s="6" t="n">
-        <v>62</v>
+      <c r="I66" s="6">
+        <v>66</v>
       </c>
       <c r="J66" s="4" t="s">
         <v>170</v>
@@ -3539,8 +3920,8 @@
       <c r="N66" s="4"/>
       <c r="O66" s="4"/>
     </row>
-    <row r="67" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A67" s="3" t="n">
+    <row r="67" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="3">
         <v>46203</v>
       </c>
       <c r="B67" s="4" t="s">
@@ -3552,18 +3933,18 @@
       <c r="D67" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="E67" s="3" t="n">
+      <c r="E67" s="3">
         <v>46259</v>
       </c>
-      <c r="F67" s="5" t="n">
+      <c r="F67" s="5">
         <v>860</v>
       </c>
-      <c r="G67" s="5" t="n">
+      <c r="G67" s="5">
         <v>860</v>
       </c>
       <c r="H67" s="3"/>
-      <c r="I67" s="6" t="n">
-        <v>31</v>
+      <c r="I67" s="6">
+        <v>35</v>
       </c>
       <c r="J67" s="4" t="s">
         <v>26</v>
@@ -3578,8 +3959,8 @@
       <c r="N67" s="4"/>
       <c r="O67" s="4"/>
     </row>
-    <row r="68" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A68" s="3" t="n">
+    <row r="68" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="3">
         <v>46224</v>
       </c>
       <c r="B68" s="4" t="s">
@@ -3591,18 +3972,18 @@
       <c r="D68" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="E68" s="3" t="n">
+      <c r="E68" s="3">
         <v>46259</v>
       </c>
-      <c r="F68" s="5" t="n">
+      <c r="F68" s="5">
         <v>2818.37</v>
       </c>
-      <c r="G68" s="5" t="n">
+      <c r="G68" s="5">
         <v>2818.37</v>
       </c>
       <c r="H68" s="3"/>
-      <c r="I68" s="6" t="n">
-        <v>31</v>
+      <c r="I68" s="6">
+        <v>35</v>
       </c>
       <c r="J68" s="4" t="s">
         <v>26</v>
@@ -3617,8 +3998,8 @@
       <c r="N68" s="4"/>
       <c r="O68" s="4"/>
     </row>
-    <row r="69" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A69" s="3" t="n">
+    <row r="69" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="3">
         <v>46232</v>
       </c>
       <c r="B69" s="4" t="s">
@@ -3630,18 +4011,18 @@
       <c r="D69" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="E69" s="3" t="n">
+      <c r="E69" s="3">
         <v>46262</v>
       </c>
-      <c r="F69" s="5" t="n">
+      <c r="F69" s="5">
         <v>9716</v>
       </c>
-      <c r="G69" s="5" t="n">
+      <c r="G69" s="5">
         <v>18957.86</v>
       </c>
       <c r="H69" s="3"/>
-      <c r="I69" s="6" t="n">
-        <v>28</v>
+      <c r="I69" s="6">
+        <v>32</v>
       </c>
       <c r="J69" s="4" t="s">
         <v>26</v>
@@ -3656,8 +4037,8 @@
       <c r="N69" s="4"/>
       <c r="O69" s="4"/>
     </row>
-    <row r="70" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A70" s="3" t="n">
+    <row r="70" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="3">
         <v>46224</v>
       </c>
       <c r="B70" s="4" t="s">
@@ -3669,18 +4050,18 @@
       <c r="D70" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="E70" s="3" t="n">
+      <c r="E70" s="3">
         <v>46266</v>
       </c>
-      <c r="F70" s="5" t="n">
+      <c r="F70" s="5">
         <v>2818.37</v>
       </c>
-      <c r="G70" s="5" t="n">
+      <c r="G70" s="5">
         <v>2818.37</v>
       </c>
       <c r="H70" s="3"/>
-      <c r="I70" s="6" t="n">
-        <v>24</v>
+      <c r="I70" s="6">
+        <v>28</v>
       </c>
       <c r="J70" s="4" t="s">
         <v>26</v>
@@ -3695,8 +4076,8 @@
       <c r="N70" s="4"/>
       <c r="O70" s="4"/>
     </row>
-    <row r="71" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A71" s="3" t="n">
+    <row r="71" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="3">
         <v>46227</v>
       </c>
       <c r="B71" s="4" t="s">
@@ -3708,18 +4089,18 @@
       <c r="D71" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="E71" s="3" t="n">
+      <c r="E71" s="3">
         <v>46269</v>
       </c>
-      <c r="F71" s="5" t="n">
+      <c r="F71" s="5">
         <v>23168.6</v>
       </c>
-      <c r="G71" s="5" t="n">
+      <c r="G71" s="5">
         <v>23168.6</v>
       </c>
       <c r="H71" s="3"/>
-      <c r="I71" s="6" t="n">
-        <v>21</v>
+      <c r="I71" s="6">
+        <v>25</v>
       </c>
       <c r="J71" s="4" t="s">
         <v>170</v>
@@ -3734,8 +4115,8 @@
       <c r="N71" s="4"/>
       <c r="O71" s="4"/>
     </row>
-    <row r="72" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A72" s="3" t="n">
+    <row r="72" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="3">
         <v>46225</v>
       </c>
       <c r="B72" s="4" t="s">
@@ -3747,18 +4128,18 @@
       <c r="D72" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="E72" s="3" t="n">
+      <c r="E72" s="3">
         <v>46270</v>
       </c>
-      <c r="F72" s="5" t="n">
+      <c r="F72" s="5">
         <v>7551.88</v>
       </c>
-      <c r="G72" s="5" t="n">
+      <c r="G72" s="5">
         <v>11442.87</v>
       </c>
       <c r="H72" s="3"/>
-      <c r="I72" s="6" t="n">
-        <v>20</v>
+      <c r="I72" s="6">
+        <v>24</v>
       </c>
       <c r="J72" s="4" t="s">
         <v>170</v>
@@ -3773,8 +4154,8 @@
       <c r="N72" s="4"/>
       <c r="O72" s="4"/>
     </row>
-    <row r="73" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A73" s="3" t="n">
+    <row r="73" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="3">
         <v>46227</v>
       </c>
       <c r="B73" s="4" t="s">
@@ -3786,18 +4167,18 @@
       <c r="D73" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="E73" s="3" t="n">
+      <c r="E73" s="3">
         <v>46272</v>
       </c>
-      <c r="F73" s="5" t="n">
+      <c r="F73" s="5">
         <v>4216.67</v>
       </c>
-      <c r="G73" s="5" t="n">
+      <c r="G73" s="5">
         <v>6389.24</v>
       </c>
       <c r="H73" s="3"/>
-      <c r="I73" s="6" t="n">
-        <v>18</v>
+      <c r="I73" s="6">
+        <v>22</v>
       </c>
       <c r="J73" s="4" t="s">
         <v>193</v>
@@ -3812,8 +4193,8 @@
       <c r="N73" s="4"/>
       <c r="O73" s="4"/>
     </row>
-    <row r="74" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A74" s="3" t="n">
+    <row r="74" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="3">
         <v>46232</v>
       </c>
       <c r="B74" s="4" t="s">
@@ -3825,18 +4206,18 @@
       <c r="D74" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="E74" s="3" t="n">
+      <c r="E74" s="3">
         <v>46272</v>
       </c>
-      <c r="F74" s="5" t="n">
+      <c r="F74" s="5">
         <v>9716</v>
       </c>
-      <c r="G74" s="5" t="n">
+      <c r="G74" s="5">
         <v>9716</v>
       </c>
       <c r="H74" s="3"/>
-      <c r="I74" s="6" t="n">
-        <v>18</v>
+      <c r="I74" s="6">
+        <v>22</v>
       </c>
       <c r="J74" s="4" t="s">
         <v>26</v>
@@ -3851,8 +4232,8 @@
       <c r="N74" s="4"/>
       <c r="O74" s="4"/>
     </row>
-    <row r="75" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A75" s="3" t="n">
+    <row r="75" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="3">
         <v>46224</v>
       </c>
       <c r="B75" s="4" t="s">
@@ -3864,18 +4245,18 @@
       <c r="D75" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="E75" s="3" t="n">
+      <c r="E75" s="3">
         <v>46273</v>
       </c>
-      <c r="F75" s="5" t="n">
+      <c r="F75" s="5">
         <v>2818.37</v>
       </c>
-      <c r="G75" s="5" t="n">
+      <c r="G75" s="5">
         <v>2818.37</v>
       </c>
       <c r="H75" s="3"/>
-      <c r="I75" s="6" t="n">
-        <v>17</v>
+      <c r="I75" s="6">
+        <v>21</v>
       </c>
       <c r="J75" s="4" t="s">
         <v>26</v>
@@ -3890,8 +4271,8 @@
       <c r="N75" s="4"/>
       <c r="O75" s="4"/>
     </row>
-    <row r="76" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A76" s="3" t="n">
+    <row r="76" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="3">
         <v>46223</v>
       </c>
       <c r="B76" s="4" t="s">
@@ -3903,18 +4284,18 @@
       <c r="D76" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="E76" s="3" t="n">
+      <c r="E76" s="3">
         <v>46273</v>
       </c>
-      <c r="F76" s="5" t="n">
+      <c r="F76" s="5">
         <v>11200</v>
       </c>
-      <c r="G76" s="5" t="n">
+      <c r="G76" s="5">
         <v>11200</v>
       </c>
       <c r="H76" s="3"/>
-      <c r="I76" s="6" t="n">
-        <v>17</v>
+      <c r="I76" s="6">
+        <v>21</v>
       </c>
       <c r="J76" s="4" t="s">
         <v>170</v>
@@ -3929,8 +4310,8 @@
       <c r="N76" s="4"/>
       <c r="O76" s="4"/>
     </row>
-    <row r="77" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A77" s="3" t="n">
+    <row r="77" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="3">
         <v>46253</v>
       </c>
       <c r="B77" s="4" t="s">
@@ -3942,18 +4323,18 @@
       <c r="D77" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="E77" s="3" t="n">
+      <c r="E77" s="3">
         <v>46274</v>
       </c>
-      <c r="F77" s="5" t="n">
+      <c r="F77" s="5">
         <v>10080</v>
       </c>
-      <c r="G77" s="5" t="n">
+      <c r="G77" s="5">
         <v>10080</v>
       </c>
       <c r="H77" s="3"/>
-      <c r="I77" s="6" t="n">
-        <v>16</v>
+      <c r="I77" s="6">
+        <v>20</v>
       </c>
       <c r="J77" s="4" t="s">
         <v>170</v>
@@ -3968,8 +4349,8 @@
       <c r="N77" s="4"/>
       <c r="O77" s="4"/>
     </row>
-    <row r="78" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A78" s="3" t="n">
+    <row r="78" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="3">
         <v>46227</v>
       </c>
       <c r="B78" s="4" t="s">
@@ -3981,18 +4362,18 @@
       <c r="D78" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="E78" s="3" t="n">
+      <c r="E78" s="3">
         <v>46276</v>
       </c>
-      <c r="F78" s="5" t="n">
+      <c r="F78" s="5">
         <v>23168.6</v>
       </c>
-      <c r="G78" s="5" t="n">
+      <c r="G78" s="5">
         <v>23168.6</v>
       </c>
       <c r="H78" s="3"/>
-      <c r="I78" s="6" t="n">
-        <v>14</v>
+      <c r="I78" s="6">
+        <v>18</v>
       </c>
       <c r="J78" s="4" t="s">
         <v>170</v>
@@ -4007,8 +4388,8 @@
       <c r="N78" s="4"/>
       <c r="O78" s="4"/>
     </row>
-    <row r="79" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A79" s="3" t="n">
+    <row r="79" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="3">
         <v>46234</v>
       </c>
       <c r="B79" s="4" t="s">
@@ -4020,18 +4401,18 @@
       <c r="D79" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="E79" s="3" t="n">
+      <c r="E79" s="3">
         <v>46279</v>
       </c>
-      <c r="F79" s="5" t="n">
+      <c r="F79" s="5">
         <v>3789.09</v>
       </c>
-      <c r="G79" s="5" t="n">
+      <c r="G79" s="5">
         <v>5741.36</v>
       </c>
       <c r="H79" s="3"/>
-      <c r="I79" s="6" t="n">
-        <v>11</v>
+      <c r="I79" s="6">
+        <v>15</v>
       </c>
       <c r="J79" s="4" t="s">
         <v>170</v>
@@ -4046,8 +4427,8 @@
       <c r="N79" s="4"/>
       <c r="O79" s="4"/>
     </row>
-    <row r="80" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A80" s="3" t="n">
+    <row r="80" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="3">
         <v>46224</v>
       </c>
       <c r="B80" s="4" t="s">
@@ -4059,18 +4440,18 @@
       <c r="D80" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="E80" s="3" t="n">
+      <c r="E80" s="3">
         <v>46280</v>
       </c>
-      <c r="F80" s="5" t="n">
+      <c r="F80" s="5">
         <v>2818.36</v>
       </c>
-      <c r="G80" s="5" t="n">
+      <c r="G80" s="5">
         <v>2818.36</v>
       </c>
       <c r="H80" s="3"/>
-      <c r="I80" s="6" t="n">
-        <v>10</v>
+      <c r="I80" s="6">
+        <v>14</v>
       </c>
       <c r="J80" s="4" t="s">
         <v>26</v>
@@ -4085,8 +4466,8 @@
       <c r="N80" s="4"/>
       <c r="O80" s="4"/>
     </row>
-    <row r="81" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A81" s="3" t="n">
+    <row r="81" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="3">
         <v>46253</v>
       </c>
       <c r="B81" s="4" t="s">
@@ -4098,18 +4479,18 @@
       <c r="D81" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="E81" s="3" t="n">
+      <c r="E81" s="3">
         <v>46281</v>
       </c>
-      <c r="F81" s="5" t="n">
+      <c r="F81" s="5">
         <v>10080</v>
       </c>
-      <c r="G81" s="5" t="n">
+      <c r="G81" s="5">
         <v>10080</v>
       </c>
       <c r="H81" s="3"/>
-      <c r="I81" s="6" t="n">
-        <v>9</v>
+      <c r="I81" s="6">
+        <v>13</v>
       </c>
       <c r="J81" s="4" t="s">
         <v>170</v>
@@ -4124,70 +4505,70 @@
       <c r="N81" s="4"/>
       <c r="O81" s="4"/>
     </row>
-    <row r="82" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A82" s="3" t="n">
-        <v>46219</v>
+    <row r="82" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="3">
+        <v>46232</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>172</v>
+        <v>15</v>
       </c>
       <c r="C82" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="D82" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="D82" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="E82" s="3" t="n">
+      <c r="E82" s="3">
         <v>46282</v>
       </c>
-      <c r="F82" s="5" t="n">
-        <v>3419.96</v>
-      </c>
-      <c r="G82" s="5" t="n">
-        <v>3419.96</v>
+      <c r="F82" s="5">
+        <v>9716</v>
+      </c>
+      <c r="G82" s="5">
+        <v>9716</v>
       </c>
       <c r="H82" s="3"/>
-      <c r="I82" s="6" t="n">
-        <v>8</v>
+      <c r="I82" s="6">
+        <v>12</v>
       </c>
       <c r="J82" s="4" t="s">
-        <v>170</v>
+        <v>26</v>
       </c>
       <c r="K82" s="4" t="s">
-        <v>175</v>
+        <v>39</v>
       </c>
       <c r="L82" s="4"/>
       <c r="M82" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="N82" s="4"/>
       <c r="O82" s="4"/>
     </row>
-    <row r="83" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A83" s="3" t="n">
-        <v>46232</v>
+    <row r="83" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="3">
+        <v>46192</v>
       </c>
       <c r="B83" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>179</v>
+        <v>214</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="E83" s="3" t="n">
+      <c r="E83" s="3">
         <v>46282</v>
       </c>
-      <c r="F83" s="5" t="n">
-        <v>9716</v>
-      </c>
-      <c r="G83" s="5" t="n">
-        <v>9716</v>
+      <c r="F83" s="5">
+        <v>22750</v>
+      </c>
+      <c r="G83" s="5">
+        <v>22750</v>
       </c>
       <c r="H83" s="3"/>
-      <c r="I83" s="6" t="n">
-        <v>8</v>
+      <c r="I83" s="6">
+        <v>12</v>
       </c>
       <c r="J83" s="4" t="s">
         <v>26</v>
@@ -4202,187 +4583,187 @@
       <c r="N83" s="4"/>
       <c r="O83" s="4"/>
     </row>
-    <row r="84" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A84" s="3" t="n">
-        <v>46192</v>
+    <row r="84" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="3">
+        <v>46223</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="C84" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="D84" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="D84" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="E84" s="3" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F84" s="5" t="n">
-        <v>22750</v>
-      </c>
-      <c r="G84" s="5" t="n">
-        <v>22750</v>
+      <c r="E84" s="3">
+        <v>46283</v>
+      </c>
+      <c r="F84" s="5">
+        <v>11200</v>
+      </c>
+      <c r="G84" s="5">
+        <v>11200</v>
       </c>
       <c r="H84" s="3"/>
-      <c r="I84" s="6" t="n">
-        <v>8</v>
+      <c r="I84" s="6">
+        <v>11</v>
       </c>
       <c r="J84" s="4" t="s">
-        <v>26</v>
+        <v>170</v>
       </c>
       <c r="K84" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="L84" s="4"/>
       <c r="M84" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="N84" s="4"/>
       <c r="O84" s="4"/>
     </row>
-    <row r="85" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A85" s="3" t="n">
-        <v>46223</v>
+    <row r="85" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="3">
+        <v>46253</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>199</v>
+        <v>166</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="E85" s="3" t="n">
+        <v>219</v>
+      </c>
+      <c r="E85" s="3">
         <v>46283</v>
       </c>
-      <c r="F85" s="5" t="n">
-        <v>11200</v>
-      </c>
-      <c r="G85" s="5" t="n">
-        <v>11200</v>
+      <c r="F85" s="5">
+        <v>1172.1600000000001</v>
+      </c>
+      <c r="G85" s="5">
+        <v>1172.1600000000001</v>
       </c>
       <c r="H85" s="3"/>
-      <c r="I85" s="6" t="n">
-        <v>7</v>
+      <c r="I85" s="6">
+        <v>11</v>
       </c>
       <c r="J85" s="4" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="K85" s="4" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="L85" s="4"/>
       <c r="M85" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="N85" s="4"/>
       <c r="O85" s="4"/>
     </row>
-    <row r="86" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A86" s="3" t="n">
-        <v>46223</v>
+    <row r="86" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="3">
+        <v>46227</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="E86" s="3" t="n">
+        <v>221</v>
+      </c>
+      <c r="E86" s="3">
         <v>46283</v>
       </c>
-      <c r="F86" s="5" t="n">
-        <v>5860.8</v>
-      </c>
-      <c r="G86" s="5" t="n">
-        <v>5860.8</v>
+      <c r="F86" s="5">
+        <v>23168.6</v>
+      </c>
+      <c r="G86" s="5">
+        <v>23168.6</v>
       </c>
       <c r="H86" s="3"/>
-      <c r="I86" s="6" t="n">
-        <v>7</v>
+      <c r="I86" s="6">
+        <v>11</v>
       </c>
       <c r="J86" s="4" t="s">
-        <v>26</v>
+        <v>170</v>
       </c>
       <c r="K86" s="4" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="L86" s="4"/>
       <c r="M86" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="N86" s="4"/>
       <c r="O86" s="4"/>
     </row>
-    <row r="87" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A87" s="3" t="n">
-        <v>46253</v>
+    <row r="87" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="3">
+        <v>46224</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>166</v>
+        <v>199</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="E87" s="3" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F87" s="5" t="n">
-        <v>1172.16</v>
-      </c>
-      <c r="G87" s="5" t="n">
-        <v>1172.16</v>
+        <v>223</v>
+      </c>
+      <c r="E87" s="3">
+        <v>46284</v>
+      </c>
+      <c r="F87" s="5">
+        <v>10666.67</v>
+      </c>
+      <c r="G87" s="5">
+        <v>10666.67</v>
       </c>
       <c r="H87" s="3"/>
-      <c r="I87" s="6" t="n">
-        <v>7</v>
+      <c r="I87" s="6">
+        <v>10</v>
       </c>
       <c r="J87" s="4" t="s">
-        <v>193</v>
+        <v>170</v>
       </c>
       <c r="K87" s="4" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="L87" s="4"/>
       <c r="M87" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="N87" s="4"/>
       <c r="O87" s="4"/>
     </row>
-    <row r="88" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A88" s="3" t="n">
-        <v>46227</v>
+    <row r="88" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="3">
+        <v>46234</v>
       </c>
       <c r="B88" s="4" t="s">
         <v>45</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="E88" s="3" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F88" s="5" t="n">
-        <v>23168.6</v>
-      </c>
-      <c r="G88" s="5" t="n">
-        <v>23168.6</v>
+        <v>225</v>
+      </c>
+      <c r="E88" s="3">
+        <v>46284</v>
+      </c>
+      <c r="F88" s="5">
+        <v>6500</v>
+      </c>
+      <c r="G88" s="5">
+        <v>6500</v>
       </c>
       <c r="H88" s="3"/>
-      <c r="I88" s="6" t="n">
-        <v>7</v>
+      <c r="I88" s="6">
+        <v>10</v>
       </c>
       <c r="J88" s="4" t="s">
         <v>170</v>
@@ -4392,14 +4773,14 @@
       </c>
       <c r="L88" s="4"/>
       <c r="M88" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="N88" s="4"/>
       <c r="O88" s="4"/>
     </row>
-    <row r="89" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A89" s="3" t="n">
-        <v>46224</v>
+    <row r="89" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="3">
+        <v>46234</v>
       </c>
       <c r="B89" s="4" t="s">
         <v>45</v>
@@ -4408,20 +4789,20 @@
         <v>199</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="E89" s="3" t="n">
+        <v>227</v>
+      </c>
+      <c r="E89" s="3">
         <v>46284</v>
       </c>
-      <c r="F89" s="5" t="n">
-        <v>10666.67</v>
-      </c>
-      <c r="G89" s="5" t="n">
-        <v>10666.67</v>
+      <c r="F89" s="5">
+        <v>4950.17</v>
+      </c>
+      <c r="G89" s="5">
+        <v>4950.17</v>
       </c>
       <c r="H89" s="3"/>
-      <c r="I89" s="6" t="n">
-        <v>6</v>
+      <c r="I89" s="6">
+        <v>10</v>
       </c>
       <c r="J89" s="4" t="s">
         <v>170</v>
@@ -4431,75 +4812,75 @@
       </c>
       <c r="L89" s="4"/>
       <c r="M89" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="N89" s="4"/>
       <c r="O89" s="4"/>
     </row>
-    <row r="90" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A90" s="3" t="n">
-        <v>46234</v>
+    <row r="90" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="3">
+        <v>46225</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>45</v>
+        <v>187</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="E90" s="3" t="n">
-        <v>46284</v>
-      </c>
-      <c r="F90" s="5" t="n">
-        <v>6500</v>
-      </c>
-      <c r="G90" s="5" t="n">
-        <v>6500</v>
+        <v>229</v>
+      </c>
+      <c r="E90" s="3">
+        <v>46285</v>
+      </c>
+      <c r="F90" s="5">
+        <v>7551.88</v>
+      </c>
+      <c r="G90" s="5">
+        <v>7551.88</v>
       </c>
       <c r="H90" s="3"/>
-      <c r="I90" s="6" t="n">
-        <v>6</v>
+      <c r="I90" s="6">
+        <v>9</v>
       </c>
       <c r="J90" s="4" t="s">
         <v>170</v>
       </c>
       <c r="K90" s="4" t="s">
-        <v>27</v>
+        <v>190</v>
       </c>
       <c r="L90" s="4"/>
       <c r="M90" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="N90" s="4"/>
       <c r="O90" s="4"/>
     </row>
-    <row r="91" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A91" s="3" t="n">
-        <v>46234</v>
+    <row r="91" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="3">
+        <v>46244</v>
       </c>
       <c r="B91" s="4" t="s">
         <v>45</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="E91" s="3" t="n">
-        <v>46284</v>
-      </c>
-      <c r="F91" s="5" t="n">
-        <v>4950.17</v>
-      </c>
-      <c r="G91" s="5" t="n">
-        <v>4950.17</v>
+        <v>231</v>
+      </c>
+      <c r="E91" s="3">
+        <v>46286</v>
+      </c>
+      <c r="F91" s="5">
+        <v>4320</v>
+      </c>
+      <c r="G91" s="5">
+        <v>4320</v>
       </c>
       <c r="H91" s="3"/>
-      <c r="I91" s="6" t="n">
-        <v>6</v>
+      <c r="I91" s="6">
+        <v>8</v>
       </c>
       <c r="J91" s="4" t="s">
         <v>170</v>
@@ -4509,159 +4890,159 @@
       </c>
       <c r="L91" s="4"/>
       <c r="M91" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="N91" s="4"/>
       <c r="O91" s="4"/>
     </row>
-    <row r="92" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A92" s="3" t="n">
-        <v>46225</v>
+    <row r="92" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="3">
+        <v>46266</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>187</v>
+        <v>45</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="E92" s="3" t="n">
-        <v>46285</v>
-      </c>
-      <c r="F92" s="5" t="n">
-        <v>7551.88</v>
-      </c>
-      <c r="G92" s="5" t="n">
-        <v>7551.88</v>
+        <v>233</v>
+      </c>
+      <c r="E92" s="3">
+        <v>46287</v>
+      </c>
+      <c r="F92" s="5">
+        <v>18600</v>
+      </c>
+      <c r="G92" s="5">
+        <v>18600</v>
       </c>
       <c r="H92" s="3"/>
-      <c r="I92" s="6" t="n">
-        <v>5</v>
+      <c r="I92" s="6">
+        <v>7</v>
       </c>
       <c r="J92" s="4" t="s">
-        <v>170</v>
+        <v>26</v>
       </c>
       <c r="K92" s="4" t="s">
-        <v>190</v>
+        <v>27</v>
       </c>
       <c r="L92" s="4"/>
       <c r="M92" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="N92" s="4"/>
       <c r="O92" s="4"/>
     </row>
-    <row r="93" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A93" s="3" t="n">
-        <v>46244</v>
+    <row r="93" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="3">
+        <v>46252</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>45</v>
+        <v>172</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>184</v>
+        <v>235</v>
       </c>
       <c r="D93" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="E93" s="3" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F93" s="5" t="n">
-        <v>4320</v>
-      </c>
-      <c r="G93" s="5" t="n">
-        <v>4320</v>
+      <c r="E93" s="3">
+        <v>46287</v>
+      </c>
+      <c r="F93" s="5">
+        <v>5443.56</v>
+      </c>
+      <c r="G93" s="5">
+        <v>5443.56</v>
       </c>
       <c r="H93" s="3"/>
-      <c r="I93" s="6" t="n">
-        <v>4</v>
+      <c r="I93" s="6">
+        <v>7</v>
       </c>
       <c r="J93" s="4" t="s">
-        <v>170</v>
+        <v>26</v>
       </c>
       <c r="K93" s="4" t="s">
-        <v>27</v>
+        <v>237</v>
       </c>
       <c r="L93" s="4"/>
       <c r="M93" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="N93" s="4"/>
       <c r="O93" s="4"/>
     </row>
-    <row r="94" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A94" s="3" t="n">
-        <v>46266</v>
+    <row r="94" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="3">
+        <v>46227</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>45</v>
+        <v>187</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="E94" s="3" t="n">
+        <v>239</v>
+      </c>
+      <c r="E94" s="3">
         <v>46287</v>
       </c>
-      <c r="F94" s="5" t="n">
-        <v>18600</v>
-      </c>
-      <c r="G94" s="5" t="n">
-        <v>18600</v>
+      <c r="F94" s="5">
+        <v>4216.67</v>
+      </c>
+      <c r="G94" s="5">
+        <v>4216.67</v>
       </c>
       <c r="H94" s="3"/>
-      <c r="I94" s="6" t="n">
-        <v>3</v>
+      <c r="I94" s="6">
+        <v>7</v>
       </c>
       <c r="J94" s="4" t="s">
-        <v>26</v>
+        <v>193</v>
       </c>
       <c r="K94" s="4" t="s">
-        <v>27</v>
+        <v>190</v>
       </c>
       <c r="L94" s="4"/>
       <c r="M94" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="N94" s="4"/>
       <c r="O94" s="4"/>
     </row>
-    <row r="95" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A95" s="3" t="n">
-        <v>46252</v>
+    <row r="95" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="3">
+        <v>46253</v>
       </c>
       <c r="B95" s="4" t="s">
         <v>172</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="E95" s="3" t="n">
-        <v>46287</v>
-      </c>
-      <c r="F95" s="5" t="n">
-        <v>5443.56</v>
-      </c>
-      <c r="G95" s="5" t="n">
-        <v>5443.56</v>
+        <v>242</v>
+      </c>
+      <c r="E95" s="3">
+        <v>46288</v>
+      </c>
+      <c r="F95" s="5">
+        <v>1452.6</v>
+      </c>
+      <c r="G95" s="5">
+        <v>1452.6</v>
       </c>
       <c r="H95" s="3"/>
-      <c r="I95" s="6" t="n">
-        <v>3</v>
+      <c r="I95" s="6">
+        <v>6</v>
       </c>
       <c r="J95" s="4" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="K95" s="4" t="s">
-        <v>242</v>
+        <v>175</v>
       </c>
       <c r="L95" s="4"/>
       <c r="M95" s="4" t="s">
@@ -4670,37 +5051,37 @@
       <c r="N95" s="4"/>
       <c r="O95" s="4"/>
     </row>
-    <row r="96" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A96" s="3" t="n">
-        <v>46227</v>
+    <row r="96" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="3">
+        <v>46253</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>187</v>
+        <v>45</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D96" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="E96" s="3" t="n">
-        <v>46287</v>
-      </c>
-      <c r="F96" s="5" t="n">
-        <v>4216.67</v>
-      </c>
-      <c r="G96" s="5" t="n">
-        <v>4216.67</v>
+      <c r="E96" s="3">
+        <v>46288</v>
+      </c>
+      <c r="F96" s="5">
+        <v>10080</v>
+      </c>
+      <c r="G96" s="5">
+        <v>10080</v>
       </c>
       <c r="H96" s="3"/>
-      <c r="I96" s="6" t="n">
-        <v>3</v>
+      <c r="I96" s="6">
+        <v>6</v>
       </c>
       <c r="J96" s="4" t="s">
-        <v>193</v>
+        <v>170</v>
       </c>
       <c r="K96" s="4" t="s">
-        <v>190</v>
+        <v>27</v>
       </c>
       <c r="L96" s="4"/>
       <c r="M96" s="4" t="s">
@@ -4709,12 +5090,12 @@
       <c r="N96" s="4"/>
       <c r="O96" s="4"/>
     </row>
-    <row r="97" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A97" s="3" t="n">
+    <row r="97" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="3">
         <v>46253</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>172</v>
+        <v>121</v>
       </c>
       <c r="C97" s="4" t="s">
         <v>246</v>
@@ -4722,24 +5103,24 @@
       <c r="D97" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="E97" s="3" t="n">
+      <c r="E97" s="3">
         <v>46288</v>
       </c>
-      <c r="F97" s="5" t="n">
-        <v>1452.6</v>
-      </c>
-      <c r="G97" s="5" t="n">
-        <v>1452.6</v>
+      <c r="F97" s="5">
+        <v>3640</v>
+      </c>
+      <c r="G97" s="5">
+        <v>3640</v>
       </c>
       <c r="H97" s="3"/>
-      <c r="I97" s="6" t="n">
-        <v>2</v>
+      <c r="I97" s="6">
+        <v>6</v>
       </c>
       <c r="J97" s="4" t="s">
-        <v>18</v>
+        <v>170</v>
       </c>
       <c r="K97" s="4" t="s">
-        <v>175</v>
+        <v>124</v>
       </c>
       <c r="L97" s="4"/>
       <c r="M97" s="4" t="s">
@@ -4748,37 +5129,37 @@
       <c r="N97" s="4"/>
       <c r="O97" s="4"/>
     </row>
-    <row r="98" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A98" s="3" t="n">
+    <row r="98" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="3">
         <v>46253</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>45</v>
+        <v>121</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>184</v>
+        <v>246</v>
       </c>
       <c r="D98" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="E98" s="3" t="n">
+      <c r="E98" s="3">
         <v>46288</v>
       </c>
-      <c r="F98" s="5" t="n">
-        <v>10080</v>
-      </c>
-      <c r="G98" s="5" t="n">
-        <v>10080</v>
+      <c r="F98" s="5">
+        <v>1660.33</v>
+      </c>
+      <c r="G98" s="5">
+        <v>1660.33</v>
       </c>
       <c r="H98" s="3"/>
-      <c r="I98" s="6" t="n">
-        <v>2</v>
+      <c r="I98" s="6">
+        <v>6</v>
       </c>
       <c r="J98" s="4" t="s">
-        <v>170</v>
+        <v>18</v>
       </c>
       <c r="K98" s="4" t="s">
-        <v>27</v>
+        <v>124</v>
       </c>
       <c r="L98" s="4"/>
       <c r="M98" s="4" t="s">
@@ -4787,12 +5168,12 @@
       <c r="N98" s="4"/>
       <c r="O98" s="4"/>
     </row>
-    <row r="99" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A99" s="3" t="n">
-        <v>46253</v>
+    <row r="99" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="3">
+        <v>46259</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>121</v>
+        <v>15</v>
       </c>
       <c r="C99" s="4" t="s">
         <v>251</v>
@@ -4800,24 +5181,24 @@
       <c r="D99" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="E99" s="3" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F99" s="5" t="n">
-        <v>3640</v>
-      </c>
-      <c r="G99" s="5" t="n">
-        <v>3640</v>
+      <c r="E99" s="3">
+        <v>46289</v>
+      </c>
+      <c r="F99" s="5">
+        <v>6265</v>
+      </c>
+      <c r="G99" s="5">
+        <v>6265</v>
       </c>
       <c r="H99" s="3"/>
-      <c r="I99" s="6" t="n">
-        <v>2</v>
+      <c r="I99" s="6">
+        <v>5</v>
       </c>
       <c r="J99" s="4" t="s">
         <v>170</v>
       </c>
       <c r="K99" s="4" t="s">
-        <v>124</v>
+        <v>19</v>
       </c>
       <c r="L99" s="4"/>
       <c r="M99" s="4" t="s">
@@ -4826,106 +5207,631 @@
       <c r="N99" s="4"/>
       <c r="O99" s="4"/>
     </row>
-    <row r="100" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A100" s="3" t="n">
-        <v>46253</v>
+    <row r="100" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="3">
+        <v>46262</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>121</v>
+        <v>254</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="E100" s="3" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F100" s="5" t="n">
-        <v>1660.33</v>
-      </c>
-      <c r="G100" s="5" t="n">
-        <v>1660.33</v>
+        <v>256</v>
+      </c>
+      <c r="E100" s="3">
+        <v>46290</v>
+      </c>
+      <c r="F100" s="5">
+        <v>7694.4</v>
+      </c>
+      <c r="G100" s="5">
+        <v>7694.4</v>
       </c>
       <c r="H100" s="3"/>
-      <c r="I100" s="6" t="n">
-        <v>2</v>
+      <c r="I100" s="6">
+        <v>4</v>
       </c>
       <c r="J100" s="4" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="K100" s="4" t="s">
-        <v>124</v>
+        <v>257</v>
       </c>
       <c r="L100" s="4"/>
       <c r="M100" s="4" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="N100" s="4"/>
       <c r="O100" s="4"/>
     </row>
-    <row r="101" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A101" s="3" t="n">
-        <v>46259</v>
+    <row r="101" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="3">
+        <v>46262</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>15</v>
+        <v>254</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="E101" s="3" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F101" s="5" t="n">
-        <v>6265</v>
-      </c>
-      <c r="G101" s="5" t="n">
-        <v>6265</v>
+        <v>259</v>
+      </c>
+      <c r="E101" s="3">
+        <v>46290</v>
+      </c>
+      <c r="F101" s="5">
+        <v>11660.11</v>
+      </c>
+      <c r="G101" s="5">
+        <v>11660.11</v>
       </c>
       <c r="H101" s="3"/>
-      <c r="I101" s="6" t="n">
-        <v>1</v>
+      <c r="I101" s="6">
+        <v>4</v>
       </c>
       <c r="J101" s="4" t="s">
         <v>170</v>
       </c>
       <c r="K101" s="4" t="s">
-        <v>19</v>
+        <v>257</v>
       </c>
       <c r="L101" s="4"/>
       <c r="M101" s="4" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N101" s="4"/>
       <c r="O101" s="4"/>
     </row>
-    <row r="102" customHeight="true" ht="13.5" customFormat="true" s="1">
-      <c r="A102" s="7"/>
-      <c r="B102" s="8"/>
-      <c r="C102" s="8"/>
-      <c r="D102" s="8"/>
-      <c r="E102" s="8"/>
-      <c r="F102" s="9" t="n">
-        <v>576377.62</v>
-      </c>
-      <c r="G102" s="9" t="n">
-        <v>609280.9</v>
-      </c>
-      <c r="H102" s="8"/>
-      <c r="I102" s="8"/>
-      <c r="J102" s="8"/>
-      <c r="K102" s="8"/>
-      <c r="L102" s="8"/>
-      <c r="M102" s="8"/>
-      <c r="N102" s="8"/>
-      <c r="O102" s="10"/>
+    <row r="102" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="3">
+        <v>46262</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="D102" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="E102" s="3">
+        <v>46290</v>
+      </c>
+      <c r="F102" s="5">
+        <v>2992</v>
+      </c>
+      <c r="G102" s="5">
+        <v>2992</v>
+      </c>
+      <c r="H102" s="3"/>
+      <c r="I102" s="6">
+        <v>4</v>
+      </c>
+      <c r="J102" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="K102" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="L102" s="4"/>
+      <c r="M102" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="N102" s="4"/>
+      <c r="O102" s="4"/>
+    </row>
+    <row r="103" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="3">
+        <v>46231</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="D103" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="E103" s="3">
+        <v>46291</v>
+      </c>
+      <c r="F103" s="5">
+        <v>6500</v>
+      </c>
+      <c r="G103" s="5">
+        <v>6500</v>
+      </c>
+      <c r="H103" s="3"/>
+      <c r="I103" s="6">
+        <v>3</v>
+      </c>
+      <c r="J103" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K103" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="L103" s="4"/>
+      <c r="M103" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="N103" s="4"/>
+      <c r="O103" s="4"/>
+    </row>
+    <row r="104" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="3">
+        <v>46262</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="D104" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="E104" s="3">
+        <v>46292</v>
+      </c>
+      <c r="F104" s="5">
+        <v>4689.22</v>
+      </c>
+      <c r="G104" s="5">
+        <v>4689.22</v>
+      </c>
+      <c r="H104" s="3"/>
+      <c r="I104" s="6">
+        <v>2</v>
+      </c>
+      <c r="J104" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="K104" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="L104" s="4"/>
+      <c r="M104" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="N104" s="4"/>
+      <c r="O104" s="4"/>
+    </row>
+    <row r="105" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="3">
+        <v>46232</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C105" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="D105" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="E105" s="3">
+        <v>46292</v>
+      </c>
+      <c r="F105" s="5">
+        <v>9716</v>
+      </c>
+      <c r="G105" s="5">
+        <v>9716</v>
+      </c>
+      <c r="H105" s="3"/>
+      <c r="I105" s="6">
+        <v>2</v>
+      </c>
+      <c r="J105" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K105" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="L105" s="4"/>
+      <c r="M105" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="N105" s="4"/>
+      <c r="O105" s="4"/>
+    </row>
+    <row r="106" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="3">
+        <v>46232</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="D106" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="E106" s="3">
+        <v>46292</v>
+      </c>
+      <c r="F106" s="5">
+        <v>4082.05</v>
+      </c>
+      <c r="G106" s="5">
+        <v>4082.05</v>
+      </c>
+      <c r="H106" s="3"/>
+      <c r="I106" s="6">
+        <v>2</v>
+      </c>
+      <c r="J106" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="K106" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="L106" s="4"/>
+      <c r="M106" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="N106" s="4"/>
+      <c r="O106" s="4"/>
+    </row>
+    <row r="107" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="3">
+        <v>46244</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="D107" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="E107" s="3">
+        <v>46293</v>
+      </c>
+      <c r="F107" s="5">
+        <v>3599.85</v>
+      </c>
+      <c r="G107" s="5">
+        <v>3599.85</v>
+      </c>
+      <c r="H107" s="3"/>
+      <c r="I107" s="6">
+        <v>1</v>
+      </c>
+      <c r="J107" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K107" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="L107" s="4"/>
+      <c r="M107" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="N107" s="4"/>
+      <c r="O107" s="4"/>
+    </row>
+    <row r="108" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="3">
+        <v>46230</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C108" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="D108" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="E108" s="3">
+        <v>46293</v>
+      </c>
+      <c r="F108" s="5">
+        <v>1513.13</v>
+      </c>
+      <c r="G108" s="5">
+        <v>1513.13</v>
+      </c>
+      <c r="H108" s="3"/>
+      <c r="I108" s="6">
+        <v>1</v>
+      </c>
+      <c r="J108" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="K108" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="L108" s="4"/>
+      <c r="M108" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="N108" s="4"/>
+      <c r="O108" s="4"/>
+    </row>
+    <row r="109" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="3">
+        <v>46223</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C109" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="D109" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="E109" s="3">
+        <v>46293</v>
+      </c>
+      <c r="F109" s="5">
+        <v>6265</v>
+      </c>
+      <c r="G109" s="5">
+        <v>6265</v>
+      </c>
+      <c r="H109" s="3"/>
+      <c r="I109" s="6">
+        <v>1</v>
+      </c>
+      <c r="J109" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="K109" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="L109" s="4"/>
+      <c r="M109" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="N109" s="4"/>
+      <c r="O109" s="4"/>
+    </row>
+    <row r="110" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="3">
+        <v>46244</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C110" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="D110" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="E110" s="3">
+        <v>46293</v>
+      </c>
+      <c r="F110" s="5">
+        <v>4320</v>
+      </c>
+      <c r="G110" s="5">
+        <v>4320</v>
+      </c>
+      <c r="H110" s="3"/>
+      <c r="I110" s="6">
+        <v>1</v>
+      </c>
+      <c r="J110" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="K110" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L110" s="4"/>
+      <c r="M110" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="N110" s="4"/>
+      <c r="O110" s="4"/>
+    </row>
+    <row r="111" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="3">
+        <v>46223</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="D111" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="E111" s="3">
+        <v>46293</v>
+      </c>
+      <c r="F111" s="5">
+        <v>11200</v>
+      </c>
+      <c r="G111" s="5">
+        <v>11200</v>
+      </c>
+      <c r="H111" s="3"/>
+      <c r="I111" s="6">
+        <v>1</v>
+      </c>
+      <c r="J111" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="K111" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L111" s="4"/>
+      <c r="M111" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="N111" s="4"/>
+      <c r="O111" s="4"/>
+    </row>
+    <row r="112" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="3">
+        <v>46251</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="D112" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="E112" s="3">
+        <v>46293</v>
+      </c>
+      <c r="F112" s="5">
+        <v>2521.25</v>
+      </c>
+      <c r="G112" s="5">
+        <v>2521.25</v>
+      </c>
+      <c r="H112" s="3"/>
+      <c r="I112" s="6">
+        <v>1</v>
+      </c>
+      <c r="J112" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="K112" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="L112" s="4"/>
+      <c r="M112" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="N112" s="4"/>
+      <c r="O112" s="4"/>
+    </row>
+    <row r="113" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="3">
+        <v>46265</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C113" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="D113" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="E113" s="3">
+        <v>46293</v>
+      </c>
+      <c r="F113" s="5">
+        <v>1664</v>
+      </c>
+      <c r="G113" s="5">
+        <v>1664</v>
+      </c>
+      <c r="H113" s="3"/>
+      <c r="I113" s="6">
+        <v>1</v>
+      </c>
+      <c r="J113" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K113" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="L113" s="4"/>
+      <c r="M113" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="N113" s="4"/>
+      <c r="O113" s="4"/>
+    </row>
+    <row r="114" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="3">
+        <v>46248</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C114" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="D114" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="E114" s="3">
+        <v>46293</v>
+      </c>
+      <c r="F114" s="5">
+        <v>23355.33</v>
+      </c>
+      <c r="G114" s="5">
+        <v>23355.33</v>
+      </c>
+      <c r="H114" s="3"/>
+      <c r="I114" s="6">
+        <v>1</v>
+      </c>
+      <c r="J114" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="K114" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="L114" s="4"/>
+      <c r="M114" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="N114" s="4"/>
+      <c r="O114" s="4"/>
+    </row>
+    <row r="115" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="3">
+        <v>46251</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C115" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="D115" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="E115" s="3">
+        <v>46293</v>
+      </c>
+      <c r="F115" s="5">
+        <v>2070.1999999999998</v>
+      </c>
+      <c r="G115" s="5">
+        <v>2070.1999999999998</v>
+      </c>
+      <c r="H115" s="3"/>
+      <c r="I115" s="6">
+        <v>1</v>
+      </c>
+      <c r="J115" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K115" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="L115" s="4"/>
+      <c r="M115" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="N115" s="4"/>
+      <c r="O115" s="4"/>
     </row>
   </sheetData>
-  <pageSetup orientation="default" cellComments="none"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
+++ b/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WINDOWS\Desktop\dados planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4441FE2C-9A11-40BB-B10C-EFCBF2BF743D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E03B8382-F475-45D1-A673-F8782CE068B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="715" uniqueCount="304">
   <si>
     <t>Dt.Emissão</t>
   </si>
@@ -462,6 +462,12 @@
     <t>00191125800002144590000003473568000002964317</t>
   </si>
   <si>
+    <t>PHARMACEUTICA DISTRIBUIDORA DE MAT. E MED. HOSPITA</t>
+  </si>
+  <si>
+    <t>01005217.1BPBPBPBP</t>
+  </si>
+  <si>
     <t>BR MEDICAMENTOS LTDA</t>
   </si>
   <si>
@@ -471,12 +477,6 @@
     <t>00195127000004480000000003473568000002981317</t>
   </si>
   <si>
-    <t>PHARMACEUTICA DISTRIBUIDORA DE MAT. E MED. HOSPITA</t>
-  </si>
-  <si>
-    <t>01005217.1BPBPBPBP</t>
-  </si>
-  <si>
     <t>01005217.2BP</t>
   </si>
   <si>
@@ -603,6 +603,12 @@
     <t>70797156000011442870001121205064100656763979</t>
   </si>
   <si>
+    <t>01007005.2</t>
+  </si>
+  <si>
+    <t>00193156200009716000000003473568000003145917</t>
+  </si>
+  <si>
     <t>01006976.1</t>
   </si>
   <si>
@@ -612,12 +618,6 @@
     <t>23791156200006389240435090000000114600304920</t>
   </si>
   <si>
-    <t>01007005.2</t>
-  </si>
-  <si>
-    <t>00193156200009716000000003473568000003145917</t>
-  </si>
-  <si>
     <t>01006941.4</t>
   </si>
   <si>
@@ -669,214 +669,169 @@
     <t>00196157200009716000000003473568000003146017</t>
   </si>
   <si>
+    <t>01006958.6</t>
+  </si>
+  <si>
+    <t>70798157300023168600001121205064100656764092</t>
+  </si>
+  <si>
+    <t>01006922.2</t>
+  </si>
+  <si>
+    <t>70792157300011200000001121205064100656763888</t>
+  </si>
+  <si>
+    <t>01006957.2</t>
+  </si>
+  <si>
+    <t>70792157400010666670001121205064100656763953</t>
+  </si>
+  <si>
+    <t>01006999.1</t>
+  </si>
+  <si>
+    <t>70799157400006500000001121205064100656764282</t>
+  </si>
+  <si>
+    <t>01007020.1</t>
+  </si>
+  <si>
+    <t>70799157400004950170001121205064100656764449</t>
+  </si>
+  <si>
+    <t>01006920.2</t>
+  </si>
+  <si>
+    <t>70794157500007551880001121205064100656763987</t>
+  </si>
+  <si>
+    <t>01007125.4</t>
+  </si>
+  <si>
+    <t>70791157600004320000001121205064100656765123</t>
+  </si>
+  <si>
+    <t>01007301.1</t>
+  </si>
+  <si>
+    <t>00192157700018600000000003473568000003161317</t>
+  </si>
+  <si>
+    <t>01006976.2</t>
+  </si>
+  <si>
+    <t>23791157700004216670435090000000114700304920</t>
+  </si>
+  <si>
+    <t>01007187.3</t>
+  </si>
+  <si>
+    <t>70793157800010080000001121205064100656766204</t>
+  </si>
+  <si>
+    <t>DROGUISTA CEARENSE LTDA</t>
+  </si>
+  <si>
+    <t>01007175.2</t>
+  </si>
+  <si>
+    <t>34193157800001660331090002618768120992717000</t>
+  </si>
+  <si>
+    <t>01007171.2</t>
+  </si>
+  <si>
+    <t>70794157800003640000001121205064100656766162</t>
+  </si>
+  <si>
+    <t>COBERMED COMERCIO DE MATERIAIS MEDICOS LTDA</t>
+  </si>
+  <si>
+    <t>01007194.1</t>
+  </si>
+  <si>
+    <t>70797157900006265000001121205064100656766642</t>
+  </si>
+  <si>
+    <t>FELIPE AQUINO - MT</t>
+  </si>
+  <si>
+    <t>FAMA DISTRIBUIDORA HOSPITALAR LTDA</t>
+  </si>
+  <si>
+    <t>01007265.1</t>
+  </si>
+  <si>
+    <t>MT</t>
+  </si>
+  <si>
+    <t>00198158000007694400000003473568000003158817</t>
+  </si>
+  <si>
+    <t>01007249.1</t>
+  </si>
+  <si>
+    <t>70793158000011660110001121205064100656766915</t>
+  </si>
+  <si>
+    <t>01006998.2</t>
+  </si>
+  <si>
+    <t>00191158100006500000000003473568000003144317</t>
+  </si>
+  <si>
+    <t>01007005.4</t>
+  </si>
+  <si>
+    <t>00197158200009716000000003473568000003146117</t>
+  </si>
+  <si>
+    <t>FERMATA LTDA</t>
+  </si>
+  <si>
+    <t>01006989.2</t>
+  </si>
+  <si>
+    <t>70795158200004082050001121205064100656764191</t>
+  </si>
+  <si>
+    <t>LICIMASTER DIST. DE MED. E PRODUTOS MEDICO</t>
+  </si>
+  <si>
+    <t>01007094.4</t>
+  </si>
+  <si>
+    <t>34191158300003599851090002612318120992717000</t>
+  </si>
+  <si>
+    <t>01006877.3</t>
+  </si>
+  <si>
+    <t>23797158300006265000435090000000110700304920</t>
+  </si>
+  <si>
+    <t>01007125.5</t>
+  </si>
+  <si>
+    <t>70799158300004320000001121205064100656765131</t>
+  </si>
+  <si>
     <t>ASPEN SERVICE COMERCIO LTDA</t>
   </si>
   <si>
-    <t>01006665.4</t>
-  </si>
-  <si>
-    <t>00192157200022750000000003473568000003126417</t>
-  </si>
-  <si>
-    <t>01006922.2</t>
-  </si>
-  <si>
-    <t>70792157300011200000001121205064100656763888</t>
-  </si>
-  <si>
-    <t>01007197.1</t>
-  </si>
-  <si>
-    <t>23791157300001172160435090000000124600304920</t>
-  </si>
-  <si>
-    <t>01006958.6</t>
-  </si>
-  <si>
-    <t>70798157300023168600001121205064100656764092</t>
-  </si>
-  <si>
-    <t>01006957.2</t>
-  </si>
-  <si>
-    <t>70792157400010666670001121205064100656763953</t>
-  </si>
-  <si>
-    <t>01006999.1</t>
-  </si>
-  <si>
-    <t>70799157400006500000001121205064100656764282</t>
-  </si>
-  <si>
-    <t>01007020.1</t>
-  </si>
-  <si>
-    <t>70799157400004950170001121205064100656764449</t>
-  </si>
-  <si>
-    <t>01006920.2</t>
-  </si>
-  <si>
-    <t>70794157500007551880001121205064100656763987</t>
-  </si>
-  <si>
-    <t>01007125.4</t>
-  </si>
-  <si>
-    <t>70791157600004320000001121205064100656765123</t>
-  </si>
-  <si>
-    <t>01007301.1</t>
-  </si>
-  <si>
-    <t>00192157700018600000000003473568000003161317</t>
-  </si>
-  <si>
-    <t>AMAZONIA HOSPITALAR LTDA</t>
-  </si>
-  <si>
-    <t>01007105.2</t>
-  </si>
-  <si>
-    <t>MA</t>
-  </si>
-  <si>
-    <t>00199157700005443560000003473568000003154817</t>
-  </si>
-  <si>
-    <t>01006976.2</t>
-  </si>
-  <si>
-    <t>23791157700004216670435090000000114700304920</t>
-  </si>
-  <si>
-    <t>HOSPMED LTDA</t>
-  </si>
-  <si>
-    <t>01007167.2</t>
-  </si>
-  <si>
-    <t>34194157800001452601090002616948120992717000</t>
-  </si>
-  <si>
-    <t>01007187.3</t>
-  </si>
-  <si>
-    <t>70793157800010080000001121205064100656766204</t>
-  </si>
-  <si>
-    <t>DROGUISTA CEARENSE LTDA</t>
-  </si>
-  <si>
-    <t>01007171.2</t>
-  </si>
-  <si>
-    <t>70794157800003640000001121205064100656766162</t>
-  </si>
-  <si>
-    <t>01007175.2</t>
-  </si>
-  <si>
-    <t>34193157800001660331090002618768120992717000</t>
-  </si>
-  <si>
-    <t>COBERMED COMERCIO DE MATERIAIS MEDICOS LTDA</t>
-  </si>
-  <si>
-    <t>01007194.1</t>
-  </si>
-  <si>
-    <t>70797157900006265000001121205064100656766642</t>
-  </si>
-  <si>
-    <t>FELIPE AQUINO - MT</t>
-  </si>
-  <si>
-    <t>FAMA DISTRIBUIDORA HOSPITALAR LTDA</t>
-  </si>
-  <si>
-    <t>01007265.1</t>
-  </si>
-  <si>
-    <t>MT</t>
-  </si>
-  <si>
-    <t>00198158000007694400000003473568000003158817</t>
-  </si>
-  <si>
-    <t>01007249.1</t>
-  </si>
-  <si>
-    <t>70793158000011660110001121205064100656766915</t>
-  </si>
-  <si>
-    <t>01007224.1</t>
-  </si>
-  <si>
-    <t>70795158000002992000001121205064100656766857</t>
-  </si>
-  <si>
-    <t>01006998.2</t>
-  </si>
-  <si>
-    <t>00191158100006500000000003473568000003144317</t>
-  </si>
-  <si>
-    <t>LEANDRA LUIZA SILVA - AM</t>
-  </si>
-  <si>
-    <t>JM COMERCIO DE PRODUTOS FARMACEUTICOS LTDA</t>
-  </si>
-  <si>
-    <t>01007186.1</t>
-  </si>
-  <si>
-    <t>AM</t>
-  </si>
-  <si>
-    <t>70796158200004689220001121205064100656766782</t>
-  </si>
-  <si>
-    <t>01007005.4</t>
-  </si>
-  <si>
-    <t>00197158200009716000000003473568000003146117</t>
-  </si>
-  <si>
-    <t>FERMATA LTDA</t>
-  </si>
-  <si>
-    <t>01006989.2</t>
-  </si>
-  <si>
-    <t>70795158200004082050001121205064100656764191</t>
-  </si>
-  <si>
-    <t>LICIMASTER DIST. DE MED. E PRODUTOS MEDICO</t>
-  </si>
-  <si>
-    <t>01007094.4</t>
-  </si>
-  <si>
-    <t>34191158300003599851090002612318120992717000</t>
-  </si>
-  <si>
-    <t>01006978.6</t>
-  </si>
-  <si>
-    <t>23796158300001513130435090000000116500304920</t>
-  </si>
-  <si>
-    <t>01006877.3</t>
-  </si>
-  <si>
-    <t>23797158300006265000435090000000110700304920</t>
-  </si>
-  <si>
-    <t>01007125.5</t>
-  </si>
-  <si>
-    <t>70799158300004320000001121205064100656765131</t>
+    <t>01007117.1</t>
+  </si>
+  <si>
+    <t>70791158300023355330001121205064100656765669</t>
+  </si>
+  <si>
+    <t>ATACAMED COMERCIO LTDA</t>
+  </si>
+  <si>
+    <t>01007274.1</t>
+  </si>
+  <si>
+    <t>34192158300001664001090002623468120992717000</t>
   </si>
   <si>
     <t>01006922.3</t>
@@ -885,37 +840,103 @@
     <t>70798158300011200000001121205064100656763896</t>
   </si>
   <si>
-    <t>R5 SOLUCOES EM SAUDE LTDA</t>
-  </si>
-  <si>
-    <t>01007136.3</t>
-  </si>
-  <si>
-    <t>70795158300002521250001121205064100656765842</t>
-  </si>
-  <si>
-    <t>ATACAMED COMERCIO LTDA</t>
-  </si>
-  <si>
-    <t>01007274.1</t>
-  </si>
-  <si>
-    <t>34192158300001664001090002623468120992717000</t>
-  </si>
-  <si>
-    <t>01007117.1</t>
-  </si>
-  <si>
-    <t>70791158300023355330001121205064100656765669</t>
-  </si>
-  <si>
-    <t>OMNIELMASTER HEMOMED REPRESENTACAO</t>
-  </si>
-  <si>
-    <t>01007164.3</t>
-  </si>
-  <si>
-    <t>34199158300002070201090002615878120992717000</t>
+    <t>01007301.2</t>
+  </si>
+  <si>
+    <t>00197158400018600000000003473568000003161417</t>
+  </si>
+  <si>
+    <t>01007023.2</t>
+  </si>
+  <si>
+    <t>70791158400003789090001121205064100656764423</t>
+  </si>
+  <si>
+    <t>01007269.1</t>
+  </si>
+  <si>
+    <t>70791158500008947500001121205064100656767137</t>
+  </si>
+  <si>
+    <t>01007187.4</t>
+  </si>
+  <si>
+    <t>70792158500010080000001121205064100656766212</t>
+  </si>
+  <si>
+    <t>VITAL DISTRIBUIDORA LTDA</t>
+  </si>
+  <si>
+    <t>01007168.3</t>
+  </si>
+  <si>
+    <t>34196158500002051221090002617698120992717000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZOE MED COMERCIO DE PRODUTOS MEDICOS HOSPITALARES </t>
+  </si>
+  <si>
+    <t>01007270.1</t>
+  </si>
+  <si>
+    <t>70793158500008565680001121205064100656766972</t>
+  </si>
+  <si>
+    <t>01007171.3</t>
+  </si>
+  <si>
+    <t>70793158500003640000001121205064100656766170</t>
+  </si>
+  <si>
+    <t>01007175.3</t>
+  </si>
+  <si>
+    <t>34194158500001660341090002618848120992717000</t>
+  </si>
+  <si>
+    <t>01007311.1</t>
+  </si>
+  <si>
+    <t>23796158600002754000435090000000130000304920</t>
+  </si>
+  <si>
+    <t>ELIENE RESENDE - RJ</t>
+  </si>
+  <si>
+    <t>MEDKA DISTRIBUIDORA HOSPITALAR LTDA</t>
+  </si>
+  <si>
+    <t>01007278.1</t>
+  </si>
+  <si>
+    <t>RJ</t>
+  </si>
+  <si>
+    <t>70793158600008973500001121205064100656767319</t>
+  </si>
+  <si>
+    <t>01007265.2</t>
+  </si>
+  <si>
+    <t>00192158700007694400000003473568000003158917</t>
+  </si>
+  <si>
+    <t>01007249.2</t>
+  </si>
+  <si>
+    <t>70792158700011660110001121205064100656766923</t>
+  </si>
+  <si>
+    <t>01007074.3</t>
+  </si>
+  <si>
+    <t>34192158700002930401090002611578120992717000</t>
+  </si>
+  <si>
+    <t>01007169.2</t>
+  </si>
+  <si>
+    <t>70797158700003809520001121205064100656765974</t>
   </si>
 </sst>
 </file>
@@ -1345,7 +1366,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O115"/>
+  <dimension ref="A1:O120"/>
   <sheetFormatPr defaultColWidth="12.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.85546875" style="1" customWidth="1"/>
@@ -1437,7 +1458,7 @@
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="6">
-        <v>968</v>
+        <v>974</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>18</v>
@@ -1476,7 +1497,7 @@
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="6">
-        <v>948</v>
+        <v>954</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>18</v>
@@ -1515,7 +1536,7 @@
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="6">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>26</v>
@@ -1554,7 +1575,7 @@
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="6">
-        <v>938</v>
+        <v>944</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>18</v>
@@ -1593,7 +1614,7 @@
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="6">
-        <v>932</v>
+        <v>938</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>26</v>
@@ -1632,7 +1653,7 @@
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="6">
-        <v>930</v>
+        <v>936</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>26</v>
@@ -1671,7 +1692,7 @@
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="6">
-        <v>916</v>
+        <v>922</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>26</v>
@@ -1710,7 +1731,7 @@
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="6">
-        <v>831</v>
+        <v>837</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>18</v>
@@ -1749,7 +1770,7 @@
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="6">
-        <v>801</v>
+        <v>807</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>18</v>
@@ -1788,7 +1809,7 @@
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="6">
-        <v>771</v>
+        <v>777</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>18</v>
@@ -1827,7 +1848,7 @@
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="6">
-        <v>694</v>
+        <v>700</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>18</v>
@@ -1866,7 +1887,7 @@
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="6">
-        <v>687</v>
+        <v>693</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>18</v>
@@ -1905,7 +1926,7 @@
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="6">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>18</v>
@@ -1944,7 +1965,7 @@
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="6">
-        <v>680</v>
+        <v>686</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>18</v>
@@ -1983,7 +2004,7 @@
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="6">
-        <v>679</v>
+        <v>685</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>18</v>
@@ -2022,7 +2043,7 @@
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="6">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>18</v>
@@ -2061,7 +2082,7 @@
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="6">
-        <v>672</v>
+        <v>678</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>18</v>
@@ -2100,7 +2121,7 @@
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="6">
-        <v>672</v>
+        <v>678</v>
       </c>
       <c r="J19" s="4" t="s">
         <v>18</v>
@@ -2139,7 +2160,7 @@
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="6">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>18</v>
@@ -2178,7 +2199,7 @@
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="6">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>18</v>
@@ -2217,7 +2238,7 @@
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="6">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="J22" s="4" t="s">
         <v>18</v>
@@ -2256,7 +2277,7 @@
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="6">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="J23" s="4" t="s">
         <v>18</v>
@@ -2295,7 +2316,7 @@
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="6">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="J24" s="4" t="s">
         <v>18</v>
@@ -2334,7 +2355,7 @@
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="6">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="J25" s="4" t="s">
         <v>26</v>
@@ -2373,7 +2394,7 @@
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="6">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="J26" s="4" t="s">
         <v>18</v>
@@ -2412,7 +2433,7 @@
       </c>
       <c r="H27" s="3"/>
       <c r="I27" s="6">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="J27" s="4" t="s">
         <v>26</v>
@@ -2451,7 +2472,7 @@
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="6">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="J28" s="4" t="s">
         <v>26</v>
@@ -2490,7 +2511,7 @@
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="6">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="J29" s="4" t="s">
         <v>18</v>
@@ -2529,7 +2550,7 @@
       </c>
       <c r="H30" s="3"/>
       <c r="I30" s="6">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="J30" s="4" t="s">
         <v>18</v>
@@ -2568,7 +2589,7 @@
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="6">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="J31" s="4" t="s">
         <v>18</v>
@@ -2607,7 +2628,7 @@
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="6">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="J32" s="4" t="s">
         <v>26</v>
@@ -2646,7 +2667,7 @@
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="6">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="J33" s="4" t="s">
         <v>18</v>
@@ -2685,7 +2706,7 @@
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="6">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="J34" s="4" t="s">
         <v>18</v>
@@ -2724,7 +2745,7 @@
       </c>
       <c r="H35" s="3"/>
       <c r="I35" s="6">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="J35" s="4" t="s">
         <v>18</v>
@@ -2763,7 +2784,7 @@
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="6">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="J36" s="4" t="s">
         <v>18</v>
@@ -2802,7 +2823,7 @@
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="6">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="J37" s="4" t="s">
         <v>18</v>
@@ -2841,7 +2862,7 @@
       </c>
       <c r="H38" s="3"/>
       <c r="I38" s="6">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="J38" s="4" t="s">
         <v>18</v>
@@ -2880,7 +2901,7 @@
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="6">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="J39" s="4" t="s">
         <v>18</v>
@@ -2919,7 +2940,7 @@
       </c>
       <c r="H40" s="3"/>
       <c r="I40" s="6">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="J40" s="4" t="s">
         <v>18</v>
@@ -2958,7 +2979,7 @@
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="6">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="J41" s="4" t="s">
         <v>18</v>
@@ -2997,7 +3018,7 @@
       </c>
       <c r="H42" s="3"/>
       <c r="I42" s="6">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="J42" s="4" t="s">
         <v>18</v>
@@ -3036,7 +3057,7 @@
       </c>
       <c r="H43" s="3"/>
       <c r="I43" s="6">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="J43" s="4" t="s">
         <v>18</v>
@@ -3075,7 +3096,7 @@
       </c>
       <c r="H44" s="3"/>
       <c r="I44" s="6">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="J44" s="4" t="s">
         <v>26</v>
@@ -3114,7 +3135,7 @@
       </c>
       <c r="H45" s="3"/>
       <c r="I45" s="6">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="J45" s="4" t="s">
         <v>26</v>
@@ -3153,7 +3174,7 @@
       </c>
       <c r="H46" s="3"/>
       <c r="I46" s="6">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="J46" s="4" t="s">
         <v>26</v>
@@ -3192,7 +3213,7 @@
       </c>
       <c r="H47" s="3"/>
       <c r="I47" s="6">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="J47" s="4" t="s">
         <v>26</v>
@@ -3231,7 +3252,7 @@
       </c>
       <c r="H48" s="3"/>
       <c r="I48" s="6">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="J48" s="4" t="s">
         <v>26</v>
@@ -3270,7 +3291,7 @@
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="6">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="J49" s="4" t="s">
         <v>26</v>
@@ -3309,7 +3330,7 @@
       </c>
       <c r="H50" s="3"/>
       <c r="I50" s="6">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="J50" s="4" t="s">
         <v>26</v>
@@ -3348,7 +3369,7 @@
       </c>
       <c r="H51" s="3"/>
       <c r="I51" s="6">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="J51" s="4" t="s">
         <v>26</v>
@@ -3387,7 +3408,7 @@
       </c>
       <c r="H52" s="3"/>
       <c r="I52" s="6">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="J52" s="4" t="s">
         <v>26</v>
@@ -3404,10 +3425,10 @@
     </row>
     <row r="53" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
-        <v>45938</v>
+        <v>45959</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>145</v>
@@ -3419,60 +3440,60 @@
         <v>45980</v>
       </c>
       <c r="F53" s="5">
-        <v>4480</v>
+        <v>28666.44</v>
       </c>
       <c r="G53" s="5">
-        <v>4480</v>
+        <v>28666.44</v>
       </c>
       <c r="H53" s="3"/>
       <c r="I53" s="6">
-        <v>314</v>
-      </c>
-      <c r="J53" s="4" t="s">
-        <v>26</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="J53" s="4"/>
       <c r="K53" s="4" t="s">
-        <v>124</v>
+        <v>54</v>
       </c>
       <c r="L53" s="4"/>
-      <c r="M53" s="4" t="s">
-        <v>147</v>
-      </c>
+      <c r="M53" s="4"/>
       <c r="N53" s="4"/>
       <c r="O53" s="4"/>
     </row>
     <row r="54" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
-        <v>45959</v>
+        <v>45938</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="C54" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="D54" s="4" t="s">
         <v>148</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>149</v>
       </c>
       <c r="E54" s="3">
         <v>45980</v>
       </c>
       <c r="F54" s="5">
-        <v>28666.44</v>
+        <v>4480</v>
       </c>
       <c r="G54" s="5">
-        <v>28666.44</v>
+        <v>4480</v>
       </c>
       <c r="H54" s="3"/>
       <c r="I54" s="6">
-        <v>314</v>
-      </c>
-      <c r="J54" s="4"/>
+        <v>320</v>
+      </c>
+      <c r="J54" s="4" t="s">
+        <v>26</v>
+      </c>
       <c r="K54" s="4" t="s">
-        <v>54</v>
+        <v>124</v>
       </c>
       <c r="L54" s="4"/>
-      <c r="M54" s="4"/>
+      <c r="M54" s="4" t="s">
+        <v>149</v>
+      </c>
       <c r="N54" s="4"/>
       <c r="O54" s="4"/>
     </row>
@@ -3484,7 +3505,7 @@
         <v>135</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>150</v>
@@ -3500,7 +3521,7 @@
       </c>
       <c r="H55" s="3"/>
       <c r="I55" s="6">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="J55" s="4"/>
       <c r="K55" s="4" t="s">
@@ -3519,7 +3540,7 @@
         <v>121</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D56" s="4" t="s">
         <v>151</v>
@@ -3535,7 +3556,7 @@
       </c>
       <c r="H56" s="3"/>
       <c r="I56" s="6">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="J56" s="4"/>
       <c r="K56" s="4" t="s">
@@ -3554,7 +3575,7 @@
         <v>135</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>152</v>
@@ -3570,7 +3591,7 @@
       </c>
       <c r="H57" s="3"/>
       <c r="I57" s="6">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="J57" s="4"/>
       <c r="K57" s="4" t="s">
@@ -3605,7 +3626,7 @@
       </c>
       <c r="H58" s="3"/>
       <c r="I58" s="6">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="J58" s="4" t="s">
         <v>26</v>
@@ -3644,7 +3665,7 @@
       </c>
       <c r="H59" s="3"/>
       <c r="I59" s="6">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="J59" s="4" t="s">
         <v>26</v>
@@ -3683,7 +3704,7 @@
       </c>
       <c r="H60" s="3"/>
       <c r="I60" s="6">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="J60" s="4" t="s">
         <v>26</v>
@@ -3722,7 +3743,7 @@
       </c>
       <c r="H61" s="3"/>
       <c r="I61" s="6">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="J61" s="4" t="s">
         <v>18</v>
@@ -3745,7 +3766,7 @@
         <v>135</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>163</v>
@@ -3761,7 +3782,7 @@
       </c>
       <c r="H62" s="3"/>
       <c r="I62" s="6">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="J62" s="4"/>
       <c r="K62" s="4" t="s">
@@ -3780,7 +3801,7 @@
         <v>135</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D63" s="4" t="s">
         <v>164</v>
@@ -3796,7 +3817,7 @@
       </c>
       <c r="H63" s="3"/>
       <c r="I63" s="6">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="J63" s="4"/>
       <c r="K63" s="4" t="s">
@@ -3815,7 +3836,7 @@
         <v>135</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D64" s="4" t="s">
         <v>165</v>
@@ -3831,7 +3852,7 @@
       </c>
       <c r="H64" s="3"/>
       <c r="I64" s="6">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="J64" s="4"/>
       <c r="K64" s="4" t="s">
@@ -3866,7 +3887,7 @@
       </c>
       <c r="H65" s="3"/>
       <c r="I65" s="6">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="J65" s="4" t="s">
         <v>18</v>
@@ -3905,7 +3926,7 @@
       </c>
       <c r="H66" s="3"/>
       <c r="I66" s="6">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J66" s="4" t="s">
         <v>170</v>
@@ -3944,7 +3965,7 @@
       </c>
       <c r="H67" s="3"/>
       <c r="I67" s="6">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="J67" s="4" t="s">
         <v>26</v>
@@ -3983,7 +4004,7 @@
       </c>
       <c r="H68" s="3"/>
       <c r="I68" s="6">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="J68" s="4" t="s">
         <v>26</v>
@@ -4022,7 +4043,7 @@
       </c>
       <c r="H69" s="3"/>
       <c r="I69" s="6">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="J69" s="4" t="s">
         <v>26</v>
@@ -4061,7 +4082,7 @@
       </c>
       <c r="H70" s="3"/>
       <c r="I70" s="6">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J70" s="4" t="s">
         <v>26</v>
@@ -4100,7 +4121,7 @@
       </c>
       <c r="H71" s="3"/>
       <c r="I71" s="6">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J71" s="4" t="s">
         <v>170</v>
@@ -4139,7 +4160,7 @@
       </c>
       <c r="H72" s="3"/>
       <c r="I72" s="6">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J72" s="4" t="s">
         <v>170</v>
@@ -4156,13 +4177,13 @@
     </row>
     <row r="73" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="3">
-        <v>46227</v>
+        <v>46232</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>187</v>
+        <v>15</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="D73" s="4" t="s">
         <v>192</v>
@@ -4171,59 +4192,59 @@
         <v>46272</v>
       </c>
       <c r="F73" s="5">
-        <v>4216.67</v>
+        <v>9716</v>
       </c>
       <c r="G73" s="5">
-        <v>6389.24</v>
+        <v>9716</v>
       </c>
       <c r="H73" s="3"/>
       <c r="I73" s="6">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J73" s="4" t="s">
-        <v>193</v>
+        <v>26</v>
       </c>
       <c r="K73" s="4" t="s">
-        <v>190</v>
+        <v>39</v>
       </c>
       <c r="L73" s="4"/>
       <c r="M73" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="N73" s="4"/>
       <c r="O73" s="4"/>
     </row>
     <row r="74" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="3">
-        <v>46232</v>
+        <v>46227</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>15</v>
+        <v>187</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E74" s="3">
         <v>46272</v>
       </c>
       <c r="F74" s="5">
-        <v>9716</v>
+        <v>4216.67</v>
       </c>
       <c r="G74" s="5">
-        <v>9716</v>
+        <v>6389.24</v>
       </c>
       <c r="H74" s="3"/>
       <c r="I74" s="6">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J74" s="4" t="s">
-        <v>26</v>
+        <v>195</v>
       </c>
       <c r="K74" s="4" t="s">
-        <v>39</v>
+        <v>190</v>
       </c>
       <c r="L74" s="4"/>
       <c r="M74" s="4" t="s">
@@ -4256,7 +4277,7 @@
       </c>
       <c r="H75" s="3"/>
       <c r="I75" s="6">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J75" s="4" t="s">
         <v>26</v>
@@ -4295,7 +4316,7 @@
       </c>
       <c r="H76" s="3"/>
       <c r="I76" s="6">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J76" s="4" t="s">
         <v>170</v>
@@ -4334,7 +4355,7 @@
       </c>
       <c r="H77" s="3"/>
       <c r="I77" s="6">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J77" s="4" t="s">
         <v>170</v>
@@ -4373,7 +4394,7 @@
       </c>
       <c r="H78" s="3"/>
       <c r="I78" s="6">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J78" s="4" t="s">
         <v>170</v>
@@ -4412,7 +4433,7 @@
       </c>
       <c r="H79" s="3"/>
       <c r="I79" s="6">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="J79" s="4" t="s">
         <v>170</v>
@@ -4451,7 +4472,7 @@
       </c>
       <c r="H80" s="3"/>
       <c r="I80" s="6">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="J80" s="4" t="s">
         <v>26</v>
@@ -4490,7 +4511,7 @@
       </c>
       <c r="H81" s="3"/>
       <c r="I81" s="6">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J81" s="4" t="s">
         <v>170</v>
@@ -4529,7 +4550,7 @@
       </c>
       <c r="H82" s="3"/>
       <c r="I82" s="6">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="J82" s="4" t="s">
         <v>26</v>
@@ -4546,39 +4567,39 @@
     </row>
     <row r="83" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="3">
-        <v>46192</v>
+        <v>46227</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="C83" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="D83" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="D83" s="4" t="s">
-        <v>215</v>
-      </c>
       <c r="E83" s="3">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" s="5">
-        <v>22750</v>
+        <v>23168.6</v>
       </c>
       <c r="G83" s="5">
-        <v>22750</v>
+        <v>23168.6</v>
       </c>
       <c r="H83" s="3"/>
       <c r="I83" s="6">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J83" s="4" t="s">
-        <v>26</v>
+        <v>170</v>
       </c>
       <c r="K83" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="L83" s="4"/>
       <c r="M83" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="N83" s="4"/>
       <c r="O83" s="4"/>
@@ -4594,7 +4615,7 @@
         <v>199</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E84" s="3">
         <v>46283</v>
@@ -4607,7 +4628,7 @@
       </c>
       <c r="H84" s="3"/>
       <c r="I84" s="6">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="J84" s="4" t="s">
         <v>170</v>
@@ -4617,75 +4638,75 @@
       </c>
       <c r="L84" s="4"/>
       <c r="M84" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="N84" s="4"/>
       <c r="O84" s="4"/>
     </row>
     <row r="85" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="3">
-        <v>46253</v>
+        <v>46224</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>166</v>
+        <v>199</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E85" s="3">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F85" s="5">
-        <v>1172.1600000000001</v>
+        <v>10666.67</v>
       </c>
       <c r="G85" s="5">
-        <v>1172.1600000000001</v>
+        <v>10666.67</v>
       </c>
       <c r="H85" s="3"/>
       <c r="I85" s="6">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="J85" s="4" t="s">
-        <v>193</v>
+        <v>170</v>
       </c>
       <c r="K85" s="4" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="L85" s="4"/>
       <c r="M85" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="N85" s="4"/>
       <c r="O85" s="4"/>
     </row>
     <row r="86" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="3">
-        <v>46227</v>
+        <v>46234</v>
       </c>
       <c r="B86" s="4" t="s">
         <v>45</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E86" s="3">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F86" s="5">
-        <v>23168.6</v>
+        <v>6500</v>
       </c>
       <c r="G86" s="5">
-        <v>23168.6</v>
+        <v>6500</v>
       </c>
       <c r="H86" s="3"/>
       <c r="I86" s="6">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="J86" s="4" t="s">
         <v>170</v>
@@ -4695,14 +4716,14 @@
       </c>
       <c r="L86" s="4"/>
       <c r="M86" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="N86" s="4"/>
       <c r="O86" s="4"/>
     </row>
     <row r="87" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="3">
-        <v>46224</v>
+        <v>46234</v>
       </c>
       <c r="B87" s="4" t="s">
         <v>45</v>
@@ -4711,20 +4732,20 @@
         <v>199</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E87" s="3">
         <v>46284</v>
       </c>
       <c r="F87" s="5">
-        <v>10666.67</v>
+        <v>4950.17</v>
       </c>
       <c r="G87" s="5">
-        <v>10666.67</v>
+        <v>4950.17</v>
       </c>
       <c r="H87" s="3"/>
       <c r="I87" s="6">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="J87" s="4" t="s">
         <v>170</v>
@@ -4734,75 +4755,75 @@
       </c>
       <c r="L87" s="4"/>
       <c r="M87" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="N87" s="4"/>
       <c r="O87" s="4"/>
     </row>
     <row r="88" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="3">
-        <v>46234</v>
+        <v>46225</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>45</v>
+        <v>187</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E88" s="3">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="F88" s="5">
-        <v>6500</v>
+        <v>7551.88</v>
       </c>
       <c r="G88" s="5">
-        <v>6500</v>
+        <v>7551.88</v>
       </c>
       <c r="H88" s="3"/>
       <c r="I88" s="6">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J88" s="4" t="s">
         <v>170</v>
       </c>
       <c r="K88" s="4" t="s">
-        <v>27</v>
+        <v>190</v>
       </c>
       <c r="L88" s="4"/>
       <c r="M88" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="N88" s="4"/>
       <c r="O88" s="4"/>
     </row>
     <row r="89" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="3">
-        <v>46234</v>
+        <v>46244</v>
       </c>
       <c r="B89" s="4" t="s">
         <v>45</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E89" s="3">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" s="5">
-        <v>4950.17</v>
+        <v>4320</v>
       </c>
       <c r="G89" s="5">
-        <v>4950.17</v>
+        <v>4320</v>
       </c>
       <c r="H89" s="3"/>
       <c r="I89" s="6">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J89" s="4" t="s">
         <v>170</v>
@@ -4812,92 +4833,92 @@
       </c>
       <c r="L89" s="4"/>
       <c r="M89" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="N89" s="4"/>
       <c r="O89" s="4"/>
     </row>
     <row r="90" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="3">
-        <v>46225</v>
+        <v>46266</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>187</v>
+        <v>45</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E90" s="3">
-        <v>46285</v>
+        <v>46287</v>
       </c>
       <c r="F90" s="5">
-        <v>7551.88</v>
+        <v>18600</v>
       </c>
       <c r="G90" s="5">
-        <v>7551.88</v>
+        <v>18600</v>
       </c>
       <c r="H90" s="3"/>
       <c r="I90" s="6">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J90" s="4" t="s">
-        <v>170</v>
+        <v>26</v>
       </c>
       <c r="K90" s="4" t="s">
-        <v>190</v>
+        <v>27</v>
       </c>
       <c r="L90" s="4"/>
       <c r="M90" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="N90" s="4"/>
       <c r="O90" s="4"/>
     </row>
     <row r="91" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="3">
-        <v>46244</v>
+        <v>46227</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>45</v>
+        <v>187</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E91" s="3">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="F91" s="5">
-        <v>4320</v>
+        <v>4216.67</v>
       </c>
       <c r="G91" s="5">
-        <v>4320</v>
+        <v>4216.67</v>
       </c>
       <c r="H91" s="3"/>
       <c r="I91" s="6">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J91" s="4" t="s">
-        <v>170</v>
+        <v>195</v>
       </c>
       <c r="K91" s="4" t="s">
-        <v>27</v>
+        <v>190</v>
       </c>
       <c r="L91" s="4"/>
       <c r="M91" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="N91" s="4"/>
       <c r="O91" s="4"/>
     </row>
     <row r="92" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="3">
-        <v>46266</v>
+        <v>46253</v>
       </c>
       <c r="B92" s="4" t="s">
         <v>45</v>
@@ -4906,221 +4927,221 @@
         <v>184</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E92" s="3">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F92" s="5">
-        <v>18600</v>
+        <v>10080</v>
       </c>
       <c r="G92" s="5">
-        <v>18600</v>
+        <v>10080</v>
       </c>
       <c r="H92" s="3"/>
       <c r="I92" s="6">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J92" s="4" t="s">
-        <v>26</v>
+        <v>170</v>
       </c>
       <c r="K92" s="4" t="s">
         <v>27</v>
       </c>
       <c r="L92" s="4"/>
       <c r="M92" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="N92" s="4"/>
       <c r="O92" s="4"/>
     </row>
     <row r="93" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="3">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>172</v>
+        <v>121</v>
       </c>
       <c r="C93" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="D93" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="D93" s="4" t="s">
-        <v>236</v>
-      </c>
       <c r="E93" s="3">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F93" s="5">
-        <v>5443.56</v>
+        <v>1660.33</v>
       </c>
       <c r="G93" s="5">
-        <v>5443.56</v>
+        <v>1660.33</v>
       </c>
       <c r="H93" s="3"/>
       <c r="I93" s="6">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J93" s="4" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="K93" s="4" t="s">
-        <v>237</v>
+        <v>124</v>
       </c>
       <c r="L93" s="4"/>
       <c r="M93" s="4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="N93" s="4"/>
       <c r="O93" s="4"/>
     </row>
     <row r="94" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="3">
-        <v>46227</v>
+        <v>46253</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>187</v>
+        <v>121</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>188</v>
+        <v>234</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E94" s="3">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F94" s="5">
-        <v>4216.67</v>
+        <v>3640</v>
       </c>
       <c r="G94" s="5">
-        <v>4216.67</v>
+        <v>3640</v>
       </c>
       <c r="H94" s="3"/>
       <c r="I94" s="6">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J94" s="4" t="s">
-        <v>193</v>
+        <v>170</v>
       </c>
       <c r="K94" s="4" t="s">
-        <v>190</v>
+        <v>124</v>
       </c>
       <c r="L94" s="4"/>
       <c r="M94" s="4" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="N94" s="4"/>
       <c r="O94" s="4"/>
     </row>
     <row r="95" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="3">
-        <v>46253</v>
+        <v>46259</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>172</v>
+        <v>15</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E95" s="3">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F95" s="5">
-        <v>1452.6</v>
+        <v>6265</v>
       </c>
       <c r="G95" s="5">
-        <v>1452.6</v>
+        <v>6265</v>
       </c>
       <c r="H95" s="3"/>
       <c r="I95" s="6">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J95" s="4" t="s">
-        <v>18</v>
+        <v>170</v>
       </c>
       <c r="K95" s="4" t="s">
-        <v>175</v>
+        <v>19</v>
       </c>
       <c r="L95" s="4"/>
       <c r="M95" s="4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="N95" s="4"/>
       <c r="O95" s="4"/>
     </row>
     <row r="96" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="3">
-        <v>46253</v>
+        <v>46262</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>45</v>
+        <v>242</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>184</v>
+        <v>243</v>
       </c>
       <c r="D96" s="4" t="s">
         <v>244</v>
       </c>
       <c r="E96" s="3">
-        <v>46288</v>
+        <v>46290</v>
       </c>
       <c r="F96" s="5">
-        <v>10080</v>
+        <v>7694.4</v>
       </c>
       <c r="G96" s="5">
-        <v>10080</v>
+        <v>7694.4</v>
       </c>
       <c r="H96" s="3"/>
       <c r="I96" s="6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J96" s="4" t="s">
-        <v>170</v>
+        <v>26</v>
       </c>
       <c r="K96" s="4" t="s">
-        <v>27</v>
+        <v>245</v>
       </c>
       <c r="L96" s="4"/>
       <c r="M96" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N96" s="4"/>
       <c r="O96" s="4"/>
     </row>
     <row r="97" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="3">
-        <v>46253</v>
+        <v>46262</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>121</v>
+        <v>242</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="D97" s="4" t="s">
         <v>247</v>
       </c>
       <c r="E97" s="3">
-        <v>46288</v>
+        <v>46290</v>
       </c>
       <c r="F97" s="5">
-        <v>3640</v>
+        <v>11660.11</v>
       </c>
       <c r="G97" s="5">
-        <v>3640</v>
+        <v>11660.11</v>
       </c>
       <c r="H97" s="3"/>
       <c r="I97" s="6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J97" s="4" t="s">
         <v>170</v>
       </c>
       <c r="K97" s="4" t="s">
-        <v>124</v>
+        <v>245</v>
       </c>
       <c r="L97" s="4"/>
       <c r="M97" s="4" t="s">
@@ -5131,35 +5152,35 @@
     </row>
     <row r="98" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="3">
-        <v>46253</v>
+        <v>46231</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>121</v>
+        <v>45</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>246</v>
+        <v>199</v>
       </c>
       <c r="D98" s="4" t="s">
         <v>249</v>
       </c>
       <c r="E98" s="3">
-        <v>46288</v>
+        <v>46291</v>
       </c>
       <c r="F98" s="5">
-        <v>1660.33</v>
+        <v>6500</v>
       </c>
       <c r="G98" s="5">
-        <v>1660.33</v>
+        <v>6500</v>
       </c>
       <c r="H98" s="3"/>
       <c r="I98" s="6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J98" s="4" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="K98" s="4" t="s">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="L98" s="4"/>
       <c r="M98" s="4" t="s">
@@ -5170,436 +5191,436 @@
     </row>
     <row r="99" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="3">
-        <v>46259</v>
+        <v>46232</v>
       </c>
       <c r="B99" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C99" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="D99" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="D99" s="4" t="s">
-        <v>252</v>
-      </c>
       <c r="E99" s="3">
-        <v>46289</v>
+        <v>46292</v>
       </c>
       <c r="F99" s="5">
-        <v>6265</v>
+        <v>9716</v>
       </c>
       <c r="G99" s="5">
-        <v>6265</v>
+        <v>9716</v>
       </c>
       <c r="H99" s="3"/>
       <c r="I99" s="6">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J99" s="4" t="s">
-        <v>170</v>
+        <v>26</v>
       </c>
       <c r="K99" s="4" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="L99" s="4"/>
       <c r="M99" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="N99" s="4"/>
       <c r="O99" s="4"/>
     </row>
     <row r="100" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="3">
-        <v>46262</v>
+        <v>46232</v>
       </c>
       <c r="B100" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="D100" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="C100" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="D100" s="4" t="s">
-        <v>256</v>
-      </c>
       <c r="E100" s="3">
-        <v>46290</v>
+        <v>46292</v>
       </c>
       <c r="F100" s="5">
-        <v>7694.4</v>
+        <v>4082.05</v>
       </c>
       <c r="G100" s="5">
-        <v>7694.4</v>
+        <v>4082.05</v>
       </c>
       <c r="H100" s="3"/>
       <c r="I100" s="6">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J100" s="4" t="s">
-        <v>26</v>
+        <v>170</v>
       </c>
       <c r="K100" s="4" t="s">
-        <v>257</v>
+        <v>190</v>
       </c>
       <c r="L100" s="4"/>
       <c r="M100" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="N100" s="4"/>
       <c r="O100" s="4"/>
     </row>
     <row r="101" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="3">
-        <v>46262</v>
+        <v>46244</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>254</v>
+        <v>135</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E101" s="3">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="F101" s="5">
-        <v>11660.11</v>
+        <v>3599.85</v>
       </c>
       <c r="G101" s="5">
-        <v>11660.11</v>
+        <v>3599.85</v>
       </c>
       <c r="H101" s="3"/>
       <c r="I101" s="6">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J101" s="4" t="s">
-        <v>170</v>
+        <v>18</v>
       </c>
       <c r="K101" s="4" t="s">
-        <v>257</v>
+        <v>54</v>
       </c>
       <c r="L101" s="4"/>
       <c r="M101" s="4" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="N101" s="4"/>
       <c r="O101" s="4"/>
     </row>
     <row r="102" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="3">
-        <v>46262</v>
+        <v>46223</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>172</v>
+        <v>15</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E102" s="3">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="F102" s="5">
-        <v>2992</v>
+        <v>6265</v>
       </c>
       <c r="G102" s="5">
-        <v>2992</v>
+        <v>6265</v>
       </c>
       <c r="H102" s="3"/>
       <c r="I102" s="6">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J102" s="4" t="s">
-        <v>170</v>
+        <v>195</v>
       </c>
       <c r="K102" s="4" t="s">
-        <v>237</v>
+        <v>19</v>
       </c>
       <c r="L102" s="4"/>
       <c r="M102" s="4" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="N102" s="4"/>
       <c r="O102" s="4"/>
     </row>
     <row r="103" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="3">
-        <v>46231</v>
+        <v>46244</v>
       </c>
       <c r="B103" s="4" t="s">
         <v>45</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E103" s="3">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="F103" s="5">
-        <v>6500</v>
+        <v>4320</v>
       </c>
       <c r="G103" s="5">
-        <v>6500</v>
+        <v>4320</v>
       </c>
       <c r="H103" s="3"/>
       <c r="I103" s="6">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J103" s="4" t="s">
-        <v>26</v>
+        <v>170</v>
       </c>
       <c r="K103" s="4" t="s">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="L103" s="4"/>
       <c r="M103" s="4" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="N103" s="4"/>
       <c r="O103" s="4"/>
     </row>
     <row r="104" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="3">
-        <v>46262</v>
+        <v>46248</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>265</v>
+        <v>15</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E104" s="3">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" s="5">
-        <v>4689.22</v>
+        <v>23355.33</v>
       </c>
       <c r="G104" s="5">
-        <v>4689.22</v>
+        <v>23355.33</v>
       </c>
       <c r="H104" s="3"/>
       <c r="I104" s="6">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J104" s="4" t="s">
         <v>170</v>
       </c>
       <c r="K104" s="4" t="s">
-        <v>268</v>
+        <v>39</v>
       </c>
       <c r="L104" s="4"/>
       <c r="M104" s="4" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="N104" s="4"/>
       <c r="O104" s="4"/>
     </row>
     <row r="105" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="3">
-        <v>46232</v>
+        <v>46265</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>179</v>
+        <v>266</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="E105" s="3">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" s="5">
-        <v>9716</v>
+        <v>1664</v>
       </c>
       <c r="G105" s="5">
-        <v>9716</v>
+        <v>1664</v>
       </c>
       <c r="H105" s="3"/>
       <c r="I105" s="6">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J105" s="4" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="K105" s="4" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="L105" s="4"/>
       <c r="M105" s="4" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="N105" s="4"/>
       <c r="O105" s="4"/>
     </row>
     <row r="106" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="3">
-        <v>46232</v>
+        <v>46223</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>187</v>
+        <v>45</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>272</v>
+        <v>199</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="E106" s="3">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" s="5">
-        <v>4082.05</v>
+        <v>11200</v>
       </c>
       <c r="G106" s="5">
-        <v>4082.05</v>
+        <v>11200</v>
       </c>
       <c r="H106" s="3"/>
       <c r="I106" s="6">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J106" s="4" t="s">
         <v>170</v>
       </c>
       <c r="K106" s="4" t="s">
-        <v>190</v>
+        <v>27</v>
       </c>
       <c r="L106" s="4"/>
       <c r="M106" s="4" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="N106" s="4"/>
       <c r="O106" s="4"/>
     </row>
     <row r="107" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="3">
-        <v>46244</v>
+        <v>46266</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>135</v>
+        <v>45</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>275</v>
+        <v>184</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="E107" s="3">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F107" s="5">
-        <v>3599.85</v>
+        <v>18600</v>
       </c>
       <c r="G107" s="5">
-        <v>3599.85</v>
+        <v>18600</v>
       </c>
       <c r="H107" s="3"/>
       <c r="I107" s="6">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J107" s="4" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="K107" s="4" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="L107" s="4"/>
       <c r="M107" s="4" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="N107" s="4"/>
       <c r="O107" s="4"/>
     </row>
     <row r="108" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="3">
-        <v>46230</v>
+        <v>46234</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>235</v>
+        <v>188</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="E108" s="3">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F108" s="5">
-        <v>1513.13</v>
+        <v>3789.09</v>
       </c>
       <c r="G108" s="5">
-        <v>1513.13</v>
+        <v>3789.09</v>
       </c>
       <c r="H108" s="3"/>
       <c r="I108" s="6">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J108" s="4" t="s">
-        <v>193</v>
+        <v>170</v>
       </c>
       <c r="K108" s="4" t="s">
-        <v>237</v>
+        <v>190</v>
       </c>
       <c r="L108" s="4"/>
       <c r="M108" s="4" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="N108" s="4"/>
       <c r="O108" s="4"/>
     </row>
     <row r="109" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="3">
-        <v>46223</v>
+        <v>46265</v>
       </c>
       <c r="B109" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="E109" s="3">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="F109" s="5">
-        <v>6265</v>
+        <v>8947.5</v>
       </c>
       <c r="G109" s="5">
-        <v>6265</v>
+        <v>8947.5</v>
       </c>
       <c r="H109" s="3"/>
       <c r="I109" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J109" s="4" t="s">
-        <v>193</v>
+        <v>170</v>
       </c>
       <c r="K109" s="4" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="L109" s="4"/>
       <c r="M109" s="4" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="N109" s="4"/>
       <c r="O109" s="4"/>
     </row>
     <row r="110" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="3">
-        <v>46244</v>
+        <v>46253</v>
       </c>
       <c r="B110" s="4" t="s">
         <v>45</v>
@@ -5608,20 +5629,20 @@
         <v>184</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="E110" s="3">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="F110" s="5">
-        <v>4320</v>
+        <v>10080</v>
       </c>
       <c r="G110" s="5">
-        <v>4320</v>
+        <v>10080</v>
       </c>
       <c r="H110" s="3"/>
       <c r="I110" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J110" s="4" t="s">
         <v>170</v>
@@ -5631,205 +5652,400 @@
       </c>
       <c r="L110" s="4"/>
       <c r="M110" s="4" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="N110" s="4"/>
       <c r="O110" s="4"/>
     </row>
     <row r="111" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="3">
-        <v>46223</v>
+        <v>46253</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>45</v>
+        <v>172</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>199</v>
+        <v>279</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="E111" s="3">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="F111" s="5">
-        <v>11200</v>
+        <v>2051.2199999999998</v>
       </c>
       <c r="G111" s="5">
-        <v>11200</v>
+        <v>2051.2199999999998</v>
       </c>
       <c r="H111" s="3"/>
       <c r="I111" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J111" s="4" t="s">
-        <v>170</v>
+        <v>18</v>
       </c>
       <c r="K111" s="4" t="s">
-        <v>27</v>
+        <v>175</v>
       </c>
       <c r="L111" s="4"/>
       <c r="M111" s="4" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="N111" s="4"/>
       <c r="O111" s="4"/>
     </row>
     <row r="112" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="3">
-        <v>46251</v>
+        <v>46265</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>45</v>
+        <v>135</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="E112" s="3">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="F112" s="5">
-        <v>2521.25</v>
+        <v>4750</v>
       </c>
       <c r="G112" s="5">
-        <v>2521.25</v>
+        <v>8565.68</v>
       </c>
       <c r="H112" s="3"/>
       <c r="I112" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J112" s="4" t="s">
         <v>170</v>
       </c>
       <c r="K112" s="4" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="L112" s="4"/>
       <c r="M112" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="N112" s="4"/>
       <c r="O112" s="4"/>
     </row>
     <row r="113" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="3">
-        <v>46265</v>
+        <v>46253</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>23</v>
+        <v>121</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>289</v>
+        <v>234</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="E113" s="3">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="F113" s="5">
-        <v>1664</v>
+        <v>3640</v>
       </c>
       <c r="G113" s="5">
-        <v>1664</v>
+        <v>3640</v>
       </c>
       <c r="H113" s="3"/>
       <c r="I113" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J113" s="4" t="s">
-        <v>18</v>
+        <v>170</v>
       </c>
       <c r="K113" s="4" t="s">
-        <v>71</v>
+        <v>124</v>
       </c>
       <c r="L113" s="4"/>
       <c r="M113" s="4" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="N113" s="4"/>
       <c r="O113" s="4"/>
     </row>
     <row r="114" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="3">
-        <v>46248</v>
+        <v>46253</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>15</v>
+        <v>121</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="E114" s="3">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="F114" s="5">
-        <v>23355.33</v>
+        <v>1660.34</v>
       </c>
       <c r="G114" s="5">
-        <v>23355.33</v>
+        <v>1660.34</v>
       </c>
       <c r="H114" s="3"/>
       <c r="I114" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J114" s="4" t="s">
-        <v>170</v>
+        <v>18</v>
       </c>
       <c r="K114" s="4" t="s">
-        <v>39</v>
+        <v>124</v>
       </c>
       <c r="L114" s="4"/>
       <c r="M114" s="4" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="N114" s="4"/>
       <c r="O114" s="4"/>
     </row>
     <row r="115" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="3">
-        <v>46251</v>
+        <v>46268</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>121</v>
+        <v>23</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>294</v>
+        <v>266</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="E115" s="3">
-        <v>46293</v>
+        <v>46296</v>
       </c>
       <c r="F115" s="5">
-        <v>2070.1999999999998</v>
+        <v>2754</v>
       </c>
       <c r="G115" s="5">
-        <v>2070.1999999999998</v>
+        <v>2754</v>
       </c>
       <c r="H115" s="3"/>
       <c r="I115" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J115" s="4" t="s">
-        <v>18</v>
+        <v>195</v>
       </c>
       <c r="K115" s="4" t="s">
-        <v>124</v>
+        <v>71</v>
       </c>
       <c r="L115" s="4"/>
       <c r="M115" s="4" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="N115" s="4"/>
       <c r="O115" s="4"/>
+    </row>
+    <row r="116" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="3">
+        <v>46266</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="C116" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="D116" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="E116" s="3">
+        <v>46296</v>
+      </c>
+      <c r="F116" s="5">
+        <v>8973.5</v>
+      </c>
+      <c r="G116" s="5">
+        <v>8973.5</v>
+      </c>
+      <c r="H116" s="3"/>
+      <c r="I116" s="6">
+        <v>4</v>
+      </c>
+      <c r="J116" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="K116" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="L116" s="4"/>
+      <c r="M116" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="N116" s="4"/>
+      <c r="O116" s="4"/>
+    </row>
+    <row r="117" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="3">
+        <v>46262</v>
+      </c>
+      <c r="B117" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="C117" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="D117" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="E117" s="3">
+        <v>46297</v>
+      </c>
+      <c r="F117" s="5">
+        <v>7694.4</v>
+      </c>
+      <c r="G117" s="5">
+        <v>7694.4</v>
+      </c>
+      <c r="H117" s="3"/>
+      <c r="I117" s="6">
+        <v>3</v>
+      </c>
+      <c r="J117" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K117" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="L117" s="4"/>
+      <c r="M117" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="N117" s="4"/>
+      <c r="O117" s="4"/>
+    </row>
+    <row r="118" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="3">
+        <v>46262</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="C118" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="D118" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="E118" s="3">
+        <v>46297</v>
+      </c>
+      <c r="F118" s="5">
+        <v>11660.11</v>
+      </c>
+      <c r="G118" s="5">
+        <v>11660.11</v>
+      </c>
+      <c r="H118" s="3"/>
+      <c r="I118" s="6">
+        <v>3</v>
+      </c>
+      <c r="J118" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="K118" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="L118" s="4"/>
+      <c r="M118" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="N118" s="4"/>
+      <c r="O118" s="4"/>
+    </row>
+    <row r="119" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="3">
+        <v>46237</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C119" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D119" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="E119" s="3">
+        <v>46297</v>
+      </c>
+      <c r="F119" s="5">
+        <v>2930.4</v>
+      </c>
+      <c r="G119" s="5">
+        <v>2930.4</v>
+      </c>
+      <c r="H119" s="3"/>
+      <c r="I119" s="6">
+        <v>3</v>
+      </c>
+      <c r="J119" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K119" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="L119" s="4"/>
+      <c r="M119" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="N119" s="4"/>
+      <c r="O119" s="4"/>
+    </row>
+    <row r="120" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="3">
+        <v>46252</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C120" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D120" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="E120" s="3">
+        <v>46297</v>
+      </c>
+      <c r="F120" s="5">
+        <v>3809.52</v>
+      </c>
+      <c r="G120" s="5">
+        <v>3809.52</v>
+      </c>
+      <c r="H120" s="3"/>
+      <c r="I120" s="6">
+        <v>3</v>
+      </c>
+      <c r="J120" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="K120" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="L120" s="4"/>
+      <c r="M120" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="N120" s="4"/>
+      <c r="O120" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
+++ b/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WINDOWS\Desktop\dados planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E03B8382-F475-45D1-A673-F8782CE068B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCB00894-F262-41B6-847D-BFC8EF7D0DBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="715" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="315">
   <si>
     <t>Dt.Emissão</t>
   </si>
@@ -96,36 +96,36 @@
     <t>34194963600005418001090001019738120992717000</t>
   </si>
   <si>
+    <t>01001504.4</t>
+  </si>
+  <si>
+    <t>34194964600005418001090001019818120992717000</t>
+  </si>
+  <si>
     <t>MARCELO LOPES</t>
   </si>
   <si>
     <t>FAROMED COMERCIO DE MATERIAIS HOSPITALARES LTDA</t>
   </si>
   <si>
+    <t>01001548.3</t>
+  </si>
+  <si>
+    <t>BANCO DO BRASIL</t>
+  </si>
+  <si>
+    <t>PE</t>
+  </si>
+  <si>
+    <t>00193965200000384000000003473568000002617517</t>
+  </si>
+  <si>
     <t>01001617.1</t>
   </si>
   <si>
-    <t>BANCO DO BRASIL</t>
-  </si>
-  <si>
-    <t>PE</t>
-  </si>
-  <si>
     <t>00191964000001264870000003473568000002622117</t>
   </si>
   <si>
-    <t>01001504.4</t>
-  </si>
-  <si>
-    <t>34194964600005418001090001019818120992717000</t>
-  </si>
-  <si>
-    <t>01001548.3</t>
-  </si>
-  <si>
-    <t>00193965200000384000000003473568000002617517</t>
-  </si>
-  <si>
     <t>01001617.2</t>
   </si>
   <si>
@@ -168,69 +168,69 @@
     <t>GLOBAL MEDIC LTDA</t>
   </si>
   <si>
+    <t>01002938.2</t>
+  </si>
+  <si>
+    <t>34194986400001216861090001218808120992717000</t>
+  </si>
+  <si>
+    <t>01002938.3</t>
+  </si>
+  <si>
+    <t>34192987800001216861090001218988120992717000</t>
+  </si>
+  <si>
+    <t>01002951.2</t>
+  </si>
+  <si>
+    <t>34193985900001843871090001228138120992717000</t>
+  </si>
+  <si>
+    <t>01002951.3</t>
+  </si>
+  <si>
+    <t>34194986600001843881090001228218120992717000</t>
+  </si>
+  <si>
+    <t>MOISES</t>
+  </si>
+  <si>
+    <t>AC FL FARMACIA E DROGARIA LTDA</t>
+  </si>
+  <si>
+    <t>01002991.3</t>
+  </si>
+  <si>
+    <t>BA</t>
+  </si>
+  <si>
+    <t>34196989800004439901090001240908120992717000</t>
+  </si>
+  <si>
+    <t>01002991.4</t>
+  </si>
+  <si>
+    <t>34197991200004439901090001241088120992717000</t>
+  </si>
+  <si>
+    <t>01003029.1</t>
+  </si>
+  <si>
+    <t>34197987600003204341090001238458120992717000</t>
+  </si>
+  <si>
     <t>01003029.2</t>
   </si>
   <si>
     <t>34195989000002000001090001238528120992717000</t>
   </si>
   <si>
-    <t>01003029.1</t>
-  </si>
-  <si>
-    <t>34197987600003204341090001238458120992717000</t>
-  </si>
-  <si>
-    <t>MOISES</t>
-  </si>
-  <si>
-    <t>AC FL FARMACIA E DROGARIA LTDA</t>
-  </si>
-  <si>
-    <t>01002991.3</t>
-  </si>
-  <si>
-    <t>BA</t>
-  </si>
-  <si>
-    <t>34196989800004439901090001240908120992717000</t>
-  </si>
-  <si>
     <t>01003029.3</t>
   </si>
   <si>
     <t>34195990400002000001090001238608120992717000</t>
   </si>
   <si>
-    <t>01002938.2</t>
-  </si>
-  <si>
-    <t>34194986400001216861090001218808120992717000</t>
-  </si>
-  <si>
-    <t>01002951.2</t>
-  </si>
-  <si>
-    <t>34193985900001843871090001228138120992717000</t>
-  </si>
-  <si>
-    <t>01002938.3</t>
-  </si>
-  <si>
-    <t>34192987800001216861090001218988120992717000</t>
-  </si>
-  <si>
-    <t>01002991.4</t>
-  </si>
-  <si>
-    <t>34197991200004439901090001241088120992717000</t>
-  </si>
-  <si>
-    <t>01002951.3</t>
-  </si>
-  <si>
-    <t>34194986600001843881090001228218120992717000</t>
-  </si>
-  <si>
     <t>SERGIO ROBERTO - PB</t>
   </si>
   <si>
@@ -249,39 +249,39 @@
     <t xml:space="preserve">RN COMERCIO DE MEDICAMENTOS E MATERIAL HOSPITALAR </t>
   </si>
   <si>
+    <t>01003409.6</t>
+  </si>
+  <si>
+    <t>RN</t>
+  </si>
+  <si>
+    <t>34199998900002330001090001290998120992717000</t>
+  </si>
+  <si>
     <t>01003464.4</t>
   </si>
   <si>
-    <t>RN</t>
-  </si>
-  <si>
     <t>34194998500003296801090001307668120992717000</t>
   </si>
   <si>
-    <t>01003409.6</t>
-  </si>
-  <si>
-    <t>34199998900002330001090001290998120992717000</t>
-  </si>
-  <si>
     <t>01003464.5</t>
   </si>
   <si>
     <t>34198999200003296801090001307748120992717000</t>
   </si>
   <si>
+    <t>01003464.6</t>
+  </si>
+  <si>
+    <t>34191999900003296801090001307828120992717000</t>
+  </si>
+  <si>
     <t>01003504.1</t>
   </si>
   <si>
     <t>00191999500002541000000003473568000002851217</t>
   </si>
   <si>
-    <t>01003464.6</t>
-  </si>
-  <si>
-    <t>34191999900003296801090001307828120992717000</t>
-  </si>
-  <si>
     <t>01003504.2</t>
   </si>
   <si>
@@ -294,6 +294,12 @@
     <t>00194101600002541000000003473568000002851517</t>
   </si>
   <si>
+    <t>01003504.6</t>
+  </si>
+  <si>
+    <t>00193103000002541000000003473568000002851717</t>
+  </si>
+  <si>
     <t>01003589.1</t>
   </si>
   <si>
@@ -306,6 +312,18 @@
     <t>34198102400007562781090001320028120992717000</t>
   </si>
   <si>
+    <t>01003589.3</t>
+  </si>
+  <si>
+    <t>34191103100007562781090001320108120992717000</t>
+  </si>
+  <si>
+    <t>01003589.4</t>
+  </si>
+  <si>
+    <t>34197103800007562761090001320288120992717000</t>
+  </si>
+  <si>
     <t>MED-K COMERCIO LTDA</t>
   </si>
   <si>
@@ -315,18 +333,6 @@
     <t>34194102400001154561090001320448120992717000</t>
   </si>
   <si>
-    <t>01003504.6</t>
-  </si>
-  <si>
-    <t>00193103000002541000000003473568000002851717</t>
-  </si>
-  <si>
-    <t>01003589.3</t>
-  </si>
-  <si>
-    <t>34191103100007562781090001320108120992717000</t>
-  </si>
-  <si>
     <t>01003592.3</t>
   </si>
   <si>
@@ -339,12 +345,6 @@
     <t>34194103800001154561090001320698120992717000</t>
   </si>
   <si>
-    <t>01003589.4</t>
-  </si>
-  <si>
-    <t>34197103800007562761090001320288120992717000</t>
-  </si>
-  <si>
     <t>01003592.5</t>
   </si>
   <si>
@@ -462,30 +462,39 @@
     <t>00191125800002144590000003473568000002964317</t>
   </si>
   <si>
+    <t>BR MEDICAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>01005075.3</t>
+  </si>
+  <si>
+    <t>00195127000004480000000003473568000002981317</t>
+  </si>
+  <si>
+    <t>01005144.3</t>
+  </si>
+  <si>
     <t>PHARMACEUTICA DISTRIBUIDORA DE MAT. E MED. HOSPITA</t>
   </si>
   <si>
     <t>01005217.1BPBPBPBP</t>
   </si>
   <si>
-    <t>BR MEDICAMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>01005075.3</t>
-  </si>
-  <si>
-    <t>00195127000004480000000003473568000002981317</t>
-  </si>
-  <si>
     <t>01005217.2BP</t>
   </si>
   <si>
-    <t>01005144.3</t>
-  </si>
-  <si>
     <t>01005217.3BPBPBP</t>
   </si>
   <si>
+    <t>MAIS SAUDE COMERCIO DE PRODUTOS HOSPITALARES LTDA</t>
+  </si>
+  <si>
+    <t>01005683.3</t>
+  </si>
+  <si>
+    <t>34199139500005466661090002533378120992717000</t>
+  </si>
+  <si>
     <t>DENTAL SORRISO LTDA</t>
   </si>
   <si>
@@ -507,13 +516,13 @@
     <t>00199139400000503280000003473568000003029617</t>
   </si>
   <si>
-    <t>MAIS SAUDE COMERCIO DE PRODUTOS HOSPITALARES LTDA</t>
-  </si>
-  <si>
-    <t>01005683.3</t>
-  </si>
-  <si>
-    <t>34199139500005466661090002533378120992717000</t>
+    <t>GRADUAL COMERCIO E SERVICOS LTDA</t>
+  </si>
+  <si>
+    <t>01006433.3</t>
+  </si>
+  <si>
+    <t>34193151200031531501090002588728120992717000</t>
   </si>
   <si>
     <t>01006508.1</t>
@@ -525,37 +534,82 @@
     <t>01006508.3</t>
   </si>
   <si>
-    <t>GRADUAL COMERCIO E SERVICOS LTDA</t>
-  </si>
-  <si>
-    <t>01006433.3</t>
-  </si>
-  <si>
-    <t>34193151200031531501090002588728120992717000</t>
-  </si>
-  <si>
-    <t>01006681.1</t>
+    <t>MARCOS DUTRA - PI</t>
+  </si>
+  <si>
+    <t>ALIANCA DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>01006753.5</t>
+  </si>
+  <si>
+    <t>PI</t>
+  </si>
+  <si>
+    <t>00197154900000860000000003473568000003129017</t>
+  </si>
+  <si>
+    <t>COBERMED COMERCIO DE MATERIAIS MEDICOS LTDA</t>
+  </si>
+  <si>
+    <t>01006877.3</t>
+  </si>
+  <si>
+    <t>BRADESCO</t>
+  </si>
+  <si>
+    <t>23797158300006265000435090000000110700304920</t>
+  </si>
+  <si>
+    <t>ALINE CERBINO - PA</t>
+  </si>
+  <si>
+    <t>CRISTALFARMA COMERCIO IMPORT E EXPORT LTDA</t>
+  </si>
+  <si>
+    <t>01006920.1</t>
   </si>
   <si>
     <t>DAYCOVAL</t>
   </si>
   <si>
-    <t>70793151800003516480001121205064100656760355</t>
-  </si>
-  <si>
-    <t>MARCOS DUTRA - PI</t>
-  </si>
-  <si>
-    <t>ALIANCA DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>01006753.5</t>
-  </si>
-  <si>
-    <t>PI</t>
-  </si>
-  <si>
-    <t>00197154900000860000000003473568000003129017</t>
+    <t>PA</t>
+  </si>
+  <si>
+    <t>70797156000011442870001121205064100656763979</t>
+  </si>
+  <si>
+    <t>01006920.2</t>
+  </si>
+  <si>
+    <t>70794157500007551880001121205064100656763987</t>
+  </si>
+  <si>
+    <t>01006920.3</t>
+  </si>
+  <si>
+    <t>70797159000007551880001121205064100656763995</t>
+  </si>
+  <si>
+    <t>PLENA DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>01006922.1</t>
+  </si>
+  <si>
+    <t>70795156300011200000001121205064100656763870</t>
+  </si>
+  <si>
+    <t>01006922.2</t>
+  </si>
+  <si>
+    <t>70792157300011200000001121205064100656763888</t>
+  </si>
+  <si>
+    <t>01006922.3</t>
+  </si>
+  <si>
+    <t>70798158300011200000001121205064100656763896</t>
   </si>
   <si>
     <t>01006941.2</t>
@@ -564,6 +618,66 @@
     <t>00195154900002818370000003473568000003141117</t>
   </si>
   <si>
+    <t>01006941.4</t>
+  </si>
+  <si>
+    <t>00194156300002818370000003473568000003141317</t>
+  </si>
+  <si>
+    <t>01006941.5</t>
+  </si>
+  <si>
+    <t>00191157000002818360000003473568000003141417</t>
+  </si>
+  <si>
+    <t>01006957.2</t>
+  </si>
+  <si>
+    <t>70792157400010666670001121205064100656763953</t>
+  </si>
+  <si>
+    <t>CIRURGICA MONTEBELLO LTDA</t>
+  </si>
+  <si>
+    <t>01006958.5</t>
+  </si>
+  <si>
+    <t>70799156600023168600001121205064100656764084</t>
+  </si>
+  <si>
+    <t>01006958.6</t>
+  </si>
+  <si>
+    <t>70798157300023168600001121205064100656764092</t>
+  </si>
+  <si>
+    <t>01006976.1</t>
+  </si>
+  <si>
+    <t>23791156200006389240435090000000114600304920</t>
+  </si>
+  <si>
+    <t>01006976.2</t>
+  </si>
+  <si>
+    <t>23791157700004216670435090000000114700304920</t>
+  </si>
+  <si>
+    <t>FERMATA LTDA</t>
+  </si>
+  <si>
+    <t>01006989.2</t>
+  </si>
+  <si>
+    <t>70795158200004082050001121205064100656764191</t>
+  </si>
+  <si>
+    <t>01006999.1</t>
+  </si>
+  <si>
+    <t>70799157400006500000001121205064100656764282</t>
+  </si>
+  <si>
     <t>JT COSTA COMERCIAL LTDA</t>
   </si>
   <si>
@@ -573,64 +687,139 @@
     <t>00197155200018957860000003473568000003145817</t>
   </si>
   <si>
-    <t>01006941.3</t>
-  </si>
-  <si>
-    <t>00191155600002818370000003473568000003141217</t>
-  </si>
-  <si>
-    <t>CIRURGICA MONTEBELLO LTDA</t>
-  </si>
-  <si>
-    <t>01006958.4</t>
-  </si>
-  <si>
-    <t>70791155900023168600001121205064100656764076</t>
-  </si>
-  <si>
-    <t>ALINE CERBINO - PA</t>
-  </si>
-  <si>
-    <t>CRISTALFARMA COMERCIO IMPORT E EXPORT LTDA</t>
-  </si>
-  <si>
-    <t>01006920.1</t>
-  </si>
-  <si>
-    <t>PA</t>
-  </si>
-  <si>
-    <t>70797156000011442870001121205064100656763979</t>
-  </si>
-  <si>
     <t>01007005.2</t>
   </si>
   <si>
     <t>00193156200009716000000003473568000003145917</t>
   </si>
   <si>
-    <t>01006976.1</t>
-  </si>
-  <si>
-    <t>BRADESCO</t>
-  </si>
-  <si>
-    <t>23791156200006389240435090000000114600304920</t>
-  </si>
-  <si>
-    <t>01006941.4</t>
-  </si>
-  <si>
-    <t>00194156300002818370000003473568000003141317</t>
-  </si>
-  <si>
-    <t>PLENA DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>01006922.1</t>
-  </si>
-  <si>
-    <t>70795156300011200000001121205064100656763870</t>
+    <t>01007005.3</t>
+  </si>
+  <si>
+    <t>00196157200009716000000003473568000003146017</t>
+  </si>
+  <si>
+    <t>01007005.4</t>
+  </si>
+  <si>
+    <t>00197158200009716000000003473568000003146117</t>
+  </si>
+  <si>
+    <t>01007020.1</t>
+  </si>
+  <si>
+    <t>70799157400004950170001121205064100656764449</t>
+  </si>
+  <si>
+    <t>01007023.1</t>
+  </si>
+  <si>
+    <t>70799156900005741360001121205064100656764415</t>
+  </si>
+  <si>
+    <t>01007023.2</t>
+  </si>
+  <si>
+    <t>70791158400003789090001121205064100656764423</t>
+  </si>
+  <si>
+    <t>01007074.3</t>
+  </si>
+  <si>
+    <t>34192158700002930401090002611578120992717000</t>
+  </si>
+  <si>
+    <t>LICIMASTER DIST. DE MED. E PRODUTOS MEDICO</t>
+  </si>
+  <si>
+    <t>01007094.4</t>
+  </si>
+  <si>
+    <t>34191158300003599851090002612318120992717000</t>
+  </si>
+  <si>
+    <t>AMAZONIA HOSPITALAR LTDA</t>
+  </si>
+  <si>
+    <t>01007105.4</t>
+  </si>
+  <si>
+    <t>MA</t>
+  </si>
+  <si>
+    <t>00191159100005443560000003473568000003155017</t>
+  </si>
+  <si>
+    <t>ASPEN SERVICE COMERCIO LTDA</t>
+  </si>
+  <si>
+    <t>01007117.1</t>
+  </si>
+  <si>
+    <t>70791158300023355330001121205064100656765669</t>
+  </si>
+  <si>
+    <t>01007125.4</t>
+  </si>
+  <si>
+    <t>70791157600004320000001121205064100656765123</t>
+  </si>
+  <si>
+    <t>01007125.5</t>
+  </si>
+  <si>
+    <t>70799158300004320000001121205064100656765131</t>
+  </si>
+  <si>
+    <t>HOSPMED LTDA</t>
+  </si>
+  <si>
+    <t>01007129.5</t>
+  </si>
+  <si>
+    <t>70791159100001840960001121205064100656765180</t>
+  </si>
+  <si>
+    <t>VITAL DISTRIBUIDORA LTDA</t>
+  </si>
+  <si>
+    <t>01007168.3</t>
+  </si>
+  <si>
+    <t>34196158500002051221090002617698120992717000</t>
+  </si>
+  <si>
+    <t>01007169.2</t>
+  </si>
+  <si>
+    <t>70797158700003809520001121205064100656765974</t>
+  </si>
+  <si>
+    <t>DROGUISTA CEARENSE LTDA</t>
+  </si>
+  <si>
+    <t>01007171.2</t>
+  </si>
+  <si>
+    <t>70794157800003640000001121205064100656766162</t>
+  </si>
+  <si>
+    <t>01007171.3</t>
+  </si>
+  <si>
+    <t>70793158500003640000001121205064100656766170</t>
+  </si>
+  <si>
+    <t>01007175.2</t>
+  </si>
+  <si>
+    <t>34193157800001660331090002618768120992717000</t>
+  </si>
+  <si>
+    <t>01007175.3</t>
+  </si>
+  <si>
+    <t>34194158500001660341090002618848120992717000</t>
   </si>
   <si>
     <t>01007187.1</t>
@@ -639,76 +828,124 @@
     <t>70791156400010080000001121205064100656766188</t>
   </si>
   <si>
-    <t>01006958.5</t>
-  </si>
-  <si>
-    <t>70799156600023168600001121205064100656764084</t>
-  </si>
-  <si>
-    <t>01007023.1</t>
-  </si>
-  <si>
-    <t>70799156900005741360001121205064100656764415</t>
-  </si>
-  <si>
-    <t>01006941.5</t>
-  </si>
-  <si>
-    <t>00191157000002818360000003473568000003141417</t>
-  </si>
-  <si>
     <t>01007187.2</t>
   </si>
   <si>
     <t>70791157100010080000001121205064100656766196</t>
   </si>
   <si>
-    <t>01007005.3</t>
-  </si>
-  <si>
-    <t>00196157200009716000000003473568000003146017</t>
-  </si>
-  <si>
-    <t>01006958.6</t>
-  </si>
-  <si>
-    <t>70798157300023168600001121205064100656764092</t>
-  </si>
-  <si>
-    <t>01006922.2</t>
-  </si>
-  <si>
-    <t>70792157300011200000001121205064100656763888</t>
-  </si>
-  <si>
-    <t>01006957.2</t>
-  </si>
-  <si>
-    <t>70792157400010666670001121205064100656763953</t>
-  </si>
-  <si>
-    <t>01006999.1</t>
-  </si>
-  <si>
-    <t>70799157400006500000001121205064100656764282</t>
-  </si>
-  <si>
-    <t>01007020.1</t>
-  </si>
-  <si>
-    <t>70799157400004950170001121205064100656764449</t>
-  </si>
-  <si>
-    <t>01006920.2</t>
-  </si>
-  <si>
-    <t>70794157500007551880001121205064100656763987</t>
-  </si>
-  <si>
-    <t>01007125.4</t>
-  </si>
-  <si>
-    <t>70791157600004320000001121205064100656765123</t>
+    <t>01007187.3</t>
+  </si>
+  <si>
+    <t>70793157800010080000001121205064100656766204</t>
+  </si>
+  <si>
+    <t>01007187.4</t>
+  </si>
+  <si>
+    <t>70792158500010080000001121205064100656766212</t>
+  </si>
+  <si>
+    <t>01007194.1</t>
+  </si>
+  <si>
+    <t>70797157900006265000001121205064100656766642</t>
+  </si>
+  <si>
+    <t>01007197.2</t>
+  </si>
+  <si>
+    <t>23791158800001172160435090000000124700304920</t>
+  </si>
+  <si>
+    <t>01007215.2</t>
+  </si>
+  <si>
+    <t>70791159100003979060001121205064100656767418</t>
+  </si>
+  <si>
+    <t>01007221.2</t>
+  </si>
+  <si>
+    <t>23796159100001286250435090000000129500304920</t>
+  </si>
+  <si>
+    <t>FELIPE AQUINO - MT</t>
+  </si>
+  <si>
+    <t>FAMA DISTRIBUIDORA HOSPITALAR LTDA</t>
+  </si>
+  <si>
+    <t>01007249.1</t>
+  </si>
+  <si>
+    <t>MT</t>
+  </si>
+  <si>
+    <t>70793158000011660110001121205064100656766915</t>
+  </si>
+  <si>
+    <t>01007249.2</t>
+  </si>
+  <si>
+    <t>70792158700011660110001121205064100656766923</t>
+  </si>
+  <si>
+    <t>01007265.1</t>
+  </si>
+  <si>
+    <t>00198158000007694400000003473568000003158817</t>
+  </si>
+  <si>
+    <t>01007265.2</t>
+  </si>
+  <si>
+    <t>00192158700007694400000003473568000003158917</t>
+  </si>
+  <si>
+    <t>01007269.1</t>
+  </si>
+  <si>
+    <t>70791158500008947500001121205064100656767137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZOE MED COMERCIO DE PRODUTOS MEDICOS HOSPITALARES </t>
+  </si>
+  <si>
+    <t>01007270.1</t>
+  </si>
+  <si>
+    <t>70793158500008565680001121205064100656766972</t>
+  </si>
+  <si>
+    <t>ATACAMED COMERCIO LTDA</t>
+  </si>
+  <si>
+    <t>01007274.1</t>
+  </si>
+  <si>
+    <t>34192158300001664001090002623468120992717000</t>
+  </si>
+  <si>
+    <t>01007274.2</t>
+  </si>
+  <si>
+    <t>34192159000001664001090002623538120992717000</t>
+  </si>
+  <si>
+    <t>ELIENE RESENDE - RJ</t>
+  </si>
+  <si>
+    <t>MEDKA DISTRIBUIDORA HOSPITALAR LTDA</t>
+  </si>
+  <si>
+    <t>01007278.1</t>
+  </si>
+  <si>
+    <t>RJ</t>
+  </si>
+  <si>
+    <t>70793158600008973500001121205064100656767319</t>
   </si>
   <si>
     <t>01007301.1</t>
@@ -717,226 +954,22 @@
     <t>00192157700018600000000003473568000003161317</t>
   </si>
   <si>
-    <t>01006976.2</t>
-  </si>
-  <si>
-    <t>23791157700004216670435090000000114700304920</t>
-  </si>
-  <si>
-    <t>01007187.3</t>
-  </si>
-  <si>
-    <t>70793157800010080000001121205064100656766204</t>
-  </si>
-  <si>
-    <t>DROGUISTA CEARENSE LTDA</t>
-  </si>
-  <si>
-    <t>01007175.2</t>
-  </si>
-  <si>
-    <t>34193157800001660331090002618768120992717000</t>
-  </si>
-  <si>
-    <t>01007171.2</t>
-  </si>
-  <si>
-    <t>70794157800003640000001121205064100656766162</t>
-  </si>
-  <si>
-    <t>COBERMED COMERCIO DE MATERIAIS MEDICOS LTDA</t>
-  </si>
-  <si>
-    <t>01007194.1</t>
-  </si>
-  <si>
-    <t>70797157900006265000001121205064100656766642</t>
-  </si>
-  <si>
-    <t>FELIPE AQUINO - MT</t>
-  </si>
-  <si>
-    <t>FAMA DISTRIBUIDORA HOSPITALAR LTDA</t>
-  </si>
-  <si>
-    <t>01007265.1</t>
-  </si>
-  <si>
-    <t>MT</t>
-  </si>
-  <si>
-    <t>00198158000007694400000003473568000003158817</t>
-  </si>
-  <si>
-    <t>01007249.1</t>
-  </si>
-  <si>
-    <t>70793158000011660110001121205064100656766915</t>
-  </si>
-  <si>
-    <t>01006998.2</t>
-  </si>
-  <si>
-    <t>00191158100006500000000003473568000003144317</t>
-  </si>
-  <si>
-    <t>01007005.4</t>
-  </si>
-  <si>
-    <t>00197158200009716000000003473568000003146117</t>
-  </si>
-  <si>
-    <t>FERMATA LTDA</t>
-  </si>
-  <si>
-    <t>01006989.2</t>
-  </si>
-  <si>
-    <t>70795158200004082050001121205064100656764191</t>
-  </si>
-  <si>
-    <t>LICIMASTER DIST. DE MED. E PRODUTOS MEDICO</t>
-  </si>
-  <si>
-    <t>01007094.4</t>
-  </si>
-  <si>
-    <t>34191158300003599851090002612318120992717000</t>
-  </si>
-  <si>
-    <t>01006877.3</t>
-  </si>
-  <si>
-    <t>23797158300006265000435090000000110700304920</t>
-  </si>
-  <si>
-    <t>01007125.5</t>
-  </si>
-  <si>
-    <t>70799158300004320000001121205064100656765131</t>
-  </si>
-  <si>
-    <t>ASPEN SERVICE COMERCIO LTDA</t>
-  </si>
-  <si>
-    <t>01007117.1</t>
-  </si>
-  <si>
-    <t>70791158300023355330001121205064100656765669</t>
-  </si>
-  <si>
-    <t>ATACAMED COMERCIO LTDA</t>
-  </si>
-  <si>
-    <t>01007274.1</t>
-  </si>
-  <si>
-    <t>34192158300001664001090002623468120992717000</t>
-  </si>
-  <si>
-    <t>01006922.3</t>
-  </si>
-  <si>
-    <t>70798158300011200000001121205064100656763896</t>
-  </si>
-  <si>
     <t>01007301.2</t>
   </si>
   <si>
     <t>00197158400018600000000003473568000003161417</t>
   </si>
   <si>
-    <t>01007023.2</t>
-  </si>
-  <si>
-    <t>70791158400003789090001121205064100656764423</t>
-  </si>
-  <si>
-    <t>01007269.1</t>
-  </si>
-  <si>
-    <t>70791158500008947500001121205064100656767137</t>
-  </si>
-  <si>
-    <t>01007187.4</t>
-  </si>
-  <si>
-    <t>70792158500010080000001121205064100656766212</t>
-  </si>
-  <si>
-    <t>VITAL DISTRIBUIDORA LTDA</t>
-  </si>
-  <si>
-    <t>01007168.3</t>
-  </si>
-  <si>
-    <t>34196158500002051221090002617698120992717000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZOE MED COMERCIO DE PRODUTOS MEDICOS HOSPITALARES </t>
-  </si>
-  <si>
-    <t>01007270.1</t>
-  </si>
-  <si>
-    <t>70793158500008565680001121205064100656766972</t>
-  </si>
-  <si>
-    <t>01007171.3</t>
-  </si>
-  <si>
-    <t>70793158500003640000001121205064100656766170</t>
-  </si>
-  <si>
-    <t>01007175.3</t>
-  </si>
-  <si>
-    <t>34194158500001660341090002618848120992717000</t>
+    <t>01007301.3</t>
+  </si>
+  <si>
+    <t>00191159100018600000000003473568000003161517</t>
   </si>
   <si>
     <t>01007311.1</t>
   </si>
   <si>
     <t>23796158600002754000435090000000130000304920</t>
-  </si>
-  <si>
-    <t>ELIENE RESENDE - RJ</t>
-  </si>
-  <si>
-    <t>MEDKA DISTRIBUIDORA HOSPITALAR LTDA</t>
-  </si>
-  <si>
-    <t>01007278.1</t>
-  </si>
-  <si>
-    <t>RJ</t>
-  </si>
-  <si>
-    <t>70793158600008973500001121205064100656767319</t>
-  </si>
-  <si>
-    <t>01007265.2</t>
-  </si>
-  <si>
-    <t>00192158700007694400000003473568000003158917</t>
-  </si>
-  <si>
-    <t>01007249.2</t>
-  </si>
-  <si>
-    <t>70792158700011660110001121205064100656766923</t>
-  </si>
-  <si>
-    <t>01007074.3</t>
-  </si>
-  <si>
-    <t>34192158700002930401090002611578120992717000</t>
-  </si>
-  <si>
-    <t>01007169.2</t>
-  </si>
-  <si>
-    <t>70797158700003809520001121205064100656765974</t>
   </si>
 </sst>
 </file>
@@ -1366,7 +1399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O120"/>
+  <dimension ref="A1:O124"/>
   <sheetFormatPr defaultColWidth="12.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.85546875" style="1" customWidth="1"/>
@@ -1458,7 +1491,7 @@
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="6">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>18</v>
@@ -1497,7 +1530,7 @@
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="6">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>18</v>
@@ -1514,74 +1547,74 @@
     </row>
     <row r="4" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
-        <v>45322</v>
+        <v>45296</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>25</v>
-      </c>
       <c r="E4" s="3">
-        <v>45350</v>
+        <v>45356</v>
       </c>
       <c r="F4" s="5">
-        <v>816</v>
+        <v>5418</v>
       </c>
       <c r="G4" s="5">
-        <v>1264.8699999999999</v>
+        <v>5418</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="6">
-        <v>950</v>
+        <v>946</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="L4" s="4"/>
       <c r="M4" s="4" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
     </row>
     <row r="5" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
-        <v>45296</v>
+        <v>45306</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E5" s="3">
-        <v>45356</v>
+        <v>45362</v>
       </c>
       <c r="F5" s="5">
-        <v>5418</v>
+        <v>384</v>
       </c>
       <c r="G5" s="5">
-        <v>5418</v>
+        <v>384</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="6">
-        <v>944</v>
+        <v>940</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="L5" s="4"/>
       <c r="M5" s="4" t="s">
@@ -1592,35 +1625,35 @@
     </row>
     <row r="6" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
-        <v>45306</v>
+        <v>45322</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E6" s="3">
-        <v>45362</v>
+        <v>45350</v>
       </c>
       <c r="F6" s="5">
-        <v>384</v>
+        <v>816</v>
       </c>
       <c r="G6" s="5">
-        <v>384</v>
+        <v>1264.8699999999999</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="6">
-        <v>938</v>
+        <v>952</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L6" s="4"/>
       <c r="M6" s="4" t="s">
@@ -1634,10 +1667,10 @@
         <v>45322</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>33</v>
@@ -1653,13 +1686,13 @@
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="6">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L7" s="4"/>
       <c r="M7" s="4" t="s">
@@ -1673,10 +1706,10 @@
         <v>45322</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>35</v>
@@ -1692,13 +1725,13 @@
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="6">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L8" s="4"/>
       <c r="M8" s="4" t="s">
@@ -1731,7 +1764,7 @@
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="6">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>18</v>
@@ -1770,7 +1803,7 @@
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="6">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>18</v>
@@ -1809,7 +1842,7 @@
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="6">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>18</v>
@@ -1826,7 +1859,7 @@
     </row>
     <row r="12" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
-        <v>45558</v>
+        <v>45546</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>45</v>
@@ -1838,23 +1871,23 @@
         <v>47</v>
       </c>
       <c r="E12" s="3">
-        <v>45600</v>
+        <v>45615</v>
       </c>
       <c r="F12" s="5">
-        <v>2000</v>
+        <v>1216.8599999999999</v>
       </c>
       <c r="G12" s="5">
-        <v>2000</v>
+        <v>1216.8599999999999</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="6">
-        <v>700</v>
+        <v>687</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>18</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L12" s="4"/>
       <c r="M12" s="4" t="s">
@@ -1865,7 +1898,7 @@
     </row>
     <row r="13" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
-        <v>45558</v>
+        <v>45546</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>45</v>
@@ -1877,23 +1910,23 @@
         <v>49</v>
       </c>
       <c r="E13" s="3">
-        <v>45607</v>
+        <v>45622</v>
       </c>
       <c r="F13" s="5">
-        <v>2000</v>
+        <v>1216.8599999999999</v>
       </c>
       <c r="G13" s="5">
-        <v>3204.34</v>
+        <v>1216.8599999999999</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="6">
-        <v>693</v>
+        <v>680</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>18</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L13" s="4"/>
       <c r="M13" s="4" t="s">
@@ -1904,46 +1937,46 @@
     </row>
     <row r="14" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
-        <v>45552</v>
+        <v>45548</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>53</v>
-      </c>
       <c r="E14" s="3">
-        <v>45608</v>
+        <v>45617</v>
       </c>
       <c r="F14" s="5">
-        <v>4439.8999999999996</v>
+        <v>1843.87</v>
       </c>
       <c r="G14" s="5">
-        <v>4439.8999999999996</v>
+        <v>1843.87</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="6">
-        <v>692</v>
+        <v>685</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>18</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="L14" s="4"/>
       <c r="M14" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="N14" s="4"/>
       <c r="O14" s="4"/>
     </row>
     <row r="15" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
-        <v>45558</v>
+        <v>45548</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>45</v>
@@ -1952,65 +1985,65 @@
         <v>46</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E15" s="3">
-        <v>45614</v>
+        <v>45624</v>
       </c>
       <c r="F15" s="5">
-        <v>2000</v>
+        <v>1843.88</v>
       </c>
       <c r="G15" s="5">
-        <v>2000</v>
+        <v>1843.88</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="6">
-        <v>686</v>
+        <v>678</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>18</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L15" s="4"/>
       <c r="M15" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="N15" s="4"/>
       <c r="O15" s="4"/>
     </row>
     <row r="16" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
-        <v>45546</v>
+        <v>45552</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E16" s="3">
-        <v>45615</v>
+        <v>45608</v>
       </c>
       <c r="F16" s="5">
-        <v>1216.8599999999999</v>
+        <v>4439.8999999999996</v>
       </c>
       <c r="G16" s="5">
-        <v>1216.8599999999999</v>
+        <v>4439.8999999999996</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="6">
-        <v>685</v>
+        <v>694</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>18</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="L16" s="4"/>
       <c r="M16" s="4" t="s">
@@ -2021,35 +2054,35 @@
     </row>
     <row r="17" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
-        <v>45548</v>
+        <v>45552</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>60</v>
       </c>
       <c r="E17" s="3">
-        <v>45617</v>
+        <v>45622</v>
       </c>
       <c r="F17" s="5">
-        <v>1843.87</v>
+        <v>4439.8999999999996</v>
       </c>
       <c r="G17" s="5">
-        <v>1843.87</v>
+        <v>4439.8999999999996</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="6">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>18</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="L17" s="4"/>
       <c r="M17" s="4" t="s">
@@ -2060,7 +2093,7 @@
     </row>
     <row r="18" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
-        <v>45546</v>
+        <v>45558</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>45</v>
@@ -2072,23 +2105,23 @@
         <v>62</v>
       </c>
       <c r="E18" s="3">
-        <v>45622</v>
+        <v>45607</v>
       </c>
       <c r="F18" s="5">
-        <v>1216.8599999999999</v>
+        <v>2000</v>
       </c>
       <c r="G18" s="5">
-        <v>1216.8599999999999</v>
+        <v>3204.34</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="6">
-        <v>678</v>
+        <v>695</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>18</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L18" s="4"/>
       <c r="M18" s="4" t="s">
@@ -2099,35 +2132,35 @@
     </row>
     <row r="19" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
-        <v>45552</v>
+        <v>45558</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>64</v>
       </c>
       <c r="E19" s="3">
-        <v>45622</v>
+        <v>45600</v>
       </c>
       <c r="F19" s="5">
-        <v>4439.8999999999996</v>
+        <v>2000</v>
       </c>
       <c r="G19" s="5">
-        <v>4439.8999999999996</v>
+        <v>2000</v>
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="6">
-        <v>678</v>
+        <v>702</v>
       </c>
       <c r="J19" s="4" t="s">
         <v>18</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="L19" s="4"/>
       <c r="M19" s="4" t="s">
@@ -2138,7 +2171,7 @@
     </row>
     <row r="20" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
-        <v>45548</v>
+        <v>45558</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>45</v>
@@ -2150,23 +2183,23 @@
         <v>66</v>
       </c>
       <c r="E20" s="3">
-        <v>45624</v>
+        <v>45614</v>
       </c>
       <c r="F20" s="5">
-        <v>1843.88</v>
+        <v>2000</v>
       </c>
       <c r="G20" s="5">
-        <v>1843.88</v>
+        <v>2000</v>
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="6">
-        <v>676</v>
+        <v>688</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>18</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L20" s="4"/>
       <c r="M20" s="4" t="s">
@@ -2199,7 +2232,7 @@
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="6">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>18</v>
@@ -2216,7 +2249,7 @@
     </row>
     <row r="22" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
-        <v>45646</v>
+        <v>45636</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>45</v>
@@ -2228,17 +2261,17 @@
         <v>74</v>
       </c>
       <c r="E22" s="3">
-        <v>45695</v>
+        <v>45699</v>
       </c>
       <c r="F22" s="5">
-        <v>3296.8</v>
+        <v>2330</v>
       </c>
       <c r="G22" s="5">
-        <v>3296.8</v>
+        <v>2330</v>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="6">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="J22" s="4" t="s">
         <v>18</v>
@@ -2255,7 +2288,7 @@
     </row>
     <row r="23" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
-        <v>45636</v>
+        <v>45646</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>45</v>
@@ -2267,17 +2300,17 @@
         <v>77</v>
       </c>
       <c r="E23" s="3">
-        <v>45699</v>
+        <v>45695</v>
       </c>
       <c r="F23" s="5">
-        <v>2330</v>
+        <v>3296.8</v>
       </c>
       <c r="G23" s="5">
-        <v>2330</v>
+        <v>3296.8</v>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="6">
-        <v>601</v>
+        <v>607</v>
       </c>
       <c r="J23" s="4" t="s">
         <v>18</v>
@@ -2316,7 +2349,7 @@
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="6">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="J24" s="4" t="s">
         <v>18</v>
@@ -2333,7 +2366,7 @@
     </row>
     <row r="25" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
-        <v>45677</v>
+        <v>45646</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>45</v>
@@ -2345,20 +2378,20 @@
         <v>81</v>
       </c>
       <c r="E25" s="3">
-        <v>45705</v>
+        <v>45709</v>
       </c>
       <c r="F25" s="5">
-        <v>2541</v>
+        <v>3296.8</v>
       </c>
       <c r="G25" s="5">
-        <v>2541</v>
+        <v>3296.8</v>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="6">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="K25" s="4" t="s">
         <v>75</v>
@@ -2372,7 +2405,7 @@
     </row>
     <row r="26" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
-        <v>45646</v>
+        <v>45677</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>45</v>
@@ -2384,20 +2417,20 @@
         <v>83</v>
       </c>
       <c r="E26" s="3">
-        <v>45709</v>
+        <v>45705</v>
       </c>
       <c r="F26" s="5">
-        <v>3296.8</v>
+        <v>2541</v>
       </c>
       <c r="G26" s="5">
-        <v>3296.8</v>
+        <v>2541</v>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="6">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="K26" s="4" t="s">
         <v>75</v>
@@ -2433,10 +2466,10 @@
       </c>
       <c r="H27" s="3"/>
       <c r="I27" s="6">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K27" s="4" t="s">
         <v>75</v>
@@ -2472,10 +2505,10 @@
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="6">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K28" s="4" t="s">
         <v>75</v>
@@ -2489,7 +2522,7 @@
     </row>
     <row r="29" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
-        <v>45699</v>
+        <v>45677</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>45</v>
@@ -2501,20 +2534,20 @@
         <v>89</v>
       </c>
       <c r="E29" s="3">
-        <v>45727</v>
+        <v>45740</v>
       </c>
       <c r="F29" s="5">
-        <v>7562.78</v>
+        <v>2541</v>
       </c>
       <c r="G29" s="5">
-        <v>7562.78</v>
+        <v>2541</v>
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="6">
-        <v>573</v>
+        <v>562</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="K29" s="4" t="s">
         <v>75</v>
@@ -2540,7 +2573,7 @@
         <v>91</v>
       </c>
       <c r="E30" s="3">
-        <v>45734</v>
+        <v>45727</v>
       </c>
       <c r="F30" s="5">
         <v>7562.78</v>
@@ -2550,7 +2583,7 @@
       </c>
       <c r="H30" s="3"/>
       <c r="I30" s="6">
-        <v>566</v>
+        <v>575</v>
       </c>
       <c r="J30" s="4" t="s">
         <v>18</v>
@@ -2570,43 +2603,43 @@
         <v>45699</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C31" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D31" s="4" t="s">
         <v>93</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>94</v>
       </c>
       <c r="E31" s="3">
         <v>45734</v>
       </c>
       <c r="F31" s="5">
-        <v>1154.56</v>
+        <v>7562.78</v>
       </c>
       <c r="G31" s="5">
-        <v>1154.56</v>
+        <v>7562.78</v>
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="6">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="J31" s="4" t="s">
         <v>18</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="L31" s="4"/>
       <c r="M31" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N31" s="4"/>
       <c r="O31" s="4"/>
     </row>
     <row r="32" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
-        <v>45677</v>
+        <v>45699</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>45</v>
@@ -2615,30 +2648,30 @@
         <v>73</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E32" s="3">
-        <v>45740</v>
+        <v>45741</v>
       </c>
       <c r="F32" s="5">
-        <v>2541</v>
+        <v>7562.78</v>
       </c>
       <c r="G32" s="5">
-        <v>2541</v>
+        <v>7562.78</v>
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="6">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="K32" s="4" t="s">
         <v>75</v>
       </c>
       <c r="L32" s="4"/>
       <c r="M32" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N32" s="4"/>
       <c r="O32" s="4"/>
@@ -2654,20 +2687,20 @@
         <v>73</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E33" s="3">
-        <v>45741</v>
+        <v>45748</v>
       </c>
       <c r="F33" s="5">
-        <v>7562.78</v>
+        <v>7562.76</v>
       </c>
       <c r="G33" s="5">
-        <v>7562.78</v>
+        <v>7562.76</v>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="6">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="J33" s="4" t="s">
         <v>18</v>
@@ -2677,7 +2710,7 @@
       </c>
       <c r="L33" s="4"/>
       <c r="M33" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="N33" s="4"/>
       <c r="O33" s="4"/>
@@ -2687,16 +2720,16 @@
         <v>45699</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>100</v>
       </c>
       <c r="E34" s="3">
-        <v>45741</v>
+        <v>45734</v>
       </c>
       <c r="F34" s="5">
         <v>1154.56</v>
@@ -2706,13 +2739,13 @@
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="6">
-        <v>559</v>
+        <v>568</v>
       </c>
       <c r="J34" s="4" t="s">
         <v>18</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="L34" s="4"/>
       <c r="M34" s="4" t="s">
@@ -2726,16 +2759,16 @@
         <v>45699</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>102</v>
       </c>
       <c r="E35" s="3">
-        <v>45748</v>
+        <v>45741</v>
       </c>
       <c r="F35" s="5">
         <v>1154.56</v>
@@ -2745,13 +2778,13 @@
       </c>
       <c r="H35" s="3"/>
       <c r="I35" s="6">
-        <v>552</v>
+        <v>561</v>
       </c>
       <c r="J35" s="4" t="s">
         <v>18</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="L35" s="4"/>
       <c r="M35" s="4" t="s">
@@ -2765,10 +2798,10 @@
         <v>45699</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>104</v>
@@ -2777,20 +2810,20 @@
         <v>45748</v>
       </c>
       <c r="F36" s="5">
-        <v>7562.76</v>
+        <v>1154.56</v>
       </c>
       <c r="G36" s="5">
-        <v>7562.76</v>
+        <v>1154.56</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="6">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="J36" s="4" t="s">
         <v>18</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="L36" s="4"/>
       <c r="M36" s="4" t="s">
@@ -2804,10 +2837,10 @@
         <v>45699</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>106</v>
@@ -2823,13 +2856,13 @@
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="6">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="J37" s="4" t="s">
         <v>18</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="L37" s="4"/>
       <c r="M37" s="4" t="s">
@@ -2843,7 +2876,7 @@
         <v>45733</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>108</v>
@@ -2862,13 +2895,13 @@
       </c>
       <c r="H38" s="3"/>
       <c r="I38" s="6">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="J38" s="4" t="s">
         <v>18</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="L38" s="4"/>
       <c r="M38" s="4" t="s">
@@ -2882,7 +2915,7 @@
         <v>45733</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>108</v>
@@ -2901,13 +2934,13 @@
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="6">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="J39" s="4" t="s">
         <v>18</v>
       </c>
       <c r="K39" s="4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="L39" s="4"/>
       <c r="M39" s="4" t="s">
@@ -2921,7 +2954,7 @@
         <v>45733</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>108</v>
@@ -2940,13 +2973,13 @@
       </c>
       <c r="H40" s="3"/>
       <c r="I40" s="6">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="J40" s="4" t="s">
         <v>18</v>
       </c>
       <c r="K40" s="4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="L40" s="4"/>
       <c r="M40" s="4" t="s">
@@ -2960,7 +2993,7 @@
         <v>45747</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>108</v>
@@ -2979,13 +3012,13 @@
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="6">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="J41" s="4" t="s">
         <v>18</v>
       </c>
       <c r="K41" s="4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="L41" s="4"/>
       <c r="M41" s="4" t="s">
@@ -2999,7 +3032,7 @@
         <v>45747</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>108</v>
@@ -3018,13 +3051,13 @@
       </c>
       <c r="H42" s="3"/>
       <c r="I42" s="6">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="J42" s="4" t="s">
         <v>18</v>
       </c>
       <c r="K42" s="4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="L42" s="4"/>
       <c r="M42" s="4" t="s">
@@ -3038,7 +3071,7 @@
         <v>45747</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>108</v>
@@ -3057,13 +3090,13 @@
       </c>
       <c r="H43" s="3"/>
       <c r="I43" s="6">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="J43" s="4" t="s">
         <v>18</v>
       </c>
       <c r="K43" s="4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="L43" s="4"/>
       <c r="M43" s="4" t="s">
@@ -3096,10 +3129,10 @@
       </c>
       <c r="H44" s="3"/>
       <c r="I44" s="6">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K44" s="4" t="s">
         <v>124</v>
@@ -3135,10 +3168,10 @@
       </c>
       <c r="H45" s="3"/>
       <c r="I45" s="6">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K45" s="4" t="s">
         <v>124</v>
@@ -3174,10 +3207,10 @@
       </c>
       <c r="H46" s="3"/>
       <c r="I46" s="6">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K46" s="4" t="s">
         <v>71</v>
@@ -3213,10 +3246,10 @@
       </c>
       <c r="H47" s="3"/>
       <c r="I47" s="6">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K47" s="4" t="s">
         <v>71</v>
@@ -3252,10 +3285,10 @@
       </c>
       <c r="H48" s="3"/>
       <c r="I48" s="6">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K48" s="4" t="s">
         <v>71</v>
@@ -3291,13 +3324,13 @@
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="6">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K49" s="4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="L49" s="4"/>
       <c r="M49" s="4" t="s">
@@ -3330,13 +3363,13 @@
       </c>
       <c r="H50" s="3"/>
       <c r="I50" s="6">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K50" s="4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="L50" s="4"/>
       <c r="M50" s="4" t="s">
@@ -3369,13 +3402,13 @@
       </c>
       <c r="H51" s="3"/>
       <c r="I51" s="6">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K51" s="4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="L51" s="4"/>
       <c r="M51" s="4" t="s">
@@ -3408,13 +3441,13 @@
       </c>
       <c r="H52" s="3"/>
       <c r="I52" s="6">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="L52" s="4"/>
       <c r="M52" s="4" t="s">
@@ -3425,10 +3458,10 @@
     </row>
     <row r="53" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
-        <v>45959</v>
+        <v>45938</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>145</v>
@@ -3440,60 +3473,60 @@
         <v>45980</v>
       </c>
       <c r="F53" s="5">
-        <v>28666.44</v>
+        <v>4480</v>
       </c>
       <c r="G53" s="5">
-        <v>28666.44</v>
+        <v>4480</v>
       </c>
       <c r="H53" s="3"/>
       <c r="I53" s="6">
-        <v>320</v>
-      </c>
-      <c r="J53" s="4"/>
+        <v>322</v>
+      </c>
+      <c r="J53" s="4" t="s">
+        <v>28</v>
+      </c>
       <c r="K53" s="4" t="s">
-        <v>54</v>
+        <v>124</v>
       </c>
       <c r="L53" s="4"/>
-      <c r="M53" s="4"/>
+      <c r="M53" s="4" t="s">
+        <v>147</v>
+      </c>
       <c r="N53" s="4"/>
       <c r="O53" s="4"/>
     </row>
     <row r="54" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
-        <v>45938</v>
+        <v>45947</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>121</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>148</v>
       </c>
       <c r="E54" s="3">
-        <v>45980</v>
+        <v>45989</v>
       </c>
       <c r="F54" s="5">
-        <v>4480</v>
+        <v>3220</v>
       </c>
       <c r="G54" s="5">
-        <v>4480</v>
+        <v>3220</v>
       </c>
       <c r="H54" s="3"/>
       <c r="I54" s="6">
-        <v>320</v>
-      </c>
-      <c r="J54" s="4" t="s">
-        <v>26</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="J54" s="4"/>
       <c r="K54" s="4" t="s">
         <v>124</v>
       </c>
       <c r="L54" s="4"/>
-      <c r="M54" s="4" t="s">
-        <v>149</v>
-      </c>
+      <c r="M54" s="4"/>
       <c r="N54" s="4"/>
       <c r="O54" s="4"/>
     </row>
@@ -3505,27 +3538,27 @@
         <v>135</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>150</v>
       </c>
       <c r="E55" s="3">
-        <v>45987</v>
+        <v>45980</v>
       </c>
       <c r="F55" s="5">
-        <v>33844.160000000003</v>
+        <v>28666.44</v>
       </c>
       <c r="G55" s="5">
-        <v>33844.160000000003</v>
+        <v>28666.44</v>
       </c>
       <c r="H55" s="3"/>
       <c r="I55" s="6">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="J55" s="4"/>
       <c r="K55" s="4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="L55" s="4"/>
       <c r="M55" s="4"/>
@@ -3534,33 +3567,33 @@
     </row>
     <row r="56" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
-        <v>45947</v>
+        <v>45959</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D56" s="4" t="s">
         <v>151</v>
       </c>
       <c r="E56" s="3">
-        <v>45989</v>
+        <v>45987</v>
       </c>
       <c r="F56" s="5">
-        <v>3220</v>
+        <v>33844.160000000003</v>
       </c>
       <c r="G56" s="5">
-        <v>3220</v>
+        <v>33844.160000000003</v>
       </c>
       <c r="H56" s="3"/>
       <c r="I56" s="6">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="J56" s="4"/>
       <c r="K56" s="4" t="s">
-        <v>124</v>
+        <v>58</v>
       </c>
       <c r="L56" s="4"/>
       <c r="M56" s="4"/>
@@ -3575,7 +3608,7 @@
         <v>135</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>152</v>
@@ -3591,11 +3624,11 @@
       </c>
       <c r="H57" s="3"/>
       <c r="I57" s="6">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="J57" s="4"/>
       <c r="K57" s="4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="L57" s="4"/>
       <c r="M57" s="4"/>
@@ -3604,10 +3637,10 @@
     </row>
     <row r="58" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
-        <v>46062</v>
+        <v>46045</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>153</v>
@@ -3616,23 +3649,23 @@
         <v>154</v>
       </c>
       <c r="E58" s="3">
-        <v>46090</v>
+        <v>46105</v>
       </c>
       <c r="F58" s="5">
-        <v>503.28</v>
+        <v>5466.66</v>
       </c>
       <c r="G58" s="5">
-        <v>806.34</v>
+        <v>5466.66</v>
       </c>
       <c r="H58" s="3"/>
       <c r="I58" s="6">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="L58" s="4"/>
       <c r="M58" s="4" t="s">
@@ -3646,36 +3679,36 @@
         <v>46062</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E59" s="3">
-        <v>46097</v>
+        <v>46090</v>
       </c>
       <c r="F59" s="5">
         <v>503.28</v>
       </c>
       <c r="G59" s="5">
-        <v>503.28</v>
+        <v>806.34</v>
       </c>
       <c r="H59" s="3"/>
       <c r="I59" s="6">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L59" s="4"/>
       <c r="M59" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N59" s="4"/>
       <c r="O59" s="4"/>
@@ -3685,16 +3718,16 @@
         <v>46062</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E60" s="3">
-        <v>46104</v>
+        <v>46097</v>
       </c>
       <c r="F60" s="5">
         <v>503.28</v>
@@ -3704,52 +3737,52 @@
       </c>
       <c r="H60" s="3"/>
       <c r="I60" s="6">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="J60" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K60" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L60" s="4"/>
       <c r="M60" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N60" s="4"/>
       <c r="O60" s="4"/>
     </row>
     <row r="61" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
-        <v>46045</v>
+        <v>46062</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>161</v>
       </c>
       <c r="E61" s="3">
-        <v>46105</v>
+        <v>46104</v>
       </c>
       <c r="F61" s="5">
-        <v>5466.66</v>
+        <v>503.28</v>
       </c>
       <c r="G61" s="5">
-        <v>5466.66</v>
+        <v>503.28</v>
       </c>
       <c r="H61" s="3"/>
       <c r="I61" s="6">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="K61" s="4" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="L61" s="4"/>
       <c r="M61" s="4" t="s">
@@ -3760,36 +3793,40 @@
     </row>
     <row r="62" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
-        <v>46171</v>
+        <v>46162</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>135</v>
+        <v>25</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E62" s="3">
-        <v>46192</v>
+        <v>46222</v>
       </c>
       <c r="F62" s="5">
-        <v>4676.8500000000004</v>
+        <v>31531.5</v>
       </c>
       <c r="G62" s="5">
-        <v>7494.53</v>
+        <v>31531.5</v>
       </c>
       <c r="H62" s="3"/>
       <c r="I62" s="6">
-        <v>108</v>
-      </c>
-      <c r="J62" s="4"/>
+        <v>80</v>
+      </c>
+      <c r="J62" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="K62" s="4" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="L62" s="4"/>
-      <c r="M62" s="4"/>
+      <c r="M62" s="4" t="s">
+        <v>165</v>
+      </c>
       <c r="N62" s="4"/>
       <c r="O62" s="4"/>
     </row>
@@ -3801,27 +3838,27 @@
         <v>135</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E63" s="3">
-        <v>46199</v>
+        <v>46192</v>
       </c>
       <c r="F63" s="5">
         <v>4676.8500000000004</v>
       </c>
       <c r="G63" s="5">
-        <v>4676.8500000000004</v>
+        <v>7494.53</v>
       </c>
       <c r="H63" s="3"/>
       <c r="I63" s="6">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="J63" s="4"/>
       <c r="K63" s="4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="L63" s="4"/>
       <c r="M63" s="4"/>
@@ -3836,13 +3873,13 @@
         <v>135</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E64" s="3">
-        <v>46206</v>
+        <v>46199</v>
       </c>
       <c r="F64" s="5">
         <v>4676.8500000000004</v>
@@ -3852,11 +3889,11 @@
       </c>
       <c r="H64" s="3"/>
       <c r="I64" s="6">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="J64" s="4"/>
       <c r="K64" s="4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="L64" s="4"/>
       <c r="M64" s="4"/>
@@ -3865,386 +3902,382 @@
     </row>
     <row r="65" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
-        <v>46162</v>
+        <v>46171</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>23</v>
+        <v>135</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E65" s="3">
-        <v>46222</v>
+        <v>46206</v>
       </c>
       <c r="F65" s="5">
-        <v>31531.5</v>
+        <v>4676.8500000000004</v>
       </c>
       <c r="G65" s="5">
-        <v>31531.5</v>
+        <v>4676.8500000000004</v>
       </c>
       <c r="H65" s="3"/>
       <c r="I65" s="6">
-        <v>78</v>
-      </c>
-      <c r="J65" s="4" t="s">
-        <v>18</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="J65" s="4"/>
       <c r="K65" s="4" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="L65" s="4"/>
-      <c r="M65" s="4" t="s">
-        <v>168</v>
-      </c>
+      <c r="M65" s="4"/>
       <c r="N65" s="4"/>
       <c r="O65" s="4"/>
     </row>
     <row r="66" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
-        <v>46198</v>
+        <v>46203</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>23</v>
+        <v>169</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E66" s="3">
-        <v>46228</v>
+        <v>46259</v>
       </c>
       <c r="F66" s="5">
-        <v>3516.48</v>
+        <v>860</v>
       </c>
       <c r="G66" s="5">
-        <v>3516.48</v>
+        <v>860</v>
       </c>
       <c r="H66" s="3"/>
       <c r="I66" s="6">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="J66" s="4" t="s">
-        <v>170</v>
+        <v>28</v>
       </c>
       <c r="K66" s="4" t="s">
-        <v>71</v>
+        <v>172</v>
       </c>
       <c r="L66" s="4"/>
       <c r="M66" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N66" s="4"/>
       <c r="O66" s="4"/>
     </row>
     <row r="67" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
-        <v>46203</v>
+        <v>46223</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>172</v>
+        <v>15</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E67" s="3">
-        <v>46259</v>
+        <v>46293</v>
       </c>
       <c r="F67" s="5">
-        <v>860</v>
+        <v>6265</v>
       </c>
       <c r="G67" s="5">
-        <v>860</v>
+        <v>6265</v>
       </c>
       <c r="H67" s="3"/>
       <c r="I67" s="6">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="J67" s="4" t="s">
-        <v>26</v>
+        <v>176</v>
       </c>
       <c r="K67" s="4" t="s">
-        <v>175</v>
+        <v>19</v>
       </c>
       <c r="L67" s="4"/>
       <c r="M67" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N67" s="4"/>
       <c r="O67" s="4"/>
     </row>
     <row r="68" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E68" s="3">
-        <v>46259</v>
+        <v>46270</v>
       </c>
       <c r="F68" s="5">
-        <v>2818.37</v>
+        <v>7551.88</v>
       </c>
       <c r="G68" s="5">
-        <v>2818.37</v>
+        <v>11442.87</v>
       </c>
       <c r="H68" s="3"/>
       <c r="I68" s="6">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="J68" s="4" t="s">
-        <v>26</v>
+        <v>181</v>
       </c>
       <c r="K68" s="4" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="L68" s="4"/>
       <c r="M68" s="4" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="N68" s="4"/>
       <c r="O68" s="4"/>
     </row>
     <row r="69" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>15</v>
+        <v>178</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>179</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E69" s="3">
-        <v>46262</v>
+        <v>46285</v>
       </c>
       <c r="F69" s="5">
-        <v>9716</v>
+        <v>7551.88</v>
       </c>
       <c r="G69" s="5">
-        <v>18957.86</v>
+        <v>7551.88</v>
       </c>
       <c r="H69" s="3"/>
       <c r="I69" s="6">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="J69" s="4" t="s">
-        <v>26</v>
+        <v>181</v>
       </c>
       <c r="K69" s="4" t="s">
-        <v>39</v>
+        <v>182</v>
       </c>
       <c r="L69" s="4"/>
       <c r="M69" s="4" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="N69" s="4"/>
       <c r="O69" s="4"/>
     </row>
     <row r="70" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E70" s="3">
-        <v>46266</v>
+        <v>46300</v>
       </c>
       <c r="F70" s="5">
-        <v>2818.37</v>
+        <v>7551.88</v>
       </c>
       <c r="G70" s="5">
-        <v>2818.37</v>
+        <v>7551.88</v>
       </c>
       <c r="H70" s="3"/>
       <c r="I70" s="6">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="J70" s="4" t="s">
-        <v>26</v>
+        <v>181</v>
       </c>
       <c r="K70" s="4" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="L70" s="4"/>
       <c r="M70" s="4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="N70" s="4"/>
       <c r="O70" s="4"/>
     </row>
     <row r="71" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3">
-        <v>46227</v>
+        <v>46223</v>
       </c>
       <c r="B71" s="4" t="s">
         <v>45</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E71" s="3">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="F71" s="5">
-        <v>23168.6</v>
+        <v>11200</v>
       </c>
       <c r="G71" s="5">
-        <v>23168.6</v>
+        <v>11200</v>
       </c>
       <c r="H71" s="3"/>
       <c r="I71" s="6">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J71" s="4" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="K71" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L71" s="4"/>
       <c r="M71" s="4" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="N71" s="4"/>
       <c r="O71" s="4"/>
     </row>
     <row r="72" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
-        <v>46225</v>
+        <v>46223</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>187</v>
+        <v>45</v>
       </c>
       <c r="C72" s="4" t="s">
         <v>188</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E72" s="3">
-        <v>46270</v>
+        <v>46283</v>
       </c>
       <c r="F72" s="5">
-        <v>7551.88</v>
+        <v>11200</v>
       </c>
       <c r="G72" s="5">
-        <v>11442.87</v>
+        <v>11200</v>
       </c>
       <c r="H72" s="3"/>
       <c r="I72" s="6">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="J72" s="4" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="K72" s="4" t="s">
-        <v>190</v>
+        <v>29</v>
       </c>
       <c r="L72" s="4"/>
       <c r="M72" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N72" s="4"/>
       <c r="O72" s="4"/>
     </row>
     <row r="73" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="3">
-        <v>46232</v>
+        <v>46223</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E73" s="3">
-        <v>46272</v>
+        <v>46293</v>
       </c>
       <c r="F73" s="5">
-        <v>9716</v>
+        <v>11200</v>
       </c>
       <c r="G73" s="5">
-        <v>9716</v>
+        <v>11200</v>
       </c>
       <c r="H73" s="3"/>
       <c r="I73" s="6">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="J73" s="4" t="s">
-        <v>26</v>
+        <v>181</v>
       </c>
       <c r="K73" s="4" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="L73" s="4"/>
       <c r="M73" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N73" s="4"/>
       <c r="O73" s="4"/>
     </row>
     <row r="74" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="3">
-        <v>46227</v>
+        <v>46224</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E74" s="3">
-        <v>46272</v>
+        <v>46259</v>
       </c>
       <c r="F74" s="5">
-        <v>4216.67</v>
+        <v>2818.37</v>
       </c>
       <c r="G74" s="5">
-        <v>6389.24</v>
+        <v>2818.37</v>
       </c>
       <c r="H74" s="3"/>
       <c r="I74" s="6">
+        <v>43</v>
+      </c>
+      <c r="J74" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="J74" s="4" t="s">
-        <v>195</v>
-      </c>
       <c r="K74" s="4" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
       <c r="L74" s="4"/>
       <c r="M74" s="4" t="s">
@@ -4258,10 +4291,10 @@
         <v>46224</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D75" s="4" t="s">
         <v>197</v>
@@ -4277,13 +4310,13 @@
       </c>
       <c r="H75" s="3"/>
       <c r="I75" s="6">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J75" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K75" s="4" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="L75" s="4"/>
       <c r="M75" s="4" t="s">
@@ -4294,78 +4327,78 @@
     </row>
     <row r="76" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="3">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>45</v>
+        <v>169</v>
       </c>
       <c r="C76" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="D76" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="D76" s="4" t="s">
-        <v>200</v>
-      </c>
       <c r="E76" s="3">
-        <v>46273</v>
+        <v>46280</v>
       </c>
       <c r="F76" s="5">
-        <v>11200</v>
+        <v>2818.36</v>
       </c>
       <c r="G76" s="5">
-        <v>11200</v>
+        <v>2818.36</v>
       </c>
       <c r="H76" s="3"/>
       <c r="I76" s="6">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J76" s="4" t="s">
-        <v>170</v>
+        <v>28</v>
       </c>
       <c r="K76" s="4" t="s">
-        <v>27</v>
+        <v>172</v>
       </c>
       <c r="L76" s="4"/>
       <c r="M76" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N76" s="4"/>
       <c r="O76" s="4"/>
     </row>
     <row r="77" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="3">
-        <v>46253</v>
+        <v>46224</v>
       </c>
       <c r="B77" s="4" t="s">
         <v>45</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E77" s="3">
-        <v>46274</v>
+        <v>46284</v>
       </c>
       <c r="F77" s="5">
-        <v>10080</v>
+        <v>10666.67</v>
       </c>
       <c r="G77" s="5">
-        <v>10080</v>
+        <v>10666.67</v>
       </c>
       <c r="H77" s="3"/>
       <c r="I77" s="6">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J77" s="4" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="K77" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L77" s="4"/>
       <c r="M77" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="N77" s="4"/>
       <c r="O77" s="4"/>
@@ -4378,7 +4411,7 @@
         <v>45</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>184</v>
+        <v>203</v>
       </c>
       <c r="D78" s="4" t="s">
         <v>204</v>
@@ -4394,13 +4427,13 @@
       </c>
       <c r="H78" s="3"/>
       <c r="I78" s="6">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J78" s="4" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="K78" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L78" s="4"/>
       <c r="M78" s="4" t="s">
@@ -4411,35 +4444,35 @@
     </row>
     <row r="79" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="3">
-        <v>46234</v>
+        <v>46227</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>187</v>
+        <v>45</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="D79" s="4" t="s">
         <v>206</v>
       </c>
       <c r="E79" s="3">
-        <v>46279</v>
+        <v>46283</v>
       </c>
       <c r="F79" s="5">
-        <v>3789.09</v>
+        <v>23168.6</v>
       </c>
       <c r="G79" s="5">
-        <v>5741.36</v>
+        <v>23168.6</v>
       </c>
       <c r="H79" s="3"/>
       <c r="I79" s="6">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J79" s="4" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="K79" s="4" t="s">
-        <v>190</v>
+        <v>29</v>
       </c>
       <c r="L79" s="4"/>
       <c r="M79" s="4" t="s">
@@ -4450,35 +4483,35 @@
     </row>
     <row r="80" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="3">
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="D80" s="4" t="s">
         <v>208</v>
       </c>
       <c r="E80" s="3">
-        <v>46280</v>
+        <v>46272</v>
       </c>
       <c r="F80" s="5">
-        <v>2818.36</v>
+        <v>4216.67</v>
       </c>
       <c r="G80" s="5">
-        <v>2818.36</v>
+        <v>6389.24</v>
       </c>
       <c r="H80" s="3"/>
       <c r="I80" s="6">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J80" s="4" t="s">
-        <v>26</v>
+        <v>176</v>
       </c>
       <c r="K80" s="4" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="L80" s="4"/>
       <c r="M80" s="4" t="s">
@@ -4489,35 +4522,35 @@
     </row>
     <row r="81" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="3">
-        <v>46253</v>
+        <v>46227</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>45</v>
+        <v>178</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="D81" s="4" t="s">
         <v>210</v>
       </c>
       <c r="E81" s="3">
-        <v>46281</v>
+        <v>46287</v>
       </c>
       <c r="F81" s="5">
-        <v>10080</v>
+        <v>4216.67</v>
       </c>
       <c r="G81" s="5">
-        <v>10080</v>
+        <v>4216.67</v>
       </c>
       <c r="H81" s="3"/>
       <c r="I81" s="6">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J81" s="4" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="K81" s="4" t="s">
-        <v>27</v>
+        <v>182</v>
       </c>
       <c r="L81" s="4"/>
       <c r="M81" s="4" t="s">
@@ -4531,929 +4564,929 @@
         <v>46232</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>15</v>
+        <v>178</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>179</v>
+        <v>212</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E82" s="3">
-        <v>46282</v>
+        <v>46292</v>
       </c>
       <c r="F82" s="5">
-        <v>9716</v>
+        <v>4082.05</v>
       </c>
       <c r="G82" s="5">
-        <v>9716</v>
+        <v>4082.05</v>
       </c>
       <c r="H82" s="3"/>
       <c r="I82" s="6">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="J82" s="4" t="s">
-        <v>26</v>
+        <v>181</v>
       </c>
       <c r="K82" s="4" t="s">
-        <v>39</v>
+        <v>182</v>
       </c>
       <c r="L82" s="4"/>
       <c r="M82" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N82" s="4"/>
       <c r="O82" s="4"/>
     </row>
     <row r="83" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="3">
-        <v>46227</v>
+        <v>46234</v>
       </c>
       <c r="B83" s="4" t="s">
         <v>45</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E83" s="3">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" s="5">
-        <v>23168.6</v>
+        <v>6500</v>
       </c>
       <c r="G83" s="5">
-        <v>23168.6</v>
+        <v>6500</v>
       </c>
       <c r="H83" s="3"/>
       <c r="I83" s="6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J83" s="4" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="K83" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L83" s="4"/>
       <c r="M83" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N83" s="4"/>
       <c r="O83" s="4"/>
     </row>
     <row r="84" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="3">
-        <v>46223</v>
+        <v>46232</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E84" s="3">
-        <v>46283</v>
+        <v>46262</v>
       </c>
       <c r="F84" s="5">
-        <v>11200</v>
+        <v>9716</v>
       </c>
       <c r="G84" s="5">
-        <v>11200</v>
+        <v>18957.86</v>
       </c>
       <c r="H84" s="3"/>
       <c r="I84" s="6">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="J84" s="4" t="s">
-        <v>170</v>
+        <v>28</v>
       </c>
       <c r="K84" s="4" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="L84" s="4"/>
       <c r="M84" s="4" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="N84" s="4"/>
       <c r="O84" s="4"/>
     </row>
     <row r="85" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="3">
-        <v>46224</v>
+        <v>46232</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E85" s="3">
-        <v>46284</v>
+        <v>46272</v>
       </c>
       <c r="F85" s="5">
-        <v>10666.67</v>
+        <v>9716</v>
       </c>
       <c r="G85" s="5">
-        <v>10666.67</v>
+        <v>9716</v>
       </c>
       <c r="H85" s="3"/>
       <c r="I85" s="6">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="J85" s="4" t="s">
-        <v>170</v>
+        <v>28</v>
       </c>
       <c r="K85" s="4" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="L85" s="4"/>
       <c r="M85" s="4" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="N85" s="4"/>
       <c r="O85" s="4"/>
     </row>
     <row r="86" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="3">
-        <v>46234</v>
+        <v>46232</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E86" s="3">
-        <v>46284</v>
+        <v>46282</v>
       </c>
       <c r="F86" s="5">
-        <v>6500</v>
+        <v>9716</v>
       </c>
       <c r="G86" s="5">
-        <v>6500</v>
+        <v>9716</v>
       </c>
       <c r="H86" s="3"/>
       <c r="I86" s="6">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J86" s="4" t="s">
-        <v>170</v>
+        <v>28</v>
       </c>
       <c r="K86" s="4" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="L86" s="4"/>
       <c r="M86" s="4" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="N86" s="4"/>
       <c r="O86" s="4"/>
     </row>
     <row r="87" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="3">
-        <v>46234</v>
+        <v>46232</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E87" s="3">
-        <v>46284</v>
+        <v>46292</v>
       </c>
       <c r="F87" s="5">
-        <v>4950.17</v>
+        <v>9716</v>
       </c>
       <c r="G87" s="5">
-        <v>4950.17</v>
+        <v>9716</v>
       </c>
       <c r="H87" s="3"/>
       <c r="I87" s="6">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J87" s="4" t="s">
-        <v>170</v>
+        <v>28</v>
       </c>
       <c r="K87" s="4" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="L87" s="4"/>
       <c r="M87" s="4" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="N87" s="4"/>
       <c r="O87" s="4"/>
     </row>
     <row r="88" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="3">
-        <v>46225</v>
+        <v>46234</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>187</v>
+        <v>45</v>
       </c>
       <c r="C88" s="4" t="s">
         <v>188</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E88" s="3">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="F88" s="5">
-        <v>7551.88</v>
+        <v>4950.17</v>
       </c>
       <c r="G88" s="5">
-        <v>7551.88</v>
+        <v>4950.17</v>
       </c>
       <c r="H88" s="3"/>
       <c r="I88" s="6">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J88" s="4" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="K88" s="4" t="s">
-        <v>190</v>
+        <v>29</v>
       </c>
       <c r="L88" s="4"/>
       <c r="M88" s="4" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="N88" s="4"/>
       <c r="O88" s="4"/>
     </row>
     <row r="89" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="3">
-        <v>46244</v>
+        <v>46234</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>45</v>
+        <v>178</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E89" s="3">
-        <v>46286</v>
+        <v>46279</v>
       </c>
       <c r="F89" s="5">
-        <v>4320</v>
+        <v>3789.09</v>
       </c>
       <c r="G89" s="5">
-        <v>4320</v>
+        <v>5741.36</v>
       </c>
       <c r="H89" s="3"/>
       <c r="I89" s="6">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J89" s="4" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="K89" s="4" t="s">
-        <v>27</v>
+        <v>182</v>
       </c>
       <c r="L89" s="4"/>
       <c r="M89" s="4" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="N89" s="4"/>
       <c r="O89" s="4"/>
     </row>
     <row r="90" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="3">
-        <v>46266</v>
+        <v>46234</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>45</v>
+        <v>178</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E90" s="3">
-        <v>46287</v>
+        <v>46294</v>
       </c>
       <c r="F90" s="5">
-        <v>18600</v>
+        <v>3789.09</v>
       </c>
       <c r="G90" s="5">
-        <v>18600</v>
+        <v>3789.09</v>
       </c>
       <c r="H90" s="3"/>
       <c r="I90" s="6">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J90" s="4" t="s">
-        <v>26</v>
+        <v>181</v>
       </c>
       <c r="K90" s="4" t="s">
-        <v>27</v>
+        <v>182</v>
       </c>
       <c r="L90" s="4"/>
       <c r="M90" s="4" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="N90" s="4"/>
       <c r="O90" s="4"/>
     </row>
     <row r="91" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="3">
-        <v>46227</v>
+        <v>46237</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>187</v>
+        <v>25</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>188</v>
+        <v>163</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E91" s="3">
-        <v>46287</v>
+        <v>46297</v>
       </c>
       <c r="F91" s="5">
-        <v>4216.67</v>
+        <v>2930.4</v>
       </c>
       <c r="G91" s="5">
-        <v>4216.67</v>
+        <v>2930.4</v>
       </c>
       <c r="H91" s="3"/>
       <c r="I91" s="6">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J91" s="4" t="s">
-        <v>195</v>
+        <v>18</v>
       </c>
       <c r="K91" s="4" t="s">
-        <v>190</v>
+        <v>71</v>
       </c>
       <c r="L91" s="4"/>
       <c r="M91" s="4" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="N91" s="4"/>
       <c r="O91" s="4"/>
     </row>
     <row r="92" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="3">
-        <v>46253</v>
+        <v>46244</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>45</v>
+        <v>135</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>184</v>
+        <v>234</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="E92" s="3">
-        <v>46288</v>
+        <v>46293</v>
       </c>
       <c r="F92" s="5">
-        <v>10080</v>
+        <v>3599.85</v>
       </c>
       <c r="G92" s="5">
-        <v>10080</v>
+        <v>3599.85</v>
       </c>
       <c r="H92" s="3"/>
       <c r="I92" s="6">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J92" s="4" t="s">
-        <v>170</v>
+        <v>18</v>
       </c>
       <c r="K92" s="4" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="L92" s="4"/>
       <c r="M92" s="4" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="N92" s="4"/>
       <c r="O92" s="4"/>
     </row>
     <row r="93" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="3">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>121</v>
+        <v>169</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="E93" s="3">
-        <v>46288</v>
+        <v>46301</v>
       </c>
       <c r="F93" s="5">
-        <v>1660.33</v>
+        <v>5443.56</v>
       </c>
       <c r="G93" s="5">
-        <v>1660.33</v>
+        <v>5443.56</v>
       </c>
       <c r="H93" s="3"/>
       <c r="I93" s="6">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="J93" s="4" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="K93" s="4" t="s">
-        <v>124</v>
+        <v>239</v>
       </c>
       <c r="L93" s="4"/>
       <c r="M93" s="4" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="N93" s="4"/>
       <c r="O93" s="4"/>
     </row>
     <row r="94" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="3">
-        <v>46253</v>
+        <v>46248</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>121</v>
+        <v>15</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="E94" s="3">
-        <v>46288</v>
+        <v>46293</v>
       </c>
       <c r="F94" s="5">
-        <v>3640</v>
+        <v>23355.33</v>
       </c>
       <c r="G94" s="5">
-        <v>3640</v>
+        <v>23355.33</v>
       </c>
       <c r="H94" s="3"/>
       <c r="I94" s="6">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J94" s="4" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="K94" s="4" t="s">
-        <v>124</v>
+        <v>39</v>
       </c>
       <c r="L94" s="4"/>
       <c r="M94" s="4" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="N94" s="4"/>
       <c r="O94" s="4"/>
     </row>
     <row r="95" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="3">
-        <v>46259</v>
+        <v>46244</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>239</v>
+        <v>203</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="E95" s="3">
-        <v>46289</v>
+        <v>46286</v>
       </c>
       <c r="F95" s="5">
-        <v>6265</v>
+        <v>4320</v>
       </c>
       <c r="G95" s="5">
-        <v>6265</v>
+        <v>4320</v>
       </c>
       <c r="H95" s="3"/>
       <c r="I95" s="6">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="J95" s="4" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="K95" s="4" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="L95" s="4"/>
       <c r="M95" s="4" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="N95" s="4"/>
       <c r="O95" s="4"/>
     </row>
     <row r="96" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="3">
-        <v>46262</v>
+        <v>46244</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>242</v>
+        <v>45</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>243</v>
+        <v>203</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E96" s="3">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="F96" s="5">
-        <v>7694.4</v>
+        <v>4320</v>
       </c>
       <c r="G96" s="5">
-        <v>7694.4</v>
+        <v>4320</v>
       </c>
       <c r="H96" s="3"/>
       <c r="I96" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J96" s="4" t="s">
-        <v>26</v>
+        <v>181</v>
       </c>
       <c r="K96" s="4" t="s">
-        <v>245</v>
+        <v>29</v>
       </c>
       <c r="L96" s="4"/>
       <c r="M96" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N96" s="4"/>
       <c r="O96" s="4"/>
     </row>
     <row r="97" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="3">
-        <v>46262</v>
+        <v>46245</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>242</v>
+        <v>169</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E97" s="3">
-        <v>46290</v>
+        <v>46301</v>
       </c>
       <c r="F97" s="5">
-        <v>11660.11</v>
+        <v>1840.96</v>
       </c>
       <c r="G97" s="5">
-        <v>11660.11</v>
+        <v>1840.96</v>
       </c>
       <c r="H97" s="3"/>
       <c r="I97" s="6">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J97" s="4" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="K97" s="4" t="s">
-        <v>245</v>
+        <v>172</v>
       </c>
       <c r="L97" s="4"/>
       <c r="M97" s="4" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="N97" s="4"/>
       <c r="O97" s="4"/>
     </row>
     <row r="98" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="3">
-        <v>46231</v>
+        <v>46253</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>45</v>
+        <v>169</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>199</v>
+        <v>251</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="E98" s="3">
-        <v>46291</v>
+        <v>46295</v>
       </c>
       <c r="F98" s="5">
-        <v>6500</v>
+        <v>2051.2199999999998</v>
       </c>
       <c r="G98" s="5">
-        <v>6500</v>
+        <v>2051.2199999999998</v>
       </c>
       <c r="H98" s="3"/>
       <c r="I98" s="6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J98" s="4" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="K98" s="4" t="s">
-        <v>75</v>
+        <v>172</v>
       </c>
       <c r="L98" s="4"/>
       <c r="M98" s="4" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="N98" s="4"/>
       <c r="O98" s="4"/>
     </row>
     <row r="99" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="3">
-        <v>46232</v>
+        <v>46252</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="E99" s="3">
-        <v>46292</v>
+        <v>46297</v>
       </c>
       <c r="F99" s="5">
-        <v>9716</v>
+        <v>3809.52</v>
       </c>
       <c r="G99" s="5">
-        <v>9716</v>
+        <v>3809.52</v>
       </c>
       <c r="H99" s="3"/>
       <c r="I99" s="6">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J99" s="4" t="s">
-        <v>26</v>
+        <v>181</v>
       </c>
       <c r="K99" s="4" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="L99" s="4"/>
       <c r="M99" s="4" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="N99" s="4"/>
       <c r="O99" s="4"/>
     </row>
     <row r="100" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="3">
-        <v>46232</v>
+        <v>46253</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>187</v>
+        <v>121</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="E100" s="3">
-        <v>46292</v>
+        <v>46288</v>
       </c>
       <c r="F100" s="5">
-        <v>4082.05</v>
+        <v>3640</v>
       </c>
       <c r="G100" s="5">
-        <v>4082.05</v>
+        <v>3640</v>
       </c>
       <c r="H100" s="3"/>
       <c r="I100" s="6">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J100" s="4" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="K100" s="4" t="s">
-        <v>190</v>
+        <v>124</v>
       </c>
       <c r="L100" s="4"/>
       <c r="M100" s="4" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="N100" s="4"/>
       <c r="O100" s="4"/>
     </row>
     <row r="101" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="3">
-        <v>46244</v>
+        <v>46253</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="C101" s="4" t="s">
         <v>256</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E101" s="3">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="F101" s="5">
-        <v>3599.85</v>
+        <v>3640</v>
       </c>
       <c r="G101" s="5">
-        <v>3599.85</v>
+        <v>3640</v>
       </c>
       <c r="H101" s="3"/>
       <c r="I101" s="6">
         <v>7</v>
       </c>
       <c r="J101" s="4" t="s">
-        <v>18</v>
+        <v>181</v>
       </c>
       <c r="K101" s="4" t="s">
-        <v>54</v>
+        <v>124</v>
       </c>
       <c r="L101" s="4"/>
       <c r="M101" s="4" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N101" s="4"/>
       <c r="O101" s="4"/>
     </row>
     <row r="102" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="3">
-        <v>46223</v>
+        <v>46253</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>15</v>
+        <v>121</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E102" s="3">
-        <v>46293</v>
+        <v>46288</v>
       </c>
       <c r="F102" s="5">
-        <v>6265</v>
+        <v>1660.33</v>
       </c>
       <c r="G102" s="5">
-        <v>6265</v>
+        <v>1660.33</v>
       </c>
       <c r="H102" s="3"/>
       <c r="I102" s="6">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J102" s="4" t="s">
-        <v>195</v>
+        <v>18</v>
       </c>
       <c r="K102" s="4" t="s">
-        <v>19</v>
+        <v>124</v>
       </c>
       <c r="L102" s="4"/>
       <c r="M102" s="4" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N102" s="4"/>
       <c r="O102" s="4"/>
     </row>
     <row r="103" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="3">
-        <v>46244</v>
+        <v>46253</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>45</v>
+        <v>121</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>184</v>
+        <v>256</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E103" s="3">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="F103" s="5">
-        <v>4320</v>
+        <v>1660.34</v>
       </c>
       <c r="G103" s="5">
-        <v>4320</v>
+        <v>1660.34</v>
       </c>
       <c r="H103" s="3"/>
       <c r="I103" s="6">
         <v>7</v>
       </c>
       <c r="J103" s="4" t="s">
-        <v>170</v>
+        <v>18</v>
       </c>
       <c r="K103" s="4" t="s">
-        <v>27</v>
+        <v>124</v>
       </c>
       <c r="L103" s="4"/>
       <c r="M103" s="4" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="N103" s="4"/>
       <c r="O103" s="4"/>
     </row>
     <row r="104" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="3">
-        <v>46248</v>
+        <v>46253</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>263</v>
+        <v>203</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E104" s="3">
-        <v>46293</v>
+        <v>46274</v>
       </c>
       <c r="F104" s="5">
-        <v>23355.33</v>
+        <v>10080</v>
       </c>
       <c r="G104" s="5">
-        <v>23355.33</v>
+        <v>10080</v>
       </c>
       <c r="H104" s="3"/>
       <c r="I104" s="6">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="J104" s="4" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="K104" s="4" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="L104" s="4"/>
       <c r="M104" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N104" s="4"/>
       <c r="O104" s="4"/>
     </row>
     <row r="105" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="3">
-        <v>46265</v>
+        <v>46253</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>266</v>
+        <v>203</v>
       </c>
       <c r="D105" s="4" t="s">
         <v>267</v>
       </c>
       <c r="E105" s="3">
-        <v>46293</v>
+        <v>46281</v>
       </c>
       <c r="F105" s="5">
-        <v>1664</v>
+        <v>10080</v>
       </c>
       <c r="G105" s="5">
-        <v>1664</v>
+        <v>10080</v>
       </c>
       <c r="H105" s="3"/>
       <c r="I105" s="6">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="J105" s="4" t="s">
-        <v>18</v>
+        <v>181</v>
       </c>
       <c r="K105" s="4" t="s">
-        <v>71</v>
+        <v>29</v>
       </c>
       <c r="L105" s="4"/>
       <c r="M105" s="4" t="s">
@@ -5464,35 +5497,35 @@
     </row>
     <row r="106" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="3">
-        <v>46223</v>
+        <v>46253</v>
       </c>
       <c r="B106" s="4" t="s">
         <v>45</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="D106" s="4" t="s">
         <v>269</v>
       </c>
       <c r="E106" s="3">
-        <v>46293</v>
+        <v>46288</v>
       </c>
       <c r="F106" s="5">
-        <v>11200</v>
+        <v>10080</v>
       </c>
       <c r="G106" s="5">
-        <v>11200</v>
+        <v>10080</v>
       </c>
       <c r="H106" s="3"/>
       <c r="I106" s="6">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J106" s="4" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="K106" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L106" s="4"/>
       <c r="M106" s="4" t="s">
@@ -5503,35 +5536,35 @@
     </row>
     <row r="107" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="3">
-        <v>46266</v>
+        <v>46253</v>
       </c>
       <c r="B107" s="4" t="s">
         <v>45</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>184</v>
+        <v>203</v>
       </c>
       <c r="D107" s="4" t="s">
         <v>271</v>
       </c>
       <c r="E107" s="3">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F107" s="5">
-        <v>18600</v>
+        <v>10080</v>
       </c>
       <c r="G107" s="5">
-        <v>18600</v>
+        <v>10080</v>
       </c>
       <c r="H107" s="3"/>
       <c r="I107" s="6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J107" s="4" t="s">
-        <v>26</v>
+        <v>181</v>
       </c>
       <c r="K107" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L107" s="4"/>
       <c r="M107" s="4" t="s">
@@ -5542,35 +5575,35 @@
     </row>
     <row r="108" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="3">
-        <v>46234</v>
+        <v>46259</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>187</v>
+        <v>15</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="D108" s="4" t="s">
         <v>273</v>
       </c>
       <c r="E108" s="3">
-        <v>46294</v>
+        <v>46289</v>
       </c>
       <c r="F108" s="5">
-        <v>3789.09</v>
+        <v>6265</v>
       </c>
       <c r="G108" s="5">
-        <v>3789.09</v>
+        <v>6265</v>
       </c>
       <c r="H108" s="3"/>
       <c r="I108" s="6">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="J108" s="4" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="K108" s="4" t="s">
-        <v>190</v>
+        <v>19</v>
       </c>
       <c r="L108" s="4"/>
       <c r="M108" s="4" t="s">
@@ -5581,35 +5614,35 @@
     </row>
     <row r="109" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="3">
-        <v>46265</v>
+        <v>46253</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>263</v>
+        <v>163</v>
       </c>
       <c r="D109" s="4" t="s">
         <v>275</v>
       </c>
       <c r="E109" s="3">
-        <v>46295</v>
+        <v>46298</v>
       </c>
       <c r="F109" s="5">
-        <v>8947.5</v>
+        <v>1172.1600000000001</v>
       </c>
       <c r="G109" s="5">
-        <v>8947.5</v>
+        <v>1172.1600000000001</v>
       </c>
       <c r="H109" s="3"/>
       <c r="I109" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J109" s="4" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="K109" s="4" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="L109" s="4"/>
       <c r="M109" s="4" t="s">
@@ -5620,35 +5653,35 @@
     </row>
     <row r="110" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="3">
-        <v>46253</v>
+        <v>46266</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>45</v>
+        <v>169</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>184</v>
+        <v>237</v>
       </c>
       <c r="D110" s="4" t="s">
         <v>277</v>
       </c>
       <c r="E110" s="3">
-        <v>46295</v>
+        <v>46301</v>
       </c>
       <c r="F110" s="5">
-        <v>10080</v>
+        <v>3979.06</v>
       </c>
       <c r="G110" s="5">
-        <v>10080</v>
+        <v>3979.06</v>
       </c>
       <c r="H110" s="3"/>
       <c r="I110" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J110" s="4" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="K110" s="4" t="s">
-        <v>27</v>
+        <v>239</v>
       </c>
       <c r="L110" s="4"/>
       <c r="M110" s="4" t="s">
@@ -5659,49 +5692,49 @@
     </row>
     <row r="111" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="3">
-        <v>46253</v>
+        <v>46266</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="C111" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="D111" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="D111" s="4" t="s">
-        <v>280</v>
-      </c>
       <c r="E111" s="3">
-        <v>46295</v>
+        <v>46301</v>
       </c>
       <c r="F111" s="5">
-        <v>2051.2199999999998</v>
+        <v>1286.25</v>
       </c>
       <c r="G111" s="5">
-        <v>2051.2199999999998</v>
+        <v>1286.25</v>
       </c>
       <c r="H111" s="3"/>
       <c r="I111" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J111" s="4" t="s">
-        <v>18</v>
+        <v>176</v>
       </c>
       <c r="K111" s="4" t="s">
-        <v>175</v>
+        <v>58</v>
       </c>
       <c r="L111" s="4"/>
       <c r="M111" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="N111" s="4"/>
       <c r="O111" s="4"/>
     </row>
     <row r="112" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="3">
-        <v>46265</v>
+        <v>46262</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>135</v>
+        <v>281</v>
       </c>
       <c r="C112" s="4" t="s">
         <v>282</v>
@@ -5710,257 +5743,257 @@
         <v>283</v>
       </c>
       <c r="E112" s="3">
-        <v>46295</v>
+        <v>46290</v>
       </c>
       <c r="F112" s="5">
-        <v>4750</v>
+        <v>11660.11</v>
       </c>
       <c r="G112" s="5">
-        <v>8565.68</v>
+        <v>11660.11</v>
       </c>
       <c r="H112" s="3"/>
       <c r="I112" s="6">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J112" s="4" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="K112" s="4" t="s">
-        <v>54</v>
+        <v>284</v>
       </c>
       <c r="L112" s="4"/>
       <c r="M112" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N112" s="4"/>
       <c r="O112" s="4"/>
     </row>
     <row r="113" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="3">
-        <v>46253</v>
+        <v>46262</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>121</v>
+        <v>281</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>234</v>
+        <v>282</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E113" s="3">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="F113" s="5">
-        <v>3640</v>
+        <v>11660.11</v>
       </c>
       <c r="G113" s="5">
-        <v>3640</v>
+        <v>11660.11</v>
       </c>
       <c r="H113" s="3"/>
       <c r="I113" s="6">
         <v>5</v>
       </c>
       <c r="J113" s="4" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="K113" s="4" t="s">
-        <v>124</v>
+        <v>284</v>
       </c>
       <c r="L113" s="4"/>
       <c r="M113" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N113" s="4"/>
       <c r="O113" s="4"/>
     </row>
     <row r="114" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="3">
-        <v>46253</v>
+        <v>46262</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>121</v>
+        <v>281</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>234</v>
+        <v>282</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E114" s="3">
-        <v>46295</v>
+        <v>46290</v>
       </c>
       <c r="F114" s="5">
-        <v>1660.34</v>
+        <v>7694.4</v>
       </c>
       <c r="G114" s="5">
-        <v>1660.34</v>
+        <v>7694.4</v>
       </c>
       <c r="H114" s="3"/>
       <c r="I114" s="6">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J114" s="4" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="K114" s="4" t="s">
-        <v>124</v>
+        <v>284</v>
       </c>
       <c r="L114" s="4"/>
       <c r="M114" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N114" s="4"/>
       <c r="O114" s="4"/>
     </row>
     <row r="115" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="3">
-        <v>46268</v>
+        <v>46262</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>23</v>
+        <v>281</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E115" s="3">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F115" s="5">
-        <v>2754</v>
+        <v>7694.4</v>
       </c>
       <c r="G115" s="5">
-        <v>2754</v>
+        <v>7694.4</v>
       </c>
       <c r="H115" s="3"/>
       <c r="I115" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J115" s="4" t="s">
-        <v>195</v>
+        <v>28</v>
       </c>
       <c r="K115" s="4" t="s">
-        <v>71</v>
+        <v>284</v>
       </c>
       <c r="L115" s="4"/>
       <c r="M115" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N115" s="4"/>
       <c r="O115" s="4"/>
     </row>
     <row r="116" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="3">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>291</v>
+        <v>15</v>
       </c>
       <c r="C116" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="D116" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="D116" s="4" t="s">
-        <v>293</v>
-      </c>
       <c r="E116" s="3">
-        <v>46296</v>
+        <v>46295</v>
       </c>
       <c r="F116" s="5">
-        <v>8973.5</v>
+        <v>8947.5</v>
       </c>
       <c r="G116" s="5">
-        <v>8973.5</v>
+        <v>8947.5</v>
       </c>
       <c r="H116" s="3"/>
       <c r="I116" s="6">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J116" s="4" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="K116" s="4" t="s">
-        <v>294</v>
+        <v>39</v>
       </c>
       <c r="L116" s="4"/>
       <c r="M116" s="4" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="N116" s="4"/>
       <c r="O116" s="4"/>
     </row>
     <row r="117" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="3">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>242</v>
+        <v>135</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>243</v>
+        <v>294</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E117" s="3">
-        <v>46297</v>
+        <v>46295</v>
       </c>
       <c r="F117" s="5">
-        <v>7694.4</v>
+        <v>4750</v>
       </c>
       <c r="G117" s="5">
-        <v>7694.4</v>
+        <v>8565.68</v>
       </c>
       <c r="H117" s="3"/>
       <c r="I117" s="6">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J117" s="4" t="s">
-        <v>26</v>
+        <v>181</v>
       </c>
       <c r="K117" s="4" t="s">
-        <v>245</v>
+        <v>58</v>
       </c>
       <c r="L117" s="4"/>
       <c r="M117" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="N117" s="4"/>
       <c r="O117" s="4"/>
     </row>
     <row r="118" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="3">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>242</v>
+        <v>25</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>243</v>
+        <v>297</v>
       </c>
       <c r="D118" s="4" t="s">
         <v>298</v>
       </c>
       <c r="E118" s="3">
-        <v>46297</v>
+        <v>46293</v>
       </c>
       <c r="F118" s="5">
-        <v>11660.11</v>
+        <v>1664</v>
       </c>
       <c r="G118" s="5">
-        <v>11660.11</v>
+        <v>1664</v>
       </c>
       <c r="H118" s="3"/>
       <c r="I118" s="6">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J118" s="4" t="s">
-        <v>170</v>
+        <v>18</v>
       </c>
       <c r="K118" s="4" t="s">
-        <v>245</v>
+        <v>71</v>
       </c>
       <c r="L118" s="4"/>
       <c r="M118" s="4" t="s">
@@ -5971,29 +6004,29 @@
     </row>
     <row r="119" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="3">
-        <v>46237</v>
+        <v>46265</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>166</v>
+        <v>297</v>
       </c>
       <c r="D119" s="4" t="s">
         <v>300</v>
       </c>
       <c r="E119" s="3">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="F119" s="5">
-        <v>2930.4</v>
+        <v>1664</v>
       </c>
       <c r="G119" s="5">
-        <v>2930.4</v>
+        <v>1664</v>
       </c>
       <c r="H119" s="3"/>
       <c r="I119" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J119" s="4" t="s">
         <v>18</v>
@@ -6010,42 +6043,198 @@
     </row>
     <row r="120" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="3">
-        <v>46252</v>
+        <v>46266</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>23</v>
+        <v>302</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>166</v>
+        <v>303</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="E120" s="3">
-        <v>46297</v>
+        <v>46296</v>
       </c>
       <c r="F120" s="5">
-        <v>3809.52</v>
+        <v>8973.5</v>
       </c>
       <c r="G120" s="5">
-        <v>3809.52</v>
+        <v>8973.5</v>
       </c>
       <c r="H120" s="3"/>
       <c r="I120" s="6">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J120" s="4" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="K120" s="4" t="s">
-        <v>71</v>
+        <v>305</v>
       </c>
       <c r="L120" s="4"/>
       <c r="M120" s="4" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="N120" s="4"/>
       <c r="O120" s="4"/>
+    </row>
+    <row r="121" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="3">
+        <v>46266</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C121" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="D121" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="E121" s="3">
+        <v>46287</v>
+      </c>
+      <c r="F121" s="5">
+        <v>18600</v>
+      </c>
+      <c r="G121" s="5">
+        <v>18600</v>
+      </c>
+      <c r="H121" s="3"/>
+      <c r="I121" s="6">
+        <v>15</v>
+      </c>
+      <c r="J121" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K121" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="L121" s="4"/>
+      <c r="M121" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="N121" s="4"/>
+      <c r="O121" s="4"/>
+    </row>
+    <row r="122" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="3">
+        <v>46266</v>
+      </c>
+      <c r="B122" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C122" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="D122" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="E122" s="3">
+        <v>46294</v>
+      </c>
+      <c r="F122" s="5">
+        <v>18600</v>
+      </c>
+      <c r="G122" s="5">
+        <v>18600</v>
+      </c>
+      <c r="H122" s="3"/>
+      <c r="I122" s="6">
+        <v>8</v>
+      </c>
+      <c r="J122" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K122" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="L122" s="4"/>
+      <c r="M122" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="N122" s="4"/>
+      <c r="O122" s="4"/>
+    </row>
+    <row r="123" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="3">
+        <v>46266</v>
+      </c>
+      <c r="B123" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C123" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="D123" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="E123" s="3">
+        <v>46301</v>
+      </c>
+      <c r="F123" s="5">
+        <v>18600</v>
+      </c>
+      <c r="G123" s="5">
+        <v>18600</v>
+      </c>
+      <c r="H123" s="3"/>
+      <c r="I123" s="6">
+        <v>1</v>
+      </c>
+      <c r="J123" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K123" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="L123" s="4"/>
+      <c r="M123" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="N123" s="4"/>
+      <c r="O123" s="4"/>
+    </row>
+    <row r="124" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="3">
+        <v>46268</v>
+      </c>
+      <c r="B124" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C124" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="D124" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="E124" s="3">
+        <v>46296</v>
+      </c>
+      <c r="F124" s="5">
+        <v>2754</v>
+      </c>
+      <c r="G124" s="5">
+        <v>2754</v>
+      </c>
+      <c r="H124" s="3"/>
+      <c r="I124" s="6">
+        <v>6</v>
+      </c>
+      <c r="J124" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="K124" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="L124" s="4"/>
+      <c r="M124" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="N124" s="4"/>
+      <c r="O124" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
+++ b/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WINDOWS\Desktop\dados planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCB00894-F262-41B6-847D-BFC8EF7D0DBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49654609-7B74-4183-ADC7-B85F903F133F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="299">
   <si>
     <t>Dt.Emissão</t>
   </si>
@@ -96,36 +96,36 @@
     <t>34194963600005418001090001019738120992717000</t>
   </si>
   <si>
+    <t>MARCELO LOPES</t>
+  </si>
+  <si>
+    <t>FAROMED COMERCIO DE MATERIAIS HOSPITALARES LTDA</t>
+  </si>
+  <si>
+    <t>01001617.1</t>
+  </si>
+  <si>
+    <t>BANCO DO BRASIL</t>
+  </si>
+  <si>
+    <t>PE</t>
+  </si>
+  <si>
+    <t>00191964000001264870000003473568000002622117</t>
+  </si>
+  <si>
     <t>01001504.4</t>
   </si>
   <si>
     <t>34194964600005418001090001019818120992717000</t>
   </si>
   <si>
-    <t>MARCELO LOPES</t>
-  </si>
-  <si>
-    <t>FAROMED COMERCIO DE MATERIAIS HOSPITALARES LTDA</t>
-  </si>
-  <si>
     <t>01001548.3</t>
   </si>
   <si>
-    <t>BANCO DO BRASIL</t>
-  </si>
-  <si>
-    <t>PE</t>
-  </si>
-  <si>
     <t>00193965200000384000000003473568000002617517</t>
   </si>
   <si>
-    <t>01001617.1</t>
-  </si>
-  <si>
-    <t>00191964000001264870000003473568000002622117</t>
-  </si>
-  <si>
     <t>01001617.2</t>
   </si>
   <si>
@@ -168,22 +168,61 @@
     <t>GLOBAL MEDIC LTDA</t>
   </si>
   <si>
+    <t>01003029.2</t>
+  </si>
+  <si>
+    <t>34195989000002000001090001238528120992717000</t>
+  </si>
+  <si>
+    <t>01003029.1</t>
+  </si>
+  <si>
+    <t>34197987600003204341090001238458120992717000</t>
+  </si>
+  <si>
+    <t>MOISES</t>
+  </si>
+  <si>
+    <t>AC FL FARMACIA E DROGARIA LTDA</t>
+  </si>
+  <si>
+    <t>01002991.3</t>
+  </si>
+  <si>
+    <t>BA</t>
+  </si>
+  <si>
+    <t>34196989800004439901090001240908120992717000</t>
+  </si>
+  <si>
+    <t>01003029.3</t>
+  </si>
+  <si>
+    <t>34195990400002000001090001238608120992717000</t>
+  </si>
+  <si>
     <t>01002938.2</t>
   </si>
   <si>
     <t>34194986400001216861090001218808120992717000</t>
   </si>
   <si>
+    <t>01002951.2</t>
+  </si>
+  <si>
+    <t>34193985900001843871090001228138120992717000</t>
+  </si>
+  <si>
     <t>01002938.3</t>
   </si>
   <si>
     <t>34192987800001216861090001218988120992717000</t>
   </si>
   <si>
-    <t>01002951.2</t>
-  </si>
-  <si>
-    <t>34193985900001843871090001228138120992717000</t>
+    <t>01002991.4</t>
+  </si>
+  <si>
+    <t>34197991200004439901090001241088120992717000</t>
   </si>
   <si>
     <t>01002951.3</t>
@@ -192,45 +231,6 @@
     <t>34194986600001843881090001228218120992717000</t>
   </si>
   <si>
-    <t>MOISES</t>
-  </si>
-  <si>
-    <t>AC FL FARMACIA E DROGARIA LTDA</t>
-  </si>
-  <si>
-    <t>01002991.3</t>
-  </si>
-  <si>
-    <t>BA</t>
-  </si>
-  <si>
-    <t>34196989800004439901090001240908120992717000</t>
-  </si>
-  <si>
-    <t>01002991.4</t>
-  </si>
-  <si>
-    <t>34197991200004439901090001241088120992717000</t>
-  </si>
-  <si>
-    <t>01003029.1</t>
-  </si>
-  <si>
-    <t>34197987600003204341090001238458120992717000</t>
-  </si>
-  <si>
-    <t>01003029.2</t>
-  </si>
-  <si>
-    <t>34195989000002000001090001238528120992717000</t>
-  </si>
-  <si>
-    <t>01003029.3</t>
-  </si>
-  <si>
-    <t>34195990400002000001090001238608120992717000</t>
-  </si>
-  <si>
     <t>SERGIO ROBERTO - PB</t>
   </si>
   <si>
@@ -249,39 +249,39 @@
     <t xml:space="preserve">RN COMERCIO DE MEDICAMENTOS E MATERIAL HOSPITALAR </t>
   </si>
   <si>
+    <t>01003464.4</t>
+  </si>
+  <si>
+    <t>RN</t>
+  </si>
+  <si>
+    <t>34194998500003296801090001307668120992717000</t>
+  </si>
+  <si>
     <t>01003409.6</t>
   </si>
   <si>
-    <t>RN</t>
-  </si>
-  <si>
     <t>34199998900002330001090001290998120992717000</t>
   </si>
   <si>
-    <t>01003464.4</t>
-  </si>
-  <si>
-    <t>34194998500003296801090001307668120992717000</t>
-  </si>
-  <si>
     <t>01003464.5</t>
   </si>
   <si>
     <t>34198999200003296801090001307748120992717000</t>
   </si>
   <si>
+    <t>01003504.1</t>
+  </si>
+  <si>
+    <t>00191999500002541000000003473568000002851217</t>
+  </si>
+  <si>
     <t>01003464.6</t>
   </si>
   <si>
     <t>34191999900003296801090001307828120992717000</t>
   </si>
   <si>
-    <t>01003504.1</t>
-  </si>
-  <si>
-    <t>00191999500002541000000003473568000002851217</t>
-  </si>
-  <si>
     <t>01003504.2</t>
   </si>
   <si>
@@ -294,57 +294,57 @@
     <t>00194101600002541000000003473568000002851517</t>
   </si>
   <si>
+    <t>01003589.1</t>
+  </si>
+  <si>
+    <t>34197101700007562781090001319968120992717000</t>
+  </si>
+  <si>
+    <t>01003589.2</t>
+  </si>
+  <si>
+    <t>34198102400007562781090001320028120992717000</t>
+  </si>
+  <si>
+    <t>MED-K COMERCIO LTDA</t>
+  </si>
+  <si>
+    <t>01003592.2</t>
+  </si>
+  <si>
+    <t>34194102400001154561090001320448120992717000</t>
+  </si>
+  <si>
     <t>01003504.6</t>
   </si>
   <si>
     <t>00193103000002541000000003473568000002851717</t>
   </si>
   <si>
-    <t>01003589.1</t>
-  </si>
-  <si>
-    <t>34197101700007562781090001319968120992717000</t>
-  </si>
-  <si>
-    <t>01003589.2</t>
-  </si>
-  <si>
-    <t>34198102400007562781090001320028120992717000</t>
-  </si>
-  <si>
     <t>01003589.3</t>
   </si>
   <si>
     <t>34191103100007562781090001320108120992717000</t>
   </si>
   <si>
+    <t>01003592.3</t>
+  </si>
+  <si>
+    <t>34194103100001154561090001320518120992717000</t>
+  </si>
+  <si>
+    <t>01003592.4</t>
+  </si>
+  <si>
+    <t>34194103800001154561090001320698120992717000</t>
+  </si>
+  <si>
     <t>01003589.4</t>
   </si>
   <si>
     <t>34197103800007562761090001320288120992717000</t>
   </si>
   <si>
-    <t>MED-K COMERCIO LTDA</t>
-  </si>
-  <si>
-    <t>01003592.2</t>
-  </si>
-  <si>
-    <t>34194102400001154561090001320448120992717000</t>
-  </si>
-  <si>
-    <t>01003592.3</t>
-  </si>
-  <si>
-    <t>34194103100001154561090001320518120992717000</t>
-  </si>
-  <si>
-    <t>01003592.4</t>
-  </si>
-  <si>
-    <t>34194103800001154561090001320698120992717000</t>
-  </si>
-  <si>
     <t>01003592.5</t>
   </si>
   <si>
@@ -462,6 +462,12 @@
     <t>00191125800002144590000003473568000002964317</t>
   </si>
   <si>
+    <t>PHARMACEUTICA DISTRIBUIDORA DE MAT. E MED. HOSPITA</t>
+  </si>
+  <si>
+    <t>01005217.1BPBPBPBP</t>
+  </si>
+  <si>
     <t>BR MEDICAMENTOS LTDA</t>
   </si>
   <si>
@@ -471,21 +477,36 @@
     <t>00195127000004480000000003473568000002981317</t>
   </si>
   <si>
+    <t>01005217.2BP</t>
+  </si>
+  <si>
     <t>01005144.3</t>
   </si>
   <si>
-    <t>PHARMACEUTICA DISTRIBUIDORA DE MAT. E MED. HOSPITA</t>
-  </si>
-  <si>
-    <t>01005217.1BPBPBPBP</t>
-  </si>
-  <si>
-    <t>01005217.2BP</t>
-  </si>
-  <si>
     <t>01005217.3BPBPBP</t>
   </si>
   <si>
+    <t>DENTAL SORRISO LTDA</t>
+  </si>
+  <si>
+    <t>01005781.1</t>
+  </si>
+  <si>
+    <t>00194138000000806340000003473568000003029417</t>
+  </si>
+  <si>
+    <t>01005781.2</t>
+  </si>
+  <si>
+    <t>00194138700000503280000003473568000003029517</t>
+  </si>
+  <si>
+    <t>01005781.3</t>
+  </si>
+  <si>
+    <t>00199139400000503280000003473568000003029617</t>
+  </si>
+  <si>
     <t>MAIS SAUDE COMERCIO DE PRODUTOS HOSPITALARES LTDA</t>
   </si>
   <si>
@@ -495,43 +516,19 @@
     <t>34199139500005466661090002533378120992717000</t>
   </si>
   <si>
-    <t>DENTAL SORRISO LTDA</t>
-  </si>
-  <si>
-    <t>01005781.1</t>
-  </si>
-  <si>
-    <t>00194138000000806340000003473568000003029417</t>
-  </si>
-  <si>
-    <t>01005781.2</t>
-  </si>
-  <si>
-    <t>00194138700000503280000003473568000003029517</t>
-  </si>
-  <si>
-    <t>01005781.3</t>
-  </si>
-  <si>
-    <t>00199139400000503280000003473568000003029617</t>
+    <t>01006508.1</t>
+  </si>
+  <si>
+    <t>01006508.2</t>
+  </si>
+  <si>
+    <t>01006508.3</t>
   </si>
   <si>
     <t>GRADUAL COMERCIO E SERVICOS LTDA</t>
   </si>
   <si>
-    <t>01006433.3</t>
-  </si>
-  <si>
-    <t>34193151200031531501090002588728120992717000</t>
-  </si>
-  <si>
-    <t>01006508.1</t>
-  </si>
-  <si>
-    <t>01006508.2</t>
-  </si>
-  <si>
-    <t>01006508.3</t>
+    <t>01006433.3BP</t>
   </si>
   <si>
     <t>MARCOS DUTRA - PI</t>
@@ -549,40 +546,328 @@
     <t>00197154900000860000000003473568000003129017</t>
   </si>
   <si>
+    <t>01006941.2</t>
+  </si>
+  <si>
+    <t>00195154900002818370000003473568000003141117</t>
+  </si>
+  <si>
+    <t>JT COSTA COMERCIAL LTDA</t>
+  </si>
+  <si>
+    <t>01007005.1</t>
+  </si>
+  <si>
+    <t>00197155200018957860000003473568000003145817</t>
+  </si>
+  <si>
+    <t>ALINE CERBINO - PA</t>
+  </si>
+  <si>
+    <t>CRISTALFARMA COMERCIO IMPORT E EXPORT LTDA</t>
+  </si>
+  <si>
+    <t>01006920.1</t>
+  </si>
+  <si>
+    <t>DAYCOVAL</t>
+  </si>
+  <si>
+    <t>PA</t>
+  </si>
+  <si>
+    <t>70797156000011442870001121205064100656763979</t>
+  </si>
+  <si>
+    <t>01007005.2</t>
+  </si>
+  <si>
+    <t>00193156200009716000000003473568000003145917</t>
+  </si>
+  <si>
+    <t>01006976.1</t>
+  </si>
+  <si>
+    <t>BRADESCO</t>
+  </si>
+  <si>
+    <t>23791156200006389240435090000000114600304920</t>
+  </si>
+  <si>
+    <t>01006941.4</t>
+  </si>
+  <si>
+    <t>00194156300002818370000003473568000003141317</t>
+  </si>
+  <si>
+    <t>PLENA DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>01006922.1</t>
+  </si>
+  <si>
+    <t>70795156300011200000001121205064100656763870</t>
+  </si>
+  <si>
+    <t>CIRURGICA MONTEBELLO LTDA</t>
+  </si>
+  <si>
+    <t>01007187.1</t>
+  </si>
+  <si>
+    <t>70791156400010080000001121205064100656766188</t>
+  </si>
+  <si>
+    <t>01006958.5</t>
+  </si>
+  <si>
+    <t>70799156600023168600001121205064100656764084</t>
+  </si>
+  <si>
+    <t>01007023.1</t>
+  </si>
+  <si>
+    <t>70799156900005741360001121205064100656764415</t>
+  </si>
+  <si>
+    <t>01006941.5</t>
+  </si>
+  <si>
+    <t>00191157000002818360000003473568000003141417</t>
+  </si>
+  <si>
+    <t>01007187.2</t>
+  </si>
+  <si>
+    <t>70791157100010080000001121205064100656766196</t>
+  </si>
+  <si>
+    <t>01007005.3</t>
+  </si>
+  <si>
+    <t>00196157200009716000000003473568000003146017</t>
+  </si>
+  <si>
+    <t>01006958.6</t>
+  </si>
+  <si>
+    <t>70798157300023168600001121205064100656764092</t>
+  </si>
+  <si>
+    <t>01006922.2</t>
+  </si>
+  <si>
+    <t>70792157300011200000001121205064100656763888</t>
+  </si>
+  <si>
+    <t>01006957.2</t>
+  </si>
+  <si>
+    <t>70792157400010666670001121205064100656763953</t>
+  </si>
+  <si>
+    <t>01006999.1</t>
+  </si>
+  <si>
+    <t>70799157400006500000001121205064100656764282</t>
+  </si>
+  <si>
+    <t>01007020.1</t>
+  </si>
+  <si>
+    <t>70799157400004950170001121205064100656764449</t>
+  </si>
+  <si>
+    <t>01006920.2</t>
+  </si>
+  <si>
+    <t>70794157500007551880001121205064100656763987</t>
+  </si>
+  <si>
+    <t>01007125.4</t>
+  </si>
+  <si>
+    <t>70791157600004320000001121205064100656765123</t>
+  </si>
+  <si>
+    <t>01007301.1</t>
+  </si>
+  <si>
+    <t>00192157700018600000000003473568000003161317</t>
+  </si>
+  <si>
+    <t>01006976.2</t>
+  </si>
+  <si>
+    <t>23791157700004216670435090000000114700304920</t>
+  </si>
+  <si>
+    <t>01007187.3</t>
+  </si>
+  <si>
+    <t>70793157800010080000001121205064100656766204</t>
+  </si>
+  <si>
+    <t>DROGUISTA CEARENSE LTDA</t>
+  </si>
+  <si>
+    <t>01007175.2</t>
+  </si>
+  <si>
+    <t>34193157800001660331090002618768120992717000</t>
+  </si>
+  <si>
+    <t>01007171.2</t>
+  </si>
+  <si>
+    <t>70794157800003640000001121205064100656766162</t>
+  </si>
+  <si>
     <t>COBERMED COMERCIO DE MATERIAIS MEDICOS LTDA</t>
   </si>
   <si>
+    <t>01007194.1</t>
+  </si>
+  <si>
+    <t>70797157900006265000001121205064100656766642</t>
+  </si>
+  <si>
+    <t>FELIPE AQUINO - MT</t>
+  </si>
+  <si>
+    <t>FAMA DISTRIBUIDORA HOSPITALAR LTDA</t>
+  </si>
+  <si>
+    <t>01007265.1</t>
+  </si>
+  <si>
+    <t>MT</t>
+  </si>
+  <si>
+    <t>00198158000007694400000003473568000003158817</t>
+  </si>
+  <si>
+    <t>01007249.1</t>
+  </si>
+  <si>
+    <t>70793158000011660110001121205064100656766915</t>
+  </si>
+  <si>
+    <t>FERMATA LTDA</t>
+  </si>
+  <si>
+    <t>01006989.2</t>
+  </si>
+  <si>
+    <t>70795158200004082050001121205064100656764191</t>
+  </si>
+  <si>
+    <t>01007005.4</t>
+  </si>
+  <si>
+    <t>00197158200009716000000003473568000003146117</t>
+  </si>
+  <si>
     <t>01006877.3</t>
   </si>
   <si>
-    <t>BRADESCO</t>
-  </si>
-  <si>
     <t>23797158300006265000435090000000110700304920</t>
   </si>
   <si>
-    <t>ALINE CERBINO - PA</t>
-  </si>
-  <si>
-    <t>CRISTALFARMA COMERCIO IMPORT E EXPORT LTDA</t>
-  </si>
-  <si>
-    <t>01006920.1</t>
-  </si>
-  <si>
-    <t>DAYCOVAL</t>
-  </si>
-  <si>
-    <t>PA</t>
-  </si>
-  <si>
-    <t>70797156000011442870001121205064100656763979</t>
-  </si>
-  <si>
-    <t>01006920.2</t>
-  </si>
-  <si>
-    <t>70794157500007551880001121205064100656763987</t>
+    <t>01007125.5</t>
+  </si>
+  <si>
+    <t>70799158300004320000001121205064100656765131</t>
+  </si>
+  <si>
+    <t>01006922.3</t>
+  </si>
+  <si>
+    <t>70798158300011200000001121205064100656763896</t>
+  </si>
+  <si>
+    <t>01007301.2</t>
+  </si>
+  <si>
+    <t>00197158400018600000000003473568000003161417</t>
+  </si>
+  <si>
+    <t>01007023.2</t>
+  </si>
+  <si>
+    <t>70791158400003789090001121205064100656764423</t>
+  </si>
+  <si>
+    <t>01007187.4</t>
+  </si>
+  <si>
+    <t>70792158500010080000001121205064100656766212</t>
+  </si>
+  <si>
+    <t>01007171.3</t>
+  </si>
+  <si>
+    <t>70793158500003640000001121205064100656766170</t>
+  </si>
+  <si>
+    <t>01007175.3</t>
+  </si>
+  <si>
+    <t>34194158500001660341090002618848120992717000</t>
+  </si>
+  <si>
+    <t>VITAL DISTRIBUIDORA LTDA</t>
+  </si>
+  <si>
+    <t>01007168.3</t>
+  </si>
+  <si>
+    <t>34196158500002051221090002617698120992717000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZOE MED COMERCIO DE PRODUTOS MEDICOS HOSPITALARES </t>
+  </si>
+  <si>
+    <t>01007270.1</t>
+  </si>
+  <si>
+    <t>70793158500008565680001121205064100656766972</t>
+  </si>
+  <si>
+    <t>ATACAMED COMERCIO LTDA</t>
+  </si>
+  <si>
+    <t>01007311.1</t>
+  </si>
+  <si>
+    <t>23796158600002754000435090000000130000304920</t>
+  </si>
+  <si>
+    <t>ELIENE RESENDE - RJ</t>
+  </si>
+  <si>
+    <t>MEDKA DISTRIBUIDORA HOSPITALAR LTDA</t>
+  </si>
+  <si>
+    <t>01007278.1</t>
+  </si>
+  <si>
+    <t>RJ</t>
+  </si>
+  <si>
+    <t>70793158600008973500001121205064100656767319</t>
+  </si>
+  <si>
+    <t>01007249.2</t>
+  </si>
+  <si>
+    <t>70792158700011660110001121205064100656766923</t>
+  </si>
+  <si>
+    <t>01007265.2</t>
+  </si>
+  <si>
+    <t>00192158700007694400000003473568000003158917</t>
   </si>
   <si>
     <t>01006920.3</t>
@@ -591,385 +876,52 @@
     <t>70797159000007551880001121205064100656763995</t>
   </si>
   <si>
-    <t>PLENA DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>01006922.1</t>
-  </si>
-  <si>
-    <t>70795156300011200000001121205064100656763870</t>
-  </si>
-  <si>
-    <t>01006922.2</t>
-  </si>
-  <si>
-    <t>70792157300011200000001121205064100656763888</t>
-  </si>
-  <si>
-    <t>01006922.3</t>
-  </si>
-  <si>
-    <t>70798158300011200000001121205064100656763896</t>
-  </si>
-  <si>
-    <t>01006941.2</t>
-  </si>
-  <si>
-    <t>00195154900002818370000003473568000003141117</t>
-  </si>
-  <si>
-    <t>01006941.4</t>
-  </si>
-  <si>
-    <t>00194156300002818370000003473568000003141317</t>
-  </si>
-  <si>
-    <t>01006941.5</t>
-  </si>
-  <si>
-    <t>00191157000002818360000003473568000003141417</t>
-  </si>
-  <si>
-    <t>01006957.2</t>
-  </si>
-  <si>
-    <t>70792157400010666670001121205064100656763953</t>
-  </si>
-  <si>
-    <t>CIRURGICA MONTEBELLO LTDA</t>
-  </si>
-  <si>
-    <t>01006958.5</t>
-  </si>
-  <si>
-    <t>70799156600023168600001121205064100656764084</t>
-  </si>
-  <si>
-    <t>01006958.6</t>
-  </si>
-  <si>
-    <t>70798157300023168600001121205064100656764092</t>
-  </si>
-  <si>
-    <t>01006976.1</t>
-  </si>
-  <si>
-    <t>23791156200006389240435090000000114600304920</t>
-  </si>
-  <si>
-    <t>01006976.2</t>
-  </si>
-  <si>
-    <t>23791157700004216670435090000000114700304920</t>
-  </si>
-  <si>
-    <t>FERMATA LTDA</t>
-  </si>
-  <si>
-    <t>01006989.2</t>
-  </si>
-  <si>
-    <t>70795158200004082050001121205064100656764191</t>
-  </si>
-  <si>
-    <t>01006999.1</t>
-  </si>
-  <si>
-    <t>70799157400006500000001121205064100656764282</t>
-  </si>
-  <si>
-    <t>JT COSTA COMERCIAL LTDA</t>
-  </si>
-  <si>
-    <t>01007005.1</t>
-  </si>
-  <si>
-    <t>00197155200018957860000003473568000003145817</t>
-  </si>
-  <si>
-    <t>01007005.2</t>
-  </si>
-  <si>
-    <t>00193156200009716000000003473568000003145917</t>
-  </si>
-  <si>
-    <t>01007005.3</t>
-  </si>
-  <si>
-    <t>00196157200009716000000003473568000003146017</t>
-  </si>
-  <si>
-    <t>01007005.4</t>
-  </si>
-  <si>
-    <t>00197158200009716000000003473568000003146117</t>
-  </si>
-  <si>
-    <t>01007020.1</t>
-  </si>
-  <si>
-    <t>70799157400004950170001121205064100656764449</t>
-  </si>
-  <si>
-    <t>01007023.1</t>
-  </si>
-  <si>
-    <t>70799156900005741360001121205064100656764415</t>
-  </si>
-  <si>
-    <t>01007023.2</t>
-  </si>
-  <si>
-    <t>70791158400003789090001121205064100656764423</t>
-  </si>
-  <si>
-    <t>01007074.3</t>
-  </si>
-  <si>
-    <t>34192158700002930401090002611578120992717000</t>
-  </si>
-  <si>
-    <t>LICIMASTER DIST. DE MED. E PRODUTOS MEDICO</t>
-  </si>
-  <si>
-    <t>01007094.4</t>
-  </si>
-  <si>
-    <t>34191158300003599851090002612318120992717000</t>
-  </si>
-  <si>
-    <t>AMAZONIA HOSPITALAR LTDA</t>
-  </si>
-  <si>
-    <t>01007105.4</t>
-  </si>
-  <si>
-    <t>MA</t>
-  </si>
-  <si>
-    <t>00191159100005443560000003473568000003155017</t>
-  </si>
-  <si>
-    <t>ASPEN SERVICE COMERCIO LTDA</t>
-  </si>
-  <si>
-    <t>01007117.1</t>
-  </si>
-  <si>
-    <t>70791158300023355330001121205064100656765669</t>
-  </si>
-  <si>
-    <t>01007125.4</t>
-  </si>
-  <si>
-    <t>70791157600004320000001121205064100656765123</t>
-  </si>
-  <si>
-    <t>01007125.5</t>
-  </si>
-  <si>
-    <t>70799158300004320000001121205064100656765131</t>
-  </si>
-  <si>
-    <t>HOSPMED LTDA</t>
-  </si>
-  <si>
-    <t>01007129.5</t>
-  </si>
-  <si>
-    <t>70791159100001840960001121205064100656765180</t>
-  </si>
-  <si>
-    <t>VITAL DISTRIBUIDORA LTDA</t>
-  </si>
-  <si>
-    <t>01007168.3</t>
-  </si>
-  <si>
-    <t>34196158500002051221090002617698120992717000</t>
-  </si>
-  <si>
-    <t>01007169.2</t>
-  </si>
-  <si>
-    <t>70797158700003809520001121205064100656765974</t>
-  </si>
-  <si>
-    <t>DROGUISTA CEARENSE LTDA</t>
-  </si>
-  <si>
-    <t>01007171.2</t>
-  </si>
-  <si>
-    <t>70794157800003640000001121205064100656766162</t>
-  </si>
-  <si>
-    <t>01007171.3</t>
-  </si>
-  <si>
-    <t>70793158500003640000001121205064100656766170</t>
-  </si>
-  <si>
-    <t>01007175.2</t>
-  </si>
-  <si>
-    <t>34193157800001660331090002618768120992717000</t>
-  </si>
-  <si>
-    <t>01007175.3</t>
-  </si>
-  <si>
-    <t>34194158500001660341090002618848120992717000</t>
-  </si>
-  <si>
-    <t>01007187.1</t>
-  </si>
-  <si>
-    <t>70791156400010080000001121205064100656766188</t>
-  </si>
-  <si>
-    <t>01007187.2</t>
-  </si>
-  <si>
-    <t>70791157100010080000001121205064100656766196</t>
-  </si>
-  <si>
-    <t>01007187.3</t>
-  </si>
-  <si>
-    <t>70793157800010080000001121205064100656766204</t>
-  </si>
-  <si>
-    <t>01007187.4</t>
-  </si>
-  <si>
-    <t>70792158500010080000001121205064100656766212</t>
-  </si>
-  <si>
-    <t>01007194.1</t>
-  </si>
-  <si>
-    <t>70797157900006265000001121205064100656766642</t>
-  </si>
-  <si>
-    <t>01007197.2</t>
-  </si>
-  <si>
-    <t>23791158800001172160435090000000124700304920</t>
-  </si>
-  <si>
-    <t>01007215.2</t>
-  </si>
-  <si>
-    <t>70791159100003979060001121205064100656767418</t>
-  </si>
-  <si>
-    <t>01007221.2</t>
-  </si>
-  <si>
-    <t>23796159100001286250435090000000129500304920</t>
-  </si>
-  <si>
-    <t>FELIPE AQUINO - MT</t>
-  </si>
-  <si>
-    <t>FAMA DISTRIBUIDORA HOSPITALAR LTDA</t>
-  </si>
-  <si>
-    <t>01007249.1</t>
-  </si>
-  <si>
-    <t>MT</t>
-  </si>
-  <si>
-    <t>70793158000011660110001121205064100656766915</t>
-  </si>
-  <si>
-    <t>01007249.2</t>
-  </si>
-  <si>
-    <t>70792158700011660110001121205064100656766923</t>
-  </si>
-  <si>
-    <t>01007265.1</t>
-  </si>
-  <si>
-    <t>00198158000007694400000003473568000003158817</t>
-  </si>
-  <si>
-    <t>01007265.2</t>
-  </si>
-  <si>
-    <t>00192158700007694400000003473568000003158917</t>
-  </si>
-  <si>
-    <t>01007269.1</t>
-  </si>
-  <si>
-    <t>70791158500008947500001121205064100656767137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZOE MED COMERCIO DE PRODUTOS MEDICOS HOSPITALARES </t>
-  </si>
-  <si>
-    <t>01007270.1</t>
-  </si>
-  <si>
-    <t>70793158500008565680001121205064100656766972</t>
-  </si>
-  <si>
-    <t>ATACAMED COMERCIO LTDA</t>
-  </si>
-  <si>
-    <t>01007274.1</t>
-  </si>
-  <si>
-    <t>34192158300001664001090002623468120992717000</t>
-  </si>
-  <si>
     <t>01007274.2</t>
   </si>
   <si>
     <t>34192159000001664001090002623538120992717000</t>
   </si>
   <si>
-    <t>ELIENE RESENDE - RJ</t>
-  </si>
-  <si>
-    <t>MEDKA DISTRIBUIDORA HOSPITALAR LTDA</t>
-  </si>
-  <si>
-    <t>01007278.1</t>
-  </si>
-  <si>
-    <t>RJ</t>
-  </si>
-  <si>
-    <t>70793158600008973500001121205064100656767319</t>
-  </si>
-  <si>
-    <t>01007301.1</t>
-  </si>
-  <si>
-    <t>00192157700018600000000003473568000003161317</t>
-  </si>
-  <si>
-    <t>01007301.2</t>
-  </si>
-  <si>
-    <t>00197158400018600000000003473568000003161417</t>
-  </si>
-  <si>
     <t>01007301.3</t>
   </si>
   <si>
     <t>00191159100018600000000003473568000003161517</t>
   </si>
   <si>
-    <t>01007311.1</t>
-  </si>
-  <si>
-    <t>23796158600002754000435090000000130000304920</t>
+    <t>01006976.3</t>
+  </si>
+  <si>
+    <t>23792159200004216660435090000000114800304920</t>
+  </si>
+  <si>
+    <t>01007005.5</t>
+  </si>
+  <si>
+    <t>00198159200009716000000003473568000003146217</t>
+  </si>
+  <si>
+    <t>01007187.5</t>
+  </si>
+  <si>
+    <t>70791159200010080000001121205064100656766220</t>
+  </si>
+  <si>
+    <t>01007175.1</t>
+  </si>
+  <si>
+    <t>34194159200001660331090002618688120992717000</t>
+  </si>
+  <si>
+    <t>01007171.1</t>
+  </si>
+  <si>
+    <t>70791159200003640000001121205064100656766154</t>
+  </si>
+  <si>
+    <t>01007311.2</t>
+  </si>
+  <si>
+    <t>23792159300002754000435090000000130100304920</t>
   </si>
 </sst>
 </file>
@@ -1399,7 +1351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O124"/>
+  <dimension ref="A1:O119"/>
   <sheetFormatPr defaultColWidth="12.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.85546875" style="1" customWidth="1"/>
@@ -1491,7 +1443,7 @@
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="6">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>18</v>
@@ -1530,7 +1482,7 @@
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="6">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>18</v>
@@ -1547,74 +1499,74 @@
     </row>
     <row r="4" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
-        <v>45296</v>
+        <v>45322</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E4" s="3">
-        <v>45356</v>
+        <v>45350</v>
       </c>
       <c r="F4" s="5">
-        <v>5418</v>
+        <v>816</v>
       </c>
       <c r="G4" s="5">
-        <v>5418</v>
+        <v>1264.8699999999999</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="6">
-        <v>946</v>
+        <v>954</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="L4" s="4"/>
       <c r="M4" s="4" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
     </row>
     <row r="5" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
-        <v>45306</v>
+        <v>45296</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E5" s="3">
-        <v>45362</v>
+        <v>45356</v>
       </c>
       <c r="F5" s="5">
-        <v>384</v>
+        <v>5418</v>
       </c>
       <c r="G5" s="5">
-        <v>384</v>
+        <v>5418</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="6">
-        <v>940</v>
+        <v>948</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="L5" s="4"/>
       <c r="M5" s="4" t="s">
@@ -1625,35 +1577,35 @@
     </row>
     <row r="6" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
-        <v>45322</v>
+        <v>45306</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E6" s="3">
-        <v>45350</v>
+        <v>45362</v>
       </c>
       <c r="F6" s="5">
-        <v>816</v>
+        <v>384</v>
       </c>
       <c r="G6" s="5">
-        <v>1264.8699999999999</v>
+        <v>384</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="6">
-        <v>952</v>
+        <v>942</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L6" s="4"/>
       <c r="M6" s="4" t="s">
@@ -1667,10 +1619,10 @@
         <v>45322</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>33</v>
@@ -1686,13 +1638,13 @@
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="6">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L7" s="4"/>
       <c r="M7" s="4" t="s">
@@ -1706,10 +1658,10 @@
         <v>45322</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>35</v>
@@ -1725,13 +1677,13 @@
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="6">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L8" s="4"/>
       <c r="M8" s="4" t="s">
@@ -1764,7 +1716,7 @@
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="6">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>18</v>
@@ -1803,7 +1755,7 @@
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="6">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>18</v>
@@ -1842,7 +1794,7 @@
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="6">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>18</v>
@@ -1859,7 +1811,7 @@
     </row>
     <row r="12" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
-        <v>45546</v>
+        <v>45558</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>45</v>
@@ -1871,23 +1823,23 @@
         <v>47</v>
       </c>
       <c r="E12" s="3">
-        <v>45615</v>
+        <v>45600</v>
       </c>
       <c r="F12" s="5">
-        <v>1216.8599999999999</v>
+        <v>2000</v>
       </c>
       <c r="G12" s="5">
-        <v>1216.8599999999999</v>
+        <v>2000</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="6">
-        <v>687</v>
+        <v>704</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>18</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L12" s="4"/>
       <c r="M12" s="4" t="s">
@@ -1898,7 +1850,7 @@
     </row>
     <row r="13" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
-        <v>45546</v>
+        <v>45558</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>45</v>
@@ -1910,23 +1862,23 @@
         <v>49</v>
       </c>
       <c r="E13" s="3">
-        <v>45622</v>
+        <v>45607</v>
       </c>
       <c r="F13" s="5">
-        <v>1216.8599999999999</v>
+        <v>2000</v>
       </c>
       <c r="G13" s="5">
-        <v>1216.8599999999999</v>
+        <v>3204.34</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="6">
-        <v>680</v>
+        <v>697</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>18</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L13" s="4"/>
       <c r="M13" s="4" t="s">
@@ -1937,46 +1889,46 @@
     </row>
     <row r="14" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
-        <v>45548</v>
+        <v>45552</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E14" s="3">
-        <v>45617</v>
+        <v>45608</v>
       </c>
       <c r="F14" s="5">
-        <v>1843.87</v>
+        <v>4439.8999999999996</v>
       </c>
       <c r="G14" s="5">
-        <v>1843.87</v>
+        <v>4439.8999999999996</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="6">
-        <v>685</v>
+        <v>696</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>18</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="L14" s="4"/>
       <c r="M14" s="4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="N14" s="4"/>
       <c r="O14" s="4"/>
     </row>
     <row r="15" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
-        <v>45548</v>
+        <v>45558</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>45</v>
@@ -1985,65 +1937,65 @@
         <v>46</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E15" s="3">
-        <v>45624</v>
+        <v>45614</v>
       </c>
       <c r="F15" s="5">
-        <v>1843.88</v>
+        <v>2000</v>
       </c>
       <c r="G15" s="5">
-        <v>1843.88</v>
+        <v>2000</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="6">
-        <v>678</v>
+        <v>690</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>18</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L15" s="4"/>
       <c r="M15" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="N15" s="4"/>
       <c r="O15" s="4"/>
     </row>
     <row r="16" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
-        <v>45552</v>
+        <v>45546</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E16" s="3">
-        <v>45608</v>
+        <v>45615</v>
       </c>
       <c r="F16" s="5">
-        <v>4439.8999999999996</v>
+        <v>1216.8599999999999</v>
       </c>
       <c r="G16" s="5">
-        <v>4439.8999999999996</v>
+        <v>1216.8599999999999</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="6">
-        <v>694</v>
+        <v>689</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>18</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="L16" s="4"/>
       <c r="M16" s="4" t="s">
@@ -2054,35 +2006,35 @@
     </row>
     <row r="17" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
-        <v>45552</v>
+        <v>45548</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>60</v>
       </c>
       <c r="E17" s="3">
-        <v>45622</v>
+        <v>45617</v>
       </c>
       <c r="F17" s="5">
-        <v>4439.8999999999996</v>
+        <v>1843.87</v>
       </c>
       <c r="G17" s="5">
-        <v>4439.8999999999996</v>
+        <v>1843.87</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="6">
-        <v>680</v>
+        <v>687</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>18</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="L17" s="4"/>
       <c r="M17" s="4" t="s">
@@ -2093,7 +2045,7 @@
     </row>
     <row r="18" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
-        <v>45558</v>
+        <v>45546</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>45</v>
@@ -2105,23 +2057,23 @@
         <v>62</v>
       </c>
       <c r="E18" s="3">
-        <v>45607</v>
+        <v>45622</v>
       </c>
       <c r="F18" s="5">
-        <v>2000</v>
+        <v>1216.8599999999999</v>
       </c>
       <c r="G18" s="5">
-        <v>3204.34</v>
+        <v>1216.8599999999999</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="6">
-        <v>695</v>
+        <v>682</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>18</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L18" s="4"/>
       <c r="M18" s="4" t="s">
@@ -2132,35 +2084,35 @@
     </row>
     <row r="19" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
-        <v>45558</v>
+        <v>45552</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>64</v>
       </c>
       <c r="E19" s="3">
-        <v>45600</v>
+        <v>45622</v>
       </c>
       <c r="F19" s="5">
-        <v>2000</v>
+        <v>4439.8999999999996</v>
       </c>
       <c r="G19" s="5">
-        <v>2000</v>
+        <v>4439.8999999999996</v>
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="6">
-        <v>702</v>
+        <v>682</v>
       </c>
       <c r="J19" s="4" t="s">
         <v>18</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="L19" s="4"/>
       <c r="M19" s="4" t="s">
@@ -2171,7 +2123,7 @@
     </row>
     <row r="20" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
-        <v>45558</v>
+        <v>45548</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>45</v>
@@ -2183,23 +2135,23 @@
         <v>66</v>
       </c>
       <c r="E20" s="3">
-        <v>45614</v>
+        <v>45624</v>
       </c>
       <c r="F20" s="5">
-        <v>2000</v>
+        <v>1843.88</v>
       </c>
       <c r="G20" s="5">
-        <v>2000</v>
+        <v>1843.88</v>
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="6">
-        <v>688</v>
+        <v>680</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>18</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L20" s="4"/>
       <c r="M20" s="4" t="s">
@@ -2232,7 +2184,7 @@
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="6">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>18</v>
@@ -2249,7 +2201,7 @@
     </row>
     <row r="22" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
-        <v>45636</v>
+        <v>45646</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>45</v>
@@ -2261,17 +2213,17 @@
         <v>74</v>
       </c>
       <c r="E22" s="3">
-        <v>45699</v>
+        <v>45695</v>
       </c>
       <c r="F22" s="5">
-        <v>2330</v>
+        <v>3296.8</v>
       </c>
       <c r="G22" s="5">
-        <v>2330</v>
+        <v>3296.8</v>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="6">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="J22" s="4" t="s">
         <v>18</v>
@@ -2288,7 +2240,7 @@
     </row>
     <row r="23" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
-        <v>45646</v>
+        <v>45636</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>45</v>
@@ -2300,17 +2252,17 @@
         <v>77</v>
       </c>
       <c r="E23" s="3">
-        <v>45695</v>
+        <v>45699</v>
       </c>
       <c r="F23" s="5">
-        <v>3296.8</v>
+        <v>2330</v>
       </c>
       <c r="G23" s="5">
-        <v>3296.8</v>
+        <v>2330</v>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="6">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="J23" s="4" t="s">
         <v>18</v>
@@ -2349,7 +2301,7 @@
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="6">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="J24" s="4" t="s">
         <v>18</v>
@@ -2366,7 +2318,7 @@
     </row>
     <row r="25" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
-        <v>45646</v>
+        <v>45677</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>45</v>
@@ -2378,20 +2330,20 @@
         <v>81</v>
       </c>
       <c r="E25" s="3">
-        <v>45709</v>
+        <v>45705</v>
       </c>
       <c r="F25" s="5">
-        <v>3296.8</v>
+        <v>2541</v>
       </c>
       <c r="G25" s="5">
-        <v>3296.8</v>
+        <v>2541</v>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="6">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="K25" s="4" t="s">
         <v>75</v>
@@ -2405,7 +2357,7 @@
     </row>
     <row r="26" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
-        <v>45677</v>
+        <v>45646</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>45</v>
@@ -2417,20 +2369,20 @@
         <v>83</v>
       </c>
       <c r="E26" s="3">
-        <v>45705</v>
+        <v>45709</v>
       </c>
       <c r="F26" s="5">
-        <v>2541</v>
+        <v>3296.8</v>
       </c>
       <c r="G26" s="5">
-        <v>2541</v>
+        <v>3296.8</v>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="6">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="K26" s="4" t="s">
         <v>75</v>
@@ -2466,10 +2418,10 @@
       </c>
       <c r="H27" s="3"/>
       <c r="I27" s="6">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K27" s="4" t="s">
         <v>75</v>
@@ -2505,10 +2457,10 @@
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="6">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K28" s="4" t="s">
         <v>75</v>
@@ -2522,7 +2474,7 @@
     </row>
     <row r="29" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
-        <v>45677</v>
+        <v>45699</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>45</v>
@@ -2534,20 +2486,20 @@
         <v>89</v>
       </c>
       <c r="E29" s="3">
-        <v>45740</v>
+        <v>45727</v>
       </c>
       <c r="F29" s="5">
-        <v>2541</v>
+        <v>7562.78</v>
       </c>
       <c r="G29" s="5">
-        <v>2541</v>
+        <v>7562.78</v>
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="6">
-        <v>562</v>
+        <v>577</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="K29" s="4" t="s">
         <v>75</v>
@@ -2573,7 +2525,7 @@
         <v>91</v>
       </c>
       <c r="E30" s="3">
-        <v>45727</v>
+        <v>45734</v>
       </c>
       <c r="F30" s="5">
         <v>7562.78</v>
@@ -2583,7 +2535,7 @@
       </c>
       <c r="H30" s="3"/>
       <c r="I30" s="6">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="J30" s="4" t="s">
         <v>18</v>
@@ -2603,43 +2555,43 @@
         <v>45699</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E31" s="3">
         <v>45734</v>
       </c>
       <c r="F31" s="5">
-        <v>7562.78</v>
+        <v>1154.56</v>
       </c>
       <c r="G31" s="5">
-        <v>7562.78</v>
+        <v>1154.56</v>
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="6">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="J31" s="4" t="s">
         <v>18</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="L31" s="4"/>
       <c r="M31" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N31" s="4"/>
       <c r="O31" s="4"/>
     </row>
     <row r="32" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
-        <v>45699</v>
+        <v>45677</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>45</v>
@@ -2648,30 +2600,30 @@
         <v>73</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E32" s="3">
-        <v>45741</v>
+        <v>45740</v>
       </c>
       <c r="F32" s="5">
-        <v>7562.78</v>
+        <v>2541</v>
       </c>
       <c r="G32" s="5">
-        <v>7562.78</v>
+        <v>2541</v>
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="6">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="K32" s="4" t="s">
         <v>75</v>
       </c>
       <c r="L32" s="4"/>
       <c r="M32" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N32" s="4"/>
       <c r="O32" s="4"/>
@@ -2687,20 +2639,20 @@
         <v>73</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E33" s="3">
-        <v>45748</v>
+        <v>45741</v>
       </c>
       <c r="F33" s="5">
-        <v>7562.76</v>
+        <v>7562.78</v>
       </c>
       <c r="G33" s="5">
-        <v>7562.76</v>
+        <v>7562.78</v>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="6">
-        <v>554</v>
+        <v>563</v>
       </c>
       <c r="J33" s="4" t="s">
         <v>18</v>
@@ -2710,7 +2662,7 @@
       </c>
       <c r="L33" s="4"/>
       <c r="M33" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N33" s="4"/>
       <c r="O33" s="4"/>
@@ -2720,16 +2672,16 @@
         <v>45699</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>100</v>
       </c>
       <c r="E34" s="3">
-        <v>45734</v>
+        <v>45741</v>
       </c>
       <c r="F34" s="5">
         <v>1154.56</v>
@@ -2739,13 +2691,13 @@
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="6">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="J34" s="4" t="s">
         <v>18</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="L34" s="4"/>
       <c r="M34" s="4" t="s">
@@ -2759,16 +2711,16 @@
         <v>45699</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>102</v>
       </c>
       <c r="E35" s="3">
-        <v>45741</v>
+        <v>45748</v>
       </c>
       <c r="F35" s="5">
         <v>1154.56</v>
@@ -2778,13 +2730,13 @@
       </c>
       <c r="H35" s="3"/>
       <c r="I35" s="6">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="J35" s="4" t="s">
         <v>18</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="L35" s="4"/>
       <c r="M35" s="4" t="s">
@@ -2798,10 +2750,10 @@
         <v>45699</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>99</v>
+        <v>73</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>104</v>
@@ -2810,20 +2762,20 @@
         <v>45748</v>
       </c>
       <c r="F36" s="5">
-        <v>1154.56</v>
+        <v>7562.76</v>
       </c>
       <c r="G36" s="5">
-        <v>1154.56</v>
+        <v>7562.76</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="6">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="J36" s="4" t="s">
         <v>18</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="L36" s="4"/>
       <c r="M36" s="4" t="s">
@@ -2837,10 +2789,10 @@
         <v>45699</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>106</v>
@@ -2856,13 +2808,13 @@
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="6">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="J37" s="4" t="s">
         <v>18</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="L37" s="4"/>
       <c r="M37" s="4" t="s">
@@ -2876,7 +2828,7 @@
         <v>45733</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>108</v>
@@ -2895,13 +2847,13 @@
       </c>
       <c r="H38" s="3"/>
       <c r="I38" s="6">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="J38" s="4" t="s">
         <v>18</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="L38" s="4"/>
       <c r="M38" s="4" t="s">
@@ -2915,7 +2867,7 @@
         <v>45733</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>108</v>
@@ -2934,13 +2886,13 @@
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="6">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="J39" s="4" t="s">
         <v>18</v>
       </c>
       <c r="K39" s="4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="L39" s="4"/>
       <c r="M39" s="4" t="s">
@@ -2954,7 +2906,7 @@
         <v>45733</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>108</v>
@@ -2973,13 +2925,13 @@
       </c>
       <c r="H40" s="3"/>
       <c r="I40" s="6">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="J40" s="4" t="s">
         <v>18</v>
       </c>
       <c r="K40" s="4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="L40" s="4"/>
       <c r="M40" s="4" t="s">
@@ -2993,7 +2945,7 @@
         <v>45747</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>108</v>
@@ -3012,13 +2964,13 @@
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="6">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="J41" s="4" t="s">
         <v>18</v>
       </c>
       <c r="K41" s="4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="L41" s="4"/>
       <c r="M41" s="4" t="s">
@@ -3032,7 +2984,7 @@
         <v>45747</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>108</v>
@@ -3051,13 +3003,13 @@
       </c>
       <c r="H42" s="3"/>
       <c r="I42" s="6">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="J42" s="4" t="s">
         <v>18</v>
       </c>
       <c r="K42" s="4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="L42" s="4"/>
       <c r="M42" s="4" t="s">
@@ -3071,7 +3023,7 @@
         <v>45747</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>108</v>
@@ -3090,13 +3042,13 @@
       </c>
       <c r="H43" s="3"/>
       <c r="I43" s="6">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="J43" s="4" t="s">
         <v>18</v>
       </c>
       <c r="K43" s="4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="L43" s="4"/>
       <c r="M43" s="4" t="s">
@@ -3129,10 +3081,10 @@
       </c>
       <c r="H44" s="3"/>
       <c r="I44" s="6">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K44" s="4" t="s">
         <v>124</v>
@@ -3168,10 +3120,10 @@
       </c>
       <c r="H45" s="3"/>
       <c r="I45" s="6">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K45" s="4" t="s">
         <v>124</v>
@@ -3207,10 +3159,10 @@
       </c>
       <c r="H46" s="3"/>
       <c r="I46" s="6">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K46" s="4" t="s">
         <v>71</v>
@@ -3246,10 +3198,10 @@
       </c>
       <c r="H47" s="3"/>
       <c r="I47" s="6">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K47" s="4" t="s">
         <v>71</v>
@@ -3285,10 +3237,10 @@
       </c>
       <c r="H48" s="3"/>
       <c r="I48" s="6">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K48" s="4" t="s">
         <v>71</v>
@@ -3324,13 +3276,13 @@
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="6">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K49" s="4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="L49" s="4"/>
       <c r="M49" s="4" t="s">
@@ -3363,13 +3315,13 @@
       </c>
       <c r="H50" s="3"/>
       <c r="I50" s="6">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K50" s="4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="L50" s="4"/>
       <c r="M50" s="4" t="s">
@@ -3402,13 +3354,13 @@
       </c>
       <c r="H51" s="3"/>
       <c r="I51" s="6">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K51" s="4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="L51" s="4"/>
       <c r="M51" s="4" t="s">
@@ -3441,13 +3393,13 @@
       </c>
       <c r="H52" s="3"/>
       <c r="I52" s="6">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="L52" s="4"/>
       <c r="M52" s="4" t="s">
@@ -3458,10 +3410,10 @@
     </row>
     <row r="53" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
-        <v>45938</v>
+        <v>45959</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>145</v>
@@ -3473,60 +3425,60 @@
         <v>45980</v>
       </c>
       <c r="F53" s="5">
-        <v>4480</v>
+        <v>28666.44</v>
       </c>
       <c r="G53" s="5">
-        <v>4480</v>
+        <v>28666.44</v>
       </c>
       <c r="H53" s="3"/>
       <c r="I53" s="6">
-        <v>322</v>
-      </c>
-      <c r="J53" s="4" t="s">
-        <v>28</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="J53" s="4"/>
       <c r="K53" s="4" t="s">
-        <v>124</v>
+        <v>54</v>
       </c>
       <c r="L53" s="4"/>
-      <c r="M53" s="4" t="s">
-        <v>147</v>
-      </c>
+      <c r="M53" s="4"/>
       <c r="N53" s="4"/>
       <c r="O53" s="4"/>
     </row>
     <row r="54" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
-        <v>45947</v>
+        <v>45938</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>121</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>148</v>
       </c>
       <c r="E54" s="3">
-        <v>45989</v>
+        <v>45980</v>
       </c>
       <c r="F54" s="5">
-        <v>3220</v>
+        <v>4480</v>
       </c>
       <c r="G54" s="5">
-        <v>3220</v>
+        <v>4480</v>
       </c>
       <c r="H54" s="3"/>
       <c r="I54" s="6">
-        <v>313</v>
-      </c>
-      <c r="J54" s="4"/>
+        <v>324</v>
+      </c>
+      <c r="J54" s="4" t="s">
+        <v>26</v>
+      </c>
       <c r="K54" s="4" t="s">
         <v>124</v>
       </c>
       <c r="L54" s="4"/>
-      <c r="M54" s="4"/>
+      <c r="M54" s="4" t="s">
+        <v>149</v>
+      </c>
       <c r="N54" s="4"/>
       <c r="O54" s="4"/>
     </row>
@@ -3538,27 +3490,27 @@
         <v>135</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>150</v>
       </c>
       <c r="E55" s="3">
-        <v>45980</v>
+        <v>45987</v>
       </c>
       <c r="F55" s="5">
-        <v>28666.44</v>
+        <v>33844.160000000003</v>
       </c>
       <c r="G55" s="5">
-        <v>28666.44</v>
+        <v>33844.160000000003</v>
       </c>
       <c r="H55" s="3"/>
       <c r="I55" s="6">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="J55" s="4"/>
       <c r="K55" s="4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="L55" s="4"/>
       <c r="M55" s="4"/>
@@ -3567,25 +3519,25 @@
     </row>
     <row r="56" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
-        <v>45959</v>
+        <v>45947</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D56" s="4" t="s">
         <v>151</v>
       </c>
       <c r="E56" s="3">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="F56" s="5">
-        <v>33844.160000000003</v>
+        <v>3220</v>
       </c>
       <c r="G56" s="5">
-        <v>33844.160000000003</v>
+        <v>3220</v>
       </c>
       <c r="H56" s="3"/>
       <c r="I56" s="6">
@@ -3593,7 +3545,7 @@
       </c>
       <c r="J56" s="4"/>
       <c r="K56" s="4" t="s">
-        <v>58</v>
+        <v>124</v>
       </c>
       <c r="L56" s="4"/>
       <c r="M56" s="4"/>
@@ -3608,7 +3560,7 @@
         <v>135</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>152</v>
@@ -3624,11 +3576,11 @@
       </c>
       <c r="H57" s="3"/>
       <c r="I57" s="6">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="J57" s="4"/>
       <c r="K57" s="4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="L57" s="4"/>
       <c r="M57" s="4"/>
@@ -3637,10 +3589,10 @@
     </row>
     <row r="58" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
-        <v>46045</v>
+        <v>46062</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>153</v>
@@ -3649,23 +3601,23 @@
         <v>154</v>
       </c>
       <c r="E58" s="3">
-        <v>46105</v>
+        <v>46090</v>
       </c>
       <c r="F58" s="5">
-        <v>5466.66</v>
+        <v>503.28</v>
       </c>
       <c r="G58" s="5">
-        <v>5466.66</v>
+        <v>806.34</v>
       </c>
       <c r="H58" s="3"/>
       <c r="I58" s="6">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="L58" s="4"/>
       <c r="M58" s="4" t="s">
@@ -3679,36 +3631,36 @@
         <v>46062</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C59" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="D59" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="D59" s="4" t="s">
-        <v>157</v>
-      </c>
       <c r="E59" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="F59" s="5">
         <v>503.28</v>
       </c>
       <c r="G59" s="5">
-        <v>806.34</v>
+        <v>503.28</v>
       </c>
       <c r="H59" s="3"/>
       <c r="I59" s="6">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L59" s="4"/>
       <c r="M59" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="N59" s="4"/>
       <c r="O59" s="4"/>
@@ -3718,16 +3670,16 @@
         <v>46062</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E60" s="3">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="F60" s="5">
         <v>503.28</v>
@@ -3737,52 +3689,52 @@
       </c>
       <c r="H60" s="3"/>
       <c r="I60" s="6">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="J60" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K60" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L60" s="4"/>
       <c r="M60" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N60" s="4"/>
       <c r="O60" s="4"/>
     </row>
     <row r="61" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
-        <v>46062</v>
+        <v>46045</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>161</v>
       </c>
       <c r="E61" s="3">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="F61" s="5">
-        <v>503.28</v>
+        <v>5466.66</v>
       </c>
       <c r="G61" s="5">
-        <v>503.28</v>
+        <v>5466.66</v>
       </c>
       <c r="H61" s="3"/>
       <c r="I61" s="6">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="K61" s="4" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="L61" s="4"/>
       <c r="M61" s="4" t="s">
@@ -3793,40 +3745,36 @@
     </row>
     <row r="62" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
-        <v>46162</v>
+        <v>46171</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>25</v>
+        <v>135</v>
       </c>
       <c r="C62" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D62" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="D62" s="4" t="s">
-        <v>164</v>
-      </c>
       <c r="E62" s="3">
-        <v>46222</v>
+        <v>46192</v>
       </c>
       <c r="F62" s="5">
-        <v>31531.5</v>
+        <v>4676.8500000000004</v>
       </c>
       <c r="G62" s="5">
-        <v>31531.5</v>
+        <v>7494.53</v>
       </c>
       <c r="H62" s="3"/>
       <c r="I62" s="6">
-        <v>80</v>
-      </c>
-      <c r="J62" s="4" t="s">
-        <v>18</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="J62" s="4"/>
       <c r="K62" s="4" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="L62" s="4"/>
-      <c r="M62" s="4" t="s">
-        <v>165</v>
-      </c>
+      <c r="M62" s="4"/>
       <c r="N62" s="4"/>
       <c r="O62" s="4"/>
     </row>
@@ -3838,27 +3786,27 @@
         <v>135</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E63" s="3">
-        <v>46192</v>
+        <v>46199</v>
       </c>
       <c r="F63" s="5">
         <v>4676.8500000000004</v>
       </c>
       <c r="G63" s="5">
-        <v>7494.53</v>
+        <v>4676.8500000000004</v>
       </c>
       <c r="H63" s="3"/>
       <c r="I63" s="6">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="J63" s="4"/>
       <c r="K63" s="4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="L63" s="4"/>
       <c r="M63" s="4"/>
@@ -3873,13 +3821,13 @@
         <v>135</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E64" s="3">
-        <v>46199</v>
+        <v>46206</v>
       </c>
       <c r="F64" s="5">
         <v>4676.8500000000004</v>
@@ -3889,11 +3837,11 @@
       </c>
       <c r="H64" s="3"/>
       <c r="I64" s="6">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="J64" s="4"/>
       <c r="K64" s="4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="L64" s="4"/>
       <c r="M64" s="4"/>
@@ -3902,33 +3850,33 @@
     </row>
     <row r="65" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
-        <v>46171</v>
+        <v>46162</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>135</v>
+        <v>23</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E65" s="3">
-        <v>46206</v>
+        <v>46222</v>
       </c>
       <c r="F65" s="5">
-        <v>4676.8500000000004</v>
+        <v>22349.79</v>
       </c>
       <c r="G65" s="5">
-        <v>4676.8500000000004</v>
+        <v>22349.79</v>
       </c>
       <c r="H65" s="3"/>
       <c r="I65" s="6">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="J65" s="4"/>
       <c r="K65" s="4" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="L65" s="4"/>
       <c r="M65" s="4"/>
@@ -3940,13 +3888,13 @@
         <v>46203</v>
       </c>
       <c r="B66" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C66" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="C66" s="4" t="s">
+      <c r="D66" s="4" t="s">
         <v>170</v>
-      </c>
-      <c r="D66" s="4" t="s">
-        <v>171</v>
       </c>
       <c r="E66" s="3">
         <v>46259</v>
@@ -3959,95 +3907,95 @@
       </c>
       <c r="H66" s="3"/>
       <c r="I66" s="6">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J66" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K66" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L66" s="4"/>
       <c r="M66" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="N66" s="4"/>
       <c r="O66" s="4"/>
     </row>
     <row r="67" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>15</v>
+        <v>168</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E67" s="3">
-        <v>46293</v>
+        <v>46259</v>
       </c>
       <c r="F67" s="5">
-        <v>6265</v>
+        <v>2818.37</v>
       </c>
       <c r="G67" s="5">
-        <v>6265</v>
+        <v>2818.37</v>
       </c>
       <c r="H67" s="3"/>
       <c r="I67" s="6">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="J67" s="4" t="s">
-        <v>176</v>
+        <v>26</v>
       </c>
       <c r="K67" s="4" t="s">
-        <v>19</v>
+        <v>171</v>
       </c>
       <c r="L67" s="4"/>
       <c r="M67" s="4" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="N67" s="4"/>
       <c r="O67" s="4"/>
     </row>
     <row r="68" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>178</v>
+        <v>15</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E68" s="3">
-        <v>46270</v>
+        <v>46262</v>
       </c>
       <c r="F68" s="5">
-        <v>7551.88</v>
+        <v>9716</v>
       </c>
       <c r="G68" s="5">
-        <v>11442.87</v>
+        <v>18957.86</v>
       </c>
       <c r="H68" s="3"/>
       <c r="I68" s="6">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="J68" s="4" t="s">
-        <v>181</v>
+        <v>26</v>
       </c>
       <c r="K68" s="4" t="s">
-        <v>182</v>
+        <v>39</v>
       </c>
       <c r="L68" s="4"/>
       <c r="M68" s="4" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="N68" s="4"/>
       <c r="O68" s="4"/>
@@ -4063,20 +4011,20 @@
         <v>179</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="E69" s="3">
-        <v>46285</v>
+        <v>46270</v>
       </c>
       <c r="F69" s="5">
         <v>7551.88</v>
       </c>
       <c r="G69" s="5">
-        <v>7551.88</v>
+        <v>11442.87</v>
       </c>
       <c r="H69" s="3"/>
       <c r="I69" s="6">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="J69" s="4" t="s">
         <v>181</v>
@@ -4086,124 +4034,124 @@
       </c>
       <c r="L69" s="4"/>
       <c r="M69" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="N69" s="4"/>
       <c r="O69" s="4"/>
     </row>
     <row r="70" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>178</v>
+        <v>15</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E70" s="3">
-        <v>46300</v>
+        <v>46272</v>
       </c>
       <c r="F70" s="5">
-        <v>7551.88</v>
+        <v>9716</v>
       </c>
       <c r="G70" s="5">
-        <v>7551.88</v>
+        <v>9716</v>
       </c>
       <c r="H70" s="3"/>
       <c r="I70" s="6">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="J70" s="4" t="s">
-        <v>181</v>
+        <v>26</v>
       </c>
       <c r="K70" s="4" t="s">
-        <v>182</v>
+        <v>39</v>
       </c>
       <c r="L70" s="4"/>
       <c r="M70" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="N70" s="4"/>
       <c r="O70" s="4"/>
     </row>
     <row r="71" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3">
-        <v>46223</v>
+        <v>46227</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>45</v>
+        <v>178</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E71" s="3">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="F71" s="5">
-        <v>11200</v>
+        <v>4216.67</v>
       </c>
       <c r="G71" s="5">
-        <v>11200</v>
+        <v>6389.24</v>
       </c>
       <c r="H71" s="3"/>
       <c r="I71" s="6">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J71" s="4" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="K71" s="4" t="s">
-        <v>29</v>
+        <v>182</v>
       </c>
       <c r="L71" s="4"/>
       <c r="M71" s="4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="N71" s="4"/>
       <c r="O71" s="4"/>
     </row>
     <row r="72" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>45</v>
+        <v>168</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>188</v>
+        <v>169</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E72" s="3">
-        <v>46283</v>
+        <v>46273</v>
       </c>
       <c r="F72" s="5">
-        <v>11200</v>
+        <v>2818.37</v>
       </c>
       <c r="G72" s="5">
-        <v>11200</v>
+        <v>2818.37</v>
       </c>
       <c r="H72" s="3"/>
       <c r="I72" s="6">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="J72" s="4" t="s">
-        <v>181</v>
+        <v>26</v>
       </c>
       <c r="K72" s="4" t="s">
-        <v>29</v>
+        <v>171</v>
       </c>
       <c r="L72" s="4"/>
       <c r="M72" s="4" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="N72" s="4"/>
       <c r="O72" s="4"/>
@@ -4216,13 +4164,13 @@
         <v>45</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E73" s="3">
-        <v>46293</v>
+        <v>46273</v>
       </c>
       <c r="F73" s="5">
         <v>11200</v>
@@ -4232,52 +4180,52 @@
       </c>
       <c r="H73" s="3"/>
       <c r="I73" s="6">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="J73" s="4" t="s">
         <v>181</v>
       </c>
       <c r="K73" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L73" s="4"/>
       <c r="M73" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="N73" s="4"/>
       <c r="O73" s="4"/>
     </row>
     <row r="74" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="3">
-        <v>46224</v>
+        <v>46253</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>169</v>
+        <v>45</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>170</v>
+        <v>194</v>
       </c>
       <c r="D74" s="4" t="s">
         <v>195</v>
       </c>
       <c r="E74" s="3">
-        <v>46259</v>
+        <v>46274</v>
       </c>
       <c r="F74" s="5">
-        <v>2818.37</v>
+        <v>10080</v>
       </c>
       <c r="G74" s="5">
-        <v>2818.37</v>
+        <v>10080</v>
       </c>
       <c r="H74" s="3"/>
       <c r="I74" s="6">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="J74" s="4" t="s">
-        <v>28</v>
+        <v>181</v>
       </c>
       <c r="K74" s="4" t="s">
-        <v>172</v>
+        <v>27</v>
       </c>
       <c r="L74" s="4"/>
       <c r="M74" s="4" t="s">
@@ -4288,35 +4236,35 @@
     </row>
     <row r="75" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="3">
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>169</v>
+        <v>45</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>170</v>
+        <v>194</v>
       </c>
       <c r="D75" s="4" t="s">
         <v>197</v>
       </c>
       <c r="E75" s="3">
-        <v>46273</v>
+        <v>46276</v>
       </c>
       <c r="F75" s="5">
-        <v>2818.37</v>
+        <v>23168.6</v>
       </c>
       <c r="G75" s="5">
-        <v>2818.37</v>
+        <v>23168.6</v>
       </c>
       <c r="H75" s="3"/>
       <c r="I75" s="6">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J75" s="4" t="s">
-        <v>28</v>
+        <v>181</v>
       </c>
       <c r="K75" s="4" t="s">
-        <v>172</v>
+        <v>27</v>
       </c>
       <c r="L75" s="4"/>
       <c r="M75" s="4" t="s">
@@ -4327,35 +4275,35 @@
     </row>
     <row r="76" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="3">
-        <v>46224</v>
+        <v>46234</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="D76" s="4" t="s">
         <v>199</v>
       </c>
       <c r="E76" s="3">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="F76" s="5">
-        <v>2818.36</v>
+        <v>3789.09</v>
       </c>
       <c r="G76" s="5">
-        <v>2818.36</v>
+        <v>5741.36</v>
       </c>
       <c r="H76" s="3"/>
       <c r="I76" s="6">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J76" s="4" t="s">
-        <v>28</v>
+        <v>181</v>
       </c>
       <c r="K76" s="4" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="L76" s="4"/>
       <c r="M76" s="4" t="s">
@@ -4369,32 +4317,32 @@
         <v>46224</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>45</v>
+        <v>168</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>188</v>
+        <v>169</v>
       </c>
       <c r="D77" s="4" t="s">
         <v>201</v>
       </c>
       <c r="E77" s="3">
-        <v>46284</v>
+        <v>46280</v>
       </c>
       <c r="F77" s="5">
-        <v>10666.67</v>
+        <v>2818.36</v>
       </c>
       <c r="G77" s="5">
-        <v>10666.67</v>
+        <v>2818.36</v>
       </c>
       <c r="H77" s="3"/>
       <c r="I77" s="6">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J77" s="4" t="s">
-        <v>181</v>
+        <v>26</v>
       </c>
       <c r="K77" s="4" t="s">
-        <v>29</v>
+        <v>171</v>
       </c>
       <c r="L77" s="4"/>
       <c r="M77" s="4" t="s">
@@ -4405,78 +4353,78 @@
     </row>
     <row r="78" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="3">
-        <v>46227</v>
+        <v>46253</v>
       </c>
       <c r="B78" s="4" t="s">
         <v>45</v>
       </c>
       <c r="C78" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="D78" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="D78" s="4" t="s">
-        <v>204</v>
-      </c>
       <c r="E78" s="3">
-        <v>46276</v>
+        <v>46281</v>
       </c>
       <c r="F78" s="5">
-        <v>23168.6</v>
+        <v>10080</v>
       </c>
       <c r="G78" s="5">
-        <v>23168.6</v>
+        <v>10080</v>
       </c>
       <c r="H78" s="3"/>
       <c r="I78" s="6">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J78" s="4" t="s">
         <v>181</v>
       </c>
       <c r="K78" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L78" s="4"/>
       <c r="M78" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="N78" s="4"/>
       <c r="O78" s="4"/>
     </row>
     <row r="79" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="3">
-        <v>46227</v>
+        <v>46232</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>203</v>
+        <v>175</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E79" s="3">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="F79" s="5">
-        <v>23168.6</v>
+        <v>9716</v>
       </c>
       <c r="G79" s="5">
-        <v>23168.6</v>
+        <v>9716</v>
       </c>
       <c r="H79" s="3"/>
       <c r="I79" s="6">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J79" s="4" t="s">
-        <v>181</v>
+        <v>26</v>
       </c>
       <c r="K79" s="4" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="L79" s="4"/>
       <c r="M79" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="N79" s="4"/>
       <c r="O79" s="4"/>
@@ -4486,114 +4434,114 @@
         <v>46227</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>178</v>
+        <v>45</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E80" s="3">
-        <v>46272</v>
+        <v>46283</v>
       </c>
       <c r="F80" s="5">
-        <v>4216.67</v>
+        <v>23168.6</v>
       </c>
       <c r="G80" s="5">
-        <v>6389.24</v>
+        <v>23168.6</v>
       </c>
       <c r="H80" s="3"/>
       <c r="I80" s="6">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="J80" s="4" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="K80" s="4" t="s">
-        <v>182</v>
+        <v>27</v>
       </c>
       <c r="L80" s="4"/>
       <c r="M80" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="N80" s="4"/>
       <c r="O80" s="4"/>
     </row>
     <row r="81" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="3">
-        <v>46227</v>
+        <v>46223</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>178</v>
+        <v>45</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E81" s="3">
-        <v>46287</v>
+        <v>46283</v>
       </c>
       <c r="F81" s="5">
-        <v>4216.67</v>
+        <v>11200</v>
       </c>
       <c r="G81" s="5">
-        <v>4216.67</v>
+        <v>11200</v>
       </c>
       <c r="H81" s="3"/>
       <c r="I81" s="6">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="J81" s="4" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="K81" s="4" t="s">
-        <v>182</v>
+        <v>27</v>
       </c>
       <c r="L81" s="4"/>
       <c r="M81" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N81" s="4"/>
       <c r="O81" s="4"/>
     </row>
     <row r="82" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3">
-        <v>46232</v>
+        <v>46224</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>178</v>
+        <v>45</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>212</v>
+        <v>191</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E82" s="3">
-        <v>46292</v>
+        <v>46284</v>
       </c>
       <c r="F82" s="5">
-        <v>4082.05</v>
+        <v>10666.67</v>
       </c>
       <c r="G82" s="5">
-        <v>4082.05</v>
+        <v>10666.67</v>
       </c>
       <c r="H82" s="3"/>
       <c r="I82" s="6">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J82" s="4" t="s">
         <v>181</v>
       </c>
       <c r="K82" s="4" t="s">
-        <v>182</v>
+        <v>27</v>
       </c>
       <c r="L82" s="4"/>
       <c r="M82" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="N82" s="4"/>
       <c r="O82" s="4"/>
@@ -4606,10 +4554,10 @@
         <v>45</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E83" s="3">
         <v>46284</v>
@@ -4622,719 +4570,719 @@
       </c>
       <c r="H83" s="3"/>
       <c r="I83" s="6">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J83" s="4" t="s">
         <v>181</v>
       </c>
       <c r="K83" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L83" s="4"/>
       <c r="M83" s="4" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="N83" s="4"/>
       <c r="O83" s="4"/>
     </row>
     <row r="84" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="3">
-        <v>46232</v>
+        <v>46234</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>217</v>
+        <v>191</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E84" s="3">
-        <v>46262</v>
+        <v>46284</v>
       </c>
       <c r="F84" s="5">
-        <v>9716</v>
+        <v>4950.17</v>
       </c>
       <c r="G84" s="5">
-        <v>18957.86</v>
+        <v>4950.17</v>
       </c>
       <c r="H84" s="3"/>
       <c r="I84" s="6">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="J84" s="4" t="s">
-        <v>28</v>
+        <v>181</v>
       </c>
       <c r="K84" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="L84" s="4"/>
       <c r="M84" s="4" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="N84" s="4"/>
       <c r="O84" s="4"/>
     </row>
     <row r="85" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="3">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>15</v>
+        <v>178</v>
       </c>
       <c r="C85" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="D85" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="D85" s="4" t="s">
-        <v>220</v>
-      </c>
       <c r="E85" s="3">
-        <v>46272</v>
+        <v>46285</v>
       </c>
       <c r="F85" s="5">
-        <v>9716</v>
+        <v>7551.88</v>
       </c>
       <c r="G85" s="5">
-        <v>9716</v>
+        <v>7551.88</v>
       </c>
       <c r="H85" s="3"/>
       <c r="I85" s="6">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="J85" s="4" t="s">
-        <v>28</v>
+        <v>181</v>
       </c>
       <c r="K85" s="4" t="s">
-        <v>39</v>
+        <v>182</v>
       </c>
       <c r="L85" s="4"/>
       <c r="M85" s="4" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="N85" s="4"/>
       <c r="O85" s="4"/>
     </row>
     <row r="86" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="3">
-        <v>46232</v>
+        <v>46244</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>217</v>
+        <v>194</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E86" s="3">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="F86" s="5">
-        <v>9716</v>
+        <v>4320</v>
       </c>
       <c r="G86" s="5">
-        <v>9716</v>
+        <v>4320</v>
       </c>
       <c r="H86" s="3"/>
       <c r="I86" s="6">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J86" s="4" t="s">
-        <v>28</v>
+        <v>181</v>
       </c>
       <c r="K86" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="L86" s="4"/>
       <c r="M86" s="4" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="N86" s="4"/>
       <c r="O86" s="4"/>
     </row>
     <row r="87" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="3">
-        <v>46232</v>
+        <v>46266</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>217</v>
+        <v>194</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E87" s="3">
-        <v>46292</v>
+        <v>46287</v>
       </c>
       <c r="F87" s="5">
-        <v>9716</v>
+        <v>18600</v>
       </c>
       <c r="G87" s="5">
-        <v>9716</v>
+        <v>18600</v>
       </c>
       <c r="H87" s="3"/>
       <c r="I87" s="6">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="J87" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K87" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="L87" s="4"/>
       <c r="M87" s="4" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="N87" s="4"/>
       <c r="O87" s="4"/>
     </row>
     <row r="88" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="3">
-        <v>46234</v>
+        <v>46227</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>45</v>
+        <v>178</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E88" s="3">
-        <v>46284</v>
+        <v>46287</v>
       </c>
       <c r="F88" s="5">
-        <v>4950.17</v>
+        <v>4216.67</v>
       </c>
       <c r="G88" s="5">
-        <v>4950.17</v>
+        <v>4216.67</v>
       </c>
       <c r="H88" s="3"/>
       <c r="I88" s="6">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J88" s="4" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="K88" s="4" t="s">
-        <v>29</v>
+        <v>182</v>
       </c>
       <c r="L88" s="4"/>
       <c r="M88" s="4" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="N88" s="4"/>
       <c r="O88" s="4"/>
     </row>
     <row r="89" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="3">
-        <v>46234</v>
+        <v>46253</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>178</v>
+        <v>45</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="E89" s="3">
-        <v>46279</v>
+        <v>46288</v>
       </c>
       <c r="F89" s="5">
-        <v>3789.09</v>
+        <v>10080</v>
       </c>
       <c r="G89" s="5">
-        <v>5741.36</v>
+        <v>10080</v>
       </c>
       <c r="H89" s="3"/>
       <c r="I89" s="6">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J89" s="4" t="s">
         <v>181</v>
       </c>
       <c r="K89" s="4" t="s">
-        <v>182</v>
+        <v>27</v>
       </c>
       <c r="L89" s="4"/>
       <c r="M89" s="4" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="N89" s="4"/>
       <c r="O89" s="4"/>
     </row>
     <row r="90" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="3">
-        <v>46234</v>
+        <v>46253</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>178</v>
+        <v>121</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>179</v>
+        <v>227</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E90" s="3">
-        <v>46294</v>
+        <v>46288</v>
       </c>
       <c r="F90" s="5">
-        <v>3789.09</v>
+        <v>1660.33</v>
       </c>
       <c r="G90" s="5">
-        <v>3789.09</v>
+        <v>1660.33</v>
       </c>
       <c r="H90" s="3"/>
       <c r="I90" s="6">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="J90" s="4" t="s">
-        <v>181</v>
+        <v>18</v>
       </c>
       <c r="K90" s="4" t="s">
-        <v>182</v>
+        <v>124</v>
       </c>
       <c r="L90" s="4"/>
       <c r="M90" s="4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="N90" s="4"/>
       <c r="O90" s="4"/>
     </row>
     <row r="91" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="3">
-        <v>46237</v>
+        <v>46253</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>25</v>
+        <v>121</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>163</v>
+        <v>227</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E91" s="3">
-        <v>46297</v>
+        <v>46288</v>
       </c>
       <c r="F91" s="5">
-        <v>2930.4</v>
+        <v>3640</v>
       </c>
       <c r="G91" s="5">
-        <v>2930.4</v>
+        <v>3640</v>
       </c>
       <c r="H91" s="3"/>
       <c r="I91" s="6">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="J91" s="4" t="s">
-        <v>18</v>
+        <v>181</v>
       </c>
       <c r="K91" s="4" t="s">
-        <v>71</v>
+        <v>124</v>
       </c>
       <c r="L91" s="4"/>
       <c r="M91" s="4" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="N91" s="4"/>
       <c r="O91" s="4"/>
     </row>
     <row r="92" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="3">
-        <v>46244</v>
+        <v>46259</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>135</v>
+        <v>15</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E92" s="3">
-        <v>46293</v>
+        <v>46289</v>
       </c>
       <c r="F92" s="5">
-        <v>3599.85</v>
+        <v>6265</v>
       </c>
       <c r="G92" s="5">
-        <v>3599.85</v>
+        <v>6265</v>
       </c>
       <c r="H92" s="3"/>
       <c r="I92" s="6">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="J92" s="4" t="s">
-        <v>18</v>
+        <v>181</v>
       </c>
       <c r="K92" s="4" t="s">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="L92" s="4"/>
       <c r="M92" s="4" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="N92" s="4"/>
       <c r="O92" s="4"/>
     </row>
     <row r="93" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="3">
-        <v>46252</v>
+        <v>46262</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>169</v>
+        <v>235</v>
       </c>
       <c r="C93" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="D93" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="D93" s="4" t="s">
-        <v>238</v>
-      </c>
       <c r="E93" s="3">
-        <v>46301</v>
+        <v>46290</v>
       </c>
       <c r="F93" s="5">
-        <v>5443.56</v>
+        <v>7694.4</v>
       </c>
       <c r="G93" s="5">
-        <v>5443.56</v>
+        <v>7694.4</v>
       </c>
       <c r="H93" s="3"/>
       <c r="I93" s="6">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="J93" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K93" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="L93" s="4"/>
       <c r="M93" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="N93" s="4"/>
       <c r="O93" s="4"/>
     </row>
     <row r="94" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="3">
-        <v>46248</v>
+        <v>46262</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>15</v>
+        <v>235</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E94" s="3">
-        <v>46293</v>
+        <v>46290</v>
       </c>
       <c r="F94" s="5">
-        <v>23355.33</v>
+        <v>11660.11</v>
       </c>
       <c r="G94" s="5">
-        <v>23355.33</v>
+        <v>11660.11</v>
       </c>
       <c r="H94" s="3"/>
       <c r="I94" s="6">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J94" s="4" t="s">
         <v>181</v>
       </c>
       <c r="K94" s="4" t="s">
-        <v>39</v>
+        <v>238</v>
       </c>
       <c r="L94" s="4"/>
       <c r="M94" s="4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="N94" s="4"/>
       <c r="O94" s="4"/>
     </row>
     <row r="95" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="3">
-        <v>46244</v>
+        <v>46232</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>45</v>
+        <v>178</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>203</v>
+        <v>242</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E95" s="3">
-        <v>46286</v>
+        <v>46292</v>
       </c>
       <c r="F95" s="5">
-        <v>4320</v>
+        <v>4082.05</v>
       </c>
       <c r="G95" s="5">
-        <v>4320</v>
+        <v>4082.05</v>
       </c>
       <c r="H95" s="3"/>
       <c r="I95" s="6">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J95" s="4" t="s">
         <v>181</v>
       </c>
       <c r="K95" s="4" t="s">
-        <v>29</v>
+        <v>182</v>
       </c>
       <c r="L95" s="4"/>
       <c r="M95" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="N95" s="4"/>
       <c r="O95" s="4"/>
     </row>
     <row r="96" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="3">
-        <v>46244</v>
+        <v>46232</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>203</v>
+        <v>175</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E96" s="3">
-        <v>46293</v>
+        <v>46292</v>
       </c>
       <c r="F96" s="5">
-        <v>4320</v>
+        <v>9716</v>
       </c>
       <c r="G96" s="5">
-        <v>4320</v>
+        <v>9716</v>
       </c>
       <c r="H96" s="3"/>
       <c r="I96" s="6">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J96" s="4" t="s">
-        <v>181</v>
+        <v>26</v>
       </c>
       <c r="K96" s="4" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="L96" s="4"/>
       <c r="M96" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="N96" s="4"/>
       <c r="O96" s="4"/>
     </row>
     <row r="97" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="3">
-        <v>46245</v>
+        <v>46223</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>169</v>
+        <v>15</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E97" s="3">
-        <v>46301</v>
+        <v>46293</v>
       </c>
       <c r="F97" s="5">
-        <v>1840.96</v>
+        <v>6265</v>
       </c>
       <c r="G97" s="5">
-        <v>1840.96</v>
+        <v>6265</v>
       </c>
       <c r="H97" s="3"/>
       <c r="I97" s="6">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J97" s="4" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="K97" s="4" t="s">
-        <v>172</v>
+        <v>19</v>
       </c>
       <c r="L97" s="4"/>
       <c r="M97" s="4" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="N97" s="4"/>
       <c r="O97" s="4"/>
     </row>
     <row r="98" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="3">
-        <v>46253</v>
+        <v>46244</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>169</v>
+        <v>45</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>251</v>
+        <v>194</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="E98" s="3">
-        <v>46295</v>
+        <v>46293</v>
       </c>
       <c r="F98" s="5">
-        <v>2051.2199999999998</v>
+        <v>4320</v>
       </c>
       <c r="G98" s="5">
-        <v>2051.2199999999998</v>
+        <v>4320</v>
       </c>
       <c r="H98" s="3"/>
       <c r="I98" s="6">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J98" s="4" t="s">
-        <v>18</v>
+        <v>181</v>
       </c>
       <c r="K98" s="4" t="s">
-        <v>172</v>
+        <v>27</v>
       </c>
       <c r="L98" s="4"/>
       <c r="M98" s="4" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="N98" s="4"/>
       <c r="O98" s="4"/>
     </row>
     <row r="99" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="3">
-        <v>46252</v>
+        <v>46223</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>163</v>
+        <v>191</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E99" s="3">
-        <v>46297</v>
+        <v>46293</v>
       </c>
       <c r="F99" s="5">
-        <v>3809.52</v>
+        <v>11200</v>
       </c>
       <c r="G99" s="5">
-        <v>3809.52</v>
+        <v>11200</v>
       </c>
       <c r="H99" s="3"/>
       <c r="I99" s="6">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J99" s="4" t="s">
         <v>181</v>
       </c>
       <c r="K99" s="4" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="L99" s="4"/>
       <c r="M99" s="4" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="N99" s="4"/>
       <c r="O99" s="4"/>
     </row>
     <row r="100" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="3">
-        <v>46253</v>
+        <v>46266</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>121</v>
+        <v>45</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>256</v>
+        <v>194</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="E100" s="3">
-        <v>46288</v>
+        <v>46294</v>
       </c>
       <c r="F100" s="5">
-        <v>3640</v>
+        <v>18600</v>
       </c>
       <c r="G100" s="5">
-        <v>3640</v>
+        <v>18600</v>
       </c>
       <c r="H100" s="3"/>
       <c r="I100" s="6">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J100" s="4" t="s">
-        <v>181</v>
+        <v>26</v>
       </c>
       <c r="K100" s="4" t="s">
-        <v>124</v>
+        <v>27</v>
       </c>
       <c r="L100" s="4"/>
       <c r="M100" s="4" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="N100" s="4"/>
       <c r="O100" s="4"/>
     </row>
     <row r="101" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="3">
-        <v>46253</v>
+        <v>46234</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>121</v>
+        <v>178</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>256</v>
+        <v>179</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="E101" s="3">
-        <v>46295</v>
+        <v>46294</v>
       </c>
       <c r="F101" s="5">
-        <v>3640</v>
+        <v>3789.09</v>
       </c>
       <c r="G101" s="5">
-        <v>3640</v>
+        <v>3789.09</v>
       </c>
       <c r="H101" s="3"/>
       <c r="I101" s="6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J101" s="4" t="s">
         <v>181</v>
       </c>
       <c r="K101" s="4" t="s">
-        <v>124</v>
+        <v>182</v>
       </c>
       <c r="L101" s="4"/>
       <c r="M101" s="4" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="N101" s="4"/>
       <c r="O101" s="4"/>
@@ -5344,36 +5292,36 @@
         <v>46253</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>121</v>
+        <v>45</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>256</v>
+        <v>194</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="E102" s="3">
-        <v>46288</v>
+        <v>46295</v>
       </c>
       <c r="F102" s="5">
-        <v>1660.33</v>
+        <v>10080</v>
       </c>
       <c r="G102" s="5">
-        <v>1660.33</v>
+        <v>10080</v>
       </c>
       <c r="H102" s="3"/>
       <c r="I102" s="6">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J102" s="4" t="s">
-        <v>18</v>
+        <v>181</v>
       </c>
       <c r="K102" s="4" t="s">
-        <v>124</v>
+        <v>27</v>
       </c>
       <c r="L102" s="4"/>
       <c r="M102" s="4" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="N102" s="4"/>
       <c r="O102" s="4"/>
@@ -5386,33 +5334,33 @@
         <v>121</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>256</v>
+        <v>227</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="E103" s="3">
         <v>46295</v>
       </c>
       <c r="F103" s="5">
-        <v>1660.34</v>
+        <v>3640</v>
       </c>
       <c r="G103" s="5">
-        <v>1660.34</v>
+        <v>3640</v>
       </c>
       <c r="H103" s="3"/>
       <c r="I103" s="6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J103" s="4" t="s">
-        <v>18</v>
+        <v>181</v>
       </c>
       <c r="K103" s="4" t="s">
         <v>124</v>
       </c>
       <c r="L103" s="4"/>
       <c r="M103" s="4" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="N103" s="4"/>
       <c r="O103" s="4"/>
@@ -5422,36 +5370,36 @@
         <v>46253</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>45</v>
+        <v>121</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>203</v>
+        <v>227</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="E104" s="3">
-        <v>46274</v>
+        <v>46295</v>
       </c>
       <c r="F104" s="5">
-        <v>10080</v>
+        <v>1660.34</v>
       </c>
       <c r="G104" s="5">
-        <v>10080</v>
+        <v>1660.34</v>
       </c>
       <c r="H104" s="3"/>
       <c r="I104" s="6">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="J104" s="4" t="s">
-        <v>181</v>
+        <v>18</v>
       </c>
       <c r="K104" s="4" t="s">
-        <v>29</v>
+        <v>124</v>
       </c>
       <c r="L104" s="4"/>
       <c r="M104" s="4" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="N104" s="4"/>
       <c r="O104" s="4"/>
@@ -5461,780 +5409,585 @@
         <v>46253</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>45</v>
+        <v>168</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>203</v>
+        <v>263</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E105" s="3">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="F105" s="5">
-        <v>10080</v>
+        <v>2051.2199999999998</v>
       </c>
       <c r="G105" s="5">
-        <v>10080</v>
+        <v>2051.2199999999998</v>
       </c>
       <c r="H105" s="3"/>
       <c r="I105" s="6">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="J105" s="4" t="s">
-        <v>181</v>
+        <v>18</v>
       </c>
       <c r="K105" s="4" t="s">
-        <v>29</v>
+        <v>171</v>
       </c>
       <c r="L105" s="4"/>
       <c r="M105" s="4" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="N105" s="4"/>
       <c r="O105" s="4"/>
     </row>
     <row r="106" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="3">
-        <v>46253</v>
+        <v>46265</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>45</v>
+        <v>135</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>203</v>
+        <v>266</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="E106" s="3">
-        <v>46288</v>
+        <v>46295</v>
       </c>
       <c r="F106" s="5">
-        <v>10080</v>
+        <v>4750</v>
       </c>
       <c r="G106" s="5">
-        <v>10080</v>
+        <v>8565.68</v>
       </c>
       <c r="H106" s="3"/>
       <c r="I106" s="6">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J106" s="4" t="s">
         <v>181</v>
       </c>
       <c r="K106" s="4" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="L106" s="4"/>
       <c r="M106" s="4" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="N106" s="4"/>
       <c r="O106" s="4"/>
     </row>
     <row r="107" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="3">
-        <v>46253</v>
+        <v>46268</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>203</v>
+        <v>269</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E107" s="3">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F107" s="5">
-        <v>10080</v>
+        <v>2754</v>
       </c>
       <c r="G107" s="5">
-        <v>10080</v>
+        <v>2754</v>
       </c>
       <c r="H107" s="3"/>
       <c r="I107" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J107" s="4" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="K107" s="4" t="s">
-        <v>29</v>
+        <v>71</v>
       </c>
       <c r="L107" s="4"/>
       <c r="M107" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="N107" s="4"/>
       <c r="O107" s="4"/>
     </row>
     <row r="108" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="3">
-        <v>46259</v>
+        <v>46266</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>15</v>
+        <v>272</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>174</v>
+        <v>273</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E108" s="3">
-        <v>46289</v>
+        <v>46296</v>
       </c>
       <c r="F108" s="5">
-        <v>6265</v>
+        <v>8973.5</v>
       </c>
       <c r="G108" s="5">
-        <v>6265</v>
+        <v>8973.5</v>
       </c>
       <c r="H108" s="3"/>
       <c r="I108" s="6">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J108" s="4" t="s">
         <v>181</v>
       </c>
       <c r="K108" s="4" t="s">
-        <v>19</v>
+        <v>275</v>
       </c>
       <c r="L108" s="4"/>
       <c r="M108" s="4" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="N108" s="4"/>
       <c r="O108" s="4"/>
     </row>
     <row r="109" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="3">
-        <v>46253</v>
+        <v>46262</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>25</v>
+        <v>235</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>163</v>
+        <v>236</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E109" s="3">
-        <v>46298</v>
+        <v>46297</v>
       </c>
       <c r="F109" s="5">
-        <v>1172.1600000000001</v>
+        <v>11660.11</v>
       </c>
       <c r="G109" s="5">
-        <v>1172.1600000000001</v>
+        <v>11660.11</v>
       </c>
       <c r="H109" s="3"/>
       <c r="I109" s="6">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J109" s="4" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="K109" s="4" t="s">
-        <v>71</v>
+        <v>238</v>
       </c>
       <c r="L109" s="4"/>
       <c r="M109" s="4" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N109" s="4"/>
       <c r="O109" s="4"/>
     </row>
     <row r="110" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="3">
-        <v>46266</v>
+        <v>46262</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>169</v>
+        <v>235</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E110" s="3">
-        <v>46301</v>
+        <v>46297</v>
       </c>
       <c r="F110" s="5">
-        <v>3979.06</v>
+        <v>7694.4</v>
       </c>
       <c r="G110" s="5">
-        <v>3979.06</v>
+        <v>7694.4</v>
       </c>
       <c r="H110" s="3"/>
       <c r="I110" s="6">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J110" s="4" t="s">
-        <v>181</v>
+        <v>26</v>
       </c>
       <c r="K110" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="L110" s="4"/>
       <c r="M110" s="4" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="N110" s="4"/>
       <c r="O110" s="4"/>
     </row>
     <row r="111" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="3">
-        <v>46266</v>
+        <v>46225</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>135</v>
+        <v>178</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>234</v>
+        <v>179</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E111" s="3">
-        <v>46301</v>
+        <v>46300</v>
       </c>
       <c r="F111" s="5">
-        <v>1286.25</v>
+        <v>7551.88</v>
       </c>
       <c r="G111" s="5">
-        <v>1286.25</v>
+        <v>7551.88</v>
       </c>
       <c r="H111" s="3"/>
       <c r="I111" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J111" s="4" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="K111" s="4" t="s">
-        <v>58</v>
+        <v>182</v>
       </c>
       <c r="L111" s="4"/>
       <c r="M111" s="4" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="N111" s="4"/>
       <c r="O111" s="4"/>
     </row>
     <row r="112" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="3">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>281</v>
+        <v>23</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>282</v>
+        <v>269</v>
       </c>
       <c r="D112" s="4" t="s">
         <v>283</v>
       </c>
       <c r="E112" s="3">
-        <v>46290</v>
+        <v>46300</v>
       </c>
       <c r="F112" s="5">
-        <v>11660.11</v>
+        <v>1664</v>
       </c>
       <c r="G112" s="5">
-        <v>11660.11</v>
+        <v>1664</v>
       </c>
       <c r="H112" s="3"/>
       <c r="I112" s="6">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J112" s="4" t="s">
-        <v>181</v>
+        <v>18</v>
       </c>
       <c r="K112" s="4" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="L112" s="4"/>
       <c r="M112" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="N112" s="4"/>
       <c r="O112" s="4"/>
     </row>
     <row r="113" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="3">
-        <v>46262</v>
+        <v>46266</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>281</v>
+        <v>45</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>282</v>
+        <v>194</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E113" s="3">
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="F113" s="5">
-        <v>11660.11</v>
+        <v>18600</v>
       </c>
       <c r="G113" s="5">
-        <v>11660.11</v>
+        <v>18600</v>
       </c>
       <c r="H113" s="3"/>
       <c r="I113" s="6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J113" s="4" t="s">
-        <v>181</v>
+        <v>26</v>
       </c>
       <c r="K113" s="4" t="s">
-        <v>284</v>
+        <v>27</v>
       </c>
       <c r="L113" s="4"/>
       <c r="M113" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="N113" s="4"/>
       <c r="O113" s="4"/>
     </row>
     <row r="114" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="3">
-        <v>46262</v>
+        <v>46227</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>281</v>
+        <v>178</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>282</v>
+        <v>179</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E114" s="3">
-        <v>46290</v>
+        <v>46302</v>
       </c>
       <c r="F114" s="5">
-        <v>7694.4</v>
+        <v>4216.66</v>
       </c>
       <c r="G114" s="5">
-        <v>7694.4</v>
+        <v>4216.66</v>
       </c>
       <c r="H114" s="3"/>
       <c r="I114" s="6">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J114" s="4" t="s">
-        <v>28</v>
+        <v>187</v>
       </c>
       <c r="K114" s="4" t="s">
-        <v>284</v>
+        <v>182</v>
       </c>
       <c r="L114" s="4"/>
       <c r="M114" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="N114" s="4"/>
       <c r="O114" s="4"/>
     </row>
     <row r="115" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="3">
-        <v>46262</v>
+        <v>46232</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>281</v>
+        <v>15</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>282</v>
+        <v>175</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E115" s="3">
-        <v>46297</v>
+        <v>46302</v>
       </c>
       <c r="F115" s="5">
-        <v>7694.4</v>
+        <v>9716</v>
       </c>
       <c r="G115" s="5">
-        <v>7694.4</v>
+        <v>9716</v>
       </c>
       <c r="H115" s="3"/>
       <c r="I115" s="6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J115" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K115" s="4" t="s">
-        <v>284</v>
+        <v>39</v>
       </c>
       <c r="L115" s="4"/>
       <c r="M115" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N115" s="4"/>
       <c r="O115" s="4"/>
     </row>
     <row r="116" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="3">
-        <v>46265</v>
+        <v>46253</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>241</v>
+        <v>194</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E116" s="3">
-        <v>46295</v>
+        <v>46302</v>
       </c>
       <c r="F116" s="5">
-        <v>8947.5</v>
+        <v>10080</v>
       </c>
       <c r="G116" s="5">
-        <v>8947.5</v>
+        <v>10080</v>
       </c>
       <c r="H116" s="3"/>
       <c r="I116" s="6">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J116" s="4" t="s">
         <v>181</v>
       </c>
       <c r="K116" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="L116" s="4"/>
       <c r="M116" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="N116" s="4"/>
       <c r="O116" s="4"/>
     </row>
     <row r="117" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="3">
-        <v>46265</v>
+        <v>46253</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>294</v>
+        <v>227</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E117" s="3">
-        <v>46295</v>
+        <v>46302</v>
       </c>
       <c r="F117" s="5">
-        <v>4750</v>
+        <v>1660.33</v>
       </c>
       <c r="G117" s="5">
-        <v>8565.68</v>
+        <v>1660.33</v>
       </c>
       <c r="H117" s="3"/>
       <c r="I117" s="6">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J117" s="4" t="s">
-        <v>181</v>
+        <v>18</v>
       </c>
       <c r="K117" s="4" t="s">
-        <v>58</v>
+        <v>124</v>
       </c>
       <c r="L117" s="4"/>
       <c r="M117" s="4" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="N117" s="4"/>
       <c r="O117" s="4"/>
     </row>
     <row r="118" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="3">
-        <v>46265</v>
+        <v>46253</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>25</v>
+        <v>121</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>297</v>
+        <v>227</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="E118" s="3">
-        <v>46293</v>
+        <v>46302</v>
       </c>
       <c r="F118" s="5">
-        <v>1664</v>
+        <v>3640</v>
       </c>
       <c r="G118" s="5">
-        <v>1664</v>
+        <v>3640</v>
       </c>
       <c r="H118" s="3"/>
       <c r="I118" s="6">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J118" s="4" t="s">
-        <v>18</v>
+        <v>181</v>
       </c>
       <c r="K118" s="4" t="s">
-        <v>71</v>
+        <v>124</v>
       </c>
       <c r="L118" s="4"/>
       <c r="M118" s="4" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="N118" s="4"/>
       <c r="O118" s="4"/>
     </row>
     <row r="119" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="3">
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C119" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D119" s="4" t="s">
         <v>297</v>
       </c>
-      <c r="D119" s="4" t="s">
-        <v>300</v>
-      </c>
       <c r="E119" s="3">
-        <v>46300</v>
+        <v>46303</v>
       </c>
       <c r="F119" s="5">
-        <v>1664</v>
+        <v>2754</v>
       </c>
       <c r="G119" s="5">
-        <v>1664</v>
+        <v>2754</v>
       </c>
       <c r="H119" s="3"/>
       <c r="I119" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J119" s="4" t="s">
-        <v>18</v>
+        <v>187</v>
       </c>
       <c r="K119" s="4" t="s">
         <v>71</v>
       </c>
       <c r="L119" s="4"/>
       <c r="M119" s="4" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="N119" s="4"/>
       <c r="O119" s="4"/>
-    </row>
-    <row r="120" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="3">
-        <v>46266</v>
-      </c>
-      <c r="B120" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="C120" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="D120" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="E120" s="3">
-        <v>46296</v>
-      </c>
-      <c r="F120" s="5">
-        <v>8973.5</v>
-      </c>
-      <c r="G120" s="5">
-        <v>8973.5</v>
-      </c>
-      <c r="H120" s="3"/>
-      <c r="I120" s="6">
-        <v>6</v>
-      </c>
-      <c r="J120" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="K120" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="L120" s="4"/>
-      <c r="M120" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="N120" s="4"/>
-      <c r="O120" s="4"/>
-    </row>
-    <row r="121" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="3">
-        <v>46266</v>
-      </c>
-      <c r="B121" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C121" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="D121" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="E121" s="3">
-        <v>46287</v>
-      </c>
-      <c r="F121" s="5">
-        <v>18600</v>
-      </c>
-      <c r="G121" s="5">
-        <v>18600</v>
-      </c>
-      <c r="H121" s="3"/>
-      <c r="I121" s="6">
-        <v>15</v>
-      </c>
-      <c r="J121" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K121" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="L121" s="4"/>
-      <c r="M121" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="N121" s="4"/>
-      <c r="O121" s="4"/>
-    </row>
-    <row r="122" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="3">
-        <v>46266</v>
-      </c>
-      <c r="B122" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C122" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="D122" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="E122" s="3">
-        <v>46294</v>
-      </c>
-      <c r="F122" s="5">
-        <v>18600</v>
-      </c>
-      <c r="G122" s="5">
-        <v>18600</v>
-      </c>
-      <c r="H122" s="3"/>
-      <c r="I122" s="6">
-        <v>8</v>
-      </c>
-      <c r="J122" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K122" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="L122" s="4"/>
-      <c r="M122" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="N122" s="4"/>
-      <c r="O122" s="4"/>
-    </row>
-    <row r="123" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="3">
-        <v>46266</v>
-      </c>
-      <c r="B123" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C123" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="D123" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="E123" s="3">
-        <v>46301</v>
-      </c>
-      <c r="F123" s="5">
-        <v>18600</v>
-      </c>
-      <c r="G123" s="5">
-        <v>18600</v>
-      </c>
-      <c r="H123" s="3"/>
-      <c r="I123" s="6">
-        <v>1</v>
-      </c>
-      <c r="J123" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K123" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="L123" s="4"/>
-      <c r="M123" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="N123" s="4"/>
-      <c r="O123" s="4"/>
-    </row>
-    <row r="124" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="3">
-        <v>46268</v>
-      </c>
-      <c r="B124" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C124" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="D124" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="E124" s="3">
-        <v>46296</v>
-      </c>
-      <c r="F124" s="5">
-        <v>2754</v>
-      </c>
-      <c r="G124" s="5">
-        <v>2754</v>
-      </c>
-      <c r="H124" s="3"/>
-      <c r="I124" s="6">
-        <v>6</v>
-      </c>
-      <c r="J124" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="K124" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="L124" s="4"/>
-      <c r="M124" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="N124" s="4"/>
-      <c r="O124" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
+++ b/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WINDOWS\Desktop\dados planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49654609-7B74-4183-ADC7-B85F903F133F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B66C2A8E-7023-4143-8F70-BAE77AAF06DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="304">
   <si>
     <t>Dt.Emissão</t>
   </si>
@@ -72,9 +72,609 @@
     <t>Centro de Custo</t>
   </si>
   <si>
+    <t>JOSEMAR - BA</t>
+  </si>
+  <si>
+    <t>PHARMACEUTICA DISTRIBUIDORA DE MAT. E MED. HOSPITA</t>
+  </si>
+  <si>
+    <t>01005217.1BPBPBPBP</t>
+  </si>
+  <si>
+    <t>BA</t>
+  </si>
+  <si>
+    <t>01005217.2BP</t>
+  </si>
+  <si>
+    <t>MALCA - CE</t>
+  </si>
+  <si>
+    <t>BR MEDICAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>01005144.3</t>
+  </si>
+  <si>
+    <t>CE</t>
+  </si>
+  <si>
+    <t>01005217.3BPBPBP</t>
+  </si>
+  <si>
+    <t>01006508.1</t>
+  </si>
+  <si>
+    <t>01006508.2</t>
+  </si>
+  <si>
+    <t>01006508.3</t>
+  </si>
+  <si>
+    <t>MARCELO LOPES</t>
+  </si>
+  <si>
+    <t>GRADUAL COMERCIO E SERVICOS LTDA</t>
+  </si>
+  <si>
+    <t>01006433.3BP</t>
+  </si>
+  <si>
+    <t>PB</t>
+  </si>
+  <si>
+    <t>FAROMED COMERCIO DE MATERIAIS HOSPITALARES LTDA</t>
+  </si>
+  <si>
+    <t>01001617.1</t>
+  </si>
+  <si>
+    <t>BANCO DO BRASIL</t>
+  </si>
+  <si>
+    <t>PE</t>
+  </si>
+  <si>
+    <t>00191964000001264870000003473568000002622117</t>
+  </si>
+  <si>
+    <t>01001548.3</t>
+  </si>
+  <si>
+    <t>00193965200000384000000003473568000002617517</t>
+  </si>
+  <si>
+    <t>01001617.2</t>
+  </si>
+  <si>
+    <t>00191965400000816000000003473568000002622217</t>
+  </si>
+  <si>
+    <t>01001617.3</t>
+  </si>
+  <si>
+    <t>00192966800000816000000003473568000002622317</t>
+  </si>
+  <si>
+    <t>MARIO JR - PE/PB/RN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RN COMERCIO DE MEDICAMENTOS E MATERIAL HOSPITALAR </t>
+  </si>
+  <si>
+    <t>01003504.1</t>
+  </si>
+  <si>
+    <t>RN</t>
+  </si>
+  <si>
+    <t>00191999500002541000000003473568000002851217</t>
+  </si>
+  <si>
+    <t>01003504.2</t>
+  </si>
+  <si>
+    <t>00195100200002541000000003473568000002851317</t>
+  </si>
+  <si>
+    <t>01003504.4</t>
+  </si>
+  <si>
+    <t>00194101600002541000000003473568000002851517</t>
+  </si>
+  <si>
+    <t>01003504.6</t>
+  </si>
+  <si>
+    <t>00193103000002541000000003473568000002851717</t>
+  </si>
+  <si>
+    <t>AGILE DISTRIBUIDORA LTDA</t>
+  </si>
+  <si>
+    <t>01003847.2</t>
+  </si>
+  <si>
+    <t>00196107900002287070000003473568000002883717</t>
+  </si>
+  <si>
+    <t>01003847.3</t>
+  </si>
+  <si>
+    <t>00193108600002287060000003473568000002883817</t>
+  </si>
+  <si>
+    <t>ISA COMERCIO VAREJISTA DE PRODUTOS HOSPITALARES LT</t>
+  </si>
+  <si>
+    <t>01004522.1</t>
+  </si>
+  <si>
+    <t>00191118600004572620000003473568000002940517</t>
+  </si>
+  <si>
+    <t>01004522.2</t>
+  </si>
+  <si>
+    <t>00191120000003663840000003473568000002940617</t>
+  </si>
+  <si>
+    <t>01004522.3</t>
+  </si>
+  <si>
+    <t>00193121400003663840000003473568000002940717</t>
+  </si>
+  <si>
+    <t>FOCUS - COMERCIO DE MEDICAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>01004900.1</t>
+  </si>
+  <si>
+    <t>00192123700003867340000003473568000002964017</t>
+  </si>
+  <si>
+    <t>01004900.2</t>
+  </si>
+  <si>
+    <t>00192124400002144590000003473568000002964117</t>
+  </si>
+  <si>
+    <t>01004900.3</t>
+  </si>
+  <si>
+    <t>00197125100002144590000003473568000002964217</t>
+  </si>
+  <si>
+    <t>01004900.4</t>
+  </si>
+  <si>
+    <t>00191125800002144590000003473568000002964317</t>
+  </si>
+  <si>
+    <t>01005075.3</t>
+  </si>
+  <si>
+    <t>00195127000004480000000003473568000002981317</t>
+  </si>
+  <si>
+    <t>DENTAL SORRISO LTDA</t>
+  </si>
+  <si>
+    <t>01005781.1</t>
+  </si>
+  <si>
+    <t>00194138000000806340000003473568000003029417</t>
+  </si>
+  <si>
+    <t>01005781.2</t>
+  </si>
+  <si>
+    <t>00194138700000503280000003473568000003029517</t>
+  </si>
+  <si>
+    <t>01005781.3</t>
+  </si>
+  <si>
+    <t>00199139400000503280000003473568000003029617</t>
+  </si>
+  <si>
+    <t>MARCOS DUTRA - PI</t>
+  </si>
+  <si>
+    <t>ALIANCA DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>01006753.5</t>
+  </si>
+  <si>
+    <t>PI</t>
+  </si>
+  <si>
+    <t>00197154900000860000000003473568000003129017</t>
+  </si>
+  <si>
+    <t>01006941.2</t>
+  </si>
+  <si>
+    <t>00195154900002818370000003473568000003141117</t>
+  </si>
+  <si>
     <t>DANILO - AL/SE/BA</t>
   </si>
   <si>
+    <t>JT COSTA COMERCIAL LTDA</t>
+  </si>
+  <si>
+    <t>01007005.1</t>
+  </si>
+  <si>
+    <t>SE</t>
+  </si>
+  <si>
+    <t>00197155200018957860000003473568000003145817</t>
+  </si>
+  <si>
+    <t>01007005.2</t>
+  </si>
+  <si>
+    <t>00193156200009716000000003473568000003145917</t>
+  </si>
+  <si>
+    <t>01006941.4</t>
+  </si>
+  <si>
+    <t>00194156300002818370000003473568000003141317</t>
+  </si>
+  <si>
+    <t>01006941.5</t>
+  </si>
+  <si>
+    <t>00191157000002818360000003473568000003141417</t>
+  </si>
+  <si>
+    <t>01007005.3</t>
+  </si>
+  <si>
+    <t>00196157200009716000000003473568000003146017</t>
+  </si>
+  <si>
+    <t>CIRURGICA MONTEBELLO LTDA</t>
+  </si>
+  <si>
+    <t>01007301.1</t>
+  </si>
+  <si>
+    <t>00192157700018600000000003473568000003161317</t>
+  </si>
+  <si>
+    <t>FELIPE AQUINO - MT</t>
+  </si>
+  <si>
+    <t>FAMA DISTRIBUIDORA HOSPITALAR LTDA</t>
+  </si>
+  <si>
+    <t>01007265.1</t>
+  </si>
+  <si>
+    <t>MT</t>
+  </si>
+  <si>
+    <t>00198158000007694400000003473568000003158817</t>
+  </si>
+  <si>
+    <t>01007005.4</t>
+  </si>
+  <si>
+    <t>00197158200009716000000003473568000003146117</t>
+  </si>
+  <si>
+    <t>01007301.2</t>
+  </si>
+  <si>
+    <t>00197158400018600000000003473568000003161417</t>
+  </si>
+  <si>
+    <t>01007265.2</t>
+  </si>
+  <si>
+    <t>00192158700007694400000003473568000003158917</t>
+  </si>
+  <si>
+    <t>01007301.3</t>
+  </si>
+  <si>
+    <t>00191159100018600000000003473568000003161517</t>
+  </si>
+  <si>
+    <t>01007005.5</t>
+  </si>
+  <si>
+    <t>00198159200009716000000003473568000003146217</t>
+  </si>
+  <si>
+    <t>A. M. FARMA MEDICAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>01007018.3</t>
+  </si>
+  <si>
+    <t>00195159400005556100000003473568000003149117</t>
+  </si>
+  <si>
+    <t>01007265.3</t>
+  </si>
+  <si>
+    <t>00199159400007694400000003473568000003159017</t>
+  </si>
+  <si>
+    <t>ALINE CERBINO - PA</t>
+  </si>
+  <si>
+    <t>CRISTALFARMA COMERCIO IMPORT E EXPORT LTDA</t>
+  </si>
+  <si>
+    <t>01006976.1</t>
+  </si>
+  <si>
+    <t>BRADESCO</t>
+  </si>
+  <si>
+    <t>PA</t>
+  </si>
+  <si>
+    <t>23791156200006389240435090000000114600304920</t>
+  </si>
+  <si>
+    <t>01006976.2</t>
+  </si>
+  <si>
+    <t>23791157700004216670435090000000114700304920</t>
+  </si>
+  <si>
+    <t>COBERMED COMERCIO DE MATERIAIS MEDICOS LTDA</t>
+  </si>
+  <si>
+    <t>01006877.3</t>
+  </si>
+  <si>
+    <t>AL</t>
+  </si>
+  <si>
+    <t>23797158300006265000435090000000110700304920</t>
+  </si>
+  <si>
+    <t>ATACAMED COMERCIO LTDA</t>
+  </si>
+  <si>
+    <t>01007311.1</t>
+  </si>
+  <si>
+    <t>23796158600002754000435090000000130000304920</t>
+  </si>
+  <si>
+    <t>01006976.3</t>
+  </si>
+  <si>
+    <t>23792159200004216660435090000000114800304920</t>
+  </si>
+  <si>
+    <t>01007311.2</t>
+  </si>
+  <si>
+    <t>23792159300002754000435090000000130100304920</t>
+  </si>
+  <si>
+    <t>01006920.1</t>
+  </si>
+  <si>
+    <t>DAYCOVAL</t>
+  </si>
+  <si>
+    <t>70797156000011442870001121205064100656763979</t>
+  </si>
+  <si>
+    <t>PLENA DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>01006922.1</t>
+  </si>
+  <si>
+    <t>70795156300011200000001121205064100656763870</t>
+  </si>
+  <si>
+    <t>01007187.1</t>
+  </si>
+  <si>
+    <t>70791156400010080000001121205064100656766188</t>
+  </si>
+  <si>
+    <t>01006958.5</t>
+  </si>
+  <si>
+    <t>70799156600023168600001121205064100656764084</t>
+  </si>
+  <si>
+    <t>01007023.1</t>
+  </si>
+  <si>
+    <t>70799156900005741360001121205064100656764415</t>
+  </si>
+  <si>
+    <t>01007187.2</t>
+  </si>
+  <si>
+    <t>70791157100010080000001121205064100656766196</t>
+  </si>
+  <si>
+    <t>01006958.6</t>
+  </si>
+  <si>
+    <t>70798157300023168600001121205064100656764092</t>
+  </si>
+  <si>
+    <t>01006922.2</t>
+  </si>
+  <si>
+    <t>70792157300011200000001121205064100656763888</t>
+  </si>
+  <si>
+    <t>01006957.2</t>
+  </si>
+  <si>
+    <t>70792157400010666670001121205064100656763953</t>
+  </si>
+  <si>
+    <t>01006999.1</t>
+  </si>
+  <si>
+    <t>70799157400006500000001121205064100656764282</t>
+  </si>
+  <si>
+    <t>01007020.1</t>
+  </si>
+  <si>
+    <t>70799157400004950170001121205064100656764449</t>
+  </si>
+  <si>
+    <t>01006920.2</t>
+  </si>
+  <si>
+    <t>70794157500007551880001121205064100656763987</t>
+  </si>
+  <si>
+    <t>01007125.4</t>
+  </si>
+  <si>
+    <t>70791157600004320000001121205064100656765123</t>
+  </si>
+  <si>
+    <t>01007187.3</t>
+  </si>
+  <si>
+    <t>70793157800010080000001121205064100656766204</t>
+  </si>
+  <si>
+    <t>DROGUISTA CEARENSE LTDA</t>
+  </si>
+  <si>
+    <t>01007171.2</t>
+  </si>
+  <si>
+    <t>70794157800003640000001121205064100656766162</t>
+  </si>
+  <si>
+    <t>01007194.1</t>
+  </si>
+  <si>
+    <t>70797157900006265000001121205064100656766642</t>
+  </si>
+  <si>
+    <t>01007249.1</t>
+  </si>
+  <si>
+    <t>70793158000011660110001121205064100656766915</t>
+  </si>
+  <si>
+    <t>FERMATA LTDA</t>
+  </si>
+  <si>
+    <t>01006989.2</t>
+  </si>
+  <si>
+    <t>70795158200004082050001121205064100656764191</t>
+  </si>
+  <si>
+    <t>01007125.5</t>
+  </si>
+  <si>
+    <t>70799158300004320000001121205064100656765131</t>
+  </si>
+  <si>
+    <t>01006922.3</t>
+  </si>
+  <si>
+    <t>70798158300011200000001121205064100656763896</t>
+  </si>
+  <si>
+    <t>01007023.2</t>
+  </si>
+  <si>
+    <t>70791158400003789090001121205064100656764423</t>
+  </si>
+  <si>
+    <t>01007187.4</t>
+  </si>
+  <si>
+    <t>70792158500010080000001121205064100656766212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZOE MED COMERCIO DE PRODUTOS MEDICOS HOSPITALARES </t>
+  </si>
+  <si>
+    <t>01007270.1</t>
+  </si>
+  <si>
+    <t>70793158500008565680001121205064100656766972</t>
+  </si>
+  <si>
+    <t>ELIENE RESENDE - RJ</t>
+  </si>
+  <si>
+    <t>MEDKA DISTRIBUIDORA HOSPITALAR LTDA</t>
+  </si>
+  <si>
+    <t>01007278.1</t>
+  </si>
+  <si>
+    <t>RJ</t>
+  </si>
+  <si>
+    <t>70793158600008973500001121205064100656767319</t>
+  </si>
+  <si>
+    <t>01007249.2</t>
+  </si>
+  <si>
+    <t>70792158700011660110001121205064100656766923</t>
+  </si>
+  <si>
+    <t>01006920.3</t>
+  </si>
+  <si>
+    <t>70797159000007551880001121205064100656763995</t>
+  </si>
+  <si>
+    <t>01007187.5</t>
+  </si>
+  <si>
+    <t>70791159200010080000001121205064100656766220</t>
+  </si>
+  <si>
+    <t>AMAZONIA HOSPITALAR LTDA</t>
+  </si>
+  <si>
+    <t>01007224.3</t>
+  </si>
+  <si>
+    <t>MA</t>
+  </si>
+  <si>
+    <t>70793159400002992000001121205064100656766873</t>
+  </si>
+  <si>
+    <t>01007194.2</t>
+  </si>
+  <si>
+    <t>70793159400006265000001121205064100656766659</t>
+  </si>
+  <si>
+    <t>01007249.3</t>
+  </si>
+  <si>
+    <t>70791159400011660110001121205064100656766931</t>
+  </si>
+  <si>
     <t>RB DISTRIBUIDORA DE PRODUTOS HOSPITALARES LTDA</t>
   </si>
   <si>
@@ -84,9 +684,6 @@
     <t>ITAU</t>
   </si>
   <si>
-    <t>AL</t>
-  </si>
-  <si>
     <t>34192961600009391781090001019578120992717000</t>
   </si>
   <si>
@@ -96,57 +693,18 @@
     <t>34194963600005418001090001019738120992717000</t>
   </si>
   <si>
-    <t>MARCELO LOPES</t>
-  </si>
-  <si>
-    <t>FAROMED COMERCIO DE MATERIAIS HOSPITALARES LTDA</t>
-  </si>
-  <si>
-    <t>01001617.1</t>
-  </si>
-  <si>
-    <t>BANCO DO BRASIL</t>
-  </si>
-  <si>
-    <t>PE</t>
-  </si>
-  <si>
-    <t>00191964000001264870000003473568000002622117</t>
-  </si>
-  <si>
     <t>01001504.4</t>
   </si>
   <si>
     <t>34194964600005418001090001019818120992717000</t>
   </si>
   <si>
-    <t>01001548.3</t>
-  </si>
-  <si>
-    <t>00193965200000384000000003473568000002617517</t>
-  </si>
-  <si>
-    <t>01001617.2</t>
-  </si>
-  <si>
-    <t>00191965400000816000000003473568000002622217</t>
-  </si>
-  <si>
-    <t>01001617.3</t>
-  </si>
-  <si>
-    <t>00192966800000816000000003473568000002622317</t>
-  </si>
-  <si>
     <t>VEC HOSPITALAR LTDA ME</t>
   </si>
   <si>
     <t>01002233.1</t>
   </si>
   <si>
-    <t>SE</t>
-  </si>
-  <si>
     <t>34192975300001674521090001106858120992717000</t>
   </si>
   <si>
@@ -162,9 +720,6 @@
     <t>34191981300000873601090001107278120992717000</t>
   </si>
   <si>
-    <t>MARIO JR - PE/PB/RN</t>
-  </si>
-  <si>
     <t>GLOBAL MEDIC LTDA</t>
   </si>
   <si>
@@ -189,9 +744,6 @@
     <t>01002991.3</t>
   </si>
   <si>
-    <t>BA</t>
-  </si>
-  <si>
     <t>34196989800004439901090001240908120992717000</t>
   </si>
   <si>
@@ -240,21 +792,12 @@
     <t>01003384.3</t>
   </si>
   <si>
-    <t>PB</t>
-  </si>
-  <si>
     <t>34191997800001118401090001280758120992717000</t>
   </si>
   <si>
-    <t xml:space="preserve">RN COMERCIO DE MEDICAMENTOS E MATERIAL HOSPITALAR </t>
-  </si>
-  <si>
     <t>01003464.4</t>
   </si>
   <si>
-    <t>RN</t>
-  </si>
-  <si>
     <t>34194998500003296801090001307668120992717000</t>
   </si>
   <si>
@@ -270,30 +813,12 @@
     <t>34198999200003296801090001307748120992717000</t>
   </si>
   <si>
-    <t>01003504.1</t>
-  </si>
-  <si>
-    <t>00191999500002541000000003473568000002851217</t>
-  </si>
-  <si>
     <t>01003464.6</t>
   </si>
   <si>
     <t>34191999900003296801090001307828120992717000</t>
   </si>
   <si>
-    <t>01003504.2</t>
-  </si>
-  <si>
-    <t>00195100200002541000000003473568000002851317</t>
-  </si>
-  <si>
-    <t>01003504.4</t>
-  </si>
-  <si>
-    <t>00194101600002541000000003473568000002851517</t>
-  </si>
-  <si>
     <t>01003589.1</t>
   </si>
   <si>
@@ -315,12 +840,6 @@
     <t>34194102400001154561090001320448120992717000</t>
   </si>
   <si>
-    <t>01003504.6</t>
-  </si>
-  <si>
-    <t>00193103000002541000000003473568000002851717</t>
-  </si>
-  <si>
     <t>01003589.3</t>
   </si>
   <si>
@@ -390,123 +909,6 @@
     <t>34191107900003800001090001356908120992717000</t>
   </si>
   <si>
-    <t>MALCA - CE</t>
-  </si>
-  <si>
-    <t>AGILE DISTRIBUIDORA LTDA</t>
-  </si>
-  <si>
-    <t>01003847.2</t>
-  </si>
-  <si>
-    <t>CE</t>
-  </si>
-  <si>
-    <t>00196107900002287070000003473568000002883717</t>
-  </si>
-  <si>
-    <t>01003847.3</t>
-  </si>
-  <si>
-    <t>00193108600002287060000003473568000002883817</t>
-  </si>
-  <si>
-    <t>ISA COMERCIO VAREJISTA DE PRODUTOS HOSPITALARES LT</t>
-  </si>
-  <si>
-    <t>01004522.1</t>
-  </si>
-  <si>
-    <t>00191118600004572620000003473568000002940517</t>
-  </si>
-  <si>
-    <t>01004522.2</t>
-  </si>
-  <si>
-    <t>00191120000003663840000003473568000002940617</t>
-  </si>
-  <si>
-    <t>01004522.3</t>
-  </si>
-  <si>
-    <t>00193121400003663840000003473568000002940717</t>
-  </si>
-  <si>
-    <t>JOSEMAR - BA</t>
-  </si>
-  <si>
-    <t>FOCUS - COMERCIO DE MEDICAMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>01004900.1</t>
-  </si>
-  <si>
-    <t>00192123700003867340000003473568000002964017</t>
-  </si>
-  <si>
-    <t>01004900.2</t>
-  </si>
-  <si>
-    <t>00192124400002144590000003473568000002964117</t>
-  </si>
-  <si>
-    <t>01004900.3</t>
-  </si>
-  <si>
-    <t>00197125100002144590000003473568000002964217</t>
-  </si>
-  <si>
-    <t>01004900.4</t>
-  </si>
-  <si>
-    <t>00191125800002144590000003473568000002964317</t>
-  </si>
-  <si>
-    <t>PHARMACEUTICA DISTRIBUIDORA DE MAT. E MED. HOSPITA</t>
-  </si>
-  <si>
-    <t>01005217.1BPBPBPBP</t>
-  </si>
-  <si>
-    <t>BR MEDICAMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>01005075.3</t>
-  </si>
-  <si>
-    <t>00195127000004480000000003473568000002981317</t>
-  </si>
-  <si>
-    <t>01005217.2BP</t>
-  </si>
-  <si>
-    <t>01005144.3</t>
-  </si>
-  <si>
-    <t>01005217.3BPBPBP</t>
-  </si>
-  <si>
-    <t>DENTAL SORRISO LTDA</t>
-  </si>
-  <si>
-    <t>01005781.1</t>
-  </si>
-  <si>
-    <t>00194138000000806340000003473568000003029417</t>
-  </si>
-  <si>
-    <t>01005781.2</t>
-  </si>
-  <si>
-    <t>00194138700000503280000003473568000003029517</t>
-  </si>
-  <si>
-    <t>01005781.3</t>
-  </si>
-  <si>
-    <t>00199139400000503280000003473568000003029617</t>
-  </si>
-  <si>
     <t>MAIS SAUDE COMERCIO DE PRODUTOS HOSPITALARES LTDA</t>
   </si>
   <si>
@@ -516,306 +918,12 @@
     <t>34199139500005466661090002533378120992717000</t>
   </si>
   <si>
-    <t>01006508.1</t>
-  </si>
-  <si>
-    <t>01006508.2</t>
-  </si>
-  <si>
-    <t>01006508.3</t>
-  </si>
-  <si>
-    <t>GRADUAL COMERCIO E SERVICOS LTDA</t>
-  </si>
-  <si>
-    <t>01006433.3BP</t>
-  </si>
-  <si>
-    <t>MARCOS DUTRA - PI</t>
-  </si>
-  <si>
-    <t>ALIANCA DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>01006753.5</t>
-  </si>
-  <si>
-    <t>PI</t>
-  </si>
-  <si>
-    <t>00197154900000860000000003473568000003129017</t>
-  </si>
-  <si>
-    <t>01006941.2</t>
-  </si>
-  <si>
-    <t>00195154900002818370000003473568000003141117</t>
-  </si>
-  <si>
-    <t>JT COSTA COMERCIAL LTDA</t>
-  </si>
-  <si>
-    <t>01007005.1</t>
-  </si>
-  <si>
-    <t>00197155200018957860000003473568000003145817</t>
-  </si>
-  <si>
-    <t>ALINE CERBINO - PA</t>
-  </si>
-  <si>
-    <t>CRISTALFARMA COMERCIO IMPORT E EXPORT LTDA</t>
-  </si>
-  <si>
-    <t>01006920.1</t>
-  </si>
-  <si>
-    <t>DAYCOVAL</t>
-  </si>
-  <si>
-    <t>PA</t>
-  </si>
-  <si>
-    <t>70797156000011442870001121205064100656763979</t>
-  </si>
-  <si>
-    <t>01007005.2</t>
-  </si>
-  <si>
-    <t>00193156200009716000000003473568000003145917</t>
-  </si>
-  <si>
-    <t>01006976.1</t>
-  </si>
-  <si>
-    <t>BRADESCO</t>
-  </si>
-  <si>
-    <t>23791156200006389240435090000000114600304920</t>
-  </si>
-  <si>
-    <t>01006941.4</t>
-  </si>
-  <si>
-    <t>00194156300002818370000003473568000003141317</t>
-  </si>
-  <si>
-    <t>PLENA DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>01006922.1</t>
-  </si>
-  <si>
-    <t>70795156300011200000001121205064100656763870</t>
-  </si>
-  <si>
-    <t>CIRURGICA MONTEBELLO LTDA</t>
-  </si>
-  <si>
-    <t>01007187.1</t>
-  </si>
-  <si>
-    <t>70791156400010080000001121205064100656766188</t>
-  </si>
-  <si>
-    <t>01006958.5</t>
-  </si>
-  <si>
-    <t>70799156600023168600001121205064100656764084</t>
-  </si>
-  <si>
-    <t>01007023.1</t>
-  </si>
-  <si>
-    <t>70799156900005741360001121205064100656764415</t>
-  </si>
-  <si>
-    <t>01006941.5</t>
-  </si>
-  <si>
-    <t>00191157000002818360000003473568000003141417</t>
-  </si>
-  <si>
-    <t>01007187.2</t>
-  </si>
-  <si>
-    <t>70791157100010080000001121205064100656766196</t>
-  </si>
-  <si>
-    <t>01007005.3</t>
-  </si>
-  <si>
-    <t>00196157200009716000000003473568000003146017</t>
-  </si>
-  <si>
-    <t>01006958.6</t>
-  </si>
-  <si>
-    <t>70798157300023168600001121205064100656764092</t>
-  </si>
-  <si>
-    <t>01006922.2</t>
-  </si>
-  <si>
-    <t>70792157300011200000001121205064100656763888</t>
-  </si>
-  <si>
-    <t>01006957.2</t>
-  </si>
-  <si>
-    <t>70792157400010666670001121205064100656763953</t>
-  </si>
-  <si>
-    <t>01006999.1</t>
-  </si>
-  <si>
-    <t>70799157400006500000001121205064100656764282</t>
-  </si>
-  <si>
-    <t>01007020.1</t>
-  </si>
-  <si>
-    <t>70799157400004950170001121205064100656764449</t>
-  </si>
-  <si>
-    <t>01006920.2</t>
-  </si>
-  <si>
-    <t>70794157500007551880001121205064100656763987</t>
-  </si>
-  <si>
-    <t>01007125.4</t>
-  </si>
-  <si>
-    <t>70791157600004320000001121205064100656765123</t>
-  </si>
-  <si>
-    <t>01007301.1</t>
-  </si>
-  <si>
-    <t>00192157700018600000000003473568000003161317</t>
-  </si>
-  <si>
-    <t>01006976.2</t>
-  </si>
-  <si>
-    <t>23791157700004216670435090000000114700304920</t>
-  </si>
-  <si>
-    <t>01007187.3</t>
-  </si>
-  <si>
-    <t>70793157800010080000001121205064100656766204</t>
-  </si>
-  <si>
-    <t>DROGUISTA CEARENSE LTDA</t>
-  </si>
-  <si>
     <t>01007175.2</t>
   </si>
   <si>
     <t>34193157800001660331090002618768120992717000</t>
   </si>
   <si>
-    <t>01007171.2</t>
-  </si>
-  <si>
-    <t>70794157800003640000001121205064100656766162</t>
-  </si>
-  <si>
-    <t>COBERMED COMERCIO DE MATERIAIS MEDICOS LTDA</t>
-  </si>
-  <si>
-    <t>01007194.1</t>
-  </si>
-  <si>
-    <t>70797157900006265000001121205064100656766642</t>
-  </si>
-  <si>
-    <t>FELIPE AQUINO - MT</t>
-  </si>
-  <si>
-    <t>FAMA DISTRIBUIDORA HOSPITALAR LTDA</t>
-  </si>
-  <si>
-    <t>01007265.1</t>
-  </si>
-  <si>
-    <t>MT</t>
-  </si>
-  <si>
-    <t>00198158000007694400000003473568000003158817</t>
-  </si>
-  <si>
-    <t>01007249.1</t>
-  </si>
-  <si>
-    <t>70793158000011660110001121205064100656766915</t>
-  </si>
-  <si>
-    <t>FERMATA LTDA</t>
-  </si>
-  <si>
-    <t>01006989.2</t>
-  </si>
-  <si>
-    <t>70795158200004082050001121205064100656764191</t>
-  </si>
-  <si>
-    <t>01007005.4</t>
-  </si>
-  <si>
-    <t>00197158200009716000000003473568000003146117</t>
-  </si>
-  <si>
-    <t>01006877.3</t>
-  </si>
-  <si>
-    <t>23797158300006265000435090000000110700304920</t>
-  </si>
-  <si>
-    <t>01007125.5</t>
-  </si>
-  <si>
-    <t>70799158300004320000001121205064100656765131</t>
-  </si>
-  <si>
-    <t>01006922.3</t>
-  </si>
-  <si>
-    <t>70798158300011200000001121205064100656763896</t>
-  </si>
-  <si>
-    <t>01007301.2</t>
-  </si>
-  <si>
-    <t>00197158400018600000000003473568000003161417</t>
-  </si>
-  <si>
-    <t>01007023.2</t>
-  </si>
-  <si>
-    <t>70791158400003789090001121205064100656764423</t>
-  </si>
-  <si>
-    <t>01007187.4</t>
-  </si>
-  <si>
-    <t>70792158500010080000001121205064100656766212</t>
-  </si>
-  <si>
-    <t>01007171.3</t>
-  </si>
-  <si>
-    <t>70793158500003640000001121205064100656766170</t>
-  </si>
-  <si>
-    <t>01007175.3</t>
-  </si>
-  <si>
-    <t>34194158500001660341090002618848120992717000</t>
-  </si>
-  <si>
     <t>VITAL DISTRIBUIDORA LTDA</t>
   </si>
   <si>
@@ -825,103 +933,10 @@
     <t>34196158500002051221090002617698120992717000</t>
   </si>
   <si>
-    <t xml:space="preserve">ZOE MED COMERCIO DE PRODUTOS MEDICOS HOSPITALARES </t>
-  </si>
-  <si>
-    <t>01007270.1</t>
-  </si>
-  <si>
-    <t>70793158500008565680001121205064100656766972</t>
-  </si>
-  <si>
-    <t>ATACAMED COMERCIO LTDA</t>
-  </si>
-  <si>
-    <t>01007311.1</t>
-  </si>
-  <si>
-    <t>23796158600002754000435090000000130000304920</t>
-  </si>
-  <si>
-    <t>ELIENE RESENDE - RJ</t>
-  </si>
-  <si>
-    <t>MEDKA DISTRIBUIDORA HOSPITALAR LTDA</t>
-  </si>
-  <si>
-    <t>01007278.1</t>
-  </si>
-  <si>
-    <t>RJ</t>
-  </si>
-  <si>
-    <t>70793158600008973500001121205064100656767319</t>
-  </si>
-  <si>
-    <t>01007249.2</t>
-  </si>
-  <si>
-    <t>70792158700011660110001121205064100656766923</t>
-  </si>
-  <si>
-    <t>01007265.2</t>
-  </si>
-  <si>
-    <t>00192158700007694400000003473568000003158917</t>
-  </si>
-  <si>
-    <t>01006920.3</t>
-  </si>
-  <si>
-    <t>70797159000007551880001121205064100656763995</t>
-  </si>
-  <si>
     <t>01007274.2</t>
   </si>
   <si>
     <t>34192159000001664001090002623538120992717000</t>
-  </si>
-  <si>
-    <t>01007301.3</t>
-  </si>
-  <si>
-    <t>00191159100018600000000003473568000003161517</t>
-  </si>
-  <si>
-    <t>01006976.3</t>
-  </si>
-  <si>
-    <t>23792159200004216660435090000000114800304920</t>
-  </si>
-  <si>
-    <t>01007005.5</t>
-  </si>
-  <si>
-    <t>00198159200009716000000003473568000003146217</t>
-  </si>
-  <si>
-    <t>01007187.5</t>
-  </si>
-  <si>
-    <t>70791159200010080000001121205064100656766220</t>
-  </si>
-  <si>
-    <t>01007175.1</t>
-  </si>
-  <si>
-    <t>34194159200001660331090002618688120992717000</t>
-  </si>
-  <si>
-    <t>01007171.1</t>
-  </si>
-  <si>
-    <t>70791159200003640000001121205064100656766154</t>
-  </si>
-  <si>
-    <t>01007311.2</t>
-  </si>
-  <si>
-    <t>23792159300002754000435090000000130100304920</t>
   </si>
 </sst>
 </file>
@@ -1351,7 +1366,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O119"/>
+  <dimension ref="A1:O120"/>
   <sheetFormatPr defaultColWidth="12.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.85546875" style="1" customWidth="1"/>
@@ -1421,7 +1436,7 @@
     </row>
     <row r="2" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
-        <v>45296</v>
+        <v>45959</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>15</v>
@@ -1433,34 +1448,30 @@
         <v>17</v>
       </c>
       <c r="E2" s="3">
-        <v>45326</v>
+        <v>45980</v>
       </c>
       <c r="F2" s="5">
-        <v>5418</v>
+        <v>28666.44</v>
       </c>
       <c r="G2" s="5">
-        <v>9391.7800000000007</v>
+        <v>28666.44</v>
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="6">
-        <v>978</v>
-      </c>
-      <c r="J2" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="K2" s="4" t="s">
-        <v>19</v>
-      </c>
       <c r="L2" s="4"/>
-      <c r="M2" s="4" t="s">
-        <v>20</v>
-      </c>
+      <c r="M2" s="4"/>
       <c r="N2" s="4"/>
       <c r="O2" s="4"/>
     </row>
     <row r="3" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
-        <v>45296</v>
+        <v>45959</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>15</v>
@@ -1469,76 +1480,68 @@
         <v>16</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E3" s="3">
-        <v>45346</v>
+        <v>45987</v>
       </c>
       <c r="F3" s="5">
-        <v>5418</v>
+        <v>33844.160000000003</v>
       </c>
       <c r="G3" s="5">
-        <v>5418</v>
+        <v>33844.160000000003</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="6">
-        <v>958</v>
-      </c>
-      <c r="J3" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="4" t="s">
-        <v>19</v>
-      </c>
       <c r="L3" s="4"/>
-      <c r="M3" s="4" t="s">
-        <v>22</v>
-      </c>
+      <c r="M3" s="4"/>
       <c r="N3" s="4"/>
       <c r="O3" s="4"/>
     </row>
     <row r="4" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
-        <v>45322</v>
+        <v>45947</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E4" s="3">
-        <v>45350</v>
+        <v>45989</v>
       </c>
       <c r="F4" s="5">
-        <v>816</v>
+        <v>3220</v>
       </c>
       <c r="G4" s="5">
-        <v>1264.8699999999999</v>
+        <v>3220</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="6">
-        <v>954</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>26</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="J4" s="4"/>
       <c r="K4" s="4" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="L4" s="4"/>
-      <c r="M4" s="4" t="s">
-        <v>28</v>
-      </c>
+      <c r="M4" s="4"/>
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
     </row>
     <row r="5" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
-        <v>45296</v>
+        <v>45959</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>15</v>
@@ -1547,1664 +1550,1644 @@
         <v>16</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E5" s="3">
-        <v>45356</v>
+        <v>45994</v>
       </c>
       <c r="F5" s="5">
-        <v>5418</v>
+        <v>14483.06</v>
       </c>
       <c r="G5" s="5">
-        <v>5418</v>
+        <v>14483.06</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="6">
-        <v>948</v>
-      </c>
-      <c r="J5" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="K5" s="4" t="s">
-        <v>19</v>
-      </c>
       <c r="L5" s="4"/>
-      <c r="M5" s="4" t="s">
-        <v>30</v>
-      </c>
+      <c r="M5" s="4"/>
       <c r="N5" s="4"/>
       <c r="O5" s="4"/>
     </row>
     <row r="6" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
-        <v>45306</v>
+        <v>46171</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="E6" s="3">
-        <v>45362</v>
+        <v>46192</v>
       </c>
       <c r="F6" s="5">
-        <v>384</v>
+        <v>4676.8500000000004</v>
       </c>
       <c r="G6" s="5">
-        <v>384</v>
+        <v>7494.53</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="6">
-        <v>942</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>26</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="J6" s="4"/>
       <c r="K6" s="4" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="L6" s="4"/>
-      <c r="M6" s="4" t="s">
-        <v>32</v>
-      </c>
+      <c r="M6" s="4"/>
       <c r="N6" s="4"/>
       <c r="O6" s="4"/>
     </row>
     <row r="7" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
-        <v>45322</v>
+        <v>46171</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="E7" s="3">
-        <v>45364</v>
+        <v>46199</v>
       </c>
       <c r="F7" s="5">
-        <v>816</v>
+        <v>4676.8500000000004</v>
       </c>
       <c r="G7" s="5">
-        <v>816</v>
+        <v>4676.8500000000004</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="6">
-        <v>940</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>26</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="J7" s="4"/>
       <c r="K7" s="4" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="L7" s="4"/>
-      <c r="M7" s="4" t="s">
-        <v>34</v>
-      </c>
+      <c r="M7" s="4"/>
       <c r="N7" s="4"/>
       <c r="O7" s="4"/>
     </row>
     <row r="8" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
-        <v>45322</v>
+        <v>46171</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="E8" s="3">
-        <v>45378</v>
+        <v>46206</v>
       </c>
       <c r="F8" s="5">
-        <v>816</v>
+        <v>4676.8500000000004</v>
       </c>
       <c r="G8" s="5">
-        <v>816</v>
+        <v>4676.8500000000004</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="6">
-        <v>926</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>26</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="J8" s="4"/>
       <c r="K8" s="4" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="L8" s="4"/>
-      <c r="M8" s="4" t="s">
-        <v>36</v>
-      </c>
+      <c r="M8" s="4"/>
       <c r="N8" s="4"/>
       <c r="O8" s="4"/>
     </row>
     <row r="9" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
-        <v>45433</v>
+        <v>46162</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="E9" s="3">
-        <v>45463</v>
+        <v>46222</v>
       </c>
       <c r="F9" s="5">
-        <v>873.6</v>
+        <v>22349.79</v>
       </c>
       <c r="G9" s="5">
-        <v>1674.52</v>
+        <v>22349.79</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="6">
-        <v>841</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>18</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="J9" s="4"/>
       <c r="K9" s="4" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="L9" s="4"/>
-      <c r="M9" s="4" t="s">
-        <v>40</v>
-      </c>
+      <c r="M9" s="4"/>
       <c r="N9" s="4"/>
       <c r="O9" s="4"/>
     </row>
     <row r="10" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
-        <v>45433</v>
+        <v>45322</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E10" s="3">
-        <v>45493</v>
+        <v>45350</v>
       </c>
       <c r="F10" s="5">
-        <v>873.6</v>
+        <v>816</v>
       </c>
       <c r="G10" s="5">
-        <v>873.6</v>
+        <v>1264.8699999999999</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="6">
-        <v>811</v>
+        <v>958</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="L10" s="4"/>
       <c r="M10" s="4" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="N10" s="4"/>
       <c r="O10" s="4"/>
     </row>
     <row r="11" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
-        <v>45433</v>
+        <v>45306</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C11" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="E11" s="3">
-        <v>45523</v>
+        <v>45362</v>
       </c>
       <c r="F11" s="5">
-        <v>873.6</v>
+        <v>384</v>
       </c>
       <c r="G11" s="5">
-        <v>873.6</v>
+        <v>384</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="6">
-        <v>781</v>
+        <v>946</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="L11" s="4"/>
       <c r="M11" s="4" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="N11" s="4"/>
       <c r="O11" s="4"/>
     </row>
     <row r="12" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
-        <v>45558</v>
+        <v>45322</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="E12" s="3">
-        <v>45600</v>
+        <v>45364</v>
       </c>
       <c r="F12" s="5">
-        <v>2000</v>
+        <v>816</v>
       </c>
       <c r="G12" s="5">
-        <v>2000</v>
+        <v>816</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="6">
-        <v>704</v>
+        <v>944</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="L12" s="4"/>
       <c r="M12" s="4" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="N12" s="4"/>
       <c r="O12" s="4"/>
     </row>
     <row r="13" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
-        <v>45558</v>
+        <v>45322</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="E13" s="3">
-        <v>45607</v>
+        <v>45378</v>
       </c>
       <c r="F13" s="5">
-        <v>2000</v>
+        <v>816</v>
       </c>
       <c r="G13" s="5">
-        <v>3204.34</v>
+        <v>816</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="6">
-        <v>697</v>
+        <v>930</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="L13" s="4"/>
       <c r="M13" s="4" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N13" s="4"/>
       <c r="O13" s="4"/>
     </row>
     <row r="14" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
-        <v>45552</v>
+        <v>45677</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="E14" s="3">
-        <v>45608</v>
+        <v>45705</v>
       </c>
       <c r="F14" s="5">
-        <v>4439.8999999999996</v>
+        <v>2541</v>
       </c>
       <c r="G14" s="5">
-        <v>4439.8999999999996</v>
+        <v>2541</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="6">
-        <v>696</v>
+        <v>603</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="L14" s="4"/>
       <c r="M14" s="4" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="N14" s="4"/>
       <c r="O14" s="4"/>
     </row>
     <row r="15" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
-        <v>45558</v>
+        <v>45677</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="E15" s="3">
-        <v>45614</v>
+        <v>45712</v>
       </c>
       <c r="F15" s="5">
-        <v>2000</v>
+        <v>2541</v>
       </c>
       <c r="G15" s="5">
-        <v>2000</v>
+        <v>2541</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="6">
-        <v>690</v>
+        <v>596</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="L15" s="4"/>
       <c r="M15" s="4" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="N15" s="4"/>
       <c r="O15" s="4"/>
     </row>
     <row r="16" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
-        <v>45546</v>
+        <v>45677</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E16" s="3">
-        <v>45615</v>
+        <v>45726</v>
       </c>
       <c r="F16" s="5">
-        <v>1216.8599999999999</v>
+        <v>2541</v>
       </c>
       <c r="G16" s="5">
-        <v>1216.8599999999999</v>
+        <v>2541</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="6">
-        <v>689</v>
+        <v>582</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="L16" s="4"/>
       <c r="M16" s="4" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="N16" s="4"/>
       <c r="O16" s="4"/>
     </row>
     <row r="17" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
-        <v>45548</v>
+        <v>45677</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="E17" s="3">
-        <v>45617</v>
+        <v>45740</v>
       </c>
       <c r="F17" s="5">
-        <v>1843.87</v>
+        <v>2541</v>
       </c>
       <c r="G17" s="5">
-        <v>1843.87</v>
+        <v>2541</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="6">
-        <v>687</v>
+        <v>568</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="L17" s="4"/>
       <c r="M17" s="4" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="N17" s="4"/>
       <c r="O17" s="4"/>
     </row>
     <row r="18" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
-        <v>45546</v>
+        <v>45754</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E18" s="3">
-        <v>45622</v>
+        <v>45789</v>
       </c>
       <c r="F18" s="5">
-        <v>1216.8599999999999</v>
+        <v>2287.0700000000002</v>
       </c>
       <c r="G18" s="5">
-        <v>1216.8599999999999</v>
+        <v>1143.54</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="6">
-        <v>682</v>
+        <v>519</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="L18" s="4"/>
       <c r="M18" s="4" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="N18" s="4"/>
       <c r="O18" s="4"/>
     </row>
     <row r="19" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
-        <v>45552</v>
+        <v>45754</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E19" s="3">
-        <v>45622</v>
+        <v>45796</v>
       </c>
       <c r="F19" s="5">
-        <v>4439.8999999999996</v>
+        <v>2287.06</v>
       </c>
       <c r="G19" s="5">
-        <v>4439.8999999999996</v>
+        <v>2287.06</v>
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="6">
-        <v>682</v>
+        <v>512</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="L19" s="4"/>
       <c r="M19" s="4" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N19" s="4"/>
       <c r="O19" s="4"/>
     </row>
     <row r="20" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
-        <v>45548</v>
+        <v>45868</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E20" s="3">
-        <v>45624</v>
+        <v>45896</v>
       </c>
       <c r="F20" s="5">
-        <v>1843.88</v>
+        <v>3663.84</v>
       </c>
       <c r="G20" s="5">
-        <v>1843.88</v>
+        <v>4572.62</v>
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="6">
-        <v>680</v>
+        <v>412</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L20" s="4"/>
       <c r="M20" s="4" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="N20" s="4"/>
       <c r="O20" s="4"/>
     </row>
     <row r="21" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
-        <v>45632</v>
+        <v>45868</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E21" s="3">
-        <v>45688</v>
+        <v>45910</v>
       </c>
       <c r="F21" s="5">
-        <v>1118.4000000000001</v>
+        <v>3663.84</v>
       </c>
       <c r="G21" s="5">
-        <v>1118.4000000000001</v>
+        <v>3663.84</v>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="6">
-        <v>616</v>
+        <v>398</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>71</v>
+        <v>31</v>
       </c>
       <c r="L21" s="4"/>
       <c r="M21" s="4" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="N21" s="4"/>
       <c r="O21" s="4"/>
     </row>
     <row r="22" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
-        <v>45646</v>
+        <v>45868</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="E22" s="3">
-        <v>45695</v>
+        <v>45924</v>
       </c>
       <c r="F22" s="5">
-        <v>3296.8</v>
+        <v>3663.84</v>
       </c>
       <c r="G22" s="5">
-        <v>3296.8</v>
+        <v>3663.84</v>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="6">
-        <v>609</v>
+        <v>384</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>75</v>
+        <v>31</v>
       </c>
       <c r="L22" s="4"/>
       <c r="M22" s="4" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="N22" s="4"/>
       <c r="O22" s="4"/>
     </row>
     <row r="23" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
-        <v>45636</v>
+        <v>45919</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="E23" s="3">
-        <v>45699</v>
+        <v>45947</v>
       </c>
       <c r="F23" s="5">
-        <v>2330</v>
+        <v>2144.59</v>
       </c>
       <c r="G23" s="5">
-        <v>2330</v>
+        <v>3867.34</v>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="6">
-        <v>605</v>
+        <v>361</v>
       </c>
       <c r="J23" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K23" s="4" t="s">
         <v>18</v>
-      </c>
-      <c r="K23" s="4" t="s">
-        <v>75</v>
       </c>
       <c r="L23" s="4"/>
       <c r="M23" s="4" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="N23" s="4"/>
       <c r="O23" s="4"/>
     </row>
     <row r="24" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
-        <v>45646</v>
+        <v>45919</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="E24" s="3">
-        <v>45702</v>
+        <v>45954</v>
       </c>
       <c r="F24" s="5">
-        <v>3296.8</v>
+        <v>2144.59</v>
       </c>
       <c r="G24" s="5">
-        <v>3296.8</v>
+        <v>2144.59</v>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="6">
-        <v>602</v>
+        <v>354</v>
       </c>
       <c r="J24" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K24" s="4" t="s">
         <v>18</v>
-      </c>
-      <c r="K24" s="4" t="s">
-        <v>75</v>
       </c>
       <c r="L24" s="4"/>
       <c r="M24" s="4" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="N24" s="4"/>
       <c r="O24" s="4"/>
     </row>
     <row r="25" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
-        <v>45677</v>
+        <v>45919</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="E25" s="3">
-        <v>45705</v>
+        <v>45961</v>
       </c>
       <c r="F25" s="5">
-        <v>2541</v>
+        <v>2144.59</v>
       </c>
       <c r="G25" s="5">
-        <v>2541</v>
+        <v>2144.59</v>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="6">
-        <v>599</v>
+        <v>347</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="L25" s="4"/>
       <c r="M25" s="4" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="N25" s="4"/>
       <c r="O25" s="4"/>
     </row>
     <row r="26" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
-        <v>45646</v>
+        <v>45919</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="C26" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D26" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="D26" s="4" t="s">
-        <v>83</v>
-      </c>
       <c r="E26" s="3">
-        <v>45709</v>
+        <v>45968</v>
       </c>
       <c r="F26" s="5">
-        <v>3296.8</v>
+        <v>2144.59</v>
       </c>
       <c r="G26" s="5">
-        <v>3296.8</v>
+        <v>2144.59</v>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="6">
-        <v>595</v>
+        <v>340</v>
       </c>
       <c r="J26" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K26" s="4" t="s">
         <v>18</v>
-      </c>
-      <c r="K26" s="4" t="s">
-        <v>75</v>
       </c>
       <c r="L26" s="4"/>
       <c r="M26" s="4" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="N26" s="4"/>
       <c r="O26" s="4"/>
     </row>
     <row r="27" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
-        <v>45677</v>
+        <v>45938</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>73</v>
+        <v>21</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="E27" s="3">
-        <v>45712</v>
+        <v>45980</v>
       </c>
       <c r="F27" s="5">
-        <v>2541</v>
+        <v>4480</v>
       </c>
       <c r="G27" s="5">
-        <v>2541</v>
+        <v>4480</v>
       </c>
       <c r="H27" s="3"/>
       <c r="I27" s="6">
-        <v>592</v>
+        <v>328</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="L27" s="4"/>
       <c r="M27" s="4" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="N27" s="4"/>
       <c r="O27" s="4"/>
     </row>
     <row r="28" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
-        <v>45677</v>
+        <v>46062</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="E28" s="3">
-        <v>45726</v>
+        <v>46090</v>
       </c>
       <c r="F28" s="5">
-        <v>2541</v>
+        <v>503.28</v>
       </c>
       <c r="G28" s="5">
-        <v>2541</v>
+        <v>806.34</v>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="6">
-        <v>578</v>
+        <v>218</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="L28" s="4"/>
       <c r="M28" s="4" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="N28" s="4"/>
       <c r="O28" s="4"/>
     </row>
     <row r="29" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
-        <v>45699</v>
+        <v>46062</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="E29" s="3">
-        <v>45727</v>
+        <v>46097</v>
       </c>
       <c r="F29" s="5">
-        <v>7562.78</v>
+        <v>503.28</v>
       </c>
       <c r="G29" s="5">
-        <v>7562.78</v>
+        <v>503.28</v>
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="6">
-        <v>577</v>
+        <v>211</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="L29" s="4"/>
       <c r="M29" s="4" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="N29" s="4"/>
       <c r="O29" s="4"/>
     </row>
     <row r="30" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
-        <v>45699</v>
+        <v>46062</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="E30" s="3">
-        <v>45734</v>
+        <v>46104</v>
       </c>
       <c r="F30" s="5">
-        <v>7562.78</v>
+        <v>503.28</v>
       </c>
       <c r="G30" s="5">
-        <v>7562.78</v>
+        <v>503.28</v>
       </c>
       <c r="H30" s="3"/>
       <c r="I30" s="6">
-        <v>570</v>
+        <v>204</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="L30" s="4"/>
       <c r="M30" s="4" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="N30" s="4"/>
       <c r="O30" s="4"/>
     </row>
     <row r="31" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
-        <v>45699</v>
+        <v>46203</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="E31" s="3">
-        <v>45734</v>
+        <v>46259</v>
       </c>
       <c r="F31" s="5">
-        <v>1154.56</v>
+        <v>860</v>
       </c>
       <c r="G31" s="5">
-        <v>1154.56</v>
+        <v>860</v>
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="6">
-        <v>570</v>
+        <v>49</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="L31" s="4"/>
       <c r="M31" s="4" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="N31" s="4"/>
       <c r="O31" s="4"/>
     </row>
     <row r="32" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
-        <v>45677</v>
+        <v>46224</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="E32" s="3">
-        <v>45740</v>
+        <v>46259</v>
       </c>
       <c r="F32" s="5">
-        <v>2541</v>
+        <v>2818.37</v>
       </c>
       <c r="G32" s="5">
-        <v>2541</v>
+        <v>2818.37</v>
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="6">
-        <v>564</v>
+        <v>49</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="L32" s="4"/>
       <c r="M32" s="4" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="N32" s="4"/>
       <c r="O32" s="4"/>
     </row>
     <row r="33" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
-        <v>45699</v>
+        <v>46232</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>45</v>
+        <v>91</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="E33" s="3">
-        <v>45741</v>
+        <v>46262</v>
       </c>
       <c r="F33" s="5">
-        <v>7562.78</v>
+        <v>9716</v>
       </c>
       <c r="G33" s="5">
-        <v>7562.78</v>
+        <v>18957.86</v>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="6">
-        <v>563</v>
+        <v>46</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="L33" s="4"/>
       <c r="M33" s="4" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N33" s="4"/>
       <c r="O33" s="4"/>
     </row>
     <row r="34" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
-        <v>45699</v>
+        <v>46232</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E34" s="3">
-        <v>45741</v>
+        <v>46272</v>
       </c>
       <c r="F34" s="5">
-        <v>1154.56</v>
+        <v>9716</v>
       </c>
       <c r="G34" s="5">
-        <v>1154.56</v>
+        <v>9716</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="6">
-        <v>563</v>
+        <v>36</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>54</v>
+        <v>94</v>
       </c>
       <c r="L34" s="4"/>
       <c r="M34" s="4" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="N34" s="4"/>
       <c r="O34" s="4"/>
     </row>
     <row r="35" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
-        <v>45699</v>
+        <v>46224</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E35" s="3">
-        <v>45748</v>
+        <v>46273</v>
       </c>
       <c r="F35" s="5">
-        <v>1154.56</v>
+        <v>2818.37</v>
       </c>
       <c r="G35" s="5">
-        <v>1154.56</v>
+        <v>2818.37</v>
       </c>
       <c r="H35" s="3"/>
       <c r="I35" s="6">
-        <v>556</v>
+        <v>35</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="L35" s="4"/>
       <c r="M35" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="N35" s="4"/>
       <c r="O35" s="4"/>
     </row>
     <row r="36" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
-        <v>45699</v>
+        <v>46224</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E36" s="3">
-        <v>45748</v>
+        <v>46280</v>
       </c>
       <c r="F36" s="5">
-        <v>7562.76</v>
+        <v>2818.36</v>
       </c>
       <c r="G36" s="5">
-        <v>7562.76</v>
+        <v>2818.36</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="6">
-        <v>556</v>
+        <v>28</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="L36" s="4"/>
       <c r="M36" s="4" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="N36" s="4"/>
       <c r="O36" s="4"/>
     </row>
     <row r="37" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
-        <v>45699</v>
+        <v>46232</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E37" s="3">
-        <v>45755</v>
+        <v>46282</v>
       </c>
       <c r="F37" s="5">
-        <v>1154.56</v>
+        <v>9716</v>
       </c>
       <c r="G37" s="5">
-        <v>1154.56</v>
+        <v>9716</v>
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="6">
-        <v>549</v>
+        <v>26</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>54</v>
+        <v>94</v>
       </c>
       <c r="L37" s="4"/>
       <c r="M37" s="4" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="N37" s="4"/>
       <c r="O37" s="4"/>
     </row>
     <row r="38" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
-        <v>45733</v>
+        <v>46266</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E38" s="3">
-        <v>45761</v>
+        <v>46287</v>
       </c>
       <c r="F38" s="5">
-        <v>3850</v>
+        <v>18600</v>
       </c>
       <c r="G38" s="5">
-        <v>6169.53</v>
+        <v>18600</v>
       </c>
       <c r="H38" s="3"/>
       <c r="I38" s="6">
-        <v>543</v>
+        <v>21</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="L38" s="4"/>
       <c r="M38" s="4" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="N38" s="4"/>
       <c r="O38" s="4"/>
     </row>
     <row r="39" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
-        <v>45733</v>
+        <v>46262</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>51</v>
+        <v>107</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>108</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E39" s="3">
-        <v>45768</v>
+        <v>46290</v>
       </c>
       <c r="F39" s="5">
-        <v>3850</v>
+        <v>7694.4</v>
       </c>
       <c r="G39" s="5">
-        <v>3850</v>
+        <v>7694.4</v>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="6">
-        <v>536</v>
+        <v>18</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="K39" s="4" t="s">
-        <v>54</v>
+        <v>110</v>
       </c>
       <c r="L39" s="4"/>
       <c r="M39" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N39" s="4"/>
       <c r="O39" s="4"/>
     </row>
     <row r="40" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
-        <v>45733</v>
+        <v>46232</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E40" s="3">
-        <v>45775</v>
+        <v>46292</v>
       </c>
       <c r="F40" s="5">
-        <v>3850</v>
+        <v>9716</v>
       </c>
       <c r="G40" s="5">
-        <v>3850</v>
+        <v>9716</v>
       </c>
       <c r="H40" s="3"/>
       <c r="I40" s="6">
-        <v>529</v>
+        <v>16</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="K40" s="4" t="s">
-        <v>54</v>
+        <v>94</v>
       </c>
       <c r="L40" s="4"/>
       <c r="M40" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="N40" s="4"/>
       <c r="O40" s="4"/>
     </row>
     <row r="41" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
-        <v>45747</v>
+        <v>46266</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E41" s="3">
-        <v>45775</v>
+        <v>46294</v>
       </c>
       <c r="F41" s="5">
-        <v>3800</v>
+        <v>18600</v>
       </c>
       <c r="G41" s="5">
-        <v>6089.41</v>
+        <v>18600</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="6">
-        <v>529</v>
+        <v>14</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="K41" s="4" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="L41" s="4"/>
       <c r="M41" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N41" s="4"/>
       <c r="O41" s="4"/>
     </row>
     <row r="42" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
-        <v>45747</v>
+        <v>46262</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>51</v>
+        <v>107</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>108</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E42" s="3">
-        <v>45782</v>
+        <v>46297</v>
       </c>
       <c r="F42" s="5">
-        <v>3800</v>
+        <v>7694.4</v>
       </c>
       <c r="G42" s="5">
-        <v>3800</v>
+        <v>7694.4</v>
       </c>
       <c r="H42" s="3"/>
       <c r="I42" s="6">
-        <v>522</v>
+        <v>11</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="K42" s="4" t="s">
-        <v>54</v>
+        <v>110</v>
       </c>
       <c r="L42" s="4"/>
       <c r="M42" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N42" s="4"/>
       <c r="O42" s="4"/>
     </row>
     <row r="43" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
-        <v>45747</v>
+        <v>46266</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E43" s="3">
-        <v>45789</v>
+        <v>46301</v>
       </c>
       <c r="F43" s="5">
-        <v>3800</v>
+        <v>18600</v>
       </c>
       <c r="G43" s="5">
-        <v>3800</v>
+        <v>18600</v>
       </c>
       <c r="H43" s="3"/>
       <c r="I43" s="6">
-        <v>515</v>
+        <v>7</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="K43" s="4" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="L43" s="4"/>
       <c r="M43" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="N43" s="4"/>
       <c r="O43" s="4"/>
     </row>
     <row r="44" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
-        <v>45754</v>
+        <v>46232</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>122</v>
+        <v>92</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E44" s="3">
-        <v>45789</v>
+        <v>46302</v>
       </c>
       <c r="F44" s="5">
-        <v>2287.0700000000002</v>
+        <v>9716</v>
       </c>
       <c r="G44" s="5">
-        <v>1143.54</v>
+        <v>9716</v>
       </c>
       <c r="H44" s="3"/>
       <c r="I44" s="6">
-        <v>515</v>
+        <v>6</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="K44" s="4" t="s">
-        <v>124</v>
+        <v>94</v>
       </c>
       <c r="L44" s="4"/>
       <c r="M44" s="4" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="N44" s="4"/>
       <c r="O44" s="4"/>
     </row>
     <row r="45" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
-        <v>45754</v>
+        <v>46234</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>122</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E45" s="3">
-        <v>45796</v>
+        <v>46304</v>
       </c>
       <c r="F45" s="5">
-        <v>2287.06</v>
+        <v>5556.1</v>
       </c>
       <c r="G45" s="5">
-        <v>2287.06</v>
+        <v>5556.1</v>
       </c>
       <c r="H45" s="3"/>
       <c r="I45" s="6">
-        <v>508</v>
+        <v>4</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>124</v>
+        <v>87</v>
       </c>
       <c r="L45" s="4"/>
       <c r="M45" s="4" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="N45" s="4"/>
       <c r="O45" s="4"/>
     </row>
     <row r="46" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
-        <v>45868</v>
+        <v>46262</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>45</v>
+        <v>107</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E46" s="3">
-        <v>45896</v>
+        <v>46304</v>
       </c>
       <c r="F46" s="5">
-        <v>3663.84</v>
+        <v>7694.4</v>
       </c>
       <c r="G46" s="5">
-        <v>4572.62</v>
+        <v>7694.4</v>
       </c>
       <c r="H46" s="3"/>
       <c r="I46" s="6">
-        <v>408</v>
+        <v>4</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="K46" s="4" t="s">
-        <v>71</v>
+        <v>110</v>
       </c>
       <c r="L46" s="4"/>
       <c r="M46" s="4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="N46" s="4"/>
       <c r="O46" s="4"/>
     </row>
     <row r="47" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
-        <v>45868</v>
+        <v>46227</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>45</v>
+        <v>127</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>128</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E47" s="3">
-        <v>45910</v>
+        <v>46272</v>
       </c>
       <c r="F47" s="5">
-        <v>3663.84</v>
+        <v>4216.67</v>
       </c>
       <c r="G47" s="5">
-        <v>3663.84</v>
+        <v>6389.24</v>
       </c>
       <c r="H47" s="3"/>
       <c r="I47" s="6">
-        <v>394</v>
+        <v>36</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>26</v>
+        <v>130</v>
       </c>
       <c r="K47" s="4" t="s">
-        <v>71</v>
+        <v>131</v>
       </c>
       <c r="L47" s="4"/>
       <c r="M47" s="4" t="s">
@@ -3215,10 +3198,10 @@
     </row>
     <row r="48" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
-        <v>45868</v>
+        <v>46227</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>45</v>
+        <v>127</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>128</v>
@@ -3227,23 +3210,23 @@
         <v>133</v>
       </c>
       <c r="E48" s="3">
-        <v>45924</v>
+        <v>46287</v>
       </c>
       <c r="F48" s="5">
-        <v>3663.84</v>
+        <v>4216.67</v>
       </c>
       <c r="G48" s="5">
-        <v>3663.84</v>
+        <v>4216.67</v>
       </c>
       <c r="H48" s="3"/>
       <c r="I48" s="6">
-        <v>380</v>
+        <v>21</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>26</v>
+        <v>130</v>
       </c>
       <c r="K48" s="4" t="s">
-        <v>71</v>
+        <v>131</v>
       </c>
       <c r="L48" s="4"/>
       <c r="M48" s="4" t="s">
@@ -3254,35 +3237,35 @@
     </row>
     <row r="49" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
-        <v>45919</v>
+        <v>46223</v>
       </c>
       <c r="B49" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C49" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="C49" s="4" t="s">
+      <c r="D49" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="D49" s="4" t="s">
-        <v>137</v>
-      </c>
       <c r="E49" s="3">
-        <v>45947</v>
+        <v>46293</v>
       </c>
       <c r="F49" s="5">
-        <v>2144.59</v>
+        <v>6265</v>
       </c>
       <c r="G49" s="5">
-        <v>3867.34</v>
+        <v>6265</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="6">
-        <v>357</v>
+        <v>15</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>26</v>
+        <v>130</v>
       </c>
       <c r="K49" s="4" t="s">
-        <v>54</v>
+        <v>137</v>
       </c>
       <c r="L49" s="4"/>
       <c r="M49" s="4" t="s">
@@ -3293,748 +3276,780 @@
     </row>
     <row r="50" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
-        <v>45919</v>
+        <v>46268</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>135</v>
+        <v>28</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E50" s="3">
-        <v>45954</v>
+        <v>46296</v>
       </c>
       <c r="F50" s="5">
-        <v>2144.59</v>
+        <v>2754</v>
       </c>
       <c r="G50" s="5">
-        <v>2144.59</v>
+        <v>2754</v>
       </c>
       <c r="H50" s="3"/>
       <c r="I50" s="6">
-        <v>350</v>
+        <v>12</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>26</v>
+        <v>130</v>
       </c>
       <c r="K50" s="4" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="L50" s="4"/>
       <c r="M50" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N50" s="4"/>
       <c r="O50" s="4"/>
     </row>
     <row r="51" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
-        <v>45919</v>
+        <v>46227</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E51" s="3">
-        <v>45961</v>
+        <v>46302</v>
       </c>
       <c r="F51" s="5">
-        <v>2144.59</v>
+        <v>4216.66</v>
       </c>
       <c r="G51" s="5">
-        <v>2144.59</v>
+        <v>4216.66</v>
       </c>
       <c r="H51" s="3"/>
       <c r="I51" s="6">
-        <v>343</v>
+        <v>6</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>26</v>
+        <v>130</v>
       </c>
       <c r="K51" s="4" t="s">
-        <v>54</v>
+        <v>131</v>
       </c>
       <c r="L51" s="4"/>
       <c r="M51" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N51" s="4"/>
       <c r="O51" s="4"/>
     </row>
     <row r="52" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
-        <v>45919</v>
+        <v>46268</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>135</v>
+        <v>28</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E52" s="3">
-        <v>45968</v>
+        <v>46303</v>
       </c>
       <c r="F52" s="5">
-        <v>2144.59</v>
+        <v>2754</v>
       </c>
       <c r="G52" s="5">
-        <v>2144.59</v>
+        <v>2754</v>
       </c>
       <c r="H52" s="3"/>
       <c r="I52" s="6">
-        <v>336</v>
+        <v>5</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>26</v>
+        <v>130</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="L52" s="4"/>
       <c r="M52" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N52" s="4"/>
       <c r="O52" s="4"/>
     </row>
     <row r="53" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
-        <v>45959</v>
+        <v>46225</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="D53" s="4" t="s">
         <v>146</v>
       </c>
       <c r="E53" s="3">
-        <v>45980</v>
+        <v>46270</v>
       </c>
       <c r="F53" s="5">
-        <v>28666.44</v>
+        <v>7551.88</v>
       </c>
       <c r="G53" s="5">
-        <v>28666.44</v>
+        <v>11442.87</v>
       </c>
       <c r="H53" s="3"/>
       <c r="I53" s="6">
-        <v>324</v>
-      </c>
-      <c r="J53" s="4"/>
+        <v>38</v>
+      </c>
+      <c r="J53" s="4" t="s">
+        <v>147</v>
+      </c>
       <c r="K53" s="4" t="s">
-        <v>54</v>
+        <v>131</v>
       </c>
       <c r="L53" s="4"/>
-      <c r="M53" s="4"/>
+      <c r="M53" s="4" t="s">
+        <v>148</v>
+      </c>
       <c r="N53" s="4"/>
       <c r="O53" s="4"/>
     </row>
     <row r="54" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
-        <v>45938</v>
+        <v>46223</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>121</v>
+        <v>43</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E54" s="3">
-        <v>45980</v>
+        <v>46273</v>
       </c>
       <c r="F54" s="5">
-        <v>4480</v>
+        <v>11200</v>
       </c>
       <c r="G54" s="5">
-        <v>4480</v>
+        <v>11200</v>
       </c>
       <c r="H54" s="3"/>
       <c r="I54" s="6">
-        <v>324</v>
+        <v>35</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>26</v>
+        <v>147</v>
       </c>
       <c r="K54" s="4" t="s">
-        <v>124</v>
+        <v>35</v>
       </c>
       <c r="L54" s="4"/>
       <c r="M54" s="4" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="N54" s="4"/>
       <c r="O54" s="4"/>
     </row>
     <row r="55" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
-        <v>45959</v>
+        <v>46253</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>135</v>
+        <v>43</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>145</v>
+        <v>104</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E55" s="3">
-        <v>45987</v>
+        <v>46274</v>
       </c>
       <c r="F55" s="5">
-        <v>33844.160000000003</v>
+        <v>10080</v>
       </c>
       <c r="G55" s="5">
-        <v>33844.160000000003</v>
+        <v>10080</v>
       </c>
       <c r="H55" s="3"/>
       <c r="I55" s="6">
-        <v>317</v>
-      </c>
-      <c r="J55" s="4"/>
+        <v>34</v>
+      </c>
+      <c r="J55" s="4" t="s">
+        <v>147</v>
+      </c>
       <c r="K55" s="4" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="L55" s="4"/>
-      <c r="M55" s="4"/>
+      <c r="M55" s="4" t="s">
+        <v>153</v>
+      </c>
       <c r="N55" s="4"/>
       <c r="O55" s="4"/>
     </row>
     <row r="56" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
-        <v>45947</v>
+        <v>46227</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>121</v>
+        <v>43</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>147</v>
+        <v>104</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E56" s="3">
-        <v>45989</v>
+        <v>46276</v>
       </c>
       <c r="F56" s="5">
-        <v>3220</v>
+        <v>23168.6</v>
       </c>
       <c r="G56" s="5">
-        <v>3220</v>
+        <v>23168.6</v>
       </c>
       <c r="H56" s="3"/>
       <c r="I56" s="6">
-        <v>315</v>
-      </c>
-      <c r="J56" s="4"/>
+        <v>32</v>
+      </c>
+      <c r="J56" s="4" t="s">
+        <v>147</v>
+      </c>
       <c r="K56" s="4" t="s">
-        <v>124</v>
+        <v>35</v>
       </c>
       <c r="L56" s="4"/>
-      <c r="M56" s="4"/>
+      <c r="M56" s="4" t="s">
+        <v>155</v>
+      </c>
       <c r="N56" s="4"/>
       <c r="O56" s="4"/>
     </row>
     <row r="57" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
-        <v>45959</v>
+        <v>46234</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E57" s="3">
-        <v>45994</v>
+        <v>46279</v>
       </c>
       <c r="F57" s="5">
-        <v>14483.06</v>
+        <v>3789.09</v>
       </c>
       <c r="G57" s="5">
-        <v>14483.06</v>
+        <v>5741.36</v>
       </c>
       <c r="H57" s="3"/>
       <c r="I57" s="6">
-        <v>310</v>
-      </c>
-      <c r="J57" s="4"/>
+        <v>29</v>
+      </c>
+      <c r="J57" s="4" t="s">
+        <v>147</v>
+      </c>
       <c r="K57" s="4" t="s">
-        <v>54</v>
+        <v>131</v>
       </c>
       <c r="L57" s="4"/>
-      <c r="M57" s="4"/>
+      <c r="M57" s="4" t="s">
+        <v>157</v>
+      </c>
       <c r="N57" s="4"/>
       <c r="O57" s="4"/>
     </row>
     <row r="58" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
-        <v>46062</v>
+        <v>46253</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>153</v>
+        <v>104</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E58" s="3">
-        <v>46090</v>
+        <v>46281</v>
       </c>
       <c r="F58" s="5">
-        <v>503.28</v>
+        <v>10080</v>
       </c>
       <c r="G58" s="5">
-        <v>806.34</v>
+        <v>10080</v>
       </c>
       <c r="H58" s="3"/>
       <c r="I58" s="6">
-        <v>214</v>
+        <v>27</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>26</v>
+        <v>147</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="L58" s="4"/>
       <c r="M58" s="4" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="N58" s="4"/>
       <c r="O58" s="4"/>
     </row>
     <row r="59" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
-        <v>46062</v>
+        <v>46227</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>153</v>
+        <v>104</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E59" s="3">
-        <v>46097</v>
+        <v>46283</v>
       </c>
       <c r="F59" s="5">
-        <v>503.28</v>
+        <v>23168.6</v>
       </c>
       <c r="G59" s="5">
-        <v>503.28</v>
+        <v>23168.6</v>
       </c>
       <c r="H59" s="3"/>
       <c r="I59" s="6">
-        <v>207</v>
+        <v>25</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>26</v>
+        <v>147</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="L59" s="4"/>
       <c r="M59" s="4" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="N59" s="4"/>
       <c r="O59" s="4"/>
     </row>
     <row r="60" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
-        <v>46062</v>
+        <v>46223</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="E60" s="3">
-        <v>46104</v>
+        <v>46283</v>
       </c>
       <c r="F60" s="5">
-        <v>503.28</v>
+        <v>11200</v>
       </c>
       <c r="G60" s="5">
-        <v>503.28</v>
+        <v>11200</v>
       </c>
       <c r="H60" s="3"/>
       <c r="I60" s="6">
-        <v>200</v>
+        <v>25</v>
       </c>
       <c r="J60" s="4" t="s">
-        <v>26</v>
+        <v>147</v>
       </c>
       <c r="K60" s="4" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="L60" s="4"/>
       <c r="M60" s="4" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="N60" s="4"/>
       <c r="O60" s="4"/>
     </row>
     <row r="61" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
-        <v>46045</v>
+        <v>46224</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E61" s="3">
-        <v>46105</v>
+        <v>46284</v>
       </c>
       <c r="F61" s="5">
-        <v>5466.66</v>
+        <v>10666.67</v>
       </c>
       <c r="G61" s="5">
-        <v>5466.66</v>
+        <v>10666.67</v>
       </c>
       <c r="H61" s="3"/>
       <c r="I61" s="6">
-        <v>199</v>
+        <v>24</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K61" s="4" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="L61" s="4"/>
       <c r="M61" s="4" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="N61" s="4"/>
       <c r="O61" s="4"/>
     </row>
     <row r="62" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
-        <v>46171</v>
+        <v>46234</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>135</v>
+        <v>43</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E62" s="3">
-        <v>46192</v>
+        <v>46284</v>
       </c>
       <c r="F62" s="5">
-        <v>4676.8500000000004</v>
+        <v>6500</v>
       </c>
       <c r="G62" s="5">
-        <v>7494.53</v>
+        <v>6500</v>
       </c>
       <c r="H62" s="3"/>
       <c r="I62" s="6">
-        <v>112</v>
-      </c>
-      <c r="J62" s="4"/>
+        <v>24</v>
+      </c>
+      <c r="J62" s="4" t="s">
+        <v>147</v>
+      </c>
       <c r="K62" s="4" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="L62" s="4"/>
-      <c r="M62" s="4"/>
+      <c r="M62" s="4" t="s">
+        <v>167</v>
+      </c>
       <c r="N62" s="4"/>
       <c r="O62" s="4"/>
     </row>
     <row r="63" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
-        <v>46171</v>
+        <v>46234</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>135</v>
+        <v>43</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E63" s="3">
-        <v>46199</v>
+        <v>46284</v>
       </c>
       <c r="F63" s="5">
-        <v>4676.8500000000004</v>
+        <v>4950.17</v>
       </c>
       <c r="G63" s="5">
-        <v>4676.8500000000004</v>
+        <v>4950.17</v>
       </c>
       <c r="H63" s="3"/>
       <c r="I63" s="6">
-        <v>105</v>
-      </c>
-      <c r="J63" s="4"/>
+        <v>24</v>
+      </c>
+      <c r="J63" s="4" t="s">
+        <v>147</v>
+      </c>
       <c r="K63" s="4" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="L63" s="4"/>
-      <c r="M63" s="4"/>
+      <c r="M63" s="4" t="s">
+        <v>169</v>
+      </c>
       <c r="N63" s="4"/>
       <c r="O63" s="4"/>
     </row>
     <row r="64" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
-        <v>46171</v>
+        <v>46225</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="E64" s="3">
-        <v>46206</v>
+        <v>46285</v>
       </c>
       <c r="F64" s="5">
-        <v>4676.8500000000004</v>
+        <v>7551.88</v>
       </c>
       <c r="G64" s="5">
-        <v>4676.8500000000004</v>
+        <v>7551.88</v>
       </c>
       <c r="H64" s="3"/>
       <c r="I64" s="6">
-        <v>98</v>
-      </c>
-      <c r="J64" s="4"/>
+        <v>23</v>
+      </c>
+      <c r="J64" s="4" t="s">
+        <v>147</v>
+      </c>
       <c r="K64" s="4" t="s">
-        <v>54</v>
+        <v>131</v>
       </c>
       <c r="L64" s="4"/>
-      <c r="M64" s="4"/>
+      <c r="M64" s="4" t="s">
+        <v>171</v>
+      </c>
       <c r="N64" s="4"/>
       <c r="O64" s="4"/>
     </row>
     <row r="65" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
-        <v>46162</v>
+        <v>46244</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>166</v>
+        <v>104</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E65" s="3">
-        <v>46222</v>
+        <v>46286</v>
       </c>
       <c r="F65" s="5">
-        <v>22349.79</v>
+        <v>4320</v>
       </c>
       <c r="G65" s="5">
-        <v>22349.79</v>
+        <v>4320</v>
       </c>
       <c r="H65" s="3"/>
       <c r="I65" s="6">
-        <v>82</v>
-      </c>
-      <c r="J65" s="4"/>
+        <v>22</v>
+      </c>
+      <c r="J65" s="4" t="s">
+        <v>147</v>
+      </c>
       <c r="K65" s="4" t="s">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="L65" s="4"/>
-      <c r="M65" s="4"/>
+      <c r="M65" s="4" t="s">
+        <v>173</v>
+      </c>
       <c r="N65" s="4"/>
       <c r="O65" s="4"/>
     </row>
     <row r="66" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
-        <v>46203</v>
+        <v>46253</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>168</v>
+        <v>43</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>169</v>
+        <v>104</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="E66" s="3">
-        <v>46259</v>
+        <v>46288</v>
       </c>
       <c r="F66" s="5">
-        <v>860</v>
+        <v>10080</v>
       </c>
       <c r="G66" s="5">
-        <v>860</v>
+        <v>10080</v>
       </c>
       <c r="H66" s="3"/>
       <c r="I66" s="6">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="J66" s="4" t="s">
-        <v>26</v>
+        <v>147</v>
       </c>
       <c r="K66" s="4" t="s">
-        <v>171</v>
+        <v>35</v>
       </c>
       <c r="L66" s="4"/>
       <c r="M66" s="4" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="N66" s="4"/>
       <c r="O66" s="4"/>
     </row>
     <row r="67" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
-        <v>46224</v>
+        <v>46253</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>168</v>
+        <v>20</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="E67" s="3">
-        <v>46259</v>
+        <v>46288</v>
       </c>
       <c r="F67" s="5">
-        <v>2818.37</v>
+        <v>3640</v>
       </c>
       <c r="G67" s="5">
-        <v>2818.37</v>
+        <v>3640</v>
       </c>
       <c r="H67" s="3"/>
       <c r="I67" s="6">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="J67" s="4" t="s">
-        <v>26</v>
+        <v>147</v>
       </c>
       <c r="K67" s="4" t="s">
-        <v>171</v>
+        <v>23</v>
       </c>
       <c r="L67" s="4"/>
       <c r="M67" s="4" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="N67" s="4"/>
       <c r="O67" s="4"/>
     </row>
     <row r="68" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
-        <v>46232</v>
+        <v>46259</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>15</v>
+        <v>91</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E68" s="3">
-        <v>46262</v>
+        <v>46289</v>
       </c>
       <c r="F68" s="5">
-        <v>9716</v>
+        <v>6265</v>
       </c>
       <c r="G68" s="5">
-        <v>18957.86</v>
+        <v>6265</v>
       </c>
       <c r="H68" s="3"/>
       <c r="I68" s="6">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="J68" s="4" t="s">
-        <v>26</v>
+        <v>147</v>
       </c>
       <c r="K68" s="4" t="s">
-        <v>39</v>
+        <v>137</v>
       </c>
       <c r="L68" s="4"/>
       <c r="M68" s="4" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="N68" s="4"/>
       <c r="O68" s="4"/>
     </row>
     <row r="69" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
-        <v>46225</v>
+        <v>46262</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>178</v>
+        <v>107</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>179</v>
+        <v>108</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E69" s="3">
-        <v>46270</v>
+        <v>46290</v>
       </c>
       <c r="F69" s="5">
-        <v>7551.88</v>
+        <v>11660.11</v>
       </c>
       <c r="G69" s="5">
-        <v>11442.87</v>
+        <v>11660.11</v>
       </c>
       <c r="H69" s="3"/>
       <c r="I69" s="6">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="J69" s="4" t="s">
-        <v>181</v>
+        <v>147</v>
       </c>
       <c r="K69" s="4" t="s">
-        <v>182</v>
+        <v>110</v>
       </c>
       <c r="L69" s="4"/>
       <c r="M69" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="N69" s="4"/>
       <c r="O69" s="4"/>
@@ -4044,32 +4059,32 @@
         <v>46232</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="D70" s="4" t="s">
         <v>184</v>
       </c>
       <c r="E70" s="3">
-        <v>46272</v>
+        <v>46292</v>
       </c>
       <c r="F70" s="5">
-        <v>9716</v>
+        <v>4082.05</v>
       </c>
       <c r="G70" s="5">
-        <v>9716</v>
+        <v>4082.05</v>
       </c>
       <c r="H70" s="3"/>
       <c r="I70" s="6">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="J70" s="4" t="s">
-        <v>26</v>
+        <v>147</v>
       </c>
       <c r="K70" s="4" t="s">
-        <v>39</v>
+        <v>131</v>
       </c>
       <c r="L70" s="4"/>
       <c r="M70" s="4" t="s">
@@ -4080,117 +4095,117 @@
     </row>
     <row r="71" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3">
-        <v>46227</v>
+        <v>46244</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>178</v>
+        <v>43</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>179</v>
+        <v>104</v>
       </c>
       <c r="D71" s="4" t="s">
         <v>186</v>
       </c>
       <c r="E71" s="3">
-        <v>46272</v>
+        <v>46293</v>
       </c>
       <c r="F71" s="5">
-        <v>4216.67</v>
+        <v>4320</v>
       </c>
       <c r="G71" s="5">
-        <v>6389.24</v>
+        <v>4320</v>
       </c>
       <c r="H71" s="3"/>
       <c r="I71" s="6">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="J71" s="4" t="s">
-        <v>187</v>
+        <v>147</v>
       </c>
       <c r="K71" s="4" t="s">
-        <v>182</v>
+        <v>35</v>
       </c>
       <c r="L71" s="4"/>
       <c r="M71" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="N71" s="4"/>
       <c r="O71" s="4"/>
     </row>
     <row r="72" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
-        <v>46224</v>
+        <v>46223</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>168</v>
+        <v>43</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>169</v>
+        <v>149</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E72" s="3">
-        <v>46273</v>
+        <v>46293</v>
       </c>
       <c r="F72" s="5">
-        <v>2818.37</v>
+        <v>11200</v>
       </c>
       <c r="G72" s="5">
-        <v>2818.37</v>
+        <v>11200</v>
       </c>
       <c r="H72" s="3"/>
       <c r="I72" s="6">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="J72" s="4" t="s">
-        <v>26</v>
+        <v>147</v>
       </c>
       <c r="K72" s="4" t="s">
-        <v>171</v>
+        <v>35</v>
       </c>
       <c r="L72" s="4"/>
       <c r="M72" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="N72" s="4"/>
       <c r="O72" s="4"/>
     </row>
     <row r="73" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="3">
-        <v>46223</v>
+        <v>46234</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>45</v>
+        <v>127</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>191</v>
+        <v>128</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E73" s="3">
-        <v>46273</v>
+        <v>46294</v>
       </c>
       <c r="F73" s="5">
-        <v>11200</v>
+        <v>3789.09</v>
       </c>
       <c r="G73" s="5">
-        <v>11200</v>
+        <v>3789.09</v>
       </c>
       <c r="H73" s="3"/>
       <c r="I73" s="6">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="J73" s="4" t="s">
-        <v>181</v>
+        <v>147</v>
       </c>
       <c r="K73" s="4" t="s">
-        <v>27</v>
+        <v>131</v>
       </c>
       <c r="L73" s="4"/>
       <c r="M73" s="4" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="N73" s="4"/>
       <c r="O73" s="4"/>
@@ -4200,16 +4215,16 @@
         <v>46253</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>194</v>
+        <v>104</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E74" s="3">
-        <v>46274</v>
+        <v>46295</v>
       </c>
       <c r="F74" s="5">
         <v>10080</v>
@@ -4219,1339 +4234,1339 @@
       </c>
       <c r="H74" s="3"/>
       <c r="I74" s="6">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="J74" s="4" t="s">
-        <v>181</v>
+        <v>147</v>
       </c>
       <c r="K74" s="4" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="L74" s="4"/>
       <c r="M74" s="4" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="N74" s="4"/>
       <c r="O74" s="4"/>
     </row>
     <row r="75" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="3">
-        <v>46227</v>
+        <v>46265</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>194</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E75" s="3">
-        <v>46276</v>
+        <v>46295</v>
       </c>
       <c r="F75" s="5">
-        <v>23168.6</v>
+        <v>4750</v>
       </c>
       <c r="G75" s="5">
-        <v>23168.6</v>
+        <v>8565.68</v>
       </c>
       <c r="H75" s="3"/>
       <c r="I75" s="6">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="J75" s="4" t="s">
-        <v>181</v>
+        <v>147</v>
       </c>
       <c r="K75" s="4" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="L75" s="4"/>
       <c r="M75" s="4" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="N75" s="4"/>
       <c r="O75" s="4"/>
     </row>
     <row r="76" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="3">
-        <v>46234</v>
+        <v>46266</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>178</v>
+        <v>197</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="D76" s="4" t="s">
         <v>199</v>
       </c>
       <c r="E76" s="3">
-        <v>46279</v>
+        <v>46296</v>
       </c>
       <c r="F76" s="5">
-        <v>3789.09</v>
+        <v>8973.5</v>
       </c>
       <c r="G76" s="5">
-        <v>5741.36</v>
+        <v>8973.5</v>
       </c>
       <c r="H76" s="3"/>
       <c r="I76" s="6">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="J76" s="4" t="s">
-        <v>181</v>
+        <v>147</v>
       </c>
       <c r="K76" s="4" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="L76" s="4"/>
       <c r="M76" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N76" s="4"/>
       <c r="O76" s="4"/>
     </row>
     <row r="77" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="3">
-        <v>46224</v>
+        <v>46262</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>168</v>
+        <v>107</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>169</v>
+        <v>108</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E77" s="3">
-        <v>46280</v>
+        <v>46297</v>
       </c>
       <c r="F77" s="5">
-        <v>2818.36</v>
+        <v>11660.11</v>
       </c>
       <c r="G77" s="5">
-        <v>2818.36</v>
+        <v>11660.11</v>
       </c>
       <c r="H77" s="3"/>
       <c r="I77" s="6">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="J77" s="4" t="s">
-        <v>26</v>
+        <v>147</v>
       </c>
       <c r="K77" s="4" t="s">
-        <v>171</v>
+        <v>110</v>
       </c>
       <c r="L77" s="4"/>
       <c r="M77" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N77" s="4"/>
       <c r="O77" s="4"/>
     </row>
     <row r="78" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="3">
-        <v>46253</v>
+        <v>46225</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>45</v>
+        <v>127</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>194</v>
+        <v>128</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E78" s="3">
-        <v>46281</v>
+        <v>46300</v>
       </c>
       <c r="F78" s="5">
-        <v>10080</v>
+        <v>7551.88</v>
       </c>
       <c r="G78" s="5">
-        <v>10080</v>
+        <v>7551.88</v>
       </c>
       <c r="H78" s="3"/>
       <c r="I78" s="6">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="J78" s="4" t="s">
-        <v>181</v>
+        <v>147</v>
       </c>
       <c r="K78" s="4" t="s">
-        <v>27</v>
+        <v>131</v>
       </c>
       <c r="L78" s="4"/>
       <c r="M78" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N78" s="4"/>
       <c r="O78" s="4"/>
     </row>
     <row r="79" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="3">
-        <v>46232</v>
+        <v>46253</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>175</v>
+        <v>104</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E79" s="3">
-        <v>46282</v>
+        <v>46302</v>
       </c>
       <c r="F79" s="5">
-        <v>9716</v>
+        <v>10080</v>
       </c>
       <c r="G79" s="5">
-        <v>9716</v>
+        <v>10080</v>
       </c>
       <c r="H79" s="3"/>
       <c r="I79" s="6">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="J79" s="4" t="s">
-        <v>26</v>
+        <v>147</v>
       </c>
       <c r="K79" s="4" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="L79" s="4"/>
       <c r="M79" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="N79" s="4"/>
       <c r="O79" s="4"/>
     </row>
     <row r="80" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="3">
-        <v>46227</v>
+        <v>46262</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E80" s="3">
-        <v>46283</v>
+        <v>46304</v>
       </c>
       <c r="F80" s="5">
-        <v>23168.6</v>
+        <v>2992</v>
       </c>
       <c r="G80" s="5">
-        <v>23168.6</v>
+        <v>2992</v>
       </c>
       <c r="H80" s="3"/>
       <c r="I80" s="6">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="J80" s="4" t="s">
-        <v>181</v>
+        <v>147</v>
       </c>
       <c r="K80" s="4" t="s">
-        <v>27</v>
+        <v>210</v>
       </c>
       <c r="L80" s="4"/>
       <c r="M80" s="4" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="N80" s="4"/>
       <c r="O80" s="4"/>
     </row>
     <row r="81" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="3">
-        <v>46223</v>
+        <v>46259</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>45</v>
+        <v>91</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>191</v>
+        <v>135</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="E81" s="3">
-        <v>46283</v>
+        <v>46304</v>
       </c>
       <c r="F81" s="5">
-        <v>11200</v>
+        <v>6265</v>
       </c>
       <c r="G81" s="5">
-        <v>11200</v>
+        <v>6265</v>
       </c>
       <c r="H81" s="3"/>
       <c r="I81" s="6">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="J81" s="4" t="s">
-        <v>181</v>
+        <v>147</v>
       </c>
       <c r="K81" s="4" t="s">
-        <v>27</v>
+        <v>137</v>
       </c>
       <c r="L81" s="4"/>
       <c r="M81" s="4" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="N81" s="4"/>
       <c r="O81" s="4"/>
     </row>
     <row r="82" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3">
-        <v>46224</v>
+        <v>46262</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>45</v>
+        <v>107</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>191</v>
+        <v>108</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="E82" s="3">
-        <v>46284</v>
+        <v>46304</v>
       </c>
       <c r="F82" s="5">
-        <v>10666.67</v>
+        <v>11660.11</v>
       </c>
       <c r="G82" s="5">
-        <v>10666.67</v>
+        <v>11660.11</v>
       </c>
       <c r="H82" s="3"/>
       <c r="I82" s="6">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="J82" s="4" t="s">
-        <v>181</v>
+        <v>147</v>
       </c>
       <c r="K82" s="4" t="s">
-        <v>27</v>
+        <v>110</v>
       </c>
       <c r="L82" s="4"/>
       <c r="M82" s="4" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="N82" s="4"/>
       <c r="O82" s="4"/>
     </row>
     <row r="83" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="3">
-        <v>46234</v>
+        <v>45296</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>45</v>
+        <v>91</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>191</v>
+        <v>216</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E83" s="3">
-        <v>46284</v>
+        <v>45326</v>
       </c>
       <c r="F83" s="5">
-        <v>6500</v>
+        <v>5418</v>
       </c>
       <c r="G83" s="5">
-        <v>6500</v>
+        <v>9391.7800000000007</v>
       </c>
       <c r="H83" s="3"/>
       <c r="I83" s="6">
-        <v>20</v>
+        <v>982</v>
       </c>
       <c r="J83" s="4" t="s">
-        <v>181</v>
+        <v>218</v>
       </c>
       <c r="K83" s="4" t="s">
-        <v>27</v>
+        <v>137</v>
       </c>
       <c r="L83" s="4"/>
       <c r="M83" s="4" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="N83" s="4"/>
       <c r="O83" s="4"/>
     </row>
     <row r="84" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="3">
-        <v>46234</v>
+        <v>45296</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>45</v>
+        <v>91</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>191</v>
+        <v>216</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="E84" s="3">
-        <v>46284</v>
+        <v>45346</v>
       </c>
       <c r="F84" s="5">
-        <v>4950.17</v>
+        <v>5418</v>
       </c>
       <c r="G84" s="5">
-        <v>4950.17</v>
+        <v>5418</v>
       </c>
       <c r="H84" s="3"/>
       <c r="I84" s="6">
-        <v>20</v>
+        <v>962</v>
       </c>
       <c r="J84" s="4" t="s">
-        <v>181</v>
+        <v>218</v>
       </c>
       <c r="K84" s="4" t="s">
-        <v>27</v>
+        <v>137</v>
       </c>
       <c r="L84" s="4"/>
       <c r="M84" s="4" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N84" s="4"/>
       <c r="O84" s="4"/>
     </row>
     <row r="85" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="3">
-        <v>46225</v>
+        <v>45296</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>178</v>
+        <v>91</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>179</v>
+        <v>216</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="E85" s="3">
-        <v>46285</v>
+        <v>45356</v>
       </c>
       <c r="F85" s="5">
-        <v>7551.88</v>
+        <v>5418</v>
       </c>
       <c r="G85" s="5">
-        <v>7551.88</v>
+        <v>5418</v>
       </c>
       <c r="H85" s="3"/>
       <c r="I85" s="6">
-        <v>19</v>
+        <v>952</v>
       </c>
       <c r="J85" s="4" t="s">
-        <v>181</v>
+        <v>218</v>
       </c>
       <c r="K85" s="4" t="s">
-        <v>182</v>
+        <v>137</v>
       </c>
       <c r="L85" s="4"/>
       <c r="M85" s="4" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="N85" s="4"/>
       <c r="O85" s="4"/>
     </row>
     <row r="86" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="3">
-        <v>46244</v>
+        <v>45433</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>45</v>
+        <v>91</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>194</v>
+        <v>224</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="E86" s="3">
-        <v>46286</v>
+        <v>45463</v>
       </c>
       <c r="F86" s="5">
-        <v>4320</v>
+        <v>873.6</v>
       </c>
       <c r="G86" s="5">
-        <v>4320</v>
+        <v>1674.52</v>
       </c>
       <c r="H86" s="3"/>
       <c r="I86" s="6">
-        <v>18</v>
+        <v>845</v>
       </c>
       <c r="J86" s="4" t="s">
-        <v>181</v>
+        <v>218</v>
       </c>
       <c r="K86" s="4" t="s">
-        <v>27</v>
+        <v>94</v>
       </c>
       <c r="L86" s="4"/>
       <c r="M86" s="4" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="N86" s="4"/>
       <c r="O86" s="4"/>
     </row>
     <row r="87" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="3">
-        <v>46266</v>
+        <v>45433</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>45</v>
+        <v>91</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>194</v>
+        <v>224</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="E87" s="3">
-        <v>46287</v>
+        <v>45493</v>
       </c>
       <c r="F87" s="5">
-        <v>18600</v>
+        <v>873.6</v>
       </c>
       <c r="G87" s="5">
-        <v>18600</v>
+        <v>873.6</v>
       </c>
       <c r="H87" s="3"/>
       <c r="I87" s="6">
-        <v>17</v>
+        <v>815</v>
       </c>
       <c r="J87" s="4" t="s">
-        <v>26</v>
+        <v>218</v>
       </c>
       <c r="K87" s="4" t="s">
-        <v>27</v>
+        <v>94</v>
       </c>
       <c r="L87" s="4"/>
       <c r="M87" s="4" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="N87" s="4"/>
       <c r="O87" s="4"/>
     </row>
     <row r="88" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="3">
-        <v>46227</v>
+        <v>45433</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>178</v>
+        <v>91</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>179</v>
+        <v>224</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="E88" s="3">
-        <v>46287</v>
+        <v>45523</v>
       </c>
       <c r="F88" s="5">
-        <v>4216.67</v>
+        <v>873.6</v>
       </c>
       <c r="G88" s="5">
-        <v>4216.67</v>
+        <v>873.6</v>
       </c>
       <c r="H88" s="3"/>
       <c r="I88" s="6">
-        <v>17</v>
+        <v>785</v>
       </c>
       <c r="J88" s="4" t="s">
-        <v>187</v>
+        <v>218</v>
       </c>
       <c r="K88" s="4" t="s">
-        <v>182</v>
+        <v>94</v>
       </c>
       <c r="L88" s="4"/>
       <c r="M88" s="4" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="N88" s="4"/>
       <c r="O88" s="4"/>
     </row>
     <row r="89" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="3">
-        <v>46253</v>
+        <v>45558</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>194</v>
+        <v>231</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="E89" s="3">
-        <v>46288</v>
+        <v>45600</v>
       </c>
       <c r="F89" s="5">
-        <v>10080</v>
+        <v>2000</v>
       </c>
       <c r="G89" s="5">
-        <v>10080</v>
+        <v>2000</v>
       </c>
       <c r="H89" s="3"/>
       <c r="I89" s="6">
-        <v>16</v>
+        <v>708</v>
       </c>
       <c r="J89" s="4" t="s">
-        <v>181</v>
+        <v>218</v>
       </c>
       <c r="K89" s="4" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="L89" s="4"/>
       <c r="M89" s="4" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="N89" s="4"/>
       <c r="O89" s="4"/>
     </row>
     <row r="90" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="3">
-        <v>46253</v>
+        <v>45558</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>121</v>
+        <v>43</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="E90" s="3">
-        <v>46288</v>
+        <v>45607</v>
       </c>
       <c r="F90" s="5">
-        <v>1660.33</v>
+        <v>2000</v>
       </c>
       <c r="G90" s="5">
-        <v>1660.33</v>
+        <v>3204.34</v>
       </c>
       <c r="H90" s="3"/>
       <c r="I90" s="6">
-        <v>16</v>
+        <v>701</v>
       </c>
       <c r="J90" s="4" t="s">
-        <v>18</v>
+        <v>218</v>
       </c>
       <c r="K90" s="4" t="s">
-        <v>124</v>
+        <v>35</v>
       </c>
       <c r="L90" s="4"/>
       <c r="M90" s="4" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="N90" s="4"/>
       <c r="O90" s="4"/>
     </row>
     <row r="91" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="3">
-        <v>46253</v>
+        <v>45552</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>121</v>
+        <v>236</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="E91" s="3">
-        <v>46288</v>
+        <v>45608</v>
       </c>
       <c r="F91" s="5">
-        <v>3640</v>
+        <v>4439.8999999999996</v>
       </c>
       <c r="G91" s="5">
-        <v>3640</v>
+        <v>4439.8999999999996</v>
       </c>
       <c r="H91" s="3"/>
       <c r="I91" s="6">
-        <v>16</v>
+        <v>700</v>
       </c>
       <c r="J91" s="4" t="s">
-        <v>181</v>
+        <v>218</v>
       </c>
       <c r="K91" s="4" t="s">
-        <v>124</v>
+        <v>18</v>
       </c>
       <c r="L91" s="4"/>
       <c r="M91" s="4" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="N91" s="4"/>
       <c r="O91" s="4"/>
     </row>
     <row r="92" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="3">
-        <v>46259</v>
+        <v>45558</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="E92" s="3">
-        <v>46289</v>
+        <v>45614</v>
       </c>
       <c r="F92" s="5">
-        <v>6265</v>
+        <v>2000</v>
       </c>
       <c r="G92" s="5">
-        <v>6265</v>
+        <v>2000</v>
       </c>
       <c r="H92" s="3"/>
       <c r="I92" s="6">
-        <v>15</v>
+        <v>694</v>
       </c>
       <c r="J92" s="4" t="s">
-        <v>181</v>
+        <v>218</v>
       </c>
       <c r="K92" s="4" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="L92" s="4"/>
       <c r="M92" s="4" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="N92" s="4"/>
       <c r="O92" s="4"/>
     </row>
     <row r="93" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="3">
-        <v>46262</v>
+        <v>45546</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>235</v>
+        <v>43</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="E93" s="3">
-        <v>46290</v>
+        <v>45615</v>
       </c>
       <c r="F93" s="5">
-        <v>7694.4</v>
+        <v>1216.8599999999999</v>
       </c>
       <c r="G93" s="5">
-        <v>7694.4</v>
+        <v>1216.8599999999999</v>
       </c>
       <c r="H93" s="3"/>
       <c r="I93" s="6">
-        <v>14</v>
+        <v>693</v>
       </c>
       <c r="J93" s="4" t="s">
-        <v>26</v>
+        <v>218</v>
       </c>
       <c r="K93" s="4" t="s">
-        <v>238</v>
+        <v>35</v>
       </c>
       <c r="L93" s="4"/>
       <c r="M93" s="4" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="N93" s="4"/>
       <c r="O93" s="4"/>
     </row>
     <row r="94" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="3">
-        <v>46262</v>
+        <v>45548</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>235</v>
+        <v>43</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="E94" s="3">
-        <v>46290</v>
+        <v>45617</v>
       </c>
       <c r="F94" s="5">
-        <v>11660.11</v>
+        <v>1843.87</v>
       </c>
       <c r="G94" s="5">
-        <v>11660.11</v>
+        <v>1843.87</v>
       </c>
       <c r="H94" s="3"/>
       <c r="I94" s="6">
-        <v>14</v>
+        <v>691</v>
       </c>
       <c r="J94" s="4" t="s">
-        <v>181</v>
+        <v>218</v>
       </c>
       <c r="K94" s="4" t="s">
-        <v>238</v>
+        <v>35</v>
       </c>
       <c r="L94" s="4"/>
       <c r="M94" s="4" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="N94" s="4"/>
       <c r="O94" s="4"/>
     </row>
     <row r="95" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="3">
-        <v>46232</v>
+        <v>45546</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>178</v>
+        <v>43</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="E95" s="3">
-        <v>46292</v>
+        <v>45622</v>
       </c>
       <c r="F95" s="5">
-        <v>4082.05</v>
+        <v>1216.8599999999999</v>
       </c>
       <c r="G95" s="5">
-        <v>4082.05</v>
+        <v>1216.8599999999999</v>
       </c>
       <c r="H95" s="3"/>
       <c r="I95" s="6">
-        <v>12</v>
+        <v>686</v>
       </c>
       <c r="J95" s="4" t="s">
-        <v>181</v>
+        <v>218</v>
       </c>
       <c r="K95" s="4" t="s">
-        <v>182</v>
+        <v>35</v>
       </c>
       <c r="L95" s="4"/>
       <c r="M95" s="4" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="N95" s="4"/>
       <c r="O95" s="4"/>
     </row>
     <row r="96" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="3">
-        <v>46232</v>
+        <v>45552</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>15</v>
+        <v>236</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>175</v>
+        <v>237</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="E96" s="3">
-        <v>46292</v>
+        <v>45622</v>
       </c>
       <c r="F96" s="5">
-        <v>9716</v>
+        <v>4439.8999999999996</v>
       </c>
       <c r="G96" s="5">
-        <v>9716</v>
+        <v>4439.8999999999996</v>
       </c>
       <c r="H96" s="3"/>
       <c r="I96" s="6">
-        <v>12</v>
+        <v>686</v>
       </c>
       <c r="J96" s="4" t="s">
-        <v>26</v>
+        <v>218</v>
       </c>
       <c r="K96" s="4" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="L96" s="4"/>
       <c r="M96" s="4" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="N96" s="4"/>
       <c r="O96" s="4"/>
     </row>
     <row r="97" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="3">
-        <v>46223</v>
+        <v>45548</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="E97" s="3">
-        <v>46293</v>
+        <v>45624</v>
       </c>
       <c r="F97" s="5">
-        <v>6265</v>
+        <v>1843.88</v>
       </c>
       <c r="G97" s="5">
-        <v>6265</v>
+        <v>1843.88</v>
       </c>
       <c r="H97" s="3"/>
       <c r="I97" s="6">
-        <v>11</v>
+        <v>684</v>
       </c>
       <c r="J97" s="4" t="s">
-        <v>187</v>
+        <v>218</v>
       </c>
       <c r="K97" s="4" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="L97" s="4"/>
       <c r="M97" s="4" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="N97" s="4"/>
       <c r="O97" s="4"/>
     </row>
     <row r="98" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="3">
-        <v>46244</v>
+        <v>45632</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>45</v>
+        <v>252</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>194</v>
+        <v>253</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="E98" s="3">
-        <v>46293</v>
+        <v>45688</v>
       </c>
       <c r="F98" s="5">
-        <v>4320</v>
+        <v>1118.4000000000001</v>
       </c>
       <c r="G98" s="5">
-        <v>4320</v>
+        <v>1118.4000000000001</v>
       </c>
       <c r="H98" s="3"/>
       <c r="I98" s="6">
-        <v>11</v>
+        <v>620</v>
       </c>
       <c r="J98" s="4" t="s">
-        <v>181</v>
+        <v>218</v>
       </c>
       <c r="K98" s="4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L98" s="4"/>
       <c r="M98" s="4" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="N98" s="4"/>
       <c r="O98" s="4"/>
     </row>
     <row r="99" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="3">
-        <v>46223</v>
+        <v>45646</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>191</v>
+        <v>44</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="E99" s="3">
-        <v>46293</v>
+        <v>45695</v>
       </c>
       <c r="F99" s="5">
-        <v>11200</v>
+        <v>3296.8</v>
       </c>
       <c r="G99" s="5">
-        <v>11200</v>
+        <v>3296.8</v>
       </c>
       <c r="H99" s="3"/>
       <c r="I99" s="6">
-        <v>11</v>
+        <v>613</v>
       </c>
       <c r="J99" s="4" t="s">
-        <v>181</v>
+        <v>218</v>
       </c>
       <c r="K99" s="4" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="L99" s="4"/>
       <c r="M99" s="4" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="N99" s="4"/>
       <c r="O99" s="4"/>
     </row>
     <row r="100" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="3">
-        <v>46266</v>
+        <v>45636</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>194</v>
+        <v>44</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="E100" s="3">
-        <v>46294</v>
+        <v>45699</v>
       </c>
       <c r="F100" s="5">
-        <v>18600</v>
+        <v>2330</v>
       </c>
       <c r="G100" s="5">
-        <v>18600</v>
+        <v>2330</v>
       </c>
       <c r="H100" s="3"/>
       <c r="I100" s="6">
-        <v>10</v>
+        <v>609</v>
       </c>
       <c r="J100" s="4" t="s">
-        <v>26</v>
+        <v>218</v>
       </c>
       <c r="K100" s="4" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="L100" s="4"/>
       <c r="M100" s="4" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="N100" s="4"/>
       <c r="O100" s="4"/>
     </row>
     <row r="101" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="3">
-        <v>46234</v>
+        <v>45646</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>178</v>
+        <v>43</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>179</v>
+        <v>44</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="E101" s="3">
-        <v>46294</v>
+        <v>45702</v>
       </c>
       <c r="F101" s="5">
-        <v>3789.09</v>
+        <v>3296.8</v>
       </c>
       <c r="G101" s="5">
-        <v>3789.09</v>
+        <v>3296.8</v>
       </c>
       <c r="H101" s="3"/>
       <c r="I101" s="6">
-        <v>10</v>
+        <v>606</v>
       </c>
       <c r="J101" s="4" t="s">
-        <v>181</v>
+        <v>218</v>
       </c>
       <c r="K101" s="4" t="s">
-        <v>182</v>
+        <v>46</v>
       </c>
       <c r="L101" s="4"/>
       <c r="M101" s="4" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="N101" s="4"/>
       <c r="O101" s="4"/>
     </row>
     <row r="102" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="3">
-        <v>46253</v>
+        <v>45646</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>194</v>
+        <v>44</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="E102" s="3">
-        <v>46295</v>
+        <v>45709</v>
       </c>
       <c r="F102" s="5">
-        <v>10080</v>
+        <v>3296.8</v>
       </c>
       <c r="G102" s="5">
-        <v>10080</v>
+        <v>3296.8</v>
       </c>
       <c r="H102" s="3"/>
       <c r="I102" s="6">
-        <v>9</v>
+        <v>599</v>
       </c>
       <c r="J102" s="4" t="s">
-        <v>181</v>
+        <v>218</v>
       </c>
       <c r="K102" s="4" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="L102" s="4"/>
       <c r="M102" s="4" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="N102" s="4"/>
       <c r="O102" s="4"/>
     </row>
     <row r="103" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="3">
-        <v>46253</v>
+        <v>45699</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>121</v>
+        <v>43</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>227</v>
+        <v>44</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="E103" s="3">
-        <v>46295</v>
+        <v>45727</v>
       </c>
       <c r="F103" s="5">
-        <v>3640</v>
+        <v>7562.78</v>
       </c>
       <c r="G103" s="5">
-        <v>3640</v>
+        <v>7562.78</v>
       </c>
       <c r="H103" s="3"/>
       <c r="I103" s="6">
-        <v>9</v>
+        <v>581</v>
       </c>
       <c r="J103" s="4" t="s">
-        <v>181</v>
+        <v>218</v>
       </c>
       <c r="K103" s="4" t="s">
-        <v>124</v>
+        <v>46</v>
       </c>
       <c r="L103" s="4"/>
       <c r="M103" s="4" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="N103" s="4"/>
       <c r="O103" s="4"/>
     </row>
     <row r="104" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="3">
-        <v>46253</v>
+        <v>45699</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>121</v>
+        <v>43</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>227</v>
+        <v>44</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="E104" s="3">
-        <v>46295</v>
+        <v>45734</v>
       </c>
       <c r="F104" s="5">
-        <v>1660.34</v>
+        <v>7562.78</v>
       </c>
       <c r="G104" s="5">
-        <v>1660.34</v>
+        <v>7562.78</v>
       </c>
       <c r="H104" s="3"/>
       <c r="I104" s="6">
-        <v>9</v>
+        <v>574</v>
       </c>
       <c r="J104" s="4" t="s">
-        <v>18</v>
+        <v>218</v>
       </c>
       <c r="K104" s="4" t="s">
-        <v>124</v>
+        <v>46</v>
       </c>
       <c r="L104" s="4"/>
       <c r="M104" s="4" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="N104" s="4"/>
       <c r="O104" s="4"/>
     </row>
     <row r="105" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="3">
-        <v>46253</v>
+        <v>45699</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>168</v>
+        <v>236</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="E105" s="3">
-        <v>46295</v>
+        <v>45734</v>
       </c>
       <c r="F105" s="5">
-        <v>2051.2199999999998</v>
+        <v>1154.56</v>
       </c>
       <c r="G105" s="5">
-        <v>2051.2199999999998</v>
+        <v>1154.56</v>
       </c>
       <c r="H105" s="3"/>
       <c r="I105" s="6">
-        <v>9</v>
+        <v>574</v>
       </c>
       <c r="J105" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="K105" s="4" t="s">
         <v>18</v>
-      </c>
-      <c r="K105" s="4" t="s">
-        <v>171</v>
       </c>
       <c r="L105" s="4"/>
       <c r="M105" s="4" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="N105" s="4"/>
       <c r="O105" s="4"/>
     </row>
     <row r="106" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="3">
-        <v>46265</v>
+        <v>45699</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>135</v>
+        <v>43</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>266</v>
+        <v>44</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="E106" s="3">
-        <v>46295</v>
+        <v>45741</v>
       </c>
       <c r="F106" s="5">
-        <v>4750</v>
+        <v>7562.78</v>
       </c>
       <c r="G106" s="5">
-        <v>8565.68</v>
+        <v>7562.78</v>
       </c>
       <c r="H106" s="3"/>
       <c r="I106" s="6">
-        <v>9</v>
+        <v>567</v>
       </c>
       <c r="J106" s="4" t="s">
-        <v>181</v>
+        <v>218</v>
       </c>
       <c r="K106" s="4" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="L106" s="4"/>
       <c r="M106" s="4" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="N106" s="4"/>
       <c r="O106" s="4"/>
     </row>
     <row r="107" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="3">
-        <v>46268</v>
+        <v>45699</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>23</v>
+        <v>236</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="E107" s="3">
-        <v>46296</v>
+        <v>45741</v>
       </c>
       <c r="F107" s="5">
-        <v>2754</v>
+        <v>1154.56</v>
       </c>
       <c r="G107" s="5">
-        <v>2754</v>
+        <v>1154.56</v>
       </c>
       <c r="H107" s="3"/>
       <c r="I107" s="6">
-        <v>8</v>
+        <v>567</v>
       </c>
       <c r="J107" s="4" t="s">
-        <v>187</v>
+        <v>218</v>
       </c>
       <c r="K107" s="4" t="s">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="L107" s="4"/>
       <c r="M107" s="4" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="N107" s="4"/>
       <c r="O107" s="4"/>
     </row>
     <row r="108" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="3">
-        <v>46266</v>
+        <v>45699</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>272</v>
+        <v>236</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E108" s="3">
-        <v>46296</v>
+        <v>45748</v>
       </c>
       <c r="F108" s="5">
-        <v>8973.5</v>
+        <v>1154.56</v>
       </c>
       <c r="G108" s="5">
-        <v>8973.5</v>
+        <v>1154.56</v>
       </c>
       <c r="H108" s="3"/>
       <c r="I108" s="6">
-        <v>8</v>
+        <v>560</v>
       </c>
       <c r="J108" s="4" t="s">
-        <v>181</v>
+        <v>218</v>
       </c>
       <c r="K108" s="4" t="s">
-        <v>275</v>
+        <v>18</v>
       </c>
       <c r="L108" s="4"/>
       <c r="M108" s="4" t="s">
@@ -5562,35 +5577,35 @@
     </row>
     <row r="109" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="3">
-        <v>46262</v>
+        <v>45699</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>235</v>
+        <v>43</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>236</v>
+        <v>44</v>
       </c>
       <c r="D109" s="4" t="s">
         <v>277</v>
       </c>
       <c r="E109" s="3">
-        <v>46297</v>
+        <v>45748</v>
       </c>
       <c r="F109" s="5">
-        <v>11660.11</v>
+        <v>7562.76</v>
       </c>
       <c r="G109" s="5">
-        <v>11660.11</v>
+        <v>7562.76</v>
       </c>
       <c r="H109" s="3"/>
       <c r="I109" s="6">
-        <v>7</v>
+        <v>560</v>
       </c>
       <c r="J109" s="4" t="s">
-        <v>181</v>
+        <v>218</v>
       </c>
       <c r="K109" s="4" t="s">
-        <v>238</v>
+        <v>46</v>
       </c>
       <c r="L109" s="4"/>
       <c r="M109" s="4" t="s">
@@ -5601,35 +5616,35 @@
     </row>
     <row r="110" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="3">
-        <v>46262</v>
+        <v>45699</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>236</v>
+        <v>268</v>
       </c>
       <c r="D110" s="4" t="s">
         <v>279</v>
       </c>
       <c r="E110" s="3">
-        <v>46297</v>
+        <v>45755</v>
       </c>
       <c r="F110" s="5">
-        <v>7694.4</v>
+        <v>1154.56</v>
       </c>
       <c r="G110" s="5">
-        <v>7694.4</v>
+        <v>1154.56</v>
       </c>
       <c r="H110" s="3"/>
       <c r="I110" s="6">
-        <v>7</v>
+        <v>553</v>
       </c>
       <c r="J110" s="4" t="s">
-        <v>26</v>
+        <v>218</v>
       </c>
       <c r="K110" s="4" t="s">
-        <v>238</v>
+        <v>18</v>
       </c>
       <c r="L110" s="4"/>
       <c r="M110" s="4" t="s">
@@ -5640,273 +5655,273 @@
     </row>
     <row r="111" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="3">
-        <v>46225</v>
+        <v>45733</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>178</v>
+        <v>236</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>179</v>
+        <v>281</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E111" s="3">
-        <v>46300</v>
+        <v>45761</v>
       </c>
       <c r="F111" s="5">
-        <v>7551.88</v>
+        <v>3850</v>
       </c>
       <c r="G111" s="5">
-        <v>7551.88</v>
+        <v>6169.53</v>
       </c>
       <c r="H111" s="3"/>
       <c r="I111" s="6">
-        <v>4</v>
+        <v>547</v>
       </c>
       <c r="J111" s="4" t="s">
-        <v>181</v>
+        <v>218</v>
       </c>
       <c r="K111" s="4" t="s">
-        <v>182</v>
+        <v>18</v>
       </c>
       <c r="L111" s="4"/>
       <c r="M111" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="N111" s="4"/>
       <c r="O111" s="4"/>
     </row>
     <row r="112" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="3">
-        <v>46265</v>
+        <v>45733</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>23</v>
+        <v>236</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E112" s="3">
-        <v>46300</v>
+        <v>45768</v>
       </c>
       <c r="F112" s="5">
-        <v>1664</v>
+        <v>3850</v>
       </c>
       <c r="G112" s="5">
-        <v>1664</v>
+        <v>3850</v>
       </c>
       <c r="H112" s="3"/>
       <c r="I112" s="6">
-        <v>4</v>
+        <v>540</v>
       </c>
       <c r="J112" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="K112" s="4" t="s">
         <v>18</v>
-      </c>
-      <c r="K112" s="4" t="s">
-        <v>71</v>
       </c>
       <c r="L112" s="4"/>
       <c r="M112" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N112" s="4"/>
       <c r="O112" s="4"/>
     </row>
     <row r="113" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="3">
-        <v>46266</v>
+        <v>45733</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>45</v>
+        <v>236</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>194</v>
+        <v>281</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E113" s="3">
-        <v>46301</v>
+        <v>45775</v>
       </c>
       <c r="F113" s="5">
-        <v>18600</v>
+        <v>3850</v>
       </c>
       <c r="G113" s="5">
-        <v>18600</v>
+        <v>3850</v>
       </c>
       <c r="H113" s="3"/>
       <c r="I113" s="6">
-        <v>3</v>
+        <v>533</v>
       </c>
       <c r="J113" s="4" t="s">
-        <v>26</v>
+        <v>218</v>
       </c>
       <c r="K113" s="4" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="L113" s="4"/>
       <c r="M113" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N113" s="4"/>
       <c r="O113" s="4"/>
     </row>
     <row r="114" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="3">
-        <v>46227</v>
+        <v>45747</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>178</v>
+        <v>236</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>179</v>
+        <v>281</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E114" s="3">
-        <v>46302</v>
+        <v>45775</v>
       </c>
       <c r="F114" s="5">
-        <v>4216.66</v>
+        <v>3800</v>
       </c>
       <c r="G114" s="5">
-        <v>4216.66</v>
+        <v>6089.41</v>
       </c>
       <c r="H114" s="3"/>
       <c r="I114" s="6">
-        <v>2</v>
+        <v>533</v>
       </c>
       <c r="J114" s="4" t="s">
-        <v>187</v>
+        <v>218</v>
       </c>
       <c r="K114" s="4" t="s">
-        <v>182</v>
+        <v>18</v>
       </c>
       <c r="L114" s="4"/>
       <c r="M114" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N114" s="4"/>
       <c r="O114" s="4"/>
     </row>
     <row r="115" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="3">
-        <v>46232</v>
+        <v>45747</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>15</v>
+        <v>236</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>175</v>
+        <v>281</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E115" s="3">
-        <v>46302</v>
+        <v>45782</v>
       </c>
       <c r="F115" s="5">
-        <v>9716</v>
+        <v>3800</v>
       </c>
       <c r="G115" s="5">
-        <v>9716</v>
+        <v>3800</v>
       </c>
       <c r="H115" s="3"/>
       <c r="I115" s="6">
-        <v>2</v>
+        <v>526</v>
       </c>
       <c r="J115" s="4" t="s">
-        <v>26</v>
+        <v>218</v>
       </c>
       <c r="K115" s="4" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="L115" s="4"/>
       <c r="M115" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N115" s="4"/>
       <c r="O115" s="4"/>
     </row>
     <row r="116" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="3">
-        <v>46253</v>
+        <v>45747</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>45</v>
+        <v>236</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>194</v>
+        <v>281</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E116" s="3">
-        <v>46302</v>
+        <v>45789</v>
       </c>
       <c r="F116" s="5">
-        <v>10080</v>
+        <v>3800</v>
       </c>
       <c r="G116" s="5">
-        <v>10080</v>
+        <v>3800</v>
       </c>
       <c r="H116" s="3"/>
       <c r="I116" s="6">
-        <v>2</v>
+        <v>519</v>
       </c>
       <c r="J116" s="4" t="s">
-        <v>181</v>
+        <v>218</v>
       </c>
       <c r="K116" s="4" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="L116" s="4"/>
       <c r="M116" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N116" s="4"/>
       <c r="O116" s="4"/>
     </row>
     <row r="117" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="3">
-        <v>46253</v>
+        <v>46045</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>227</v>
+        <v>294</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E117" s="3">
-        <v>46302</v>
+        <v>46105</v>
       </c>
       <c r="F117" s="5">
-        <v>1660.33</v>
+        <v>5466.66</v>
       </c>
       <c r="G117" s="5">
-        <v>1660.33</v>
+        <v>5466.66</v>
       </c>
       <c r="H117" s="3"/>
       <c r="I117" s="6">
-        <v>2</v>
+        <v>203</v>
       </c>
       <c r="J117" s="4" t="s">
-        <v>18</v>
+        <v>218</v>
       </c>
       <c r="K117" s="4" t="s">
-        <v>124</v>
+        <v>94</v>
       </c>
       <c r="L117" s="4"/>
       <c r="M117" s="4" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="N117" s="4"/>
       <c r="O117" s="4"/>
@@ -5916,78 +5931,117 @@
         <v>46253</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>121</v>
+        <v>20</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>227</v>
+        <v>176</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E118" s="3">
-        <v>46302</v>
+        <v>46288</v>
       </c>
       <c r="F118" s="5">
-        <v>3640</v>
+        <v>1660.33</v>
       </c>
       <c r="G118" s="5">
-        <v>3640</v>
+        <v>1660.33</v>
       </c>
       <c r="H118" s="3"/>
       <c r="I118" s="6">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="J118" s="4" t="s">
-        <v>181</v>
+        <v>218</v>
       </c>
       <c r="K118" s="4" t="s">
-        <v>124</v>
+        <v>23</v>
       </c>
       <c r="L118" s="4"/>
       <c r="M118" s="4" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="N118" s="4"/>
       <c r="O118" s="4"/>
     </row>
     <row r="119" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="3">
-        <v>46268</v>
+        <v>46253</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>269</v>
+        <v>299</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="E119" s="3">
-        <v>46303</v>
+        <v>46295</v>
       </c>
       <c r="F119" s="5">
-        <v>2754</v>
+        <v>2051.2199999999998</v>
       </c>
       <c r="G119" s="5">
-        <v>2754</v>
+        <v>2051.2199999999998</v>
       </c>
       <c r="H119" s="3"/>
       <c r="I119" s="6">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="J119" s="4" t="s">
-        <v>187</v>
+        <v>218</v>
       </c>
       <c r="K119" s="4" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="L119" s="4"/>
       <c r="M119" s="4" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="N119" s="4"/>
       <c r="O119" s="4"/>
+    </row>
+    <row r="120" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="3">
+        <v>46265</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C120" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="D120" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="E120" s="3">
+        <v>46300</v>
+      </c>
+      <c r="F120" s="5">
+        <v>1664</v>
+      </c>
+      <c r="G120" s="5">
+        <v>1664</v>
+      </c>
+      <c r="H120" s="3"/>
+      <c r="I120" s="6">
+        <v>8</v>
+      </c>
+      <c r="J120" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="K120" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="L120" s="4"/>
+      <c r="M120" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="N120" s="4"/>
+      <c r="O120" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
+++ b/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WINDOWS\Desktop\dados planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B66C2A8E-7023-4143-8F70-BAE77AAF06DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{883C6B4A-5C47-4951-AA9B-07CDF00B2C10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="297">
   <si>
     <t>Dt.Emissão</t>
   </si>
@@ -72,36 +72,450 @@
     <t>Centro de Custo</t>
   </si>
   <si>
+    <t>DANILO - AL/SE/BA</t>
+  </si>
+  <si>
+    <t>RB DISTRIBUIDORA DE PRODUTOS HOSPITALARES LTDA</t>
+  </si>
+  <si>
+    <t>01001504.1</t>
+  </si>
+  <si>
+    <t>ITAU</t>
+  </si>
+  <si>
+    <t>AL</t>
+  </si>
+  <si>
+    <t>34192961600009391781090001019578120992717000</t>
+  </si>
+  <si>
+    <t>01001504.3</t>
+  </si>
+  <si>
+    <t>34194963600005418001090001019738120992717000</t>
+  </si>
+  <si>
+    <t>MARCELO LOPES</t>
+  </si>
+  <si>
+    <t>FAROMED COMERCIO DE MATERIAIS HOSPITALARES LTDA</t>
+  </si>
+  <si>
+    <t>01001617.1</t>
+  </si>
+  <si>
+    <t>BANCO DO BRASIL</t>
+  </si>
+  <si>
+    <t>PE</t>
+  </si>
+  <si>
+    <t>00191964000001264870000003473568000002622117</t>
+  </si>
+  <si>
+    <t>01001504.4</t>
+  </si>
+  <si>
+    <t>34194964600005418001090001019818120992717000</t>
+  </si>
+  <si>
+    <t>01001548.3</t>
+  </si>
+  <si>
+    <t>00193965200000384000000003473568000002617517</t>
+  </si>
+  <si>
+    <t>01001617.2</t>
+  </si>
+  <si>
+    <t>00191965400000816000000003473568000002622217</t>
+  </si>
+  <si>
+    <t>01001617.3</t>
+  </si>
+  <si>
+    <t>00192966800000816000000003473568000002622317</t>
+  </si>
+  <si>
+    <t>VEC HOSPITALAR LTDA ME</t>
+  </si>
+  <si>
+    <t>01002233.1</t>
+  </si>
+  <si>
+    <t>SE</t>
+  </si>
+  <si>
+    <t>34192975300001674521090001106858120992717000</t>
+  </si>
+  <si>
+    <t>01002233.3</t>
+  </si>
+  <si>
+    <t>34192978300000873601090001107018120992717000</t>
+  </si>
+  <si>
+    <t>01002233.5</t>
+  </si>
+  <si>
+    <t>34191981300000873601090001107278120992717000</t>
+  </si>
+  <si>
+    <t>MARIO JR - PE/PB/RN</t>
+  </si>
+  <si>
+    <t>GLOBAL MEDIC LTDA</t>
+  </si>
+  <si>
+    <t>01003029.2</t>
+  </si>
+  <si>
+    <t>34195989000002000001090001238528120992717000</t>
+  </si>
+  <si>
+    <t>01003029.1</t>
+  </si>
+  <si>
+    <t>34197987600003204341090001238458120992717000</t>
+  </si>
+  <si>
+    <t>MOISES</t>
+  </si>
+  <si>
+    <t>AC FL FARMACIA E DROGARIA LTDA</t>
+  </si>
+  <si>
+    <t>01002991.3</t>
+  </si>
+  <si>
+    <t>BA</t>
+  </si>
+  <si>
+    <t>34196989800004439901090001240908120992717000</t>
+  </si>
+  <si>
+    <t>01003029.3</t>
+  </si>
+  <si>
+    <t>34195990400002000001090001238608120992717000</t>
+  </si>
+  <si>
+    <t>01002938.2</t>
+  </si>
+  <si>
+    <t>34194986400001216861090001218808120992717000</t>
+  </si>
+  <si>
+    <t>01002951.2</t>
+  </si>
+  <si>
+    <t>34193985900001843871090001228138120992717000</t>
+  </si>
+  <si>
+    <t>01002938.3</t>
+  </si>
+  <si>
+    <t>34192987800001216861090001218988120992717000</t>
+  </si>
+  <si>
+    <t>01002991.4</t>
+  </si>
+  <si>
+    <t>34197991200004439901090001241088120992717000</t>
+  </si>
+  <si>
+    <t>01002951.3</t>
+  </si>
+  <si>
+    <t>34194986600001843881090001228218120992717000</t>
+  </si>
+  <si>
+    <t>SERGIO ROBERTO - PB</t>
+  </si>
+  <si>
+    <t>RUBEM E MEDEIROS PRODUTOS PARA SAUDE LTDA</t>
+  </si>
+  <si>
+    <t>01003384.3</t>
+  </si>
+  <si>
+    <t>PB</t>
+  </si>
+  <si>
+    <t>34191997800001118401090001280758120992717000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RN COMERCIO DE MEDICAMENTOS E MATERIAL HOSPITALAR </t>
+  </si>
+  <si>
+    <t>01003464.4</t>
+  </si>
+  <si>
+    <t>RN</t>
+  </si>
+  <si>
+    <t>34194998500003296801090001307668120992717000</t>
+  </si>
+  <si>
+    <t>01003409.6</t>
+  </si>
+  <si>
+    <t>34199998900002330001090001290998120992717000</t>
+  </si>
+  <si>
+    <t>01003464.5</t>
+  </si>
+  <si>
+    <t>34198999200003296801090001307748120992717000</t>
+  </si>
+  <si>
+    <t>01003504.1</t>
+  </si>
+  <si>
+    <t>00191999500002541000000003473568000002851217</t>
+  </si>
+  <si>
+    <t>01003464.6</t>
+  </si>
+  <si>
+    <t>34191999900003296801090001307828120992717000</t>
+  </si>
+  <si>
+    <t>01003504.2</t>
+  </si>
+  <si>
+    <t>00195100200002541000000003473568000002851317</t>
+  </si>
+  <si>
+    <t>01003504.4</t>
+  </si>
+  <si>
+    <t>00194101600002541000000003473568000002851517</t>
+  </si>
+  <si>
+    <t>01003589.1</t>
+  </si>
+  <si>
+    <t>34197101700007562781090001319968120992717000</t>
+  </si>
+  <si>
+    <t>01003589.2</t>
+  </si>
+  <si>
+    <t>34198102400007562781090001320028120992717000</t>
+  </si>
+  <si>
+    <t>MED-K COMERCIO LTDA</t>
+  </si>
+  <si>
+    <t>01003592.2</t>
+  </si>
+  <si>
+    <t>34194102400001154561090001320448120992717000</t>
+  </si>
+  <si>
+    <t>01003504.6</t>
+  </si>
+  <si>
+    <t>00193103000002541000000003473568000002851717</t>
+  </si>
+  <si>
+    <t>01003589.3</t>
+  </si>
+  <si>
+    <t>34191103100007562781090001320108120992717000</t>
+  </si>
+  <si>
+    <t>01003592.3</t>
+  </si>
+  <si>
+    <t>34194103100001154561090001320518120992717000</t>
+  </si>
+  <si>
+    <t>01003592.4</t>
+  </si>
+  <si>
+    <t>34194103800001154561090001320698120992717000</t>
+  </si>
+  <si>
+    <t>01003589.4</t>
+  </si>
+  <si>
+    <t>34197103800007562761090001320288120992717000</t>
+  </si>
+  <si>
+    <t>01003592.5</t>
+  </si>
+  <si>
+    <t>34198104500001154561090001320778120992717000</t>
+  </si>
+  <si>
+    <t>ICARE MED LTDA</t>
+  </si>
+  <si>
+    <t>01003747.1</t>
+  </si>
+  <si>
+    <t>34194105100006169531090001342898120992717000</t>
+  </si>
+  <si>
+    <t>01003747.2</t>
+  </si>
+  <si>
+    <t>34198105800003850001090001342978120992717000</t>
+  </si>
+  <si>
+    <t>01003747.3</t>
+  </si>
+  <si>
+    <t>34196106500003850001090001343058120992717000</t>
+  </si>
+  <si>
+    <t>01003828.1</t>
+  </si>
+  <si>
+    <t>34191106500006089411090001356748120992717000</t>
+  </si>
+  <si>
+    <t>01003828.2</t>
+  </si>
+  <si>
+    <t>34196107200003800001090001356828120992717000</t>
+  </si>
+  <si>
+    <t>01003828.3</t>
+  </si>
+  <si>
+    <t>34191107900003800001090001356908120992717000</t>
+  </si>
+  <si>
+    <t>MALCA - CE</t>
+  </si>
+  <si>
+    <t>AGILE DISTRIBUIDORA LTDA</t>
+  </si>
+  <si>
+    <t>01003847.2</t>
+  </si>
+  <si>
+    <t>CE</t>
+  </si>
+  <si>
+    <t>00196107900002287070000003473568000002883717</t>
+  </si>
+  <si>
+    <t>01003847.3</t>
+  </si>
+  <si>
+    <t>00193108600002287060000003473568000002883817</t>
+  </si>
+  <si>
+    <t>ISA COMERCIO VAREJISTA DE PRODUTOS HOSPITALARES LT</t>
+  </si>
+  <si>
+    <t>01004522.1</t>
+  </si>
+  <si>
+    <t>00191118600004572620000003473568000002940517</t>
+  </si>
+  <si>
+    <t>01004522.2</t>
+  </si>
+  <si>
+    <t>00191120000003663840000003473568000002940617</t>
+  </si>
+  <si>
+    <t>01004522.3</t>
+  </si>
+  <si>
+    <t>00193121400003663840000003473568000002940717</t>
+  </si>
+  <si>
     <t>JOSEMAR - BA</t>
   </si>
   <si>
+    <t>FOCUS - COMERCIO DE MEDICAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>01004900.1</t>
+  </si>
+  <si>
+    <t>00192123700003867340000003473568000002964017</t>
+  </si>
+  <si>
+    <t>01004900.2</t>
+  </si>
+  <si>
+    <t>00192124400002144590000003473568000002964117</t>
+  </si>
+  <si>
+    <t>01004900.3</t>
+  </si>
+  <si>
+    <t>00197125100002144590000003473568000002964217</t>
+  </si>
+  <si>
+    <t>01004900.4</t>
+  </si>
+  <si>
+    <t>00191125800002144590000003473568000002964317</t>
+  </si>
+  <si>
+    <t>BR MEDICAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>01005075.3</t>
+  </si>
+  <si>
+    <t>00195127000004480000000003473568000002981317</t>
+  </si>
+  <si>
     <t>PHARMACEUTICA DISTRIBUIDORA DE MAT. E MED. HOSPITA</t>
   </si>
   <si>
     <t>01005217.1BPBPBPBP</t>
   </si>
   <si>
-    <t>BA</t>
-  </si>
-  <si>
     <t>01005217.2BP</t>
   </si>
   <si>
-    <t>MALCA - CE</t>
-  </si>
-  <si>
-    <t>BR MEDICAMENTOS LTDA</t>
-  </si>
-  <si>
     <t>01005144.3</t>
   </si>
   <si>
-    <t>CE</t>
-  </si>
-  <si>
     <t>01005217.3BPBPBP</t>
   </si>
   <si>
+    <t>DENTAL SORRISO LTDA</t>
+  </si>
+  <si>
+    <t>01005781.1</t>
+  </si>
+  <si>
+    <t>00194138000000806340000003473568000003029417</t>
+  </si>
+  <si>
+    <t>01005781.2</t>
+  </si>
+  <si>
+    <t>00194138700000503280000003473568000003029517</t>
+  </si>
+  <si>
+    <t>01005781.3</t>
+  </si>
+  <si>
+    <t>00199139400000503280000003473568000003029617</t>
+  </si>
+  <si>
+    <t>MAIS SAUDE COMERCIO DE PRODUTOS HOSPITALARES LTDA</t>
+  </si>
+  <si>
+    <t>01005683.3</t>
+  </si>
+  <si>
+    <t>34199139500005466661090002533378120992717000</t>
+  </si>
+  <si>
     <t>01006508.1</t>
   </si>
   <si>
@@ -111,174 +525,12 @@
     <t>01006508.3</t>
   </si>
   <si>
-    <t>MARCELO LOPES</t>
-  </si>
-  <si>
     <t>GRADUAL COMERCIO E SERVICOS LTDA</t>
   </si>
   <si>
     <t>01006433.3BP</t>
   </si>
   <si>
-    <t>PB</t>
-  </si>
-  <si>
-    <t>FAROMED COMERCIO DE MATERIAIS HOSPITALARES LTDA</t>
-  </si>
-  <si>
-    <t>01001617.1</t>
-  </si>
-  <si>
-    <t>BANCO DO BRASIL</t>
-  </si>
-  <si>
-    <t>PE</t>
-  </si>
-  <si>
-    <t>00191964000001264870000003473568000002622117</t>
-  </si>
-  <si>
-    <t>01001548.3</t>
-  </si>
-  <si>
-    <t>00193965200000384000000003473568000002617517</t>
-  </si>
-  <si>
-    <t>01001617.2</t>
-  </si>
-  <si>
-    <t>00191965400000816000000003473568000002622217</t>
-  </si>
-  <si>
-    <t>01001617.3</t>
-  </si>
-  <si>
-    <t>00192966800000816000000003473568000002622317</t>
-  </si>
-  <si>
-    <t>MARIO JR - PE/PB/RN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RN COMERCIO DE MEDICAMENTOS E MATERIAL HOSPITALAR </t>
-  </si>
-  <si>
-    <t>01003504.1</t>
-  </si>
-  <si>
-    <t>RN</t>
-  </si>
-  <si>
-    <t>00191999500002541000000003473568000002851217</t>
-  </si>
-  <si>
-    <t>01003504.2</t>
-  </si>
-  <si>
-    <t>00195100200002541000000003473568000002851317</t>
-  </si>
-  <si>
-    <t>01003504.4</t>
-  </si>
-  <si>
-    <t>00194101600002541000000003473568000002851517</t>
-  </si>
-  <si>
-    <t>01003504.6</t>
-  </si>
-  <si>
-    <t>00193103000002541000000003473568000002851717</t>
-  </si>
-  <si>
-    <t>AGILE DISTRIBUIDORA LTDA</t>
-  </si>
-  <si>
-    <t>01003847.2</t>
-  </si>
-  <si>
-    <t>00196107900002287070000003473568000002883717</t>
-  </si>
-  <si>
-    <t>01003847.3</t>
-  </si>
-  <si>
-    <t>00193108600002287060000003473568000002883817</t>
-  </si>
-  <si>
-    <t>ISA COMERCIO VAREJISTA DE PRODUTOS HOSPITALARES LT</t>
-  </si>
-  <si>
-    <t>01004522.1</t>
-  </si>
-  <si>
-    <t>00191118600004572620000003473568000002940517</t>
-  </si>
-  <si>
-    <t>01004522.2</t>
-  </si>
-  <si>
-    <t>00191120000003663840000003473568000002940617</t>
-  </si>
-  <si>
-    <t>01004522.3</t>
-  </si>
-  <si>
-    <t>00193121400003663840000003473568000002940717</t>
-  </si>
-  <si>
-    <t>FOCUS - COMERCIO DE MEDICAMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>01004900.1</t>
-  </si>
-  <si>
-    <t>00192123700003867340000003473568000002964017</t>
-  </si>
-  <si>
-    <t>01004900.2</t>
-  </si>
-  <si>
-    <t>00192124400002144590000003473568000002964117</t>
-  </si>
-  <si>
-    <t>01004900.3</t>
-  </si>
-  <si>
-    <t>00197125100002144590000003473568000002964217</t>
-  </si>
-  <si>
-    <t>01004900.4</t>
-  </si>
-  <si>
-    <t>00191125800002144590000003473568000002964317</t>
-  </si>
-  <si>
-    <t>01005075.3</t>
-  </si>
-  <si>
-    <t>00195127000004480000000003473568000002981317</t>
-  </si>
-  <si>
-    <t>DENTAL SORRISO LTDA</t>
-  </si>
-  <si>
-    <t>01005781.1</t>
-  </si>
-  <si>
-    <t>00194138000000806340000003473568000003029417</t>
-  </si>
-  <si>
-    <t>01005781.2</t>
-  </si>
-  <si>
-    <t>00194138700000503280000003473568000003029517</t>
-  </si>
-  <si>
-    <t>01005781.3</t>
-  </si>
-  <si>
-    <t>00199139400000503280000003473568000003029617</t>
-  </si>
-  <si>
     <t>MARCOS DUTRA - PI</t>
   </si>
   <si>
@@ -300,18 +552,12 @@
     <t>00195154900002818370000003473568000003141117</t>
   </si>
   <si>
-    <t>DANILO - AL/SE/BA</t>
-  </si>
-  <si>
     <t>JT COSTA COMERCIAL LTDA</t>
   </si>
   <si>
     <t>01007005.1</t>
   </si>
   <si>
-    <t>SE</t>
-  </si>
-  <si>
     <t>00197155200018957860000003473568000003145817</t>
   </si>
   <si>
@@ -321,16 +567,46 @@
     <t>00193156200009716000000003473568000003145917</t>
   </si>
   <si>
+    <t>ALINE CERBINO - PA</t>
+  </si>
+  <si>
+    <t>CRISTALFARMA COMERCIO IMPORT E EXPORT LTDA</t>
+  </si>
+  <si>
+    <t>01006976.1</t>
+  </si>
+  <si>
+    <t>BRADESCO</t>
+  </si>
+  <si>
+    <t>PA</t>
+  </si>
+  <si>
+    <t>23791156200006389240435090000000114600304920</t>
+  </si>
+  <si>
     <t>01006941.4</t>
   </si>
   <si>
     <t>00194156300002818370000003473568000003141317</t>
   </si>
   <si>
-    <t>01006941.5</t>
-  </si>
-  <si>
-    <t>00191157000002818360000003473568000003141417</t>
+    <t>01007023.1</t>
+  </si>
+  <si>
+    <t>DAYCOVAL</t>
+  </si>
+  <si>
+    <t>70799156900005741360001121205064100656764415</t>
+  </si>
+  <si>
+    <t>CIRURGICA MONTEBELLO LTDA</t>
+  </si>
+  <si>
+    <t>01007187.2</t>
+  </si>
+  <si>
+    <t>70791157100010080000001121205064100656766196</t>
   </si>
   <si>
     <t>01007005.3</t>
@@ -339,7 +615,43 @@
     <t>00196157200009716000000003473568000003146017</t>
   </si>
   <si>
-    <t>CIRURGICA MONTEBELLO LTDA</t>
+    <t>01006958.6</t>
+  </si>
+  <si>
+    <t>70798157300023168600001121205064100656764092</t>
+  </si>
+  <si>
+    <t>PLENA DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>01006957.2</t>
+  </si>
+  <si>
+    <t>70792157400010666670001121205064100656763953</t>
+  </si>
+  <si>
+    <t>01006999.1</t>
+  </si>
+  <si>
+    <t>70799157400006500000001121205064100656764282</t>
+  </si>
+  <si>
+    <t>01007020.1</t>
+  </si>
+  <si>
+    <t>70799157400004950170001121205064100656764449</t>
+  </si>
+  <si>
+    <t>01006920.2</t>
+  </si>
+  <si>
+    <t>70794157500007551880001121205064100656763987</t>
+  </si>
+  <si>
+    <t>01007125.4</t>
+  </si>
+  <si>
+    <t>70791157600004320000001121205064100656765123</t>
   </si>
   <si>
     <t>01007301.1</t>
@@ -348,6 +660,42 @@
     <t>00192157700018600000000003473568000003161317</t>
   </si>
   <si>
+    <t>01006976.2</t>
+  </si>
+  <si>
+    <t>23791157700004216670435090000000114700304920</t>
+  </si>
+  <si>
+    <t>01007187.3</t>
+  </si>
+  <si>
+    <t>70793157800010080000001121205064100656766204</t>
+  </si>
+  <si>
+    <t>DROGUISTA CEARENSE LTDA</t>
+  </si>
+  <si>
+    <t>01007171.2</t>
+  </si>
+  <si>
+    <t>70794157800003640000001121205064100656766162</t>
+  </si>
+  <si>
+    <t>01007175.2</t>
+  </si>
+  <si>
+    <t>34193157800001660331090002618768120992717000</t>
+  </si>
+  <si>
+    <t>COBERMED COMERCIO DE MATERIAIS MEDICOS LTDA</t>
+  </si>
+  <si>
+    <t>01007194.1</t>
+  </si>
+  <si>
+    <t>70797157900006265000001121205064100656766642</t>
+  </si>
+  <si>
     <t>FELIPE AQUINO - MT</t>
   </si>
   <si>
@@ -363,43 +711,127 @@
     <t>00198158000007694400000003473568000003158817</t>
   </si>
   <si>
+    <t>01007249.1</t>
+  </si>
+  <si>
+    <t>70793158000011660110001121205064100656766915</t>
+  </si>
+  <si>
     <t>01007005.4</t>
   </si>
   <si>
     <t>00197158200009716000000003473568000003146117</t>
   </si>
   <si>
+    <t>FERMATA LTDA</t>
+  </si>
+  <si>
+    <t>01006989.2</t>
+  </si>
+  <si>
+    <t>70795158200004082050001121205064100656764191</t>
+  </si>
+  <si>
+    <t>01007125.5</t>
+  </si>
+  <si>
+    <t>70799158300004320000001121205064100656765131</t>
+  </si>
+  <si>
+    <t>01006877.3</t>
+  </si>
+  <si>
+    <t>23797158300006265000435090000000110700304920</t>
+  </si>
+  <si>
+    <t>01006922.3</t>
+  </si>
+  <si>
+    <t>70798158300011200000001121205064100656763896</t>
+  </si>
+  <si>
     <t>01007301.2</t>
   </si>
   <si>
     <t>00197158400018600000000003473568000003161417</t>
   </si>
   <si>
+    <t>01007023.2</t>
+  </si>
+  <si>
+    <t>70791158400003789090001121205064100656764423</t>
+  </si>
+  <si>
+    <t>01007187.4</t>
+  </si>
+  <si>
+    <t>70792158500010080000001121205064100656766212</t>
+  </si>
+  <si>
+    <t>VITAL DISTRIBUIDORA LTDA</t>
+  </si>
+  <si>
+    <t>01007168.3</t>
+  </si>
+  <si>
+    <t>34196158500002051221090002617698120992717000</t>
+  </si>
+  <si>
+    <t>01007249.2</t>
+  </si>
+  <si>
+    <t>70792158700011660110001121205064100656766923</t>
+  </si>
+  <si>
     <t>01007265.2</t>
   </si>
   <si>
     <t>00192158700007694400000003473568000003158917</t>
   </si>
   <si>
+    <t>01006920.3</t>
+  </si>
+  <si>
+    <t>70797159000007551880001121205064100656763995</t>
+  </si>
+  <si>
     <t>01007301.3</t>
   </si>
   <si>
     <t>00191159100018600000000003473568000003161517</t>
   </si>
   <si>
+    <t>01007187.5</t>
+  </si>
+  <si>
+    <t>70791159200010080000001121205064100656766220</t>
+  </si>
+  <si>
+    <t>01006976.3</t>
+  </si>
+  <si>
+    <t>23792159200004216660435090000000114800304920</t>
+  </si>
+  <si>
     <t>01007005.5</t>
   </si>
   <si>
     <t>00198159200009716000000003473568000003146217</t>
   </si>
   <si>
-    <t>A. M. FARMA MEDICAMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>01007018.3</t>
-  </si>
-  <si>
-    <t>00195159400005556100000003473568000003149117</t>
+    <t>ATACAMED COMERCIO LTDA</t>
+  </si>
+  <si>
+    <t>01007311.2</t>
+  </si>
+  <si>
+    <t>23792159300002754000435090000000130100304920</t>
+  </si>
+  <si>
+    <t>01007194.2</t>
+  </si>
+  <si>
+    <t>70793159400006265000001121205064100656766659</t>
   </si>
   <si>
     <t>01007265.3</t>
@@ -408,535 +840,82 @@
     <t>00199159400007694400000003473568000003159017</t>
   </si>
   <si>
-    <t>ALINE CERBINO - PA</t>
-  </si>
-  <si>
-    <t>CRISTALFARMA COMERCIO IMPORT E EXPORT LTDA</t>
-  </si>
-  <si>
-    <t>01006976.1</t>
-  </si>
-  <si>
-    <t>BRADESCO</t>
-  </si>
-  <si>
-    <t>PA</t>
-  </si>
-  <si>
-    <t>23791156200006389240435090000000114600304920</t>
-  </si>
-  <si>
-    <t>01006976.2</t>
-  </si>
-  <si>
-    <t>23791157700004216670435090000000114700304920</t>
-  </si>
-  <si>
-    <t>COBERMED COMERCIO DE MATERIAIS MEDICOS LTDA</t>
-  </si>
-  <si>
-    <t>01006877.3</t>
-  </si>
-  <si>
-    <t>AL</t>
-  </si>
-  <si>
-    <t>23797158300006265000435090000000110700304920</t>
-  </si>
-  <si>
-    <t>ATACAMED COMERCIO LTDA</t>
-  </si>
-  <si>
-    <t>01007311.1</t>
-  </si>
-  <si>
-    <t>23796158600002754000435090000000130000304920</t>
-  </si>
-  <si>
-    <t>01006976.3</t>
-  </si>
-  <si>
-    <t>23792159200004216660435090000000114800304920</t>
-  </si>
-  <si>
-    <t>01007311.2</t>
-  </si>
-  <si>
-    <t>23792159300002754000435090000000130100304920</t>
-  </si>
-  <si>
-    <t>01006920.1</t>
-  </si>
-  <si>
-    <t>DAYCOVAL</t>
-  </si>
-  <si>
-    <t>70797156000011442870001121205064100656763979</t>
-  </si>
-  <si>
-    <t>PLENA DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>01006922.1</t>
-  </si>
-  <si>
-    <t>70795156300011200000001121205064100656763870</t>
-  </si>
-  <si>
-    <t>01007187.1</t>
-  </si>
-  <si>
-    <t>70791156400010080000001121205064100656766188</t>
-  </si>
-  <si>
-    <t>01006958.5</t>
-  </si>
-  <si>
-    <t>70799156600023168600001121205064100656764084</t>
-  </si>
-  <si>
-    <t>01007023.1</t>
-  </si>
-  <si>
-    <t>70799156900005741360001121205064100656764415</t>
-  </si>
-  <si>
-    <t>01007187.2</t>
-  </si>
-  <si>
-    <t>70791157100010080000001121205064100656766196</t>
-  </si>
-  <si>
-    <t>01006958.6</t>
-  </si>
-  <si>
-    <t>70798157300023168600001121205064100656764092</t>
-  </si>
-  <si>
-    <t>01006922.2</t>
-  </si>
-  <si>
-    <t>70792157300011200000001121205064100656763888</t>
-  </si>
-  <si>
-    <t>01006957.2</t>
-  </si>
-  <si>
-    <t>70792157400010666670001121205064100656763953</t>
-  </si>
-  <si>
-    <t>01006999.1</t>
-  </si>
-  <si>
-    <t>70799157400006500000001121205064100656764282</t>
-  </si>
-  <si>
-    <t>01007020.1</t>
-  </si>
-  <si>
-    <t>70799157400004950170001121205064100656764449</t>
-  </si>
-  <si>
-    <t>01006920.2</t>
-  </si>
-  <si>
-    <t>70794157500007551880001121205064100656763987</t>
-  </si>
-  <si>
-    <t>01007125.4</t>
-  </si>
-  <si>
-    <t>70791157600004320000001121205064100656765123</t>
-  </si>
-  <si>
-    <t>01007187.3</t>
-  </si>
-  <si>
-    <t>70793157800010080000001121205064100656766204</t>
-  </si>
-  <si>
-    <t>DROGUISTA CEARENSE LTDA</t>
-  </si>
-  <si>
-    <t>01007171.2</t>
-  </si>
-  <si>
-    <t>70794157800003640000001121205064100656766162</t>
-  </si>
-  <si>
-    <t>01007194.1</t>
-  </si>
-  <si>
-    <t>70797157900006265000001121205064100656766642</t>
-  </si>
-  <si>
-    <t>01007249.1</t>
-  </si>
-  <si>
-    <t>70793158000011660110001121205064100656766915</t>
-  </si>
-  <si>
-    <t>FERMATA LTDA</t>
-  </si>
-  <si>
-    <t>01006989.2</t>
-  </si>
-  <si>
-    <t>70795158200004082050001121205064100656764191</t>
-  </si>
-  <si>
-    <t>01007125.5</t>
-  </si>
-  <si>
-    <t>70799158300004320000001121205064100656765131</t>
-  </si>
-  <si>
-    <t>01006922.3</t>
-  </si>
-  <si>
-    <t>70798158300011200000001121205064100656763896</t>
-  </si>
-  <si>
-    <t>01007023.2</t>
-  </si>
-  <si>
-    <t>70791158400003789090001121205064100656764423</t>
-  </si>
-  <si>
-    <t>01007187.4</t>
-  </si>
-  <si>
-    <t>70792158500010080000001121205064100656766212</t>
+    <t>01007249.3</t>
+  </si>
+  <si>
+    <t>70791159400011660110001121205064100656766931</t>
   </si>
   <si>
     <t xml:space="preserve">ZOE MED COMERCIO DE PRODUTOS MEDICOS HOSPITALARES </t>
   </si>
   <si>
-    <t>01007270.1</t>
-  </si>
-  <si>
-    <t>70793158500008565680001121205064100656766972</t>
-  </si>
-  <si>
-    <t>ELIENE RESENDE - RJ</t>
-  </si>
-  <si>
-    <t>MEDKA DISTRIBUIDORA HOSPITALAR LTDA</t>
-  </si>
-  <si>
-    <t>01007278.1</t>
-  </si>
-  <si>
-    <t>RJ</t>
-  </si>
-  <si>
-    <t>70793158600008973500001121205064100656767319</t>
-  </si>
-  <si>
-    <t>01007249.2</t>
-  </si>
-  <si>
-    <t>70792158700011660110001121205064100656766923</t>
-  </si>
-  <si>
-    <t>01006920.3</t>
-  </si>
-  <si>
-    <t>70797159000007551880001121205064100656763995</t>
-  </si>
-  <si>
-    <t>01007187.5</t>
-  </si>
-  <si>
-    <t>70791159200010080000001121205064100656766220</t>
-  </si>
-  <si>
-    <t>AMAZONIA HOSPITALAR LTDA</t>
-  </si>
-  <si>
-    <t>01007224.3</t>
-  </si>
-  <si>
-    <t>MA</t>
-  </si>
-  <si>
-    <t>70793159400002992000001121205064100656766873</t>
-  </si>
-  <si>
-    <t>01007194.2</t>
-  </si>
-  <si>
-    <t>70793159400006265000001121205064100656766659</t>
-  </si>
-  <si>
-    <t>01007249.3</t>
-  </si>
-  <si>
-    <t>70791159400011660110001121205064100656766931</t>
-  </si>
-  <si>
-    <t>RB DISTRIBUIDORA DE PRODUTOS HOSPITALARES LTDA</t>
-  </si>
-  <si>
-    <t>01001504.1</t>
-  </si>
-  <si>
-    <t>ITAU</t>
-  </si>
-  <si>
-    <t>34192961600009391781090001019578120992717000</t>
-  </si>
-  <si>
-    <t>01001504.3</t>
-  </si>
-  <si>
-    <t>34194963600005418001090001019738120992717000</t>
-  </si>
-  <si>
-    <t>01001504.4</t>
-  </si>
-  <si>
-    <t>34194964600005418001090001019818120992717000</t>
-  </si>
-  <si>
-    <t>VEC HOSPITALAR LTDA ME</t>
-  </si>
-  <si>
-    <t>01002233.1</t>
-  </si>
-  <si>
-    <t>34192975300001674521090001106858120992717000</t>
-  </si>
-  <si>
-    <t>01002233.3</t>
-  </si>
-  <si>
-    <t>34192978300000873601090001107018120992717000</t>
-  </si>
-  <si>
-    <t>01002233.5</t>
-  </si>
-  <si>
-    <t>34191981300000873601090001107278120992717000</t>
-  </si>
-  <si>
-    <t>GLOBAL MEDIC LTDA</t>
-  </si>
-  <si>
-    <t>01003029.2</t>
-  </si>
-  <si>
-    <t>34195989000002000001090001238528120992717000</t>
-  </si>
-  <si>
-    <t>01003029.1</t>
-  </si>
-  <si>
-    <t>34197987600003204341090001238458120992717000</t>
-  </si>
-  <si>
-    <t>MOISES</t>
-  </si>
-  <si>
-    <t>AC FL FARMACIA E DROGARIA LTDA</t>
-  </si>
-  <si>
-    <t>01002991.3</t>
-  </si>
-  <si>
-    <t>34196989800004439901090001240908120992717000</t>
-  </si>
-  <si>
-    <t>01003029.3</t>
-  </si>
-  <si>
-    <t>34195990400002000001090001238608120992717000</t>
-  </si>
-  <si>
-    <t>01002938.2</t>
-  </si>
-  <si>
-    <t>34194986400001216861090001218808120992717000</t>
-  </si>
-  <si>
-    <t>01002951.2</t>
-  </si>
-  <si>
-    <t>34193985900001843871090001228138120992717000</t>
-  </si>
-  <si>
-    <t>01002938.3</t>
-  </si>
-  <si>
-    <t>34192987800001216861090001218988120992717000</t>
-  </si>
-  <si>
-    <t>01002991.4</t>
-  </si>
-  <si>
-    <t>34197991200004439901090001241088120992717000</t>
-  </si>
-  <si>
-    <t>01002951.3</t>
-  </si>
-  <si>
-    <t>34194986600001843881090001228218120992717000</t>
-  </si>
-  <si>
-    <t>SERGIO ROBERTO - PB</t>
-  </si>
-  <si>
-    <t>RUBEM E MEDEIROS PRODUTOS PARA SAUDE LTDA</t>
-  </si>
-  <si>
-    <t>01003384.3</t>
-  </si>
-  <si>
-    <t>34191997800001118401090001280758120992717000</t>
-  </si>
-  <si>
-    <t>01003464.4</t>
-  </si>
-  <si>
-    <t>34194998500003296801090001307668120992717000</t>
-  </si>
-  <si>
-    <t>01003409.6</t>
-  </si>
-  <si>
-    <t>34199998900002330001090001290998120992717000</t>
-  </si>
-  <si>
-    <t>01003464.5</t>
-  </si>
-  <si>
-    <t>34198999200003296801090001307748120992717000</t>
-  </si>
-  <si>
-    <t>01003464.6</t>
-  </si>
-  <si>
-    <t>34191999900003296801090001307828120992717000</t>
-  </si>
-  <si>
-    <t>01003589.1</t>
-  </si>
-  <si>
-    <t>34197101700007562781090001319968120992717000</t>
-  </si>
-  <si>
-    <t>01003589.2</t>
-  </si>
-  <si>
-    <t>34198102400007562781090001320028120992717000</t>
-  </si>
-  <si>
-    <t>MED-K COMERCIO LTDA</t>
-  </si>
-  <si>
-    <t>01003592.2</t>
-  </si>
-  <si>
-    <t>34194102400001154561090001320448120992717000</t>
-  </si>
-  <si>
-    <t>01003589.3</t>
-  </si>
-  <si>
-    <t>34191103100007562781090001320108120992717000</t>
-  </si>
-  <si>
-    <t>01003592.3</t>
-  </si>
-  <si>
-    <t>34194103100001154561090001320518120992717000</t>
-  </si>
-  <si>
-    <t>01003592.4</t>
-  </si>
-  <si>
-    <t>34194103800001154561090001320698120992717000</t>
-  </si>
-  <si>
-    <t>01003589.4</t>
-  </si>
-  <si>
-    <t>34197103800007562761090001320288120992717000</t>
-  </si>
-  <si>
-    <t>01003592.5</t>
-  </si>
-  <si>
-    <t>34198104500001154561090001320778120992717000</t>
-  </si>
-  <si>
-    <t>ICARE MED LTDA</t>
-  </si>
-  <si>
-    <t>01003747.1</t>
-  </si>
-  <si>
-    <t>34194105100006169531090001342898120992717000</t>
-  </si>
-  <si>
-    <t>01003747.2</t>
-  </si>
-  <si>
-    <t>34198105800003850001090001342978120992717000</t>
-  </si>
-  <si>
-    <t>01003747.3</t>
-  </si>
-  <si>
-    <t>34196106500003850001090001343058120992717000</t>
-  </si>
-  <si>
-    <t>01003828.1</t>
-  </si>
-  <si>
-    <t>34191106500006089411090001356748120992717000</t>
-  </si>
-  <si>
-    <t>01003828.2</t>
-  </si>
-  <si>
-    <t>34196107200003800001090001356828120992717000</t>
-  </si>
-  <si>
-    <t>01003828.3</t>
-  </si>
-  <si>
-    <t>34191107900003800001090001356908120992717000</t>
-  </si>
-  <si>
-    <t>MAIS SAUDE COMERCIO DE PRODUTOS HOSPITALARES LTDA</t>
-  </si>
-  <si>
-    <t>01005683.3</t>
-  </si>
-  <si>
-    <t>34199139500005466661090002533378120992717000</t>
-  </si>
-  <si>
-    <t>01007175.2</t>
-  </si>
-  <si>
-    <t>34193157800001660331090002618768120992717000</t>
-  </si>
-  <si>
-    <t>VITAL DISTRIBUIDORA LTDA</t>
-  </si>
-  <si>
-    <t>01007168.3</t>
-  </si>
-  <si>
-    <t>34196158500002051221090002617698120992717000</t>
-  </si>
-  <si>
-    <t>01007274.2</t>
-  </si>
-  <si>
-    <t>34192159000001664001090002623538120992717000</t>
+    <t>01007270.2</t>
+  </si>
+  <si>
+    <t>70797159500004750000001121205064100656766980</t>
+  </si>
+  <si>
+    <t>01007274.3</t>
+  </si>
+  <si>
+    <t>34196159700001664001090002623618120992717000</t>
+  </si>
+  <si>
+    <t>01006989.3</t>
+  </si>
+  <si>
+    <t>70796159700004082040001121205064100656764209</t>
+  </si>
+  <si>
+    <t>01007301.4</t>
+  </si>
+  <si>
+    <t>00196159800018600000000003473568000003161617</t>
+  </si>
+  <si>
+    <t>ASPEN SERVICE COMERCIO LTDA</t>
+  </si>
+  <si>
+    <t>01007117.2</t>
+  </si>
+  <si>
+    <t>70793159800023355330001121205064100656765677</t>
+  </si>
+  <si>
+    <t>01007023.3</t>
+  </si>
+  <si>
+    <t>70794159900003789100001121205064100656764431</t>
+  </si>
+  <si>
+    <t>01007269.2</t>
+  </si>
+  <si>
+    <t>70792160000008947500001121205064100656767145</t>
+  </si>
+  <si>
+    <t>01007311.3</t>
+  </si>
+  <si>
+    <t>23797160000002754000435090000000130200304920</t>
+  </si>
+  <si>
+    <t>01007222.1</t>
+  </si>
+  <si>
+    <t>70798160100011266120001121205064100656766576</t>
+  </si>
+  <si>
+    <t>01007249.4</t>
+  </si>
+  <si>
+    <t>70791160100011660110001121205064100656766949</t>
+  </si>
+  <si>
+    <t>01007265.4</t>
+  </si>
+  <si>
+    <t>00191160100007694400000003473568000003159117</t>
   </si>
 </sst>
 </file>
@@ -1366,7 +1345,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O120"/>
+  <dimension ref="A1:O119"/>
   <sheetFormatPr defaultColWidth="12.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.85546875" style="1" customWidth="1"/>
@@ -1436,7 +1415,7 @@
     </row>
     <row r="2" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
-        <v>45959</v>
+        <v>45296</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>15</v>
@@ -1448,30 +1427,34 @@
         <v>17</v>
       </c>
       <c r="E2" s="3">
-        <v>45980</v>
+        <v>45326</v>
       </c>
       <c r="F2" s="5">
-        <v>28666.44</v>
+        <v>5418</v>
       </c>
       <c r="G2" s="5">
-        <v>28666.44</v>
+        <v>9391.7800000000007</v>
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="6">
-        <v>328</v>
-      </c>
-      <c r="J2" s="4"/>
+        <v>988</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="K2" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
+      <c r="M2" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="N2" s="4"/>
       <c r="O2" s="4"/>
     </row>
     <row r="3" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
-        <v>45959</v>
+        <v>45296</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>15</v>
@@ -1480,68 +1463,76 @@
         <v>16</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E3" s="3">
-        <v>45987</v>
+        <v>45346</v>
       </c>
       <c r="F3" s="5">
-        <v>33844.160000000003</v>
+        <v>5418</v>
       </c>
       <c r="G3" s="5">
-        <v>33844.160000000003</v>
+        <v>5418</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="6">
-        <v>321</v>
-      </c>
-      <c r="J3" s="4"/>
+        <v>968</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="K3" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
+      <c r="M3" s="4" t="s">
+        <v>22</v>
+      </c>
       <c r="N3" s="4"/>
       <c r="O3" s="4"/>
     </row>
     <row r="4" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
-        <v>45947</v>
+        <v>45322</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E4" s="3">
-        <v>45989</v>
+        <v>45350</v>
       </c>
       <c r="F4" s="5">
-        <v>3220</v>
+        <v>816</v>
       </c>
       <c r="G4" s="5">
-        <v>3220</v>
+        <v>1264.8699999999999</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="6">
-        <v>319</v>
-      </c>
-      <c r="J4" s="4"/>
+        <v>964</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>26</v>
+      </c>
       <c r="K4" s="4" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
+      <c r="M4" s="4" t="s">
+        <v>28</v>
+      </c>
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
     </row>
     <row r="5" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
-        <v>45959</v>
+        <v>45296</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>15</v>
@@ -1550,1644 +1541,1664 @@
         <v>16</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E5" s="3">
-        <v>45994</v>
+        <v>45356</v>
       </c>
       <c r="F5" s="5">
-        <v>14483.06</v>
+        <v>5418</v>
       </c>
       <c r="G5" s="5">
-        <v>14483.06</v>
+        <v>5418</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="6">
-        <v>314</v>
-      </c>
-      <c r="J5" s="4"/>
+        <v>958</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="K5" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
+      <c r="M5" s="4" t="s">
+        <v>30</v>
+      </c>
       <c r="N5" s="4"/>
       <c r="O5" s="4"/>
     </row>
     <row r="6" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
-        <v>46171</v>
+        <v>45306</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E6" s="3">
-        <v>46192</v>
+        <v>45362</v>
       </c>
       <c r="F6" s="5">
-        <v>4676.8500000000004</v>
+        <v>384</v>
       </c>
       <c r="G6" s="5">
-        <v>7494.53</v>
+        <v>384</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="6">
-        <v>116</v>
-      </c>
-      <c r="J6" s="4"/>
+        <v>952</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>26</v>
+      </c>
       <c r="K6" s="4" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
+      <c r="M6" s="4" t="s">
+        <v>32</v>
+      </c>
       <c r="N6" s="4"/>
       <c r="O6" s="4"/>
     </row>
     <row r="7" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
-        <v>46171</v>
+        <v>45322</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="E7" s="3">
-        <v>46199</v>
+        <v>45364</v>
       </c>
       <c r="F7" s="5">
-        <v>4676.8500000000004</v>
+        <v>816</v>
       </c>
       <c r="G7" s="5">
-        <v>4676.8500000000004</v>
+        <v>816</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="6">
-        <v>109</v>
-      </c>
-      <c r="J7" s="4"/>
+        <v>950</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>26</v>
+      </c>
       <c r="K7" s="4" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
+      <c r="M7" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="N7" s="4"/>
       <c r="O7" s="4"/>
     </row>
     <row r="8" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
-        <v>46171</v>
+        <v>45322</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E8" s="3">
-        <v>46206</v>
+        <v>45378</v>
       </c>
       <c r="F8" s="5">
-        <v>4676.8500000000004</v>
+        <v>816</v>
       </c>
       <c r="G8" s="5">
-        <v>4676.8500000000004</v>
+        <v>816</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="6">
-        <v>102</v>
-      </c>
-      <c r="J8" s="4"/>
+        <v>936</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>26</v>
+      </c>
       <c r="K8" s="4" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
+      <c r="M8" s="4" t="s">
+        <v>36</v>
+      </c>
       <c r="N8" s="4"/>
       <c r="O8" s="4"/>
     </row>
     <row r="9" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
-        <v>46162</v>
+        <v>45433</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E9" s="3">
-        <v>46222</v>
+        <v>45463</v>
       </c>
       <c r="F9" s="5">
-        <v>22349.79</v>
+        <v>873.6</v>
       </c>
       <c r="G9" s="5">
-        <v>22349.79</v>
+        <v>1674.52</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="6">
-        <v>86</v>
-      </c>
-      <c r="J9" s="4"/>
+        <v>851</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="K9" s="4" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="L9" s="4"/>
-      <c r="M9" s="4"/>
+      <c r="M9" s="4" t="s">
+        <v>40</v>
+      </c>
       <c r="N9" s="4"/>
       <c r="O9" s="4"/>
     </row>
     <row r="10" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
-        <v>45322</v>
+        <v>45433</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="E10" s="3">
-        <v>45350</v>
+        <v>45493</v>
       </c>
       <c r="F10" s="5">
-        <v>816</v>
+        <v>873.6</v>
       </c>
       <c r="G10" s="5">
-        <v>1264.8699999999999</v>
+        <v>873.6</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="6">
-        <v>958</v>
+        <v>821</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="L10" s="4"/>
       <c r="M10" s="4" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="N10" s="4"/>
       <c r="O10" s="4"/>
     </row>
     <row r="11" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
-        <v>45306</v>
+        <v>45433</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E11" s="3">
-        <v>45362</v>
+        <v>45523</v>
       </c>
       <c r="F11" s="5">
-        <v>384</v>
+        <v>873.6</v>
       </c>
       <c r="G11" s="5">
-        <v>384</v>
+        <v>873.6</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="6">
-        <v>946</v>
+        <v>791</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="L11" s="4"/>
       <c r="M11" s="4" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="N11" s="4"/>
       <c r="O11" s="4"/>
     </row>
     <row r="12" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
-        <v>45322</v>
+        <v>45558</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="E12" s="3">
-        <v>45364</v>
+        <v>45600</v>
       </c>
       <c r="F12" s="5">
-        <v>816</v>
+        <v>2000</v>
       </c>
       <c r="G12" s="5">
-        <v>816</v>
+        <v>2000</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="6">
-        <v>944</v>
+        <v>714</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="L12" s="4"/>
       <c r="M12" s="4" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="N12" s="4"/>
       <c r="O12" s="4"/>
     </row>
     <row r="13" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
-        <v>45322</v>
+        <v>45558</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="E13" s="3">
-        <v>45378</v>
+        <v>45607</v>
       </c>
       <c r="F13" s="5">
-        <v>816</v>
+        <v>2000</v>
       </c>
       <c r="G13" s="5">
-        <v>816</v>
+        <v>3204.34</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="6">
-        <v>930</v>
+        <v>707</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="L13" s="4"/>
       <c r="M13" s="4" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N13" s="4"/>
       <c r="O13" s="4"/>
     </row>
     <row r="14" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
-        <v>45677</v>
+        <v>45552</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="E14" s="3">
-        <v>45705</v>
+        <v>45608</v>
       </c>
       <c r="F14" s="5">
-        <v>2541</v>
+        <v>4439.8999999999996</v>
       </c>
       <c r="G14" s="5">
-        <v>2541</v>
+        <v>4439.8999999999996</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="6">
-        <v>603</v>
+        <v>706</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="L14" s="4"/>
       <c r="M14" s="4" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="N14" s="4"/>
       <c r="O14" s="4"/>
     </row>
     <row r="15" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
-        <v>45677</v>
+        <v>45558</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="E15" s="3">
-        <v>45712</v>
+        <v>45614</v>
       </c>
       <c r="F15" s="5">
-        <v>2541</v>
+        <v>2000</v>
       </c>
       <c r="G15" s="5">
-        <v>2541</v>
+        <v>2000</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="6">
-        <v>596</v>
+        <v>700</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="L15" s="4"/>
       <c r="M15" s="4" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="N15" s="4"/>
       <c r="O15" s="4"/>
     </row>
     <row r="16" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
-        <v>45677</v>
+        <v>45546</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E16" s="3">
-        <v>45726</v>
+        <v>45615</v>
       </c>
       <c r="F16" s="5">
-        <v>2541</v>
+        <v>1216.8599999999999</v>
       </c>
       <c r="G16" s="5">
-        <v>2541</v>
+        <v>1216.8599999999999</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="6">
-        <v>582</v>
+        <v>699</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="L16" s="4"/>
       <c r="M16" s="4" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="N16" s="4"/>
       <c r="O16" s="4"/>
     </row>
     <row r="17" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
-        <v>45677</v>
+        <v>45548</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="E17" s="3">
-        <v>45740</v>
+        <v>45617</v>
       </c>
       <c r="F17" s="5">
-        <v>2541</v>
+        <v>1843.87</v>
       </c>
       <c r="G17" s="5">
-        <v>2541</v>
+        <v>1843.87</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="6">
-        <v>568</v>
+        <v>697</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="L17" s="4"/>
       <c r="M17" s="4" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="N17" s="4"/>
       <c r="O17" s="4"/>
     </row>
     <row r="18" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
-        <v>45754</v>
+        <v>45546</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="E18" s="3">
-        <v>45789</v>
+        <v>45622</v>
       </c>
       <c r="F18" s="5">
-        <v>2287.0700000000002</v>
+        <v>1216.8599999999999</v>
       </c>
       <c r="G18" s="5">
-        <v>1143.54</v>
+        <v>1216.8599999999999</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="6">
-        <v>519</v>
+        <v>692</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="L18" s="4"/>
       <c r="M18" s="4" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="N18" s="4"/>
       <c r="O18" s="4"/>
     </row>
     <row r="19" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
-        <v>45754</v>
+        <v>45552</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E19" s="3">
-        <v>45796</v>
+        <v>45622</v>
       </c>
       <c r="F19" s="5">
-        <v>2287.06</v>
+        <v>4439.8999999999996</v>
       </c>
       <c r="G19" s="5">
-        <v>2287.06</v>
+        <v>4439.8999999999996</v>
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="6">
-        <v>512</v>
+        <v>692</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="L19" s="4"/>
       <c r="M19" s="4" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="N19" s="4"/>
       <c r="O19" s="4"/>
     </row>
     <row r="20" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
-        <v>45868</v>
+        <v>45548</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E20" s="3">
-        <v>45896</v>
+        <v>45624</v>
       </c>
       <c r="F20" s="5">
-        <v>3663.84</v>
+        <v>1843.88</v>
       </c>
       <c r="G20" s="5">
-        <v>4572.62</v>
+        <v>1843.88</v>
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="6">
-        <v>412</v>
+        <v>690</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L20" s="4"/>
       <c r="M20" s="4" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="N20" s="4"/>
       <c r="O20" s="4"/>
     </row>
     <row r="21" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
-        <v>45868</v>
+        <v>45632</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="E21" s="3">
-        <v>45910</v>
+        <v>45688</v>
       </c>
       <c r="F21" s="5">
-        <v>3663.84</v>
+        <v>1118.4000000000001</v>
       </c>
       <c r="G21" s="5">
-        <v>3663.84</v>
+        <v>1118.4000000000001</v>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="6">
-        <v>398</v>
+        <v>626</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>31</v>
+        <v>71</v>
       </c>
       <c r="L21" s="4"/>
       <c r="M21" s="4" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="N21" s="4"/>
       <c r="O21" s="4"/>
     </row>
     <row r="22" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
-        <v>45868</v>
+        <v>45646</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="E22" s="3">
-        <v>45924</v>
+        <v>45695</v>
       </c>
       <c r="F22" s="5">
-        <v>3663.84</v>
+        <v>3296.8</v>
       </c>
       <c r="G22" s="5">
-        <v>3663.84</v>
+        <v>3296.8</v>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="6">
-        <v>384</v>
+        <v>619</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="L22" s="4"/>
       <c r="M22" s="4" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="N22" s="4"/>
       <c r="O22" s="4"/>
     </row>
     <row r="23" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
-        <v>45919</v>
+        <v>45636</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="E23" s="3">
-        <v>45947</v>
+        <v>45699</v>
       </c>
       <c r="F23" s="5">
-        <v>2144.59</v>
+        <v>2330</v>
       </c>
       <c r="G23" s="5">
-        <v>3867.34</v>
+        <v>2330</v>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="6">
-        <v>361</v>
+        <v>615</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="L23" s="4"/>
       <c r="M23" s="4" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="N23" s="4"/>
       <c r="O23" s="4"/>
     </row>
     <row r="24" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
-        <v>45919</v>
+        <v>45646</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="E24" s="3">
-        <v>45954</v>
+        <v>45702</v>
       </c>
       <c r="F24" s="5">
-        <v>2144.59</v>
+        <v>3296.8</v>
       </c>
       <c r="G24" s="5">
-        <v>2144.59</v>
+        <v>3296.8</v>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="6">
-        <v>354</v>
+        <v>612</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="L24" s="4"/>
       <c r="M24" s="4" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="N24" s="4"/>
       <c r="O24" s="4"/>
     </row>
     <row r="25" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
-        <v>45919</v>
+        <v>45677</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="E25" s="3">
-        <v>45961</v>
+        <v>45705</v>
       </c>
       <c r="F25" s="5">
-        <v>2144.59</v>
+        <v>2541</v>
       </c>
       <c r="G25" s="5">
-        <v>2144.59</v>
+        <v>2541</v>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="6">
-        <v>347</v>
+        <v>609</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="L25" s="4"/>
       <c r="M25" s="4" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="N25" s="4"/>
       <c r="O25" s="4"/>
     </row>
     <row r="26" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
-        <v>45919</v>
+        <v>45646</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="E26" s="3">
-        <v>45968</v>
+        <v>45709</v>
       </c>
       <c r="F26" s="5">
-        <v>2144.59</v>
+        <v>3296.8</v>
       </c>
       <c r="G26" s="5">
-        <v>2144.59</v>
+        <v>3296.8</v>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="6">
-        <v>340</v>
+        <v>605</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="L26" s="4"/>
       <c r="M26" s="4" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="N26" s="4"/>
       <c r="O26" s="4"/>
     </row>
     <row r="27" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
-        <v>45938</v>
+        <v>45677</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>21</v>
+        <v>73</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="E27" s="3">
-        <v>45980</v>
+        <v>45712</v>
       </c>
       <c r="F27" s="5">
-        <v>4480</v>
+        <v>2541</v>
       </c>
       <c r="G27" s="5">
-        <v>4480</v>
+        <v>2541</v>
       </c>
       <c r="H27" s="3"/>
       <c r="I27" s="6">
-        <v>328</v>
+        <v>602</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="L27" s="4"/>
       <c r="M27" s="4" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="N27" s="4"/>
       <c r="O27" s="4"/>
     </row>
     <row r="28" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
-        <v>46062</v>
+        <v>45677</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E28" s="3">
-        <v>46090</v>
+        <v>45726</v>
       </c>
       <c r="F28" s="5">
-        <v>503.28</v>
+        <v>2541</v>
       </c>
       <c r="G28" s="5">
-        <v>806.34</v>
+        <v>2541</v>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="6">
-        <v>218</v>
+        <v>588</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="L28" s="4"/>
       <c r="M28" s="4" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="N28" s="4"/>
       <c r="O28" s="4"/>
     </row>
     <row r="29" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
-        <v>46062</v>
+        <v>45699</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="E29" s="3">
-        <v>46097</v>
+        <v>45727</v>
       </c>
       <c r="F29" s="5">
-        <v>503.28</v>
+        <v>7562.78</v>
       </c>
       <c r="G29" s="5">
-        <v>503.28</v>
+        <v>7562.78</v>
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="6">
-        <v>211</v>
+        <v>587</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="L29" s="4"/>
       <c r="M29" s="4" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="N29" s="4"/>
       <c r="O29" s="4"/>
     </row>
     <row r="30" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
-        <v>46062</v>
+        <v>45699</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="E30" s="3">
-        <v>46104</v>
+        <v>45734</v>
       </c>
       <c r="F30" s="5">
-        <v>503.28</v>
+        <v>7562.78</v>
       </c>
       <c r="G30" s="5">
-        <v>503.28</v>
+        <v>7562.78</v>
       </c>
       <c r="H30" s="3"/>
       <c r="I30" s="6">
-        <v>204</v>
+        <v>580</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="L30" s="4"/>
       <c r="M30" s="4" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="N30" s="4"/>
       <c r="O30" s="4"/>
     </row>
     <row r="31" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
-        <v>46203</v>
+        <v>45699</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="E31" s="3">
-        <v>46259</v>
+        <v>45734</v>
       </c>
       <c r="F31" s="5">
-        <v>860</v>
+        <v>1154.56</v>
       </c>
       <c r="G31" s="5">
-        <v>860</v>
+        <v>1154.56</v>
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="6">
-        <v>49</v>
+        <v>580</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="L31" s="4"/>
       <c r="M31" s="4" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="N31" s="4"/>
       <c r="O31" s="4"/>
     </row>
     <row r="32" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
-        <v>46224</v>
+        <v>45677</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>84</v>
+        <v>45</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E32" s="3">
-        <v>46259</v>
+        <v>45740</v>
       </c>
       <c r="F32" s="5">
-        <v>2818.37</v>
+        <v>2541</v>
       </c>
       <c r="G32" s="5">
-        <v>2818.37</v>
+        <v>2541</v>
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="6">
-        <v>49</v>
+        <v>574</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="L32" s="4"/>
       <c r="M32" s="4" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="N32" s="4"/>
       <c r="O32" s="4"/>
     </row>
     <row r="33" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
-        <v>46232</v>
+        <v>45699</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>91</v>
+        <v>45</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E33" s="3">
-        <v>46262</v>
+        <v>45741</v>
       </c>
       <c r="F33" s="5">
-        <v>9716</v>
+        <v>7562.78</v>
       </c>
       <c r="G33" s="5">
-        <v>18957.86</v>
+        <v>7562.78</v>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="6">
-        <v>46</v>
+        <v>573</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="L33" s="4"/>
       <c r="M33" s="4" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="N33" s="4"/>
       <c r="O33" s="4"/>
     </row>
     <row r="34" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
-        <v>46232</v>
+        <v>45699</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>91</v>
+        <v>51</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E34" s="3">
-        <v>46272</v>
+        <v>45741</v>
       </c>
       <c r="F34" s="5">
-        <v>9716</v>
+        <v>1154.56</v>
       </c>
       <c r="G34" s="5">
-        <v>9716</v>
+        <v>1154.56</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="6">
-        <v>36</v>
+        <v>573</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>94</v>
+        <v>54</v>
       </c>
       <c r="L34" s="4"/>
       <c r="M34" s="4" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N34" s="4"/>
       <c r="O34" s="4"/>
     </row>
     <row r="35" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
-        <v>46224</v>
+        <v>45699</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E35" s="3">
-        <v>46273</v>
+        <v>45748</v>
       </c>
       <c r="F35" s="5">
-        <v>2818.37</v>
+        <v>1154.56</v>
       </c>
       <c r="G35" s="5">
-        <v>2818.37</v>
+        <v>1154.56</v>
       </c>
       <c r="H35" s="3"/>
       <c r="I35" s="6">
-        <v>35</v>
+        <v>566</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="L35" s="4"/>
       <c r="M35" s="4" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="N35" s="4"/>
       <c r="O35" s="4"/>
     </row>
     <row r="36" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
-        <v>46224</v>
+        <v>45699</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>84</v>
+        <v>45</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E36" s="3">
-        <v>46280</v>
+        <v>45748</v>
       </c>
       <c r="F36" s="5">
-        <v>2818.36</v>
+        <v>7562.76</v>
       </c>
       <c r="G36" s="5">
-        <v>2818.36</v>
+        <v>7562.76</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="6">
-        <v>28</v>
+        <v>566</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="L36" s="4"/>
       <c r="M36" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N36" s="4"/>
       <c r="O36" s="4"/>
     </row>
     <row r="37" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
-        <v>46232</v>
+        <v>45699</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>91</v>
+        <v>51</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E37" s="3">
-        <v>46282</v>
+        <v>45755</v>
       </c>
       <c r="F37" s="5">
-        <v>9716</v>
+        <v>1154.56</v>
       </c>
       <c r="G37" s="5">
-        <v>9716</v>
+        <v>1154.56</v>
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="6">
-        <v>26</v>
+        <v>559</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>94</v>
+        <v>54</v>
       </c>
       <c r="L37" s="4"/>
       <c r="M37" s="4" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="N37" s="4"/>
       <c r="O37" s="4"/>
     </row>
     <row r="38" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
-        <v>46266</v>
+        <v>45733</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="E38" s="3">
-        <v>46287</v>
+        <v>45761</v>
       </c>
       <c r="F38" s="5">
-        <v>18600</v>
+        <v>3850</v>
       </c>
       <c r="G38" s="5">
-        <v>18600</v>
+        <v>6169.53</v>
       </c>
       <c r="H38" s="3"/>
       <c r="I38" s="6">
-        <v>21</v>
+        <v>553</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="L38" s="4"/>
       <c r="M38" s="4" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="N38" s="4"/>
       <c r="O38" s="4"/>
     </row>
     <row r="39" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
-        <v>46262</v>
+        <v>45733</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>108</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E39" s="3">
-        <v>46290</v>
+        <v>45768</v>
       </c>
       <c r="F39" s="5">
-        <v>7694.4</v>
+        <v>3850</v>
       </c>
       <c r="G39" s="5">
-        <v>7694.4</v>
+        <v>3850</v>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="6">
+        <v>546</v>
+      </c>
+      <c r="J39" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="J39" s="4" t="s">
-        <v>34</v>
-      </c>
       <c r="K39" s="4" t="s">
-        <v>110</v>
+        <v>54</v>
       </c>
       <c r="L39" s="4"/>
       <c r="M39" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N39" s="4"/>
       <c r="O39" s="4"/>
     </row>
     <row r="40" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
-        <v>46232</v>
+        <v>45733</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>91</v>
+        <v>51</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E40" s="3">
-        <v>46292</v>
+        <v>45775</v>
       </c>
       <c r="F40" s="5">
-        <v>9716</v>
+        <v>3850</v>
       </c>
       <c r="G40" s="5">
-        <v>9716</v>
+        <v>3850</v>
       </c>
       <c r="H40" s="3"/>
       <c r="I40" s="6">
-        <v>16</v>
+        <v>539</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="K40" s="4" t="s">
-        <v>94</v>
+        <v>54</v>
       </c>
       <c r="L40" s="4"/>
       <c r="M40" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N40" s="4"/>
       <c r="O40" s="4"/>
     </row>
     <row r="41" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
-        <v>46266</v>
+        <v>45747</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E41" s="3">
-        <v>46294</v>
+        <v>45775</v>
       </c>
       <c r="F41" s="5">
-        <v>18600</v>
+        <v>3800</v>
       </c>
       <c r="G41" s="5">
-        <v>18600</v>
+        <v>6089.41</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="6">
-        <v>14</v>
+        <v>539</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="K41" s="4" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="L41" s="4"/>
       <c r="M41" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N41" s="4"/>
       <c r="O41" s="4"/>
     </row>
     <row r="42" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
-        <v>46262</v>
+        <v>45747</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>108</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E42" s="3">
-        <v>46297</v>
+        <v>45782</v>
       </c>
       <c r="F42" s="5">
-        <v>7694.4</v>
+        <v>3800</v>
       </c>
       <c r="G42" s="5">
-        <v>7694.4</v>
+        <v>3800</v>
       </c>
       <c r="H42" s="3"/>
       <c r="I42" s="6">
-        <v>11</v>
+        <v>532</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="K42" s="4" t="s">
-        <v>110</v>
+        <v>54</v>
       </c>
       <c r="L42" s="4"/>
       <c r="M42" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N42" s="4"/>
       <c r="O42" s="4"/>
     </row>
     <row r="43" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
-        <v>46266</v>
+        <v>45747</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E43" s="3">
-        <v>46301</v>
+        <v>45789</v>
       </c>
       <c r="F43" s="5">
-        <v>18600</v>
+        <v>3800</v>
       </c>
       <c r="G43" s="5">
-        <v>18600</v>
+        <v>3800</v>
       </c>
       <c r="H43" s="3"/>
       <c r="I43" s="6">
-        <v>7</v>
+        <v>525</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="K43" s="4" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="L43" s="4"/>
       <c r="M43" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N43" s="4"/>
       <c r="O43" s="4"/>
     </row>
     <row r="44" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
-        <v>46232</v>
+        <v>45754</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E44" s="3">
-        <v>46302</v>
+        <v>45789</v>
       </c>
       <c r="F44" s="5">
-        <v>9716</v>
+        <v>2287.0700000000002</v>
       </c>
       <c r="G44" s="5">
-        <v>9716</v>
+        <v>1143.54</v>
       </c>
       <c r="H44" s="3"/>
       <c r="I44" s="6">
-        <v>6</v>
+        <v>525</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="K44" s="4" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="L44" s="4"/>
       <c r="M44" s="4" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="N44" s="4"/>
       <c r="O44" s="4"/>
     </row>
     <row r="45" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
-        <v>46234</v>
+        <v>45754</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>84</v>
+        <v>121</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>122</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E45" s="3">
-        <v>46304</v>
+        <v>45796</v>
       </c>
       <c r="F45" s="5">
-        <v>5556.1</v>
+        <v>2287.06</v>
       </c>
       <c r="G45" s="5">
-        <v>5556.1</v>
+        <v>2287.06</v>
       </c>
       <c r="H45" s="3"/>
       <c r="I45" s="6">
-        <v>4</v>
+        <v>518</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>87</v>
+        <v>124</v>
       </c>
       <c r="L45" s="4"/>
       <c r="M45" s="4" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="N45" s="4"/>
       <c r="O45" s="4"/>
     </row>
     <row r="46" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
-        <v>46262</v>
+        <v>45868</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>107</v>
+        <v>45</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E46" s="3">
-        <v>46304</v>
+        <v>45896</v>
       </c>
       <c r="F46" s="5">
-        <v>7694.4</v>
+        <v>3663.84</v>
       </c>
       <c r="G46" s="5">
-        <v>7694.4</v>
+        <v>4572.62</v>
       </c>
       <c r="H46" s="3"/>
       <c r="I46" s="6">
-        <v>4</v>
+        <v>418</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="K46" s="4" t="s">
-        <v>110</v>
+        <v>71</v>
       </c>
       <c r="L46" s="4"/>
       <c r="M46" s="4" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="N46" s="4"/>
       <c r="O46" s="4"/>
     </row>
     <row r="47" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
-        <v>46227</v>
+        <v>45868</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>127</v>
+        <v>45</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>128</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E47" s="3">
-        <v>46272</v>
+        <v>45910</v>
       </c>
       <c r="F47" s="5">
-        <v>4216.67</v>
+        <v>3663.84</v>
       </c>
       <c r="G47" s="5">
-        <v>6389.24</v>
+        <v>3663.84</v>
       </c>
       <c r="H47" s="3"/>
       <c r="I47" s="6">
-        <v>36</v>
+        <v>404</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>130</v>
+        <v>26</v>
       </c>
       <c r="K47" s="4" t="s">
-        <v>131</v>
+        <v>71</v>
       </c>
       <c r="L47" s="4"/>
       <c r="M47" s="4" t="s">
@@ -3198,10 +3209,10 @@
     </row>
     <row r="48" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
-        <v>46227</v>
+        <v>45868</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>127</v>
+        <v>45</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>128</v>
@@ -3210,23 +3221,23 @@
         <v>133</v>
       </c>
       <c r="E48" s="3">
-        <v>46287</v>
+        <v>45924</v>
       </c>
       <c r="F48" s="5">
-        <v>4216.67</v>
+        <v>3663.84</v>
       </c>
       <c r="G48" s="5">
-        <v>4216.67</v>
+        <v>3663.84</v>
       </c>
       <c r="H48" s="3"/>
       <c r="I48" s="6">
-        <v>21</v>
+        <v>390</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>130</v>
+        <v>26</v>
       </c>
       <c r="K48" s="4" t="s">
-        <v>131</v>
+        <v>71</v>
       </c>
       <c r="L48" s="4"/>
       <c r="M48" s="4" t="s">
@@ -3237,35 +3248,35 @@
     </row>
     <row r="49" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
-        <v>46223</v>
+        <v>45919</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>91</v>
+        <v>135</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E49" s="3">
-        <v>46293</v>
+        <v>45947</v>
       </c>
       <c r="F49" s="5">
-        <v>6265</v>
+        <v>2144.59</v>
       </c>
       <c r="G49" s="5">
-        <v>6265</v>
+        <v>3867.34</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="6">
-        <v>15</v>
+        <v>367</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>130</v>
+        <v>26</v>
       </c>
       <c r="K49" s="4" t="s">
-        <v>137</v>
+        <v>54</v>
       </c>
       <c r="L49" s="4"/>
       <c r="M49" s="4" t="s">
@@ -3276,815 +3287,783 @@
     </row>
     <row r="50" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
-        <v>46268</v>
+        <v>45919</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>28</v>
+        <v>135</v>
       </c>
       <c r="C50" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D50" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="D50" s="4" t="s">
-        <v>140</v>
-      </c>
       <c r="E50" s="3">
-        <v>46296</v>
+        <v>45954</v>
       </c>
       <c r="F50" s="5">
-        <v>2754</v>
+        <v>2144.59</v>
       </c>
       <c r="G50" s="5">
-        <v>2754</v>
+        <v>2144.59</v>
       </c>
       <c r="H50" s="3"/>
       <c r="I50" s="6">
-        <v>12</v>
+        <v>360</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>130</v>
+        <v>26</v>
       </c>
       <c r="K50" s="4" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="L50" s="4"/>
       <c r="M50" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="N50" s="4"/>
       <c r="O50" s="4"/>
     </row>
     <row r="51" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
-        <v>46227</v>
+        <v>45919</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E51" s="3">
-        <v>46302</v>
+        <v>45961</v>
       </c>
       <c r="F51" s="5">
-        <v>4216.66</v>
+        <v>2144.59</v>
       </c>
       <c r="G51" s="5">
-        <v>4216.66</v>
+        <v>2144.59</v>
       </c>
       <c r="H51" s="3"/>
       <c r="I51" s="6">
-        <v>6</v>
+        <v>353</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>130</v>
+        <v>26</v>
       </c>
       <c r="K51" s="4" t="s">
-        <v>131</v>
+        <v>54</v>
       </c>
       <c r="L51" s="4"/>
       <c r="M51" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="N51" s="4"/>
       <c r="O51" s="4"/>
     </row>
     <row r="52" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
-        <v>46268</v>
+        <v>45919</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>28</v>
+        <v>135</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E52" s="3">
-        <v>46303</v>
+        <v>45968</v>
       </c>
       <c r="F52" s="5">
-        <v>2754</v>
+        <v>2144.59</v>
       </c>
       <c r="G52" s="5">
-        <v>2754</v>
+        <v>2144.59</v>
       </c>
       <c r="H52" s="3"/>
       <c r="I52" s="6">
-        <v>5</v>
+        <v>346</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>130</v>
+        <v>26</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="L52" s="4"/>
       <c r="M52" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N52" s="4"/>
       <c r="O52" s="4"/>
     </row>
     <row r="53" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
-        <v>46225</v>
+        <v>45938</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="D53" s="4" t="s">
         <v>146</v>
       </c>
       <c r="E53" s="3">
-        <v>46270</v>
+        <v>45980</v>
       </c>
       <c r="F53" s="5">
-        <v>7551.88</v>
+        <v>4480</v>
       </c>
       <c r="G53" s="5">
-        <v>11442.87</v>
+        <v>4480</v>
       </c>
       <c r="H53" s="3"/>
       <c r="I53" s="6">
-        <v>38</v>
+        <v>334</v>
       </c>
       <c r="J53" s="4" t="s">
-        <v>147</v>
+        <v>26</v>
       </c>
       <c r="K53" s="4" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="L53" s="4"/>
       <c r="M53" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N53" s="4"/>
       <c r="O53" s="4"/>
     </row>
     <row r="54" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
-        <v>46223</v>
+        <v>45959</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>43</v>
+        <v>135</v>
       </c>
       <c r="C54" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D54" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="D54" s="4" t="s">
-        <v>150</v>
-      </c>
       <c r="E54" s="3">
-        <v>46273</v>
+        <v>45980</v>
       </c>
       <c r="F54" s="5">
-        <v>11200</v>
+        <v>28666.44</v>
       </c>
       <c r="G54" s="5">
-        <v>11200</v>
+        <v>28666.44</v>
       </c>
       <c r="H54" s="3"/>
       <c r="I54" s="6">
-        <v>35</v>
-      </c>
-      <c r="J54" s="4" t="s">
-        <v>147</v>
-      </c>
+        <v>334</v>
+      </c>
+      <c r="J54" s="4"/>
       <c r="K54" s="4" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="L54" s="4"/>
-      <c r="M54" s="4" t="s">
-        <v>151</v>
-      </c>
+      <c r="M54" s="4"/>
       <c r="N54" s="4"/>
       <c r="O54" s="4"/>
     </row>
     <row r="55" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
-        <v>46253</v>
+        <v>45959</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>43</v>
+        <v>135</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>104</v>
+        <v>148</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E55" s="3">
-        <v>46274</v>
+        <v>45987</v>
       </c>
       <c r="F55" s="5">
-        <v>10080</v>
+        <v>33844.160000000003</v>
       </c>
       <c r="G55" s="5">
-        <v>10080</v>
+        <v>33844.160000000003</v>
       </c>
       <c r="H55" s="3"/>
       <c r="I55" s="6">
-        <v>34</v>
-      </c>
-      <c r="J55" s="4" t="s">
-        <v>147</v>
-      </c>
+        <v>327</v>
+      </c>
+      <c r="J55" s="4"/>
       <c r="K55" s="4" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="L55" s="4"/>
-      <c r="M55" s="4" t="s">
-        <v>153</v>
-      </c>
+      <c r="M55" s="4"/>
       <c r="N55" s="4"/>
       <c r="O55" s="4"/>
     </row>
     <row r="56" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
-        <v>46227</v>
+        <v>45947</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>43</v>
+        <v>121</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>104</v>
+        <v>145</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E56" s="3">
-        <v>46276</v>
+        <v>45989</v>
       </c>
       <c r="F56" s="5">
-        <v>23168.6</v>
+        <v>3220</v>
       </c>
       <c r="G56" s="5">
-        <v>23168.6</v>
+        <v>3220</v>
       </c>
       <c r="H56" s="3"/>
       <c r="I56" s="6">
-        <v>32</v>
-      </c>
-      <c r="J56" s="4" t="s">
-        <v>147</v>
-      </c>
+        <v>325</v>
+      </c>
+      <c r="J56" s="4"/>
       <c r="K56" s="4" t="s">
-        <v>35</v>
+        <v>124</v>
       </c>
       <c r="L56" s="4"/>
-      <c r="M56" s="4" t="s">
-        <v>155</v>
-      </c>
+      <c r="M56" s="4"/>
       <c r="N56" s="4"/>
       <c r="O56" s="4"/>
     </row>
     <row r="57" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
-        <v>46234</v>
+        <v>45959</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E57" s="3">
-        <v>46279</v>
+        <v>45994</v>
       </c>
       <c r="F57" s="5">
-        <v>3789.09</v>
+        <v>14483.06</v>
       </c>
       <c r="G57" s="5">
-        <v>5741.36</v>
+        <v>14483.06</v>
       </c>
       <c r="H57" s="3"/>
       <c r="I57" s="6">
-        <v>29</v>
-      </c>
-      <c r="J57" s="4" t="s">
-        <v>147</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="J57" s="4"/>
       <c r="K57" s="4" t="s">
-        <v>131</v>
+        <v>54</v>
       </c>
       <c r="L57" s="4"/>
-      <c r="M57" s="4" t="s">
-        <v>157</v>
-      </c>
+      <c r="M57" s="4"/>
       <c r="N57" s="4"/>
       <c r="O57" s="4"/>
     </row>
     <row r="58" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
-        <v>46253</v>
+        <v>46062</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>104</v>
+        <v>153</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="E58" s="3">
-        <v>46281</v>
+        <v>46090</v>
       </c>
       <c r="F58" s="5">
-        <v>10080</v>
+        <v>503.28</v>
       </c>
       <c r="G58" s="5">
-        <v>10080</v>
+        <v>806.34</v>
       </c>
       <c r="H58" s="3"/>
       <c r="I58" s="6">
+        <v>224</v>
+      </c>
+      <c r="J58" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K58" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="J58" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="K58" s="4" t="s">
-        <v>35</v>
       </c>
       <c r="L58" s="4"/>
       <c r="M58" s="4" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="N58" s="4"/>
       <c r="O58" s="4"/>
     </row>
     <row r="59" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
-        <v>46227</v>
+        <v>46062</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>104</v>
+        <v>153</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E59" s="3">
-        <v>46283</v>
+        <v>46097</v>
       </c>
       <c r="F59" s="5">
-        <v>23168.6</v>
+        <v>503.28</v>
       </c>
       <c r="G59" s="5">
-        <v>23168.6</v>
+        <v>503.28</v>
       </c>
       <c r="H59" s="3"/>
       <c r="I59" s="6">
-        <v>25</v>
+        <v>217</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>147</v>
+        <v>26</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="L59" s="4"/>
       <c r="M59" s="4" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="N59" s="4"/>
       <c r="O59" s="4"/>
     </row>
     <row r="60" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
-        <v>46223</v>
+        <v>46062</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="E60" s="3">
-        <v>46283</v>
+        <v>46104</v>
       </c>
       <c r="F60" s="5">
-        <v>11200</v>
+        <v>503.28</v>
       </c>
       <c r="G60" s="5">
-        <v>11200</v>
+        <v>503.28</v>
       </c>
       <c r="H60" s="3"/>
       <c r="I60" s="6">
-        <v>25</v>
+        <v>210</v>
       </c>
       <c r="J60" s="4" t="s">
-        <v>147</v>
+        <v>26</v>
       </c>
       <c r="K60" s="4" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="L60" s="4"/>
       <c r="M60" s="4" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="N60" s="4"/>
       <c r="O60" s="4"/>
     </row>
     <row r="61" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
-        <v>46224</v>
+        <v>46045</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E61" s="3">
-        <v>46284</v>
+        <v>46105</v>
       </c>
       <c r="F61" s="5">
-        <v>10666.67</v>
+        <v>5466.66</v>
       </c>
       <c r="G61" s="5">
-        <v>10666.67</v>
+        <v>5466.66</v>
       </c>
       <c r="H61" s="3"/>
       <c r="I61" s="6">
-        <v>24</v>
+        <v>209</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="K61" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="L61" s="4"/>
       <c r="M61" s="4" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="N61" s="4"/>
       <c r="O61" s="4"/>
     </row>
     <row r="62" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
-        <v>46234</v>
+        <v>46171</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>43</v>
+        <v>135</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E62" s="3">
-        <v>46284</v>
+        <v>46192</v>
       </c>
       <c r="F62" s="5">
-        <v>6500</v>
+        <v>4676.8500000000004</v>
       </c>
       <c r="G62" s="5">
-        <v>6500</v>
+        <v>7494.53</v>
       </c>
       <c r="H62" s="3"/>
       <c r="I62" s="6">
-        <v>24</v>
-      </c>
-      <c r="J62" s="4" t="s">
-        <v>147</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="J62" s="4"/>
       <c r="K62" s="4" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="L62" s="4"/>
-      <c r="M62" s="4" t="s">
-        <v>167</v>
-      </c>
+      <c r="M62" s="4"/>
       <c r="N62" s="4"/>
       <c r="O62" s="4"/>
     </row>
     <row r="63" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
-        <v>46234</v>
+        <v>46171</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>43</v>
+        <v>135</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E63" s="3">
-        <v>46284</v>
+        <v>46199</v>
       </c>
       <c r="F63" s="5">
-        <v>4950.17</v>
+        <v>4676.8500000000004</v>
       </c>
       <c r="G63" s="5">
-        <v>4950.17</v>
+        <v>4676.8500000000004</v>
       </c>
       <c r="H63" s="3"/>
       <c r="I63" s="6">
-        <v>24</v>
-      </c>
-      <c r="J63" s="4" t="s">
-        <v>147</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="J63" s="4"/>
       <c r="K63" s="4" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="L63" s="4"/>
-      <c r="M63" s="4" t="s">
-        <v>169</v>
-      </c>
+      <c r="M63" s="4"/>
       <c r="N63" s="4"/>
       <c r="O63" s="4"/>
     </row>
     <row r="64" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
-        <v>46225</v>
+        <v>46171</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="E64" s="3">
-        <v>46285</v>
+        <v>46206</v>
       </c>
       <c r="F64" s="5">
-        <v>7551.88</v>
+        <v>4676.8500000000004</v>
       </c>
       <c r="G64" s="5">
-        <v>7551.88</v>
+        <v>4676.8500000000004</v>
       </c>
       <c r="H64" s="3"/>
       <c r="I64" s="6">
-        <v>23</v>
-      </c>
-      <c r="J64" s="4" t="s">
-        <v>147</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="J64" s="4"/>
       <c r="K64" s="4" t="s">
-        <v>131</v>
+        <v>54</v>
       </c>
       <c r="L64" s="4"/>
-      <c r="M64" s="4" t="s">
-        <v>171</v>
-      </c>
+      <c r="M64" s="4"/>
       <c r="N64" s="4"/>
       <c r="O64" s="4"/>
     </row>
     <row r="65" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
-        <v>46244</v>
+        <v>46162</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>104</v>
+        <v>166</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E65" s="3">
-        <v>46286</v>
+        <v>46222</v>
       </c>
       <c r="F65" s="5">
-        <v>4320</v>
+        <v>22349.79</v>
       </c>
       <c r="G65" s="5">
-        <v>4320</v>
+        <v>22349.79</v>
       </c>
       <c r="H65" s="3"/>
       <c r="I65" s="6">
-        <v>22</v>
-      </c>
-      <c r="J65" s="4" t="s">
-        <v>147</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="J65" s="4"/>
       <c r="K65" s="4" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="L65" s="4"/>
-      <c r="M65" s="4" t="s">
-        <v>173</v>
-      </c>
+      <c r="M65" s="4"/>
       <c r="N65" s="4"/>
       <c r="O65" s="4"/>
     </row>
     <row r="66" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
-        <v>46253</v>
+        <v>46203</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>43</v>
+        <v>168</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="E66" s="3">
-        <v>46288</v>
+        <v>46259</v>
       </c>
       <c r="F66" s="5">
-        <v>10080</v>
+        <v>860</v>
       </c>
       <c r="G66" s="5">
-        <v>10080</v>
+        <v>860</v>
       </c>
       <c r="H66" s="3"/>
       <c r="I66" s="6">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="J66" s="4" t="s">
-        <v>147</v>
+        <v>26</v>
       </c>
       <c r="K66" s="4" t="s">
-        <v>35</v>
+        <v>171</v>
       </c>
       <c r="L66" s="4"/>
       <c r="M66" s="4" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="N66" s="4"/>
       <c r="O66" s="4"/>
     </row>
     <row r="67" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
-        <v>46253</v>
+        <v>46224</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>20</v>
+        <v>168</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E67" s="3">
-        <v>46288</v>
+        <v>46259</v>
       </c>
       <c r="F67" s="5">
-        <v>3640</v>
+        <v>2818.37</v>
       </c>
       <c r="G67" s="5">
-        <v>3640</v>
+        <v>2818.37</v>
       </c>
       <c r="H67" s="3"/>
       <c r="I67" s="6">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="J67" s="4" t="s">
-        <v>147</v>
+        <v>26</v>
       </c>
       <c r="K67" s="4" t="s">
-        <v>23</v>
+        <v>171</v>
       </c>
       <c r="L67" s="4"/>
       <c r="M67" s="4" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="N67" s="4"/>
       <c r="O67" s="4"/>
     </row>
     <row r="68" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
-        <v>46259</v>
+        <v>46232</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>91</v>
+        <v>15</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>135</v>
+        <v>175</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="E68" s="3">
-        <v>46289</v>
+        <v>46262</v>
       </c>
       <c r="F68" s="5">
-        <v>6265</v>
+        <v>9716</v>
       </c>
       <c r="G68" s="5">
-        <v>6265</v>
+        <v>18957.86</v>
       </c>
       <c r="H68" s="3"/>
       <c r="I68" s="6">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="J68" s="4" t="s">
-        <v>147</v>
+        <v>26</v>
       </c>
       <c r="K68" s="4" t="s">
-        <v>137</v>
+        <v>39</v>
       </c>
       <c r="L68" s="4"/>
       <c r="M68" s="4" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="N68" s="4"/>
       <c r="O68" s="4"/>
     </row>
     <row r="69" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
-        <v>46262</v>
+        <v>46232</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>107</v>
+        <v>15</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>108</v>
+        <v>175</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E69" s="3">
-        <v>46290</v>
+        <v>46272</v>
       </c>
       <c r="F69" s="5">
-        <v>11660.11</v>
+        <v>9716</v>
       </c>
       <c r="G69" s="5">
-        <v>11660.11</v>
+        <v>9716</v>
       </c>
       <c r="H69" s="3"/>
       <c r="I69" s="6">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="J69" s="4" t="s">
-        <v>147</v>
+        <v>26</v>
       </c>
       <c r="K69" s="4" t="s">
-        <v>110</v>
+        <v>39</v>
       </c>
       <c r="L69" s="4"/>
       <c r="M69" s="4" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="N69" s="4"/>
       <c r="O69" s="4"/>
     </row>
     <row r="70" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
-        <v>46232</v>
+        <v>46227</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>127</v>
+        <v>180</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E70" s="3">
-        <v>46292</v>
+        <v>46272</v>
       </c>
       <c r="F70" s="5">
-        <v>4082.05</v>
+        <v>4216.67</v>
       </c>
       <c r="G70" s="5">
-        <v>4082.05</v>
+        <v>6389.24</v>
       </c>
       <c r="H70" s="3"/>
       <c r="I70" s="6">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="J70" s="4" t="s">
-        <v>147</v>
+        <v>183</v>
       </c>
       <c r="K70" s="4" t="s">
-        <v>131</v>
+        <v>184</v>
       </c>
       <c r="L70" s="4"/>
       <c r="M70" s="4" t="s">
@@ -4095,35 +4074,35 @@
     </row>
     <row r="71" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3">
-        <v>46244</v>
+        <v>46224</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>43</v>
+        <v>168</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D71" s="4" t="s">
         <v>186</v>
       </c>
       <c r="E71" s="3">
-        <v>46293</v>
+        <v>46273</v>
       </c>
       <c r="F71" s="5">
-        <v>4320</v>
+        <v>2818.37</v>
       </c>
       <c r="G71" s="5">
-        <v>4320</v>
+        <v>2818.37</v>
       </c>
       <c r="H71" s="3"/>
       <c r="I71" s="6">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="J71" s="4" t="s">
-        <v>147</v>
+        <v>26</v>
       </c>
       <c r="K71" s="4" t="s">
-        <v>35</v>
+        <v>171</v>
       </c>
       <c r="L71" s="4"/>
       <c r="M71" s="4" t="s">
@@ -4134,166 +4113,166 @@
     </row>
     <row r="72" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
-        <v>46223</v>
+        <v>46234</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>43</v>
+        <v>180</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>149</v>
+        <v>181</v>
       </c>
       <c r="D72" s="4" t="s">
         <v>188</v>
       </c>
       <c r="E72" s="3">
-        <v>46293</v>
+        <v>46279</v>
       </c>
       <c r="F72" s="5">
-        <v>11200</v>
+        <v>3789.09</v>
       </c>
       <c r="G72" s="5">
-        <v>11200</v>
+        <v>5741.36</v>
       </c>
       <c r="H72" s="3"/>
       <c r="I72" s="6">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="J72" s="4" t="s">
-        <v>147</v>
+        <v>189</v>
       </c>
       <c r="K72" s="4" t="s">
-        <v>35</v>
+        <v>184</v>
       </c>
       <c r="L72" s="4"/>
       <c r="M72" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N72" s="4"/>
       <c r="O72" s="4"/>
     </row>
     <row r="73" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="3">
-        <v>46234</v>
+        <v>46253</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>127</v>
+        <v>45</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>128</v>
+        <v>191</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E73" s="3">
-        <v>46294</v>
+        <v>46281</v>
       </c>
       <c r="F73" s="5">
-        <v>3789.09</v>
+        <v>10080</v>
       </c>
       <c r="G73" s="5">
-        <v>3789.09</v>
+        <v>10080</v>
       </c>
       <c r="H73" s="3"/>
       <c r="I73" s="6">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="J73" s="4" t="s">
-        <v>147</v>
+        <v>189</v>
       </c>
       <c r="K73" s="4" t="s">
-        <v>131</v>
+        <v>27</v>
       </c>
       <c r="L73" s="4"/>
       <c r="M73" s="4" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="N73" s="4"/>
       <c r="O73" s="4"/>
     </row>
     <row r="74" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="3">
-        <v>46253</v>
+        <v>46232</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>104</v>
+        <v>175</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E74" s="3">
-        <v>46295</v>
+        <v>46282</v>
       </c>
       <c r="F74" s="5">
-        <v>10080</v>
+        <v>9716</v>
       </c>
       <c r="G74" s="5">
-        <v>10080</v>
+        <v>9716</v>
       </c>
       <c r="H74" s="3"/>
       <c r="I74" s="6">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="J74" s="4" t="s">
-        <v>147</v>
+        <v>26</v>
       </c>
       <c r="K74" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="L74" s="4"/>
       <c r="M74" s="4" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="N74" s="4"/>
       <c r="O74" s="4"/>
     </row>
     <row r="75" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="3">
-        <v>46265</v>
+        <v>46227</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E75" s="3">
-        <v>46295</v>
+        <v>46283</v>
       </c>
       <c r="F75" s="5">
-        <v>4750</v>
+        <v>23168.6</v>
       </c>
       <c r="G75" s="5">
-        <v>8565.68</v>
+        <v>23168.6</v>
       </c>
       <c r="H75" s="3"/>
       <c r="I75" s="6">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="J75" s="4" t="s">
-        <v>147</v>
+        <v>189</v>
       </c>
       <c r="K75" s="4" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="L75" s="4"/>
       <c r="M75" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N75" s="4"/>
       <c r="O75" s="4"/>
     </row>
     <row r="76" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="3">
-        <v>46266</v>
+        <v>46224</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>197</v>
+        <v>45</v>
       </c>
       <c r="C76" s="4" t="s">
         <v>198</v>
@@ -4302,1746 +4281,1707 @@
         <v>199</v>
       </c>
       <c r="E76" s="3">
-        <v>46296</v>
+        <v>46284</v>
       </c>
       <c r="F76" s="5">
-        <v>8973.5</v>
+        <v>10666.67</v>
       </c>
       <c r="G76" s="5">
-        <v>8973.5</v>
+        <v>10666.67</v>
       </c>
       <c r="H76" s="3"/>
       <c r="I76" s="6">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="J76" s="4" t="s">
-        <v>147</v>
+        <v>189</v>
       </c>
       <c r="K76" s="4" t="s">
-        <v>200</v>
+        <v>27</v>
       </c>
       <c r="L76" s="4"/>
       <c r="M76" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N76" s="4"/>
       <c r="O76" s="4"/>
     </row>
     <row r="77" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="3">
-        <v>46262</v>
+        <v>46234</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>107</v>
+        <v>45</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>108</v>
+        <v>198</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E77" s="3">
-        <v>46297</v>
+        <v>46284</v>
       </c>
       <c r="F77" s="5">
-        <v>11660.11</v>
+        <v>6500</v>
       </c>
       <c r="G77" s="5">
-        <v>11660.11</v>
+        <v>6500</v>
       </c>
       <c r="H77" s="3"/>
       <c r="I77" s="6">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="J77" s="4" t="s">
-        <v>147</v>
+        <v>189</v>
       </c>
       <c r="K77" s="4" t="s">
-        <v>110</v>
+        <v>27</v>
       </c>
       <c r="L77" s="4"/>
       <c r="M77" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="N77" s="4"/>
       <c r="O77" s="4"/>
     </row>
     <row r="78" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="3">
-        <v>46225</v>
+        <v>46234</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>127</v>
+        <v>45</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>128</v>
+        <v>198</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E78" s="3">
-        <v>46300</v>
+        <v>46284</v>
       </c>
       <c r="F78" s="5">
-        <v>7551.88</v>
+        <v>4950.17</v>
       </c>
       <c r="G78" s="5">
-        <v>7551.88</v>
+        <v>4950.17</v>
       </c>
       <c r="H78" s="3"/>
       <c r="I78" s="6">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="J78" s="4" t="s">
-        <v>147</v>
+        <v>189</v>
       </c>
       <c r="K78" s="4" t="s">
-        <v>131</v>
+        <v>27</v>
       </c>
       <c r="L78" s="4"/>
       <c r="M78" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="N78" s="4"/>
       <c r="O78" s="4"/>
     </row>
     <row r="79" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="3">
-        <v>46253</v>
+        <v>46225</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>43</v>
+        <v>180</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>104</v>
+        <v>181</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E79" s="3">
-        <v>46302</v>
+        <v>46285</v>
       </c>
       <c r="F79" s="5">
-        <v>10080</v>
+        <v>7551.88</v>
       </c>
       <c r="G79" s="5">
-        <v>10080</v>
+        <v>7551.88</v>
       </c>
       <c r="H79" s="3"/>
       <c r="I79" s="6">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="J79" s="4" t="s">
-        <v>147</v>
+        <v>189</v>
       </c>
       <c r="K79" s="4" t="s">
-        <v>35</v>
+        <v>184</v>
       </c>
       <c r="L79" s="4"/>
       <c r="M79" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="N79" s="4"/>
       <c r="O79" s="4"/>
     </row>
     <row r="80" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="3">
-        <v>46262</v>
+        <v>46244</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>84</v>
+        <v>45</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E80" s="3">
-        <v>46304</v>
+        <v>46286</v>
       </c>
       <c r="F80" s="5">
-        <v>2992</v>
+        <v>4320</v>
       </c>
       <c r="G80" s="5">
-        <v>2992</v>
+        <v>4320</v>
       </c>
       <c r="H80" s="3"/>
       <c r="I80" s="6">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="J80" s="4" t="s">
-        <v>147</v>
+        <v>189</v>
       </c>
       <c r="K80" s="4" t="s">
-        <v>210</v>
+        <v>27</v>
       </c>
       <c r="L80" s="4"/>
       <c r="M80" s="4" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="N80" s="4"/>
       <c r="O80" s="4"/>
     </row>
     <row r="81" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="3">
-        <v>46259</v>
+        <v>46266</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>91</v>
+        <v>45</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>135</v>
+        <v>191</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E81" s="3">
-        <v>46304</v>
+        <v>46287</v>
       </c>
       <c r="F81" s="5">
-        <v>6265</v>
+        <v>18600</v>
       </c>
       <c r="G81" s="5">
-        <v>6265</v>
+        <v>18600</v>
       </c>
       <c r="H81" s="3"/>
       <c r="I81" s="6">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="J81" s="4" t="s">
-        <v>147</v>
+        <v>26</v>
       </c>
       <c r="K81" s="4" t="s">
-        <v>137</v>
+        <v>27</v>
       </c>
       <c r="L81" s="4"/>
       <c r="M81" s="4" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="N81" s="4"/>
       <c r="O81" s="4"/>
     </row>
     <row r="82" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3">
-        <v>46262</v>
+        <v>46227</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>107</v>
+        <v>180</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>108</v>
+        <v>181</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="E82" s="3">
-        <v>46304</v>
+        <v>46287</v>
       </c>
       <c r="F82" s="5">
-        <v>11660.11</v>
+        <v>4216.67</v>
       </c>
       <c r="G82" s="5">
-        <v>11660.11</v>
+        <v>4216.67</v>
       </c>
       <c r="H82" s="3"/>
       <c r="I82" s="6">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="J82" s="4" t="s">
-        <v>147</v>
+        <v>183</v>
       </c>
       <c r="K82" s="4" t="s">
-        <v>110</v>
+        <v>184</v>
       </c>
       <c r="L82" s="4"/>
       <c r="M82" s="4" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N82" s="4"/>
       <c r="O82" s="4"/>
     </row>
     <row r="83" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="3">
-        <v>45296</v>
+        <v>46253</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>91</v>
+        <v>45</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>216</v>
+        <v>191</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="E83" s="3">
-        <v>45326</v>
+        <v>46288</v>
       </c>
       <c r="F83" s="5">
-        <v>5418</v>
+        <v>10080</v>
       </c>
       <c r="G83" s="5">
-        <v>9391.7800000000007</v>
+        <v>10080</v>
       </c>
       <c r="H83" s="3"/>
       <c r="I83" s="6">
-        <v>982</v>
+        <v>26</v>
       </c>
       <c r="J83" s="4" t="s">
-        <v>218</v>
+        <v>189</v>
       </c>
       <c r="K83" s="4" t="s">
-        <v>137</v>
+        <v>27</v>
       </c>
       <c r="L83" s="4"/>
       <c r="M83" s="4" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="N83" s="4"/>
       <c r="O83" s="4"/>
     </row>
     <row r="84" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="3">
-        <v>45296</v>
+        <v>46253</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="C84" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="D84" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="D84" s="4" t="s">
-        <v>220</v>
-      </c>
       <c r="E84" s="3">
-        <v>45346</v>
+        <v>46288</v>
       </c>
       <c r="F84" s="5">
-        <v>5418</v>
+        <v>3640</v>
       </c>
       <c r="G84" s="5">
-        <v>5418</v>
+        <v>3640</v>
       </c>
       <c r="H84" s="3"/>
       <c r="I84" s="6">
-        <v>962</v>
+        <v>26</v>
       </c>
       <c r="J84" s="4" t="s">
-        <v>218</v>
+        <v>189</v>
       </c>
       <c r="K84" s="4" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="L84" s="4"/>
       <c r="M84" s="4" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="N84" s="4"/>
       <c r="O84" s="4"/>
     </row>
     <row r="85" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="3">
-        <v>45296</v>
+        <v>46253</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="E85" s="3">
-        <v>45356</v>
+        <v>46288</v>
       </c>
       <c r="F85" s="5">
-        <v>5418</v>
+        <v>1660.33</v>
       </c>
       <c r="G85" s="5">
-        <v>5418</v>
+        <v>1660.33</v>
       </c>
       <c r="H85" s="3"/>
       <c r="I85" s="6">
-        <v>952</v>
+        <v>26</v>
       </c>
       <c r="J85" s="4" t="s">
-        <v>218</v>
+        <v>18</v>
       </c>
       <c r="K85" s="4" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="L85" s="4"/>
       <c r="M85" s="4" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="N85" s="4"/>
       <c r="O85" s="4"/>
     </row>
     <row r="86" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="3">
-        <v>45433</v>
+        <v>46259</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>91</v>
+        <v>15</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="E86" s="3">
-        <v>45463</v>
+        <v>46289</v>
       </c>
       <c r="F86" s="5">
-        <v>873.6</v>
+        <v>6265</v>
       </c>
       <c r="G86" s="5">
-        <v>1674.52</v>
+        <v>6265</v>
       </c>
       <c r="H86" s="3"/>
       <c r="I86" s="6">
-        <v>845</v>
+        <v>25</v>
       </c>
       <c r="J86" s="4" t="s">
-        <v>218</v>
+        <v>189</v>
       </c>
       <c r="K86" s="4" t="s">
-        <v>94</v>
+        <v>19</v>
       </c>
       <c r="L86" s="4"/>
       <c r="M86" s="4" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="N86" s="4"/>
       <c r="O86" s="4"/>
     </row>
     <row r="87" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="3">
-        <v>45433</v>
+        <v>46262</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>91</v>
+        <v>223</v>
       </c>
       <c r="C87" s="4" t="s">
         <v>224</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E87" s="3">
-        <v>45493</v>
+        <v>46290</v>
       </c>
       <c r="F87" s="5">
-        <v>873.6</v>
+        <v>7694.4</v>
       </c>
       <c r="G87" s="5">
-        <v>873.6</v>
+        <v>7694.4</v>
       </c>
       <c r="H87" s="3"/>
       <c r="I87" s="6">
-        <v>815</v>
+        <v>24</v>
       </c>
       <c r="J87" s="4" t="s">
-        <v>218</v>
+        <v>26</v>
       </c>
       <c r="K87" s="4" t="s">
-        <v>94</v>
+        <v>226</v>
       </c>
       <c r="L87" s="4"/>
       <c r="M87" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="N87" s="4"/>
       <c r="O87" s="4"/>
     </row>
     <row r="88" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="3">
-        <v>45433</v>
+        <v>46262</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>91</v>
+        <v>223</v>
       </c>
       <c r="C88" s="4" t="s">
         <v>224</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E88" s="3">
-        <v>45523</v>
+        <v>46290</v>
       </c>
       <c r="F88" s="5">
-        <v>873.6</v>
+        <v>11660.11</v>
       </c>
       <c r="G88" s="5">
-        <v>873.6</v>
+        <v>11660.11</v>
       </c>
       <c r="H88" s="3"/>
       <c r="I88" s="6">
-        <v>785</v>
+        <v>24</v>
       </c>
       <c r="J88" s="4" t="s">
-        <v>218</v>
+        <v>189</v>
       </c>
       <c r="K88" s="4" t="s">
-        <v>94</v>
+        <v>226</v>
       </c>
       <c r="L88" s="4"/>
       <c r="M88" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="N88" s="4"/>
       <c r="O88" s="4"/>
     </row>
     <row r="89" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="3">
-        <v>45558</v>
+        <v>46232</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>231</v>
+        <v>175</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E89" s="3">
-        <v>45600</v>
+        <v>46292</v>
       </c>
       <c r="F89" s="5">
-        <v>2000</v>
+        <v>9716</v>
       </c>
       <c r="G89" s="5">
-        <v>2000</v>
+        <v>9716</v>
       </c>
       <c r="H89" s="3"/>
       <c r="I89" s="6">
-        <v>708</v>
+        <v>22</v>
       </c>
       <c r="J89" s="4" t="s">
-        <v>218</v>
+        <v>26</v>
       </c>
       <c r="K89" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="L89" s="4"/>
       <c r="M89" s="4" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="N89" s="4"/>
       <c r="O89" s="4"/>
     </row>
     <row r="90" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="3">
-        <v>45558</v>
+        <v>46232</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>43</v>
+        <v>180</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E90" s="3">
-        <v>45607</v>
+        <v>46292</v>
       </c>
       <c r="F90" s="5">
-        <v>2000</v>
+        <v>4082.05</v>
       </c>
       <c r="G90" s="5">
-        <v>3204.34</v>
+        <v>4082.05</v>
       </c>
       <c r="H90" s="3"/>
       <c r="I90" s="6">
-        <v>701</v>
+        <v>22</v>
       </c>
       <c r="J90" s="4" t="s">
-        <v>218</v>
+        <v>189</v>
       </c>
       <c r="K90" s="4" t="s">
-        <v>35</v>
+        <v>184</v>
       </c>
       <c r="L90" s="4"/>
       <c r="M90" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="N90" s="4"/>
       <c r="O90" s="4"/>
     </row>
     <row r="91" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="3">
-        <v>45552</v>
+        <v>46244</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>236</v>
+        <v>45</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>237</v>
+        <v>191</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="E91" s="3">
-        <v>45608</v>
+        <v>46293</v>
       </c>
       <c r="F91" s="5">
-        <v>4439.8999999999996</v>
+        <v>4320</v>
       </c>
       <c r="G91" s="5">
-        <v>4439.8999999999996</v>
+        <v>4320</v>
       </c>
       <c r="H91" s="3"/>
       <c r="I91" s="6">
-        <v>700</v>
+        <v>21</v>
       </c>
       <c r="J91" s="4" t="s">
-        <v>218</v>
+        <v>189</v>
       </c>
       <c r="K91" s="4" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="L91" s="4"/>
       <c r="M91" s="4" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="N91" s="4"/>
       <c r="O91" s="4"/>
     </row>
     <row r="92" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="3">
-        <v>45558</v>
+        <v>46223</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="E92" s="3">
-        <v>45614</v>
+        <v>46293</v>
       </c>
       <c r="F92" s="5">
-        <v>2000</v>
+        <v>6265</v>
       </c>
       <c r="G92" s="5">
-        <v>2000</v>
+        <v>6265</v>
       </c>
       <c r="H92" s="3"/>
       <c r="I92" s="6">
-        <v>694</v>
+        <v>21</v>
       </c>
       <c r="J92" s="4" t="s">
-        <v>218</v>
+        <v>183</v>
       </c>
       <c r="K92" s="4" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="L92" s="4"/>
       <c r="M92" s="4" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="N92" s="4"/>
       <c r="O92" s="4"/>
     </row>
     <row r="93" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="3">
-        <v>45546</v>
+        <v>46223</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>231</v>
+        <v>198</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="E93" s="3">
-        <v>45615</v>
+        <v>46293</v>
       </c>
       <c r="F93" s="5">
-        <v>1216.8599999999999</v>
+        <v>11200</v>
       </c>
       <c r="G93" s="5">
-        <v>1216.8599999999999</v>
+        <v>11200</v>
       </c>
       <c r="H93" s="3"/>
       <c r="I93" s="6">
-        <v>693</v>
+        <v>21</v>
       </c>
       <c r="J93" s="4" t="s">
-        <v>218</v>
+        <v>189</v>
       </c>
       <c r="K93" s="4" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="L93" s="4"/>
       <c r="M93" s="4" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="N93" s="4"/>
       <c r="O93" s="4"/>
     </row>
     <row r="94" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="3">
-        <v>45548</v>
+        <v>46266</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="E94" s="3">
-        <v>45617</v>
+        <v>46294</v>
       </c>
       <c r="F94" s="5">
-        <v>1843.87</v>
+        <v>18600</v>
       </c>
       <c r="G94" s="5">
-        <v>1843.87</v>
+        <v>18600</v>
       </c>
       <c r="H94" s="3"/>
       <c r="I94" s="6">
-        <v>691</v>
+        <v>20</v>
       </c>
       <c r="J94" s="4" t="s">
-        <v>218</v>
+        <v>26</v>
       </c>
       <c r="K94" s="4" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="L94" s="4"/>
       <c r="M94" s="4" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="N94" s="4"/>
       <c r="O94" s="4"/>
     </row>
     <row r="95" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="3">
-        <v>45546</v>
+        <v>46234</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>43</v>
+        <v>180</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>231</v>
+        <v>181</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E95" s="3">
-        <v>45622</v>
+        <v>46294</v>
       </c>
       <c r="F95" s="5">
-        <v>1216.8599999999999</v>
+        <v>3789.09</v>
       </c>
       <c r="G95" s="5">
-        <v>1216.8599999999999</v>
+        <v>3789.09</v>
       </c>
       <c r="H95" s="3"/>
       <c r="I95" s="6">
-        <v>686</v>
+        <v>20</v>
       </c>
       <c r="J95" s="4" t="s">
-        <v>218</v>
+        <v>189</v>
       </c>
       <c r="K95" s="4" t="s">
-        <v>35</v>
+        <v>184</v>
       </c>
       <c r="L95" s="4"/>
       <c r="M95" s="4" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="N95" s="4"/>
       <c r="O95" s="4"/>
     </row>
     <row r="96" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="3">
-        <v>45552</v>
+        <v>46253</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>236</v>
+        <v>45</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>237</v>
+        <v>191</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="E96" s="3">
-        <v>45622</v>
+        <v>46295</v>
       </c>
       <c r="F96" s="5">
-        <v>4439.8999999999996</v>
+        <v>10080</v>
       </c>
       <c r="G96" s="5">
-        <v>4439.8999999999996</v>
+        <v>10080</v>
       </c>
       <c r="H96" s="3"/>
       <c r="I96" s="6">
-        <v>686</v>
+        <v>19</v>
       </c>
       <c r="J96" s="4" t="s">
-        <v>218</v>
+        <v>189</v>
       </c>
       <c r="K96" s="4" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="L96" s="4"/>
       <c r="M96" s="4" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="N96" s="4"/>
       <c r="O96" s="4"/>
     </row>
     <row r="97" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="3">
-        <v>45548</v>
+        <v>46253</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>43</v>
+        <v>168</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>231</v>
+        <v>247</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E97" s="3">
-        <v>45624</v>
+        <v>46295</v>
       </c>
       <c r="F97" s="5">
-        <v>1843.88</v>
+        <v>2051.2199999999998</v>
       </c>
       <c r="G97" s="5">
-        <v>1843.88</v>
+        <v>2051.2199999999998</v>
       </c>
       <c r="H97" s="3"/>
       <c r="I97" s="6">
-        <v>684</v>
+        <v>19</v>
       </c>
       <c r="J97" s="4" t="s">
-        <v>218</v>
+        <v>18</v>
       </c>
       <c r="K97" s="4" t="s">
-        <v>35</v>
+        <v>171</v>
       </c>
       <c r="L97" s="4"/>
       <c r="M97" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="N97" s="4"/>
       <c r="O97" s="4"/>
     </row>
     <row r="98" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="3">
-        <v>45632</v>
+        <v>46262</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>252</v>
+        <v>223</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>253</v>
+        <v>224</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="E98" s="3">
-        <v>45688</v>
+        <v>46297</v>
       </c>
       <c r="F98" s="5">
-        <v>1118.4000000000001</v>
+        <v>11660.11</v>
       </c>
       <c r="G98" s="5">
-        <v>1118.4000000000001</v>
+        <v>11660.11</v>
       </c>
       <c r="H98" s="3"/>
       <c r="I98" s="6">
-        <v>620</v>
+        <v>17</v>
       </c>
       <c r="J98" s="4" t="s">
-        <v>218</v>
+        <v>189</v>
       </c>
       <c r="K98" s="4" t="s">
-        <v>31</v>
+        <v>226</v>
       </c>
       <c r="L98" s="4"/>
       <c r="M98" s="4" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="N98" s="4"/>
       <c r="O98" s="4"/>
     </row>
     <row r="99" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="3">
-        <v>45646</v>
+        <v>46262</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>43</v>
+        <v>223</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>44</v>
+        <v>224</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="E99" s="3">
-        <v>45695</v>
+        <v>46297</v>
       </c>
       <c r="F99" s="5">
-        <v>3296.8</v>
+        <v>7694.4</v>
       </c>
       <c r="G99" s="5">
-        <v>3296.8</v>
+        <v>7694.4</v>
       </c>
       <c r="H99" s="3"/>
       <c r="I99" s="6">
-        <v>613</v>
+        <v>17</v>
       </c>
       <c r="J99" s="4" t="s">
-        <v>218</v>
+        <v>26</v>
       </c>
       <c r="K99" s="4" t="s">
-        <v>46</v>
+        <v>226</v>
       </c>
       <c r="L99" s="4"/>
       <c r="M99" s="4" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="N99" s="4"/>
       <c r="O99" s="4"/>
     </row>
     <row r="100" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="3">
-        <v>45636</v>
+        <v>46225</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>43</v>
+        <v>180</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>44</v>
+        <v>181</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="E100" s="3">
-        <v>45699</v>
+        <v>46300</v>
       </c>
       <c r="F100" s="5">
-        <v>2330</v>
+        <v>7551.88</v>
       </c>
       <c r="G100" s="5">
-        <v>2330</v>
+        <v>7551.88</v>
       </c>
       <c r="H100" s="3"/>
       <c r="I100" s="6">
-        <v>609</v>
+        <v>14</v>
       </c>
       <c r="J100" s="4" t="s">
-        <v>218</v>
+        <v>189</v>
       </c>
       <c r="K100" s="4" t="s">
-        <v>46</v>
+        <v>184</v>
       </c>
       <c r="L100" s="4"/>
       <c r="M100" s="4" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="N100" s="4"/>
       <c r="O100" s="4"/>
     </row>
     <row r="101" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="3">
-        <v>45646</v>
+        <v>46266</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>44</v>
+        <v>191</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E101" s="3">
-        <v>45702</v>
+        <v>46301</v>
       </c>
       <c r="F101" s="5">
-        <v>3296.8</v>
+        <v>18600</v>
       </c>
       <c r="G101" s="5">
-        <v>3296.8</v>
+        <v>18600</v>
       </c>
       <c r="H101" s="3"/>
       <c r="I101" s="6">
-        <v>606</v>
+        <v>13</v>
       </c>
       <c r="J101" s="4" t="s">
-        <v>218</v>
+        <v>26</v>
       </c>
       <c r="K101" s="4" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="L101" s="4"/>
       <c r="M101" s="4" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="N101" s="4"/>
       <c r="O101" s="4"/>
     </row>
     <row r="102" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="3">
-        <v>45646</v>
+        <v>46253</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>44</v>
+        <v>191</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="E102" s="3">
-        <v>45709</v>
+        <v>46302</v>
       </c>
       <c r="F102" s="5">
-        <v>3296.8</v>
+        <v>10080</v>
       </c>
       <c r="G102" s="5">
-        <v>3296.8</v>
+        <v>10080</v>
       </c>
       <c r="H102" s="3"/>
       <c r="I102" s="6">
-        <v>599</v>
+        <v>12</v>
       </c>
       <c r="J102" s="4" t="s">
-        <v>218</v>
+        <v>189</v>
       </c>
       <c r="K102" s="4" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="L102" s="4"/>
       <c r="M102" s="4" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="N102" s="4"/>
       <c r="O102" s="4"/>
     </row>
     <row r="103" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="3">
-        <v>45699</v>
+        <v>46227</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>43</v>
+        <v>180</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>44</v>
+        <v>181</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="E103" s="3">
-        <v>45727</v>
+        <v>46302</v>
       </c>
       <c r="F103" s="5">
-        <v>7562.78</v>
+        <v>4216.66</v>
       </c>
       <c r="G103" s="5">
-        <v>7562.78</v>
+        <v>4216.66</v>
       </c>
       <c r="H103" s="3"/>
       <c r="I103" s="6">
-        <v>581</v>
+        <v>12</v>
       </c>
       <c r="J103" s="4" t="s">
-        <v>218</v>
+        <v>183</v>
       </c>
       <c r="K103" s="4" t="s">
-        <v>46</v>
+        <v>184</v>
       </c>
       <c r="L103" s="4"/>
       <c r="M103" s="4" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="N103" s="4"/>
       <c r="O103" s="4"/>
     </row>
     <row r="104" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="3">
-        <v>45699</v>
+        <v>46232</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>44</v>
+        <v>175</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="E104" s="3">
-        <v>45734</v>
+        <v>46302</v>
       </c>
       <c r="F104" s="5">
-        <v>7562.78</v>
+        <v>9716</v>
       </c>
       <c r="G104" s="5">
-        <v>7562.78</v>
+        <v>9716</v>
       </c>
       <c r="H104" s="3"/>
       <c r="I104" s="6">
-        <v>574</v>
+        <v>12</v>
       </c>
       <c r="J104" s="4" t="s">
-        <v>218</v>
+        <v>26</v>
       </c>
       <c r="K104" s="4" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="L104" s="4"/>
       <c r="M104" s="4" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="N104" s="4"/>
       <c r="O104" s="4"/>
     </row>
     <row r="105" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="3">
-        <v>45699</v>
+        <v>46268</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>236</v>
+        <v>23</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="E105" s="3">
-        <v>45734</v>
+        <v>46303</v>
       </c>
       <c r="F105" s="5">
-        <v>1154.56</v>
+        <v>2754</v>
       </c>
       <c r="G105" s="5">
-        <v>1154.56</v>
+        <v>2754</v>
       </c>
       <c r="H105" s="3"/>
       <c r="I105" s="6">
-        <v>574</v>
+        <v>11</v>
       </c>
       <c r="J105" s="4" t="s">
-        <v>218</v>
+        <v>183</v>
       </c>
       <c r="K105" s="4" t="s">
-        <v>18</v>
+        <v>71</v>
       </c>
       <c r="L105" s="4"/>
       <c r="M105" s="4" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="N105" s="4"/>
       <c r="O105" s="4"/>
     </row>
     <row r="106" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="3">
-        <v>45699</v>
+        <v>46259</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="E106" s="3">
-        <v>45741</v>
+        <v>46304</v>
       </c>
       <c r="F106" s="5">
-        <v>7562.78</v>
+        <v>6265</v>
       </c>
       <c r="G106" s="5">
-        <v>7562.78</v>
+        <v>6265</v>
       </c>
       <c r="H106" s="3"/>
       <c r="I106" s="6">
-        <v>567</v>
+        <v>10</v>
       </c>
       <c r="J106" s="4" t="s">
-        <v>218</v>
+        <v>189</v>
       </c>
       <c r="K106" s="4" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="L106" s="4"/>
       <c r="M106" s="4" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="N106" s="4"/>
       <c r="O106" s="4"/>
     </row>
     <row r="107" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="3">
-        <v>45699</v>
+        <v>46262</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>268</v>
+        <v>224</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="E107" s="3">
-        <v>45741</v>
+        <v>46304</v>
       </c>
       <c r="F107" s="5">
-        <v>1154.56</v>
+        <v>7694.4</v>
       </c>
       <c r="G107" s="5">
-        <v>1154.56</v>
+        <v>7694.4</v>
       </c>
       <c r="H107" s="3"/>
       <c r="I107" s="6">
-        <v>567</v>
+        <v>10</v>
       </c>
       <c r="J107" s="4" t="s">
-        <v>218</v>
+        <v>26</v>
       </c>
       <c r="K107" s="4" t="s">
-        <v>18</v>
+        <v>226</v>
       </c>
       <c r="L107" s="4"/>
       <c r="M107" s="4" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="N107" s="4"/>
       <c r="O107" s="4"/>
     </row>
     <row r="108" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="3">
-        <v>45699</v>
+        <v>46262</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>268</v>
+        <v>224</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="E108" s="3">
-        <v>45748</v>
+        <v>46304</v>
       </c>
       <c r="F108" s="5">
-        <v>1154.56</v>
+        <v>11660.11</v>
       </c>
       <c r="G108" s="5">
-        <v>1154.56</v>
+        <v>11660.11</v>
       </c>
       <c r="H108" s="3"/>
       <c r="I108" s="6">
-        <v>560</v>
+        <v>10</v>
       </c>
       <c r="J108" s="4" t="s">
-        <v>218</v>
+        <v>189</v>
       </c>
       <c r="K108" s="4" t="s">
-        <v>18</v>
+        <v>226</v>
       </c>
       <c r="L108" s="4"/>
       <c r="M108" s="4" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="N108" s="4"/>
       <c r="O108" s="4"/>
     </row>
     <row r="109" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="3">
-        <v>45699</v>
+        <v>46265</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>43</v>
+        <v>135</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>44</v>
+        <v>273</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="E109" s="3">
-        <v>45748</v>
+        <v>46305</v>
       </c>
       <c r="F109" s="5">
-        <v>7562.76</v>
+        <v>4750</v>
       </c>
       <c r="G109" s="5">
-        <v>7562.76</v>
+        <v>4750</v>
       </c>
       <c r="H109" s="3"/>
       <c r="I109" s="6">
-        <v>560</v>
+        <v>9</v>
       </c>
       <c r="J109" s="4" t="s">
-        <v>218</v>
+        <v>189</v>
       </c>
       <c r="K109" s="4" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="L109" s="4"/>
       <c r="M109" s="4" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="N109" s="4"/>
       <c r="O109" s="4"/>
     </row>
     <row r="110" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="3">
-        <v>45699</v>
+        <v>46265</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>236</v>
+        <v>23</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="E110" s="3">
-        <v>45755</v>
+        <v>46307</v>
       </c>
       <c r="F110" s="5">
-        <v>1154.56</v>
+        <v>1664</v>
       </c>
       <c r="G110" s="5">
-        <v>1154.56</v>
+        <v>1664</v>
       </c>
       <c r="H110" s="3"/>
       <c r="I110" s="6">
-        <v>553</v>
+        <v>7</v>
       </c>
       <c r="J110" s="4" t="s">
-        <v>218</v>
+        <v>18</v>
       </c>
       <c r="K110" s="4" t="s">
-        <v>18</v>
+        <v>71</v>
       </c>
       <c r="L110" s="4"/>
       <c r="M110" s="4" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="N110" s="4"/>
       <c r="O110" s="4"/>
     </row>
     <row r="111" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="3">
-        <v>45733</v>
+        <v>46232</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>236</v>
+        <v>180</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>281</v>
+        <v>232</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="E111" s="3">
-        <v>45761</v>
+        <v>46307</v>
       </c>
       <c r="F111" s="5">
-        <v>3850</v>
+        <v>4082.04</v>
       </c>
       <c r="G111" s="5">
-        <v>6169.53</v>
+        <v>4082.04</v>
       </c>
       <c r="H111" s="3"/>
       <c r="I111" s="6">
-        <v>547</v>
+        <v>7</v>
       </c>
       <c r="J111" s="4" t="s">
-        <v>218</v>
+        <v>189</v>
       </c>
       <c r="K111" s="4" t="s">
-        <v>18</v>
+        <v>184</v>
       </c>
       <c r="L111" s="4"/>
       <c r="M111" s="4" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="N111" s="4"/>
       <c r="O111" s="4"/>
     </row>
     <row r="112" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="3">
-        <v>45733</v>
+        <v>46266</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>236</v>
+        <v>45</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>281</v>
+        <v>191</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="E112" s="3">
-        <v>45768</v>
+        <v>46308</v>
       </c>
       <c r="F112" s="5">
-        <v>3850</v>
+        <v>18600</v>
       </c>
       <c r="G112" s="5">
-        <v>3850</v>
+        <v>18600</v>
       </c>
       <c r="H112" s="3"/>
       <c r="I112" s="6">
-        <v>540</v>
+        <v>6</v>
       </c>
       <c r="J112" s="4" t="s">
-        <v>218</v>
+        <v>26</v>
       </c>
       <c r="K112" s="4" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="L112" s="4"/>
       <c r="M112" s="4" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="N112" s="4"/>
       <c r="O112" s="4"/>
     </row>
     <row r="113" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="3">
-        <v>45733</v>
+        <v>46248</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>236</v>
+        <v>15</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="E113" s="3">
-        <v>45775</v>
+        <v>46308</v>
       </c>
       <c r="F113" s="5">
-        <v>3850</v>
+        <v>23355.33</v>
       </c>
       <c r="G113" s="5">
-        <v>3850</v>
+        <v>23355.33</v>
       </c>
       <c r="H113" s="3"/>
       <c r="I113" s="6">
-        <v>533</v>
+        <v>6</v>
       </c>
       <c r="J113" s="4" t="s">
-        <v>218</v>
+        <v>189</v>
       </c>
       <c r="K113" s="4" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="L113" s="4"/>
       <c r="M113" s="4" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="N113" s="4"/>
       <c r="O113" s="4"/>
     </row>
     <row r="114" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="3">
-        <v>45747</v>
+        <v>46234</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>236</v>
+        <v>180</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>281</v>
+        <v>181</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="E114" s="3">
-        <v>45775</v>
+        <v>46309</v>
       </c>
       <c r="F114" s="5">
-        <v>3800</v>
+        <v>3789.1</v>
       </c>
       <c r="G114" s="5">
-        <v>6089.41</v>
+        <v>3789.1</v>
       </c>
       <c r="H114" s="3"/>
       <c r="I114" s="6">
-        <v>533</v>
+        <v>5</v>
       </c>
       <c r="J114" s="4" t="s">
-        <v>218</v>
+        <v>189</v>
       </c>
       <c r="K114" s="4" t="s">
-        <v>18</v>
+        <v>184</v>
       </c>
       <c r="L114" s="4"/>
       <c r="M114" s="4" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="N114" s="4"/>
       <c r="O114" s="4"/>
     </row>
     <row r="115" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="3">
-        <v>45747</v>
+        <v>46265</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>236</v>
+        <v>15</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="E115" s="3">
-        <v>45782</v>
+        <v>46310</v>
       </c>
       <c r="F115" s="5">
-        <v>3800</v>
+        <v>8947.5</v>
       </c>
       <c r="G115" s="5">
-        <v>3800</v>
+        <v>8947.5</v>
       </c>
       <c r="H115" s="3"/>
       <c r="I115" s="6">
-        <v>526</v>
+        <v>4</v>
       </c>
       <c r="J115" s="4" t="s">
-        <v>218</v>
+        <v>189</v>
       </c>
       <c r="K115" s="4" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="L115" s="4"/>
       <c r="M115" s="4" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="N115" s="4"/>
       <c r="O115" s="4"/>
     </row>
     <row r="116" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="3">
-        <v>45747</v>
+        <v>46268</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>236</v>
+        <v>23</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>281</v>
+        <v>264</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="E116" s="3">
-        <v>45789</v>
+        <v>46310</v>
       </c>
       <c r="F116" s="5">
-        <v>3800</v>
+        <v>2754</v>
       </c>
       <c r="G116" s="5">
-        <v>3800</v>
+        <v>2754</v>
       </c>
       <c r="H116" s="3"/>
       <c r="I116" s="6">
-        <v>519</v>
+        <v>4</v>
       </c>
       <c r="J116" s="4" t="s">
-        <v>218</v>
+        <v>183</v>
       </c>
       <c r="K116" s="4" t="s">
-        <v>18</v>
+        <v>71</v>
       </c>
       <c r="L116" s="4"/>
       <c r="M116" s="4" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="N116" s="4"/>
       <c r="O116" s="4"/>
     </row>
     <row r="117" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="3">
-        <v>46045</v>
+        <v>46258</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>91</v>
+        <v>135</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>294</v>
+        <v>273</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="E117" s="3">
-        <v>46105</v>
+        <v>46311</v>
       </c>
       <c r="F117" s="5">
-        <v>5466.66</v>
+        <v>6247.5</v>
       </c>
       <c r="G117" s="5">
-        <v>5466.66</v>
+        <v>11266.12</v>
       </c>
       <c r="H117" s="3"/>
       <c r="I117" s="6">
-        <v>203</v>
+        <v>3</v>
       </c>
       <c r="J117" s="4" t="s">
-        <v>218</v>
+        <v>189</v>
       </c>
       <c r="K117" s="4" t="s">
-        <v>94</v>
+        <v>54</v>
       </c>
       <c r="L117" s="4"/>
       <c r="M117" s="4" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="N117" s="4"/>
       <c r="O117" s="4"/>
     </row>
     <row r="118" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="3">
-        <v>46253</v>
+        <v>46262</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>20</v>
+        <v>223</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>176</v>
+        <v>224</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="E118" s="3">
-        <v>46288</v>
+        <v>46311</v>
       </c>
       <c r="F118" s="5">
-        <v>1660.33</v>
+        <v>11660.11</v>
       </c>
       <c r="G118" s="5">
-        <v>1660.33</v>
+        <v>11660.11</v>
       </c>
       <c r="H118" s="3"/>
       <c r="I118" s="6">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="J118" s="4" t="s">
-        <v>218</v>
+        <v>189</v>
       </c>
       <c r="K118" s="4" t="s">
-        <v>23</v>
+        <v>226</v>
       </c>
       <c r="L118" s="4"/>
       <c r="M118" s="4" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="N118" s="4"/>
       <c r="O118" s="4"/>
     </row>
     <row r="119" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="3">
-        <v>46253</v>
+        <v>46262</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>84</v>
+        <v>223</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>299</v>
+        <v>224</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="E119" s="3">
-        <v>46295</v>
+        <v>46311</v>
       </c>
       <c r="F119" s="5">
-        <v>2051.2199999999998</v>
+        <v>7694.4</v>
       </c>
       <c r="G119" s="5">
-        <v>2051.2199999999998</v>
+        <v>7694.4</v>
       </c>
       <c r="H119" s="3"/>
       <c r="I119" s="6">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="J119" s="4" t="s">
-        <v>218</v>
+        <v>26</v>
       </c>
       <c r="K119" s="4" t="s">
-        <v>87</v>
+        <v>226</v>
       </c>
       <c r="L119" s="4"/>
       <c r="M119" s="4" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="N119" s="4"/>
       <c r="O119" s="4"/>
-    </row>
-    <row r="120" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="3">
-        <v>46265</v>
-      </c>
-      <c r="B120" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C120" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="D120" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="E120" s="3">
-        <v>46300</v>
-      </c>
-      <c r="F120" s="5">
-        <v>1664</v>
-      </c>
-      <c r="G120" s="5">
-        <v>1664</v>
-      </c>
-      <c r="H120" s="3"/>
-      <c r="I120" s="6">
-        <v>8</v>
-      </c>
-      <c r="J120" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="K120" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="L120" s="4"/>
-      <c r="M120" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="N120" s="4"/>
-      <c r="O120" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
+++ b/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WINDOWS\Desktop\dados planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{883C6B4A-5C47-4951-AA9B-07CDF00B2C10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6390D8DE-43C3-4C04-923B-E883FB485D3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="306">
   <si>
     <t>Dt.Emissão</t>
   </si>
@@ -528,7 +528,7 @@
     <t>GRADUAL COMERCIO E SERVICOS LTDA</t>
   </si>
   <si>
-    <t>01006433.3BP</t>
+    <t>01006433.3BPBP</t>
   </si>
   <si>
     <t>MARCOS DUTRA - PI</t>
@@ -717,21 +717,21 @@
     <t>70793158000011660110001121205064100656766915</t>
   </si>
   <si>
+    <t>FERMATA LTDA</t>
+  </si>
+  <si>
+    <t>01006989.2</t>
+  </si>
+  <si>
+    <t>70795158200004082050001121205064100656764191</t>
+  </si>
+  <si>
     <t>01007005.4</t>
   </si>
   <si>
     <t>00197158200009716000000003473568000003146117</t>
   </si>
   <si>
-    <t>FERMATA LTDA</t>
-  </si>
-  <si>
-    <t>01006989.2</t>
-  </si>
-  <si>
-    <t>70795158200004082050001121205064100656764191</t>
-  </si>
-  <si>
     <t>01007125.5</t>
   </si>
   <si>
@@ -750,18 +750,18 @@
     <t>70798158300011200000001121205064100656763896</t>
   </si>
   <si>
+    <t>01007023.2</t>
+  </si>
+  <si>
+    <t>70791158400003789090001121205064100656764423</t>
+  </si>
+  <si>
     <t>01007301.2</t>
   </si>
   <si>
     <t>00197158400018600000000003473568000003161417</t>
   </si>
   <si>
-    <t>01007023.2</t>
-  </si>
-  <si>
-    <t>70791158400003789090001121205064100656764423</t>
-  </si>
-  <si>
     <t>01007187.4</t>
   </si>
   <si>
@@ -801,24 +801,24 @@
     <t>00191159100018600000000003473568000003161517</t>
   </si>
   <si>
+    <t>01006976.3</t>
+  </si>
+  <si>
+    <t>23792159200004216660435090000000114800304920</t>
+  </si>
+  <si>
+    <t>01007005.5</t>
+  </si>
+  <si>
+    <t>00198159200009716000000003473568000003146217</t>
+  </si>
+  <si>
     <t>01007187.5</t>
   </si>
   <si>
     <t>70791159200010080000001121205064100656766220</t>
   </si>
   <si>
-    <t>01006976.3</t>
-  </si>
-  <si>
-    <t>23792159200004216660435090000000114800304920</t>
-  </si>
-  <si>
-    <t>01007005.5</t>
-  </si>
-  <si>
-    <t>00198159200009716000000003473568000003146217</t>
-  </si>
-  <si>
     <t>ATACAMED COMERCIO LTDA</t>
   </si>
   <si>
@@ -916,6 +916,33 @@
   </si>
   <si>
     <t>00191160100007694400000003473568000003159117</t>
+  </si>
+  <si>
+    <t>01007169.3</t>
+  </si>
+  <si>
+    <t>70798160200003809520001121205064100656765982</t>
+  </si>
+  <si>
+    <t>01007197.3</t>
+  </si>
+  <si>
+    <t>23799160300001172160435090000000124800304920</t>
+  </si>
+  <si>
+    <t>01007222.2</t>
+  </si>
+  <si>
+    <t>70799160300006247500001121205064100656766584</t>
+  </si>
+  <si>
+    <t>PIAUI HOSPITALAR LTDA</t>
+  </si>
+  <si>
+    <t>01007342.1</t>
+  </si>
+  <si>
+    <t>70799160400005475860001121205064100656768663</t>
   </si>
 </sst>
 </file>
@@ -1345,7 +1372,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O119"/>
+  <dimension ref="A1:O123"/>
   <sheetFormatPr defaultColWidth="12.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.85546875" style="1" customWidth="1"/>
@@ -1437,7 +1464,7 @@
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="6">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>18</v>
@@ -1476,7 +1503,7 @@
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="6">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>18</v>
@@ -1515,7 +1542,7 @@
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="6">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>26</v>
@@ -1554,7 +1581,7 @@
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="6">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>18</v>
@@ -1593,7 +1620,7 @@
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="6">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>26</v>
@@ -1632,7 +1659,7 @@
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="6">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>26</v>
@@ -1671,7 +1698,7 @@
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="6">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>26</v>
@@ -1710,7 +1737,7 @@
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="6">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>18</v>
@@ -1749,7 +1776,7 @@
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="6">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>18</v>
@@ -1788,7 +1815,7 @@
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="6">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>18</v>
@@ -1827,7 +1854,7 @@
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="6">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>18</v>
@@ -1866,7 +1893,7 @@
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="6">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>18</v>
@@ -1905,7 +1932,7 @@
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="6">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>18</v>
@@ -1944,7 +1971,7 @@
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="6">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>18</v>
@@ -1983,7 +2010,7 @@
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="6">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>18</v>
@@ -2022,7 +2049,7 @@
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="6">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>18</v>
@@ -2061,7 +2088,7 @@
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="6">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>18</v>
@@ -2100,7 +2127,7 @@
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="6">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="J19" s="4" t="s">
         <v>18</v>
@@ -2139,7 +2166,7 @@
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="6">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>18</v>
@@ -2178,7 +2205,7 @@
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="6">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>18</v>
@@ -2217,7 +2244,7 @@
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="6">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="J22" s="4" t="s">
         <v>18</v>
@@ -2256,7 +2283,7 @@
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="6">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="J23" s="4" t="s">
         <v>18</v>
@@ -2295,7 +2322,7 @@
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="6">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="J24" s="4" t="s">
         <v>18</v>
@@ -2334,7 +2361,7 @@
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="6">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="J25" s="4" t="s">
         <v>26</v>
@@ -2373,7 +2400,7 @@
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="6">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="J26" s="4" t="s">
         <v>18</v>
@@ -2412,7 +2439,7 @@
       </c>
       <c r="H27" s="3"/>
       <c r="I27" s="6">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="J27" s="4" t="s">
         <v>26</v>
@@ -2451,7 +2478,7 @@
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="6">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="J28" s="4" t="s">
         <v>26</v>
@@ -2490,7 +2517,7 @@
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="6">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="J29" s="4" t="s">
         <v>18</v>
@@ -2529,7 +2556,7 @@
       </c>
       <c r="H30" s="3"/>
       <c r="I30" s="6">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="J30" s="4" t="s">
         <v>18</v>
@@ -2568,7 +2595,7 @@
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="6">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="J31" s="4" t="s">
         <v>18</v>
@@ -2607,7 +2634,7 @@
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="6">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="J32" s="4" t="s">
         <v>26</v>
@@ -2646,7 +2673,7 @@
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="6">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="J33" s="4" t="s">
         <v>18</v>
@@ -2685,7 +2712,7 @@
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="6">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="J34" s="4" t="s">
         <v>18</v>
@@ -2724,7 +2751,7 @@
       </c>
       <c r="H35" s="3"/>
       <c r="I35" s="6">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="J35" s="4" t="s">
         <v>18</v>
@@ -2763,7 +2790,7 @@
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="6">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="J36" s="4" t="s">
         <v>18</v>
@@ -2802,7 +2829,7 @@
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="6">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="J37" s="4" t="s">
         <v>18</v>
@@ -2841,7 +2868,7 @@
       </c>
       <c r="H38" s="3"/>
       <c r="I38" s="6">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="J38" s="4" t="s">
         <v>18</v>
@@ -2880,7 +2907,7 @@
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="6">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="J39" s="4" t="s">
         <v>18</v>
@@ -2919,7 +2946,7 @@
       </c>
       <c r="H40" s="3"/>
       <c r="I40" s="6">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="J40" s="4" t="s">
         <v>18</v>
@@ -2958,7 +2985,7 @@
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="6">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="J41" s="4" t="s">
         <v>18</v>
@@ -2997,7 +3024,7 @@
       </c>
       <c r="H42" s="3"/>
       <c r="I42" s="6">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="J42" s="4" t="s">
         <v>18</v>
@@ -3036,7 +3063,7 @@
       </c>
       <c r="H43" s="3"/>
       <c r="I43" s="6">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="J43" s="4" t="s">
         <v>18</v>
@@ -3075,7 +3102,7 @@
       </c>
       <c r="H44" s="3"/>
       <c r="I44" s="6">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="J44" s="4" t="s">
         <v>26</v>
@@ -3114,7 +3141,7 @@
       </c>
       <c r="H45" s="3"/>
       <c r="I45" s="6">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="J45" s="4" t="s">
         <v>26</v>
@@ -3153,7 +3180,7 @@
       </c>
       <c r="H46" s="3"/>
       <c r="I46" s="6">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="J46" s="4" t="s">
         <v>26</v>
@@ -3192,7 +3219,7 @@
       </c>
       <c r="H47" s="3"/>
       <c r="I47" s="6">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="J47" s="4" t="s">
         <v>26</v>
@@ -3231,7 +3258,7 @@
       </c>
       <c r="H48" s="3"/>
       <c r="I48" s="6">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="J48" s="4" t="s">
         <v>26</v>
@@ -3270,7 +3297,7 @@
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="6">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="J49" s="4" t="s">
         <v>26</v>
@@ -3309,7 +3336,7 @@
       </c>
       <c r="H50" s="3"/>
       <c r="I50" s="6">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="J50" s="4" t="s">
         <v>26</v>
@@ -3348,7 +3375,7 @@
       </c>
       <c r="H51" s="3"/>
       <c r="I51" s="6">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="J51" s="4" t="s">
         <v>26</v>
@@ -3387,7 +3414,7 @@
       </c>
       <c r="H52" s="3"/>
       <c r="I52" s="6">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="J52" s="4" t="s">
         <v>26</v>
@@ -3426,7 +3453,7 @@
       </c>
       <c r="H53" s="3"/>
       <c r="I53" s="6">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="J53" s="4" t="s">
         <v>26</v>
@@ -3465,7 +3492,7 @@
       </c>
       <c r="H54" s="3"/>
       <c r="I54" s="6">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="J54" s="4"/>
       <c r="K54" s="4" t="s">
@@ -3500,7 +3527,7 @@
       </c>
       <c r="H55" s="3"/>
       <c r="I55" s="6">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="J55" s="4"/>
       <c r="K55" s="4" t="s">
@@ -3535,7 +3562,7 @@
       </c>
       <c r="H56" s="3"/>
       <c r="I56" s="6">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="J56" s="4"/>
       <c r="K56" s="4" t="s">
@@ -3570,7 +3597,7 @@
       </c>
       <c r="H57" s="3"/>
       <c r="I57" s="6">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J57" s="4"/>
       <c r="K57" s="4" t="s">
@@ -3605,7 +3632,7 @@
       </c>
       <c r="H58" s="3"/>
       <c r="I58" s="6">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J58" s="4" t="s">
         <v>26</v>
@@ -3644,7 +3671,7 @@
       </c>
       <c r="H59" s="3"/>
       <c r="I59" s="6">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="J59" s="4" t="s">
         <v>26</v>
@@ -3683,7 +3710,7 @@
       </c>
       <c r="H60" s="3"/>
       <c r="I60" s="6">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J60" s="4" t="s">
         <v>26</v>
@@ -3722,7 +3749,7 @@
       </c>
       <c r="H61" s="3"/>
       <c r="I61" s="6">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="J61" s="4" t="s">
         <v>18</v>
@@ -3761,7 +3788,7 @@
       </c>
       <c r="H62" s="3"/>
       <c r="I62" s="6">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J62" s="4"/>
       <c r="K62" s="4" t="s">
@@ -3796,7 +3823,7 @@
       </c>
       <c r="H63" s="3"/>
       <c r="I63" s="6">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J63" s="4"/>
       <c r="K63" s="4" t="s">
@@ -3831,7 +3858,7 @@
       </c>
       <c r="H64" s="3"/>
       <c r="I64" s="6">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J64" s="4"/>
       <c r="K64" s="4" t="s">
@@ -3859,14 +3886,14 @@
         <v>46222</v>
       </c>
       <c r="F65" s="5">
-        <v>22349.79</v>
+        <v>12349.79</v>
       </c>
       <c r="G65" s="5">
-        <v>22349.79</v>
+        <v>12349.79</v>
       </c>
       <c r="H65" s="3"/>
       <c r="I65" s="6">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J65" s="4"/>
       <c r="K65" s="4" t="s">
@@ -3901,7 +3928,7 @@
       </c>
       <c r="H66" s="3"/>
       <c r="I66" s="6">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J66" s="4" t="s">
         <v>26</v>
@@ -3940,7 +3967,7 @@
       </c>
       <c r="H67" s="3"/>
       <c r="I67" s="6">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J67" s="4" t="s">
         <v>26</v>
@@ -3979,7 +4006,7 @@
       </c>
       <c r="H68" s="3"/>
       <c r="I68" s="6">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J68" s="4" t="s">
         <v>26</v>
@@ -4018,7 +4045,7 @@
       </c>
       <c r="H69" s="3"/>
       <c r="I69" s="6">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J69" s="4" t="s">
         <v>26</v>
@@ -4057,7 +4084,7 @@
       </c>
       <c r="H70" s="3"/>
       <c r="I70" s="6">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J70" s="4" t="s">
         <v>183</v>
@@ -4096,7 +4123,7 @@
       </c>
       <c r="H71" s="3"/>
       <c r="I71" s="6">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J71" s="4" t="s">
         <v>26</v>
@@ -4135,7 +4162,7 @@
       </c>
       <c r="H72" s="3"/>
       <c r="I72" s="6">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J72" s="4" t="s">
         <v>189</v>
@@ -4174,7 +4201,7 @@
       </c>
       <c r="H73" s="3"/>
       <c r="I73" s="6">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J73" s="4" t="s">
         <v>189</v>
@@ -4213,7 +4240,7 @@
       </c>
       <c r="H74" s="3"/>
       <c r="I74" s="6">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J74" s="4" t="s">
         <v>26</v>
@@ -4252,7 +4279,7 @@
       </c>
       <c r="H75" s="3"/>
       <c r="I75" s="6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J75" s="4" t="s">
         <v>189</v>
@@ -4291,7 +4318,7 @@
       </c>
       <c r="H76" s="3"/>
       <c r="I76" s="6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J76" s="4" t="s">
         <v>189</v>
@@ -4330,7 +4357,7 @@
       </c>
       <c r="H77" s="3"/>
       <c r="I77" s="6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J77" s="4" t="s">
         <v>189</v>
@@ -4369,7 +4396,7 @@
       </c>
       <c r="H78" s="3"/>
       <c r="I78" s="6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J78" s="4" t="s">
         <v>189</v>
@@ -4408,7 +4435,7 @@
       </c>
       <c r="H79" s="3"/>
       <c r="I79" s="6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J79" s="4" t="s">
         <v>189</v>
@@ -4447,7 +4474,7 @@
       </c>
       <c r="H80" s="3"/>
       <c r="I80" s="6">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J80" s="4" t="s">
         <v>189</v>
@@ -4486,7 +4513,7 @@
       </c>
       <c r="H81" s="3"/>
       <c r="I81" s="6">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J81" s="4" t="s">
         <v>26</v>
@@ -4525,7 +4552,7 @@
       </c>
       <c r="H82" s="3"/>
       <c r="I82" s="6">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J82" s="4" t="s">
         <v>183</v>
@@ -4564,7 +4591,7 @@
       </c>
       <c r="H83" s="3"/>
       <c r="I83" s="6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J83" s="4" t="s">
         <v>189</v>
@@ -4603,7 +4630,7 @@
       </c>
       <c r="H84" s="3"/>
       <c r="I84" s="6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J84" s="4" t="s">
         <v>189</v>
@@ -4642,7 +4669,7 @@
       </c>
       <c r="H85" s="3"/>
       <c r="I85" s="6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J85" s="4" t="s">
         <v>18</v>
@@ -4681,7 +4708,7 @@
       </c>
       <c r="H86" s="3"/>
       <c r="I86" s="6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J86" s="4" t="s">
         <v>189</v>
@@ -4720,7 +4747,7 @@
       </c>
       <c r="H87" s="3"/>
       <c r="I87" s="6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J87" s="4" t="s">
         <v>26</v>
@@ -4759,7 +4786,7 @@
       </c>
       <c r="H88" s="3"/>
       <c r="I88" s="6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J88" s="4" t="s">
         <v>189</v>
@@ -4779,36 +4806,36 @@
         <v>46232</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>175</v>
+        <v>230</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E89" s="3">
         <v>46292</v>
       </c>
       <c r="F89" s="5">
-        <v>9716</v>
+        <v>4082.05</v>
       </c>
       <c r="G89" s="5">
-        <v>9716</v>
+        <v>4082.05</v>
       </c>
       <c r="H89" s="3"/>
       <c r="I89" s="6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J89" s="4" t="s">
-        <v>26</v>
+        <v>189</v>
       </c>
       <c r="K89" s="4" t="s">
-        <v>39</v>
+        <v>184</v>
       </c>
       <c r="L89" s="4"/>
       <c r="M89" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N89" s="4"/>
       <c r="O89" s="4"/>
@@ -4818,10 +4845,10 @@
         <v>46232</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>180</v>
+        <v>15</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>232</v>
+        <v>175</v>
       </c>
       <c r="D90" s="4" t="s">
         <v>233</v>
@@ -4830,20 +4857,20 @@
         <v>46292</v>
       </c>
       <c r="F90" s="5">
-        <v>4082.05</v>
+        <v>9716</v>
       </c>
       <c r="G90" s="5">
-        <v>4082.05</v>
+        <v>9716</v>
       </c>
       <c r="H90" s="3"/>
       <c r="I90" s="6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J90" s="4" t="s">
-        <v>189</v>
+        <v>26</v>
       </c>
       <c r="K90" s="4" t="s">
-        <v>184</v>
+        <v>39</v>
       </c>
       <c r="L90" s="4"/>
       <c r="M90" s="4" t="s">
@@ -4876,7 +4903,7 @@
       </c>
       <c r="H91" s="3"/>
       <c r="I91" s="6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J91" s="4" t="s">
         <v>189</v>
@@ -4915,7 +4942,7 @@
       </c>
       <c r="H92" s="3"/>
       <c r="I92" s="6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J92" s="4" t="s">
         <v>183</v>
@@ -4954,7 +4981,7 @@
       </c>
       <c r="H93" s="3"/>
       <c r="I93" s="6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J93" s="4" t="s">
         <v>189</v>
@@ -4971,13 +4998,13 @@
     </row>
     <row r="94" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="3">
-        <v>46266</v>
+        <v>46234</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>45</v>
+        <v>180</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="D94" s="4" t="s">
         <v>241</v>
@@ -4986,20 +5013,20 @@
         <v>46294</v>
       </c>
       <c r="F94" s="5">
-        <v>18600</v>
+        <v>3789.09</v>
       </c>
       <c r="G94" s="5">
-        <v>18600</v>
+        <v>3789.09</v>
       </c>
       <c r="H94" s="3"/>
       <c r="I94" s="6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J94" s="4" t="s">
-        <v>26</v>
+        <v>189</v>
       </c>
       <c r="K94" s="4" t="s">
-        <v>27</v>
+        <v>184</v>
       </c>
       <c r="L94" s="4"/>
       <c r="M94" s="4" t="s">
@@ -5010,13 +5037,13 @@
     </row>
     <row r="95" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="3">
-        <v>46234</v>
+        <v>46266</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>180</v>
+        <v>45</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="D95" s="4" t="s">
         <v>243</v>
@@ -5025,20 +5052,20 @@
         <v>46294</v>
       </c>
       <c r="F95" s="5">
-        <v>3789.09</v>
+        <v>18600</v>
       </c>
       <c r="G95" s="5">
-        <v>3789.09</v>
+        <v>18600</v>
       </c>
       <c r="H95" s="3"/>
       <c r="I95" s="6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J95" s="4" t="s">
-        <v>189</v>
+        <v>26</v>
       </c>
       <c r="K95" s="4" t="s">
-        <v>184</v>
+        <v>27</v>
       </c>
       <c r="L95" s="4"/>
       <c r="M95" s="4" t="s">
@@ -5071,7 +5098,7 @@
       </c>
       <c r="H96" s="3"/>
       <c r="I96" s="6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J96" s="4" t="s">
         <v>189</v>
@@ -5110,7 +5137,7 @@
       </c>
       <c r="H97" s="3"/>
       <c r="I97" s="6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J97" s="4" t="s">
         <v>18</v>
@@ -5149,7 +5176,7 @@
       </c>
       <c r="H98" s="3"/>
       <c r="I98" s="6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J98" s="4" t="s">
         <v>189</v>
@@ -5188,7 +5215,7 @@
       </c>
       <c r="H99" s="3"/>
       <c r="I99" s="6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J99" s="4" t="s">
         <v>26</v>
@@ -5227,7 +5254,7 @@
       </c>
       <c r="H100" s="3"/>
       <c r="I100" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J100" s="4" t="s">
         <v>189</v>
@@ -5266,7 +5293,7 @@
       </c>
       <c r="H101" s="3"/>
       <c r="I101" s="6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J101" s="4" t="s">
         <v>26</v>
@@ -5283,13 +5310,13 @@
     </row>
     <row r="102" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="3">
-        <v>46253</v>
+        <v>46227</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>45</v>
+        <v>180</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="D102" s="4" t="s">
         <v>258</v>
@@ -5298,20 +5325,20 @@
         <v>46302</v>
       </c>
       <c r="F102" s="5">
-        <v>10080</v>
+        <v>4216.66</v>
       </c>
       <c r="G102" s="5">
-        <v>10080</v>
+        <v>4216.66</v>
       </c>
       <c r="H102" s="3"/>
       <c r="I102" s="6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J102" s="4" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="K102" s="4" t="s">
-        <v>27</v>
+        <v>184</v>
       </c>
       <c r="L102" s="4"/>
       <c r="M102" s="4" t="s">
@@ -5322,13 +5349,13 @@
     </row>
     <row r="103" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="3">
-        <v>46227</v>
+        <v>46232</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>180</v>
+        <v>15</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="D103" s="4" t="s">
         <v>260</v>
@@ -5337,20 +5364,20 @@
         <v>46302</v>
       </c>
       <c r="F103" s="5">
-        <v>4216.66</v>
+        <v>9716</v>
       </c>
       <c r="G103" s="5">
-        <v>4216.66</v>
+        <v>9716</v>
       </c>
       <c r="H103" s="3"/>
       <c r="I103" s="6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J103" s="4" t="s">
-        <v>183</v>
+        <v>26</v>
       </c>
       <c r="K103" s="4" t="s">
-        <v>184</v>
+        <v>39</v>
       </c>
       <c r="L103" s="4"/>
       <c r="M103" s="4" t="s">
@@ -5361,13 +5388,13 @@
     </row>
     <row r="104" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="3">
-        <v>46232</v>
+        <v>46253</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>175</v>
+        <v>191</v>
       </c>
       <c r="D104" s="4" t="s">
         <v>262</v>
@@ -5376,20 +5403,20 @@
         <v>46302</v>
       </c>
       <c r="F104" s="5">
-        <v>9716</v>
+        <v>10080</v>
       </c>
       <c r="G104" s="5">
-        <v>9716</v>
+        <v>10080</v>
       </c>
       <c r="H104" s="3"/>
       <c r="I104" s="6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J104" s="4" t="s">
-        <v>26</v>
+        <v>189</v>
       </c>
       <c r="K104" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="L104" s="4"/>
       <c r="M104" s="4" t="s">
@@ -5422,7 +5449,7 @@
       </c>
       <c r="H105" s="3"/>
       <c r="I105" s="6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J105" s="4" t="s">
         <v>183</v>
@@ -5461,7 +5488,7 @@
       </c>
       <c r="H106" s="3"/>
       <c r="I106" s="6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J106" s="4" t="s">
         <v>189</v>
@@ -5500,7 +5527,7 @@
       </c>
       <c r="H107" s="3"/>
       <c r="I107" s="6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J107" s="4" t="s">
         <v>26</v>
@@ -5539,7 +5566,7 @@
       </c>
       <c r="H108" s="3"/>
       <c r="I108" s="6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J108" s="4" t="s">
         <v>189</v>
@@ -5578,7 +5605,7 @@
       </c>
       <c r="H109" s="3"/>
       <c r="I109" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J109" s="4" t="s">
         <v>189</v>
@@ -5617,7 +5644,7 @@
       </c>
       <c r="H110" s="3"/>
       <c r="I110" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J110" s="4" t="s">
         <v>18</v>
@@ -5640,7 +5667,7 @@
         <v>180</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D111" s="4" t="s">
         <v>278</v>
@@ -5656,7 +5683,7 @@
       </c>
       <c r="H111" s="3"/>
       <c r="I111" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J111" s="4" t="s">
         <v>189</v>
@@ -5695,7 +5722,7 @@
       </c>
       <c r="H112" s="3"/>
       <c r="I112" s="6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J112" s="4" t="s">
         <v>26</v>
@@ -5734,7 +5761,7 @@
       </c>
       <c r="H113" s="3"/>
       <c r="I113" s="6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J113" s="4" t="s">
         <v>189</v>
@@ -5773,7 +5800,7 @@
       </c>
       <c r="H114" s="3"/>
       <c r="I114" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J114" s="4" t="s">
         <v>189</v>
@@ -5812,7 +5839,7 @@
       </c>
       <c r="H115" s="3"/>
       <c r="I115" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J115" s="4" t="s">
         <v>189</v>
@@ -5851,7 +5878,7 @@
       </c>
       <c r="H116" s="3"/>
       <c r="I116" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J116" s="4" t="s">
         <v>183</v>
@@ -5890,7 +5917,7 @@
       </c>
       <c r="H117" s="3"/>
       <c r="I117" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J117" s="4" t="s">
         <v>189</v>
@@ -5929,7 +5956,7 @@
       </c>
       <c r="H118" s="3"/>
       <c r="I118" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J118" s="4" t="s">
         <v>189</v>
@@ -5968,7 +5995,7 @@
       </c>
       <c r="H119" s="3"/>
       <c r="I119" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J119" s="4" t="s">
         <v>26</v>
@@ -5982,6 +6009,162 @@
       </c>
       <c r="N119" s="4"/>
       <c r="O119" s="4"/>
+    </row>
+    <row r="120" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="3">
+        <v>46252</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C120" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D120" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="E120" s="3">
+        <v>46312</v>
+      </c>
+      <c r="F120" s="5">
+        <v>3809.52</v>
+      </c>
+      <c r="G120" s="5">
+        <v>3809.52</v>
+      </c>
+      <c r="H120" s="3"/>
+      <c r="I120" s="6">
+        <v>3</v>
+      </c>
+      <c r="J120" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="K120" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="L120" s="4"/>
+      <c r="M120" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="N120" s="4"/>
+      <c r="O120" s="4"/>
+    </row>
+    <row r="121" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="3">
+        <v>46253</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C121" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D121" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="E121" s="3">
+        <v>46313</v>
+      </c>
+      <c r="F121" s="5">
+        <v>1172.1600000000001</v>
+      </c>
+      <c r="G121" s="5">
+        <v>1172.1600000000001</v>
+      </c>
+      <c r="H121" s="3"/>
+      <c r="I121" s="6">
+        <v>2</v>
+      </c>
+      <c r="J121" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="K121" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="L121" s="4"/>
+      <c r="M121" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="N121" s="4"/>
+      <c r="O121" s="4"/>
+    </row>
+    <row r="122" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="3">
+        <v>46258</v>
+      </c>
+      <c r="B122" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C122" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="D122" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="E122" s="3">
+        <v>46313</v>
+      </c>
+      <c r="F122" s="5">
+        <v>6247.5</v>
+      </c>
+      <c r="G122" s="5">
+        <v>6247.5</v>
+      </c>
+      <c r="H122" s="3"/>
+      <c r="I122" s="6">
+        <v>2</v>
+      </c>
+      <c r="J122" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="K122" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="L122" s="4"/>
+      <c r="M122" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="N122" s="4"/>
+      <c r="O122" s="4"/>
+    </row>
+    <row r="123" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="3">
+        <v>46286</v>
+      </c>
+      <c r="B123" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C123" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="D123" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="E123" s="3">
+        <v>46314</v>
+      </c>
+      <c r="F123" s="5">
+        <v>5475.86</v>
+      </c>
+      <c r="G123" s="5">
+        <v>5475.86</v>
+      </c>
+      <c r="H123" s="3"/>
+      <c r="I123" s="6">
+        <v>1</v>
+      </c>
+      <c r="J123" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="K123" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="L123" s="4"/>
+      <c r="M123" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="N123" s="4"/>
+      <c r="O123" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
+++ b/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WINDOWS\Desktop\dados planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6390D8DE-43C3-4C04-923B-E883FB485D3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{743BB8CC-36A9-4B6F-91E1-7BC592DDEE05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="309">
   <si>
     <t>Dt.Emissão</t>
   </si>
@@ -600,21 +600,15 @@
     <t>70799156900005741360001121205064100656764415</t>
   </si>
   <si>
+    <t>01007005.3</t>
+  </si>
+  <si>
+    <t>00196157200009716000000003473568000003146017</t>
+  </si>
+  <si>
     <t>CIRURGICA MONTEBELLO LTDA</t>
   </si>
   <si>
-    <t>01007187.2</t>
-  </si>
-  <si>
-    <t>70791157100010080000001121205064100656766196</t>
-  </si>
-  <si>
-    <t>01007005.3</t>
-  </si>
-  <si>
-    <t>00196157200009716000000003473568000003146017</t>
-  </si>
-  <si>
     <t>01006958.6</t>
   </si>
   <si>
@@ -624,18 +618,6 @@
     <t>PLENA DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
   </si>
   <si>
-    <t>01006957.2</t>
-  </si>
-  <si>
-    <t>70792157400010666670001121205064100656763953</t>
-  </si>
-  <si>
-    <t>01006999.1</t>
-  </si>
-  <si>
-    <t>70799157400006500000001121205064100656764282</t>
-  </si>
-  <si>
     <t>01007020.1</t>
   </si>
   <si>
@@ -654,12 +636,6 @@
     <t>70791157600004320000001121205064100656765123</t>
   </si>
   <si>
-    <t>01007301.1</t>
-  </si>
-  <si>
-    <t>00192157700018600000000003473568000003161317</t>
-  </si>
-  <si>
     <t>01006976.2</t>
   </si>
   <si>
@@ -681,21 +657,6 @@
     <t>70794157800003640000001121205064100656766162</t>
   </si>
   <si>
-    <t>01007175.2</t>
-  </si>
-  <si>
-    <t>34193157800001660331090002618768120992717000</t>
-  </si>
-  <si>
-    <t>COBERMED COMERCIO DE MATERIAIS MEDICOS LTDA</t>
-  </si>
-  <si>
-    <t>01007194.1</t>
-  </si>
-  <si>
-    <t>70797157900006265000001121205064100656766642</t>
-  </si>
-  <si>
     <t>FELIPE AQUINO - MT</t>
   </si>
   <si>
@@ -738,30 +699,24 @@
     <t>70799158300004320000001121205064100656765131</t>
   </si>
   <si>
-    <t>01006877.3</t>
-  </si>
-  <si>
-    <t>23797158300006265000435090000000110700304920</t>
-  </si>
-  <si>
     <t>01006922.3</t>
   </si>
   <si>
     <t>70798158300011200000001121205064100656763896</t>
   </si>
   <si>
+    <t>01007301.2</t>
+  </si>
+  <si>
+    <t>00197158400018600000000003473568000003161417</t>
+  </si>
+  <si>
     <t>01007023.2</t>
   </si>
   <si>
     <t>70791158400003789090001121205064100656764423</t>
   </si>
   <si>
-    <t>01007301.2</t>
-  </si>
-  <si>
-    <t>00197158400018600000000003473568000003161417</t>
-  </si>
-  <si>
     <t>01007187.4</t>
   </si>
   <si>
@@ -777,18 +732,18 @@
     <t>34196158500002051221090002617698120992717000</t>
   </si>
   <si>
+    <t>01007265.2</t>
+  </si>
+  <si>
+    <t>00192158700007694400000003473568000003158917</t>
+  </si>
+  <si>
     <t>01007249.2</t>
   </si>
   <si>
     <t>70792158700011660110001121205064100656766923</t>
   </si>
   <si>
-    <t>01007265.2</t>
-  </si>
-  <si>
-    <t>00192158700007694400000003473568000003158917</t>
-  </si>
-  <si>
     <t>01006920.3</t>
   </si>
   <si>
@@ -801,6 +756,12 @@
     <t>00191159100018600000000003473568000003161517</t>
   </si>
   <si>
+    <t>01007187.5</t>
+  </si>
+  <si>
+    <t>70791159200010080000001121205064100656766220</t>
+  </si>
+  <si>
     <t>01006976.3</t>
   </si>
   <si>
@@ -813,87 +774,57 @@
     <t>00198159200009716000000003473568000003146217</t>
   </si>
   <si>
-    <t>01007187.5</t>
-  </si>
-  <si>
-    <t>70791159200010080000001121205064100656766220</t>
+    <t>01007265.3</t>
+  </si>
+  <si>
+    <t>00199159400007694400000003473568000003159017</t>
+  </si>
+  <si>
+    <t>01007249.3</t>
+  </si>
+  <si>
+    <t>70791159400011660110001121205064100656766931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZOE MED COMERCIO DE PRODUTOS MEDICOS HOSPITALARES </t>
+  </si>
+  <si>
+    <t>01007270.2</t>
+  </si>
+  <si>
+    <t>70797159500004750000001121205064100656766980</t>
+  </si>
+  <si>
+    <t>01006989.3</t>
+  </si>
+  <si>
+    <t>70796159700004082040001121205064100656764209</t>
+  </si>
+  <si>
+    <t>01007301.4</t>
+  </si>
+  <si>
+    <t>00196159800018600000000003473568000003161617</t>
+  </si>
+  <si>
+    <t>ASPEN SERVICE COMERCIO LTDA</t>
+  </si>
+  <si>
+    <t>01007117.2</t>
+  </si>
+  <si>
+    <t>70793159800023355330001121205064100656765677</t>
+  </si>
+  <si>
+    <t>01007023.3</t>
+  </si>
+  <si>
+    <t>70794159900003789100001121205064100656764431</t>
   </si>
   <si>
     <t>ATACAMED COMERCIO LTDA</t>
   </si>
   <si>
-    <t>01007311.2</t>
-  </si>
-  <si>
-    <t>23792159300002754000435090000000130100304920</t>
-  </si>
-  <si>
-    <t>01007194.2</t>
-  </si>
-  <si>
-    <t>70793159400006265000001121205064100656766659</t>
-  </si>
-  <si>
-    <t>01007265.3</t>
-  </si>
-  <si>
-    <t>00199159400007694400000003473568000003159017</t>
-  </si>
-  <si>
-    <t>01007249.3</t>
-  </si>
-  <si>
-    <t>70791159400011660110001121205064100656766931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZOE MED COMERCIO DE PRODUTOS MEDICOS HOSPITALARES </t>
-  </si>
-  <si>
-    <t>01007270.2</t>
-  </si>
-  <si>
-    <t>70797159500004750000001121205064100656766980</t>
-  </si>
-  <si>
-    <t>01007274.3</t>
-  </si>
-  <si>
-    <t>34196159700001664001090002623618120992717000</t>
-  </si>
-  <si>
-    <t>01006989.3</t>
-  </si>
-  <si>
-    <t>70796159700004082040001121205064100656764209</t>
-  </si>
-  <si>
-    <t>01007301.4</t>
-  </si>
-  <si>
-    <t>00196159800018600000000003473568000003161617</t>
-  </si>
-  <si>
-    <t>ASPEN SERVICE COMERCIO LTDA</t>
-  </si>
-  <si>
-    <t>01007117.2</t>
-  </si>
-  <si>
-    <t>70793159800023355330001121205064100656765677</t>
-  </si>
-  <si>
-    <t>01007023.3</t>
-  </si>
-  <si>
-    <t>70794159900003789100001121205064100656764431</t>
-  </si>
-  <si>
-    <t>01007269.2</t>
-  </si>
-  <si>
-    <t>70792160000008947500001121205064100656767145</t>
-  </si>
-  <si>
     <t>01007311.3</t>
   </si>
   <si>
@@ -906,30 +837,18 @@
     <t>70798160100011266120001121205064100656766576</t>
   </si>
   <si>
+    <t>01007265.4</t>
+  </si>
+  <si>
+    <t>00191160100007694400000003473568000003159117</t>
+  </si>
+  <si>
     <t>01007249.4</t>
   </si>
   <si>
     <t>70791160100011660110001121205064100656766949</t>
   </si>
   <si>
-    <t>01007265.4</t>
-  </si>
-  <si>
-    <t>00191160100007694400000003473568000003159117</t>
-  </si>
-  <si>
-    <t>01007169.3</t>
-  </si>
-  <si>
-    <t>70798160200003809520001121205064100656765982</t>
-  </si>
-  <si>
-    <t>01007197.3</t>
-  </si>
-  <si>
-    <t>23799160300001172160435090000000124800304920</t>
-  </si>
-  <si>
     <t>01007222.2</t>
   </si>
   <si>
@@ -943,6 +862,96 @@
   </si>
   <si>
     <t>70799160400005475860001121205064100656768663</t>
+  </si>
+  <si>
+    <t>01007270.3</t>
+  </si>
+  <si>
+    <t>70792160500004750000001121205064100656766998</t>
+  </si>
+  <si>
+    <t>ESTRELA COMERCIO DE PRODUTOS MEDICOS E HOSPITALARE</t>
+  </si>
+  <si>
+    <t>01007366.1</t>
+  </si>
+  <si>
+    <t>70796160500012695590001121205064100656767988</t>
+  </si>
+  <si>
+    <t>M. A. M COMERCIO E DISTRIBUIDORA DE MEDICAMENTOS L</t>
+  </si>
+  <si>
+    <t>01007371.1</t>
+  </si>
+  <si>
+    <t>70791160500004466270001121205064100656768713</t>
+  </si>
+  <si>
+    <t>MULTIMAIS ATACADO LTDA</t>
+  </si>
+  <si>
+    <t>01007400.2</t>
+  </si>
+  <si>
+    <t>70798160500001600000001121205064100656768069</t>
+  </si>
+  <si>
+    <t>LOPES BARRETO COMERCIO DE PRODUTOS MEDICOS LTDA</t>
+  </si>
+  <si>
+    <t>01007429.1</t>
+  </si>
+  <si>
+    <t>34194160500000979251090002632528120992717000</t>
+  </si>
+  <si>
+    <t>01007301.5</t>
+  </si>
+  <si>
+    <t>00199160500018600000000003473568000003161717</t>
+  </si>
+  <si>
+    <t>HOSPMED LTDA</t>
+  </si>
+  <si>
+    <t>01007167.6</t>
+  </si>
+  <si>
+    <t>34198160600001452601090002617368120992717000</t>
+  </si>
+  <si>
+    <t>AMAZONIA HOSPITALAR LTDA</t>
+  </si>
+  <si>
+    <t>01007389.1</t>
+  </si>
+  <si>
+    <t>MA</t>
+  </si>
+  <si>
+    <t>70791160600004772900001121205064100656768978</t>
+  </si>
+  <si>
+    <t>01007445.1</t>
+  </si>
+  <si>
+    <t>34191160600002334241090002633698120992717000</t>
+  </si>
+  <si>
+    <t>LEANDRA LUIZA SILVA - AM</t>
+  </si>
+  <si>
+    <t>JM COMERCIO DE PRODUTOS FARMACEUTICOS LTDA</t>
+  </si>
+  <si>
+    <t>01007348.1</t>
+  </si>
+  <si>
+    <t>AM</t>
+  </si>
+  <si>
+    <t>70794160700009617800001121205064100656768895</t>
   </si>
 </sst>
 </file>
@@ -1372,7 +1381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O123"/>
+  <dimension ref="A1:O120"/>
   <sheetFormatPr defaultColWidth="12.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.85546875" style="1" customWidth="1"/>
@@ -1464,7 +1473,7 @@
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="6">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>18</v>
@@ -1503,7 +1512,7 @@
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="6">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>18</v>
@@ -1542,7 +1551,7 @@
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="6">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>26</v>
@@ -1581,7 +1590,7 @@
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="6">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>18</v>
@@ -1620,7 +1629,7 @@
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="6">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>26</v>
@@ -1659,7 +1668,7 @@
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="6">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>26</v>
@@ -1698,7 +1707,7 @@
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="6">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>26</v>
@@ -1737,7 +1746,7 @@
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="6">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>18</v>
@@ -1776,7 +1785,7 @@
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="6">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>18</v>
@@ -1815,7 +1824,7 @@
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="6">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>18</v>
@@ -1854,7 +1863,7 @@
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="6">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>18</v>
@@ -1893,7 +1902,7 @@
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="6">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>18</v>
@@ -1932,7 +1941,7 @@
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="6">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>18</v>
@@ -1971,7 +1980,7 @@
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="6">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>18</v>
@@ -2010,7 +2019,7 @@
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="6">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>18</v>
@@ -2049,7 +2058,7 @@
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="6">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>18</v>
@@ -2088,7 +2097,7 @@
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="6">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>18</v>
@@ -2127,7 +2136,7 @@
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="6">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="J19" s="4" t="s">
         <v>18</v>
@@ -2166,7 +2175,7 @@
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="6">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>18</v>
@@ -2205,7 +2214,7 @@
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="6">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>18</v>
@@ -2244,7 +2253,7 @@
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="6">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="J22" s="4" t="s">
         <v>18</v>
@@ -2283,7 +2292,7 @@
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="6">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="J23" s="4" t="s">
         <v>18</v>
@@ -2322,7 +2331,7 @@
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="6">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="J24" s="4" t="s">
         <v>18</v>
@@ -2361,7 +2370,7 @@
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="6">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="J25" s="4" t="s">
         <v>26</v>
@@ -2400,7 +2409,7 @@
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="6">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="J26" s="4" t="s">
         <v>18</v>
@@ -2439,7 +2448,7 @@
       </c>
       <c r="H27" s="3"/>
       <c r="I27" s="6">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="J27" s="4" t="s">
         <v>26</v>
@@ -2478,7 +2487,7 @@
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="6">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="J28" s="4" t="s">
         <v>26</v>
@@ -2517,7 +2526,7 @@
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="6">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="J29" s="4" t="s">
         <v>18</v>
@@ -2556,7 +2565,7 @@
       </c>
       <c r="H30" s="3"/>
       <c r="I30" s="6">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="J30" s="4" t="s">
         <v>18</v>
@@ -2595,7 +2604,7 @@
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="6">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="J31" s="4" t="s">
         <v>18</v>
@@ -2634,7 +2643,7 @@
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="6">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="J32" s="4" t="s">
         <v>26</v>
@@ -2673,7 +2682,7 @@
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="6">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="J33" s="4" t="s">
         <v>18</v>
@@ -2712,7 +2721,7 @@
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="6">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="J34" s="4" t="s">
         <v>18</v>
@@ -2751,7 +2760,7 @@
       </c>
       <c r="H35" s="3"/>
       <c r="I35" s="6">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="J35" s="4" t="s">
         <v>18</v>
@@ -2790,7 +2799,7 @@
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="6">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="J36" s="4" t="s">
         <v>18</v>
@@ -2829,7 +2838,7 @@
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="6">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="J37" s="4" t="s">
         <v>18</v>
@@ -2868,7 +2877,7 @@
       </c>
       <c r="H38" s="3"/>
       <c r="I38" s="6">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="J38" s="4" t="s">
         <v>18</v>
@@ -2907,7 +2916,7 @@
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="6">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="J39" s="4" t="s">
         <v>18</v>
@@ -2946,7 +2955,7 @@
       </c>
       <c r="H40" s="3"/>
       <c r="I40" s="6">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="J40" s="4" t="s">
         <v>18</v>
@@ -2985,7 +2994,7 @@
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="6">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="J41" s="4" t="s">
         <v>18</v>
@@ -3024,7 +3033,7 @@
       </c>
       <c r="H42" s="3"/>
       <c r="I42" s="6">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="J42" s="4" t="s">
         <v>18</v>
@@ -3063,7 +3072,7 @@
       </c>
       <c r="H43" s="3"/>
       <c r="I43" s="6">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="J43" s="4" t="s">
         <v>18</v>
@@ -3102,7 +3111,7 @@
       </c>
       <c r="H44" s="3"/>
       <c r="I44" s="6">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="J44" s="4" t="s">
         <v>26</v>
@@ -3141,7 +3150,7 @@
       </c>
       <c r="H45" s="3"/>
       <c r="I45" s="6">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="J45" s="4" t="s">
         <v>26</v>
@@ -3180,7 +3189,7 @@
       </c>
       <c r="H46" s="3"/>
       <c r="I46" s="6">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="J46" s="4" t="s">
         <v>26</v>
@@ -3219,7 +3228,7 @@
       </c>
       <c r="H47" s="3"/>
       <c r="I47" s="6">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="J47" s="4" t="s">
         <v>26</v>
@@ -3258,7 +3267,7 @@
       </c>
       <c r="H48" s="3"/>
       <c r="I48" s="6">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="J48" s="4" t="s">
         <v>26</v>
@@ -3297,7 +3306,7 @@
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="6">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="J49" s="4" t="s">
         <v>26</v>
@@ -3336,7 +3345,7 @@
       </c>
       <c r="H50" s="3"/>
       <c r="I50" s="6">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="J50" s="4" t="s">
         <v>26</v>
@@ -3375,7 +3384,7 @@
       </c>
       <c r="H51" s="3"/>
       <c r="I51" s="6">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="J51" s="4" t="s">
         <v>26</v>
@@ -3414,7 +3423,7 @@
       </c>
       <c r="H52" s="3"/>
       <c r="I52" s="6">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="J52" s="4" t="s">
         <v>26</v>
@@ -3453,7 +3462,7 @@
       </c>
       <c r="H53" s="3"/>
       <c r="I53" s="6">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="J53" s="4" t="s">
         <v>26</v>
@@ -3492,7 +3501,7 @@
       </c>
       <c r="H54" s="3"/>
       <c r="I54" s="6">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="J54" s="4"/>
       <c r="K54" s="4" t="s">
@@ -3527,7 +3536,7 @@
       </c>
       <c r="H55" s="3"/>
       <c r="I55" s="6">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="J55" s="4"/>
       <c r="K55" s="4" t="s">
@@ -3562,7 +3571,7 @@
       </c>
       <c r="H56" s="3"/>
       <c r="I56" s="6">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="J56" s="4"/>
       <c r="K56" s="4" t="s">
@@ -3597,7 +3606,7 @@
       </c>
       <c r="H57" s="3"/>
       <c r="I57" s="6">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="J57" s="4"/>
       <c r="K57" s="4" t="s">
@@ -3632,7 +3641,7 @@
       </c>
       <c r="H58" s="3"/>
       <c r="I58" s="6">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="J58" s="4" t="s">
         <v>26</v>
@@ -3671,7 +3680,7 @@
       </c>
       <c r="H59" s="3"/>
       <c r="I59" s="6">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="J59" s="4" t="s">
         <v>26</v>
@@ -3710,7 +3719,7 @@
       </c>
       <c r="H60" s="3"/>
       <c r="I60" s="6">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="J60" s="4" t="s">
         <v>26</v>
@@ -3749,7 +3758,7 @@
       </c>
       <c r="H61" s="3"/>
       <c r="I61" s="6">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="J61" s="4" t="s">
         <v>18</v>
@@ -3788,7 +3797,7 @@
       </c>
       <c r="H62" s="3"/>
       <c r="I62" s="6">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="J62" s="4"/>
       <c r="K62" s="4" t="s">
@@ -3823,7 +3832,7 @@
       </c>
       <c r="H63" s="3"/>
       <c r="I63" s="6">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="J63" s="4"/>
       <c r="K63" s="4" t="s">
@@ -3858,7 +3867,7 @@
       </c>
       <c r="H64" s="3"/>
       <c r="I64" s="6">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="J64" s="4"/>
       <c r="K64" s="4" t="s">
@@ -3893,7 +3902,7 @@
       </c>
       <c r="H65" s="3"/>
       <c r="I65" s="6">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="J65" s="4"/>
       <c r="K65" s="4" t="s">
@@ -3928,7 +3937,7 @@
       </c>
       <c r="H66" s="3"/>
       <c r="I66" s="6">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="J66" s="4" t="s">
         <v>26</v>
@@ -3967,7 +3976,7 @@
       </c>
       <c r="H67" s="3"/>
       <c r="I67" s="6">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="J67" s="4" t="s">
         <v>26</v>
@@ -4006,7 +4015,7 @@
       </c>
       <c r="H68" s="3"/>
       <c r="I68" s="6">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J68" s="4" t="s">
         <v>26</v>
@@ -4045,7 +4054,7 @@
       </c>
       <c r="H69" s="3"/>
       <c r="I69" s="6">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J69" s="4" t="s">
         <v>26</v>
@@ -4084,7 +4093,7 @@
       </c>
       <c r="H70" s="3"/>
       <c r="I70" s="6">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J70" s="4" t="s">
         <v>183</v>
@@ -4123,7 +4132,7 @@
       </c>
       <c r="H71" s="3"/>
       <c r="I71" s="6">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="J71" s="4" t="s">
         <v>26</v>
@@ -4162,7 +4171,7 @@
       </c>
       <c r="H72" s="3"/>
       <c r="I72" s="6">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="J72" s="4" t="s">
         <v>189</v>
@@ -4179,74 +4188,74 @@
     </row>
     <row r="73" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="3">
-        <v>46253</v>
+        <v>46232</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="C73" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="D73" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="D73" s="4" t="s">
-        <v>192</v>
-      </c>
       <c r="E73" s="3">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" s="5">
-        <v>10080</v>
+        <v>9716</v>
       </c>
       <c r="G73" s="5">
-        <v>10080</v>
+        <v>9716</v>
       </c>
       <c r="H73" s="3"/>
       <c r="I73" s="6">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J73" s="4" t="s">
-        <v>189</v>
+        <v>26</v>
       </c>
       <c r="K73" s="4" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="L73" s="4"/>
       <c r="M73" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N73" s="4"/>
       <c r="O73" s="4"/>
     </row>
     <row r="74" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="3">
-        <v>46232</v>
+        <v>46227</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>175</v>
+        <v>193</v>
       </c>
       <c r="D74" s="4" t="s">
         <v>194</v>
       </c>
       <c r="E74" s="3">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" s="5">
-        <v>9716</v>
+        <v>23168.6</v>
       </c>
       <c r="G74" s="5">
-        <v>9716</v>
+        <v>23168.6</v>
       </c>
       <c r="H74" s="3"/>
       <c r="I74" s="6">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J74" s="4" t="s">
-        <v>26</v>
+        <v>189</v>
       </c>
       <c r="K74" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="L74" s="4"/>
       <c r="M74" s="4" t="s">
@@ -4257,29 +4266,29 @@
     </row>
     <row r="75" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="3">
-        <v>46227</v>
+        <v>46234</v>
       </c>
       <c r="B75" s="4" t="s">
         <v>45</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E75" s="3">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" s="5">
-        <v>23168.6</v>
+        <v>4950.17</v>
       </c>
       <c r="G75" s="5">
-        <v>23168.6</v>
+        <v>4950.17</v>
       </c>
       <c r="H75" s="3"/>
       <c r="I75" s="6">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J75" s="4" t="s">
         <v>189</v>
@@ -4289,42 +4298,42 @@
       </c>
       <c r="L75" s="4"/>
       <c r="M75" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N75" s="4"/>
       <c r="O75" s="4"/>
     </row>
     <row r="76" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="3">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>45</v>
+        <v>180</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="D76" s="4" t="s">
         <v>199</v>
       </c>
       <c r="E76" s="3">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="F76" s="5">
-        <v>10666.67</v>
+        <v>7551.88</v>
       </c>
       <c r="G76" s="5">
-        <v>10666.67</v>
+        <v>7551.88</v>
       </c>
       <c r="H76" s="3"/>
       <c r="I76" s="6">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J76" s="4" t="s">
         <v>189</v>
       </c>
       <c r="K76" s="4" t="s">
-        <v>27</v>
+        <v>184</v>
       </c>
       <c r="L76" s="4"/>
       <c r="M76" s="4" t="s">
@@ -4335,29 +4344,29 @@
     </row>
     <row r="77" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="3">
-        <v>46234</v>
+        <v>46244</v>
       </c>
       <c r="B77" s="4" t="s">
         <v>45</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="D77" s="4" t="s">
         <v>201</v>
       </c>
       <c r="E77" s="3">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" s="5">
-        <v>6500</v>
+        <v>4320</v>
       </c>
       <c r="G77" s="5">
-        <v>6500</v>
+        <v>4320</v>
       </c>
       <c r="H77" s="3"/>
       <c r="I77" s="6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J77" s="4" t="s">
         <v>189</v>
@@ -4374,35 +4383,35 @@
     </row>
     <row r="78" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="3">
-        <v>46234</v>
+        <v>46227</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>45</v>
+        <v>180</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="D78" s="4" t="s">
         <v>203</v>
       </c>
       <c r="E78" s="3">
-        <v>46284</v>
+        <v>46287</v>
       </c>
       <c r="F78" s="5">
-        <v>4950.17</v>
+        <v>4216.67</v>
       </c>
       <c r="G78" s="5">
-        <v>4950.17</v>
+        <v>4216.67</v>
       </c>
       <c r="H78" s="3"/>
       <c r="I78" s="6">
         <v>31</v>
       </c>
       <c r="J78" s="4" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="K78" s="4" t="s">
-        <v>27</v>
+        <v>184</v>
       </c>
       <c r="L78" s="4"/>
       <c r="M78" s="4" t="s">
@@ -4413,25 +4422,25 @@
     </row>
     <row r="79" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="3">
-        <v>46225</v>
+        <v>46253</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>180</v>
+        <v>45</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="D79" s="4" t="s">
         <v>205</v>
       </c>
       <c r="E79" s="3">
-        <v>46285</v>
+        <v>46288</v>
       </c>
       <c r="F79" s="5">
-        <v>7551.88</v>
+        <v>10080</v>
       </c>
       <c r="G79" s="5">
-        <v>7551.88</v>
+        <v>10080</v>
       </c>
       <c r="H79" s="3"/>
       <c r="I79" s="6">
@@ -4441,7 +4450,7 @@
         <v>189</v>
       </c>
       <c r="K79" s="4" t="s">
-        <v>184</v>
+        <v>27</v>
       </c>
       <c r="L79" s="4"/>
       <c r="M79" s="4" t="s">
@@ -4452,64 +4461,64 @@
     </row>
     <row r="80" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="3">
-        <v>46244</v>
+        <v>46253</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>45</v>
+        <v>121</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>191</v>
+        <v>207</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E80" s="3">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" s="5">
-        <v>4320</v>
+        <v>3640</v>
       </c>
       <c r="G80" s="5">
-        <v>4320</v>
+        <v>3640</v>
       </c>
       <c r="H80" s="3"/>
       <c r="I80" s="6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J80" s="4" t="s">
         <v>189</v>
       </c>
       <c r="K80" s="4" t="s">
-        <v>27</v>
+        <v>124</v>
       </c>
       <c r="L80" s="4"/>
       <c r="M80" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N80" s="4"/>
       <c r="O80" s="4"/>
     </row>
     <row r="81" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="3">
-        <v>46266</v>
+        <v>46262</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>45</v>
+        <v>210</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>191</v>
+        <v>211</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="E81" s="3">
-        <v>46287</v>
+        <v>46290</v>
       </c>
       <c r="F81" s="5">
-        <v>18600</v>
+        <v>7694.4</v>
       </c>
       <c r="G81" s="5">
-        <v>18600</v>
+        <v>7694.4</v>
       </c>
       <c r="H81" s="3"/>
       <c r="I81" s="6">
@@ -4519,241 +4528,241 @@
         <v>26</v>
       </c>
       <c r="K81" s="4" t="s">
-        <v>27</v>
+        <v>213</v>
       </c>
       <c r="L81" s="4"/>
       <c r="M81" s="4" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="N81" s="4"/>
       <c r="O81" s="4"/>
     </row>
     <row r="82" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3">
-        <v>46227</v>
+        <v>46262</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>181</v>
+        <v>211</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="E82" s="3">
-        <v>46287</v>
+        <v>46290</v>
       </c>
       <c r="F82" s="5">
-        <v>4216.67</v>
+        <v>11660.11</v>
       </c>
       <c r="G82" s="5">
-        <v>4216.67</v>
+        <v>11660.11</v>
       </c>
       <c r="H82" s="3"/>
       <c r="I82" s="6">
         <v>28</v>
       </c>
       <c r="J82" s="4" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="K82" s="4" t="s">
-        <v>184</v>
+        <v>213</v>
       </c>
       <c r="L82" s="4"/>
       <c r="M82" s="4" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="N82" s="4"/>
       <c r="O82" s="4"/>
     </row>
     <row r="83" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="3">
-        <v>46253</v>
+        <v>46232</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>45</v>
+        <v>180</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>191</v>
+        <v>217</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="E83" s="3">
-        <v>46288</v>
+        <v>46292</v>
       </c>
       <c r="F83" s="5">
-        <v>10080</v>
+        <v>4082.05</v>
       </c>
       <c r="G83" s="5">
-        <v>10080</v>
+        <v>4082.05</v>
       </c>
       <c r="H83" s="3"/>
       <c r="I83" s="6">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J83" s="4" t="s">
         <v>189</v>
       </c>
       <c r="K83" s="4" t="s">
-        <v>27</v>
+        <v>184</v>
       </c>
       <c r="L83" s="4"/>
       <c r="M83" s="4" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="N83" s="4"/>
       <c r="O83" s="4"/>
     </row>
     <row r="84" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="3">
-        <v>46253</v>
+        <v>46232</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>121</v>
+        <v>15</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>215</v>
+        <v>175</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="E84" s="3">
-        <v>46288</v>
+        <v>46292</v>
       </c>
       <c r="F84" s="5">
-        <v>3640</v>
+        <v>9716</v>
       </c>
       <c r="G84" s="5">
-        <v>3640</v>
+        <v>9716</v>
       </c>
       <c r="H84" s="3"/>
       <c r="I84" s="6">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J84" s="4" t="s">
-        <v>189</v>
+        <v>26</v>
       </c>
       <c r="K84" s="4" t="s">
-        <v>124</v>
+        <v>39</v>
       </c>
       <c r="L84" s="4"/>
       <c r="M84" s="4" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="N84" s="4"/>
       <c r="O84" s="4"/>
     </row>
     <row r="85" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="3">
-        <v>46253</v>
+        <v>46244</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>121</v>
+        <v>45</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>215</v>
+        <v>193</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E85" s="3">
-        <v>46288</v>
+        <v>46293</v>
       </c>
       <c r="F85" s="5">
-        <v>1660.33</v>
+        <v>4320</v>
       </c>
       <c r="G85" s="5">
-        <v>1660.33</v>
+        <v>4320</v>
       </c>
       <c r="H85" s="3"/>
       <c r="I85" s="6">
+        <v>25</v>
+      </c>
+      <c r="J85" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="K85" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="J85" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K85" s="4" t="s">
-        <v>124</v>
       </c>
       <c r="L85" s="4"/>
       <c r="M85" s="4" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="N85" s="4"/>
       <c r="O85" s="4"/>
     </row>
     <row r="86" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="3">
-        <v>46259</v>
+        <v>46223</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>220</v>
+        <v>196</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="E86" s="3">
-        <v>46289</v>
+        <v>46293</v>
       </c>
       <c r="F86" s="5">
-        <v>6265</v>
+        <v>11200</v>
       </c>
       <c r="G86" s="5">
-        <v>6265</v>
+        <v>11200</v>
       </c>
       <c r="H86" s="3"/>
       <c r="I86" s="6">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J86" s="4" t="s">
         <v>189</v>
       </c>
       <c r="K86" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="L86" s="4"/>
       <c r="M86" s="4" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="N86" s="4"/>
       <c r="O86" s="4"/>
     </row>
     <row r="87" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="3">
-        <v>46262</v>
+        <v>46266</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>223</v>
+        <v>45</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>224</v>
+        <v>193</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E87" s="3">
-        <v>46290</v>
+        <v>46294</v>
       </c>
       <c r="F87" s="5">
-        <v>7694.4</v>
+        <v>18600</v>
       </c>
       <c r="G87" s="5">
-        <v>7694.4</v>
+        <v>18600</v>
       </c>
       <c r="H87" s="3"/>
       <c r="I87" s="6">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J87" s="4" t="s">
         <v>26</v>
       </c>
       <c r="K87" s="4" t="s">
-        <v>226</v>
+        <v>27</v>
       </c>
       <c r="L87" s="4"/>
       <c r="M87" s="4" t="s">
@@ -4764,35 +4773,35 @@
     </row>
     <row r="88" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="3">
-        <v>46262</v>
+        <v>46234</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>223</v>
+        <v>180</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>224</v>
+        <v>181</v>
       </c>
       <c r="D88" s="4" t="s">
         <v>228</v>
       </c>
       <c r="E88" s="3">
-        <v>46290</v>
+        <v>46294</v>
       </c>
       <c r="F88" s="5">
-        <v>11660.11</v>
+        <v>3789.09</v>
       </c>
       <c r="G88" s="5">
-        <v>11660.11</v>
+        <v>3789.09</v>
       </c>
       <c r="H88" s="3"/>
       <c r="I88" s="6">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J88" s="4" t="s">
         <v>189</v>
       </c>
       <c r="K88" s="4" t="s">
-        <v>226</v>
+        <v>184</v>
       </c>
       <c r="L88" s="4"/>
       <c r="M88" s="4" t="s">
@@ -4803,25 +4812,25 @@
     </row>
     <row r="89" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="3">
-        <v>46232</v>
+        <v>46253</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>180</v>
+        <v>45</v>
       </c>
       <c r="C89" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="D89" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="D89" s="4" t="s">
-        <v>231</v>
-      </c>
       <c r="E89" s="3">
-        <v>46292</v>
+        <v>46295</v>
       </c>
       <c r="F89" s="5">
-        <v>4082.05</v>
+        <v>10080</v>
       </c>
       <c r="G89" s="5">
-        <v>4082.05</v>
+        <v>10080</v>
       </c>
       <c r="H89" s="3"/>
       <c r="I89" s="6">
@@ -4831,46 +4840,46 @@
         <v>189</v>
       </c>
       <c r="K89" s="4" t="s">
-        <v>184</v>
+        <v>27</v>
       </c>
       <c r="L89" s="4"/>
       <c r="M89" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="N89" s="4"/>
       <c r="O89" s="4"/>
     </row>
     <row r="90" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="3">
-        <v>46232</v>
+        <v>46253</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>15</v>
+        <v>168</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>175</v>
+        <v>232</v>
       </c>
       <c r="D90" s="4" t="s">
         <v>233</v>
       </c>
       <c r="E90" s="3">
-        <v>46292</v>
+        <v>46295</v>
       </c>
       <c r="F90" s="5">
-        <v>9716</v>
+        <v>2051.2199999999998</v>
       </c>
       <c r="G90" s="5">
-        <v>9716</v>
+        <v>2051.2199999999998</v>
       </c>
       <c r="H90" s="3"/>
       <c r="I90" s="6">
         <v>23</v>
       </c>
       <c r="J90" s="4" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="K90" s="4" t="s">
-        <v>39</v>
+        <v>171</v>
       </c>
       <c r="L90" s="4"/>
       <c r="M90" s="4" t="s">
@@ -4881,35 +4890,35 @@
     </row>
     <row r="91" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="3">
-        <v>46244</v>
+        <v>46262</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>45</v>
+        <v>210</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>191</v>
+        <v>211</v>
       </c>
       <c r="D91" s="4" t="s">
         <v>235</v>
       </c>
       <c r="E91" s="3">
-        <v>46293</v>
+        <v>46297</v>
       </c>
       <c r="F91" s="5">
-        <v>4320</v>
+        <v>7694.4</v>
       </c>
       <c r="G91" s="5">
-        <v>4320</v>
+        <v>7694.4</v>
       </c>
       <c r="H91" s="3"/>
       <c r="I91" s="6">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J91" s="4" t="s">
-        <v>189</v>
+        <v>26</v>
       </c>
       <c r="K91" s="4" t="s">
-        <v>27</v>
+        <v>213</v>
       </c>
       <c r="L91" s="4"/>
       <c r="M91" s="4" t="s">
@@ -4920,35 +4929,35 @@
     </row>
     <row r="92" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="3">
-        <v>46223</v>
+        <v>46262</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>15</v>
+        <v>210</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="D92" s="4" t="s">
         <v>237</v>
       </c>
       <c r="E92" s="3">
-        <v>46293</v>
+        <v>46297</v>
       </c>
       <c r="F92" s="5">
-        <v>6265</v>
+        <v>11660.11</v>
       </c>
       <c r="G92" s="5">
-        <v>6265</v>
+        <v>11660.11</v>
       </c>
       <c r="H92" s="3"/>
       <c r="I92" s="6">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J92" s="4" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="K92" s="4" t="s">
-        <v>19</v>
+        <v>213</v>
       </c>
       <c r="L92" s="4"/>
       <c r="M92" s="4" t="s">
@@ -4959,35 +4968,35 @@
     </row>
     <row r="93" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="3">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>45</v>
+        <v>180</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="D93" s="4" t="s">
         <v>239</v>
       </c>
       <c r="E93" s="3">
-        <v>46293</v>
+        <v>46300</v>
       </c>
       <c r="F93" s="5">
-        <v>11200</v>
+        <v>7551.88</v>
       </c>
       <c r="G93" s="5">
-        <v>11200</v>
+        <v>7551.88</v>
       </c>
       <c r="H93" s="3"/>
       <c r="I93" s="6">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J93" s="4" t="s">
         <v>189</v>
       </c>
       <c r="K93" s="4" t="s">
-        <v>27</v>
+        <v>184</v>
       </c>
       <c r="L93" s="4"/>
       <c r="M93" s="4" t="s">
@@ -4998,35 +5007,35 @@
     </row>
     <row r="94" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="3">
-        <v>46234</v>
+        <v>46266</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>180</v>
+        <v>45</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="D94" s="4" t="s">
         <v>241</v>
       </c>
       <c r="E94" s="3">
-        <v>46294</v>
+        <v>46301</v>
       </c>
       <c r="F94" s="5">
-        <v>3789.09</v>
+        <v>18600</v>
       </c>
       <c r="G94" s="5">
-        <v>3789.09</v>
+        <v>18600</v>
       </c>
       <c r="H94" s="3"/>
       <c r="I94" s="6">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J94" s="4" t="s">
-        <v>189</v>
+        <v>26</v>
       </c>
       <c r="K94" s="4" t="s">
-        <v>184</v>
+        <v>27</v>
       </c>
       <c r="L94" s="4"/>
       <c r="M94" s="4" t="s">
@@ -5037,32 +5046,32 @@
     </row>
     <row r="95" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="3">
-        <v>46266</v>
+        <v>46253</v>
       </c>
       <c r="B95" s="4" t="s">
         <v>45</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D95" s="4" t="s">
         <v>243</v>
       </c>
       <c r="E95" s="3">
-        <v>46294</v>
+        <v>46302</v>
       </c>
       <c r="F95" s="5">
-        <v>18600</v>
+        <v>10080</v>
       </c>
       <c r="G95" s="5">
-        <v>18600</v>
+        <v>10080</v>
       </c>
       <c r="H95" s="3"/>
       <c r="I95" s="6">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J95" s="4" t="s">
-        <v>26</v>
+        <v>189</v>
       </c>
       <c r="K95" s="4" t="s">
         <v>27</v>
@@ -5076,35 +5085,35 @@
     </row>
     <row r="96" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="3">
-        <v>46253</v>
+        <v>46227</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>45</v>
+        <v>180</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="D96" s="4" t="s">
         <v>245</v>
       </c>
       <c r="E96" s="3">
-        <v>46295</v>
+        <v>46302</v>
       </c>
       <c r="F96" s="5">
-        <v>10080</v>
+        <v>4216.66</v>
       </c>
       <c r="G96" s="5">
-        <v>10080</v>
+        <v>4216.66</v>
       </c>
       <c r="H96" s="3"/>
       <c r="I96" s="6">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J96" s="4" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="K96" s="4" t="s">
-        <v>27</v>
+        <v>184</v>
       </c>
       <c r="L96" s="4"/>
       <c r="M96" s="4" t="s">
@@ -5115,39 +5124,39 @@
     </row>
     <row r="97" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="3">
-        <v>46253</v>
+        <v>46232</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>168</v>
+        <v>15</v>
       </c>
       <c r="C97" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="D97" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="D97" s="4" t="s">
-        <v>248</v>
-      </c>
       <c r="E97" s="3">
-        <v>46295</v>
+        <v>46302</v>
       </c>
       <c r="F97" s="5">
-        <v>2051.2199999999998</v>
+        <v>9716</v>
       </c>
       <c r="G97" s="5">
-        <v>2051.2199999999998</v>
+        <v>9716</v>
       </c>
       <c r="H97" s="3"/>
       <c r="I97" s="6">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J97" s="4" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="K97" s="4" t="s">
-        <v>171</v>
+        <v>39</v>
       </c>
       <c r="L97" s="4"/>
       <c r="M97" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="N97" s="4"/>
       <c r="O97" s="4"/>
@@ -5157,36 +5166,36 @@
         <v>46262</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E98" s="3">
-        <v>46297</v>
+        <v>46304</v>
       </c>
       <c r="F98" s="5">
-        <v>11660.11</v>
+        <v>7694.4</v>
       </c>
       <c r="G98" s="5">
-        <v>11660.11</v>
+        <v>7694.4</v>
       </c>
       <c r="H98" s="3"/>
       <c r="I98" s="6">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J98" s="4" t="s">
-        <v>189</v>
+        <v>26</v>
       </c>
       <c r="K98" s="4" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="L98" s="4"/>
       <c r="M98" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="N98" s="4"/>
       <c r="O98" s="4"/>
@@ -5196,71 +5205,71 @@
         <v>46262</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E99" s="3">
-        <v>46297</v>
+        <v>46304</v>
       </c>
       <c r="F99" s="5">
-        <v>7694.4</v>
+        <v>11660.11</v>
       </c>
       <c r="G99" s="5">
-        <v>7694.4</v>
+        <v>11660.11</v>
       </c>
       <c r="H99" s="3"/>
       <c r="I99" s="6">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J99" s="4" t="s">
-        <v>26</v>
+        <v>189</v>
       </c>
       <c r="K99" s="4" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="L99" s="4"/>
       <c r="M99" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="N99" s="4"/>
       <c r="O99" s="4"/>
     </row>
     <row r="100" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="3">
-        <v>46225</v>
+        <v>46265</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>180</v>
+        <v>135</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>181</v>
+        <v>253</v>
       </c>
       <c r="D100" s="4" t="s">
         <v>254</v>
       </c>
       <c r="E100" s="3">
-        <v>46300</v>
+        <v>46305</v>
       </c>
       <c r="F100" s="5">
-        <v>7551.88</v>
+        <v>4750</v>
       </c>
       <c r="G100" s="5">
-        <v>7551.88</v>
+        <v>4750</v>
       </c>
       <c r="H100" s="3"/>
       <c r="I100" s="6">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J100" s="4" t="s">
         <v>189</v>
       </c>
       <c r="K100" s="4" t="s">
-        <v>184</v>
+        <v>54</v>
       </c>
       <c r="L100" s="4"/>
       <c r="M100" s="4" t="s">
@@ -5271,35 +5280,35 @@
     </row>
     <row r="101" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="3">
-        <v>46266</v>
+        <v>46232</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>45</v>
+        <v>180</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>191</v>
+        <v>217</v>
       </c>
       <c r="D101" s="4" t="s">
         <v>256</v>
       </c>
       <c r="E101" s="3">
-        <v>46301</v>
+        <v>46307</v>
       </c>
       <c r="F101" s="5">
-        <v>18600</v>
+        <v>4082.04</v>
       </c>
       <c r="G101" s="5">
-        <v>18600</v>
+        <v>4082.04</v>
       </c>
       <c r="H101" s="3"/>
       <c r="I101" s="6">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J101" s="4" t="s">
-        <v>26</v>
+        <v>189</v>
       </c>
       <c r="K101" s="4" t="s">
-        <v>27</v>
+        <v>184</v>
       </c>
       <c r="L101" s="4"/>
       <c r="M101" s="4" t="s">
@@ -5310,35 +5319,35 @@
     </row>
     <row r="102" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="3">
-        <v>46227</v>
+        <v>46266</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>180</v>
+        <v>45</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="D102" s="4" t="s">
         <v>258</v>
       </c>
       <c r="E102" s="3">
-        <v>46302</v>
+        <v>46308</v>
       </c>
       <c r="F102" s="5">
-        <v>4216.66</v>
+        <v>18600</v>
       </c>
       <c r="G102" s="5">
-        <v>4216.66</v>
+        <v>18600</v>
       </c>
       <c r="H102" s="3"/>
       <c r="I102" s="6">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J102" s="4" t="s">
-        <v>183</v>
+        <v>26</v>
       </c>
       <c r="K102" s="4" t="s">
-        <v>184</v>
+        <v>27</v>
       </c>
       <c r="L102" s="4"/>
       <c r="M102" s="4" t="s">
@@ -5349,78 +5358,78 @@
     </row>
     <row r="103" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="3">
-        <v>46232</v>
+        <v>46248</v>
       </c>
       <c r="B103" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>175</v>
+        <v>260</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E103" s="3">
-        <v>46302</v>
+        <v>46308</v>
       </c>
       <c r="F103" s="5">
-        <v>9716</v>
+        <v>23355.33</v>
       </c>
       <c r="G103" s="5">
-        <v>9716</v>
+        <v>23355.33</v>
       </c>
       <c r="H103" s="3"/>
       <c r="I103" s="6">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J103" s="4" t="s">
-        <v>26</v>
+        <v>189</v>
       </c>
       <c r="K103" s="4" t="s">
         <v>39</v>
       </c>
       <c r="L103" s="4"/>
       <c r="M103" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N103" s="4"/>
       <c r="O103" s="4"/>
     </row>
     <row r="104" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="3">
-        <v>46253</v>
+        <v>46234</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>45</v>
+        <v>180</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E104" s="3">
-        <v>46302</v>
+        <v>46309</v>
       </c>
       <c r="F104" s="5">
-        <v>10080</v>
+        <v>3789.1</v>
       </c>
       <c r="G104" s="5">
-        <v>10080</v>
+        <v>3789.1</v>
       </c>
       <c r="H104" s="3"/>
       <c r="I104" s="6">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J104" s="4" t="s">
         <v>189</v>
       </c>
       <c r="K104" s="4" t="s">
-        <v>27</v>
+        <v>184</v>
       </c>
       <c r="L104" s="4"/>
       <c r="M104" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="N104" s="4"/>
       <c r="O104" s="4"/>
@@ -5433,13 +5442,13 @@
         <v>23</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E105" s="3">
-        <v>46303</v>
+        <v>46310</v>
       </c>
       <c r="F105" s="5">
         <v>2754</v>
@@ -5449,7 +5458,7 @@
       </c>
       <c r="H105" s="3"/>
       <c r="I105" s="6">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J105" s="4" t="s">
         <v>183</v>
@@ -5459,46 +5468,46 @@
       </c>
       <c r="L105" s="4"/>
       <c r="M105" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N105" s="4"/>
       <c r="O105" s="4"/>
     </row>
     <row r="106" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="3">
-        <v>46259</v>
+        <v>46258</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>15</v>
+        <v>135</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>220</v>
+        <v>253</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E106" s="3">
-        <v>46304</v>
+        <v>46311</v>
       </c>
       <c r="F106" s="5">
-        <v>6265</v>
+        <v>6247.5</v>
       </c>
       <c r="G106" s="5">
-        <v>6265</v>
+        <v>11266.12</v>
       </c>
       <c r="H106" s="3"/>
       <c r="I106" s="6">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J106" s="4" t="s">
         <v>189</v>
       </c>
       <c r="K106" s="4" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="L106" s="4"/>
       <c r="M106" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N106" s="4"/>
       <c r="O106" s="4"/>
@@ -5508,16 +5517,16 @@
         <v>46262</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E107" s="3">
-        <v>46304</v>
+        <v>46311</v>
       </c>
       <c r="F107" s="5">
         <v>7694.4</v>
@@ -5527,17 +5536,17 @@
       </c>
       <c r="H107" s="3"/>
       <c r="I107" s="6">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J107" s="4" t="s">
         <v>26</v>
       </c>
       <c r="K107" s="4" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="L107" s="4"/>
       <c r="M107" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N107" s="4"/>
       <c r="O107" s="4"/>
@@ -5547,16 +5556,16 @@
         <v>46262</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E108" s="3">
-        <v>46304</v>
+        <v>46311</v>
       </c>
       <c r="F108" s="5">
         <v>11660.11</v>
@@ -5566,46 +5575,46 @@
       </c>
       <c r="H108" s="3"/>
       <c r="I108" s="6">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J108" s="4" t="s">
         <v>189</v>
       </c>
       <c r="K108" s="4" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="L108" s="4"/>
       <c r="M108" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N108" s="4"/>
       <c r="O108" s="4"/>
     </row>
     <row r="109" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="3">
-        <v>46265</v>
+        <v>46258</v>
       </c>
       <c r="B109" s="4" t="s">
         <v>135</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>273</v>
+        <v>253</v>
       </c>
       <c r="D109" s="4" t="s">
         <v>274</v>
       </c>
       <c r="E109" s="3">
-        <v>46305</v>
+        <v>46313</v>
       </c>
       <c r="F109" s="5">
-        <v>4750</v>
+        <v>6247.5</v>
       </c>
       <c r="G109" s="5">
-        <v>4750</v>
+        <v>6247.5</v>
       </c>
       <c r="H109" s="3"/>
       <c r="I109" s="6">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J109" s="4" t="s">
         <v>189</v>
@@ -5622,549 +5631,432 @@
     </row>
     <row r="110" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="3">
-        <v>46265</v>
+        <v>46286</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>23</v>
+        <v>168</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E110" s="3">
-        <v>46307</v>
+        <v>46314</v>
       </c>
       <c r="F110" s="5">
-        <v>1664</v>
+        <v>5475.86</v>
       </c>
       <c r="G110" s="5">
-        <v>1664</v>
+        <v>5475.86</v>
       </c>
       <c r="H110" s="3"/>
       <c r="I110" s="6">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J110" s="4" t="s">
-        <v>18</v>
+        <v>189</v>
       </c>
       <c r="K110" s="4" t="s">
-        <v>71</v>
+        <v>171</v>
       </c>
       <c r="L110" s="4"/>
       <c r="M110" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N110" s="4"/>
       <c r="O110" s="4"/>
     </row>
     <row r="111" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="3">
-        <v>46232</v>
+        <v>46265</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>180</v>
+        <v>135</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>230</v>
+        <v>253</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E111" s="3">
-        <v>46307</v>
+        <v>46315</v>
       </c>
       <c r="F111" s="5">
-        <v>4082.04</v>
+        <v>4750</v>
       </c>
       <c r="G111" s="5">
-        <v>4082.04</v>
+        <v>4750</v>
       </c>
       <c r="H111" s="3"/>
       <c r="I111" s="6">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J111" s="4" t="s">
         <v>189</v>
       </c>
       <c r="K111" s="4" t="s">
-        <v>184</v>
+        <v>54</v>
       </c>
       <c r="L111" s="4"/>
       <c r="M111" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N111" s="4"/>
       <c r="O111" s="4"/>
     </row>
     <row r="112" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="3">
-        <v>46266</v>
+        <v>46280</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>191</v>
+        <v>281</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E112" s="3">
-        <v>46308</v>
+        <v>46315</v>
       </c>
       <c r="F112" s="5">
-        <v>18600</v>
+        <v>9196.5</v>
       </c>
       <c r="G112" s="5">
-        <v>18600</v>
+        <v>12695.59</v>
       </c>
       <c r="H112" s="3"/>
       <c r="I112" s="6">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J112" s="4" t="s">
-        <v>26</v>
+        <v>189</v>
       </c>
       <c r="K112" s="4" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="L112" s="4"/>
       <c r="M112" s="4" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="N112" s="4"/>
       <c r="O112" s="4"/>
     </row>
     <row r="113" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="3">
-        <v>46248</v>
+        <v>46287</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>15</v>
+        <v>168</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E113" s="3">
-        <v>46308</v>
+        <v>46315</v>
       </c>
       <c r="F113" s="5">
-        <v>23355.33</v>
+        <v>4466.2700000000004</v>
       </c>
       <c r="G113" s="5">
-        <v>23355.33</v>
+        <v>4466.2700000000004</v>
       </c>
       <c r="H113" s="3"/>
       <c r="I113" s="6">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J113" s="4" t="s">
         <v>189</v>
       </c>
       <c r="K113" s="4" t="s">
-        <v>39</v>
+        <v>171</v>
       </c>
       <c r="L113" s="4"/>
       <c r="M113" s="4" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="N113" s="4"/>
       <c r="O113" s="4"/>
     </row>
     <row r="114" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="3">
-        <v>46234</v>
+        <v>46280</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>180</v>
+        <v>45</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>181</v>
+        <v>287</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E114" s="3">
-        <v>46309</v>
+        <v>46315</v>
       </c>
       <c r="F114" s="5">
-        <v>3789.1</v>
+        <v>1600</v>
       </c>
       <c r="G114" s="5">
-        <v>3789.1</v>
+        <v>1600</v>
       </c>
       <c r="H114" s="3"/>
       <c r="I114" s="6">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J114" s="4" t="s">
         <v>189</v>
       </c>
       <c r="K114" s="4" t="s">
-        <v>184</v>
+        <v>75</v>
       </c>
       <c r="L114" s="4"/>
       <c r="M114" s="4" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="N114" s="4"/>
       <c r="O114" s="4"/>
     </row>
     <row r="115" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="3">
-        <v>46265</v>
+        <v>46287</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>15</v>
+        <v>68</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="E115" s="3">
-        <v>46310</v>
+        <v>46315</v>
       </c>
       <c r="F115" s="5">
-        <v>8947.5</v>
+        <v>784.63</v>
       </c>
       <c r="G115" s="5">
-        <v>8947.5</v>
+        <v>979.25</v>
       </c>
       <c r="H115" s="3"/>
       <c r="I115" s="6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J115" s="4" t="s">
-        <v>189</v>
+        <v>18</v>
       </c>
       <c r="K115" s="4" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="L115" s="4"/>
       <c r="M115" s="4" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="N115" s="4"/>
       <c r="O115" s="4"/>
     </row>
     <row r="116" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="3">
-        <v>46268</v>
+        <v>46266</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>264</v>
+        <v>193</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E116" s="3">
-        <v>46310</v>
+        <v>46315</v>
       </c>
       <c r="F116" s="5">
-        <v>2754</v>
+        <v>18600</v>
       </c>
       <c r="G116" s="5">
-        <v>2754</v>
+        <v>18600</v>
       </c>
       <c r="H116" s="3"/>
       <c r="I116" s="6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J116" s="4" t="s">
-        <v>183</v>
+        <v>26</v>
       </c>
       <c r="K116" s="4" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="L116" s="4"/>
       <c r="M116" s="4" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="N116" s="4"/>
       <c r="O116" s="4"/>
     </row>
     <row r="117" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="3">
-        <v>46258</v>
+        <v>46253</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>135</v>
+        <v>168</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>273</v>
+        <v>295</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="E117" s="3">
-        <v>46311</v>
+        <v>46316</v>
       </c>
       <c r="F117" s="5">
-        <v>6247.5</v>
+        <v>1452.6</v>
       </c>
       <c r="G117" s="5">
-        <v>11266.12</v>
+        <v>1452.6</v>
       </c>
       <c r="H117" s="3"/>
       <c r="I117" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J117" s="4" t="s">
-        <v>189</v>
+        <v>18</v>
       </c>
       <c r="K117" s="4" t="s">
-        <v>54</v>
+        <v>171</v>
       </c>
       <c r="L117" s="4"/>
       <c r="M117" s="4" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="N117" s="4"/>
       <c r="O117" s="4"/>
     </row>
     <row r="118" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="3">
-        <v>46262</v>
+        <v>46288</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>223</v>
+        <v>168</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>224</v>
+        <v>298</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="E118" s="3">
-        <v>46311</v>
+        <v>46316</v>
       </c>
       <c r="F118" s="5">
-        <v>11660.11</v>
+        <v>4772.8999999999996</v>
       </c>
       <c r="G118" s="5">
-        <v>11660.11</v>
+        <v>4772.8999999999996</v>
       </c>
       <c r="H118" s="3"/>
       <c r="I118" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J118" s="4" t="s">
         <v>189</v>
       </c>
       <c r="K118" s="4" t="s">
-        <v>226</v>
+        <v>300</v>
       </c>
       <c r="L118" s="4"/>
       <c r="M118" s="4" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="N118" s="4"/>
       <c r="O118" s="4"/>
     </row>
     <row r="119" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="3">
-        <v>46262</v>
+        <v>46288</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>223</v>
+        <v>23</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>224</v>
+        <v>265</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="E119" s="3">
-        <v>46311</v>
+        <v>46316</v>
       </c>
       <c r="F119" s="5">
-        <v>7694.4</v>
+        <v>2334.2399999999998</v>
       </c>
       <c r="G119" s="5">
-        <v>7694.4</v>
+        <v>2334.2399999999998</v>
       </c>
       <c r="H119" s="3"/>
       <c r="I119" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J119" s="4" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="K119" s="4" t="s">
-        <v>226</v>
+        <v>71</v>
       </c>
       <c r="L119" s="4"/>
       <c r="M119" s="4" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="N119" s="4"/>
       <c r="O119" s="4"/>
     </row>
     <row r="120" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="3">
-        <v>46252</v>
+        <v>46287</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>23</v>
+        <v>304</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>166</v>
+        <v>305</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="E120" s="3">
-        <v>46312</v>
+        <v>46317</v>
       </c>
       <c r="F120" s="5">
-        <v>3809.52</v>
+        <v>9617.7999999999993</v>
       </c>
       <c r="G120" s="5">
-        <v>3809.52</v>
+        <v>9617.7999999999993</v>
       </c>
       <c r="H120" s="3"/>
       <c r="I120" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J120" s="4" t="s">
         <v>189</v>
       </c>
       <c r="K120" s="4" t="s">
-        <v>71</v>
+        <v>307</v>
       </c>
       <c r="L120" s="4"/>
       <c r="M120" s="4" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="N120" s="4"/>
       <c r="O120" s="4"/>
-    </row>
-    <row r="121" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="3">
-        <v>46253</v>
-      </c>
-      <c r="B121" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C121" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="D121" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="E121" s="3">
-        <v>46313</v>
-      </c>
-      <c r="F121" s="5">
-        <v>1172.1600000000001</v>
-      </c>
-      <c r="G121" s="5">
-        <v>1172.1600000000001</v>
-      </c>
-      <c r="H121" s="3"/>
-      <c r="I121" s="6">
-        <v>2</v>
-      </c>
-      <c r="J121" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="K121" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="L121" s="4"/>
-      <c r="M121" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="N121" s="4"/>
-      <c r="O121" s="4"/>
-    </row>
-    <row r="122" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="3">
-        <v>46258</v>
-      </c>
-      <c r="B122" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="C122" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="D122" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="E122" s="3">
-        <v>46313</v>
-      </c>
-      <c r="F122" s="5">
-        <v>6247.5</v>
-      </c>
-      <c r="G122" s="5">
-        <v>6247.5</v>
-      </c>
-      <c r="H122" s="3"/>
-      <c r="I122" s="6">
-        <v>2</v>
-      </c>
-      <c r="J122" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="K122" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="L122" s="4"/>
-      <c r="M122" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="N122" s="4"/>
-      <c r="O122" s="4"/>
-    </row>
-    <row r="123" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="3">
-        <v>46286</v>
-      </c>
-      <c r="B123" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="C123" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="D123" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="E123" s="3">
-        <v>46314</v>
-      </c>
-      <c r="F123" s="5">
-        <v>5475.86</v>
-      </c>
-      <c r="G123" s="5">
-        <v>5475.86</v>
-      </c>
-      <c r="H123" s="3"/>
-      <c r="I123" s="6">
-        <v>1</v>
-      </c>
-      <c r="J123" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="K123" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="L123" s="4"/>
-      <c r="M123" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="N123" s="4"/>
-      <c r="O123" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
+++ b/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
@@ -1,31 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WINDOWS\Desktop\dados planilhas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{743BB8CC-36A9-4B6F-91E1-7BC592DDEE05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView activeTab="0" showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true"/>
   </bookViews>
   <sheets>
     <sheet name="XLS_Grid_LANCAMENTO A RECEBER" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <calcPr refMode="A1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="323">
   <si>
     <t>Dt.Emissão</t>
   </si>
@@ -705,18 +693,18 @@
     <t>70798158300011200000001121205064100656763896</t>
   </si>
   <si>
+    <t>01007023.2</t>
+  </si>
+  <si>
+    <t>70791158400003789090001121205064100656764423</t>
+  </si>
+  <si>
     <t>01007301.2</t>
   </si>
   <si>
     <t>00197158400018600000000003473568000003161417</t>
   </si>
   <si>
-    <t>01007023.2</t>
-  </si>
-  <si>
-    <t>70791158400003789090001121205064100656764423</t>
-  </si>
-  <si>
     <t>01007187.4</t>
   </si>
   <si>
@@ -732,18 +720,18 @@
     <t>34196158500002051221090002617698120992717000</t>
   </si>
   <si>
+    <t>01007249.2</t>
+  </si>
+  <si>
+    <t>70792158700011660110001121205064100656766923</t>
+  </si>
+  <si>
     <t>01007265.2</t>
   </si>
   <si>
     <t>00192158700007694400000003473568000003158917</t>
   </si>
   <si>
-    <t>01007249.2</t>
-  </si>
-  <si>
-    <t>70792158700011660110001121205064100656766923</t>
-  </si>
-  <si>
     <t>01006920.3</t>
   </si>
   <si>
@@ -756,24 +744,24 @@
     <t>00191159100018600000000003473568000003161517</t>
   </si>
   <si>
+    <t>01006976.3</t>
+  </si>
+  <si>
+    <t>23792159200004216660435090000000114800304920</t>
+  </si>
+  <si>
+    <t>01007005.5</t>
+  </si>
+  <si>
+    <t>00198159200009716000000003473568000003146217</t>
+  </si>
+  <si>
     <t>01007187.5</t>
   </si>
   <si>
     <t>70791159200010080000001121205064100656766220</t>
   </si>
   <si>
-    <t>01006976.3</t>
-  </si>
-  <si>
-    <t>23792159200004216660435090000000114800304920</t>
-  </si>
-  <si>
-    <t>01007005.5</t>
-  </si>
-  <si>
-    <t>00198159200009716000000003473568000003146217</t>
-  </si>
-  <si>
     <t>01007265.3</t>
   </si>
   <si>
@@ -801,21 +789,21 @@
     <t>70796159700004082040001121205064100656764209</t>
   </si>
   <si>
+    <t>ASPEN SERVICE COMERCIO LTDA</t>
+  </si>
+  <si>
+    <t>01007117.2</t>
+  </si>
+  <si>
+    <t>70793159800023355330001121205064100656765677</t>
+  </si>
+  <si>
     <t>01007301.4</t>
   </si>
   <si>
     <t>00196159800018600000000003473568000003161617</t>
   </si>
   <si>
-    <t>ASPEN SERVICE COMERCIO LTDA</t>
-  </si>
-  <si>
-    <t>01007117.2</t>
-  </si>
-  <si>
-    <t>70793159800023355330001121205064100656765677</t>
-  </si>
-  <si>
     <t>01007023.3</t>
   </si>
   <si>
@@ -837,18 +825,18 @@
     <t>70798160100011266120001121205064100656766576</t>
   </si>
   <si>
+    <t>01007249.4</t>
+  </si>
+  <si>
+    <t>70791160100011660110001121205064100656766949</t>
+  </si>
+  <si>
     <t>01007265.4</t>
   </si>
   <si>
     <t>00191160100007694400000003473568000003159117</t>
   </si>
   <si>
-    <t>01007249.4</t>
-  </si>
-  <si>
-    <t>70791160100011660110001121205064100656766949</t>
-  </si>
-  <si>
     <t>01007222.2</t>
   </si>
   <si>
@@ -952,35 +940,78 @@
   </si>
   <si>
     <t>70794160700009617800001121205064100656768895</t>
+  </si>
+  <si>
+    <t>01007224.5</t>
+  </si>
+  <si>
+    <t>70791160800002992000001121205064100656766899</t>
+  </si>
+  <si>
+    <t>SP HOSPITALAR LTDA</t>
+  </si>
+  <si>
+    <t>01007427.1</t>
+  </si>
+  <si>
+    <t>70796160800010139150001121205064100656769265</t>
+  </si>
+  <si>
+    <t>RC DISTRIBUIDORA FARMA E HOSPITALAR LTDA</t>
+  </si>
+  <si>
+    <t>01007319.3</t>
+  </si>
+  <si>
+    <t>70797160800003714540001121205064100656767541</t>
+  </si>
+  <si>
+    <t>01007265.5</t>
+  </si>
+  <si>
+    <t>00196160800007694400000003473568000003159217</t>
+  </si>
+  <si>
+    <t>01007249.5</t>
+  </si>
+  <si>
+    <t>70791160800011660110001121205064100656766956</t>
+  </si>
+  <si>
+    <t>01007217.3</t>
+  </si>
+  <si>
+    <t>23793160800000879120435090000000125900304920</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="###,###,##0.00"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt formatCode="dd/MM/yyyy" numFmtId="164"/>
+    <numFmt formatCode="###,###,##0.00" numFmtId="165"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
       <charset val="1"/>
     </font>
     <font>
+      <color rgb="FF000000"/>
       <sz val="8"/>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
       <charset val="1"/>
     </font>
     <font>
+      <color rgb="FF000000"/>
       <sz val="8"/>
-      <color rgb="FF000000"/>
       <name val="Segoe UI"/>
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -999,8 +1030,14 @@
         <bgColor rgb="FF7EA6D1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0F0F0"/>
+        <bgColor rgb="FFF0F0F0"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1023,386 +1060,124 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFA0A0A0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFA0A0A0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFA0A0A0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFA0A0A0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFA0A0A0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFA0A0A0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFA0A0A0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFA0A0A0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+  <cellXfs count="11">
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" shrinkToFit="false" wrapText="false"/>
+      <protection hidden="false" locked="true"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="164" xfId="0">
+      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="165" xfId="0">
+      <alignment horizontal="right" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0">
+      <alignment horizontal="right" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="2" fillId="4" fontId="1" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="3" fillId="4" fontId="1" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="4" fontId="1" numFmtId="165" xfId="0">
+      <alignment horizontal="right" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="4" fillId="4" fontId="1" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-  </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="0E2841"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="156082"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="E97132"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="196B24"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="A02B93"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="4EA72E"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="467886"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="96607D"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O120"/>
-  <sheetFormatPr defaultColWidth="12.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="true" summaryRight="true"/>
+  </sheetPr>
+  <dimension ref="A1:O127"/>
+  <sheetFormatPr defaultColWidth="12.140625" customHeight="true" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.28515625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="30.28515625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="24.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="27.28515625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="28.140625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="9.140625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="26.28515625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="3.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="43.42578125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="60.5703125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="26.28515625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="43.42578125" style="1" customWidth="1"/>
-    <col min="16" max="16384" width="12.140625" style="1"/>
+    <col max="1" min="1" style="1" width="11.85546875" customWidth="true"/>
+    <col max="2" min="2" style="1" width="22.28515625" customWidth="true"/>
+    <col max="3" min="3" style="1" width="30.28515625" customWidth="true"/>
+    <col max="4" min="4" style="1" width="12.85546875" customWidth="true"/>
+    <col max="5" min="5" style="1" width="24.7109375" customWidth="true"/>
+    <col max="6" min="6" style="1" width="9.140625" customWidth="true"/>
+    <col max="7" min="7" style="1" width="27.28515625" customWidth="true"/>
+    <col max="8" min="8" style="1" width="28.140625" customWidth="true"/>
+    <col max="9" min="9" style="1" width="9.140625" customWidth="true"/>
+    <col max="10" min="10" style="1" width="26.28515625" customWidth="true"/>
+    <col max="11" min="11" style="1" width="3.7109375" customWidth="true"/>
+    <col max="12" min="12" style="1" width="43.42578125" customWidth="true"/>
+    <col max="13" min="13" style="1" width="60.5703125" customWidth="true"/>
+    <col max="14" min="14" style="1" width="26.28515625" customWidth="true"/>
+    <col max="15" min="15" style="1" width="43.42578125" customWidth="true"/>
+    <col max="16384" min="16" style="1" width="12.140625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" customHeight="true" ht="27" customFormat="true" s="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1449,8 +1224,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
+    <row r="2" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A2" s="3" t="n">
         <v>45296</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -1462,18 +1237,18 @@
       <c r="D2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="3" t="n">
         <v>45326</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2" s="5" t="n">
         <v>5418</v>
       </c>
-      <c r="G2" s="5">
-        <v>9391.7800000000007</v>
+      <c r="G2" s="5" t="n">
+        <v>9391.78</v>
       </c>
       <c r="H2" s="3"/>
-      <c r="I2" s="6">
-        <v>992</v>
+      <c r="I2" s="6" t="n">
+        <v>995</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>18</v>
@@ -1488,8 +1263,8 @@
       <c r="N2" s="4"/>
       <c r="O2" s="4"/>
     </row>
-    <row r="3" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3">
+    <row r="3" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A3" s="3" t="n">
         <v>45296</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -1501,18 +1276,18 @@
       <c r="D3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="3" t="n">
         <v>45346</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3" s="5" t="n">
         <v>5418</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="5" t="n">
         <v>5418</v>
       </c>
       <c r="H3" s="3"/>
-      <c r="I3" s="6">
-        <v>972</v>
+      <c r="I3" s="6" t="n">
+        <v>975</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>18</v>
@@ -1527,8 +1302,8 @@
       <c r="N3" s="4"/>
       <c r="O3" s="4"/>
     </row>
-    <row r="4" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
+    <row r="4" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A4" s="3" t="n">
         <v>45322</v>
       </c>
       <c r="B4" s="4" t="s">
@@ -1540,18 +1315,18 @@
       <c r="D4" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="3" t="n">
         <v>45350</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="5" t="n">
         <v>816</v>
       </c>
-      <c r="G4" s="5">
-        <v>1264.8699999999999</v>
+      <c r="G4" s="5" t="n">
+        <v>1264.87</v>
       </c>
       <c r="H4" s="3"/>
-      <c r="I4" s="6">
-        <v>968</v>
+      <c r="I4" s="6" t="n">
+        <v>971</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>26</v>
@@ -1566,8 +1341,8 @@
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
     </row>
-    <row r="5" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3">
+    <row r="5" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A5" s="3" t="n">
         <v>45296</v>
       </c>
       <c r="B5" s="4" t="s">
@@ -1579,18 +1354,18 @@
       <c r="D5" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="3" t="n">
         <v>45356</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="5" t="n">
         <v>5418</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="5" t="n">
         <v>5418</v>
       </c>
       <c r="H5" s="3"/>
-      <c r="I5" s="6">
-        <v>962</v>
+      <c r="I5" s="6" t="n">
+        <v>965</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>18</v>
@@ -1605,8 +1380,8 @@
       <c r="N5" s="4"/>
       <c r="O5" s="4"/>
     </row>
-    <row r="6" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3">
+    <row r="6" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A6" s="3" t="n">
         <v>45306</v>
       </c>
       <c r="B6" s="4" t="s">
@@ -1618,18 +1393,18 @@
       <c r="D6" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="3" t="n">
         <v>45362</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="5" t="n">
         <v>384</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="5" t="n">
         <v>384</v>
       </c>
       <c r="H6" s="3"/>
-      <c r="I6" s="6">
-        <v>956</v>
+      <c r="I6" s="6" t="n">
+        <v>959</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>26</v>
@@ -1644,8 +1419,8 @@
       <c r="N6" s="4"/>
       <c r="O6" s="4"/>
     </row>
-    <row r="7" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3">
+    <row r="7" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A7" s="3" t="n">
         <v>45322</v>
       </c>
       <c r="B7" s="4" t="s">
@@ -1657,18 +1432,18 @@
       <c r="D7" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="3" t="n">
         <v>45364</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="5" t="n">
         <v>816</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="5" t="n">
         <v>816</v>
       </c>
       <c r="H7" s="3"/>
-      <c r="I7" s="6">
-        <v>954</v>
+      <c r="I7" s="6" t="n">
+        <v>957</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>26</v>
@@ -1683,8 +1458,8 @@
       <c r="N7" s="4"/>
       <c r="O7" s="4"/>
     </row>
-    <row r="8" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3">
+    <row r="8" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A8" s="3" t="n">
         <v>45322</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -1696,18 +1471,18 @@
       <c r="D8" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="3" t="n">
         <v>45378</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8" s="5" t="n">
         <v>816</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G8" s="5" t="n">
         <v>816</v>
       </c>
       <c r="H8" s="3"/>
-      <c r="I8" s="6">
-        <v>940</v>
+      <c r="I8" s="6" t="n">
+        <v>943</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>26</v>
@@ -1722,8 +1497,8 @@
       <c r="N8" s="4"/>
       <c r="O8" s="4"/>
     </row>
-    <row r="9" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3">
+    <row r="9" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A9" s="3" t="n">
         <v>45433</v>
       </c>
       <c r="B9" s="4" t="s">
@@ -1735,18 +1510,18 @@
       <c r="D9" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="3" t="n">
         <v>45463</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9" s="5" t="n">
         <v>873.6</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G9" s="5" t="n">
         <v>1674.52</v>
       </c>
       <c r="H9" s="3"/>
-      <c r="I9" s="6">
-        <v>855</v>
+      <c r="I9" s="6" t="n">
+        <v>858</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>18</v>
@@ -1761,8 +1536,8 @@
       <c r="N9" s="4"/>
       <c r="O9" s="4"/>
     </row>
-    <row r="10" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3">
+    <row r="10" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A10" s="3" t="n">
         <v>45433</v>
       </c>
       <c r="B10" s="4" t="s">
@@ -1774,18 +1549,18 @@
       <c r="D10" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="3" t="n">
         <v>45493</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10" s="5" t="n">
         <v>873.6</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G10" s="5" t="n">
         <v>873.6</v>
       </c>
       <c r="H10" s="3"/>
-      <c r="I10" s="6">
-        <v>825</v>
+      <c r="I10" s="6" t="n">
+        <v>828</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>18</v>
@@ -1800,8 +1575,8 @@
       <c r="N10" s="4"/>
       <c r="O10" s="4"/>
     </row>
-    <row r="11" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="3">
+    <row r="11" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A11" s="3" t="n">
         <v>45433</v>
       </c>
       <c r="B11" s="4" t="s">
@@ -1813,18 +1588,18 @@
       <c r="D11" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="3" t="n">
         <v>45523</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F11" s="5" t="n">
         <v>873.6</v>
       </c>
-      <c r="G11" s="5">
+      <c r="G11" s="5" t="n">
         <v>873.6</v>
       </c>
       <c r="H11" s="3"/>
-      <c r="I11" s="6">
-        <v>795</v>
+      <c r="I11" s="6" t="n">
+        <v>798</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>18</v>
@@ -1839,8 +1614,8 @@
       <c r="N11" s="4"/>
       <c r="O11" s="4"/>
     </row>
-    <row r="12" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="3">
+    <row r="12" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A12" s="3" t="n">
         <v>45558</v>
       </c>
       <c r="B12" s="4" t="s">
@@ -1852,18 +1627,18 @@
       <c r="D12" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="3" t="n">
         <v>45600</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="5" t="n">
         <v>2000</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G12" s="5" t="n">
         <v>2000</v>
       </c>
       <c r="H12" s="3"/>
-      <c r="I12" s="6">
-        <v>718</v>
+      <c r="I12" s="6" t="n">
+        <v>721</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>18</v>
@@ -1878,8 +1653,8 @@
       <c r="N12" s="4"/>
       <c r="O12" s="4"/>
     </row>
-    <row r="13" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="3">
+    <row r="13" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A13" s="3" t="n">
         <v>45558</v>
       </c>
       <c r="B13" s="4" t="s">
@@ -1891,18 +1666,18 @@
       <c r="D13" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="3" t="n">
         <v>45607</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F13" s="5" t="n">
         <v>2000</v>
       </c>
-      <c r="G13" s="5">
+      <c r="G13" s="5" t="n">
         <v>3204.34</v>
       </c>
       <c r="H13" s="3"/>
-      <c r="I13" s="6">
-        <v>711</v>
+      <c r="I13" s="6" t="n">
+        <v>714</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>18</v>
@@ -1917,8 +1692,8 @@
       <c r="N13" s="4"/>
       <c r="O13" s="4"/>
     </row>
-    <row r="14" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3">
+    <row r="14" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A14" s="3" t="n">
         <v>45552</v>
       </c>
       <c r="B14" s="4" t="s">
@@ -1930,18 +1705,18 @@
       <c r="D14" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="n">
         <v>45608</v>
       </c>
-      <c r="F14" s="5">
-        <v>4439.8999999999996</v>
-      </c>
-      <c r="G14" s="5">
-        <v>4439.8999999999996</v>
+      <c r="F14" s="5" t="n">
+        <v>4439.9</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>4439.9</v>
       </c>
       <c r="H14" s="3"/>
-      <c r="I14" s="6">
-        <v>710</v>
+      <c r="I14" s="6" t="n">
+        <v>713</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>18</v>
@@ -1956,8 +1731,8 @@
       <c r="N14" s="4"/>
       <c r="O14" s="4"/>
     </row>
-    <row r="15" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3">
+    <row r="15" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A15" s="3" t="n">
         <v>45558</v>
       </c>
       <c r="B15" s="4" t="s">
@@ -1969,18 +1744,18 @@
       <c r="D15" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="3" t="n">
         <v>45614</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15" s="5" t="n">
         <v>2000</v>
       </c>
-      <c r="G15" s="5">
+      <c r="G15" s="5" t="n">
         <v>2000</v>
       </c>
       <c r="H15" s="3"/>
-      <c r="I15" s="6">
-        <v>704</v>
+      <c r="I15" s="6" t="n">
+        <v>707</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>18</v>
@@ -1995,8 +1770,8 @@
       <c r="N15" s="4"/>
       <c r="O15" s="4"/>
     </row>
-    <row r="16" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="3">
+    <row r="16" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A16" s="3" t="n">
         <v>45546</v>
       </c>
       <c r="B16" s="4" t="s">
@@ -2008,18 +1783,18 @@
       <c r="D16" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E16" s="3">
+      <c r="E16" s="3" t="n">
         <v>45615</v>
       </c>
-      <c r="F16" s="5">
-        <v>1216.8599999999999</v>
-      </c>
-      <c r="G16" s="5">
-        <v>1216.8599999999999</v>
+      <c r="F16" s="5" t="n">
+        <v>1216.86</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>1216.86</v>
       </c>
       <c r="H16" s="3"/>
-      <c r="I16" s="6">
-        <v>703</v>
+      <c r="I16" s="6" t="n">
+        <v>706</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>18</v>
@@ -2034,8 +1809,8 @@
       <c r="N16" s="4"/>
       <c r="O16" s="4"/>
     </row>
-    <row r="17" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="3">
+    <row r="17" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A17" s="3" t="n">
         <v>45548</v>
       </c>
       <c r="B17" s="4" t="s">
@@ -2047,18 +1822,18 @@
       <c r="D17" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E17" s="3">
+      <c r="E17" s="3" t="n">
         <v>45617</v>
       </c>
-      <c r="F17" s="5">
+      <c r="F17" s="5" t="n">
         <v>1843.87</v>
       </c>
-      <c r="G17" s="5">
+      <c r="G17" s="5" t="n">
         <v>1843.87</v>
       </c>
       <c r="H17" s="3"/>
-      <c r="I17" s="6">
-        <v>701</v>
+      <c r="I17" s="6" t="n">
+        <v>704</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>18</v>
@@ -2073,8 +1848,8 @@
       <c r="N17" s="4"/>
       <c r="O17" s="4"/>
     </row>
-    <row r="18" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="3">
+    <row r="18" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A18" s="3" t="n">
         <v>45546</v>
       </c>
       <c r="B18" s="4" t="s">
@@ -2086,18 +1861,18 @@
       <c r="D18" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18" s="3" t="n">
         <v>45622</v>
       </c>
-      <c r="F18" s="5">
-        <v>1216.8599999999999</v>
-      </c>
-      <c r="G18" s="5">
-        <v>1216.8599999999999</v>
+      <c r="F18" s="5" t="n">
+        <v>1216.86</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>1216.86</v>
       </c>
       <c r="H18" s="3"/>
-      <c r="I18" s="6">
-        <v>696</v>
+      <c r="I18" s="6" t="n">
+        <v>699</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>18</v>
@@ -2112,8 +1887,8 @@
       <c r="N18" s="4"/>
       <c r="O18" s="4"/>
     </row>
-    <row r="19" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="3">
+    <row r="19" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A19" s="3" t="n">
         <v>45552</v>
       </c>
       <c r="B19" s="4" t="s">
@@ -2125,18 +1900,18 @@
       <c r="D19" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="E19" s="3">
+      <c r="E19" s="3" t="n">
         <v>45622</v>
       </c>
-      <c r="F19" s="5">
-        <v>4439.8999999999996</v>
-      </c>
-      <c r="G19" s="5">
-        <v>4439.8999999999996</v>
+      <c r="F19" s="5" t="n">
+        <v>4439.9</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>4439.9</v>
       </c>
       <c r="H19" s="3"/>
-      <c r="I19" s="6">
-        <v>696</v>
+      <c r="I19" s="6" t="n">
+        <v>699</v>
       </c>
       <c r="J19" s="4" t="s">
         <v>18</v>
@@ -2151,8 +1926,8 @@
       <c r="N19" s="4"/>
       <c r="O19" s="4"/>
     </row>
-    <row r="20" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="3">
+    <row r="20" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A20" s="3" t="n">
         <v>45548</v>
       </c>
       <c r="B20" s="4" t="s">
@@ -2164,18 +1939,18 @@
       <c r="D20" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="3" t="n">
         <v>45624</v>
       </c>
-      <c r="F20" s="5">
+      <c r="F20" s="5" t="n">
         <v>1843.88</v>
       </c>
-      <c r="G20" s="5">
+      <c r="G20" s="5" t="n">
         <v>1843.88</v>
       </c>
       <c r="H20" s="3"/>
-      <c r="I20" s="6">
-        <v>694</v>
+      <c r="I20" s="6" t="n">
+        <v>697</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>18</v>
@@ -2190,8 +1965,8 @@
       <c r="N20" s="4"/>
       <c r="O20" s="4"/>
     </row>
-    <row r="21" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="3">
+    <row r="21" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A21" s="3" t="n">
         <v>45632</v>
       </c>
       <c r="B21" s="4" t="s">
@@ -2203,18 +1978,18 @@
       <c r="D21" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E21" s="3">
+      <c r="E21" s="3" t="n">
         <v>45688</v>
       </c>
-      <c r="F21" s="5">
-        <v>1118.4000000000001</v>
-      </c>
-      <c r="G21" s="5">
-        <v>1118.4000000000001</v>
+      <c r="F21" s="5" t="n">
+        <v>1118.4</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>1118.4</v>
       </c>
       <c r="H21" s="3"/>
-      <c r="I21" s="6">
-        <v>630</v>
+      <c r="I21" s="6" t="n">
+        <v>633</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>18</v>
@@ -2229,8 +2004,8 @@
       <c r="N21" s="4"/>
       <c r="O21" s="4"/>
     </row>
-    <row r="22" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="3">
+    <row r="22" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A22" s="3" t="n">
         <v>45646</v>
       </c>
       <c r="B22" s="4" t="s">
@@ -2242,18 +2017,18 @@
       <c r="D22" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="E22" s="3">
+      <c r="E22" s="3" t="n">
         <v>45695</v>
       </c>
-      <c r="F22" s="5">
+      <c r="F22" s="5" t="n">
         <v>3296.8</v>
       </c>
-      <c r="G22" s="5">
+      <c r="G22" s="5" t="n">
         <v>3296.8</v>
       </c>
       <c r="H22" s="3"/>
-      <c r="I22" s="6">
-        <v>623</v>
+      <c r="I22" s="6" t="n">
+        <v>626</v>
       </c>
       <c r="J22" s="4" t="s">
         <v>18</v>
@@ -2268,8 +2043,8 @@
       <c r="N22" s="4"/>
       <c r="O22" s="4"/>
     </row>
-    <row r="23" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="3">
+    <row r="23" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A23" s="3" t="n">
         <v>45636</v>
       </c>
       <c r="B23" s="4" t="s">
@@ -2281,18 +2056,18 @@
       <c r="D23" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="E23" s="3">
+      <c r="E23" s="3" t="n">
         <v>45699</v>
       </c>
-      <c r="F23" s="5">
+      <c r="F23" s="5" t="n">
         <v>2330</v>
       </c>
-      <c r="G23" s="5">
+      <c r="G23" s="5" t="n">
         <v>2330</v>
       </c>
       <c r="H23" s="3"/>
-      <c r="I23" s="6">
-        <v>619</v>
+      <c r="I23" s="6" t="n">
+        <v>622</v>
       </c>
       <c r="J23" s="4" t="s">
         <v>18</v>
@@ -2307,8 +2082,8 @@
       <c r="N23" s="4"/>
       <c r="O23" s="4"/>
     </row>
-    <row r="24" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="3">
+    <row r="24" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A24" s="3" t="n">
         <v>45646</v>
       </c>
       <c r="B24" s="4" t="s">
@@ -2320,18 +2095,18 @@
       <c r="D24" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="E24" s="3">
+      <c r="E24" s="3" t="n">
         <v>45702</v>
       </c>
-      <c r="F24" s="5">
+      <c r="F24" s="5" t="n">
         <v>3296.8</v>
       </c>
-      <c r="G24" s="5">
+      <c r="G24" s="5" t="n">
         <v>3296.8</v>
       </c>
       <c r="H24" s="3"/>
-      <c r="I24" s="6">
-        <v>616</v>
+      <c r="I24" s="6" t="n">
+        <v>619</v>
       </c>
       <c r="J24" s="4" t="s">
         <v>18</v>
@@ -2346,8 +2121,8 @@
       <c r="N24" s="4"/>
       <c r="O24" s="4"/>
     </row>
-    <row r="25" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="3">
+    <row r="25" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A25" s="3" t="n">
         <v>45677</v>
       </c>
       <c r="B25" s="4" t="s">
@@ -2359,18 +2134,18 @@
       <c r="D25" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="E25" s="3">
+      <c r="E25" s="3" t="n">
         <v>45705</v>
       </c>
-      <c r="F25" s="5">
+      <c r="F25" s="5" t="n">
         <v>2541</v>
       </c>
-      <c r="G25" s="5">
+      <c r="G25" s="5" t="n">
         <v>2541</v>
       </c>
       <c r="H25" s="3"/>
-      <c r="I25" s="6">
-        <v>613</v>
+      <c r="I25" s="6" t="n">
+        <v>616</v>
       </c>
       <c r="J25" s="4" t="s">
         <v>26</v>
@@ -2385,8 +2160,8 @@
       <c r="N25" s="4"/>
       <c r="O25" s="4"/>
     </row>
-    <row r="26" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="3">
+    <row r="26" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A26" s="3" t="n">
         <v>45646</v>
       </c>
       <c r="B26" s="4" t="s">
@@ -2398,18 +2173,18 @@
       <c r="D26" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="E26" s="3">
+      <c r="E26" s="3" t="n">
         <v>45709</v>
       </c>
-      <c r="F26" s="5">
+      <c r="F26" s="5" t="n">
         <v>3296.8</v>
       </c>
-      <c r="G26" s="5">
+      <c r="G26" s="5" t="n">
         <v>3296.8</v>
       </c>
       <c r="H26" s="3"/>
-      <c r="I26" s="6">
-        <v>609</v>
+      <c r="I26" s="6" t="n">
+        <v>612</v>
       </c>
       <c r="J26" s="4" t="s">
         <v>18</v>
@@ -2424,8 +2199,8 @@
       <c r="N26" s="4"/>
       <c r="O26" s="4"/>
     </row>
-    <row r="27" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="3">
+    <row r="27" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A27" s="3" t="n">
         <v>45677</v>
       </c>
       <c r="B27" s="4" t="s">
@@ -2437,18 +2212,18 @@
       <c r="D27" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="E27" s="3">
+      <c r="E27" s="3" t="n">
         <v>45712</v>
       </c>
-      <c r="F27" s="5">
+      <c r="F27" s="5" t="n">
         <v>2541</v>
       </c>
-      <c r="G27" s="5">
+      <c r="G27" s="5" t="n">
         <v>2541</v>
       </c>
       <c r="H27" s="3"/>
-      <c r="I27" s="6">
-        <v>606</v>
+      <c r="I27" s="6" t="n">
+        <v>609</v>
       </c>
       <c r="J27" s="4" t="s">
         <v>26</v>
@@ -2463,8 +2238,8 @@
       <c r="N27" s="4"/>
       <c r="O27" s="4"/>
     </row>
-    <row r="28" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="3">
+    <row r="28" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A28" s="3" t="n">
         <v>45677</v>
       </c>
       <c r="B28" s="4" t="s">
@@ -2476,18 +2251,18 @@
       <c r="D28" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="E28" s="3">
+      <c r="E28" s="3" t="n">
         <v>45726</v>
       </c>
-      <c r="F28" s="5">
+      <c r="F28" s="5" t="n">
         <v>2541</v>
       </c>
-      <c r="G28" s="5">
+      <c r="G28" s="5" t="n">
         <v>2541</v>
       </c>
       <c r="H28" s="3"/>
-      <c r="I28" s="6">
-        <v>592</v>
+      <c r="I28" s="6" t="n">
+        <v>595</v>
       </c>
       <c r="J28" s="4" t="s">
         <v>26</v>
@@ -2502,8 +2277,8 @@
       <c r="N28" s="4"/>
       <c r="O28" s="4"/>
     </row>
-    <row r="29" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="3">
+    <row r="29" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A29" s="3" t="n">
         <v>45699</v>
       </c>
       <c r="B29" s="4" t="s">
@@ -2515,18 +2290,18 @@
       <c r="D29" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="E29" s="3">
+      <c r="E29" s="3" t="n">
         <v>45727</v>
       </c>
-      <c r="F29" s="5">
+      <c r="F29" s="5" t="n">
         <v>7562.78</v>
       </c>
-      <c r="G29" s="5">
+      <c r="G29" s="5" t="n">
         <v>7562.78</v>
       </c>
       <c r="H29" s="3"/>
-      <c r="I29" s="6">
-        <v>591</v>
+      <c r="I29" s="6" t="n">
+        <v>594</v>
       </c>
       <c r="J29" s="4" t="s">
         <v>18</v>
@@ -2541,8 +2316,8 @@
       <c r="N29" s="4"/>
       <c r="O29" s="4"/>
     </row>
-    <row r="30" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="3">
+    <row r="30" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A30" s="3" t="n">
         <v>45699</v>
       </c>
       <c r="B30" s="4" t="s">
@@ -2554,18 +2329,18 @@
       <c r="D30" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="E30" s="3">
+      <c r="E30" s="3" t="n">
         <v>45734</v>
       </c>
-      <c r="F30" s="5">
+      <c r="F30" s="5" t="n">
         <v>7562.78</v>
       </c>
-      <c r="G30" s="5">
+      <c r="G30" s="5" t="n">
         <v>7562.78</v>
       </c>
       <c r="H30" s="3"/>
-      <c r="I30" s="6">
-        <v>584</v>
+      <c r="I30" s="6" t="n">
+        <v>587</v>
       </c>
       <c r="J30" s="4" t="s">
         <v>18</v>
@@ -2580,8 +2355,8 @@
       <c r="N30" s="4"/>
       <c r="O30" s="4"/>
     </row>
-    <row r="31" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="3">
+    <row r="31" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A31" s="3" t="n">
         <v>45699</v>
       </c>
       <c r="B31" s="4" t="s">
@@ -2593,18 +2368,18 @@
       <c r="D31" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="E31" s="3">
+      <c r="E31" s="3" t="n">
         <v>45734</v>
       </c>
-      <c r="F31" s="5">
+      <c r="F31" s="5" t="n">
         <v>1154.56</v>
       </c>
-      <c r="G31" s="5">
+      <c r="G31" s="5" t="n">
         <v>1154.56</v>
       </c>
       <c r="H31" s="3"/>
-      <c r="I31" s="6">
-        <v>584</v>
+      <c r="I31" s="6" t="n">
+        <v>587</v>
       </c>
       <c r="J31" s="4" t="s">
         <v>18</v>
@@ -2619,8 +2394,8 @@
       <c r="N31" s="4"/>
       <c r="O31" s="4"/>
     </row>
-    <row r="32" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="3">
+    <row r="32" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A32" s="3" t="n">
         <v>45677</v>
       </c>
       <c r="B32" s="4" t="s">
@@ -2632,18 +2407,18 @@
       <c r="D32" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="E32" s="3">
+      <c r="E32" s="3" t="n">
         <v>45740</v>
       </c>
-      <c r="F32" s="5">
+      <c r="F32" s="5" t="n">
         <v>2541</v>
       </c>
-      <c r="G32" s="5">
+      <c r="G32" s="5" t="n">
         <v>2541</v>
       </c>
       <c r="H32" s="3"/>
-      <c r="I32" s="6">
-        <v>578</v>
+      <c r="I32" s="6" t="n">
+        <v>581</v>
       </c>
       <c r="J32" s="4" t="s">
         <v>26</v>
@@ -2658,8 +2433,8 @@
       <c r="N32" s="4"/>
       <c r="O32" s="4"/>
     </row>
-    <row r="33" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="3">
+    <row r="33" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A33" s="3" t="n">
         <v>45699</v>
       </c>
       <c r="B33" s="4" t="s">
@@ -2671,18 +2446,18 @@
       <c r="D33" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="E33" s="3">
+      <c r="E33" s="3" t="n">
         <v>45741</v>
       </c>
-      <c r="F33" s="5">
+      <c r="F33" s="5" t="n">
         <v>7562.78</v>
       </c>
-      <c r="G33" s="5">
+      <c r="G33" s="5" t="n">
         <v>7562.78</v>
       </c>
       <c r="H33" s="3"/>
-      <c r="I33" s="6">
-        <v>577</v>
+      <c r="I33" s="6" t="n">
+        <v>580</v>
       </c>
       <c r="J33" s="4" t="s">
         <v>18</v>
@@ -2697,8 +2472,8 @@
       <c r="N33" s="4"/>
       <c r="O33" s="4"/>
     </row>
-    <row r="34" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="3">
+    <row r="34" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A34" s="3" t="n">
         <v>45699</v>
       </c>
       <c r="B34" s="4" t="s">
@@ -2710,18 +2485,18 @@
       <c r="D34" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="E34" s="3">
+      <c r="E34" s="3" t="n">
         <v>45741</v>
       </c>
-      <c r="F34" s="5">
+      <c r="F34" s="5" t="n">
         <v>1154.56</v>
       </c>
-      <c r="G34" s="5">
+      <c r="G34" s="5" t="n">
         <v>1154.56</v>
       </c>
       <c r="H34" s="3"/>
-      <c r="I34" s="6">
-        <v>577</v>
+      <c r="I34" s="6" t="n">
+        <v>580</v>
       </c>
       <c r="J34" s="4" t="s">
         <v>18</v>
@@ -2736,8 +2511,8 @@
       <c r="N34" s="4"/>
       <c r="O34" s="4"/>
     </row>
-    <row r="35" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="3">
+    <row r="35" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A35" s="3" t="n">
         <v>45699</v>
       </c>
       <c r="B35" s="4" t="s">
@@ -2749,18 +2524,18 @@
       <c r="D35" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="E35" s="3">
+      <c r="E35" s="3" t="n">
         <v>45748</v>
       </c>
-      <c r="F35" s="5">
+      <c r="F35" s="5" t="n">
         <v>1154.56</v>
       </c>
-      <c r="G35" s="5">
+      <c r="G35" s="5" t="n">
         <v>1154.56</v>
       </c>
       <c r="H35" s="3"/>
-      <c r="I35" s="6">
-        <v>570</v>
+      <c r="I35" s="6" t="n">
+        <v>573</v>
       </c>
       <c r="J35" s="4" t="s">
         <v>18</v>
@@ -2775,8 +2550,8 @@
       <c r="N35" s="4"/>
       <c r="O35" s="4"/>
     </row>
-    <row r="36" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="3">
+    <row r="36" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A36" s="3" t="n">
         <v>45699</v>
       </c>
       <c r="B36" s="4" t="s">
@@ -2788,18 +2563,18 @@
       <c r="D36" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E36" s="3">
+      <c r="E36" s="3" t="n">
         <v>45748</v>
       </c>
-      <c r="F36" s="5">
+      <c r="F36" s="5" t="n">
         <v>7562.76</v>
       </c>
-      <c r="G36" s="5">
+      <c r="G36" s="5" t="n">
         <v>7562.76</v>
       </c>
       <c r="H36" s="3"/>
-      <c r="I36" s="6">
-        <v>570</v>
+      <c r="I36" s="6" t="n">
+        <v>573</v>
       </c>
       <c r="J36" s="4" t="s">
         <v>18</v>
@@ -2814,8 +2589,8 @@
       <c r="N36" s="4"/>
       <c r="O36" s="4"/>
     </row>
-    <row r="37" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="3">
+    <row r="37" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A37" s="3" t="n">
         <v>45699</v>
       </c>
       <c r="B37" s="4" t="s">
@@ -2827,18 +2602,18 @@
       <c r="D37" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="E37" s="3">
+      <c r="E37" s="3" t="n">
         <v>45755</v>
       </c>
-      <c r="F37" s="5">
+      <c r="F37" s="5" t="n">
         <v>1154.56</v>
       </c>
-      <c r="G37" s="5">
+      <c r="G37" s="5" t="n">
         <v>1154.56</v>
       </c>
       <c r="H37" s="3"/>
-      <c r="I37" s="6">
-        <v>563</v>
+      <c r="I37" s="6" t="n">
+        <v>566</v>
       </c>
       <c r="J37" s="4" t="s">
         <v>18</v>
@@ -2853,8 +2628,8 @@
       <c r="N37" s="4"/>
       <c r="O37" s="4"/>
     </row>
-    <row r="38" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="3">
+    <row r="38" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A38" s="3" t="n">
         <v>45733</v>
       </c>
       <c r="B38" s="4" t="s">
@@ -2866,18 +2641,18 @@
       <c r="D38" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="E38" s="3">
+      <c r="E38" s="3" t="n">
         <v>45761</v>
       </c>
-      <c r="F38" s="5">
+      <c r="F38" s="5" t="n">
         <v>3850</v>
       </c>
-      <c r="G38" s="5">
+      <c r="G38" s="5" t="n">
         <v>6169.53</v>
       </c>
       <c r="H38" s="3"/>
-      <c r="I38" s="6">
-        <v>557</v>
+      <c r="I38" s="6" t="n">
+        <v>560</v>
       </c>
       <c r="J38" s="4" t="s">
         <v>18</v>
@@ -2892,8 +2667,8 @@
       <c r="N38" s="4"/>
       <c r="O38" s="4"/>
     </row>
-    <row r="39" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="3">
+    <row r="39" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A39" s="3" t="n">
         <v>45733</v>
       </c>
       <c r="B39" s="4" t="s">
@@ -2905,18 +2680,18 @@
       <c r="D39" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="E39" s="3">
+      <c r="E39" s="3" t="n">
         <v>45768</v>
       </c>
-      <c r="F39" s="5">
+      <c r="F39" s="5" t="n">
         <v>3850</v>
       </c>
-      <c r="G39" s="5">
+      <c r="G39" s="5" t="n">
         <v>3850</v>
       </c>
       <c r="H39" s="3"/>
-      <c r="I39" s="6">
-        <v>550</v>
+      <c r="I39" s="6" t="n">
+        <v>553</v>
       </c>
       <c r="J39" s="4" t="s">
         <v>18</v>
@@ -2931,8 +2706,8 @@
       <c r="N39" s="4"/>
       <c r="O39" s="4"/>
     </row>
-    <row r="40" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="3">
+    <row r="40" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A40" s="3" t="n">
         <v>45733</v>
       </c>
       <c r="B40" s="4" t="s">
@@ -2944,18 +2719,18 @@
       <c r="D40" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="E40" s="3">
+      <c r="E40" s="3" t="n">
         <v>45775</v>
       </c>
-      <c r="F40" s="5">
+      <c r="F40" s="5" t="n">
         <v>3850</v>
       </c>
-      <c r="G40" s="5">
+      <c r="G40" s="5" t="n">
         <v>3850</v>
       </c>
       <c r="H40" s="3"/>
-      <c r="I40" s="6">
-        <v>543</v>
+      <c r="I40" s="6" t="n">
+        <v>546</v>
       </c>
       <c r="J40" s="4" t="s">
         <v>18</v>
@@ -2970,8 +2745,8 @@
       <c r="N40" s="4"/>
       <c r="O40" s="4"/>
     </row>
-    <row r="41" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="3">
+    <row r="41" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A41" s="3" t="n">
         <v>45747</v>
       </c>
       <c r="B41" s="4" t="s">
@@ -2983,18 +2758,18 @@
       <c r="D41" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="E41" s="3">
+      <c r="E41" s="3" t="n">
         <v>45775</v>
       </c>
-      <c r="F41" s="5">
+      <c r="F41" s="5" t="n">
         <v>3800</v>
       </c>
-      <c r="G41" s="5">
+      <c r="G41" s="5" t="n">
         <v>6089.41</v>
       </c>
       <c r="H41" s="3"/>
-      <c r="I41" s="6">
-        <v>543</v>
+      <c r="I41" s="6" t="n">
+        <v>546</v>
       </c>
       <c r="J41" s="4" t="s">
         <v>18</v>
@@ -3009,8 +2784,8 @@
       <c r="N41" s="4"/>
       <c r="O41" s="4"/>
     </row>
-    <row r="42" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="3">
+    <row r="42" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A42" s="3" t="n">
         <v>45747</v>
       </c>
       <c r="B42" s="4" t="s">
@@ -3022,18 +2797,18 @@
       <c r="D42" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="E42" s="3">
+      <c r="E42" s="3" t="n">
         <v>45782</v>
       </c>
-      <c r="F42" s="5">
+      <c r="F42" s="5" t="n">
         <v>3800</v>
       </c>
-      <c r="G42" s="5">
+      <c r="G42" s="5" t="n">
         <v>3800</v>
       </c>
       <c r="H42" s="3"/>
-      <c r="I42" s="6">
-        <v>536</v>
+      <c r="I42" s="6" t="n">
+        <v>539</v>
       </c>
       <c r="J42" s="4" t="s">
         <v>18</v>
@@ -3048,8 +2823,8 @@
       <c r="N42" s="4"/>
       <c r="O42" s="4"/>
     </row>
-    <row r="43" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="3">
+    <row r="43" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A43" s="3" t="n">
         <v>45747</v>
       </c>
       <c r="B43" s="4" t="s">
@@ -3061,18 +2836,18 @@
       <c r="D43" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="E43" s="3">
+      <c r="E43" s="3" t="n">
         <v>45789</v>
       </c>
-      <c r="F43" s="5">
+      <c r="F43" s="5" t="n">
         <v>3800</v>
       </c>
-      <c r="G43" s="5">
+      <c r="G43" s="5" t="n">
         <v>3800</v>
       </c>
       <c r="H43" s="3"/>
-      <c r="I43" s="6">
-        <v>529</v>
+      <c r="I43" s="6" t="n">
+        <v>532</v>
       </c>
       <c r="J43" s="4" t="s">
         <v>18</v>
@@ -3087,8 +2862,8 @@
       <c r="N43" s="4"/>
       <c r="O43" s="4"/>
     </row>
-    <row r="44" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="3">
+    <row r="44" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A44" s="3" t="n">
         <v>45754</v>
       </c>
       <c r="B44" s="4" t="s">
@@ -3100,18 +2875,18 @@
       <c r="D44" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="E44" s="3">
+      <c r="E44" s="3" t="n">
         <v>45789</v>
       </c>
-      <c r="F44" s="5">
-        <v>2287.0700000000002</v>
-      </c>
-      <c r="G44" s="5">
+      <c r="F44" s="5" t="n">
+        <v>2287.07</v>
+      </c>
+      <c r="G44" s="5" t="n">
         <v>1143.54</v>
       </c>
       <c r="H44" s="3"/>
-      <c r="I44" s="6">
-        <v>529</v>
+      <c r="I44" s="6" t="n">
+        <v>532</v>
       </c>
       <c r="J44" s="4" t="s">
         <v>26</v>
@@ -3126,8 +2901,8 @@
       <c r="N44" s="4"/>
       <c r="O44" s="4"/>
     </row>
-    <row r="45" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="3">
+    <row r="45" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A45" s="3" t="n">
         <v>45754</v>
       </c>
       <c r="B45" s="4" t="s">
@@ -3139,18 +2914,18 @@
       <c r="D45" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="3" t="n">
         <v>45796</v>
       </c>
-      <c r="F45" s="5">
+      <c r="F45" s="5" t="n">
         <v>2287.06</v>
       </c>
-      <c r="G45" s="5">
+      <c r="G45" s="5" t="n">
         <v>2287.06</v>
       </c>
       <c r="H45" s="3"/>
-      <c r="I45" s="6">
-        <v>522</v>
+      <c r="I45" s="6" t="n">
+        <v>525</v>
       </c>
       <c r="J45" s="4" t="s">
         <v>26</v>
@@ -3165,8 +2940,8 @@
       <c r="N45" s="4"/>
       <c r="O45" s="4"/>
     </row>
-    <row r="46" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="3">
+    <row r="46" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A46" s="3" t="n">
         <v>45868</v>
       </c>
       <c r="B46" s="4" t="s">
@@ -3178,18 +2953,18 @@
       <c r="D46" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="E46" s="3">
+      <c r="E46" s="3" t="n">
         <v>45896</v>
       </c>
-      <c r="F46" s="5">
+      <c r="F46" s="5" t="n">
         <v>3663.84</v>
       </c>
-      <c r="G46" s="5">
+      <c r="G46" s="5" t="n">
         <v>4572.62</v>
       </c>
       <c r="H46" s="3"/>
-      <c r="I46" s="6">
-        <v>422</v>
+      <c r="I46" s="6" t="n">
+        <v>425</v>
       </c>
       <c r="J46" s="4" t="s">
         <v>26</v>
@@ -3204,8 +2979,8 @@
       <c r="N46" s="4"/>
       <c r="O46" s="4"/>
     </row>
-    <row r="47" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="3">
+    <row r="47" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A47" s="3" t="n">
         <v>45868</v>
       </c>
       <c r="B47" s="4" t="s">
@@ -3217,18 +2992,18 @@
       <c r="D47" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="E47" s="3">
+      <c r="E47" s="3" t="n">
         <v>45910</v>
       </c>
-      <c r="F47" s="5">
+      <c r="F47" s="5" t="n">
         <v>3663.84</v>
       </c>
-      <c r="G47" s="5">
+      <c r="G47" s="5" t="n">
         <v>3663.84</v>
       </c>
       <c r="H47" s="3"/>
-      <c r="I47" s="6">
-        <v>408</v>
+      <c r="I47" s="6" t="n">
+        <v>411</v>
       </c>
       <c r="J47" s="4" t="s">
         <v>26</v>
@@ -3243,8 +3018,8 @@
       <c r="N47" s="4"/>
       <c r="O47" s="4"/>
     </row>
-    <row r="48" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="3">
+    <row r="48" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A48" s="3" t="n">
         <v>45868</v>
       </c>
       <c r="B48" s="4" t="s">
@@ -3256,18 +3031,18 @@
       <c r="D48" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="E48" s="3">
+      <c r="E48" s="3" t="n">
         <v>45924</v>
       </c>
-      <c r="F48" s="5">
+      <c r="F48" s="5" t="n">
         <v>3663.84</v>
       </c>
-      <c r="G48" s="5">
+      <c r="G48" s="5" t="n">
         <v>3663.84</v>
       </c>
       <c r="H48" s="3"/>
-      <c r="I48" s="6">
-        <v>394</v>
+      <c r="I48" s="6" t="n">
+        <v>397</v>
       </c>
       <c r="J48" s="4" t="s">
         <v>26</v>
@@ -3282,8 +3057,8 @@
       <c r="N48" s="4"/>
       <c r="O48" s="4"/>
     </row>
-    <row r="49" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="3">
+    <row r="49" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A49" s="3" t="n">
         <v>45919</v>
       </c>
       <c r="B49" s="4" t="s">
@@ -3295,18 +3070,18 @@
       <c r="D49" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="E49" s="3">
+      <c r="E49" s="3" t="n">
         <v>45947</v>
       </c>
-      <c r="F49" s="5">
+      <c r="F49" s="5" t="n">
         <v>2144.59</v>
       </c>
-      <c r="G49" s="5">
+      <c r="G49" s="5" t="n">
         <v>3867.34</v>
       </c>
       <c r="H49" s="3"/>
-      <c r="I49" s="6">
-        <v>371</v>
+      <c r="I49" s="6" t="n">
+        <v>374</v>
       </c>
       <c r="J49" s="4" t="s">
         <v>26</v>
@@ -3321,8 +3096,8 @@
       <c r="N49" s="4"/>
       <c r="O49" s="4"/>
     </row>
-    <row r="50" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="3">
+    <row r="50" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A50" s="3" t="n">
         <v>45919</v>
       </c>
       <c r="B50" s="4" t="s">
@@ -3334,18 +3109,18 @@
       <c r="D50" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="E50" s="3">
+      <c r="E50" s="3" t="n">
         <v>45954</v>
       </c>
-      <c r="F50" s="5">
+      <c r="F50" s="5" t="n">
         <v>2144.59</v>
       </c>
-      <c r="G50" s="5">
+      <c r="G50" s="5" t="n">
         <v>2144.59</v>
       </c>
       <c r="H50" s="3"/>
-      <c r="I50" s="6">
-        <v>364</v>
+      <c r="I50" s="6" t="n">
+        <v>367</v>
       </c>
       <c r="J50" s="4" t="s">
         <v>26</v>
@@ -3360,8 +3135,8 @@
       <c r="N50" s="4"/>
       <c r="O50" s="4"/>
     </row>
-    <row r="51" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="3">
+    <row r="51" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A51" s="3" t="n">
         <v>45919</v>
       </c>
       <c r="B51" s="4" t="s">
@@ -3373,18 +3148,18 @@
       <c r="D51" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="E51" s="3">
+      <c r="E51" s="3" t="n">
         <v>45961</v>
       </c>
-      <c r="F51" s="5">
+      <c r="F51" s="5" t="n">
         <v>2144.59</v>
       </c>
-      <c r="G51" s="5">
+      <c r="G51" s="5" t="n">
         <v>2144.59</v>
       </c>
       <c r="H51" s="3"/>
-      <c r="I51" s="6">
-        <v>357</v>
+      <c r="I51" s="6" t="n">
+        <v>360</v>
       </c>
       <c r="J51" s="4" t="s">
         <v>26</v>
@@ -3399,8 +3174,8 @@
       <c r="N51" s="4"/>
       <c r="O51" s="4"/>
     </row>
-    <row r="52" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="3">
+    <row r="52" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A52" s="3" t="n">
         <v>45919</v>
       </c>
       <c r="B52" s="4" t="s">
@@ -3412,18 +3187,18 @@
       <c r="D52" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="E52" s="3">
+      <c r="E52" s="3" t="n">
         <v>45968</v>
       </c>
-      <c r="F52" s="5">
+      <c r="F52" s="5" t="n">
         <v>2144.59</v>
       </c>
-      <c r="G52" s="5">
+      <c r="G52" s="5" t="n">
         <v>2144.59</v>
       </c>
       <c r="H52" s="3"/>
-      <c r="I52" s="6">
-        <v>350</v>
+      <c r="I52" s="6" t="n">
+        <v>353</v>
       </c>
       <c r="J52" s="4" t="s">
         <v>26</v>
@@ -3438,8 +3213,8 @@
       <c r="N52" s="4"/>
       <c r="O52" s="4"/>
     </row>
-    <row r="53" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="3">
+    <row r="53" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A53" s="3" t="n">
         <v>45938</v>
       </c>
       <c r="B53" s="4" t="s">
@@ -3451,18 +3226,18 @@
       <c r="D53" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="E53" s="3">
+      <c r="E53" s="3" t="n">
         <v>45980</v>
       </c>
-      <c r="F53" s="5">
+      <c r="F53" s="5" t="n">
         <v>4480</v>
       </c>
-      <c r="G53" s="5">
+      <c r="G53" s="5" t="n">
         <v>4480</v>
       </c>
       <c r="H53" s="3"/>
-      <c r="I53" s="6">
-        <v>338</v>
+      <c r="I53" s="6" t="n">
+        <v>341</v>
       </c>
       <c r="J53" s="4" t="s">
         <v>26</v>
@@ -3477,8 +3252,8 @@
       <c r="N53" s="4"/>
       <c r="O53" s="4"/>
     </row>
-    <row r="54" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="3">
+    <row r="54" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A54" s="3" t="n">
         <v>45959</v>
       </c>
       <c r="B54" s="4" t="s">
@@ -3490,18 +3265,18 @@
       <c r="D54" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="E54" s="3">
+      <c r="E54" s="3" t="n">
         <v>45980</v>
       </c>
-      <c r="F54" s="5">
+      <c r="F54" s="5" t="n">
         <v>28666.44</v>
       </c>
-      <c r="G54" s="5">
+      <c r="G54" s="5" t="n">
         <v>28666.44</v>
       </c>
       <c r="H54" s="3"/>
-      <c r="I54" s="6">
-        <v>338</v>
+      <c r="I54" s="6" t="n">
+        <v>341</v>
       </c>
       <c r="J54" s="4"/>
       <c r="K54" s="4" t="s">
@@ -3512,8 +3287,8 @@
       <c r="N54" s="4"/>
       <c r="O54" s="4"/>
     </row>
-    <row r="55" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="3">
+    <row r="55" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A55" s="3" t="n">
         <v>45959</v>
       </c>
       <c r="B55" s="4" t="s">
@@ -3525,18 +3300,18 @@
       <c r="D55" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="E55" s="3">
+      <c r="E55" s="3" t="n">
         <v>45987</v>
       </c>
-      <c r="F55" s="5">
-        <v>33844.160000000003</v>
-      </c>
-      <c r="G55" s="5">
-        <v>33844.160000000003</v>
+      <c r="F55" s="5" t="n">
+        <v>33844.16</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>33844.16</v>
       </c>
       <c r="H55" s="3"/>
-      <c r="I55" s="6">
-        <v>331</v>
+      <c r="I55" s="6" t="n">
+        <v>334</v>
       </c>
       <c r="J55" s="4"/>
       <c r="K55" s="4" t="s">
@@ -3547,8 +3322,8 @@
       <c r="N55" s="4"/>
       <c r="O55" s="4"/>
     </row>
-    <row r="56" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="3">
+    <row r="56" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A56" s="3" t="n">
         <v>45947</v>
       </c>
       <c r="B56" s="4" t="s">
@@ -3560,18 +3335,18 @@
       <c r="D56" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="E56" s="3">
+      <c r="E56" s="3" t="n">
         <v>45989</v>
       </c>
-      <c r="F56" s="5">
+      <c r="F56" s="5" t="n">
         <v>3220</v>
       </c>
-      <c r="G56" s="5">
+      <c r="G56" s="5" t="n">
         <v>3220</v>
       </c>
       <c r="H56" s="3"/>
-      <c r="I56" s="6">
-        <v>329</v>
+      <c r="I56" s="6" t="n">
+        <v>332</v>
       </c>
       <c r="J56" s="4"/>
       <c r="K56" s="4" t="s">
@@ -3582,8 +3357,8 @@
       <c r="N56" s="4"/>
       <c r="O56" s="4"/>
     </row>
-    <row r="57" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="3">
+    <row r="57" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A57" s="3" t="n">
         <v>45959</v>
       </c>
       <c r="B57" s="4" t="s">
@@ -3595,18 +3370,18 @@
       <c r="D57" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="E57" s="3">
+      <c r="E57" s="3" t="n">
         <v>45994</v>
       </c>
-      <c r="F57" s="5">
+      <c r="F57" s="5" t="n">
         <v>14483.06</v>
       </c>
-      <c r="G57" s="5">
+      <c r="G57" s="5" t="n">
         <v>14483.06</v>
       </c>
       <c r="H57" s="3"/>
-      <c r="I57" s="6">
-        <v>324</v>
+      <c r="I57" s="6" t="n">
+        <v>327</v>
       </c>
       <c r="J57" s="4"/>
       <c r="K57" s="4" t="s">
@@ -3617,8 +3392,8 @@
       <c r="N57" s="4"/>
       <c r="O57" s="4"/>
     </row>
-    <row r="58" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="3">
+    <row r="58" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A58" s="3" t="n">
         <v>46062</v>
       </c>
       <c r="B58" s="4" t="s">
@@ -3630,18 +3405,18 @@
       <c r="D58" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="E58" s="3">
+      <c r="E58" s="3" t="n">
         <v>46090</v>
       </c>
-      <c r="F58" s="5">
+      <c r="F58" s="5" t="n">
         <v>503.28</v>
       </c>
-      <c r="G58" s="5">
+      <c r="G58" s="5" t="n">
         <v>806.34</v>
       </c>
       <c r="H58" s="3"/>
-      <c r="I58" s="6">
-        <v>228</v>
+      <c r="I58" s="6" t="n">
+        <v>231</v>
       </c>
       <c r="J58" s="4" t="s">
         <v>26</v>
@@ -3656,8 +3431,8 @@
       <c r="N58" s="4"/>
       <c r="O58" s="4"/>
     </row>
-    <row r="59" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="3">
+    <row r="59" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A59" s="3" t="n">
         <v>46062</v>
       </c>
       <c r="B59" s="4" t="s">
@@ -3669,18 +3444,18 @@
       <c r="D59" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="E59" s="3">
+      <c r="E59" s="3" t="n">
         <v>46097</v>
       </c>
-      <c r="F59" s="5">
+      <c r="F59" s="5" t="n">
         <v>503.28</v>
       </c>
-      <c r="G59" s="5">
+      <c r="G59" s="5" t="n">
         <v>503.28</v>
       </c>
       <c r="H59" s="3"/>
-      <c r="I59" s="6">
-        <v>221</v>
+      <c r="I59" s="6" t="n">
+        <v>224</v>
       </c>
       <c r="J59" s="4" t="s">
         <v>26</v>
@@ -3695,8 +3470,8 @@
       <c r="N59" s="4"/>
       <c r="O59" s="4"/>
     </row>
-    <row r="60" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="3">
+    <row r="60" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A60" s="3" t="n">
         <v>46062</v>
       </c>
       <c r="B60" s="4" t="s">
@@ -3708,18 +3483,18 @@
       <c r="D60" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="E60" s="3">
+      <c r="E60" s="3" t="n">
         <v>46104</v>
       </c>
-      <c r="F60" s="5">
+      <c r="F60" s="5" t="n">
         <v>503.28</v>
       </c>
-      <c r="G60" s="5">
+      <c r="G60" s="5" t="n">
         <v>503.28</v>
       </c>
       <c r="H60" s="3"/>
-      <c r="I60" s="6">
-        <v>214</v>
+      <c r="I60" s="6" t="n">
+        <v>217</v>
       </c>
       <c r="J60" s="4" t="s">
         <v>26</v>
@@ -3734,8 +3509,8 @@
       <c r="N60" s="4"/>
       <c r="O60" s="4"/>
     </row>
-    <row r="61" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="3">
+    <row r="61" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A61" s="3" t="n">
         <v>46045</v>
       </c>
       <c r="B61" s="4" t="s">
@@ -3747,18 +3522,18 @@
       <c r="D61" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="E61" s="3">
+      <c r="E61" s="3" t="n">
         <v>46105</v>
       </c>
-      <c r="F61" s="5">
+      <c r="F61" s="5" t="n">
         <v>5466.66</v>
       </c>
-      <c r="G61" s="5">
+      <c r="G61" s="5" t="n">
         <v>5466.66</v>
       </c>
       <c r="H61" s="3"/>
-      <c r="I61" s="6">
-        <v>213</v>
+      <c r="I61" s="6" t="n">
+        <v>216</v>
       </c>
       <c r="J61" s="4" t="s">
         <v>18</v>
@@ -3773,8 +3548,8 @@
       <c r="N61" s="4"/>
       <c r="O61" s="4"/>
     </row>
-    <row r="62" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="3">
+    <row r="62" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A62" s="3" t="n">
         <v>46171</v>
       </c>
       <c r="B62" s="4" t="s">
@@ -3786,18 +3561,18 @@
       <c r="D62" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="E62" s="3">
+      <c r="E62" s="3" t="n">
         <v>46192</v>
       </c>
-      <c r="F62" s="5">
-        <v>4676.8500000000004</v>
-      </c>
-      <c r="G62" s="5">
+      <c r="F62" s="5" t="n">
+        <v>4676.85</v>
+      </c>
+      <c r="G62" s="5" t="n">
         <v>7494.53</v>
       </c>
       <c r="H62" s="3"/>
-      <c r="I62" s="6">
-        <v>126</v>
+      <c r="I62" s="6" t="n">
+        <v>129</v>
       </c>
       <c r="J62" s="4"/>
       <c r="K62" s="4" t="s">
@@ -3808,8 +3583,8 @@
       <c r="N62" s="4"/>
       <c r="O62" s="4"/>
     </row>
-    <row r="63" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="3">
+    <row r="63" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A63" s="3" t="n">
         <v>46171</v>
       </c>
       <c r="B63" s="4" t="s">
@@ -3821,18 +3596,18 @@
       <c r="D63" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="E63" s="3">
+      <c r="E63" s="3" t="n">
         <v>46199</v>
       </c>
-      <c r="F63" s="5">
-        <v>4676.8500000000004</v>
-      </c>
-      <c r="G63" s="5">
-        <v>4676.8500000000004</v>
+      <c r="F63" s="5" t="n">
+        <v>4676.85</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>4676.85</v>
       </c>
       <c r="H63" s="3"/>
-      <c r="I63" s="6">
-        <v>119</v>
+      <c r="I63" s="6" t="n">
+        <v>122</v>
       </c>
       <c r="J63" s="4"/>
       <c r="K63" s="4" t="s">
@@ -3843,8 +3618,8 @@
       <c r="N63" s="4"/>
       <c r="O63" s="4"/>
     </row>
-    <row r="64" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="3">
+    <row r="64" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A64" s="3" t="n">
         <v>46171</v>
       </c>
       <c r="B64" s="4" t="s">
@@ -3856,18 +3631,18 @@
       <c r="D64" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="E64" s="3">
+      <c r="E64" s="3" t="n">
         <v>46206</v>
       </c>
-      <c r="F64" s="5">
-        <v>4676.8500000000004</v>
-      </c>
-      <c r="G64" s="5">
-        <v>4676.8500000000004</v>
+      <c r="F64" s="5" t="n">
+        <v>4676.85</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>4676.85</v>
       </c>
       <c r="H64" s="3"/>
-      <c r="I64" s="6">
-        <v>112</v>
+      <c r="I64" s="6" t="n">
+        <v>115</v>
       </c>
       <c r="J64" s="4"/>
       <c r="K64" s="4" t="s">
@@ -3878,8 +3653,8 @@
       <c r="N64" s="4"/>
       <c r="O64" s="4"/>
     </row>
-    <row r="65" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="3">
+    <row r="65" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A65" s="3" t="n">
         <v>46162</v>
       </c>
       <c r="B65" s="4" t="s">
@@ -3891,18 +3666,18 @@
       <c r="D65" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="E65" s="3">
+      <c r="E65" s="3" t="n">
         <v>46222</v>
       </c>
-      <c r="F65" s="5">
+      <c r="F65" s="5" t="n">
         <v>12349.79</v>
       </c>
-      <c r="G65" s="5">
+      <c r="G65" s="5" t="n">
         <v>12349.79</v>
       </c>
       <c r="H65" s="3"/>
-      <c r="I65" s="6">
-        <v>96</v>
+      <c r="I65" s="6" t="n">
+        <v>99</v>
       </c>
       <c r="J65" s="4"/>
       <c r="K65" s="4" t="s">
@@ -3913,8 +3688,8 @@
       <c r="N65" s="4"/>
       <c r="O65" s="4"/>
     </row>
-    <row r="66" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="3">
+    <row r="66" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A66" s="3" t="n">
         <v>46203</v>
       </c>
       <c r="B66" s="4" t="s">
@@ -3926,18 +3701,18 @@
       <c r="D66" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="E66" s="3">
+      <c r="E66" s="3" t="n">
         <v>46259</v>
       </c>
-      <c r="F66" s="5">
+      <c r="F66" s="5" t="n">
         <v>860</v>
       </c>
-      <c r="G66" s="5">
+      <c r="G66" s="5" t="n">
         <v>860</v>
       </c>
       <c r="H66" s="3"/>
-      <c r="I66" s="6">
-        <v>59</v>
+      <c r="I66" s="6" t="n">
+        <v>62</v>
       </c>
       <c r="J66" s="4" t="s">
         <v>26</v>
@@ -3952,8 +3727,8 @@
       <c r="N66" s="4"/>
       <c r="O66" s="4"/>
     </row>
-    <row r="67" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="3">
+    <row r="67" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A67" s="3" t="n">
         <v>46224</v>
       </c>
       <c r="B67" s="4" t="s">
@@ -3965,18 +3740,18 @@
       <c r="D67" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="E67" s="3">
+      <c r="E67" s="3" t="n">
         <v>46259</v>
       </c>
-      <c r="F67" s="5">
+      <c r="F67" s="5" t="n">
         <v>2818.37</v>
       </c>
-      <c r="G67" s="5">
+      <c r="G67" s="5" t="n">
         <v>2818.37</v>
       </c>
       <c r="H67" s="3"/>
-      <c r="I67" s="6">
-        <v>59</v>
+      <c r="I67" s="6" t="n">
+        <v>62</v>
       </c>
       <c r="J67" s="4" t="s">
         <v>26</v>
@@ -3991,8 +3766,8 @@
       <c r="N67" s="4"/>
       <c r="O67" s="4"/>
     </row>
-    <row r="68" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="3">
+    <row r="68" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A68" s="3" t="n">
         <v>46232</v>
       </c>
       <c r="B68" s="4" t="s">
@@ -4004,18 +3779,18 @@
       <c r="D68" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="E68" s="3">
+      <c r="E68" s="3" t="n">
         <v>46262</v>
       </c>
-      <c r="F68" s="5">
+      <c r="F68" s="5" t="n">
         <v>9716</v>
       </c>
-      <c r="G68" s="5">
+      <c r="G68" s="5" t="n">
         <v>18957.86</v>
       </c>
       <c r="H68" s="3"/>
-      <c r="I68" s="6">
-        <v>56</v>
+      <c r="I68" s="6" t="n">
+        <v>59</v>
       </c>
       <c r="J68" s="4" t="s">
         <v>26</v>
@@ -4030,8 +3805,8 @@
       <c r="N68" s="4"/>
       <c r="O68" s="4"/>
     </row>
-    <row r="69" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="3">
+    <row r="69" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A69" s="3" t="n">
         <v>46232</v>
       </c>
       <c r="B69" s="4" t="s">
@@ -4043,18 +3818,18 @@
       <c r="D69" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="E69" s="3">
+      <c r="E69" s="3" t="n">
         <v>46272</v>
       </c>
-      <c r="F69" s="5">
+      <c r="F69" s="5" t="n">
         <v>9716</v>
       </c>
-      <c r="G69" s="5">
+      <c r="G69" s="5" t="n">
         <v>9716</v>
       </c>
       <c r="H69" s="3"/>
-      <c r="I69" s="6">
-        <v>46</v>
+      <c r="I69" s="6" t="n">
+        <v>49</v>
       </c>
       <c r="J69" s="4" t="s">
         <v>26</v>
@@ -4069,8 +3844,8 @@
       <c r="N69" s="4"/>
       <c r="O69" s="4"/>
     </row>
-    <row r="70" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="3">
+    <row r="70" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A70" s="3" t="n">
         <v>46227</v>
       </c>
       <c r="B70" s="4" t="s">
@@ -4082,18 +3857,18 @@
       <c r="D70" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="E70" s="3">
+      <c r="E70" s="3" t="n">
         <v>46272</v>
       </c>
-      <c r="F70" s="5">
+      <c r="F70" s="5" t="n">
         <v>4216.67</v>
       </c>
-      <c r="G70" s="5">
+      <c r="G70" s="5" t="n">
         <v>6389.24</v>
       </c>
       <c r="H70" s="3"/>
-      <c r="I70" s="6">
-        <v>46</v>
+      <c r="I70" s="6" t="n">
+        <v>49</v>
       </c>
       <c r="J70" s="4" t="s">
         <v>183</v>
@@ -4108,8 +3883,8 @@
       <c r="N70" s="4"/>
       <c r="O70" s="4"/>
     </row>
-    <row r="71" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="3">
+    <row r="71" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A71" s="3" t="n">
         <v>46224</v>
       </c>
       <c r="B71" s="4" t="s">
@@ -4121,18 +3896,18 @@
       <c r="D71" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="E71" s="3">
+      <c r="E71" s="3" t="n">
         <v>46273</v>
       </c>
-      <c r="F71" s="5">
+      <c r="F71" s="5" t="n">
         <v>2818.37</v>
       </c>
-      <c r="G71" s="5">
+      <c r="G71" s="5" t="n">
         <v>2818.37</v>
       </c>
       <c r="H71" s="3"/>
-      <c r="I71" s="6">
-        <v>45</v>
+      <c r="I71" s="6" t="n">
+        <v>48</v>
       </c>
       <c r="J71" s="4" t="s">
         <v>26</v>
@@ -4147,8 +3922,8 @@
       <c r="N71" s="4"/>
       <c r="O71" s="4"/>
     </row>
-    <row r="72" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="3">
+    <row r="72" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A72" s="3" t="n">
         <v>46234</v>
       </c>
       <c r="B72" s="4" t="s">
@@ -4160,18 +3935,18 @@
       <c r="D72" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="E72" s="3">
+      <c r="E72" s="3" t="n">
         <v>46279</v>
       </c>
-      <c r="F72" s="5">
+      <c r="F72" s="5" t="n">
         <v>3789.09</v>
       </c>
-      <c r="G72" s="5">
+      <c r="G72" s="5" t="n">
         <v>5741.36</v>
       </c>
       <c r="H72" s="3"/>
-      <c r="I72" s="6">
-        <v>39</v>
+      <c r="I72" s="6" t="n">
+        <v>42</v>
       </c>
       <c r="J72" s="4" t="s">
         <v>189</v>
@@ -4186,8 +3961,8 @@
       <c r="N72" s="4"/>
       <c r="O72" s="4"/>
     </row>
-    <row r="73" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="3">
+    <row r="73" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A73" s="3" t="n">
         <v>46232</v>
       </c>
       <c r="B73" s="4" t="s">
@@ -4199,18 +3974,18 @@
       <c r="D73" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="E73" s="3">
+      <c r="E73" s="3" t="n">
         <v>46282</v>
       </c>
-      <c r="F73" s="5">
+      <c r="F73" s="5" t="n">
         <v>9716</v>
       </c>
-      <c r="G73" s="5">
+      <c r="G73" s="5" t="n">
         <v>9716</v>
       </c>
       <c r="H73" s="3"/>
-      <c r="I73" s="6">
-        <v>36</v>
+      <c r="I73" s="6" t="n">
+        <v>39</v>
       </c>
       <c r="J73" s="4" t="s">
         <v>26</v>
@@ -4225,8 +4000,8 @@
       <c r="N73" s="4"/>
       <c r="O73" s="4"/>
     </row>
-    <row r="74" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="3">
+    <row r="74" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A74" s="3" t="n">
         <v>46227</v>
       </c>
       <c r="B74" s="4" t="s">
@@ -4238,18 +4013,18 @@
       <c r="D74" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="E74" s="3">
+      <c r="E74" s="3" t="n">
         <v>46283</v>
       </c>
-      <c r="F74" s="5">
+      <c r="F74" s="5" t="n">
         <v>23168.6</v>
       </c>
-      <c r="G74" s="5">
+      <c r="G74" s="5" t="n">
         <v>23168.6</v>
       </c>
       <c r="H74" s="3"/>
-      <c r="I74" s="6">
-        <v>35</v>
+      <c r="I74" s="6" t="n">
+        <v>38</v>
       </c>
       <c r="J74" s="4" t="s">
         <v>189</v>
@@ -4264,8 +4039,8 @@
       <c r="N74" s="4"/>
       <c r="O74" s="4"/>
     </row>
-    <row r="75" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="3">
+    <row r="75" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A75" s="3" t="n">
         <v>46234</v>
       </c>
       <c r="B75" s="4" t="s">
@@ -4277,18 +4052,18 @@
       <c r="D75" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="E75" s="3">
+      <c r="E75" s="3" t="n">
         <v>46284</v>
       </c>
-      <c r="F75" s="5">
+      <c r="F75" s="5" t="n">
         <v>4950.17</v>
       </c>
-      <c r="G75" s="5">
+      <c r="G75" s="5" t="n">
         <v>4950.17</v>
       </c>
       <c r="H75" s="3"/>
-      <c r="I75" s="6">
-        <v>34</v>
+      <c r="I75" s="6" t="n">
+        <v>37</v>
       </c>
       <c r="J75" s="4" t="s">
         <v>189</v>
@@ -4303,8 +4078,8 @@
       <c r="N75" s="4"/>
       <c r="O75" s="4"/>
     </row>
-    <row r="76" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="3">
+    <row r="76" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A76" s="3" t="n">
         <v>46225</v>
       </c>
       <c r="B76" s="4" t="s">
@@ -4316,18 +4091,18 @@
       <c r="D76" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="E76" s="3">
+      <c r="E76" s="3" t="n">
         <v>46285</v>
       </c>
-      <c r="F76" s="5">
+      <c r="F76" s="5" t="n">
         <v>7551.88</v>
       </c>
-      <c r="G76" s="5">
+      <c r="G76" s="5" t="n">
         <v>7551.88</v>
       </c>
       <c r="H76" s="3"/>
-      <c r="I76" s="6">
-        <v>33</v>
+      <c r="I76" s="6" t="n">
+        <v>36</v>
       </c>
       <c r="J76" s="4" t="s">
         <v>189</v>
@@ -4342,8 +4117,8 @@
       <c r="N76" s="4"/>
       <c r="O76" s="4"/>
     </row>
-    <row r="77" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="3">
+    <row r="77" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A77" s="3" t="n">
         <v>46244</v>
       </c>
       <c r="B77" s="4" t="s">
@@ -4355,18 +4130,18 @@
       <c r="D77" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="E77" s="3">
+      <c r="E77" s="3" t="n">
         <v>46286</v>
       </c>
-      <c r="F77" s="5">
+      <c r="F77" s="5" t="n">
         <v>4320</v>
       </c>
-      <c r="G77" s="5">
+      <c r="G77" s="5" t="n">
         <v>4320</v>
       </c>
       <c r="H77" s="3"/>
-      <c r="I77" s="6">
-        <v>32</v>
+      <c r="I77" s="6" t="n">
+        <v>35</v>
       </c>
       <c r="J77" s="4" t="s">
         <v>189</v>
@@ -4381,8 +4156,8 @@
       <c r="N77" s="4"/>
       <c r="O77" s="4"/>
     </row>
-    <row r="78" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="3">
+    <row r="78" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A78" s="3" t="n">
         <v>46227</v>
       </c>
       <c r="B78" s="4" t="s">
@@ -4394,18 +4169,18 @@
       <c r="D78" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="E78" s="3">
+      <c r="E78" s="3" t="n">
         <v>46287</v>
       </c>
-      <c r="F78" s="5">
+      <c r="F78" s="5" t="n">
         <v>4216.67</v>
       </c>
-      <c r="G78" s="5">
+      <c r="G78" s="5" t="n">
         <v>4216.67</v>
       </c>
       <c r="H78" s="3"/>
-      <c r="I78" s="6">
-        <v>31</v>
+      <c r="I78" s="6" t="n">
+        <v>34</v>
       </c>
       <c r="J78" s="4" t="s">
         <v>183</v>
@@ -4420,8 +4195,8 @@
       <c r="N78" s="4"/>
       <c r="O78" s="4"/>
     </row>
-    <row r="79" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="3">
+    <row r="79" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A79" s="3" t="n">
         <v>46253</v>
       </c>
       <c r="B79" s="4" t="s">
@@ -4433,18 +4208,18 @@
       <c r="D79" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="E79" s="3">
+      <c r="E79" s="3" t="n">
         <v>46288</v>
       </c>
-      <c r="F79" s="5">
+      <c r="F79" s="5" t="n">
         <v>10080</v>
       </c>
-      <c r="G79" s="5">
+      <c r="G79" s="5" t="n">
         <v>10080</v>
       </c>
       <c r="H79" s="3"/>
-      <c r="I79" s="6">
-        <v>30</v>
+      <c r="I79" s="6" t="n">
+        <v>33</v>
       </c>
       <c r="J79" s="4" t="s">
         <v>189</v>
@@ -4459,8 +4234,8 @@
       <c r="N79" s="4"/>
       <c r="O79" s="4"/>
     </row>
-    <row r="80" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="3">
+    <row r="80" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A80" s="3" t="n">
         <v>46253</v>
       </c>
       <c r="B80" s="4" t="s">
@@ -4472,18 +4247,18 @@
       <c r="D80" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="E80" s="3">
+      <c r="E80" s="3" t="n">
         <v>46288</v>
       </c>
-      <c r="F80" s="5">
+      <c r="F80" s="5" t="n">
         <v>3640</v>
       </c>
-      <c r="G80" s="5">
+      <c r="G80" s="5" t="n">
         <v>3640</v>
       </c>
       <c r="H80" s="3"/>
-      <c r="I80" s="6">
-        <v>30</v>
+      <c r="I80" s="6" t="n">
+        <v>33</v>
       </c>
       <c r="J80" s="4" t="s">
         <v>189</v>
@@ -4498,8 +4273,8 @@
       <c r="N80" s="4"/>
       <c r="O80" s="4"/>
     </row>
-    <row r="81" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="3">
+    <row r="81" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A81" s="3" t="n">
         <v>46262</v>
       </c>
       <c r="B81" s="4" t="s">
@@ -4511,18 +4286,18 @@
       <c r="D81" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="E81" s="3">
+      <c r="E81" s="3" t="n">
         <v>46290</v>
       </c>
-      <c r="F81" s="5">
+      <c r="F81" s="5" t="n">
         <v>7694.4</v>
       </c>
-      <c r="G81" s="5">
+      <c r="G81" s="5" t="n">
         <v>7694.4</v>
       </c>
       <c r="H81" s="3"/>
-      <c r="I81" s="6">
-        <v>28</v>
+      <c r="I81" s="6" t="n">
+        <v>31</v>
       </c>
       <c r="J81" s="4" t="s">
         <v>26</v>
@@ -4537,8 +4312,8 @@
       <c r="N81" s="4"/>
       <c r="O81" s="4"/>
     </row>
-    <row r="82" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="3">
+    <row r="82" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A82" s="3" t="n">
         <v>46262</v>
       </c>
       <c r="B82" s="4" t="s">
@@ -4550,18 +4325,18 @@
       <c r="D82" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="E82" s="3">
+      <c r="E82" s="3" t="n">
         <v>46290</v>
       </c>
-      <c r="F82" s="5">
+      <c r="F82" s="5" t="n">
         <v>11660.11</v>
       </c>
-      <c r="G82" s="5">
+      <c r="G82" s="5" t="n">
         <v>11660.11</v>
       </c>
       <c r="H82" s="3"/>
-      <c r="I82" s="6">
-        <v>28</v>
+      <c r="I82" s="6" t="n">
+        <v>31</v>
       </c>
       <c r="J82" s="4" t="s">
         <v>189</v>
@@ -4576,8 +4351,8 @@
       <c r="N82" s="4"/>
       <c r="O82" s="4"/>
     </row>
-    <row r="83" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="3">
+    <row r="83" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A83" s="3" t="n">
         <v>46232</v>
       </c>
       <c r="B83" s="4" t="s">
@@ -4589,18 +4364,18 @@
       <c r="D83" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="E83" s="3">
+      <c r="E83" s="3" t="n">
         <v>46292</v>
       </c>
-      <c r="F83" s="5">
+      <c r="F83" s="5" t="n">
         <v>4082.05</v>
       </c>
-      <c r="G83" s="5">
+      <c r="G83" s="5" t="n">
         <v>4082.05</v>
       </c>
       <c r="H83" s="3"/>
-      <c r="I83" s="6">
-        <v>26</v>
+      <c r="I83" s="6" t="n">
+        <v>29</v>
       </c>
       <c r="J83" s="4" t="s">
         <v>189</v>
@@ -4615,8 +4390,8 @@
       <c r="N83" s="4"/>
       <c r="O83" s="4"/>
     </row>
-    <row r="84" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="3">
+    <row r="84" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A84" s="3" t="n">
         <v>46232</v>
       </c>
       <c r="B84" s="4" t="s">
@@ -4628,18 +4403,18 @@
       <c r="D84" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="E84" s="3">
+      <c r="E84" s="3" t="n">
         <v>46292</v>
       </c>
-      <c r="F84" s="5">
+      <c r="F84" s="5" t="n">
         <v>9716</v>
       </c>
-      <c r="G84" s="5">
+      <c r="G84" s="5" t="n">
         <v>9716</v>
       </c>
       <c r="H84" s="3"/>
-      <c r="I84" s="6">
-        <v>26</v>
+      <c r="I84" s="6" t="n">
+        <v>29</v>
       </c>
       <c r="J84" s="4" t="s">
         <v>26</v>
@@ -4654,8 +4429,8 @@
       <c r="N84" s="4"/>
       <c r="O84" s="4"/>
     </row>
-    <row r="85" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="3">
+    <row r="85" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A85" s="3" t="n">
         <v>46244</v>
       </c>
       <c r="B85" s="4" t="s">
@@ -4667,18 +4442,18 @@
       <c r="D85" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="E85" s="3">
+      <c r="E85" s="3" t="n">
         <v>46293</v>
       </c>
-      <c r="F85" s="5">
+      <c r="F85" s="5" t="n">
         <v>4320</v>
       </c>
-      <c r="G85" s="5">
+      <c r="G85" s="5" t="n">
         <v>4320</v>
       </c>
       <c r="H85" s="3"/>
-      <c r="I85" s="6">
-        <v>25</v>
+      <c r="I85" s="6" t="n">
+        <v>28</v>
       </c>
       <c r="J85" s="4" t="s">
         <v>189</v>
@@ -4693,8 +4468,8 @@
       <c r="N85" s="4"/>
       <c r="O85" s="4"/>
     </row>
-    <row r="86" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="3">
+    <row r="86" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A86" s="3" t="n">
         <v>46223</v>
       </c>
       <c r="B86" s="4" t="s">
@@ -4706,18 +4481,18 @@
       <c r="D86" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="E86" s="3">
+      <c r="E86" s="3" t="n">
         <v>46293</v>
       </c>
-      <c r="F86" s="5">
+      <c r="F86" s="5" t="n">
         <v>11200</v>
       </c>
-      <c r="G86" s="5">
+      <c r="G86" s="5" t="n">
         <v>11200</v>
       </c>
       <c r="H86" s="3"/>
-      <c r="I86" s="6">
-        <v>25</v>
+      <c r="I86" s="6" t="n">
+        <v>28</v>
       </c>
       <c r="J86" s="4" t="s">
         <v>189</v>
@@ -4732,37 +4507,37 @@
       <c r="N86" s="4"/>
       <c r="O86" s="4"/>
     </row>
-    <row r="87" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="3">
-        <v>46266</v>
+    <row r="87" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A87" s="3" t="n">
+        <v>46234</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>45</v>
+        <v>180</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="D87" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="E87" s="3">
+      <c r="E87" s="3" t="n">
         <v>46294</v>
       </c>
-      <c r="F87" s="5">
-        <v>18600</v>
-      </c>
-      <c r="G87" s="5">
-        <v>18600</v>
+      <c r="F87" s="5" t="n">
+        <v>3789.09</v>
+      </c>
+      <c r="G87" s="5" t="n">
+        <v>3789.09</v>
       </c>
       <c r="H87" s="3"/>
-      <c r="I87" s="6">
-        <v>24</v>
+      <c r="I87" s="6" t="n">
+        <v>27</v>
       </c>
       <c r="J87" s="4" t="s">
-        <v>26</v>
+        <v>189</v>
       </c>
       <c r="K87" s="4" t="s">
-        <v>27</v>
+        <v>184</v>
       </c>
       <c r="L87" s="4"/>
       <c r="M87" s="4" t="s">
@@ -4771,37 +4546,37 @@
       <c r="N87" s="4"/>
       <c r="O87" s="4"/>
     </row>
-    <row r="88" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="3">
-        <v>46234</v>
+    <row r="88" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A88" s="3" t="n">
+        <v>46266</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>180</v>
+        <v>45</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="D88" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="E88" s="3">
+      <c r="E88" s="3" t="n">
         <v>46294</v>
       </c>
-      <c r="F88" s="5">
-        <v>3789.09</v>
-      </c>
-      <c r="G88" s="5">
-        <v>3789.09</v>
+      <c r="F88" s="5" t="n">
+        <v>18600</v>
+      </c>
+      <c r="G88" s="5" t="n">
+        <v>18600</v>
       </c>
       <c r="H88" s="3"/>
-      <c r="I88" s="6">
-        <v>24</v>
+      <c r="I88" s="6" t="n">
+        <v>27</v>
       </c>
       <c r="J88" s="4" t="s">
-        <v>189</v>
+        <v>26</v>
       </c>
       <c r="K88" s="4" t="s">
-        <v>184</v>
+        <v>27</v>
       </c>
       <c r="L88" s="4"/>
       <c r="M88" s="4" t="s">
@@ -4810,8 +4585,8 @@
       <c r="N88" s="4"/>
       <c r="O88" s="4"/>
     </row>
-    <row r="89" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="3">
+    <row r="89" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A89" s="3" t="n">
         <v>46253</v>
       </c>
       <c r="B89" s="4" t="s">
@@ -4823,18 +4598,18 @@
       <c r="D89" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="E89" s="3">
+      <c r="E89" s="3" t="n">
         <v>46295</v>
       </c>
-      <c r="F89" s="5">
+      <c r="F89" s="5" t="n">
         <v>10080</v>
       </c>
-      <c r="G89" s="5">
+      <c r="G89" s="5" t="n">
         <v>10080</v>
       </c>
       <c r="H89" s="3"/>
-      <c r="I89" s="6">
-        <v>23</v>
+      <c r="I89" s="6" t="n">
+        <v>26</v>
       </c>
       <c r="J89" s="4" t="s">
         <v>189</v>
@@ -4849,8 +4624,8 @@
       <c r="N89" s="4"/>
       <c r="O89" s="4"/>
     </row>
-    <row r="90" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="3">
+    <row r="90" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A90" s="3" t="n">
         <v>46253</v>
       </c>
       <c r="B90" s="4" t="s">
@@ -4862,18 +4637,18 @@
       <c r="D90" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="E90" s="3">
+      <c r="E90" s="3" t="n">
         <v>46295</v>
       </c>
-      <c r="F90" s="5">
-        <v>2051.2199999999998</v>
-      </c>
-      <c r="G90" s="5">
-        <v>2051.2199999999998</v>
+      <c r="F90" s="5" t="n">
+        <v>2051.22</v>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>2051.22</v>
       </c>
       <c r="H90" s="3"/>
-      <c r="I90" s="6">
-        <v>23</v>
+      <c r="I90" s="6" t="n">
+        <v>26</v>
       </c>
       <c r="J90" s="4" t="s">
         <v>18</v>
@@ -4888,8 +4663,8 @@
       <c r="N90" s="4"/>
       <c r="O90" s="4"/>
     </row>
-    <row r="91" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="3">
+    <row r="91" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A91" s="3" t="n">
         <v>46262</v>
       </c>
       <c r="B91" s="4" t="s">
@@ -4901,21 +4676,21 @@
       <c r="D91" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="E91" s="3">
+      <c r="E91" s="3" t="n">
         <v>46297</v>
       </c>
-      <c r="F91" s="5">
-        <v>7694.4</v>
-      </c>
-      <c r="G91" s="5">
-        <v>7694.4</v>
+      <c r="F91" s="5" t="n">
+        <v>11660.11</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>11660.11</v>
       </c>
       <c r="H91" s="3"/>
-      <c r="I91" s="6">
-        <v>21</v>
+      <c r="I91" s="6" t="n">
+        <v>24</v>
       </c>
       <c r="J91" s="4" t="s">
-        <v>26</v>
+        <v>189</v>
       </c>
       <c r="K91" s="4" t="s">
         <v>213</v>
@@ -4927,8 +4702,8 @@
       <c r="N91" s="4"/>
       <c r="O91" s="4"/>
     </row>
-    <row r="92" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="3">
+    <row r="92" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A92" s="3" t="n">
         <v>46262</v>
       </c>
       <c r="B92" s="4" t="s">
@@ -4940,21 +4715,21 @@
       <c r="D92" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="E92" s="3">
+      <c r="E92" s="3" t="n">
         <v>46297</v>
       </c>
-      <c r="F92" s="5">
-        <v>11660.11</v>
-      </c>
-      <c r="G92" s="5">
-        <v>11660.11</v>
+      <c r="F92" s="5" t="n">
+        <v>7694.4</v>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>7694.4</v>
       </c>
       <c r="H92" s="3"/>
-      <c r="I92" s="6">
-        <v>21</v>
+      <c r="I92" s="6" t="n">
+        <v>24</v>
       </c>
       <c r="J92" s="4" t="s">
-        <v>189</v>
+        <v>26</v>
       </c>
       <c r="K92" s="4" t="s">
         <v>213</v>
@@ -4966,8 +4741,8 @@
       <c r="N92" s="4"/>
       <c r="O92" s="4"/>
     </row>
-    <row r="93" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="3">
+    <row r="93" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A93" s="3" t="n">
         <v>46225</v>
       </c>
       <c r="B93" s="4" t="s">
@@ -4979,18 +4754,18 @@
       <c r="D93" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="E93" s="3">
+      <c r="E93" s="3" t="n">
         <v>46300</v>
       </c>
-      <c r="F93" s="5">
+      <c r="F93" s="5" t="n">
         <v>7551.88</v>
       </c>
-      <c r="G93" s="5">
+      <c r="G93" s="5" t="n">
         <v>7551.88</v>
       </c>
       <c r="H93" s="3"/>
-      <c r="I93" s="6">
-        <v>18</v>
+      <c r="I93" s="6" t="n">
+        <v>21</v>
       </c>
       <c r="J93" s="4" t="s">
         <v>189</v>
@@ -5005,8 +4780,8 @@
       <c r="N93" s="4"/>
       <c r="O93" s="4"/>
     </row>
-    <row r="94" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="3">
+    <row r="94" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A94" s="3" t="n">
         <v>46266</v>
       </c>
       <c r="B94" s="4" t="s">
@@ -5018,18 +4793,18 @@
       <c r="D94" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="E94" s="3">
+      <c r="E94" s="3" t="n">
         <v>46301</v>
       </c>
-      <c r="F94" s="5">
+      <c r="F94" s="5" t="n">
         <v>18600</v>
       </c>
-      <c r="G94" s="5">
+      <c r="G94" s="5" t="n">
         <v>18600</v>
       </c>
       <c r="H94" s="3"/>
-      <c r="I94" s="6">
-        <v>17</v>
+      <c r="I94" s="6" t="n">
+        <v>20</v>
       </c>
       <c r="J94" s="4" t="s">
         <v>26</v>
@@ -5044,37 +4819,37 @@
       <c r="N94" s="4"/>
       <c r="O94" s="4"/>
     </row>
-    <row r="95" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="3">
-        <v>46253</v>
+    <row r="95" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A95" s="3" t="n">
+        <v>46227</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>45</v>
+        <v>180</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="D95" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="E95" s="3">
+      <c r="E95" s="3" t="n">
         <v>46302</v>
       </c>
-      <c r="F95" s="5">
-        <v>10080</v>
-      </c>
-      <c r="G95" s="5">
-        <v>10080</v>
+      <c r="F95" s="5" t="n">
+        <v>4216.66</v>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>4216.66</v>
       </c>
       <c r="H95" s="3"/>
-      <c r="I95" s="6">
-        <v>16</v>
+      <c r="I95" s="6" t="n">
+        <v>19</v>
       </c>
       <c r="J95" s="4" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="K95" s="4" t="s">
-        <v>27</v>
+        <v>184</v>
       </c>
       <c r="L95" s="4"/>
       <c r="M95" s="4" t="s">
@@ -5083,37 +4858,37 @@
       <c r="N95" s="4"/>
       <c r="O95" s="4"/>
     </row>
-    <row r="96" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="3">
-        <v>46227</v>
+    <row r="96" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A96" s="3" t="n">
+        <v>46232</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>180</v>
+        <v>15</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="D96" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="E96" s="3">
+      <c r="E96" s="3" t="n">
         <v>46302</v>
       </c>
-      <c r="F96" s="5">
-        <v>4216.66</v>
-      </c>
-      <c r="G96" s="5">
-        <v>4216.66</v>
+      <c r="F96" s="5" t="n">
+        <v>9716</v>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>9716</v>
       </c>
       <c r="H96" s="3"/>
-      <c r="I96" s="6">
-        <v>16</v>
+      <c r="I96" s="6" t="n">
+        <v>19</v>
       </c>
       <c r="J96" s="4" t="s">
-        <v>183</v>
+        <v>26</v>
       </c>
       <c r="K96" s="4" t="s">
-        <v>184</v>
+        <v>39</v>
       </c>
       <c r="L96" s="4"/>
       <c r="M96" s="4" t="s">
@@ -5122,37 +4897,37 @@
       <c r="N96" s="4"/>
       <c r="O96" s="4"/>
     </row>
-    <row r="97" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="3">
-        <v>46232</v>
+    <row r="97" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A97" s="3" t="n">
+        <v>46253</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>175</v>
+        <v>193</v>
       </c>
       <c r="D97" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="E97" s="3">
+      <c r="E97" s="3" t="n">
         <v>46302</v>
       </c>
-      <c r="F97" s="5">
-        <v>9716</v>
-      </c>
-      <c r="G97" s="5">
-        <v>9716</v>
+      <c r="F97" s="5" t="n">
+        <v>10080</v>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>10080</v>
       </c>
       <c r="H97" s="3"/>
-      <c r="I97" s="6">
-        <v>16</v>
+      <c r="I97" s="6" t="n">
+        <v>19</v>
       </c>
       <c r="J97" s="4" t="s">
-        <v>26</v>
+        <v>189</v>
       </c>
       <c r="K97" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="L97" s="4"/>
       <c r="M97" s="4" t="s">
@@ -5161,8 +4936,8 @@
       <c r="N97" s="4"/>
       <c r="O97" s="4"/>
     </row>
-    <row r="98" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="3">
+    <row r="98" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A98" s="3" t="n">
         <v>46262</v>
       </c>
       <c r="B98" s="4" t="s">
@@ -5174,18 +4949,18 @@
       <c r="D98" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="E98" s="3">
+      <c r="E98" s="3" t="n">
         <v>46304</v>
       </c>
-      <c r="F98" s="5">
+      <c r="F98" s="5" t="n">
         <v>7694.4</v>
       </c>
-      <c r="G98" s="5">
+      <c r="G98" s="5" t="n">
         <v>7694.4</v>
       </c>
       <c r="H98" s="3"/>
-      <c r="I98" s="6">
-        <v>14</v>
+      <c r="I98" s="6" t="n">
+        <v>17</v>
       </c>
       <c r="J98" s="4" t="s">
         <v>26</v>
@@ -5200,8 +4975,8 @@
       <c r="N98" s="4"/>
       <c r="O98" s="4"/>
     </row>
-    <row r="99" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="3">
+    <row r="99" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A99" s="3" t="n">
         <v>46262</v>
       </c>
       <c r="B99" s="4" t="s">
@@ -5213,18 +4988,18 @@
       <c r="D99" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="E99" s="3">
+      <c r="E99" s="3" t="n">
         <v>46304</v>
       </c>
-      <c r="F99" s="5">
+      <c r="F99" s="5" t="n">
         <v>11660.11</v>
       </c>
-      <c r="G99" s="5">
+      <c r="G99" s="5" t="n">
         <v>11660.11</v>
       </c>
       <c r="H99" s="3"/>
-      <c r="I99" s="6">
-        <v>14</v>
+      <c r="I99" s="6" t="n">
+        <v>17</v>
       </c>
       <c r="J99" s="4" t="s">
         <v>189</v>
@@ -5239,8 +5014,8 @@
       <c r="N99" s="4"/>
       <c r="O99" s="4"/>
     </row>
-    <row r="100" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="3">
+    <row r="100" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A100" s="3" t="n">
         <v>46265</v>
       </c>
       <c r="B100" s="4" t="s">
@@ -5252,18 +5027,18 @@
       <c r="D100" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="E100" s="3">
+      <c r="E100" s="3" t="n">
         <v>46305</v>
       </c>
-      <c r="F100" s="5">
+      <c r="F100" s="5" t="n">
         <v>4750</v>
       </c>
-      <c r="G100" s="5">
+      <c r="G100" s="5" t="n">
         <v>4750</v>
       </c>
       <c r="H100" s="3"/>
-      <c r="I100" s="6">
-        <v>13</v>
+      <c r="I100" s="6" t="n">
+        <v>16</v>
       </c>
       <c r="J100" s="4" t="s">
         <v>189</v>
@@ -5278,8 +5053,8 @@
       <c r="N100" s="4"/>
       <c r="O100" s="4"/>
     </row>
-    <row r="101" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="3">
+    <row r="101" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A101" s="3" t="n">
         <v>46232</v>
       </c>
       <c r="B101" s="4" t="s">
@@ -5291,18 +5066,18 @@
       <c r="D101" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="E101" s="3">
+      <c r="E101" s="3" t="n">
         <v>46307</v>
       </c>
-      <c r="F101" s="5">
+      <c r="F101" s="5" t="n">
         <v>4082.04</v>
       </c>
-      <c r="G101" s="5">
+      <c r="G101" s="5" t="n">
         <v>4082.04</v>
       </c>
       <c r="H101" s="3"/>
-      <c r="I101" s="6">
-        <v>11</v>
+      <c r="I101" s="6" t="n">
+        <v>14</v>
       </c>
       <c r="J101" s="4" t="s">
         <v>189</v>
@@ -5317,76 +5092,76 @@
       <c r="N101" s="4"/>
       <c r="O101" s="4"/>
     </row>
-    <row r="102" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="3">
-        <v>46266</v>
+    <row r="102" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A102" s="3" t="n">
+        <v>46248</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>193</v>
+        <v>258</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="E102" s="3">
+        <v>259</v>
+      </c>
+      <c r="E102" s="3" t="n">
         <v>46308</v>
       </c>
-      <c r="F102" s="5">
-        <v>18600</v>
-      </c>
-      <c r="G102" s="5">
-        <v>18600</v>
+      <c r="F102" s="5" t="n">
+        <v>23355.33</v>
+      </c>
+      <c r="G102" s="5" t="n">
+        <v>23355.33</v>
       </c>
       <c r="H102" s="3"/>
-      <c r="I102" s="6">
-        <v>10</v>
+      <c r="I102" s="6" t="n">
+        <v>13</v>
       </c>
       <c r="J102" s="4" t="s">
-        <v>26</v>
+        <v>189</v>
       </c>
       <c r="K102" s="4" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="L102" s="4"/>
       <c r="M102" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N102" s="4"/>
       <c r="O102" s="4"/>
     </row>
-    <row r="103" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="3">
-        <v>46248</v>
+    <row r="103" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A103" s="3" t="n">
+        <v>46266</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>260</v>
+        <v>193</v>
       </c>
       <c r="D103" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="E103" s="3">
+      <c r="E103" s="3" t="n">
         <v>46308</v>
       </c>
-      <c r="F103" s="5">
-        <v>23355.33</v>
-      </c>
-      <c r="G103" s="5">
-        <v>23355.33</v>
+      <c r="F103" s="5" t="n">
+        <v>18600</v>
+      </c>
+      <c r="G103" s="5" t="n">
+        <v>18600</v>
       </c>
       <c r="H103" s="3"/>
-      <c r="I103" s="6">
-        <v>10</v>
+      <c r="I103" s="6" t="n">
+        <v>13</v>
       </c>
       <c r="J103" s="4" t="s">
-        <v>189</v>
+        <v>26</v>
       </c>
       <c r="K103" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="L103" s="4"/>
       <c r="M103" s="4" t="s">
@@ -5395,8 +5170,8 @@
       <c r="N103" s="4"/>
       <c r="O103" s="4"/>
     </row>
-    <row r="104" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="3">
+    <row r="104" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A104" s="3" t="n">
         <v>46234</v>
       </c>
       <c r="B104" s="4" t="s">
@@ -5408,18 +5183,18 @@
       <c r="D104" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="E104" s="3">
+      <c r="E104" s="3" t="n">
         <v>46309</v>
       </c>
-      <c r="F104" s="5">
+      <c r="F104" s="5" t="n">
         <v>3789.1</v>
       </c>
-      <c r="G104" s="5">
+      <c r="G104" s="5" t="n">
         <v>3789.1</v>
       </c>
       <c r="H104" s="3"/>
-      <c r="I104" s="6">
-        <v>9</v>
+      <c r="I104" s="6" t="n">
+        <v>12</v>
       </c>
       <c r="J104" s="4" t="s">
         <v>189</v>
@@ -5434,8 +5209,8 @@
       <c r="N104" s="4"/>
       <c r="O104" s="4"/>
     </row>
-    <row r="105" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="3">
+    <row r="105" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A105" s="3" t="n">
         <v>46268</v>
       </c>
       <c r="B105" s="4" t="s">
@@ -5447,18 +5222,18 @@
       <c r="D105" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="E105" s="3">
+      <c r="E105" s="3" t="n">
         <v>46310</v>
       </c>
-      <c r="F105" s="5">
+      <c r="F105" s="5" t="n">
         <v>2754</v>
       </c>
-      <c r="G105" s="5">
+      <c r="G105" s="5" t="n">
         <v>2754</v>
       </c>
       <c r="H105" s="3"/>
-      <c r="I105" s="6">
-        <v>8</v>
+      <c r="I105" s="6" t="n">
+        <v>11</v>
       </c>
       <c r="J105" s="4" t="s">
         <v>183</v>
@@ -5473,8 +5248,8 @@
       <c r="N105" s="4"/>
       <c r="O105" s="4"/>
     </row>
-    <row r="106" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="3">
+    <row r="106" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A106" s="3" t="n">
         <v>46258</v>
       </c>
       <c r="B106" s="4" t="s">
@@ -5486,18 +5261,18 @@
       <c r="D106" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="E106" s="3">
+      <c r="E106" s="3" t="n">
         <v>46311</v>
       </c>
-      <c r="F106" s="5">
+      <c r="F106" s="5" t="n">
         <v>6247.5</v>
       </c>
-      <c r="G106" s="5">
+      <c r="G106" s="5" t="n">
         <v>11266.12</v>
       </c>
       <c r="H106" s="3"/>
-      <c r="I106" s="6">
-        <v>7</v>
+      <c r="I106" s="6" t="n">
+        <v>10</v>
       </c>
       <c r="J106" s="4" t="s">
         <v>189</v>
@@ -5512,8 +5287,8 @@
       <c r="N106" s="4"/>
       <c r="O106" s="4"/>
     </row>
-    <row r="107" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="3">
+    <row r="107" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A107" s="3" t="n">
         <v>46262</v>
       </c>
       <c r="B107" s="4" t="s">
@@ -5525,21 +5300,21 @@
       <c r="D107" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="E107" s="3">
+      <c r="E107" s="3" t="n">
         <v>46311</v>
       </c>
-      <c r="F107" s="5">
-        <v>7694.4</v>
-      </c>
-      <c r="G107" s="5">
-        <v>7694.4</v>
+      <c r="F107" s="5" t="n">
+        <v>11660.11</v>
+      </c>
+      <c r="G107" s="5" t="n">
+        <v>11660.11</v>
       </c>
       <c r="H107" s="3"/>
-      <c r="I107" s="6">
-        <v>7</v>
+      <c r="I107" s="6" t="n">
+        <v>10</v>
       </c>
       <c r="J107" s="4" t="s">
-        <v>26</v>
+        <v>189</v>
       </c>
       <c r="K107" s="4" t="s">
         <v>213</v>
@@ -5551,8 +5326,8 @@
       <c r="N107" s="4"/>
       <c r="O107" s="4"/>
     </row>
-    <row r="108" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="3">
+    <row r="108" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A108" s="3" t="n">
         <v>46262</v>
       </c>
       <c r="B108" s="4" t="s">
@@ -5564,21 +5339,21 @@
       <c r="D108" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="E108" s="3">
+      <c r="E108" s="3" t="n">
         <v>46311</v>
       </c>
-      <c r="F108" s="5">
-        <v>11660.11</v>
-      </c>
-      <c r="G108" s="5">
-        <v>11660.11</v>
+      <c r="F108" s="5" t="n">
+        <v>7694.4</v>
+      </c>
+      <c r="G108" s="5" t="n">
+        <v>7694.4</v>
       </c>
       <c r="H108" s="3"/>
-      <c r="I108" s="6">
-        <v>7</v>
+      <c r="I108" s="6" t="n">
+        <v>10</v>
       </c>
       <c r="J108" s="4" t="s">
-        <v>189</v>
+        <v>26</v>
       </c>
       <c r="K108" s="4" t="s">
         <v>213</v>
@@ -5590,8 +5365,8 @@
       <c r="N108" s="4"/>
       <c r="O108" s="4"/>
     </row>
-    <row r="109" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="3">
+    <row r="109" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A109" s="3" t="n">
         <v>46258</v>
       </c>
       <c r="B109" s="4" t="s">
@@ -5603,18 +5378,18 @@
       <c r="D109" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="E109" s="3">
+      <c r="E109" s="3" t="n">
         <v>46313</v>
       </c>
-      <c r="F109" s="5">
+      <c r="F109" s="5" t="n">
         <v>6247.5</v>
       </c>
-      <c r="G109" s="5">
+      <c r="G109" s="5" t="n">
         <v>6247.5</v>
       </c>
       <c r="H109" s="3"/>
-      <c r="I109" s="6">
-        <v>5</v>
+      <c r="I109" s="6" t="n">
+        <v>8</v>
       </c>
       <c r="J109" s="4" t="s">
         <v>189</v>
@@ -5629,8 +5404,8 @@
       <c r="N109" s="4"/>
       <c r="O109" s="4"/>
     </row>
-    <row r="110" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="3">
+    <row r="110" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A110" s="3" t="n">
         <v>46286</v>
       </c>
       <c r="B110" s="4" t="s">
@@ -5642,18 +5417,18 @@
       <c r="D110" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="E110" s="3">
+      <c r="E110" s="3" t="n">
         <v>46314</v>
       </c>
-      <c r="F110" s="5">
+      <c r="F110" s="5" t="n">
         <v>5475.86</v>
       </c>
-      <c r="G110" s="5">
+      <c r="G110" s="5" t="n">
         <v>5475.86</v>
       </c>
       <c r="H110" s="3"/>
-      <c r="I110" s="6">
-        <v>4</v>
+      <c r="I110" s="6" t="n">
+        <v>7</v>
       </c>
       <c r="J110" s="4" t="s">
         <v>189</v>
@@ -5668,8 +5443,8 @@
       <c r="N110" s="4"/>
       <c r="O110" s="4"/>
     </row>
-    <row r="111" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="3">
+    <row r="111" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A111" s="3" t="n">
         <v>46265</v>
       </c>
       <c r="B111" s="4" t="s">
@@ -5681,18 +5456,18 @@
       <c r="D111" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="E111" s="3">
+      <c r="E111" s="3" t="n">
         <v>46315</v>
       </c>
-      <c r="F111" s="5">
+      <c r="F111" s="5" t="n">
         <v>4750</v>
       </c>
-      <c r="G111" s="5">
+      <c r="G111" s="5" t="n">
         <v>4750</v>
       </c>
       <c r="H111" s="3"/>
-      <c r="I111" s="6">
-        <v>3</v>
+      <c r="I111" s="6" t="n">
+        <v>6</v>
       </c>
       <c r="J111" s="4" t="s">
         <v>189</v>
@@ -5707,8 +5482,8 @@
       <c r="N111" s="4"/>
       <c r="O111" s="4"/>
     </row>
-    <row r="112" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="3">
+    <row r="112" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A112" s="3" t="n">
         <v>46280</v>
       </c>
       <c r="B112" s="4" t="s">
@@ -5720,18 +5495,18 @@
       <c r="D112" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="E112" s="3">
+      <c r="E112" s="3" t="n">
         <v>46315</v>
       </c>
-      <c r="F112" s="5">
+      <c r="F112" s="5" t="n">
         <v>9196.5</v>
       </c>
-      <c r="G112" s="5">
+      <c r="G112" s="5" t="n">
         <v>12695.59</v>
       </c>
       <c r="H112" s="3"/>
-      <c r="I112" s="6">
-        <v>3</v>
+      <c r="I112" s="6" t="n">
+        <v>6</v>
       </c>
       <c r="J112" s="4" t="s">
         <v>189</v>
@@ -5746,8 +5521,8 @@
       <c r="N112" s="4"/>
       <c r="O112" s="4"/>
     </row>
-    <row r="113" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="3">
+    <row r="113" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A113" s="3" t="n">
         <v>46287</v>
       </c>
       <c r="B113" s="4" t="s">
@@ -5759,18 +5534,18 @@
       <c r="D113" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="E113" s="3">
+      <c r="E113" s="3" t="n">
         <v>46315</v>
       </c>
-      <c r="F113" s="5">
-        <v>4466.2700000000004</v>
-      </c>
-      <c r="G113" s="5">
-        <v>4466.2700000000004</v>
+      <c r="F113" s="5" t="n">
+        <v>4466.27</v>
+      </c>
+      <c r="G113" s="5" t="n">
+        <v>4466.27</v>
       </c>
       <c r="H113" s="3"/>
-      <c r="I113" s="6">
-        <v>3</v>
+      <c r="I113" s="6" t="n">
+        <v>6</v>
       </c>
       <c r="J113" s="4" t="s">
         <v>189</v>
@@ -5785,8 +5560,8 @@
       <c r="N113" s="4"/>
       <c r="O113" s="4"/>
     </row>
-    <row r="114" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="3">
+    <row r="114" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A114" s="3" t="n">
         <v>46280</v>
       </c>
       <c r="B114" s="4" t="s">
@@ -5798,18 +5573,18 @@
       <c r="D114" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="E114" s="3">
+      <c r="E114" s="3" t="n">
         <v>46315</v>
       </c>
-      <c r="F114" s="5">
+      <c r="F114" s="5" t="n">
         <v>1600</v>
       </c>
-      <c r="G114" s="5">
+      <c r="G114" s="5" t="n">
         <v>1600</v>
       </c>
       <c r="H114" s="3"/>
-      <c r="I114" s="6">
-        <v>3</v>
+      <c r="I114" s="6" t="n">
+        <v>6</v>
       </c>
       <c r="J114" s="4" t="s">
         <v>189</v>
@@ -5824,8 +5599,8 @@
       <c r="N114" s="4"/>
       <c r="O114" s="4"/>
     </row>
-    <row r="115" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="3">
+    <row r="115" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A115" s="3" t="n">
         <v>46287</v>
       </c>
       <c r="B115" s="4" t="s">
@@ -5837,18 +5612,18 @@
       <c r="D115" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="E115" s="3">
+      <c r="E115" s="3" t="n">
         <v>46315</v>
       </c>
-      <c r="F115" s="5">
+      <c r="F115" s="5" t="n">
         <v>784.63</v>
       </c>
-      <c r="G115" s="5">
+      <c r="G115" s="5" t="n">
         <v>979.25</v>
       </c>
       <c r="H115" s="3"/>
-      <c r="I115" s="6">
-        <v>3</v>
+      <c r="I115" s="6" t="n">
+        <v>6</v>
       </c>
       <c r="J115" s="4" t="s">
         <v>18</v>
@@ -5863,8 +5638,8 @@
       <c r="N115" s="4"/>
       <c r="O115" s="4"/>
     </row>
-    <row r="116" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="3">
+    <row r="116" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A116" s="3" t="n">
         <v>46266</v>
       </c>
       <c r="B116" s="4" t="s">
@@ -5876,18 +5651,18 @@
       <c r="D116" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="E116" s="3">
+      <c r="E116" s="3" t="n">
         <v>46315</v>
       </c>
-      <c r="F116" s="5">
+      <c r="F116" s="5" t="n">
         <v>18600</v>
       </c>
-      <c r="G116" s="5">
+      <c r="G116" s="5" t="n">
         <v>18600</v>
       </c>
       <c r="H116" s="3"/>
-      <c r="I116" s="6">
-        <v>3</v>
+      <c r="I116" s="6" t="n">
+        <v>6</v>
       </c>
       <c r="J116" s="4" t="s">
         <v>26</v>
@@ -5902,8 +5677,8 @@
       <c r="N116" s="4"/>
       <c r="O116" s="4"/>
     </row>
-    <row r="117" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="3">
+    <row r="117" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A117" s="3" t="n">
         <v>46253</v>
       </c>
       <c r="B117" s="4" t="s">
@@ -5915,18 +5690,18 @@
       <c r="D117" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="E117" s="3">
+      <c r="E117" s="3" t="n">
         <v>46316</v>
       </c>
-      <c r="F117" s="5">
+      <c r="F117" s="5" t="n">
         <v>1452.6</v>
       </c>
-      <c r="G117" s="5">
+      <c r="G117" s="5" t="n">
         <v>1452.6</v>
       </c>
       <c r="H117" s="3"/>
-      <c r="I117" s="6">
-        <v>2</v>
+      <c r="I117" s="6" t="n">
+        <v>5</v>
       </c>
       <c r="J117" s="4" t="s">
         <v>18</v>
@@ -5941,8 +5716,8 @@
       <c r="N117" s="4"/>
       <c r="O117" s="4"/>
     </row>
-    <row r="118" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="3">
+    <row r="118" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A118" s="3" t="n">
         <v>46288</v>
       </c>
       <c r="B118" s="4" t="s">
@@ -5954,18 +5729,18 @@
       <c r="D118" s="4" t="s">
         <v>299</v>
       </c>
-      <c r="E118" s="3">
+      <c r="E118" s="3" t="n">
         <v>46316</v>
       </c>
-      <c r="F118" s="5">
-        <v>4772.8999999999996</v>
-      </c>
-      <c r="G118" s="5">
-        <v>4772.8999999999996</v>
+      <c r="F118" s="5" t="n">
+        <v>4772.9</v>
+      </c>
+      <c r="G118" s="5" t="n">
+        <v>4772.9</v>
       </c>
       <c r="H118" s="3"/>
-      <c r="I118" s="6">
-        <v>2</v>
+      <c r="I118" s="6" t="n">
+        <v>5</v>
       </c>
       <c r="J118" s="4" t="s">
         <v>189</v>
@@ -5980,8 +5755,8 @@
       <c r="N118" s="4"/>
       <c r="O118" s="4"/>
     </row>
-    <row r="119" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="3">
+    <row r="119" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A119" s="3" t="n">
         <v>46288</v>
       </c>
       <c r="B119" s="4" t="s">
@@ -5993,18 +5768,18 @@
       <c r="D119" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="E119" s="3">
+      <c r="E119" s="3" t="n">
         <v>46316</v>
       </c>
-      <c r="F119" s="5">
-        <v>2334.2399999999998</v>
-      </c>
-      <c r="G119" s="5">
-        <v>2334.2399999999998</v>
+      <c r="F119" s="5" t="n">
+        <v>2334.24</v>
+      </c>
+      <c r="G119" s="5" t="n">
+        <v>2334.24</v>
       </c>
       <c r="H119" s="3"/>
-      <c r="I119" s="6">
-        <v>2</v>
+      <c r="I119" s="6" t="n">
+        <v>5</v>
       </c>
       <c r="J119" s="4" t="s">
         <v>18</v>
@@ -6019,8 +5794,8 @@
       <c r="N119" s="4"/>
       <c r="O119" s="4"/>
     </row>
-    <row r="120" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="3">
+    <row r="120" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A120" s="3" t="n">
         <v>46287</v>
       </c>
       <c r="B120" s="4" t="s">
@@ -6032,18 +5807,18 @@
       <c r="D120" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="E120" s="3">
+      <c r="E120" s="3" t="n">
         <v>46317</v>
       </c>
-      <c r="F120" s="5">
-        <v>9617.7999999999993</v>
-      </c>
-      <c r="G120" s="5">
-        <v>9617.7999999999993</v>
+      <c r="F120" s="5" t="n">
+        <v>9617.8</v>
+      </c>
+      <c r="G120" s="5" t="n">
+        <v>9617.8</v>
       </c>
       <c r="H120" s="3"/>
-      <c r="I120" s="6">
-        <v>1</v>
+      <c r="I120" s="6" t="n">
+        <v>4</v>
       </c>
       <c r="J120" s="4" t="s">
         <v>189</v>
@@ -6058,7 +5833,262 @@
       <c r="N120" s="4"/>
       <c r="O120" s="4"/>
     </row>
+    <row r="121" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A121" s="3" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C121" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="D121" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>46318</v>
+      </c>
+      <c r="F121" s="5" t="n">
+        <v>2992</v>
+      </c>
+      <c r="G121" s="5" t="n">
+        <v>2992</v>
+      </c>
+      <c r="H121" s="3"/>
+      <c r="I121" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J121" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="K121" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="L121" s="4"/>
+      <c r="M121" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="N121" s="4"/>
+      <c r="O121" s="4"/>
+    </row>
+    <row r="122" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A122" s="3" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B122" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C122" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="D122" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>46318</v>
+      </c>
+      <c r="F122" s="5" t="n">
+        <v>5206.77</v>
+      </c>
+      <c r="G122" s="5" t="n">
+        <v>10139.15</v>
+      </c>
+      <c r="H122" s="3"/>
+      <c r="I122" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J122" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="K122" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="L122" s="4"/>
+      <c r="M122" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="N122" s="4"/>
+      <c r="O122" s="4"/>
+    </row>
+    <row r="123" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A123" s="3" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B123" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C123" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="D123" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>46318</v>
+      </c>
+      <c r="F123" s="5" t="n">
+        <v>3714.54</v>
+      </c>
+      <c r="G123" s="5" t="n">
+        <v>3714.54</v>
+      </c>
+      <c r="H123" s="3"/>
+      <c r="I123" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J123" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="K123" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="L123" s="4"/>
+      <c r="M123" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="N123" s="4"/>
+      <c r="O123" s="4"/>
+    </row>
+    <row r="124" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A124" s="3" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B124" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="C124" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="D124" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>46318</v>
+      </c>
+      <c r="F124" s="5" t="n">
+        <v>7694.4</v>
+      </c>
+      <c r="G124" s="5" t="n">
+        <v>7694.4</v>
+      </c>
+      <c r="H124" s="3"/>
+      <c r="I124" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J124" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K124" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="L124" s="4"/>
+      <c r="M124" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="N124" s="4"/>
+      <c r="O124" s="4"/>
+    </row>
+    <row r="125" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A125" s="3" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B125" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="C125" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="D125" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>46318</v>
+      </c>
+      <c r="F125" s="5" t="n">
+        <v>11660.11</v>
+      </c>
+      <c r="G125" s="5" t="n">
+        <v>11660.11</v>
+      </c>
+      <c r="H125" s="3"/>
+      <c r="I125" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J125" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="K125" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="L125" s="4"/>
+      <c r="M125" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="N125" s="4"/>
+      <c r="O125" s="4"/>
+    </row>
+    <row r="126" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A126" s="3" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B126" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C126" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D126" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>46318</v>
+      </c>
+      <c r="F126" s="5" t="n">
+        <v>879.12</v>
+      </c>
+      <c r="G126" s="5" t="n">
+        <v>879.12</v>
+      </c>
+      <c r="H126" s="3"/>
+      <c r="I126" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J126" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="K126" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="L126" s="4"/>
+      <c r="M126" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="N126" s="4"/>
+      <c r="O126" s="4"/>
+    </row>
+    <row r="127" customHeight="true" ht="13.5" customFormat="true" s="1">
+      <c r="A127" s="7"/>
+      <c r="B127" s="8"/>
+      <c r="C127" s="8"/>
+      <c r="D127" s="8"/>
+      <c r="E127" s="8"/>
+      <c r="F127" s="9" t="n">
+        <v>724246.69</v>
+      </c>
+      <c r="G127" s="9" t="n">
+        <v>766903.69</v>
+      </c>
+      <c r="H127" s="8"/>
+      <c r="I127" s="8"/>
+      <c r="J127" s="8"/>
+      <c r="K127" s="8"/>
+      <c r="L127" s="8"/>
+      <c r="M127" s="8"/>
+      <c r="N127" s="8"/>
+      <c r="O127" s="10"/>
+    </row>
   </sheetData>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup orientation="default" cellComments="none"/>
 </worksheet>
 </file>
--- a/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
+++ b/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
@@ -1,19 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WINDOWS\Desktop\dados planilhas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CD9840F-26CA-417F-A744-7E9A7C54B319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0" showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="XLS_Grid_LANCAMENTO A RECEBER" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr refMode="A1"/>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="743" uniqueCount="321">
   <si>
     <t>Dt.Emissão</t>
   </si>
@@ -660,12 +672,6 @@
     <t>00198158000007694400000003473568000003158817</t>
   </si>
   <si>
-    <t>01007249.1</t>
-  </si>
-  <si>
-    <t>70793158000011660110001121205064100656766915</t>
-  </si>
-  <si>
     <t>FERMATA LTDA</t>
   </si>
   <si>
@@ -720,18 +726,18 @@
     <t>34196158500002051221090002617698120992717000</t>
   </si>
   <si>
+    <t>01007265.2</t>
+  </si>
+  <si>
+    <t>00192158700007694400000003473568000003158917</t>
+  </si>
+  <si>
     <t>01007249.2</t>
   </si>
   <si>
     <t>70792158700011660110001121205064100656766923</t>
   </si>
   <si>
-    <t>01007265.2</t>
-  </si>
-  <si>
-    <t>00192158700007694400000003473568000003158917</t>
-  </si>
-  <si>
     <t>01006920.3</t>
   </si>
   <si>
@@ -762,18 +768,18 @@
     <t>70791159200010080000001121205064100656766220</t>
   </si>
   <si>
+    <t>01007249.3</t>
+  </si>
+  <si>
+    <t>70791159400011660110001121205064100656766931</t>
+  </si>
+  <si>
     <t>01007265.3</t>
   </si>
   <si>
     <t>00199159400007694400000003473568000003159017</t>
   </si>
   <si>
-    <t>01007249.3</t>
-  </si>
-  <si>
-    <t>70791159400011660110001121205064100656766931</t>
-  </si>
-  <si>
     <t xml:space="preserve">ZOE MED COMERCIO DE PRODUTOS MEDICOS HOSPITALARES </t>
   </si>
   <si>
@@ -819,10 +825,10 @@
     <t>23797160000002754000435090000000130200304920</t>
   </si>
   <si>
-    <t>01007222.1</t>
-  </si>
-  <si>
-    <t>70798160100011266120001121205064100656766576</t>
+    <t>01007265.4</t>
+  </si>
+  <si>
+    <t>00191160100007694400000003473568000003159117</t>
   </si>
   <si>
     <t>01007249.4</t>
@@ -831,12 +837,6 @@
     <t>70791160100011660110001121205064100656766949</t>
   </si>
   <si>
-    <t>01007265.4</t>
-  </si>
-  <si>
-    <t>00191160100007694400000003473568000003159117</t>
-  </si>
-  <si>
     <t>01007222.2</t>
   </si>
   <si>
@@ -876,15 +876,6 @@
     <t>70791160500004466270001121205064100656768713</t>
   </si>
   <si>
-    <t>MULTIMAIS ATACADO LTDA</t>
-  </si>
-  <si>
-    <t>01007400.2</t>
-  </si>
-  <si>
-    <t>70798160500001600000001121205064100656768069</t>
-  </si>
-  <si>
     <t>LOPES BARRETO COMERCIO DE PRODUTOS MEDICOS LTDA</t>
   </si>
   <si>
@@ -966,52 +957,66 @@
     <t>70797160800003714540001121205064100656767541</t>
   </si>
   <si>
+    <t>01007249.5</t>
+  </si>
+  <si>
+    <t>70791160800011660110001121205064100656766956</t>
+  </si>
+  <si>
     <t>01007265.5</t>
   </si>
   <si>
     <t>00196160800007694400000003473568000003159217</t>
   </si>
   <si>
-    <t>01007249.5</t>
-  </si>
-  <si>
-    <t>70791160800011660110001121205064100656766956</t>
-  </si>
-  <si>
     <t>01007217.3</t>
   </si>
   <si>
     <t>23793160800000879120435090000000125900304920</t>
+  </si>
+  <si>
+    <t>COBERMED COMERCIO DE MATERIAIS MEDICOS LTDA</t>
+  </si>
+  <si>
+    <t>01007194.3</t>
+  </si>
+  <si>
+    <t>70794160900006265000001121205064100656766667</t>
+  </si>
+  <si>
+    <t>01007342.2</t>
+  </si>
+  <si>
+    <t>70798161100005475860001121205064100656768671</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt formatCode="dd/MM/yyyy" numFmtId="164"/>
-    <numFmt formatCode="###,###,##0.00" numFmtId="165"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="###,###,##0.00"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
       <charset val="1"/>
     </font>
     <font>
+      <sz val="8"/>
       <color rgb="FF000000"/>
-      <sz val="8"/>
       <name val="Arial"/>
       <charset val="1"/>
     </font>
     <font>
+      <sz val="8"/>
       <color rgb="FF000000"/>
-      <sz val="8"/>
       <name val="Segoe UI"/>
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1030,14 +1035,8 @@
         <bgColor rgb="FF7EA6D1"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0F0F0"/>
-        <bgColor rgb="FFF0F0F0"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="5">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1060,124 +1059,386 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFA0A0A0"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FFA0A0A0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFA0A0A0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFA0A0A0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFA0A0A0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFA0A0A0"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFA0A0A0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFA0A0A0"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" shrinkToFit="false" wrapText="false"/>
-      <protection hidden="false" locked="true"/>
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="164" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="165" xfId="0">
-      <alignment horizontal="right" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="right" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="2" fillId="4" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="3" fillId="4" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="4" fontId="1" numFmtId="165" xfId="0">
-      <alignment horizontal="right" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="4" fillId="4" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="true" summaryRight="true"/>
-  </sheetPr>
-  <dimension ref="A1:O127"/>
-  <sheetFormatPr defaultColWidth="12.140625" customHeight="true" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:O125"/>
+  <sheetFormatPr defaultColWidth="12.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col max="1" min="1" style="1" width="11.85546875" customWidth="true"/>
-    <col max="2" min="2" style="1" width="22.28515625" customWidth="true"/>
-    <col max="3" min="3" style="1" width="30.28515625" customWidth="true"/>
-    <col max="4" min="4" style="1" width="12.85546875" customWidth="true"/>
-    <col max="5" min="5" style="1" width="24.7109375" customWidth="true"/>
-    <col max="6" min="6" style="1" width="9.140625" customWidth="true"/>
-    <col max="7" min="7" style="1" width="27.28515625" customWidth="true"/>
-    <col max="8" min="8" style="1" width="28.140625" customWidth="true"/>
-    <col max="9" min="9" style="1" width="9.140625" customWidth="true"/>
-    <col max="10" min="10" style="1" width="26.28515625" customWidth="true"/>
-    <col max="11" min="11" style="1" width="3.7109375" customWidth="true"/>
-    <col max="12" min="12" style="1" width="43.42578125" customWidth="true"/>
-    <col max="13" min="13" style="1" width="60.5703125" customWidth="true"/>
-    <col max="14" min="14" style="1" width="26.28515625" customWidth="true"/>
-    <col max="15" min="15" style="1" width="43.42578125" customWidth="true"/>
-    <col max="16384" min="16" style="1" width="12.140625"/>
+    <col min="1" max="1" width="11.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="30.28515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="24.7109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="27.28515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="28.140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="9.140625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="26.28515625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="3.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="43.42578125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="60.5703125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="26.28515625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="43.42578125" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="12.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="true" ht="27" customFormat="true" s="1">
+    <row r="1" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1224,8 +1485,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A2" s="3" t="n">
+    <row r="2" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
         <v>45296</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -1237,18 +1498,18 @@
       <c r="D2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="3">
         <v>45326</v>
       </c>
-      <c r="F2" s="5" t="n">
+      <c r="F2" s="5">
         <v>5418</v>
       </c>
-      <c r="G2" s="5" t="n">
-        <v>9391.78</v>
+      <c r="G2" s="5">
+        <v>9391.7800000000007</v>
       </c>
       <c r="H2" s="3"/>
-      <c r="I2" s="6" t="n">
-        <v>995</v>
+      <c r="I2" s="6">
+        <v>996</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>18</v>
@@ -1263,8 +1524,8 @@
       <c r="N2" s="4"/>
       <c r="O2" s="4"/>
     </row>
-    <row r="3" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A3" s="3" t="n">
+    <row r="3" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
         <v>45296</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -1276,18 +1537,18 @@
       <c r="D3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="3">
         <v>45346</v>
       </c>
-      <c r="F3" s="5" t="n">
+      <c r="F3" s="5">
         <v>5418</v>
       </c>
-      <c r="G3" s="5" t="n">
+      <c r="G3" s="5">
         <v>5418</v>
       </c>
       <c r="H3" s="3"/>
-      <c r="I3" s="6" t="n">
-        <v>975</v>
+      <c r="I3" s="6">
+        <v>976</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>18</v>
@@ -1302,8 +1563,8 @@
       <c r="N3" s="4"/>
       <c r="O3" s="4"/>
     </row>
-    <row r="4" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A4" s="3" t="n">
+    <row r="4" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
         <v>45322</v>
       </c>
       <c r="B4" s="4" t="s">
@@ -1315,18 +1576,18 @@
       <c r="D4" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="3">
         <v>45350</v>
       </c>
-      <c r="F4" s="5" t="n">
+      <c r="F4" s="5">
         <v>816</v>
       </c>
-      <c r="G4" s="5" t="n">
-        <v>1264.87</v>
+      <c r="G4" s="5">
+        <v>1264.8699999999999</v>
       </c>
       <c r="H4" s="3"/>
-      <c r="I4" s="6" t="n">
-        <v>971</v>
+      <c r="I4" s="6">
+        <v>972</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>26</v>
@@ -1341,8 +1602,8 @@
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
     </row>
-    <row r="5" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A5" s="3" t="n">
+    <row r="5" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
         <v>45296</v>
       </c>
       <c r="B5" s="4" t="s">
@@ -1354,18 +1615,18 @@
       <c r="D5" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="3">
         <v>45356</v>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="F5" s="5">
         <v>5418</v>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="G5" s="5">
         <v>5418</v>
       </c>
       <c r="H5" s="3"/>
-      <c r="I5" s="6" t="n">
-        <v>965</v>
+      <c r="I5" s="6">
+        <v>966</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>18</v>
@@ -1380,8 +1641,8 @@
       <c r="N5" s="4"/>
       <c r="O5" s="4"/>
     </row>
-    <row r="6" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A6" s="3" t="n">
+    <row r="6" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
         <v>45306</v>
       </c>
       <c r="B6" s="4" t="s">
@@ -1393,18 +1654,18 @@
       <c r="D6" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="3">
         <v>45362</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="5">
         <v>384</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="G6" s="5">
         <v>384</v>
       </c>
       <c r="H6" s="3"/>
-      <c r="I6" s="6" t="n">
-        <v>959</v>
+      <c r="I6" s="6">
+        <v>960</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>26</v>
@@ -1419,8 +1680,8 @@
       <c r="N6" s="4"/>
       <c r="O6" s="4"/>
     </row>
-    <row r="7" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A7" s="3" t="n">
+    <row r="7" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
         <v>45322</v>
       </c>
       <c r="B7" s="4" t="s">
@@ -1432,18 +1693,18 @@
       <c r="D7" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="3">
         <v>45364</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F7" s="5">
         <v>816</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="G7" s="5">
         <v>816</v>
       </c>
       <c r="H7" s="3"/>
-      <c r="I7" s="6" t="n">
-        <v>957</v>
+      <c r="I7" s="6">
+        <v>958</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>26</v>
@@ -1458,8 +1719,8 @@
       <c r="N7" s="4"/>
       <c r="O7" s="4"/>
     </row>
-    <row r="8" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A8" s="3" t="n">
+    <row r="8" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
         <v>45322</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -1471,18 +1732,18 @@
       <c r="D8" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="3">
         <v>45378</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F8" s="5">
         <v>816</v>
       </c>
-      <c r="G8" s="5" t="n">
+      <c r="G8" s="5">
         <v>816</v>
       </c>
       <c r="H8" s="3"/>
-      <c r="I8" s="6" t="n">
-        <v>943</v>
+      <c r="I8" s="6">
+        <v>944</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>26</v>
@@ -1497,8 +1758,8 @@
       <c r="N8" s="4"/>
       <c r="O8" s="4"/>
     </row>
-    <row r="9" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A9" s="3" t="n">
+    <row r="9" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
         <v>45433</v>
       </c>
       <c r="B9" s="4" t="s">
@@ -1510,18 +1771,18 @@
       <c r="D9" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" s="3">
         <v>45463</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="F9" s="5">
         <v>873.6</v>
       </c>
-      <c r="G9" s="5" t="n">
+      <c r="G9" s="5">
         <v>1674.52</v>
       </c>
       <c r="H9" s="3"/>
-      <c r="I9" s="6" t="n">
-        <v>858</v>
+      <c r="I9" s="6">
+        <v>859</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>18</v>
@@ -1536,8 +1797,8 @@
       <c r="N9" s="4"/>
       <c r="O9" s="4"/>
     </row>
-    <row r="10" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A10" s="3" t="n">
+    <row r="10" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
         <v>45433</v>
       </c>
       <c r="B10" s="4" t="s">
@@ -1549,18 +1810,18 @@
       <c r="D10" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="E10" s="3">
         <v>45493</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="F10" s="5">
         <v>873.6</v>
       </c>
-      <c r="G10" s="5" t="n">
+      <c r="G10" s="5">
         <v>873.6</v>
       </c>
       <c r="H10" s="3"/>
-      <c r="I10" s="6" t="n">
-        <v>828</v>
+      <c r="I10" s="6">
+        <v>829</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>18</v>
@@ -1575,8 +1836,8 @@
       <c r="N10" s="4"/>
       <c r="O10" s="4"/>
     </row>
-    <row r="11" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A11" s="3" t="n">
+    <row r="11" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
         <v>45433</v>
       </c>
       <c r="B11" s="4" t="s">
@@ -1588,18 +1849,18 @@
       <c r="D11" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="E11" s="3">
         <v>45523</v>
       </c>
-      <c r="F11" s="5" t="n">
+      <c r="F11" s="5">
         <v>873.6</v>
       </c>
-      <c r="G11" s="5" t="n">
+      <c r="G11" s="5">
         <v>873.6</v>
       </c>
       <c r="H11" s="3"/>
-      <c r="I11" s="6" t="n">
-        <v>798</v>
+      <c r="I11" s="6">
+        <v>799</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>18</v>
@@ -1614,8 +1875,8 @@
       <c r="N11" s="4"/>
       <c r="O11" s="4"/>
     </row>
-    <row r="12" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A12" s="3" t="n">
+    <row r="12" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
         <v>45558</v>
       </c>
       <c r="B12" s="4" t="s">
@@ -1627,18 +1888,18 @@
       <c r="D12" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="E12" s="3">
         <v>45600</v>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="F12" s="5">
         <v>2000</v>
       </c>
-      <c r="G12" s="5" t="n">
+      <c r="G12" s="5">
         <v>2000</v>
       </c>
       <c r="H12" s="3"/>
-      <c r="I12" s="6" t="n">
-        <v>721</v>
+      <c r="I12" s="6">
+        <v>722</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>18</v>
@@ -1653,8 +1914,8 @@
       <c r="N12" s="4"/>
       <c r="O12" s="4"/>
     </row>
-    <row r="13" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A13" s="3" t="n">
+    <row r="13" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3">
         <v>45558</v>
       </c>
       <c r="B13" s="4" t="s">
@@ -1666,18 +1927,18 @@
       <c r="D13" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="E13" s="3">
         <v>45607</v>
       </c>
-      <c r="F13" s="5" t="n">
+      <c r="F13" s="5">
         <v>2000</v>
       </c>
-      <c r="G13" s="5" t="n">
+      <c r="G13" s="5">
         <v>3204.34</v>
       </c>
       <c r="H13" s="3"/>
-      <c r="I13" s="6" t="n">
-        <v>714</v>
+      <c r="I13" s="6">
+        <v>715</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>18</v>
@@ -1692,8 +1953,8 @@
       <c r="N13" s="4"/>
       <c r="O13" s="4"/>
     </row>
-    <row r="14" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A14" s="3" t="n">
+    <row r="14" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="3">
         <v>45552</v>
       </c>
       <c r="B14" s="4" t="s">
@@ -1705,18 +1966,18 @@
       <c r="D14" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="E14" s="3">
         <v>45608</v>
       </c>
-      <c r="F14" s="5" t="n">
-        <v>4439.9</v>
-      </c>
-      <c r="G14" s="5" t="n">
-        <v>4439.9</v>
+      <c r="F14" s="5">
+        <v>4439.8999999999996</v>
+      </c>
+      <c r="G14" s="5">
+        <v>4439.8999999999996</v>
       </c>
       <c r="H14" s="3"/>
-      <c r="I14" s="6" t="n">
-        <v>713</v>
+      <c r="I14" s="6">
+        <v>714</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>18</v>
@@ -1731,8 +1992,8 @@
       <c r="N14" s="4"/>
       <c r="O14" s="4"/>
     </row>
-    <row r="15" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A15" s="3" t="n">
+    <row r="15" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3">
         <v>45558</v>
       </c>
       <c r="B15" s="4" t="s">
@@ -1744,18 +2005,18 @@
       <c r="D15" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="E15" s="3">
         <v>45614</v>
       </c>
-      <c r="F15" s="5" t="n">
+      <c r="F15" s="5">
         <v>2000</v>
       </c>
-      <c r="G15" s="5" t="n">
+      <c r="G15" s="5">
         <v>2000</v>
       </c>
       <c r="H15" s="3"/>
-      <c r="I15" s="6" t="n">
-        <v>707</v>
+      <c r="I15" s="6">
+        <v>708</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>18</v>
@@ -1770,8 +2031,8 @@
       <c r="N15" s="4"/>
       <c r="O15" s="4"/>
     </row>
-    <row r="16" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A16" s="3" t="n">
+    <row r="16" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="3">
         <v>45546</v>
       </c>
       <c r="B16" s="4" t="s">
@@ -1783,18 +2044,18 @@
       <c r="D16" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="E16" s="3">
         <v>45615</v>
       </c>
-      <c r="F16" s="5" t="n">
-        <v>1216.86</v>
-      </c>
-      <c r="G16" s="5" t="n">
-        <v>1216.86</v>
+      <c r="F16" s="5">
+        <v>1216.8599999999999</v>
+      </c>
+      <c r="G16" s="5">
+        <v>1216.8599999999999</v>
       </c>
       <c r="H16" s="3"/>
-      <c r="I16" s="6" t="n">
-        <v>706</v>
+      <c r="I16" s="6">
+        <v>707</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>18</v>
@@ -1809,8 +2070,8 @@
       <c r="N16" s="4"/>
       <c r="O16" s="4"/>
     </row>
-    <row r="17" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A17" s="3" t="n">
+    <row r="17" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3">
         <v>45548</v>
       </c>
       <c r="B17" s="4" t="s">
@@ -1822,18 +2083,18 @@
       <c r="D17" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="E17" s="3">
         <v>45617</v>
       </c>
-      <c r="F17" s="5" t="n">
+      <c r="F17" s="5">
         <v>1843.87</v>
       </c>
-      <c r="G17" s="5" t="n">
+      <c r="G17" s="5">
         <v>1843.87</v>
       </c>
       <c r="H17" s="3"/>
-      <c r="I17" s="6" t="n">
-        <v>704</v>
+      <c r="I17" s="6">
+        <v>705</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>18</v>
@@ -1848,8 +2109,8 @@
       <c r="N17" s="4"/>
       <c r="O17" s="4"/>
     </row>
-    <row r="18" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A18" s="3" t="n">
+    <row r="18" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="3">
         <v>45546</v>
       </c>
       <c r="B18" s="4" t="s">
@@ -1861,18 +2122,18 @@
       <c r="D18" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="E18" s="3">
         <v>45622</v>
       </c>
-      <c r="F18" s="5" t="n">
-        <v>1216.86</v>
-      </c>
-      <c r="G18" s="5" t="n">
-        <v>1216.86</v>
+      <c r="F18" s="5">
+        <v>1216.8599999999999</v>
+      </c>
+      <c r="G18" s="5">
+        <v>1216.8599999999999</v>
       </c>
       <c r="H18" s="3"/>
-      <c r="I18" s="6" t="n">
-        <v>699</v>
+      <c r="I18" s="6">
+        <v>700</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>18</v>
@@ -1887,8 +2148,8 @@
       <c r="N18" s="4"/>
       <c r="O18" s="4"/>
     </row>
-    <row r="19" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A19" s="3" t="n">
+    <row r="19" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
         <v>45552</v>
       </c>
       <c r="B19" s="4" t="s">
@@ -1900,18 +2161,18 @@
       <c r="D19" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="E19" s="3">
         <v>45622</v>
       </c>
-      <c r="F19" s="5" t="n">
-        <v>4439.9</v>
-      </c>
-      <c r="G19" s="5" t="n">
-        <v>4439.9</v>
+      <c r="F19" s="5">
+        <v>4439.8999999999996</v>
+      </c>
+      <c r="G19" s="5">
+        <v>4439.8999999999996</v>
       </c>
       <c r="H19" s="3"/>
-      <c r="I19" s="6" t="n">
-        <v>699</v>
+      <c r="I19" s="6">
+        <v>700</v>
       </c>
       <c r="J19" s="4" t="s">
         <v>18</v>
@@ -1926,8 +2187,8 @@
       <c r="N19" s="4"/>
       <c r="O19" s="4"/>
     </row>
-    <row r="20" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A20" s="3" t="n">
+    <row r="20" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
         <v>45548</v>
       </c>
       <c r="B20" s="4" t="s">
@@ -1939,18 +2200,18 @@
       <c r="D20" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="E20" s="3">
         <v>45624</v>
       </c>
-      <c r="F20" s="5" t="n">
+      <c r="F20" s="5">
         <v>1843.88</v>
       </c>
-      <c r="G20" s="5" t="n">
+      <c r="G20" s="5">
         <v>1843.88</v>
       </c>
       <c r="H20" s="3"/>
-      <c r="I20" s="6" t="n">
-        <v>697</v>
+      <c r="I20" s="6">
+        <v>698</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>18</v>
@@ -1965,8 +2226,8 @@
       <c r="N20" s="4"/>
       <c r="O20" s="4"/>
     </row>
-    <row r="21" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A21" s="3" t="n">
+    <row r="21" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="3">
         <v>45632</v>
       </c>
       <c r="B21" s="4" t="s">
@@ -1978,18 +2239,18 @@
       <c r="D21" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="E21" s="3">
         <v>45688</v>
       </c>
-      <c r="F21" s="5" t="n">
-        <v>1118.4</v>
-      </c>
-      <c r="G21" s="5" t="n">
-        <v>1118.4</v>
+      <c r="F21" s="5">
+        <v>1118.4000000000001</v>
+      </c>
+      <c r="G21" s="5">
+        <v>1118.4000000000001</v>
       </c>
       <c r="H21" s="3"/>
-      <c r="I21" s="6" t="n">
-        <v>633</v>
+      <c r="I21" s="6">
+        <v>634</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>18</v>
@@ -2004,8 +2265,8 @@
       <c r="N21" s="4"/>
       <c r="O21" s="4"/>
     </row>
-    <row r="22" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A22" s="3" t="n">
+    <row r="22" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="3">
         <v>45646</v>
       </c>
       <c r="B22" s="4" t="s">
@@ -2017,18 +2278,18 @@
       <c r="D22" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="E22" s="3">
         <v>45695</v>
       </c>
-      <c r="F22" s="5" t="n">
+      <c r="F22" s="5">
         <v>3296.8</v>
       </c>
-      <c r="G22" s="5" t="n">
+      <c r="G22" s="5">
         <v>3296.8</v>
       </c>
       <c r="H22" s="3"/>
-      <c r="I22" s="6" t="n">
-        <v>626</v>
+      <c r="I22" s="6">
+        <v>627</v>
       </c>
       <c r="J22" s="4" t="s">
         <v>18</v>
@@ -2043,8 +2304,8 @@
       <c r="N22" s="4"/>
       <c r="O22" s="4"/>
     </row>
-    <row r="23" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A23" s="3" t="n">
+    <row r="23" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="3">
         <v>45636</v>
       </c>
       <c r="B23" s="4" t="s">
@@ -2056,18 +2317,18 @@
       <c r="D23" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="E23" s="3">
         <v>45699</v>
       </c>
-      <c r="F23" s="5" t="n">
+      <c r="F23" s="5">
         <v>2330</v>
       </c>
-      <c r="G23" s="5" t="n">
+      <c r="G23" s="5">
         <v>2330</v>
       </c>
       <c r="H23" s="3"/>
-      <c r="I23" s="6" t="n">
-        <v>622</v>
+      <c r="I23" s="6">
+        <v>623</v>
       </c>
       <c r="J23" s="4" t="s">
         <v>18</v>
@@ -2082,8 +2343,8 @@
       <c r="N23" s="4"/>
       <c r="O23" s="4"/>
     </row>
-    <row r="24" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A24" s="3" t="n">
+    <row r="24" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="3">
         <v>45646</v>
       </c>
       <c r="B24" s="4" t="s">
@@ -2095,18 +2356,18 @@
       <c r="D24" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="E24" s="3">
         <v>45702</v>
       </c>
-      <c r="F24" s="5" t="n">
+      <c r="F24" s="5">
         <v>3296.8</v>
       </c>
-      <c r="G24" s="5" t="n">
+      <c r="G24" s="5">
         <v>3296.8</v>
       </c>
       <c r="H24" s="3"/>
-      <c r="I24" s="6" t="n">
-        <v>619</v>
+      <c r="I24" s="6">
+        <v>620</v>
       </c>
       <c r="J24" s="4" t="s">
         <v>18</v>
@@ -2121,8 +2382,8 @@
       <c r="N24" s="4"/>
       <c r="O24" s="4"/>
     </row>
-    <row r="25" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A25" s="3" t="n">
+    <row r="25" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="3">
         <v>45677</v>
       </c>
       <c r="B25" s="4" t="s">
@@ -2134,18 +2395,18 @@
       <c r="D25" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="E25" s="3">
         <v>45705</v>
       </c>
-      <c r="F25" s="5" t="n">
+      <c r="F25" s="5">
         <v>2541</v>
       </c>
-      <c r="G25" s="5" t="n">
+      <c r="G25" s="5">
         <v>2541</v>
       </c>
       <c r="H25" s="3"/>
-      <c r="I25" s="6" t="n">
-        <v>616</v>
+      <c r="I25" s="6">
+        <v>617</v>
       </c>
       <c r="J25" s="4" t="s">
         <v>26</v>
@@ -2160,8 +2421,8 @@
       <c r="N25" s="4"/>
       <c r="O25" s="4"/>
     </row>
-    <row r="26" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A26" s="3" t="n">
+    <row r="26" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="3">
         <v>45646</v>
       </c>
       <c r="B26" s="4" t="s">
@@ -2173,18 +2434,18 @@
       <c r="D26" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="E26" s="3">
         <v>45709</v>
       </c>
-      <c r="F26" s="5" t="n">
+      <c r="F26" s="5">
         <v>3296.8</v>
       </c>
-      <c r="G26" s="5" t="n">
+      <c r="G26" s="5">
         <v>3296.8</v>
       </c>
       <c r="H26" s="3"/>
-      <c r="I26" s="6" t="n">
-        <v>612</v>
+      <c r="I26" s="6">
+        <v>613</v>
       </c>
       <c r="J26" s="4" t="s">
         <v>18</v>
@@ -2199,8 +2460,8 @@
       <c r="N26" s="4"/>
       <c r="O26" s="4"/>
     </row>
-    <row r="27" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A27" s="3" t="n">
+    <row r="27" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="3">
         <v>45677</v>
       </c>
       <c r="B27" s="4" t="s">
@@ -2212,18 +2473,18 @@
       <c r="D27" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="E27" s="3">
         <v>45712</v>
       </c>
-      <c r="F27" s="5" t="n">
+      <c r="F27" s="5">
         <v>2541</v>
       </c>
-      <c r="G27" s="5" t="n">
+      <c r="G27" s="5">
         <v>2541</v>
       </c>
       <c r="H27" s="3"/>
-      <c r="I27" s="6" t="n">
-        <v>609</v>
+      <c r="I27" s="6">
+        <v>610</v>
       </c>
       <c r="J27" s="4" t="s">
         <v>26</v>
@@ -2238,8 +2499,8 @@
       <c r="N27" s="4"/>
       <c r="O27" s="4"/>
     </row>
-    <row r="28" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A28" s="3" t="n">
+    <row r="28" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="3">
         <v>45677</v>
       </c>
       <c r="B28" s="4" t="s">
@@ -2251,18 +2512,18 @@
       <c r="D28" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="E28" s="3">
         <v>45726</v>
       </c>
-      <c r="F28" s="5" t="n">
+      <c r="F28" s="5">
         <v>2541</v>
       </c>
-      <c r="G28" s="5" t="n">
+      <c r="G28" s="5">
         <v>2541</v>
       </c>
       <c r="H28" s="3"/>
-      <c r="I28" s="6" t="n">
-        <v>595</v>
+      <c r="I28" s="6">
+        <v>596</v>
       </c>
       <c r="J28" s="4" t="s">
         <v>26</v>
@@ -2277,8 +2538,8 @@
       <c r="N28" s="4"/>
       <c r="O28" s="4"/>
     </row>
-    <row r="29" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A29" s="3" t="n">
+    <row r="29" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="3">
         <v>45699</v>
       </c>
       <c r="B29" s="4" t="s">
@@ -2290,18 +2551,18 @@
       <c r="D29" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="E29" s="3">
         <v>45727</v>
       </c>
-      <c r="F29" s="5" t="n">
+      <c r="F29" s="5">
         <v>7562.78</v>
       </c>
-      <c r="G29" s="5" t="n">
+      <c r="G29" s="5">
         <v>7562.78</v>
       </c>
       <c r="H29" s="3"/>
-      <c r="I29" s="6" t="n">
-        <v>594</v>
+      <c r="I29" s="6">
+        <v>595</v>
       </c>
       <c r="J29" s="4" t="s">
         <v>18</v>
@@ -2316,8 +2577,8 @@
       <c r="N29" s="4"/>
       <c r="O29" s="4"/>
     </row>
-    <row r="30" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A30" s="3" t="n">
+    <row r="30" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="3">
         <v>45699</v>
       </c>
       <c r="B30" s="4" t="s">
@@ -2329,18 +2590,18 @@
       <c r="D30" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="E30" s="3">
         <v>45734</v>
       </c>
-      <c r="F30" s="5" t="n">
+      <c r="F30" s="5">
         <v>7562.78</v>
       </c>
-      <c r="G30" s="5" t="n">
+      <c r="G30" s="5">
         <v>7562.78</v>
       </c>
       <c r="H30" s="3"/>
-      <c r="I30" s="6" t="n">
-        <v>587</v>
+      <c r="I30" s="6">
+        <v>588</v>
       </c>
       <c r="J30" s="4" t="s">
         <v>18</v>
@@ -2355,8 +2616,8 @@
       <c r="N30" s="4"/>
       <c r="O30" s="4"/>
     </row>
-    <row r="31" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A31" s="3" t="n">
+    <row r="31" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="3">
         <v>45699</v>
       </c>
       <c r="B31" s="4" t="s">
@@ -2368,18 +2629,18 @@
       <c r="D31" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="E31" s="3">
         <v>45734</v>
       </c>
-      <c r="F31" s="5" t="n">
+      <c r="F31" s="5">
         <v>1154.56</v>
       </c>
-      <c r="G31" s="5" t="n">
+      <c r="G31" s="5">
         <v>1154.56</v>
       </c>
       <c r="H31" s="3"/>
-      <c r="I31" s="6" t="n">
-        <v>587</v>
+      <c r="I31" s="6">
+        <v>588</v>
       </c>
       <c r="J31" s="4" t="s">
         <v>18</v>
@@ -2394,8 +2655,8 @@
       <c r="N31" s="4"/>
       <c r="O31" s="4"/>
     </row>
-    <row r="32" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A32" s="3" t="n">
+    <row r="32" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="3">
         <v>45677</v>
       </c>
       <c r="B32" s="4" t="s">
@@ -2407,18 +2668,18 @@
       <c r="D32" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="E32" s="3">
         <v>45740</v>
       </c>
-      <c r="F32" s="5" t="n">
+      <c r="F32" s="5">
         <v>2541</v>
       </c>
-      <c r="G32" s="5" t="n">
+      <c r="G32" s="5">
         <v>2541</v>
       </c>
       <c r="H32" s="3"/>
-      <c r="I32" s="6" t="n">
-        <v>581</v>
+      <c r="I32" s="6">
+        <v>582</v>
       </c>
       <c r="J32" s="4" t="s">
         <v>26</v>
@@ -2433,8 +2694,8 @@
       <c r="N32" s="4"/>
       <c r="O32" s="4"/>
     </row>
-    <row r="33" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A33" s="3" t="n">
+    <row r="33" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="3">
         <v>45699</v>
       </c>
       <c r="B33" s="4" t="s">
@@ -2446,18 +2707,18 @@
       <c r="D33" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="E33" s="3">
         <v>45741</v>
       </c>
-      <c r="F33" s="5" t="n">
+      <c r="F33" s="5">
         <v>7562.78</v>
       </c>
-      <c r="G33" s="5" t="n">
+      <c r="G33" s="5">
         <v>7562.78</v>
       </c>
       <c r="H33" s="3"/>
-      <c r="I33" s="6" t="n">
-        <v>580</v>
+      <c r="I33" s="6">
+        <v>581</v>
       </c>
       <c r="J33" s="4" t="s">
         <v>18</v>
@@ -2472,8 +2733,8 @@
       <c r="N33" s="4"/>
       <c r="O33" s="4"/>
     </row>
-    <row r="34" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A34" s="3" t="n">
+    <row r="34" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="3">
         <v>45699</v>
       </c>
       <c r="B34" s="4" t="s">
@@ -2485,18 +2746,18 @@
       <c r="D34" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="E34" s="3">
         <v>45741</v>
       </c>
-      <c r="F34" s="5" t="n">
+      <c r="F34" s="5">
         <v>1154.56</v>
       </c>
-      <c r="G34" s="5" t="n">
+      <c r="G34" s="5">
         <v>1154.56</v>
       </c>
       <c r="H34" s="3"/>
-      <c r="I34" s="6" t="n">
-        <v>580</v>
+      <c r="I34" s="6">
+        <v>581</v>
       </c>
       <c r="J34" s="4" t="s">
         <v>18</v>
@@ -2511,8 +2772,8 @@
       <c r="N34" s="4"/>
       <c r="O34" s="4"/>
     </row>
-    <row r="35" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A35" s="3" t="n">
+    <row r="35" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="3">
         <v>45699</v>
       </c>
       <c r="B35" s="4" t="s">
@@ -2524,18 +2785,18 @@
       <c r="D35" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="E35" s="3">
         <v>45748</v>
       </c>
-      <c r="F35" s="5" t="n">
+      <c r="F35" s="5">
         <v>1154.56</v>
       </c>
-      <c r="G35" s="5" t="n">
+      <c r="G35" s="5">
         <v>1154.56</v>
       </c>
       <c r="H35" s="3"/>
-      <c r="I35" s="6" t="n">
-        <v>573</v>
+      <c r="I35" s="6">
+        <v>574</v>
       </c>
       <c r="J35" s="4" t="s">
         <v>18</v>
@@ -2550,8 +2811,8 @@
       <c r="N35" s="4"/>
       <c r="O35" s="4"/>
     </row>
-    <row r="36" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A36" s="3" t="n">
+    <row r="36" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="3">
         <v>45699</v>
       </c>
       <c r="B36" s="4" t="s">
@@ -2563,18 +2824,18 @@
       <c r="D36" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="E36" s="3">
         <v>45748</v>
       </c>
-      <c r="F36" s="5" t="n">
+      <c r="F36" s="5">
         <v>7562.76</v>
       </c>
-      <c r="G36" s="5" t="n">
+      <c r="G36" s="5">
         <v>7562.76</v>
       </c>
       <c r="H36" s="3"/>
-      <c r="I36" s="6" t="n">
-        <v>573</v>
+      <c r="I36" s="6">
+        <v>574</v>
       </c>
       <c r="J36" s="4" t="s">
         <v>18</v>
@@ -2589,8 +2850,8 @@
       <c r="N36" s="4"/>
       <c r="O36" s="4"/>
     </row>
-    <row r="37" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A37" s="3" t="n">
+    <row r="37" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="3">
         <v>45699</v>
       </c>
       <c r="B37" s="4" t="s">
@@ -2602,18 +2863,18 @@
       <c r="D37" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="E37" s="3">
         <v>45755</v>
       </c>
-      <c r="F37" s="5" t="n">
+      <c r="F37" s="5">
         <v>1154.56</v>
       </c>
-      <c r="G37" s="5" t="n">
+      <c r="G37" s="5">
         <v>1154.56</v>
       </c>
       <c r="H37" s="3"/>
-      <c r="I37" s="6" t="n">
-        <v>566</v>
+      <c r="I37" s="6">
+        <v>567</v>
       </c>
       <c r="J37" s="4" t="s">
         <v>18</v>
@@ -2628,8 +2889,8 @@
       <c r="N37" s="4"/>
       <c r="O37" s="4"/>
     </row>
-    <row r="38" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A38" s="3" t="n">
+    <row r="38" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="3">
         <v>45733</v>
       </c>
       <c r="B38" s="4" t="s">
@@ -2641,18 +2902,18 @@
       <c r="D38" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="E38" s="3">
         <v>45761</v>
       </c>
-      <c r="F38" s="5" t="n">
+      <c r="F38" s="5">
         <v>3850</v>
       </c>
-      <c r="G38" s="5" t="n">
+      <c r="G38" s="5">
         <v>6169.53</v>
       </c>
       <c r="H38" s="3"/>
-      <c r="I38" s="6" t="n">
-        <v>560</v>
+      <c r="I38" s="6">
+        <v>561</v>
       </c>
       <c r="J38" s="4" t="s">
         <v>18</v>
@@ -2667,8 +2928,8 @@
       <c r="N38" s="4"/>
       <c r="O38" s="4"/>
     </row>
-    <row r="39" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A39" s="3" t="n">
+    <row r="39" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="3">
         <v>45733</v>
       </c>
       <c r="B39" s="4" t="s">
@@ -2680,18 +2941,18 @@
       <c r="D39" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="E39" s="3">
         <v>45768</v>
       </c>
-      <c r="F39" s="5" t="n">
+      <c r="F39" s="5">
         <v>3850</v>
       </c>
-      <c r="G39" s="5" t="n">
+      <c r="G39" s="5">
         <v>3850</v>
       </c>
       <c r="H39" s="3"/>
-      <c r="I39" s="6" t="n">
-        <v>553</v>
+      <c r="I39" s="6">
+        <v>554</v>
       </c>
       <c r="J39" s="4" t="s">
         <v>18</v>
@@ -2706,8 +2967,8 @@
       <c r="N39" s="4"/>
       <c r="O39" s="4"/>
     </row>
-    <row r="40" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A40" s="3" t="n">
+    <row r="40" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="3">
         <v>45733</v>
       </c>
       <c r="B40" s="4" t="s">
@@ -2719,18 +2980,18 @@
       <c r="D40" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="E40" s="3">
         <v>45775</v>
       </c>
-      <c r="F40" s="5" t="n">
+      <c r="F40" s="5">
         <v>3850</v>
       </c>
-      <c r="G40" s="5" t="n">
+      <c r="G40" s="5">
         <v>3850</v>
       </c>
       <c r="H40" s="3"/>
-      <c r="I40" s="6" t="n">
-        <v>546</v>
+      <c r="I40" s="6">
+        <v>547</v>
       </c>
       <c r="J40" s="4" t="s">
         <v>18</v>
@@ -2745,8 +3006,8 @@
       <c r="N40" s="4"/>
       <c r="O40" s="4"/>
     </row>
-    <row r="41" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A41" s="3" t="n">
+    <row r="41" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="3">
         <v>45747</v>
       </c>
       <c r="B41" s="4" t="s">
@@ -2758,18 +3019,18 @@
       <c r="D41" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="E41" s="3">
         <v>45775</v>
       </c>
-      <c r="F41" s="5" t="n">
+      <c r="F41" s="5">
         <v>3800</v>
       </c>
-      <c r="G41" s="5" t="n">
+      <c r="G41" s="5">
         <v>6089.41</v>
       </c>
       <c r="H41" s="3"/>
-      <c r="I41" s="6" t="n">
-        <v>546</v>
+      <c r="I41" s="6">
+        <v>547</v>
       </c>
       <c r="J41" s="4" t="s">
         <v>18</v>
@@ -2784,8 +3045,8 @@
       <c r="N41" s="4"/>
       <c r="O41" s="4"/>
     </row>
-    <row r="42" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A42" s="3" t="n">
+    <row r="42" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="3">
         <v>45747</v>
       </c>
       <c r="B42" s="4" t="s">
@@ -2797,18 +3058,18 @@
       <c r="D42" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="E42" s="3">
         <v>45782</v>
       </c>
-      <c r="F42" s="5" t="n">
+      <c r="F42" s="5">
         <v>3800</v>
       </c>
-      <c r="G42" s="5" t="n">
+      <c r="G42" s="5">
         <v>3800</v>
       </c>
       <c r="H42" s="3"/>
-      <c r="I42" s="6" t="n">
-        <v>539</v>
+      <c r="I42" s="6">
+        <v>540</v>
       </c>
       <c r="J42" s="4" t="s">
         <v>18</v>
@@ -2823,8 +3084,8 @@
       <c r="N42" s="4"/>
       <c r="O42" s="4"/>
     </row>
-    <row r="43" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A43" s="3" t="n">
+    <row r="43" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="3">
         <v>45747</v>
       </c>
       <c r="B43" s="4" t="s">
@@ -2836,18 +3097,18 @@
       <c r="D43" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="E43" s="3">
         <v>45789</v>
       </c>
-      <c r="F43" s="5" t="n">
+      <c r="F43" s="5">
         <v>3800</v>
       </c>
-      <c r="G43" s="5" t="n">
+      <c r="G43" s="5">
         <v>3800</v>
       </c>
       <c r="H43" s="3"/>
-      <c r="I43" s="6" t="n">
-        <v>532</v>
+      <c r="I43" s="6">
+        <v>533</v>
       </c>
       <c r="J43" s="4" t="s">
         <v>18</v>
@@ -2862,8 +3123,8 @@
       <c r="N43" s="4"/>
       <c r="O43" s="4"/>
     </row>
-    <row r="44" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A44" s="3" t="n">
+    <row r="44" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="3">
         <v>45754</v>
       </c>
       <c r="B44" s="4" t="s">
@@ -2875,18 +3136,18 @@
       <c r="D44" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="E44" s="3">
         <v>45789</v>
       </c>
-      <c r="F44" s="5" t="n">
-        <v>2287.07</v>
-      </c>
-      <c r="G44" s="5" t="n">
+      <c r="F44" s="5">
+        <v>2287.0700000000002</v>
+      </c>
+      <c r="G44" s="5">
         <v>1143.54</v>
       </c>
       <c r="H44" s="3"/>
-      <c r="I44" s="6" t="n">
-        <v>532</v>
+      <c r="I44" s="6">
+        <v>533</v>
       </c>
       <c r="J44" s="4" t="s">
         <v>26</v>
@@ -2901,8 +3162,8 @@
       <c r="N44" s="4"/>
       <c r="O44" s="4"/>
     </row>
-    <row r="45" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A45" s="3" t="n">
+    <row r="45" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="3">
         <v>45754</v>
       </c>
       <c r="B45" s="4" t="s">
@@ -2914,18 +3175,18 @@
       <c r="D45" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="E45" s="3">
         <v>45796</v>
       </c>
-      <c r="F45" s="5" t="n">
+      <c r="F45" s="5">
         <v>2287.06</v>
       </c>
-      <c r="G45" s="5" t="n">
+      <c r="G45" s="5">
         <v>2287.06</v>
       </c>
       <c r="H45" s="3"/>
-      <c r="I45" s="6" t="n">
-        <v>525</v>
+      <c r="I45" s="6">
+        <v>526</v>
       </c>
       <c r="J45" s="4" t="s">
         <v>26</v>
@@ -2940,8 +3201,8 @@
       <c r="N45" s="4"/>
       <c r="O45" s="4"/>
     </row>
-    <row r="46" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A46" s="3" t="n">
+    <row r="46" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="3">
         <v>45868</v>
       </c>
       <c r="B46" s="4" t="s">
@@ -2953,18 +3214,18 @@
       <c r="D46" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="E46" s="3">
         <v>45896</v>
       </c>
-      <c r="F46" s="5" t="n">
+      <c r="F46" s="5">
         <v>3663.84</v>
       </c>
-      <c r="G46" s="5" t="n">
+      <c r="G46" s="5">
         <v>4572.62</v>
       </c>
       <c r="H46" s="3"/>
-      <c r="I46" s="6" t="n">
-        <v>425</v>
+      <c r="I46" s="6">
+        <v>426</v>
       </c>
       <c r="J46" s="4" t="s">
         <v>26</v>
@@ -2979,8 +3240,8 @@
       <c r="N46" s="4"/>
       <c r="O46" s="4"/>
     </row>
-    <row r="47" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A47" s="3" t="n">
+    <row r="47" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="3">
         <v>45868</v>
       </c>
       <c r="B47" s="4" t="s">
@@ -2992,18 +3253,18 @@
       <c r="D47" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="E47" s="3" t="n">
+      <c r="E47" s="3">
         <v>45910</v>
       </c>
-      <c r="F47" s="5" t="n">
+      <c r="F47" s="5">
         <v>3663.84</v>
       </c>
-      <c r="G47" s="5" t="n">
+      <c r="G47" s="5">
         <v>3663.84</v>
       </c>
       <c r="H47" s="3"/>
-      <c r="I47" s="6" t="n">
-        <v>411</v>
+      <c r="I47" s="6">
+        <v>412</v>
       </c>
       <c r="J47" s="4" t="s">
         <v>26</v>
@@ -3018,8 +3279,8 @@
       <c r="N47" s="4"/>
       <c r="O47" s="4"/>
     </row>
-    <row r="48" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A48" s="3" t="n">
+    <row r="48" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="3">
         <v>45868</v>
       </c>
       <c r="B48" s="4" t="s">
@@ -3031,18 +3292,18 @@
       <c r="D48" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="E48" s="3" t="n">
+      <c r="E48" s="3">
         <v>45924</v>
       </c>
-      <c r="F48" s="5" t="n">
+      <c r="F48" s="5">
         <v>3663.84</v>
       </c>
-      <c r="G48" s="5" t="n">
+      <c r="G48" s="5">
         <v>3663.84</v>
       </c>
       <c r="H48" s="3"/>
-      <c r="I48" s="6" t="n">
-        <v>397</v>
+      <c r="I48" s="6">
+        <v>398</v>
       </c>
       <c r="J48" s="4" t="s">
         <v>26</v>
@@ -3057,8 +3318,8 @@
       <c r="N48" s="4"/>
       <c r="O48" s="4"/>
     </row>
-    <row r="49" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A49" s="3" t="n">
+    <row r="49" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="3">
         <v>45919</v>
       </c>
       <c r="B49" s="4" t="s">
@@ -3070,18 +3331,18 @@
       <c r="D49" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="E49" s="3" t="n">
+      <c r="E49" s="3">
         <v>45947</v>
       </c>
-      <c r="F49" s="5" t="n">
+      <c r="F49" s="5">
         <v>2144.59</v>
       </c>
-      <c r="G49" s="5" t="n">
+      <c r="G49" s="5">
         <v>3867.34</v>
       </c>
       <c r="H49" s="3"/>
-      <c r="I49" s="6" t="n">
-        <v>374</v>
+      <c r="I49" s="6">
+        <v>375</v>
       </c>
       <c r="J49" s="4" t="s">
         <v>26</v>
@@ -3096,8 +3357,8 @@
       <c r="N49" s="4"/>
       <c r="O49" s="4"/>
     </row>
-    <row r="50" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A50" s="3" t="n">
+    <row r="50" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="3">
         <v>45919</v>
       </c>
       <c r="B50" s="4" t="s">
@@ -3109,18 +3370,18 @@
       <c r="D50" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="E50" s="3" t="n">
+      <c r="E50" s="3">
         <v>45954</v>
       </c>
-      <c r="F50" s="5" t="n">
+      <c r="F50" s="5">
         <v>2144.59</v>
       </c>
-      <c r="G50" s="5" t="n">
+      <c r="G50" s="5">
         <v>2144.59</v>
       </c>
       <c r="H50" s="3"/>
-      <c r="I50" s="6" t="n">
-        <v>367</v>
+      <c r="I50" s="6">
+        <v>368</v>
       </c>
       <c r="J50" s="4" t="s">
         <v>26</v>
@@ -3135,8 +3396,8 @@
       <c r="N50" s="4"/>
       <c r="O50" s="4"/>
     </row>
-    <row r="51" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A51" s="3" t="n">
+    <row r="51" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="3">
         <v>45919</v>
       </c>
       <c r="B51" s="4" t="s">
@@ -3148,18 +3409,18 @@
       <c r="D51" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="E51" s="3" t="n">
+      <c r="E51" s="3">
         <v>45961</v>
       </c>
-      <c r="F51" s="5" t="n">
+      <c r="F51" s="5">
         <v>2144.59</v>
       </c>
-      <c r="G51" s="5" t="n">
+      <c r="G51" s="5">
         <v>2144.59</v>
       </c>
       <c r="H51" s="3"/>
-      <c r="I51" s="6" t="n">
-        <v>360</v>
+      <c r="I51" s="6">
+        <v>361</v>
       </c>
       <c r="J51" s="4" t="s">
         <v>26</v>
@@ -3174,8 +3435,8 @@
       <c r="N51" s="4"/>
       <c r="O51" s="4"/>
     </row>
-    <row r="52" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A52" s="3" t="n">
+    <row r="52" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="3">
         <v>45919</v>
       </c>
       <c r="B52" s="4" t="s">
@@ -3187,18 +3448,18 @@
       <c r="D52" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="E52" s="3" t="n">
+      <c r="E52" s="3">
         <v>45968</v>
       </c>
-      <c r="F52" s="5" t="n">
+      <c r="F52" s="5">
         <v>2144.59</v>
       </c>
-      <c r="G52" s="5" t="n">
+      <c r="G52" s="5">
         <v>2144.59</v>
       </c>
       <c r="H52" s="3"/>
-      <c r="I52" s="6" t="n">
-        <v>353</v>
+      <c r="I52" s="6">
+        <v>354</v>
       </c>
       <c r="J52" s="4" t="s">
         <v>26</v>
@@ -3213,8 +3474,8 @@
       <c r="N52" s="4"/>
       <c r="O52" s="4"/>
     </row>
-    <row r="53" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A53" s="3" t="n">
+    <row r="53" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="3">
         <v>45938</v>
       </c>
       <c r="B53" s="4" t="s">
@@ -3226,18 +3487,18 @@
       <c r="D53" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="E53" s="3" t="n">
+      <c r="E53" s="3">
         <v>45980</v>
       </c>
-      <c r="F53" s="5" t="n">
+      <c r="F53" s="5">
         <v>4480</v>
       </c>
-      <c r="G53" s="5" t="n">
+      <c r="G53" s="5">
         <v>4480</v>
       </c>
       <c r="H53" s="3"/>
-      <c r="I53" s="6" t="n">
-        <v>341</v>
+      <c r="I53" s="6">
+        <v>342</v>
       </c>
       <c r="J53" s="4" t="s">
         <v>26</v>
@@ -3252,8 +3513,8 @@
       <c r="N53" s="4"/>
       <c r="O53" s="4"/>
     </row>
-    <row r="54" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A54" s="3" t="n">
+    <row r="54" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="3">
         <v>45959</v>
       </c>
       <c r="B54" s="4" t="s">
@@ -3265,18 +3526,18 @@
       <c r="D54" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="E54" s="3" t="n">
+      <c r="E54" s="3">
         <v>45980</v>
       </c>
-      <c r="F54" s="5" t="n">
+      <c r="F54" s="5">
         <v>28666.44</v>
       </c>
-      <c r="G54" s="5" t="n">
+      <c r="G54" s="5">
         <v>28666.44</v>
       </c>
       <c r="H54" s="3"/>
-      <c r="I54" s="6" t="n">
-        <v>341</v>
+      <c r="I54" s="6">
+        <v>342</v>
       </c>
       <c r="J54" s="4"/>
       <c r="K54" s="4" t="s">
@@ -3287,8 +3548,8 @@
       <c r="N54" s="4"/>
       <c r="O54" s="4"/>
     </row>
-    <row r="55" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A55" s="3" t="n">
+    <row r="55" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="3">
         <v>45959</v>
       </c>
       <c r="B55" s="4" t="s">
@@ -3300,18 +3561,18 @@
       <c r="D55" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="E55" s="3" t="n">
+      <c r="E55" s="3">
         <v>45987</v>
       </c>
-      <c r="F55" s="5" t="n">
-        <v>33844.16</v>
-      </c>
-      <c r="G55" s="5" t="n">
-        <v>33844.16</v>
+      <c r="F55" s="5">
+        <v>33844.160000000003</v>
+      </c>
+      <c r="G55" s="5">
+        <v>33844.160000000003</v>
       </c>
       <c r="H55" s="3"/>
-      <c r="I55" s="6" t="n">
-        <v>334</v>
+      <c r="I55" s="6">
+        <v>335</v>
       </c>
       <c r="J55" s="4"/>
       <c r="K55" s="4" t="s">
@@ -3322,8 +3583,8 @@
       <c r="N55" s="4"/>
       <c r="O55" s="4"/>
     </row>
-    <row r="56" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A56" s="3" t="n">
+    <row r="56" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="3">
         <v>45947</v>
       </c>
       <c r="B56" s="4" t="s">
@@ -3335,18 +3596,18 @@
       <c r="D56" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="E56" s="3" t="n">
+      <c r="E56" s="3">
         <v>45989</v>
       </c>
-      <c r="F56" s="5" t="n">
+      <c r="F56" s="5">
         <v>3220</v>
       </c>
-      <c r="G56" s="5" t="n">
+      <c r="G56" s="5">
         <v>3220</v>
       </c>
       <c r="H56" s="3"/>
-      <c r="I56" s="6" t="n">
-        <v>332</v>
+      <c r="I56" s="6">
+        <v>333</v>
       </c>
       <c r="J56" s="4"/>
       <c r="K56" s="4" t="s">
@@ -3357,8 +3618,8 @@
       <c r="N56" s="4"/>
       <c r="O56" s="4"/>
     </row>
-    <row r="57" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A57" s="3" t="n">
+    <row r="57" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="3">
         <v>45959</v>
       </c>
       <c r="B57" s="4" t="s">
@@ -3370,18 +3631,18 @@
       <c r="D57" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="E57" s="3" t="n">
+      <c r="E57" s="3">
         <v>45994</v>
       </c>
-      <c r="F57" s="5" t="n">
+      <c r="F57" s="5">
         <v>14483.06</v>
       </c>
-      <c r="G57" s="5" t="n">
+      <c r="G57" s="5">
         <v>14483.06</v>
       </c>
       <c r="H57" s="3"/>
-      <c r="I57" s="6" t="n">
-        <v>327</v>
+      <c r="I57" s="6">
+        <v>328</v>
       </c>
       <c r="J57" s="4"/>
       <c r="K57" s="4" t="s">
@@ -3392,8 +3653,8 @@
       <c r="N57" s="4"/>
       <c r="O57" s="4"/>
     </row>
-    <row r="58" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A58" s="3" t="n">
+    <row r="58" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="3">
         <v>46062</v>
       </c>
       <c r="B58" s="4" t="s">
@@ -3405,18 +3666,18 @@
       <c r="D58" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="E58" s="3" t="n">
+      <c r="E58" s="3">
         <v>46090</v>
       </c>
-      <c r="F58" s="5" t="n">
+      <c r="F58" s="5">
         <v>503.28</v>
       </c>
-      <c r="G58" s="5" t="n">
+      <c r="G58" s="5">
         <v>806.34</v>
       </c>
       <c r="H58" s="3"/>
-      <c r="I58" s="6" t="n">
-        <v>231</v>
+      <c r="I58" s="6">
+        <v>232</v>
       </c>
       <c r="J58" s="4" t="s">
         <v>26</v>
@@ -3431,8 +3692,8 @@
       <c r="N58" s="4"/>
       <c r="O58" s="4"/>
     </row>
-    <row r="59" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A59" s="3" t="n">
+    <row r="59" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="3">
         <v>46062</v>
       </c>
       <c r="B59" s="4" t="s">
@@ -3444,18 +3705,18 @@
       <c r="D59" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="E59" s="3" t="n">
+      <c r="E59" s="3">
         <v>46097</v>
       </c>
-      <c r="F59" s="5" t="n">
+      <c r="F59" s="5">
         <v>503.28</v>
       </c>
-      <c r="G59" s="5" t="n">
+      <c r="G59" s="5">
         <v>503.28</v>
       </c>
       <c r="H59" s="3"/>
-      <c r="I59" s="6" t="n">
-        <v>224</v>
+      <c r="I59" s="6">
+        <v>225</v>
       </c>
       <c r="J59" s="4" t="s">
         <v>26</v>
@@ -3470,8 +3731,8 @@
       <c r="N59" s="4"/>
       <c r="O59" s="4"/>
     </row>
-    <row r="60" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A60" s="3" t="n">
+    <row r="60" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="3">
         <v>46062</v>
       </c>
       <c r="B60" s="4" t="s">
@@ -3483,18 +3744,18 @@
       <c r="D60" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="E60" s="3" t="n">
+      <c r="E60" s="3">
         <v>46104</v>
       </c>
-      <c r="F60" s="5" t="n">
+      <c r="F60" s="5">
         <v>503.28</v>
       </c>
-      <c r="G60" s="5" t="n">
+      <c r="G60" s="5">
         <v>503.28</v>
       </c>
       <c r="H60" s="3"/>
-      <c r="I60" s="6" t="n">
-        <v>217</v>
+      <c r="I60" s="6">
+        <v>218</v>
       </c>
       <c r="J60" s="4" t="s">
         <v>26</v>
@@ -3509,8 +3770,8 @@
       <c r="N60" s="4"/>
       <c r="O60" s="4"/>
     </row>
-    <row r="61" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A61" s="3" t="n">
+    <row r="61" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="3">
         <v>46045</v>
       </c>
       <c r="B61" s="4" t="s">
@@ -3522,18 +3783,18 @@
       <c r="D61" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="E61" s="3" t="n">
+      <c r="E61" s="3">
         <v>46105</v>
       </c>
-      <c r="F61" s="5" t="n">
+      <c r="F61" s="5">
         <v>5466.66</v>
       </c>
-      <c r="G61" s="5" t="n">
+      <c r="G61" s="5">
         <v>5466.66</v>
       </c>
       <c r="H61" s="3"/>
-      <c r="I61" s="6" t="n">
-        <v>216</v>
+      <c r="I61" s="6">
+        <v>217</v>
       </c>
       <c r="J61" s="4" t="s">
         <v>18</v>
@@ -3548,8 +3809,8 @@
       <c r="N61" s="4"/>
       <c r="O61" s="4"/>
     </row>
-    <row r="62" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A62" s="3" t="n">
+    <row r="62" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="3">
         <v>46171</v>
       </c>
       <c r="B62" s="4" t="s">
@@ -3561,18 +3822,18 @@
       <c r="D62" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="E62" s="3" t="n">
+      <c r="E62" s="3">
         <v>46192</v>
       </c>
-      <c r="F62" s="5" t="n">
-        <v>4676.85</v>
-      </c>
-      <c r="G62" s="5" t="n">
+      <c r="F62" s="5">
+        <v>4676.8500000000004</v>
+      </c>
+      <c r="G62" s="5">
         <v>7494.53</v>
       </c>
       <c r="H62" s="3"/>
-      <c r="I62" s="6" t="n">
-        <v>129</v>
+      <c r="I62" s="6">
+        <v>130</v>
       </c>
       <c r="J62" s="4"/>
       <c r="K62" s="4" t="s">
@@ -3583,8 +3844,8 @@
       <c r="N62" s="4"/>
       <c r="O62" s="4"/>
     </row>
-    <row r="63" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A63" s="3" t="n">
+    <row r="63" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="3">
         <v>46171</v>
       </c>
       <c r="B63" s="4" t="s">
@@ -3596,18 +3857,18 @@
       <c r="D63" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="E63" s="3" t="n">
+      <c r="E63" s="3">
         <v>46199</v>
       </c>
-      <c r="F63" s="5" t="n">
-        <v>4676.85</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>4676.85</v>
+      <c r="F63" s="5">
+        <v>4676.8500000000004</v>
+      </c>
+      <c r="G63" s="5">
+        <v>4676.8500000000004</v>
       </c>
       <c r="H63" s="3"/>
-      <c r="I63" s="6" t="n">
-        <v>122</v>
+      <c r="I63" s="6">
+        <v>123</v>
       </c>
       <c r="J63" s="4"/>
       <c r="K63" s="4" t="s">
@@ -3618,8 +3879,8 @@
       <c r="N63" s="4"/>
       <c r="O63" s="4"/>
     </row>
-    <row r="64" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A64" s="3" t="n">
+    <row r="64" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="3">
         <v>46171</v>
       </c>
       <c r="B64" s="4" t="s">
@@ -3631,18 +3892,18 @@
       <c r="D64" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="E64" s="3" t="n">
+      <c r="E64" s="3">
         <v>46206</v>
       </c>
-      <c r="F64" s="5" t="n">
-        <v>4676.85</v>
-      </c>
-      <c r="G64" s="5" t="n">
-        <v>4676.85</v>
+      <c r="F64" s="5">
+        <v>4676.8500000000004</v>
+      </c>
+      <c r="G64" s="5">
+        <v>4676.8500000000004</v>
       </c>
       <c r="H64" s="3"/>
-      <c r="I64" s="6" t="n">
-        <v>115</v>
+      <c r="I64" s="6">
+        <v>116</v>
       </c>
       <c r="J64" s="4"/>
       <c r="K64" s="4" t="s">
@@ -3653,8 +3914,8 @@
       <c r="N64" s="4"/>
       <c r="O64" s="4"/>
     </row>
-    <row r="65" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A65" s="3" t="n">
+    <row r="65" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="3">
         <v>46162</v>
       </c>
       <c r="B65" s="4" t="s">
@@ -3666,18 +3927,18 @@
       <c r="D65" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="E65" s="3" t="n">
+      <c r="E65" s="3">
         <v>46222</v>
       </c>
-      <c r="F65" s="5" t="n">
+      <c r="F65" s="5">
         <v>12349.79</v>
       </c>
-      <c r="G65" s="5" t="n">
+      <c r="G65" s="5">
         <v>12349.79</v>
       </c>
       <c r="H65" s="3"/>
-      <c r="I65" s="6" t="n">
-        <v>99</v>
+      <c r="I65" s="6">
+        <v>100</v>
       </c>
       <c r="J65" s="4"/>
       <c r="K65" s="4" t="s">
@@ -3688,8 +3949,8 @@
       <c r="N65" s="4"/>
       <c r="O65" s="4"/>
     </row>
-    <row r="66" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A66" s="3" t="n">
+    <row r="66" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="3">
         <v>46203</v>
       </c>
       <c r="B66" s="4" t="s">
@@ -3701,18 +3962,18 @@
       <c r="D66" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="E66" s="3" t="n">
+      <c r="E66" s="3">
         <v>46259</v>
       </c>
-      <c r="F66" s="5" t="n">
+      <c r="F66" s="5">
         <v>860</v>
       </c>
-      <c r="G66" s="5" t="n">
+      <c r="G66" s="5">
         <v>860</v>
       </c>
       <c r="H66" s="3"/>
-      <c r="I66" s="6" t="n">
-        <v>62</v>
+      <c r="I66" s="6">
+        <v>63</v>
       </c>
       <c r="J66" s="4" t="s">
         <v>26</v>
@@ -3727,8 +3988,8 @@
       <c r="N66" s="4"/>
       <c r="O66" s="4"/>
     </row>
-    <row r="67" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A67" s="3" t="n">
+    <row r="67" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="3">
         <v>46224</v>
       </c>
       <c r="B67" s="4" t="s">
@@ -3740,18 +4001,18 @@
       <c r="D67" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="E67" s="3" t="n">
+      <c r="E67" s="3">
         <v>46259</v>
       </c>
-      <c r="F67" s="5" t="n">
+      <c r="F67" s="5">
         <v>2818.37</v>
       </c>
-      <c r="G67" s="5" t="n">
+      <c r="G67" s="5">
         <v>2818.37</v>
       </c>
       <c r="H67" s="3"/>
-      <c r="I67" s="6" t="n">
-        <v>62</v>
+      <c r="I67" s="6">
+        <v>63</v>
       </c>
       <c r="J67" s="4" t="s">
         <v>26</v>
@@ -3766,8 +4027,8 @@
       <c r="N67" s="4"/>
       <c r="O67" s="4"/>
     </row>
-    <row r="68" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A68" s="3" t="n">
+    <row r="68" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="3">
         <v>46232</v>
       </c>
       <c r="B68" s="4" t="s">
@@ -3779,18 +4040,18 @@
       <c r="D68" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="E68" s="3" t="n">
+      <c r="E68" s="3">
         <v>46262</v>
       </c>
-      <c r="F68" s="5" t="n">
+      <c r="F68" s="5">
         <v>9716</v>
       </c>
-      <c r="G68" s="5" t="n">
+      <c r="G68" s="5">
         <v>18957.86</v>
       </c>
       <c r="H68" s="3"/>
-      <c r="I68" s="6" t="n">
-        <v>59</v>
+      <c r="I68" s="6">
+        <v>60</v>
       </c>
       <c r="J68" s="4" t="s">
         <v>26</v>
@@ -3805,8 +4066,8 @@
       <c r="N68" s="4"/>
       <c r="O68" s="4"/>
     </row>
-    <row r="69" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A69" s="3" t="n">
+    <row r="69" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="3">
         <v>46232</v>
       </c>
       <c r="B69" s="4" t="s">
@@ -3818,18 +4079,18 @@
       <c r="D69" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="E69" s="3" t="n">
+      <c r="E69" s="3">
         <v>46272</v>
       </c>
-      <c r="F69" s="5" t="n">
+      <c r="F69" s="5">
         <v>9716</v>
       </c>
-      <c r="G69" s="5" t="n">
+      <c r="G69" s="5">
         <v>9716</v>
       </c>
       <c r="H69" s="3"/>
-      <c r="I69" s="6" t="n">
-        <v>49</v>
+      <c r="I69" s="6">
+        <v>50</v>
       </c>
       <c r="J69" s="4" t="s">
         <v>26</v>
@@ -3844,8 +4105,8 @@
       <c r="N69" s="4"/>
       <c r="O69" s="4"/>
     </row>
-    <row r="70" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A70" s="3" t="n">
+    <row r="70" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="3">
         <v>46227</v>
       </c>
       <c r="B70" s="4" t="s">
@@ -3857,18 +4118,18 @@
       <c r="D70" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="E70" s="3" t="n">
+      <c r="E70" s="3">
         <v>46272</v>
       </c>
-      <c r="F70" s="5" t="n">
+      <c r="F70" s="5">
         <v>4216.67</v>
       </c>
-      <c r="G70" s="5" t="n">
+      <c r="G70" s="5">
         <v>6389.24</v>
       </c>
       <c r="H70" s="3"/>
-      <c r="I70" s="6" t="n">
-        <v>49</v>
+      <c r="I70" s="6">
+        <v>50</v>
       </c>
       <c r="J70" s="4" t="s">
         <v>183</v>
@@ -3883,8 +4144,8 @@
       <c r="N70" s="4"/>
       <c r="O70" s="4"/>
     </row>
-    <row r="71" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A71" s="3" t="n">
+    <row r="71" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="3">
         <v>46224</v>
       </c>
       <c r="B71" s="4" t="s">
@@ -3896,18 +4157,18 @@
       <c r="D71" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="E71" s="3" t="n">
+      <c r="E71" s="3">
         <v>46273</v>
       </c>
-      <c r="F71" s="5" t="n">
+      <c r="F71" s="5">
         <v>2818.37</v>
       </c>
-      <c r="G71" s="5" t="n">
+      <c r="G71" s="5">
         <v>2818.37</v>
       </c>
       <c r="H71" s="3"/>
-      <c r="I71" s="6" t="n">
-        <v>48</v>
+      <c r="I71" s="6">
+        <v>49</v>
       </c>
       <c r="J71" s="4" t="s">
         <v>26</v>
@@ -3922,8 +4183,8 @@
       <c r="N71" s="4"/>
       <c r="O71" s="4"/>
     </row>
-    <row r="72" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A72" s="3" t="n">
+    <row r="72" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="3">
         <v>46234</v>
       </c>
       <c r="B72" s="4" t="s">
@@ -3935,18 +4196,18 @@
       <c r="D72" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="E72" s="3" t="n">
+      <c r="E72" s="3">
         <v>46279</v>
       </c>
-      <c r="F72" s="5" t="n">
+      <c r="F72" s="5">
         <v>3789.09</v>
       </c>
-      <c r="G72" s="5" t="n">
+      <c r="G72" s="5">
         <v>5741.36</v>
       </c>
       <c r="H72" s="3"/>
-      <c r="I72" s="6" t="n">
-        <v>42</v>
+      <c r="I72" s="6">
+        <v>43</v>
       </c>
       <c r="J72" s="4" t="s">
         <v>189</v>
@@ -3961,8 +4222,8 @@
       <c r="N72" s="4"/>
       <c r="O72" s="4"/>
     </row>
-    <row r="73" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A73" s="3" t="n">
+    <row r="73" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="3">
         <v>46232</v>
       </c>
       <c r="B73" s="4" t="s">
@@ -3974,18 +4235,18 @@
       <c r="D73" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="E73" s="3" t="n">
+      <c r="E73" s="3">
         <v>46282</v>
       </c>
-      <c r="F73" s="5" t="n">
+      <c r="F73" s="5">
         <v>9716</v>
       </c>
-      <c r="G73" s="5" t="n">
+      <c r="G73" s="5">
         <v>9716</v>
       </c>
       <c r="H73" s="3"/>
-      <c r="I73" s="6" t="n">
-        <v>39</v>
+      <c r="I73" s="6">
+        <v>40</v>
       </c>
       <c r="J73" s="4" t="s">
         <v>26</v>
@@ -4000,8 +4261,8 @@
       <c r="N73" s="4"/>
       <c r="O73" s="4"/>
     </row>
-    <row r="74" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A74" s="3" t="n">
+    <row r="74" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="3">
         <v>46227</v>
       </c>
       <c r="B74" s="4" t="s">
@@ -4013,18 +4274,18 @@
       <c r="D74" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="E74" s="3" t="n">
+      <c r="E74" s="3">
         <v>46283</v>
       </c>
-      <c r="F74" s="5" t="n">
+      <c r="F74" s="5">
         <v>23168.6</v>
       </c>
-      <c r="G74" s="5" t="n">
+      <c r="G74" s="5">
         <v>23168.6</v>
       </c>
       <c r="H74" s="3"/>
-      <c r="I74" s="6" t="n">
-        <v>38</v>
+      <c r="I74" s="6">
+        <v>39</v>
       </c>
       <c r="J74" s="4" t="s">
         <v>189</v>
@@ -4039,8 +4300,8 @@
       <c r="N74" s="4"/>
       <c r="O74" s="4"/>
     </row>
-    <row r="75" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A75" s="3" t="n">
+    <row r="75" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="3">
         <v>46234</v>
       </c>
       <c r="B75" s="4" t="s">
@@ -4052,18 +4313,18 @@
       <c r="D75" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="E75" s="3" t="n">
+      <c r="E75" s="3">
         <v>46284</v>
       </c>
-      <c r="F75" s="5" t="n">
+      <c r="F75" s="5">
         <v>4950.17</v>
       </c>
-      <c r="G75" s="5" t="n">
+      <c r="G75" s="5">
         <v>4950.17</v>
       </c>
       <c r="H75" s="3"/>
-      <c r="I75" s="6" t="n">
-        <v>37</v>
+      <c r="I75" s="6">
+        <v>38</v>
       </c>
       <c r="J75" s="4" t="s">
         <v>189</v>
@@ -4078,8 +4339,8 @@
       <c r="N75" s="4"/>
       <c r="O75" s="4"/>
     </row>
-    <row r="76" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A76" s="3" t="n">
+    <row r="76" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="3">
         <v>46225</v>
       </c>
       <c r="B76" s="4" t="s">
@@ -4091,18 +4352,18 @@
       <c r="D76" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="E76" s="3" t="n">
+      <c r="E76" s="3">
         <v>46285</v>
       </c>
-      <c r="F76" s="5" t="n">
+      <c r="F76" s="5">
         <v>7551.88</v>
       </c>
-      <c r="G76" s="5" t="n">
+      <c r="G76" s="5">
         <v>7551.88</v>
       </c>
       <c r="H76" s="3"/>
-      <c r="I76" s="6" t="n">
-        <v>36</v>
+      <c r="I76" s="6">
+        <v>37</v>
       </c>
       <c r="J76" s="4" t="s">
         <v>189</v>
@@ -4117,8 +4378,8 @@
       <c r="N76" s="4"/>
       <c r="O76" s="4"/>
     </row>
-    <row r="77" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A77" s="3" t="n">
+    <row r="77" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="3">
         <v>46244</v>
       </c>
       <c r="B77" s="4" t="s">
@@ -4130,18 +4391,18 @@
       <c r="D77" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="E77" s="3" t="n">
+      <c r="E77" s="3">
         <v>46286</v>
       </c>
-      <c r="F77" s="5" t="n">
+      <c r="F77" s="5">
         <v>4320</v>
       </c>
-      <c r="G77" s="5" t="n">
+      <c r="G77" s="5">
         <v>4320</v>
       </c>
       <c r="H77" s="3"/>
-      <c r="I77" s="6" t="n">
-        <v>35</v>
+      <c r="I77" s="6">
+        <v>36</v>
       </c>
       <c r="J77" s="4" t="s">
         <v>189</v>
@@ -4156,8 +4417,8 @@
       <c r="N77" s="4"/>
       <c r="O77" s="4"/>
     </row>
-    <row r="78" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A78" s="3" t="n">
+    <row r="78" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="3">
         <v>46227</v>
       </c>
       <c r="B78" s="4" t="s">
@@ -4169,18 +4430,18 @@
       <c r="D78" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="E78" s="3" t="n">
+      <c r="E78" s="3">
         <v>46287</v>
       </c>
-      <c r="F78" s="5" t="n">
+      <c r="F78" s="5">
         <v>4216.67</v>
       </c>
-      <c r="G78" s="5" t="n">
+      <c r="G78" s="5">
         <v>4216.67</v>
       </c>
       <c r="H78" s="3"/>
-      <c r="I78" s="6" t="n">
-        <v>34</v>
+      <c r="I78" s="6">
+        <v>35</v>
       </c>
       <c r="J78" s="4" t="s">
         <v>183</v>
@@ -4195,8 +4456,8 @@
       <c r="N78" s="4"/>
       <c r="O78" s="4"/>
     </row>
-    <row r="79" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A79" s="3" t="n">
+    <row r="79" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="3">
         <v>46253</v>
       </c>
       <c r="B79" s="4" t="s">
@@ -4208,18 +4469,18 @@
       <c r="D79" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="E79" s="3" t="n">
+      <c r="E79" s="3">
         <v>46288</v>
       </c>
-      <c r="F79" s="5" t="n">
+      <c r="F79" s="5">
         <v>10080</v>
       </c>
-      <c r="G79" s="5" t="n">
+      <c r="G79" s="5">
         <v>10080</v>
       </c>
       <c r="H79" s="3"/>
-      <c r="I79" s="6" t="n">
-        <v>33</v>
+      <c r="I79" s="6">
+        <v>34</v>
       </c>
       <c r="J79" s="4" t="s">
         <v>189</v>
@@ -4234,8 +4495,8 @@
       <c r="N79" s="4"/>
       <c r="O79" s="4"/>
     </row>
-    <row r="80" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A80" s="3" t="n">
+    <row r="80" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="3">
         <v>46253</v>
       </c>
       <c r="B80" s="4" t="s">
@@ -4247,18 +4508,18 @@
       <c r="D80" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="E80" s="3" t="n">
+      <c r="E80" s="3">
         <v>46288</v>
       </c>
-      <c r="F80" s="5" t="n">
+      <c r="F80" s="5">
         <v>3640</v>
       </c>
-      <c r="G80" s="5" t="n">
+      <c r="G80" s="5">
         <v>3640</v>
       </c>
       <c r="H80" s="3"/>
-      <c r="I80" s="6" t="n">
-        <v>33</v>
+      <c r="I80" s="6">
+        <v>34</v>
       </c>
       <c r="J80" s="4" t="s">
         <v>189</v>
@@ -4273,8 +4534,8 @@
       <c r="N80" s="4"/>
       <c r="O80" s="4"/>
     </row>
-    <row r="81" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A81" s="3" t="n">
+    <row r="81" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="3">
         <v>46262</v>
       </c>
       <c r="B81" s="4" t="s">
@@ -4286,18 +4547,18 @@
       <c r="D81" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="E81" s="3" t="n">
+      <c r="E81" s="3">
         <v>46290</v>
       </c>
-      <c r="F81" s="5" t="n">
+      <c r="F81" s="5">
         <v>7694.4</v>
       </c>
-      <c r="G81" s="5" t="n">
+      <c r="G81" s="5">
         <v>7694.4</v>
       </c>
       <c r="H81" s="3"/>
-      <c r="I81" s="6" t="n">
-        <v>31</v>
+      <c r="I81" s="6">
+        <v>32</v>
       </c>
       <c r="J81" s="4" t="s">
         <v>26</v>
@@ -4312,76 +4573,76 @@
       <c r="N81" s="4"/>
       <c r="O81" s="4"/>
     </row>
-    <row r="82" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A82" s="3" t="n">
-        <v>46262</v>
+    <row r="82" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="3">
+        <v>46232</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="E82" s="3" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F82" s="5" t="n">
-        <v>11660.11</v>
-      </c>
-      <c r="G82" s="5" t="n">
-        <v>11660.11</v>
+        <v>216</v>
+      </c>
+      <c r="E82" s="3">
+        <v>46292</v>
+      </c>
+      <c r="F82" s="5">
+        <v>4082.05</v>
+      </c>
+      <c r="G82" s="5">
+        <v>4082.05</v>
       </c>
       <c r="H82" s="3"/>
-      <c r="I82" s="6" t="n">
-        <v>31</v>
+      <c r="I82" s="6">
+        <v>30</v>
       </c>
       <c r="J82" s="4" t="s">
         <v>189</v>
       </c>
       <c r="K82" s="4" t="s">
-        <v>213</v>
+        <v>184</v>
       </c>
       <c r="L82" s="4"/>
       <c r="M82" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N82" s="4"/>
       <c r="O82" s="4"/>
     </row>
-    <row r="83" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A83" s="3" t="n">
+    <row r="83" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="3">
         <v>46232</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>180</v>
+        <v>15</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>217</v>
+        <v>175</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="E83" s="3" t="n">
+      <c r="E83" s="3">
         <v>46292</v>
       </c>
-      <c r="F83" s="5" t="n">
-        <v>4082.05</v>
-      </c>
-      <c r="G83" s="5" t="n">
-        <v>4082.05</v>
+      <c r="F83" s="5">
+        <v>9716</v>
+      </c>
+      <c r="G83" s="5">
+        <v>9716</v>
       </c>
       <c r="H83" s="3"/>
-      <c r="I83" s="6" t="n">
-        <v>29</v>
+      <c r="I83" s="6">
+        <v>30</v>
       </c>
       <c r="J83" s="4" t="s">
-        <v>189</v>
+        <v>26</v>
       </c>
       <c r="K83" s="4" t="s">
-        <v>184</v>
+        <v>39</v>
       </c>
       <c r="L83" s="4"/>
       <c r="M83" s="4" t="s">
@@ -4390,37 +4651,37 @@
       <c r="N83" s="4"/>
       <c r="O83" s="4"/>
     </row>
-    <row r="84" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A84" s="3" t="n">
-        <v>46232</v>
+    <row r="84" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="3">
+        <v>46244</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>175</v>
+        <v>193</v>
       </c>
       <c r="D84" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="E84" s="3" t="n">
-        <v>46292</v>
-      </c>
-      <c r="F84" s="5" t="n">
-        <v>9716</v>
-      </c>
-      <c r="G84" s="5" t="n">
-        <v>9716</v>
+      <c r="E84" s="3">
+        <v>46293</v>
+      </c>
+      <c r="F84" s="5">
+        <v>4320</v>
+      </c>
+      <c r="G84" s="5">
+        <v>4320</v>
       </c>
       <c r="H84" s="3"/>
-      <c r="I84" s="6" t="n">
+      <c r="I84" s="6">
         <v>29</v>
       </c>
       <c r="J84" s="4" t="s">
-        <v>26</v>
+        <v>189</v>
       </c>
       <c r="K84" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="L84" s="4"/>
       <c r="M84" s="4" t="s">
@@ -4429,31 +4690,31 @@
       <c r="N84" s="4"/>
       <c r="O84" s="4"/>
     </row>
-    <row r="85" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A85" s="3" t="n">
-        <v>46244</v>
+    <row r="85" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="3">
+        <v>46223</v>
       </c>
       <c r="B85" s="4" t="s">
         <v>45</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D85" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="E85" s="3" t="n">
+      <c r="E85" s="3">
         <v>46293</v>
       </c>
-      <c r="F85" s="5" t="n">
-        <v>4320</v>
-      </c>
-      <c r="G85" s="5" t="n">
-        <v>4320</v>
+      <c r="F85" s="5">
+        <v>11200</v>
+      </c>
+      <c r="G85" s="5">
+        <v>11200</v>
       </c>
       <c r="H85" s="3"/>
-      <c r="I85" s="6" t="n">
-        <v>28</v>
+      <c r="I85" s="6">
+        <v>29</v>
       </c>
       <c r="J85" s="4" t="s">
         <v>189</v>
@@ -4468,37 +4729,37 @@
       <c r="N85" s="4"/>
       <c r="O85" s="4"/>
     </row>
-    <row r="86" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A86" s="3" t="n">
-        <v>46223</v>
+    <row r="86" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="3">
+        <v>46234</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>45</v>
+        <v>180</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="D86" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="E86" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F86" s="5" t="n">
-        <v>11200</v>
-      </c>
-      <c r="G86" s="5" t="n">
-        <v>11200</v>
+      <c r="E86" s="3">
+        <v>46294</v>
+      </c>
+      <c r="F86" s="5">
+        <v>3789.09</v>
+      </c>
+      <c r="G86" s="5">
+        <v>3789.09</v>
       </c>
       <c r="H86" s="3"/>
-      <c r="I86" s="6" t="n">
+      <c r="I86" s="6">
         <v>28</v>
       </c>
       <c r="J86" s="4" t="s">
         <v>189</v>
       </c>
       <c r="K86" s="4" t="s">
-        <v>27</v>
+        <v>184</v>
       </c>
       <c r="L86" s="4"/>
       <c r="M86" s="4" t="s">
@@ -4507,37 +4768,37 @@
       <c r="N86" s="4"/>
       <c r="O86" s="4"/>
     </row>
-    <row r="87" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A87" s="3" t="n">
-        <v>46234</v>
+    <row r="87" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="3">
+        <v>46266</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>180</v>
+        <v>45</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="D87" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="E87" s="3" t="n">
+      <c r="E87" s="3">
         <v>46294</v>
       </c>
-      <c r="F87" s="5" t="n">
-        <v>3789.09</v>
-      </c>
-      <c r="G87" s="5" t="n">
-        <v>3789.09</v>
+      <c r="F87" s="5">
+        <v>18600</v>
+      </c>
+      <c r="G87" s="5">
+        <v>18600</v>
       </c>
       <c r="H87" s="3"/>
-      <c r="I87" s="6" t="n">
+      <c r="I87" s="6">
+        <v>28</v>
+      </c>
+      <c r="J87" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K87" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="J87" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="K87" s="4" t="s">
-        <v>184</v>
       </c>
       <c r="L87" s="4"/>
       <c r="M87" s="4" t="s">
@@ -4546,9 +4807,9 @@
       <c r="N87" s="4"/>
       <c r="O87" s="4"/>
     </row>
-    <row r="88" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A88" s="3" t="n">
-        <v>46266</v>
+    <row r="88" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="3">
+        <v>46253</v>
       </c>
       <c r="B88" s="4" t="s">
         <v>45</v>
@@ -4559,21 +4820,21 @@
       <c r="D88" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="E88" s="3" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F88" s="5" t="n">
-        <v>18600</v>
-      </c>
-      <c r="G88" s="5" t="n">
-        <v>18600</v>
+      <c r="E88" s="3">
+        <v>46295</v>
+      </c>
+      <c r="F88" s="5">
+        <v>10080</v>
+      </c>
+      <c r="G88" s="5">
+        <v>10080</v>
       </c>
       <c r="H88" s="3"/>
-      <c r="I88" s="6" t="n">
+      <c r="I88" s="6">
         <v>27</v>
       </c>
       <c r="J88" s="4" t="s">
-        <v>26</v>
+        <v>189</v>
       </c>
       <c r="K88" s="4" t="s">
         <v>27</v>
@@ -4585,76 +4846,76 @@
       <c r="N88" s="4"/>
       <c r="O88" s="4"/>
     </row>
-    <row r="89" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A89" s="3" t="n">
+    <row r="89" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="3">
         <v>46253</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>45</v>
+        <v>168</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>193</v>
+        <v>230</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="E89" s="3" t="n">
+        <v>231</v>
+      </c>
+      <c r="E89" s="3">
         <v>46295</v>
       </c>
-      <c r="F89" s="5" t="n">
-        <v>10080</v>
-      </c>
-      <c r="G89" s="5" t="n">
-        <v>10080</v>
+      <c r="F89" s="5">
+        <v>2051.2199999999998</v>
+      </c>
+      <c r="G89" s="5">
+        <v>2051.2199999999998</v>
       </c>
       <c r="H89" s="3"/>
-      <c r="I89" s="6" t="n">
-        <v>26</v>
+      <c r="I89" s="6">
+        <v>27</v>
       </c>
       <c r="J89" s="4" t="s">
-        <v>189</v>
+        <v>18</v>
       </c>
       <c r="K89" s="4" t="s">
-        <v>27</v>
+        <v>171</v>
       </c>
       <c r="L89" s="4"/>
       <c r="M89" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N89" s="4"/>
       <c r="O89" s="4"/>
     </row>
-    <row r="90" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A90" s="3" t="n">
-        <v>46253</v>
+    <row r="90" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="3">
+        <v>46262</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>168</v>
+        <v>210</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>232</v>
+        <v>211</v>
       </c>
       <c r="D90" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="E90" s="3" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F90" s="5" t="n">
-        <v>2051.22</v>
-      </c>
-      <c r="G90" s="5" t="n">
-        <v>2051.22</v>
+      <c r="E90" s="3">
+        <v>46297</v>
+      </c>
+      <c r="F90" s="5">
+        <v>7694.4</v>
+      </c>
+      <c r="G90" s="5">
+        <v>7694.4</v>
       </c>
       <c r="H90" s="3"/>
-      <c r="I90" s="6" t="n">
+      <c r="I90" s="6">
+        <v>25</v>
+      </c>
+      <c r="J90" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="J90" s="4" t="s">
-        <v>18</v>
-      </c>
       <c r="K90" s="4" t="s">
-        <v>171</v>
+        <v>213</v>
       </c>
       <c r="L90" s="4"/>
       <c r="M90" s="4" t="s">
@@ -4663,8 +4924,8 @@
       <c r="N90" s="4"/>
       <c r="O90" s="4"/>
     </row>
-    <row r="91" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A91" s="3" t="n">
+    <row r="91" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="3">
         <v>46262</v>
       </c>
       <c r="B91" s="4" t="s">
@@ -4676,18 +4937,18 @@
       <c r="D91" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="E91" s="3" t="n">
+      <c r="E91" s="3">
         <v>46297</v>
       </c>
-      <c r="F91" s="5" t="n">
+      <c r="F91" s="5">
         <v>11660.11</v>
       </c>
-      <c r="G91" s="5" t="n">
+      <c r="G91" s="5">
         <v>11660.11</v>
       </c>
       <c r="H91" s="3"/>
-      <c r="I91" s="6" t="n">
-        <v>24</v>
+      <c r="I91" s="6">
+        <v>25</v>
       </c>
       <c r="J91" s="4" t="s">
         <v>189</v>
@@ -4702,37 +4963,37 @@
       <c r="N91" s="4"/>
       <c r="O91" s="4"/>
     </row>
-    <row r="92" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A92" s="3" t="n">
-        <v>46262</v>
+    <row r="92" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="3">
+        <v>46225</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>211</v>
+        <v>181</v>
       </c>
       <c r="D92" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="E92" s="3" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F92" s="5" t="n">
-        <v>7694.4</v>
-      </c>
-      <c r="G92" s="5" t="n">
-        <v>7694.4</v>
+      <c r="E92" s="3">
+        <v>46300</v>
+      </c>
+      <c r="F92" s="5">
+        <v>7551.88</v>
+      </c>
+      <c r="G92" s="5">
+        <v>7551.88</v>
       </c>
       <c r="H92" s="3"/>
-      <c r="I92" s="6" t="n">
-        <v>24</v>
+      <c r="I92" s="6">
+        <v>22</v>
       </c>
       <c r="J92" s="4" t="s">
-        <v>26</v>
+        <v>189</v>
       </c>
       <c r="K92" s="4" t="s">
-        <v>213</v>
+        <v>184</v>
       </c>
       <c r="L92" s="4"/>
       <c r="M92" s="4" t="s">
@@ -4741,37 +5002,37 @@
       <c r="N92" s="4"/>
       <c r="O92" s="4"/>
     </row>
-    <row r="93" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A93" s="3" t="n">
-        <v>46225</v>
+    <row r="93" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="3">
+        <v>46266</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>180</v>
+        <v>45</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="D93" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="E93" s="3" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F93" s="5" t="n">
-        <v>7551.88</v>
-      </c>
-      <c r="G93" s="5" t="n">
-        <v>7551.88</v>
+      <c r="E93" s="3">
+        <v>46301</v>
+      </c>
+      <c r="F93" s="5">
+        <v>18600</v>
+      </c>
+      <c r="G93" s="5">
+        <v>18600</v>
       </c>
       <c r="H93" s="3"/>
-      <c r="I93" s="6" t="n">
+      <c r="I93" s="6">
         <v>21</v>
       </c>
       <c r="J93" s="4" t="s">
-        <v>189</v>
+        <v>26</v>
       </c>
       <c r="K93" s="4" t="s">
-        <v>184</v>
+        <v>27</v>
       </c>
       <c r="L93" s="4"/>
       <c r="M93" s="4" t="s">
@@ -4780,37 +5041,37 @@
       <c r="N93" s="4"/>
       <c r="O93" s="4"/>
     </row>
-    <row r="94" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A94" s="3" t="n">
-        <v>46266</v>
+    <row r="94" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="3">
+        <v>46227</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>45</v>
+        <v>180</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="D94" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="E94" s="3" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F94" s="5" t="n">
-        <v>18600</v>
-      </c>
-      <c r="G94" s="5" t="n">
-        <v>18600</v>
+      <c r="E94" s="3">
+        <v>46302</v>
+      </c>
+      <c r="F94" s="5">
+        <v>4216.66</v>
+      </c>
+      <c r="G94" s="5">
+        <v>4216.66</v>
       </c>
       <c r="H94" s="3"/>
-      <c r="I94" s="6" t="n">
+      <c r="I94" s="6">
         <v>20</v>
       </c>
       <c r="J94" s="4" t="s">
-        <v>26</v>
+        <v>183</v>
       </c>
       <c r="K94" s="4" t="s">
-        <v>27</v>
+        <v>184</v>
       </c>
       <c r="L94" s="4"/>
       <c r="M94" s="4" t="s">
@@ -4819,37 +5080,37 @@
       <c r="N94" s="4"/>
       <c r="O94" s="4"/>
     </row>
-    <row r="95" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A95" s="3" t="n">
-        <v>46227</v>
+    <row r="95" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="3">
+        <v>46232</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>180</v>
+        <v>15</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="D95" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="E95" s="3" t="n">
+      <c r="E95" s="3">
         <v>46302</v>
       </c>
-      <c r="F95" s="5" t="n">
-        <v>4216.66</v>
-      </c>
-      <c r="G95" s="5" t="n">
-        <v>4216.66</v>
+      <c r="F95" s="5">
+        <v>9716</v>
+      </c>
+      <c r="G95" s="5">
+        <v>9716</v>
       </c>
       <c r="H95" s="3"/>
-      <c r="I95" s="6" t="n">
-        <v>19</v>
+      <c r="I95" s="6">
+        <v>20</v>
       </c>
       <c r="J95" s="4" t="s">
-        <v>183</v>
+        <v>26</v>
       </c>
       <c r="K95" s="4" t="s">
-        <v>184</v>
+        <v>39</v>
       </c>
       <c r="L95" s="4"/>
       <c r="M95" s="4" t="s">
@@ -4858,37 +5119,37 @@
       <c r="N95" s="4"/>
       <c r="O95" s="4"/>
     </row>
-    <row r="96" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A96" s="3" t="n">
-        <v>46232</v>
+    <row r="96" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="3">
+        <v>46253</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>175</v>
+        <v>193</v>
       </c>
       <c r="D96" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="E96" s="3" t="n">
+      <c r="E96" s="3">
         <v>46302</v>
       </c>
-      <c r="F96" s="5" t="n">
-        <v>9716</v>
-      </c>
-      <c r="G96" s="5" t="n">
-        <v>9716</v>
+      <c r="F96" s="5">
+        <v>10080</v>
+      </c>
+      <c r="G96" s="5">
+        <v>10080</v>
       </c>
       <c r="H96" s="3"/>
-      <c r="I96" s="6" t="n">
-        <v>19</v>
+      <c r="I96" s="6">
+        <v>20</v>
       </c>
       <c r="J96" s="4" t="s">
-        <v>26</v>
+        <v>189</v>
       </c>
       <c r="K96" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="L96" s="4"/>
       <c r="M96" s="4" t="s">
@@ -4897,37 +5158,37 @@
       <c r="N96" s="4"/>
       <c r="O96" s="4"/>
     </row>
-    <row r="97" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A97" s="3" t="n">
-        <v>46253</v>
+    <row r="97" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="3">
+        <v>46262</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>45</v>
+        <v>210</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
       <c r="D97" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="E97" s="3" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F97" s="5" t="n">
-        <v>10080</v>
-      </c>
-      <c r="G97" s="5" t="n">
-        <v>10080</v>
+      <c r="E97" s="3">
+        <v>46304</v>
+      </c>
+      <c r="F97" s="5">
+        <v>11660.11</v>
+      </c>
+      <c r="G97" s="5">
+        <v>11660.11</v>
       </c>
       <c r="H97" s="3"/>
-      <c r="I97" s="6" t="n">
-        <v>19</v>
+      <c r="I97" s="6">
+        <v>18</v>
       </c>
       <c r="J97" s="4" t="s">
         <v>189</v>
       </c>
       <c r="K97" s="4" t="s">
-        <v>27</v>
+        <v>213</v>
       </c>
       <c r="L97" s="4"/>
       <c r="M97" s="4" t="s">
@@ -4936,8 +5197,8 @@
       <c r="N97" s="4"/>
       <c r="O97" s="4"/>
     </row>
-    <row r="98" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A98" s="3" t="n">
+    <row r="98" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="3">
         <v>46262</v>
       </c>
       <c r="B98" s="4" t="s">
@@ -4949,18 +5210,18 @@
       <c r="D98" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="E98" s="3" t="n">
+      <c r="E98" s="3">
         <v>46304</v>
       </c>
-      <c r="F98" s="5" t="n">
+      <c r="F98" s="5">
         <v>7694.4</v>
       </c>
-      <c r="G98" s="5" t="n">
+      <c r="G98" s="5">
         <v>7694.4</v>
       </c>
       <c r="H98" s="3"/>
-      <c r="I98" s="6" t="n">
-        <v>17</v>
+      <c r="I98" s="6">
+        <v>18</v>
       </c>
       <c r="J98" s="4" t="s">
         <v>26</v>
@@ -4975,76 +5236,76 @@
       <c r="N98" s="4"/>
       <c r="O98" s="4"/>
     </row>
-    <row r="99" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A99" s="3" t="n">
-        <v>46262</v>
+    <row r="99" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="3">
+        <v>46265</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>210</v>
+        <v>135</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>211</v>
+        <v>251</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="E99" s="3" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F99" s="5" t="n">
-        <v>11660.11</v>
-      </c>
-      <c r="G99" s="5" t="n">
-        <v>11660.11</v>
+        <v>252</v>
+      </c>
+      <c r="E99" s="3">
+        <v>46305</v>
+      </c>
+      <c r="F99" s="5">
+        <v>4750</v>
+      </c>
+      <c r="G99" s="5">
+        <v>4750</v>
       </c>
       <c r="H99" s="3"/>
-      <c r="I99" s="6" t="n">
+      <c r="I99" s="6">
         <v>17</v>
       </c>
       <c r="J99" s="4" t="s">
         <v>189</v>
       </c>
       <c r="K99" s="4" t="s">
-        <v>213</v>
+        <v>54</v>
       </c>
       <c r="L99" s="4"/>
       <c r="M99" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="N99" s="4"/>
       <c r="O99" s="4"/>
     </row>
-    <row r="100" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A100" s="3" t="n">
-        <v>46265</v>
+    <row r="100" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="3">
+        <v>46232</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>253</v>
+        <v>215</v>
       </c>
       <c r="D100" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="E100" s="3" t="n">
-        <v>46305</v>
-      </c>
-      <c r="F100" s="5" t="n">
-        <v>4750</v>
-      </c>
-      <c r="G100" s="5" t="n">
-        <v>4750</v>
+      <c r="E100" s="3">
+        <v>46307</v>
+      </c>
+      <c r="F100" s="5">
+        <v>4082.04</v>
+      </c>
+      <c r="G100" s="5">
+        <v>4082.04</v>
       </c>
       <c r="H100" s="3"/>
-      <c r="I100" s="6" t="n">
-        <v>16</v>
+      <c r="I100" s="6">
+        <v>15</v>
       </c>
       <c r="J100" s="4" t="s">
         <v>189</v>
       </c>
       <c r="K100" s="4" t="s">
-        <v>54</v>
+        <v>184</v>
       </c>
       <c r="L100" s="4"/>
       <c r="M100" s="4" t="s">
@@ -5053,76 +5314,76 @@
       <c r="N100" s="4"/>
       <c r="O100" s="4"/>
     </row>
-    <row r="101" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A101" s="3" t="n">
-        <v>46232</v>
+    <row r="101" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="3">
+        <v>46248</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>180</v>
+        <v>15</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>217</v>
+        <v>256</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="E101" s="3" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F101" s="5" t="n">
-        <v>4082.04</v>
-      </c>
-      <c r="G101" s="5" t="n">
-        <v>4082.04</v>
+        <v>257</v>
+      </c>
+      <c r="E101" s="3">
+        <v>46308</v>
+      </c>
+      <c r="F101" s="5">
+        <v>23355.33</v>
+      </c>
+      <c r="G101" s="5">
+        <v>23355.33</v>
       </c>
       <c r="H101" s="3"/>
-      <c r="I101" s="6" t="n">
+      <c r="I101" s="6">
         <v>14</v>
       </c>
       <c r="J101" s="4" t="s">
         <v>189</v>
       </c>
       <c r="K101" s="4" t="s">
-        <v>184</v>
+        <v>39</v>
       </c>
       <c r="L101" s="4"/>
       <c r="M101" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N101" s="4"/>
       <c r="O101" s="4"/>
     </row>
-    <row r="102" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A102" s="3" t="n">
-        <v>46248</v>
+    <row r="102" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="3">
+        <v>46266</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>258</v>
+        <v>193</v>
       </c>
       <c r="D102" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="E102" s="3" t="n">
+      <c r="E102" s="3">
         <v>46308</v>
       </c>
-      <c r="F102" s="5" t="n">
-        <v>23355.33</v>
-      </c>
-      <c r="G102" s="5" t="n">
-        <v>23355.33</v>
+      <c r="F102" s="5">
+        <v>18600</v>
+      </c>
+      <c r="G102" s="5">
+        <v>18600</v>
       </c>
       <c r="H102" s="3"/>
-      <c r="I102" s="6" t="n">
-        <v>13</v>
+      <c r="I102" s="6">
+        <v>14</v>
       </c>
       <c r="J102" s="4" t="s">
-        <v>189</v>
+        <v>26</v>
       </c>
       <c r="K102" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="L102" s="4"/>
       <c r="M102" s="4" t="s">
@@ -5131,37 +5392,37 @@
       <c r="N102" s="4"/>
       <c r="O102" s="4"/>
     </row>
-    <row r="103" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A103" s="3" t="n">
-        <v>46266</v>
+    <row r="103" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="3">
+        <v>46234</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>45</v>
+        <v>180</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="D103" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="E103" s="3" t="n">
-        <v>46308</v>
-      </c>
-      <c r="F103" s="5" t="n">
-        <v>18600</v>
-      </c>
-      <c r="G103" s="5" t="n">
-        <v>18600</v>
+      <c r="E103" s="3">
+        <v>46309</v>
+      </c>
+      <c r="F103" s="5">
+        <v>3789.1</v>
+      </c>
+      <c r="G103" s="5">
+        <v>3789.1</v>
       </c>
       <c r="H103" s="3"/>
-      <c r="I103" s="6" t="n">
+      <c r="I103" s="6">
         <v>13</v>
       </c>
       <c r="J103" s="4" t="s">
-        <v>26</v>
+        <v>189</v>
       </c>
       <c r="K103" s="4" t="s">
-        <v>27</v>
+        <v>184</v>
       </c>
       <c r="L103" s="4"/>
       <c r="M103" s="4" t="s">
@@ -5170,76 +5431,76 @@
       <c r="N103" s="4"/>
       <c r="O103" s="4"/>
     </row>
-    <row r="104" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A104" s="3" t="n">
-        <v>46234</v>
+    <row r="104" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="3">
+        <v>46268</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>180</v>
+        <v>23</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>181</v>
+        <v>263</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="E104" s="3" t="n">
-        <v>46309</v>
-      </c>
-      <c r="F104" s="5" t="n">
-        <v>3789.1</v>
-      </c>
-      <c r="G104" s="5" t="n">
-        <v>3789.1</v>
+        <v>264</v>
+      </c>
+      <c r="E104" s="3">
+        <v>46310</v>
+      </c>
+      <c r="F104" s="5">
+        <v>2754</v>
+      </c>
+      <c r="G104" s="5">
+        <v>2754</v>
       </c>
       <c r="H104" s="3"/>
-      <c r="I104" s="6" t="n">
+      <c r="I104" s="6">
         <v>12</v>
       </c>
       <c r="J104" s="4" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="K104" s="4" t="s">
-        <v>184</v>
+        <v>71</v>
       </c>
       <c r="L104" s="4"/>
       <c r="M104" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N104" s="4"/>
       <c r="O104" s="4"/>
     </row>
-    <row r="105" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A105" s="3" t="n">
-        <v>46268</v>
+    <row r="105" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="3">
+        <v>46262</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>23</v>
+        <v>210</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>265</v>
+        <v>211</v>
       </c>
       <c r="D105" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="E105" s="3" t="n">
-        <v>46310</v>
-      </c>
-      <c r="F105" s="5" t="n">
-        <v>2754</v>
-      </c>
-      <c r="G105" s="5" t="n">
-        <v>2754</v>
+      <c r="E105" s="3">
+        <v>46311</v>
+      </c>
+      <c r="F105" s="5">
+        <v>7694.4</v>
+      </c>
+      <c r="G105" s="5">
+        <v>7694.4</v>
       </c>
       <c r="H105" s="3"/>
-      <c r="I105" s="6" t="n">
+      <c r="I105" s="6">
         <v>11</v>
       </c>
       <c r="J105" s="4" t="s">
-        <v>183</v>
+        <v>26</v>
       </c>
       <c r="K105" s="4" t="s">
-        <v>71</v>
+        <v>213</v>
       </c>
       <c r="L105" s="4"/>
       <c r="M105" s="4" t="s">
@@ -5248,37 +5509,37 @@
       <c r="N105" s="4"/>
       <c r="O105" s="4"/>
     </row>
-    <row r="106" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A106" s="3" t="n">
-        <v>46258</v>
+    <row r="106" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="3">
+        <v>46262</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>135</v>
+        <v>210</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>253</v>
+        <v>211</v>
       </c>
       <c r="D106" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="E106" s="3" t="n">
+      <c r="E106" s="3">
         <v>46311</v>
       </c>
-      <c r="F106" s="5" t="n">
-        <v>6247.5</v>
-      </c>
-      <c r="G106" s="5" t="n">
-        <v>11266.12</v>
+      <c r="F106" s="5">
+        <v>11660.11</v>
+      </c>
+      <c r="G106" s="5">
+        <v>11660.11</v>
       </c>
       <c r="H106" s="3"/>
-      <c r="I106" s="6" t="n">
-        <v>10</v>
+      <c r="I106" s="6">
+        <v>11</v>
       </c>
       <c r="J106" s="4" t="s">
         <v>189</v>
       </c>
       <c r="K106" s="4" t="s">
-        <v>54</v>
+        <v>213</v>
       </c>
       <c r="L106" s="4"/>
       <c r="M106" s="4" t="s">
@@ -5287,37 +5548,37 @@
       <c r="N106" s="4"/>
       <c r="O106" s="4"/>
     </row>
-    <row r="107" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A107" s="3" t="n">
-        <v>46262</v>
+    <row r="107" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="3">
+        <v>46258</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>210</v>
+        <v>135</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>211</v>
+        <v>251</v>
       </c>
       <c r="D107" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="E107" s="3" t="n">
-        <v>46311</v>
-      </c>
-      <c r="F107" s="5" t="n">
-        <v>11660.11</v>
-      </c>
-      <c r="G107" s="5" t="n">
-        <v>11660.11</v>
+      <c r="E107" s="3">
+        <v>46313</v>
+      </c>
+      <c r="F107" s="5">
+        <v>6247.5</v>
+      </c>
+      <c r="G107" s="5">
+        <v>6247.5</v>
       </c>
       <c r="H107" s="3"/>
-      <c r="I107" s="6" t="n">
-        <v>10</v>
+      <c r="I107" s="6">
+        <v>9</v>
       </c>
       <c r="J107" s="4" t="s">
         <v>189</v>
       </c>
       <c r="K107" s="4" t="s">
-        <v>213</v>
+        <v>54</v>
       </c>
       <c r="L107" s="4"/>
       <c r="M107" s="4" t="s">
@@ -5326,70 +5587,70 @@
       <c r="N107" s="4"/>
       <c r="O107" s="4"/>
     </row>
-    <row r="108" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A108" s="3" t="n">
-        <v>46262</v>
+    <row r="108" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="3">
+        <v>46286</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>210</v>
+        <v>168</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>211</v>
+        <v>272</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="E108" s="3" t="n">
-        <v>46311</v>
-      </c>
-      <c r="F108" s="5" t="n">
-        <v>7694.4</v>
-      </c>
-      <c r="G108" s="5" t="n">
-        <v>7694.4</v>
+        <v>273</v>
+      </c>
+      <c r="E108" s="3">
+        <v>46314</v>
+      </c>
+      <c r="F108" s="5">
+        <v>5475.86</v>
+      </c>
+      <c r="G108" s="5">
+        <v>5475.86</v>
       </c>
       <c r="H108" s="3"/>
-      <c r="I108" s="6" t="n">
-        <v>10</v>
+      <c r="I108" s="6">
+        <v>8</v>
       </c>
       <c r="J108" s="4" t="s">
-        <v>26</v>
+        <v>189</v>
       </c>
       <c r="K108" s="4" t="s">
-        <v>213</v>
+        <v>171</v>
       </c>
       <c r="L108" s="4"/>
       <c r="M108" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N108" s="4"/>
       <c r="O108" s="4"/>
     </row>
-    <row r="109" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A109" s="3" t="n">
-        <v>46258</v>
+    <row r="109" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="3">
+        <v>46265</v>
       </c>
       <c r="B109" s="4" t="s">
         <v>135</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="E109" s="3" t="n">
-        <v>46313</v>
-      </c>
-      <c r="F109" s="5" t="n">
-        <v>6247.5</v>
-      </c>
-      <c r="G109" s="5" t="n">
-        <v>6247.5</v>
+        <v>275</v>
+      </c>
+      <c r="E109" s="3">
+        <v>46315</v>
+      </c>
+      <c r="F109" s="5">
+        <v>4750</v>
+      </c>
+      <c r="G109" s="5">
+        <v>4750</v>
       </c>
       <c r="H109" s="3"/>
-      <c r="I109" s="6" t="n">
-        <v>8</v>
+      <c r="I109" s="6">
+        <v>7</v>
       </c>
       <c r="J109" s="4" t="s">
         <v>189</v>
@@ -5399,510 +5660,510 @@
       </c>
       <c r="L109" s="4"/>
       <c r="M109" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N109" s="4"/>
       <c r="O109" s="4"/>
     </row>
-    <row r="110" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A110" s="3" t="n">
-        <v>46286</v>
+    <row r="110" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="3">
+        <v>46280</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>168</v>
+        <v>15</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="E110" s="3" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F110" s="5" t="n">
-        <v>5475.86</v>
-      </c>
-      <c r="G110" s="5" t="n">
-        <v>5475.86</v>
+        <v>278</v>
+      </c>
+      <c r="E110" s="3">
+        <v>46315</v>
+      </c>
+      <c r="F110" s="5">
+        <v>9196.5</v>
+      </c>
+      <c r="G110" s="5">
+        <v>12695.59</v>
       </c>
       <c r="H110" s="3"/>
-      <c r="I110" s="6" t="n">
+      <c r="I110" s="6">
         <v>7</v>
       </c>
       <c r="J110" s="4" t="s">
         <v>189</v>
       </c>
       <c r="K110" s="4" t="s">
-        <v>171</v>
+        <v>39</v>
       </c>
       <c r="L110" s="4"/>
       <c r="M110" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="N110" s="4"/>
       <c r="O110" s="4"/>
     </row>
-    <row r="111" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A111" s="3" t="n">
-        <v>46265</v>
+    <row r="111" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="3">
+        <v>46287</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>135</v>
+        <v>168</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>253</v>
+        <v>280</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="E111" s="3" t="n">
+        <v>281</v>
+      </c>
+      <c r="E111" s="3">
         <v>46315</v>
       </c>
-      <c r="F111" s="5" t="n">
-        <v>4750</v>
-      </c>
-      <c r="G111" s="5" t="n">
-        <v>4750</v>
+      <c r="F111" s="5">
+        <v>4466.2700000000004</v>
+      </c>
+      <c r="G111" s="5">
+        <v>4466.2700000000004</v>
       </c>
       <c r="H111" s="3"/>
-      <c r="I111" s="6" t="n">
-        <v>6</v>
+      <c r="I111" s="6">
+        <v>7</v>
       </c>
       <c r="J111" s="4" t="s">
         <v>189</v>
       </c>
       <c r="K111" s="4" t="s">
-        <v>54</v>
+        <v>171</v>
       </c>
       <c r="L111" s="4"/>
       <c r="M111" s="4" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="N111" s="4"/>
       <c r="O111" s="4"/>
     </row>
-    <row r="112" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A112" s="3" t="n">
-        <v>46280</v>
+    <row r="112" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="3">
+        <v>46287</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>15</v>
+        <v>68</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>282</v>
-      </c>
-      <c r="E112" s="3" t="n">
+        <v>284</v>
+      </c>
+      <c r="E112" s="3">
         <v>46315</v>
       </c>
-      <c r="F112" s="5" t="n">
-        <v>9196.5</v>
-      </c>
-      <c r="G112" s="5" t="n">
-        <v>12695.59</v>
+      <c r="F112" s="5">
+        <v>784.63</v>
+      </c>
+      <c r="G112" s="5">
+        <v>979.25</v>
       </c>
       <c r="H112" s="3"/>
-      <c r="I112" s="6" t="n">
-        <v>6</v>
+      <c r="I112" s="6">
+        <v>7</v>
       </c>
       <c r="J112" s="4" t="s">
-        <v>189</v>
+        <v>18</v>
       </c>
       <c r="K112" s="4" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="L112" s="4"/>
       <c r="M112" s="4" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="N112" s="4"/>
       <c r="O112" s="4"/>
     </row>
-    <row r="113" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A113" s="3" t="n">
-        <v>46287</v>
+    <row r="113" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="3">
+        <v>46266</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>168</v>
+        <v>45</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>284</v>
+        <v>193</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>285</v>
-      </c>
-      <c r="E113" s="3" t="n">
+        <v>286</v>
+      </c>
+      <c r="E113" s="3">
         <v>46315</v>
       </c>
-      <c r="F113" s="5" t="n">
-        <v>4466.27</v>
-      </c>
-      <c r="G113" s="5" t="n">
-        <v>4466.27</v>
+      <c r="F113" s="5">
+        <v>18600</v>
+      </c>
+      <c r="G113" s="5">
+        <v>18600</v>
       </c>
       <c r="H113" s="3"/>
-      <c r="I113" s="6" t="n">
-        <v>6</v>
+      <c r="I113" s="6">
+        <v>7</v>
       </c>
       <c r="J113" s="4" t="s">
-        <v>189</v>
+        <v>26</v>
       </c>
       <c r="K113" s="4" t="s">
-        <v>171</v>
+        <v>27</v>
       </c>
       <c r="L113" s="4"/>
       <c r="M113" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N113" s="4"/>
       <c r="O113" s="4"/>
     </row>
-    <row r="114" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A114" s="3" t="n">
-        <v>46280</v>
+    <row r="114" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="3">
+        <v>46253</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>45</v>
+        <v>168</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>288</v>
-      </c>
-      <c r="E114" s="3" t="n">
-        <v>46315</v>
-      </c>
-      <c r="F114" s="5" t="n">
-        <v>1600</v>
-      </c>
-      <c r="G114" s="5" t="n">
-        <v>1600</v>
+        <v>289</v>
+      </c>
+      <c r="E114" s="3">
+        <v>46316</v>
+      </c>
+      <c r="F114" s="5">
+        <v>1452.6</v>
+      </c>
+      <c r="G114" s="5">
+        <v>1452.6</v>
       </c>
       <c r="H114" s="3"/>
-      <c r="I114" s="6" t="n">
+      <c r="I114" s="6">
         <v>6</v>
       </c>
       <c r="J114" s="4" t="s">
-        <v>189</v>
+        <v>18</v>
       </c>
       <c r="K114" s="4" t="s">
-        <v>75</v>
+        <v>171</v>
       </c>
       <c r="L114" s="4"/>
       <c r="M114" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N114" s="4"/>
       <c r="O114" s="4"/>
     </row>
-    <row r="115" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A115" s="3" t="n">
-        <v>46287</v>
+    <row r="115" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="3">
+        <v>46288</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="E115" s="3" t="n">
-        <v>46315</v>
-      </c>
-      <c r="F115" s="5" t="n">
-        <v>784.63</v>
-      </c>
-      <c r="G115" s="5" t="n">
-        <v>979.25</v>
+        <v>292</v>
+      </c>
+      <c r="E115" s="3">
+        <v>46316</v>
+      </c>
+      <c r="F115" s="5">
+        <v>4772.8999999999996</v>
+      </c>
+      <c r="G115" s="5">
+        <v>4772.8999999999996</v>
       </c>
       <c r="H115" s="3"/>
-      <c r="I115" s="6" t="n">
+      <c r="I115" s="6">
         <v>6</v>
       </c>
       <c r="J115" s="4" t="s">
-        <v>18</v>
+        <v>189</v>
       </c>
       <c r="K115" s="4" t="s">
-        <v>71</v>
+        <v>293</v>
       </c>
       <c r="L115" s="4"/>
       <c r="M115" s="4" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="N115" s="4"/>
       <c r="O115" s="4"/>
     </row>
-    <row r="116" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A116" s="3" t="n">
-        <v>46266</v>
+    <row r="116" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="3">
+        <v>46288</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>193</v>
+        <v>263</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="E116" s="3" t="n">
-        <v>46315</v>
-      </c>
-      <c r="F116" s="5" t="n">
-        <v>18600</v>
-      </c>
-      <c r="G116" s="5" t="n">
-        <v>18600</v>
+        <v>295</v>
+      </c>
+      <c r="E116" s="3">
+        <v>46316</v>
+      </c>
+      <c r="F116" s="5">
+        <v>2334.2399999999998</v>
+      </c>
+      <c r="G116" s="5">
+        <v>2334.2399999999998</v>
       </c>
       <c r="H116" s="3"/>
-      <c r="I116" s="6" t="n">
+      <c r="I116" s="6">
         <v>6</v>
       </c>
       <c r="J116" s="4" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="K116" s="4" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="L116" s="4"/>
       <c r="M116" s="4" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="N116" s="4"/>
       <c r="O116" s="4"/>
     </row>
-    <row r="117" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A117" s="3" t="n">
-        <v>46253</v>
+    <row r="117" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="3">
+        <v>46287</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>168</v>
+        <v>297</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="E117" s="3" t="n">
-        <v>46316</v>
-      </c>
-      <c r="F117" s="5" t="n">
-        <v>1452.6</v>
-      </c>
-      <c r="G117" s="5" t="n">
-        <v>1452.6</v>
+        <v>299</v>
+      </c>
+      <c r="E117" s="3">
+        <v>46317</v>
+      </c>
+      <c r="F117" s="5">
+        <v>9617.7999999999993</v>
+      </c>
+      <c r="G117" s="5">
+        <v>9617.7999999999993</v>
       </c>
       <c r="H117" s="3"/>
-      <c r="I117" s="6" t="n">
+      <c r="I117" s="6">
         <v>5</v>
       </c>
       <c r="J117" s="4" t="s">
-        <v>18</v>
+        <v>189</v>
       </c>
       <c r="K117" s="4" t="s">
-        <v>171</v>
+        <v>300</v>
       </c>
       <c r="L117" s="4"/>
       <c r="M117" s="4" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="N117" s="4"/>
       <c r="O117" s="4"/>
     </row>
-    <row r="118" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A118" s="3" t="n">
-        <v>46288</v>
+    <row r="118" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="3">
+        <v>46262</v>
       </c>
       <c r="B118" s="4" t="s">
         <v>168</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="E118" s="3" t="n">
-        <v>46316</v>
-      </c>
-      <c r="F118" s="5" t="n">
-        <v>4772.9</v>
-      </c>
-      <c r="G118" s="5" t="n">
-        <v>4772.9</v>
+        <v>302</v>
+      </c>
+      <c r="E118" s="3">
+        <v>46318</v>
+      </c>
+      <c r="F118" s="5">
+        <v>2992</v>
+      </c>
+      <c r="G118" s="5">
+        <v>2992</v>
       </c>
       <c r="H118" s="3"/>
-      <c r="I118" s="6" t="n">
-        <v>5</v>
+      <c r="I118" s="6">
+        <v>4</v>
       </c>
       <c r="J118" s="4" t="s">
         <v>189</v>
       </c>
       <c r="K118" s="4" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="L118" s="4"/>
       <c r="M118" s="4" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="N118" s="4"/>
       <c r="O118" s="4"/>
     </row>
-    <row r="119" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A119" s="3" t="n">
-        <v>46288</v>
+    <row r="119" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="3">
+        <v>46290</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>23</v>
+        <v>168</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>265</v>
+        <v>304</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="E119" s="3" t="n">
-        <v>46316</v>
-      </c>
-      <c r="F119" s="5" t="n">
-        <v>2334.24</v>
-      </c>
-      <c r="G119" s="5" t="n">
-        <v>2334.24</v>
+        <v>305</v>
+      </c>
+      <c r="E119" s="3">
+        <v>46318</v>
+      </c>
+      <c r="F119" s="5">
+        <v>5206.7700000000004</v>
+      </c>
+      <c r="G119" s="5">
+        <v>10139.15</v>
       </c>
       <c r="H119" s="3"/>
-      <c r="I119" s="6" t="n">
-        <v>5</v>
+      <c r="I119" s="6">
+        <v>4</v>
       </c>
       <c r="J119" s="4" t="s">
-        <v>18</v>
+        <v>189</v>
       </c>
       <c r="K119" s="4" t="s">
-        <v>71</v>
+        <v>171</v>
       </c>
       <c r="L119" s="4"/>
       <c r="M119" s="4" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="N119" s="4"/>
       <c r="O119" s="4"/>
     </row>
-    <row r="120" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A120" s="3" t="n">
-        <v>46287</v>
+    <row r="120" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="3">
+        <v>46268</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>304</v>
+        <v>180</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="E120" s="3" t="n">
-        <v>46317</v>
-      </c>
-      <c r="F120" s="5" t="n">
-        <v>9617.8</v>
-      </c>
-      <c r="G120" s="5" t="n">
-        <v>9617.8</v>
+        <v>308</v>
+      </c>
+      <c r="E120" s="3">
+        <v>46318</v>
+      </c>
+      <c r="F120" s="5">
+        <v>3714.54</v>
+      </c>
+      <c r="G120" s="5">
+        <v>3714.54</v>
       </c>
       <c r="H120" s="3"/>
-      <c r="I120" s="6" t="n">
+      <c r="I120" s="6">
         <v>4</v>
       </c>
       <c r="J120" s="4" t="s">
         <v>189</v>
       </c>
       <c r="K120" s="4" t="s">
-        <v>307</v>
+        <v>184</v>
       </c>
       <c r="L120" s="4"/>
       <c r="M120" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="N120" s="4"/>
       <c r="O120" s="4"/>
     </row>
-    <row r="121" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A121" s="3" t="n">
+    <row r="121" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="3">
         <v>46262</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>168</v>
+        <v>210</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>298</v>
+        <v>211</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="E121" s="3" t="n">
+        <v>310</v>
+      </c>
+      <c r="E121" s="3">
         <v>46318</v>
       </c>
-      <c r="F121" s="5" t="n">
-        <v>2992</v>
-      </c>
-      <c r="G121" s="5" t="n">
-        <v>2992</v>
+      <c r="F121" s="5">
+        <v>11660.11</v>
+      </c>
+      <c r="G121" s="5">
+        <v>11660.11</v>
       </c>
       <c r="H121" s="3"/>
-      <c r="I121" s="6" t="n">
-        <v>3</v>
+      <c r="I121" s="6">
+        <v>4</v>
       </c>
       <c r="J121" s="4" t="s">
         <v>189</v>
       </c>
       <c r="K121" s="4" t="s">
-        <v>300</v>
+        <v>213</v>
       </c>
       <c r="L121" s="4"/>
       <c r="M121" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N121" s="4"/>
       <c r="O121" s="4"/>
     </row>
-    <row r="122" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A122" s="3" t="n">
-        <v>46290</v>
+    <row r="122" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="3">
+        <v>46262</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>168</v>
+        <v>210</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>311</v>
+        <v>211</v>
       </c>
       <c r="D122" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="E122" s="3" t="n">
+      <c r="E122" s="3">
         <v>46318</v>
       </c>
-      <c r="F122" s="5" t="n">
-        <v>5206.77</v>
-      </c>
-      <c r="G122" s="5" t="n">
-        <v>10139.15</v>
+      <c r="F122" s="5">
+        <v>7694.4</v>
+      </c>
+      <c r="G122" s="5">
+        <v>7694.4</v>
       </c>
       <c r="H122" s="3"/>
-      <c r="I122" s="6" t="n">
-        <v>3</v>
+      <c r="I122" s="6">
+        <v>4</v>
       </c>
       <c r="J122" s="4" t="s">
-        <v>189</v>
+        <v>26</v>
       </c>
       <c r="K122" s="4" t="s">
-        <v>171</v>
+        <v>213</v>
       </c>
       <c r="L122" s="4"/>
       <c r="M122" s="4" t="s">
@@ -5911,76 +6172,76 @@
       <c r="N122" s="4"/>
       <c r="O122" s="4"/>
     </row>
-    <row r="123" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A123" s="3" t="n">
-        <v>46268</v>
+    <row r="123" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="3">
+        <v>46258</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>180</v>
+        <v>23</v>
       </c>
       <c r="C123" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D123" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="D123" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="E123" s="3" t="n">
+      <c r="E123" s="3">
         <v>46318</v>
       </c>
-      <c r="F123" s="5" t="n">
-        <v>3714.54</v>
-      </c>
-      <c r="G123" s="5" t="n">
-        <v>3714.54</v>
+      <c r="F123" s="5">
+        <v>879.12</v>
+      </c>
+      <c r="G123" s="5">
+        <v>879.12</v>
       </c>
       <c r="H123" s="3"/>
-      <c r="I123" s="6" t="n">
-        <v>3</v>
+      <c r="I123" s="6">
+        <v>4</v>
       </c>
       <c r="J123" s="4" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="K123" s="4" t="s">
-        <v>184</v>
+        <v>71</v>
       </c>
       <c r="L123" s="4"/>
       <c r="M123" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="N123" s="4"/>
       <c r="O123" s="4"/>
     </row>
-    <row r="124" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A124" s="3" t="n">
-        <v>46262</v>
+    <row r="124" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="3">
+        <v>46259</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>210</v>
+        <v>15</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>211</v>
+        <v>316</v>
       </c>
       <c r="D124" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="E124" s="3" t="n">
-        <v>46318</v>
-      </c>
-      <c r="F124" s="5" t="n">
-        <v>7694.4</v>
-      </c>
-      <c r="G124" s="5" t="n">
-        <v>7694.4</v>
+      <c r="E124" s="3">
+        <v>46319</v>
+      </c>
+      <c r="F124" s="5">
+        <v>6265</v>
+      </c>
+      <c r="G124" s="5">
+        <v>6265</v>
       </c>
       <c r="H124" s="3"/>
-      <c r="I124" s="6" t="n">
+      <c r="I124" s="6">
         <v>3</v>
       </c>
       <c r="J124" s="4" t="s">
-        <v>26</v>
+        <v>189</v>
       </c>
       <c r="K124" s="4" t="s">
-        <v>213</v>
+        <v>19</v>
       </c>
       <c r="L124" s="4"/>
       <c r="M124" s="4" t="s">
@@ -5989,37 +6250,37 @@
       <c r="N124" s="4"/>
       <c r="O124" s="4"/>
     </row>
-    <row r="125" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A125" s="3" t="n">
-        <v>46262</v>
+    <row r="125" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="3">
+        <v>46286</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>210</v>
+        <v>168</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>211</v>
+        <v>272</v>
       </c>
       <c r="D125" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="E125" s="3" t="n">
-        <v>46318</v>
-      </c>
-      <c r="F125" s="5" t="n">
-        <v>11660.11</v>
-      </c>
-      <c r="G125" s="5" t="n">
-        <v>11660.11</v>
+      <c r="E125" s="3">
+        <v>46321</v>
+      </c>
+      <c r="F125" s="5">
+        <v>5475.86</v>
+      </c>
+      <c r="G125" s="5">
+        <v>5475.86</v>
       </c>
       <c r="H125" s="3"/>
-      <c r="I125" s="6" t="n">
-        <v>3</v>
+      <c r="I125" s="6">
+        <v>1</v>
       </c>
       <c r="J125" s="4" t="s">
         <v>189</v>
       </c>
       <c r="K125" s="4" t="s">
-        <v>213</v>
+        <v>171</v>
       </c>
       <c r="L125" s="4"/>
       <c r="M125" s="4" t="s">
@@ -6028,67 +6289,7 @@
       <c r="N125" s="4"/>
       <c r="O125" s="4"/>
     </row>
-    <row r="126" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A126" s="3" t="n">
-        <v>46258</v>
-      </c>
-      <c r="B126" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C126" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="D126" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="E126" s="3" t="n">
-        <v>46318</v>
-      </c>
-      <c r="F126" s="5" t="n">
-        <v>879.12</v>
-      </c>
-      <c r="G126" s="5" t="n">
-        <v>879.12</v>
-      </c>
-      <c r="H126" s="3"/>
-      <c r="I126" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J126" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="K126" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="L126" s="4"/>
-      <c r="M126" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="N126" s="4"/>
-      <c r="O126" s="4"/>
-    </row>
-    <row r="127" customHeight="true" ht="13.5" customFormat="true" s="1">
-      <c r="A127" s="7"/>
-      <c r="B127" s="8"/>
-      <c r="C127" s="8"/>
-      <c r="D127" s="8"/>
-      <c r="E127" s="8"/>
-      <c r="F127" s="9" t="n">
-        <v>724246.69</v>
-      </c>
-      <c r="G127" s="9" t="n">
-        <v>766903.69</v>
-      </c>
-      <c r="H127" s="8"/>
-      <c r="I127" s="8"/>
-      <c r="J127" s="8"/>
-      <c r="K127" s="8"/>
-      <c r="L127" s="8"/>
-      <c r="M127" s="8"/>
-      <c r="N127" s="8"/>
-      <c r="O127" s="10"/>
-    </row>
   </sheetData>
-  <pageSetup orientation="default" cellComments="none"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
+++ b/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WINDOWS\Desktop\dados planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CD9840F-26CA-417F-A744-7E9A7C54B319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CE261F3-3246-4E79-8428-6A2504B9A293}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="743" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="719" uniqueCount="309">
   <si>
     <t>Dt.Emissão</t>
   </si>
@@ -648,13 +648,58 @@
     <t>70793157800010080000001121205064100656766204</t>
   </si>
   <si>
-    <t>DROGUISTA CEARENSE LTDA</t>
-  </si>
-  <si>
-    <t>01007171.2</t>
-  </si>
-  <si>
-    <t>70794157800003640000001121205064100656766162</t>
+    <t>01007005.4</t>
+  </si>
+  <si>
+    <t>00197158200009716000000003473568000003146117</t>
+  </si>
+  <si>
+    <t>FERMATA LTDA</t>
+  </si>
+  <si>
+    <t>01006989.2</t>
+  </si>
+  <si>
+    <t>70795158200004082050001121205064100656764191</t>
+  </si>
+  <si>
+    <t>01007125.5</t>
+  </si>
+  <si>
+    <t>70799158300004320000001121205064100656765131</t>
+  </si>
+  <si>
+    <t>01006922.3</t>
+  </si>
+  <si>
+    <t>70798158300011200000001121205064100656763896</t>
+  </si>
+  <si>
+    <t>01007301.2</t>
+  </si>
+  <si>
+    <t>00197158400018600000000003473568000003161417</t>
+  </si>
+  <si>
+    <t>01007023.2</t>
+  </si>
+  <si>
+    <t>70791158400003789090001121205064100656764423</t>
+  </si>
+  <si>
+    <t>01007187.4</t>
+  </si>
+  <si>
+    <t>70792158500010080000001121205064100656766212</t>
+  </si>
+  <si>
+    <t>VITAL DISTRIBUIDORA LTDA</t>
+  </si>
+  <si>
+    <t>01007168.3</t>
+  </si>
+  <si>
+    <t>34196158500002051221090002617698120992717000</t>
   </si>
   <si>
     <t>FELIPE AQUINO - MT</t>
@@ -663,78 +708,12 @@
     <t>FAMA DISTRIBUIDORA HOSPITALAR LTDA</t>
   </si>
   <si>
-    <t>01007265.1</t>
+    <t>01007249.2</t>
   </si>
   <si>
     <t>MT</t>
   </si>
   <si>
-    <t>00198158000007694400000003473568000003158817</t>
-  </si>
-  <si>
-    <t>FERMATA LTDA</t>
-  </si>
-  <si>
-    <t>01006989.2</t>
-  </si>
-  <si>
-    <t>70795158200004082050001121205064100656764191</t>
-  </si>
-  <si>
-    <t>01007005.4</t>
-  </si>
-  <si>
-    <t>00197158200009716000000003473568000003146117</t>
-  </si>
-  <si>
-    <t>01007125.5</t>
-  </si>
-  <si>
-    <t>70799158300004320000001121205064100656765131</t>
-  </si>
-  <si>
-    <t>01006922.3</t>
-  </si>
-  <si>
-    <t>70798158300011200000001121205064100656763896</t>
-  </si>
-  <si>
-    <t>01007023.2</t>
-  </si>
-  <si>
-    <t>70791158400003789090001121205064100656764423</t>
-  </si>
-  <si>
-    <t>01007301.2</t>
-  </si>
-  <si>
-    <t>00197158400018600000000003473568000003161417</t>
-  </si>
-  <si>
-    <t>01007187.4</t>
-  </si>
-  <si>
-    <t>70792158500010080000001121205064100656766212</t>
-  </si>
-  <si>
-    <t>VITAL DISTRIBUIDORA LTDA</t>
-  </si>
-  <si>
-    <t>01007168.3</t>
-  </si>
-  <si>
-    <t>34196158500002051221090002617698120992717000</t>
-  </si>
-  <si>
-    <t>01007265.2</t>
-  </si>
-  <si>
-    <t>00192158700007694400000003473568000003158917</t>
-  </si>
-  <si>
-    <t>01007249.2</t>
-  </si>
-  <si>
     <t>70792158700011660110001121205064100656766923</t>
   </si>
   <si>
@@ -750,24 +729,24 @@
     <t>00191159100018600000000003473568000003161517</t>
   </si>
   <si>
+    <t>01007187.5</t>
+  </si>
+  <si>
+    <t>70791159200010080000001121205064100656766220</t>
+  </si>
+  <si>
+    <t>01007005.5</t>
+  </si>
+  <si>
+    <t>00198159200009716000000003473568000003146217</t>
+  </si>
+  <si>
     <t>01006976.3</t>
   </si>
   <si>
     <t>23792159200004216660435090000000114800304920</t>
   </si>
   <si>
-    <t>01007005.5</t>
-  </si>
-  <si>
-    <t>00198159200009716000000003473568000003146217</t>
-  </si>
-  <si>
-    <t>01007187.5</t>
-  </si>
-  <si>
-    <t>70791159200010080000001121205064100656766220</t>
-  </si>
-  <si>
     <t>01007249.3</t>
   </si>
   <si>
@@ -795,15 +774,6 @@
     <t>70796159700004082040001121205064100656764209</t>
   </si>
   <si>
-    <t>ASPEN SERVICE COMERCIO LTDA</t>
-  </si>
-  <si>
-    <t>01007117.2</t>
-  </si>
-  <si>
-    <t>70793159800023355330001121205064100656765677</t>
-  </si>
-  <si>
     <t>01007301.4</t>
   </si>
   <si>
@@ -876,118 +846,112 @@
     <t>70791160500004466270001121205064100656768713</t>
   </si>
   <si>
+    <t>01007301.5</t>
+  </si>
+  <si>
+    <t>00199160500018600000000003473568000003161717</t>
+  </si>
+  <si>
+    <t>01007445.1</t>
+  </si>
+  <si>
+    <t>34191160600002334241090002633698120992717000</t>
+  </si>
+  <si>
+    <t>LEANDRA LUIZA SILVA - AM</t>
+  </si>
+  <si>
+    <t>JM COMERCIO DE PRODUTOS FARMACEUTICOS LTDA</t>
+  </si>
+  <si>
+    <t>01007348.1</t>
+  </si>
+  <si>
+    <t>AM</t>
+  </si>
+  <si>
+    <t>70794160700009617800001121205064100656768895</t>
+  </si>
+  <si>
+    <t>RC DISTRIBUIDORA FARMA E HOSPITALAR LTDA</t>
+  </si>
+  <si>
+    <t>01007319.3</t>
+  </si>
+  <si>
+    <t>70797160800003714540001121205064100656767541</t>
+  </si>
+  <si>
+    <t>01007265.5</t>
+  </si>
+  <si>
+    <t>00196160800007694400000003473568000003159217</t>
+  </si>
+  <si>
+    <t>SP HOSPITALAR LTDA</t>
+  </si>
+  <si>
+    <t>01007427.1</t>
+  </si>
+  <si>
+    <t>70796160800010139150001121205064100656769265</t>
+  </si>
+  <si>
+    <t>01007249.5</t>
+  </si>
+  <si>
+    <t>70791160800011660110001121205064100656766956</t>
+  </si>
+  <si>
+    <t>COBERMED COMERCIO DE MATERIAIS MEDICOS LTDA</t>
+  </si>
+  <si>
+    <t>01007194.3</t>
+  </si>
+  <si>
+    <t>70794160900006265000001121205064100656766667</t>
+  </si>
+  <si>
+    <t>01007342.2</t>
+  </si>
+  <si>
+    <t>70798161100005475860001121205064100656768671</t>
+  </si>
+  <si>
+    <t>01007371.2</t>
+  </si>
+  <si>
+    <t>70791161200004466270001121205064100656768721</t>
+  </si>
+  <si>
+    <t>MULTIMAIS ATACADO LTDA</t>
+  </si>
+  <si>
+    <t>01007400.3</t>
+  </si>
+  <si>
+    <t>70797161200001600000001121205064100656768077</t>
+  </si>
+  <si>
     <t>LOPES BARRETO COMERCIO DE PRODUTOS MEDICOS LTDA</t>
   </si>
   <si>
-    <t>01007429.1</t>
-  </si>
-  <si>
-    <t>34194160500000979251090002632528120992717000</t>
-  </si>
-  <si>
-    <t>01007301.5</t>
-  </si>
-  <si>
-    <t>00199160500018600000000003473568000003161717</t>
-  </si>
-  <si>
-    <t>HOSPMED LTDA</t>
-  </si>
-  <si>
-    <t>01007167.6</t>
-  </si>
-  <si>
-    <t>34198160600001452601090002617368120992717000</t>
-  </si>
-  <si>
-    <t>AMAZONIA HOSPITALAR LTDA</t>
-  </si>
-  <si>
-    <t>01007389.1</t>
-  </si>
-  <si>
-    <t>MA</t>
-  </si>
-  <si>
-    <t>70791160600004772900001121205064100656768978</t>
-  </si>
-  <si>
-    <t>01007445.1</t>
-  </si>
-  <si>
-    <t>34191160600002334241090002633698120992717000</t>
-  </si>
-  <si>
-    <t>LEANDRA LUIZA SILVA - AM</t>
-  </si>
-  <si>
-    <t>JM COMERCIO DE PRODUTOS FARMACEUTICOS LTDA</t>
-  </si>
-  <si>
-    <t>01007348.1</t>
-  </si>
-  <si>
-    <t>AM</t>
-  </si>
-  <si>
-    <t>70794160700009617800001121205064100656768895</t>
-  </si>
-  <si>
-    <t>01007224.5</t>
-  </si>
-  <si>
-    <t>70791160800002992000001121205064100656766899</t>
-  </si>
-  <si>
-    <t>SP HOSPITALAR LTDA</t>
-  </si>
-  <si>
-    <t>01007427.1</t>
-  </si>
-  <si>
-    <t>70796160800010139150001121205064100656769265</t>
-  </si>
-  <si>
-    <t>RC DISTRIBUIDORA FARMA E HOSPITALAR LTDA</t>
-  </si>
-  <si>
-    <t>01007319.3</t>
-  </si>
-  <si>
-    <t>70797160800003714540001121205064100656767541</t>
-  </si>
-  <si>
-    <t>01007249.5</t>
-  </si>
-  <si>
-    <t>70791160800011660110001121205064100656766956</t>
-  </si>
-  <si>
-    <t>01007265.5</t>
-  </si>
-  <si>
-    <t>00196160800007694400000003473568000003159217</t>
-  </si>
-  <si>
-    <t>01007217.3</t>
-  </si>
-  <si>
-    <t>23793160800000879120435090000000125900304920</t>
-  </si>
-  <si>
-    <t>COBERMED COMERCIO DE MATERIAIS MEDICOS LTDA</t>
-  </si>
-  <si>
-    <t>01007194.3</t>
-  </si>
-  <si>
-    <t>70794160900006265000001121205064100656766667</t>
-  </si>
-  <si>
-    <t>01007342.2</t>
-  </si>
-  <si>
-    <t>70798161100005475860001121205064100656768671</t>
+    <t>01007429.2</t>
+  </si>
+  <si>
+    <t>34199161200000784631090002632608120992717000</t>
+  </si>
+  <si>
+    <t>01007186.3</t>
+  </si>
+  <si>
+    <t>70798161200004689210001121205064100656766808</t>
+  </si>
+  <si>
+    <t>01006877.3</t>
+  </si>
+  <si>
+    <t>23793161200006265000435090000000110700304920</t>
   </si>
 </sst>
 </file>
@@ -1417,7 +1381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O125"/>
+  <dimension ref="A1:O121"/>
   <sheetFormatPr defaultColWidth="12.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.85546875" style="1" customWidth="1"/>
@@ -1509,7 +1473,7 @@
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="6">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>18</v>
@@ -1548,7 +1512,7 @@
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="6">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>18</v>
@@ -1587,7 +1551,7 @@
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="6">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>26</v>
@@ -1626,7 +1590,7 @@
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="6">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>18</v>
@@ -1665,7 +1629,7 @@
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="6">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>26</v>
@@ -1704,7 +1668,7 @@
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="6">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>26</v>
@@ -1743,7 +1707,7 @@
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="6">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>26</v>
@@ -1782,7 +1746,7 @@
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="6">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>18</v>
@@ -1821,7 +1785,7 @@
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="6">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>18</v>
@@ -1860,7 +1824,7 @@
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="6">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>18</v>
@@ -1899,7 +1863,7 @@
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="6">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>18</v>
@@ -1938,7 +1902,7 @@
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="6">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>18</v>
@@ -1977,7 +1941,7 @@
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="6">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>18</v>
@@ -2016,7 +1980,7 @@
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="6">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>18</v>
@@ -2055,7 +2019,7 @@
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="6">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>18</v>
@@ -2094,7 +2058,7 @@
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="6">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>18</v>
@@ -2133,7 +2097,7 @@
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="6">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>18</v>
@@ -2172,7 +2136,7 @@
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="6">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="J19" s="4" t="s">
         <v>18</v>
@@ -2211,7 +2175,7 @@
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="6">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>18</v>
@@ -2250,7 +2214,7 @@
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="6">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>18</v>
@@ -2289,7 +2253,7 @@
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="6">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="J22" s="4" t="s">
         <v>18</v>
@@ -2328,7 +2292,7 @@
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="6">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="J23" s="4" t="s">
         <v>18</v>
@@ -2367,7 +2331,7 @@
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="6">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="J24" s="4" t="s">
         <v>18</v>
@@ -2406,7 +2370,7 @@
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="6">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="J25" s="4" t="s">
         <v>26</v>
@@ -2445,7 +2409,7 @@
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="6">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="J26" s="4" t="s">
         <v>18</v>
@@ -2484,7 +2448,7 @@
       </c>
       <c r="H27" s="3"/>
       <c r="I27" s="6">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="J27" s="4" t="s">
         <v>26</v>
@@ -2523,7 +2487,7 @@
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="6">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="J28" s="4" t="s">
         <v>26</v>
@@ -2562,7 +2526,7 @@
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="6">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="J29" s="4" t="s">
         <v>18</v>
@@ -2601,7 +2565,7 @@
       </c>
       <c r="H30" s="3"/>
       <c r="I30" s="6">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="J30" s="4" t="s">
         <v>18</v>
@@ -2640,7 +2604,7 @@
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="6">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="J31" s="4" t="s">
         <v>18</v>
@@ -2679,7 +2643,7 @@
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="6">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="J32" s="4" t="s">
         <v>26</v>
@@ -2718,7 +2682,7 @@
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="6">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="J33" s="4" t="s">
         <v>18</v>
@@ -2757,7 +2721,7 @@
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="6">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="J34" s="4" t="s">
         <v>18</v>
@@ -2796,7 +2760,7 @@
       </c>
       <c r="H35" s="3"/>
       <c r="I35" s="6">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="J35" s="4" t="s">
         <v>18</v>
@@ -2835,7 +2799,7 @@
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="6">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="J36" s="4" t="s">
         <v>18</v>
@@ -2874,7 +2838,7 @@
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="6">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J37" s="4" t="s">
         <v>18</v>
@@ -2913,7 +2877,7 @@
       </c>
       <c r="H38" s="3"/>
       <c r="I38" s="6">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="J38" s="4" t="s">
         <v>18</v>
@@ -2952,7 +2916,7 @@
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="6">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="J39" s="4" t="s">
         <v>18</v>
@@ -2991,7 +2955,7 @@
       </c>
       <c r="H40" s="3"/>
       <c r="I40" s="6">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="J40" s="4" t="s">
         <v>18</v>
@@ -3030,7 +2994,7 @@
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="6">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="J41" s="4" t="s">
         <v>18</v>
@@ -3069,7 +3033,7 @@
       </c>
       <c r="H42" s="3"/>
       <c r="I42" s="6">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="J42" s="4" t="s">
         <v>18</v>
@@ -3108,7 +3072,7 @@
       </c>
       <c r="H43" s="3"/>
       <c r="I43" s="6">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="J43" s="4" t="s">
         <v>18</v>
@@ -3147,7 +3111,7 @@
       </c>
       <c r="H44" s="3"/>
       <c r="I44" s="6">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="J44" s="4" t="s">
         <v>26</v>
@@ -3186,7 +3150,7 @@
       </c>
       <c r="H45" s="3"/>
       <c r="I45" s="6">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="J45" s="4" t="s">
         <v>26</v>
@@ -3225,7 +3189,7 @@
       </c>
       <c r="H46" s="3"/>
       <c r="I46" s="6">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="J46" s="4" t="s">
         <v>26</v>
@@ -3264,7 +3228,7 @@
       </c>
       <c r="H47" s="3"/>
       <c r="I47" s="6">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="J47" s="4" t="s">
         <v>26</v>
@@ -3303,7 +3267,7 @@
       </c>
       <c r="H48" s="3"/>
       <c r="I48" s="6">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="J48" s="4" t="s">
         <v>26</v>
@@ -3342,7 +3306,7 @@
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="6">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="J49" s="4" t="s">
         <v>26</v>
@@ -3381,7 +3345,7 @@
       </c>
       <c r="H50" s="3"/>
       <c r="I50" s="6">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="J50" s="4" t="s">
         <v>26</v>
@@ -3420,7 +3384,7 @@
       </c>
       <c r="H51" s="3"/>
       <c r="I51" s="6">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="J51" s="4" t="s">
         <v>26</v>
@@ -3459,7 +3423,7 @@
       </c>
       <c r="H52" s="3"/>
       <c r="I52" s="6">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="J52" s="4" t="s">
         <v>26</v>
@@ -3498,7 +3462,7 @@
       </c>
       <c r="H53" s="3"/>
       <c r="I53" s="6">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="J53" s="4" t="s">
         <v>26</v>
@@ -3537,7 +3501,7 @@
       </c>
       <c r="H54" s="3"/>
       <c r="I54" s="6">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="J54" s="4"/>
       <c r="K54" s="4" t="s">
@@ -3572,7 +3536,7 @@
       </c>
       <c r="H55" s="3"/>
       <c r="I55" s="6">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="J55" s="4"/>
       <c r="K55" s="4" t="s">
@@ -3607,7 +3571,7 @@
       </c>
       <c r="H56" s="3"/>
       <c r="I56" s="6">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="J56" s="4"/>
       <c r="K56" s="4" t="s">
@@ -3642,7 +3606,7 @@
       </c>
       <c r="H57" s="3"/>
       <c r="I57" s="6">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="J57" s="4"/>
       <c r="K57" s="4" t="s">
@@ -3677,7 +3641,7 @@
       </c>
       <c r="H58" s="3"/>
       <c r="I58" s="6">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="J58" s="4" t="s">
         <v>26</v>
@@ -3716,7 +3680,7 @@
       </c>
       <c r="H59" s="3"/>
       <c r="I59" s="6">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="J59" s="4" t="s">
         <v>26</v>
@@ -3755,7 +3719,7 @@
       </c>
       <c r="H60" s="3"/>
       <c r="I60" s="6">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="J60" s="4" t="s">
         <v>26</v>
@@ -3794,7 +3758,7 @@
       </c>
       <c r="H61" s="3"/>
       <c r="I61" s="6">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="J61" s="4" t="s">
         <v>18</v>
@@ -3833,7 +3797,7 @@
       </c>
       <c r="H62" s="3"/>
       <c r="I62" s="6">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J62" s="4"/>
       <c r="K62" s="4" t="s">
@@ -3868,7 +3832,7 @@
       </c>
       <c r="H63" s="3"/>
       <c r="I63" s="6">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J63" s="4"/>
       <c r="K63" s="4" t="s">
@@ -3903,7 +3867,7 @@
       </c>
       <c r="H64" s="3"/>
       <c r="I64" s="6">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J64" s="4"/>
       <c r="K64" s="4" t="s">
@@ -3938,7 +3902,7 @@
       </c>
       <c r="H65" s="3"/>
       <c r="I65" s="6">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J65" s="4"/>
       <c r="K65" s="4" t="s">
@@ -3973,7 +3937,7 @@
       </c>
       <c r="H66" s="3"/>
       <c r="I66" s="6">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J66" s="4" t="s">
         <v>26</v>
@@ -4012,7 +3976,7 @@
       </c>
       <c r="H67" s="3"/>
       <c r="I67" s="6">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J67" s="4" t="s">
         <v>26</v>
@@ -4051,7 +4015,7 @@
       </c>
       <c r="H68" s="3"/>
       <c r="I68" s="6">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J68" s="4" t="s">
         <v>26</v>
@@ -4090,7 +4054,7 @@
       </c>
       <c r="H69" s="3"/>
       <c r="I69" s="6">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J69" s="4" t="s">
         <v>26</v>
@@ -4129,7 +4093,7 @@
       </c>
       <c r="H70" s="3"/>
       <c r="I70" s="6">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J70" s="4" t="s">
         <v>183</v>
@@ -4168,7 +4132,7 @@
       </c>
       <c r="H71" s="3"/>
       <c r="I71" s="6">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J71" s="4" t="s">
         <v>26</v>
@@ -4207,7 +4171,7 @@
       </c>
       <c r="H72" s="3"/>
       <c r="I72" s="6">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J72" s="4" t="s">
         <v>189</v>
@@ -4246,7 +4210,7 @@
       </c>
       <c r="H73" s="3"/>
       <c r="I73" s="6">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J73" s="4" t="s">
         <v>26</v>
@@ -4285,7 +4249,7 @@
       </c>
       <c r="H74" s="3"/>
       <c r="I74" s="6">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J74" s="4" t="s">
         <v>189</v>
@@ -4324,7 +4288,7 @@
       </c>
       <c r="H75" s="3"/>
       <c r="I75" s="6">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J75" s="4" t="s">
         <v>189</v>
@@ -4363,7 +4327,7 @@
       </c>
       <c r="H76" s="3"/>
       <c r="I76" s="6">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J76" s="4" t="s">
         <v>189</v>
@@ -4402,7 +4366,7 @@
       </c>
       <c r="H77" s="3"/>
       <c r="I77" s="6">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J77" s="4" t="s">
         <v>189</v>
@@ -4441,7 +4405,7 @@
       </c>
       <c r="H78" s="3"/>
       <c r="I78" s="6">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J78" s="4" t="s">
         <v>183</v>
@@ -4480,7 +4444,7 @@
       </c>
       <c r="H79" s="3"/>
       <c r="I79" s="6">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J79" s="4" t="s">
         <v>189</v>
@@ -4497,103 +4461,103 @@
     </row>
     <row r="80" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="3">
-        <v>46253</v>
+        <v>46232</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>121</v>
+        <v>15</v>
       </c>
       <c r="C80" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="D80" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="D80" s="4" t="s">
-        <v>208</v>
-      </c>
       <c r="E80" s="3">
-        <v>46288</v>
+        <v>46292</v>
       </c>
       <c r="F80" s="5">
-        <v>3640</v>
+        <v>9716</v>
       </c>
       <c r="G80" s="5">
-        <v>3640</v>
+        <v>9716</v>
       </c>
       <c r="H80" s="3"/>
       <c r="I80" s="6">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="J80" s="4" t="s">
-        <v>189</v>
+        <v>26</v>
       </c>
       <c r="K80" s="4" t="s">
-        <v>124</v>
+        <v>39</v>
       </c>
       <c r="L80" s="4"/>
       <c r="M80" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="N80" s="4"/>
       <c r="O80" s="4"/>
     </row>
     <row r="81" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="3">
-        <v>46262</v>
+        <v>46232</v>
       </c>
       <c r="B81" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="D81" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="C81" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="D81" s="4" t="s">
-        <v>212</v>
-      </c>
       <c r="E81" s="3">
-        <v>46290</v>
+        <v>46292</v>
       </c>
       <c r="F81" s="5">
-        <v>7694.4</v>
+        <v>4082.05</v>
       </c>
       <c r="G81" s="5">
-        <v>7694.4</v>
+        <v>4082.05</v>
       </c>
       <c r="H81" s="3"/>
       <c r="I81" s="6">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J81" s="4" t="s">
-        <v>26</v>
+        <v>189</v>
       </c>
       <c r="K81" s="4" t="s">
-        <v>213</v>
+        <v>184</v>
       </c>
       <c r="L81" s="4"/>
       <c r="M81" s="4" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="N81" s="4"/>
       <c r="O81" s="4"/>
     </row>
     <row r="82" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3">
-        <v>46232</v>
+        <v>46244</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>180</v>
+        <v>45</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>215</v>
+        <v>193</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="E82" s="3">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" s="5">
-        <v>4082.05</v>
+        <v>4320</v>
       </c>
       <c r="G82" s="5">
-        <v>4082.05</v>
+        <v>4320</v>
       </c>
       <c r="H82" s="3"/>
       <c r="I82" s="6">
@@ -4603,57 +4567,57 @@
         <v>189</v>
       </c>
       <c r="K82" s="4" t="s">
-        <v>184</v>
+        <v>27</v>
       </c>
       <c r="L82" s="4"/>
       <c r="M82" s="4" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="N82" s="4"/>
       <c r="O82" s="4"/>
     </row>
     <row r="83" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="3">
-        <v>46232</v>
+        <v>46223</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>175</v>
+        <v>196</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="E83" s="3">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" s="5">
-        <v>9716</v>
+        <v>11200</v>
       </c>
       <c r="G83" s="5">
-        <v>9716</v>
+        <v>11200</v>
       </c>
       <c r="H83" s="3"/>
       <c r="I83" s="6">
         <v>30</v>
       </c>
       <c r="J83" s="4" t="s">
-        <v>26</v>
+        <v>189</v>
       </c>
       <c r="K83" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="L83" s="4"/>
       <c r="M83" s="4" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="N83" s="4"/>
       <c r="O83" s="4"/>
     </row>
     <row r="84" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="3">
-        <v>46244</v>
+        <v>46266</v>
       </c>
       <c r="B84" s="4" t="s">
         <v>45</v>
@@ -4662,55 +4626,55 @@
         <v>193</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="E84" s="3">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F84" s="5">
-        <v>4320</v>
+        <v>18600</v>
       </c>
       <c r="G84" s="5">
-        <v>4320</v>
+        <v>18600</v>
       </c>
       <c r="H84" s="3"/>
       <c r="I84" s="6">
         <v>29</v>
       </c>
       <c r="J84" s="4" t="s">
-        <v>189</v>
+        <v>26</v>
       </c>
       <c r="K84" s="4" t="s">
         <v>27</v>
       </c>
       <c r="L84" s="4"/>
       <c r="M84" s="4" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="N84" s="4"/>
       <c r="O84" s="4"/>
     </row>
     <row r="85" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="3">
-        <v>46223</v>
+        <v>46234</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>45</v>
+        <v>180</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="E85" s="3">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F85" s="5">
-        <v>11200</v>
+        <v>3789.09</v>
       </c>
       <c r="G85" s="5">
-        <v>11200</v>
+        <v>3789.09</v>
       </c>
       <c r="H85" s="3"/>
       <c r="I85" s="6">
@@ -4720,36 +4684,36 @@
         <v>189</v>
       </c>
       <c r="K85" s="4" t="s">
-        <v>27</v>
+        <v>184</v>
       </c>
       <c r="L85" s="4"/>
       <c r="M85" s="4" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="N85" s="4"/>
       <c r="O85" s="4"/>
     </row>
     <row r="86" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="3">
-        <v>46234</v>
+        <v>46253</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>180</v>
+        <v>45</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E86" s="3">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F86" s="5">
-        <v>3789.09</v>
+        <v>10080</v>
       </c>
       <c r="G86" s="5">
-        <v>3789.09</v>
+        <v>10080</v>
       </c>
       <c r="H86" s="3"/>
       <c r="I86" s="6">
@@ -4759,85 +4723,85 @@
         <v>189</v>
       </c>
       <c r="K86" s="4" t="s">
-        <v>184</v>
+        <v>27</v>
       </c>
       <c r="L86" s="4"/>
       <c r="M86" s="4" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="N86" s="4"/>
       <c r="O86" s="4"/>
     </row>
     <row r="87" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="3">
-        <v>46266</v>
+        <v>46253</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>45</v>
+        <v>168</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>193</v>
+        <v>222</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E87" s="3">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F87" s="5">
-        <v>18600</v>
+        <v>2051.2199999999998</v>
       </c>
       <c r="G87" s="5">
-        <v>18600</v>
+        <v>2051.2199999999998</v>
       </c>
       <c r="H87" s="3"/>
       <c r="I87" s="6">
         <v>28</v>
       </c>
       <c r="J87" s="4" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="K87" s="4" t="s">
-        <v>27</v>
+        <v>171</v>
       </c>
       <c r="L87" s="4"/>
       <c r="M87" s="4" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="N87" s="4"/>
       <c r="O87" s="4"/>
     </row>
     <row r="88" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="3">
-        <v>46253</v>
+        <v>46262</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>45</v>
+        <v>225</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>193</v>
+        <v>226</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E88" s="3">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="F88" s="5">
-        <v>10080</v>
+        <v>11660.11</v>
       </c>
       <c r="G88" s="5">
-        <v>10080</v>
+        <v>11660.11</v>
       </c>
       <c r="H88" s="3"/>
       <c r="I88" s="6">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J88" s="4" t="s">
         <v>189</v>
       </c>
       <c r="K88" s="4" t="s">
-        <v>27</v>
+        <v>228</v>
       </c>
       <c r="L88" s="4"/>
       <c r="M88" s="4" t="s">
@@ -4848,308 +4812,308 @@
     </row>
     <row r="89" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="3">
-        <v>46253</v>
+        <v>46225</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="C89" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="D89" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="D89" s="4" t="s">
-        <v>231</v>
-      </c>
       <c r="E89" s="3">
-        <v>46295</v>
+        <v>46300</v>
       </c>
       <c r="F89" s="5">
-        <v>2051.2199999999998</v>
+        <v>7551.88</v>
       </c>
       <c r="G89" s="5">
-        <v>2051.2199999999998</v>
+        <v>7551.88</v>
       </c>
       <c r="H89" s="3"/>
       <c r="I89" s="6">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J89" s="4" t="s">
-        <v>18</v>
+        <v>189</v>
       </c>
       <c r="K89" s="4" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="L89" s="4"/>
       <c r="M89" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="N89" s="4"/>
       <c r="O89" s="4"/>
     </row>
     <row r="90" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="3">
-        <v>46262</v>
+        <v>46266</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>210</v>
+        <v>45</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>211</v>
+        <v>193</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E90" s="3">
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="F90" s="5">
-        <v>7694.4</v>
+        <v>18600</v>
       </c>
       <c r="G90" s="5">
-        <v>7694.4</v>
+        <v>18600</v>
       </c>
       <c r="H90" s="3"/>
       <c r="I90" s="6">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J90" s="4" t="s">
         <v>26</v>
       </c>
       <c r="K90" s="4" t="s">
-        <v>213</v>
+        <v>27</v>
       </c>
       <c r="L90" s="4"/>
       <c r="M90" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="N90" s="4"/>
       <c r="O90" s="4"/>
     </row>
     <row r="91" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="3">
-        <v>46262</v>
+        <v>46253</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>210</v>
+        <v>45</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>211</v>
+        <v>193</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E91" s="3">
-        <v>46297</v>
+        <v>46302</v>
       </c>
       <c r="F91" s="5">
-        <v>11660.11</v>
+        <v>10080</v>
       </c>
       <c r="G91" s="5">
-        <v>11660.11</v>
+        <v>10080</v>
       </c>
       <c r="H91" s="3"/>
       <c r="I91" s="6">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J91" s="4" t="s">
         <v>189</v>
       </c>
       <c r="K91" s="4" t="s">
-        <v>213</v>
+        <v>27</v>
       </c>
       <c r="L91" s="4"/>
       <c r="M91" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="N91" s="4"/>
       <c r="O91" s="4"/>
     </row>
     <row r="92" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="3">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>180</v>
+        <v>15</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E92" s="3">
-        <v>46300</v>
+        <v>46302</v>
       </c>
       <c r="F92" s="5">
-        <v>7551.88</v>
+        <v>9716</v>
       </c>
       <c r="G92" s="5">
-        <v>7551.88</v>
+        <v>9716</v>
       </c>
       <c r="H92" s="3"/>
       <c r="I92" s="6">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J92" s="4" t="s">
-        <v>189</v>
+        <v>26</v>
       </c>
       <c r="K92" s="4" t="s">
-        <v>184</v>
+        <v>39</v>
       </c>
       <c r="L92" s="4"/>
       <c r="M92" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="N92" s="4"/>
       <c r="O92" s="4"/>
     </row>
     <row r="93" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="3">
-        <v>46266</v>
+        <v>46227</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>45</v>
+        <v>180</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E93" s="3">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F93" s="5">
-        <v>18600</v>
+        <v>4216.66</v>
       </c>
       <c r="G93" s="5">
-        <v>18600</v>
+        <v>4216.66</v>
       </c>
       <c r="H93" s="3"/>
       <c r="I93" s="6">
         <v>21</v>
       </c>
       <c r="J93" s="4" t="s">
-        <v>26</v>
+        <v>183</v>
       </c>
       <c r="K93" s="4" t="s">
-        <v>27</v>
+        <v>184</v>
       </c>
       <c r="L93" s="4"/>
       <c r="M93" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="N93" s="4"/>
       <c r="O93" s="4"/>
     </row>
     <row r="94" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="3">
-        <v>46227</v>
+        <v>46262</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>180</v>
+        <v>225</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>181</v>
+        <v>226</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E94" s="3">
-        <v>46302</v>
+        <v>46304</v>
       </c>
       <c r="F94" s="5">
-        <v>4216.66</v>
+        <v>11660.11</v>
       </c>
       <c r="G94" s="5">
-        <v>4216.66</v>
+        <v>11660.11</v>
       </c>
       <c r="H94" s="3"/>
       <c r="I94" s="6">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J94" s="4" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="K94" s="4" t="s">
-        <v>184</v>
+        <v>228</v>
       </c>
       <c r="L94" s="4"/>
       <c r="M94" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="N94" s="4"/>
       <c r="O94" s="4"/>
     </row>
     <row r="95" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="3">
-        <v>46232</v>
+        <v>46262</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>15</v>
+        <v>225</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>175</v>
+        <v>226</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E95" s="3">
-        <v>46302</v>
+        <v>46304</v>
       </c>
       <c r="F95" s="5">
-        <v>9716</v>
+        <v>7694.4</v>
       </c>
       <c r="G95" s="5">
-        <v>9716</v>
+        <v>7694.4</v>
       </c>
       <c r="H95" s="3"/>
       <c r="I95" s="6">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J95" s="4" t="s">
         <v>26</v>
       </c>
       <c r="K95" s="4" t="s">
-        <v>39</v>
+        <v>228</v>
       </c>
       <c r="L95" s="4"/>
       <c r="M95" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="N95" s="4"/>
       <c r="O95" s="4"/>
     </row>
     <row r="96" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="3">
-        <v>46253</v>
+        <v>46265</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>45</v>
+        <v>135</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>193</v>
+        <v>244</v>
       </c>
       <c r="D96" s="4" t="s">
         <v>245</v>
       </c>
       <c r="E96" s="3">
-        <v>46302</v>
+        <v>46305</v>
       </c>
       <c r="F96" s="5">
-        <v>10080</v>
+        <v>4750</v>
       </c>
       <c r="G96" s="5">
-        <v>10080</v>
+        <v>4750</v>
       </c>
       <c r="H96" s="3"/>
       <c r="I96" s="6">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J96" s="4" t="s">
         <v>189</v>
       </c>
       <c r="K96" s="4" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="L96" s="4"/>
       <c r="M96" s="4" t="s">
@@ -5160,35 +5124,35 @@
     </row>
     <row r="97" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="3">
-        <v>46262</v>
+        <v>46232</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D97" s="4" t="s">
         <v>247</v>
       </c>
       <c r="E97" s="3">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="F97" s="5">
-        <v>11660.11</v>
+        <v>4082.04</v>
       </c>
       <c r="G97" s="5">
-        <v>11660.11</v>
+        <v>4082.04</v>
       </c>
       <c r="H97" s="3"/>
       <c r="I97" s="6">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J97" s="4" t="s">
         <v>189</v>
       </c>
       <c r="K97" s="4" t="s">
-        <v>213</v>
+        <v>184</v>
       </c>
       <c r="L97" s="4"/>
       <c r="M97" s="4" t="s">
@@ -5199,35 +5163,35 @@
     </row>
     <row r="98" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="3">
-        <v>46262</v>
+        <v>46266</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>210</v>
+        <v>45</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>211</v>
+        <v>193</v>
       </c>
       <c r="D98" s="4" t="s">
         <v>249</v>
       </c>
       <c r="E98" s="3">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="F98" s="5">
-        <v>7694.4</v>
+        <v>18600</v>
       </c>
       <c r="G98" s="5">
-        <v>7694.4</v>
+        <v>18600</v>
       </c>
       <c r="H98" s="3"/>
       <c r="I98" s="6">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J98" s="4" t="s">
         <v>26</v>
       </c>
       <c r="K98" s="4" t="s">
-        <v>213</v>
+        <v>27</v>
       </c>
       <c r="L98" s="4"/>
       <c r="M98" s="4" t="s">
@@ -5238,74 +5202,74 @@
     </row>
     <row r="99" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="3">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="C99" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="D99" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="D99" s="4" t="s">
-        <v>252</v>
-      </c>
       <c r="E99" s="3">
-        <v>46305</v>
+        <v>46309</v>
       </c>
       <c r="F99" s="5">
-        <v>4750</v>
+        <v>3789.1</v>
       </c>
       <c r="G99" s="5">
-        <v>4750</v>
+        <v>3789.1</v>
       </c>
       <c r="H99" s="3"/>
       <c r="I99" s="6">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J99" s="4" t="s">
         <v>189</v>
       </c>
       <c r="K99" s="4" t="s">
-        <v>54</v>
+        <v>184</v>
       </c>
       <c r="L99" s="4"/>
       <c r="M99" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="N99" s="4"/>
       <c r="O99" s="4"/>
     </row>
     <row r="100" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="3">
-        <v>46232</v>
+        <v>46268</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>180</v>
+        <v>23</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="D100" s="4" t="s">
         <v>254</v>
       </c>
       <c r="E100" s="3">
-        <v>46307</v>
+        <v>46310</v>
       </c>
       <c r="F100" s="5">
-        <v>4082.04</v>
+        <v>2754</v>
       </c>
       <c r="G100" s="5">
-        <v>4082.04</v>
+        <v>2754</v>
       </c>
       <c r="H100" s="3"/>
       <c r="I100" s="6">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J100" s="4" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="K100" s="4" t="s">
-        <v>184</v>
+        <v>71</v>
       </c>
       <c r="L100" s="4"/>
       <c r="M100" s="4" t="s">
@@ -5316,230 +5280,230 @@
     </row>
     <row r="101" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="3">
-        <v>46248</v>
+        <v>46262</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>15</v>
+        <v>225</v>
       </c>
       <c r="C101" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="D101" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="D101" s="4" t="s">
-        <v>257</v>
-      </c>
       <c r="E101" s="3">
-        <v>46308</v>
+        <v>46311</v>
       </c>
       <c r="F101" s="5">
-        <v>23355.33</v>
+        <v>7694.4</v>
       </c>
       <c r="G101" s="5">
-        <v>23355.33</v>
+        <v>7694.4</v>
       </c>
       <c r="H101" s="3"/>
       <c r="I101" s="6">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J101" s="4" t="s">
-        <v>189</v>
+        <v>26</v>
       </c>
       <c r="K101" s="4" t="s">
-        <v>39</v>
+        <v>228</v>
       </c>
       <c r="L101" s="4"/>
       <c r="M101" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N101" s="4"/>
       <c r="O101" s="4"/>
     </row>
     <row r="102" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="3">
-        <v>46266</v>
+        <v>46262</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>45</v>
+        <v>225</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>193</v>
+        <v>226</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E102" s="3">
-        <v>46308</v>
+        <v>46311</v>
       </c>
       <c r="F102" s="5">
-        <v>18600</v>
+        <v>11660.11</v>
       </c>
       <c r="G102" s="5">
-        <v>18600</v>
+        <v>11660.11</v>
       </c>
       <c r="H102" s="3"/>
       <c r="I102" s="6">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J102" s="4" t="s">
-        <v>26</v>
+        <v>189</v>
       </c>
       <c r="K102" s="4" t="s">
-        <v>27</v>
+        <v>228</v>
       </c>
       <c r="L102" s="4"/>
       <c r="M102" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="N102" s="4"/>
       <c r="O102" s="4"/>
     </row>
     <row r="103" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="3">
-        <v>46234</v>
+        <v>46258</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>180</v>
+        <v>135</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>181</v>
+        <v>244</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E103" s="3">
-        <v>46309</v>
+        <v>46313</v>
       </c>
       <c r="F103" s="5">
-        <v>3789.1</v>
+        <v>6247.5</v>
       </c>
       <c r="G103" s="5">
-        <v>3789.1</v>
+        <v>6247.5</v>
       </c>
       <c r="H103" s="3"/>
       <c r="I103" s="6">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J103" s="4" t="s">
         <v>189</v>
       </c>
       <c r="K103" s="4" t="s">
-        <v>184</v>
+        <v>54</v>
       </c>
       <c r="L103" s="4"/>
       <c r="M103" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="N103" s="4"/>
       <c r="O103" s="4"/>
     </row>
     <row r="104" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="3">
-        <v>46268</v>
+        <v>46286</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>23</v>
+        <v>168</v>
       </c>
       <c r="C104" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="D104" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="D104" s="4" t="s">
-        <v>264</v>
-      </c>
       <c r="E104" s="3">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="F104" s="5">
-        <v>2754</v>
+        <v>5475.86</v>
       </c>
       <c r="G104" s="5">
-        <v>2754</v>
+        <v>5475.86</v>
       </c>
       <c r="H104" s="3"/>
       <c r="I104" s="6">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J104" s="4" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="K104" s="4" t="s">
-        <v>71</v>
+        <v>171</v>
       </c>
       <c r="L104" s="4"/>
       <c r="M104" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="N104" s="4"/>
       <c r="O104" s="4"/>
     </row>
     <row r="105" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="3">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>210</v>
+        <v>135</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>211</v>
+        <v>244</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E105" s="3">
-        <v>46311</v>
+        <v>46315</v>
       </c>
       <c r="F105" s="5">
-        <v>7694.4</v>
+        <v>4750</v>
       </c>
       <c r="G105" s="5">
-        <v>7694.4</v>
+        <v>4750</v>
       </c>
       <c r="H105" s="3"/>
       <c r="I105" s="6">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J105" s="4" t="s">
-        <v>26</v>
+        <v>189</v>
       </c>
       <c r="K105" s="4" t="s">
-        <v>213</v>
+        <v>54</v>
       </c>
       <c r="L105" s="4"/>
       <c r="M105" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="N105" s="4"/>
       <c r="O105" s="4"/>
     </row>
     <row r="106" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="3">
-        <v>46262</v>
+        <v>46280</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>210</v>
+        <v>15</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>211</v>
+        <v>267</v>
       </c>
       <c r="D106" s="4" t="s">
         <v>268</v>
       </c>
       <c r="E106" s="3">
-        <v>46311</v>
+        <v>46315</v>
       </c>
       <c r="F106" s="5">
-        <v>11660.11</v>
+        <v>9196.5</v>
       </c>
       <c r="G106" s="5">
-        <v>11660.11</v>
+        <v>12695.59</v>
       </c>
       <c r="H106" s="3"/>
       <c r="I106" s="6">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J106" s="4" t="s">
         <v>189</v>
       </c>
       <c r="K106" s="4" t="s">
-        <v>213</v>
+        <v>39</v>
       </c>
       <c r="L106" s="4"/>
       <c r="M106" s="4" t="s">
@@ -5550,74 +5514,74 @@
     </row>
     <row r="107" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="3">
-        <v>46258</v>
+        <v>46287</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>135</v>
+        <v>168</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>251</v>
+        <v>270</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E107" s="3">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="F107" s="5">
-        <v>6247.5</v>
+        <v>4466.2700000000004</v>
       </c>
       <c r="G107" s="5">
-        <v>6247.5</v>
+        <v>4466.2700000000004</v>
       </c>
       <c r="H107" s="3"/>
       <c r="I107" s="6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J107" s="4" t="s">
         <v>189</v>
       </c>
       <c r="K107" s="4" t="s">
-        <v>54</v>
+        <v>171</v>
       </c>
       <c r="L107" s="4"/>
       <c r="M107" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N107" s="4"/>
       <c r="O107" s="4"/>
     </row>
     <row r="108" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="3">
-        <v>46286</v>
+        <v>46266</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>168</v>
+        <v>45</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>272</v>
+        <v>193</v>
       </c>
       <c r="D108" s="4" t="s">
         <v>273</v>
       </c>
       <c r="E108" s="3">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F108" s="5">
-        <v>5475.86</v>
+        <v>18600</v>
       </c>
       <c r="G108" s="5">
-        <v>5475.86</v>
+        <v>18600</v>
       </c>
       <c r="H108" s="3"/>
       <c r="I108" s="6">
         <v>8</v>
       </c>
       <c r="J108" s="4" t="s">
-        <v>189</v>
+        <v>26</v>
       </c>
       <c r="K108" s="4" t="s">
-        <v>171</v>
+        <v>27</v>
       </c>
       <c r="L108" s="4"/>
       <c r="M108" s="4" t="s">
@@ -5628,35 +5592,35 @@
     </row>
     <row r="109" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="3">
-        <v>46265</v>
+        <v>46288</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>135</v>
+        <v>23</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D109" s="4" t="s">
         <v>275</v>
       </c>
       <c r="E109" s="3">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F109" s="5">
-        <v>4750</v>
+        <v>2334.2399999999998</v>
       </c>
       <c r="G109" s="5">
-        <v>4750</v>
+        <v>2334.2399999999998</v>
       </c>
       <c r="H109" s="3"/>
       <c r="I109" s="6">
         <v>7</v>
       </c>
       <c r="J109" s="4" t="s">
-        <v>189</v>
+        <v>18</v>
       </c>
       <c r="K109" s="4" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="L109" s="4"/>
       <c r="M109" s="4" t="s">
@@ -5667,230 +5631,230 @@
     </row>
     <row r="110" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="3">
-        <v>46280</v>
+        <v>46287</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>15</v>
+        <v>277</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E110" s="3">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="F110" s="5">
-        <v>9196.5</v>
+        <v>9617.7999999999993</v>
       </c>
       <c r="G110" s="5">
-        <v>12695.59</v>
+        <v>9617.7999999999993</v>
       </c>
       <c r="H110" s="3"/>
       <c r="I110" s="6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J110" s="4" t="s">
         <v>189</v>
       </c>
       <c r="K110" s="4" t="s">
-        <v>39</v>
+        <v>280</v>
       </c>
       <c r="L110" s="4"/>
       <c r="M110" s="4" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="N110" s="4"/>
       <c r="O110" s="4"/>
     </row>
     <row r="111" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="3">
-        <v>46287</v>
+        <v>46268</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E111" s="3">
-        <v>46315</v>
+        <v>46318</v>
       </c>
       <c r="F111" s="5">
-        <v>4466.2700000000004</v>
+        <v>3714.54</v>
       </c>
       <c r="G111" s="5">
-        <v>4466.2700000000004</v>
+        <v>3714.54</v>
       </c>
       <c r="H111" s="3"/>
       <c r="I111" s="6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J111" s="4" t="s">
         <v>189</v>
       </c>
       <c r="K111" s="4" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="L111" s="4"/>
       <c r="M111" s="4" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="N111" s="4"/>
       <c r="O111" s="4"/>
     </row>
     <row r="112" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="3">
-        <v>46287</v>
+        <v>46262</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>68</v>
+        <v>225</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>283</v>
+        <v>226</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E112" s="3">
-        <v>46315</v>
+        <v>46318</v>
       </c>
       <c r="F112" s="5">
-        <v>784.63</v>
+        <v>7694.4</v>
       </c>
       <c r="G112" s="5">
-        <v>979.25</v>
+        <v>7694.4</v>
       </c>
       <c r="H112" s="3"/>
       <c r="I112" s="6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J112" s="4" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="K112" s="4" t="s">
-        <v>71</v>
+        <v>228</v>
       </c>
       <c r="L112" s="4"/>
       <c r="M112" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N112" s="4"/>
       <c r="O112" s="4"/>
     </row>
     <row r="113" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="3">
-        <v>46266</v>
+        <v>46290</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>45</v>
+        <v>168</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>193</v>
+        <v>287</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E113" s="3">
-        <v>46315</v>
+        <v>46318</v>
       </c>
       <c r="F113" s="5">
-        <v>18600</v>
+        <v>5206.7700000000004</v>
       </c>
       <c r="G113" s="5">
-        <v>18600</v>
+        <v>10139.15</v>
       </c>
       <c r="H113" s="3"/>
       <c r="I113" s="6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J113" s="4" t="s">
-        <v>26</v>
+        <v>189</v>
       </c>
       <c r="K113" s="4" t="s">
-        <v>27</v>
+        <v>171</v>
       </c>
       <c r="L113" s="4"/>
       <c r="M113" s="4" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="N113" s="4"/>
       <c r="O113" s="4"/>
     </row>
     <row r="114" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="3">
-        <v>46253</v>
+        <v>46262</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>168</v>
+        <v>225</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>288</v>
+        <v>226</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E114" s="3">
-        <v>46316</v>
+        <v>46318</v>
       </c>
       <c r="F114" s="5">
-        <v>1452.6</v>
+        <v>11660.11</v>
       </c>
       <c r="G114" s="5">
-        <v>1452.6</v>
+        <v>11660.11</v>
       </c>
       <c r="H114" s="3"/>
       <c r="I114" s="6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J114" s="4" t="s">
-        <v>18</v>
+        <v>189</v>
       </c>
       <c r="K114" s="4" t="s">
-        <v>171</v>
+        <v>228</v>
       </c>
       <c r="L114" s="4"/>
       <c r="M114" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N114" s="4"/>
       <c r="O114" s="4"/>
     </row>
     <row r="115" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="3">
-        <v>46288</v>
+        <v>46259</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>168</v>
+        <v>15</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E115" s="3">
-        <v>46316</v>
+        <v>46319</v>
       </c>
       <c r="F115" s="5">
-        <v>4772.8999999999996</v>
+        <v>6265</v>
       </c>
       <c r="G115" s="5">
-        <v>4772.8999999999996</v>
+        <v>6265</v>
       </c>
       <c r="H115" s="3"/>
       <c r="I115" s="6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J115" s="4" t="s">
         <v>189</v>
       </c>
       <c r="K115" s="4" t="s">
-        <v>293</v>
+        <v>19</v>
       </c>
       <c r="L115" s="4"/>
       <c r="M115" s="4" t="s">
@@ -5901,35 +5865,35 @@
     </row>
     <row r="116" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="3">
-        <v>46288</v>
+        <v>46286</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>23</v>
+        <v>168</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D116" s="4" t="s">
         <v>295</v>
       </c>
       <c r="E116" s="3">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="F116" s="5">
-        <v>2334.2399999999998</v>
+        <v>5475.86</v>
       </c>
       <c r="G116" s="5">
-        <v>2334.2399999999998</v>
+        <v>5475.86</v>
       </c>
       <c r="H116" s="3"/>
       <c r="I116" s="6">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J116" s="4" t="s">
-        <v>18</v>
+        <v>189</v>
       </c>
       <c r="K116" s="4" t="s">
-        <v>71</v>
+        <v>171</v>
       </c>
       <c r="L116" s="4"/>
       <c r="M116" s="4" t="s">
@@ -5943,351 +5907,195 @@
         <v>46287</v>
       </c>
       <c r="B117" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C117" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="D117" s="4" t="s">
         <v>297</v>
       </c>
-      <c r="C117" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="D117" s="4" t="s">
-        <v>299</v>
-      </c>
       <c r="E117" s="3">
-        <v>46317</v>
+        <v>46322</v>
       </c>
       <c r="F117" s="5">
-        <v>9617.7999999999993</v>
+        <v>4466.2700000000004</v>
       </c>
       <c r="G117" s="5">
-        <v>9617.7999999999993</v>
+        <v>4466.2700000000004</v>
       </c>
       <c r="H117" s="3"/>
       <c r="I117" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J117" s="4" t="s">
         <v>189</v>
       </c>
       <c r="K117" s="4" t="s">
-        <v>300</v>
+        <v>171</v>
       </c>
       <c r="L117" s="4"/>
       <c r="M117" s="4" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="N117" s="4"/>
       <c r="O117" s="4"/>
     </row>
     <row r="118" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="3">
-        <v>46262</v>
+        <v>46280</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>168</v>
+        <v>45</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E118" s="3">
-        <v>46318</v>
+        <v>46322</v>
       </c>
       <c r="F118" s="5">
-        <v>2992</v>
+        <v>1600</v>
       </c>
       <c r="G118" s="5">
-        <v>2992</v>
+        <v>1600</v>
       </c>
       <c r="H118" s="3"/>
       <c r="I118" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J118" s="4" t="s">
         <v>189</v>
       </c>
       <c r="K118" s="4" t="s">
-        <v>293</v>
+        <v>75</v>
       </c>
       <c r="L118" s="4"/>
       <c r="M118" s="4" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="N118" s="4"/>
       <c r="O118" s="4"/>
     </row>
     <row r="119" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="3">
-        <v>46290</v>
+        <v>46287</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>168</v>
+        <v>68</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E119" s="3">
-        <v>46318</v>
+        <v>46322</v>
       </c>
       <c r="F119" s="5">
-        <v>5206.7700000000004</v>
+        <v>784.63</v>
       </c>
       <c r="G119" s="5">
-        <v>10139.15</v>
+        <v>784.63</v>
       </c>
       <c r="H119" s="3"/>
       <c r="I119" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J119" s="4" t="s">
-        <v>189</v>
+        <v>18</v>
       </c>
       <c r="K119" s="4" t="s">
-        <v>171</v>
+        <v>71</v>
       </c>
       <c r="L119" s="4"/>
       <c r="M119" s="4" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="N119" s="4"/>
       <c r="O119" s="4"/>
     </row>
     <row r="120" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="3">
-        <v>46268</v>
+        <v>46262</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>180</v>
+        <v>277</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>307</v>
+        <v>278</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="E120" s="3">
-        <v>46318</v>
+        <v>46322</v>
       </c>
       <c r="F120" s="5">
-        <v>3714.54</v>
+        <v>4689.21</v>
       </c>
       <c r="G120" s="5">
-        <v>3714.54</v>
+        <v>4689.21</v>
       </c>
       <c r="H120" s="3"/>
       <c r="I120" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J120" s="4" t="s">
         <v>189</v>
       </c>
       <c r="K120" s="4" t="s">
-        <v>184</v>
+        <v>280</v>
       </c>
       <c r="L120" s="4"/>
       <c r="M120" s="4" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="N120" s="4"/>
       <c r="O120" s="4"/>
     </row>
     <row r="121" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="3">
-        <v>46262</v>
+        <v>46223</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>210</v>
+        <v>15</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>211</v>
+        <v>292</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="E121" s="3">
-        <v>46318</v>
+        <v>46322</v>
       </c>
       <c r="F121" s="5">
-        <v>11660.11</v>
+        <v>6265</v>
       </c>
       <c r="G121" s="5">
-        <v>11660.11</v>
+        <v>6265</v>
       </c>
       <c r="H121" s="3"/>
       <c r="I121" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J121" s="4" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="K121" s="4" t="s">
-        <v>213</v>
+        <v>19</v>
       </c>
       <c r="L121" s="4"/>
       <c r="M121" s="4" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="N121" s="4"/>
       <c r="O121" s="4"/>
-    </row>
-    <row r="122" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="3">
-        <v>46262</v>
-      </c>
-      <c r="B122" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="C122" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="D122" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="E122" s="3">
-        <v>46318</v>
-      </c>
-      <c r="F122" s="5">
-        <v>7694.4</v>
-      </c>
-      <c r="G122" s="5">
-        <v>7694.4</v>
-      </c>
-      <c r="H122" s="3"/>
-      <c r="I122" s="6">
-        <v>4</v>
-      </c>
-      <c r="J122" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K122" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="L122" s="4"/>
-      <c r="M122" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="N122" s="4"/>
-      <c r="O122" s="4"/>
-    </row>
-    <row r="123" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="3">
-        <v>46258</v>
-      </c>
-      <c r="B123" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C123" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="D123" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="E123" s="3">
-        <v>46318</v>
-      </c>
-      <c r="F123" s="5">
-        <v>879.12</v>
-      </c>
-      <c r="G123" s="5">
-        <v>879.12</v>
-      </c>
-      <c r="H123" s="3"/>
-      <c r="I123" s="6">
-        <v>4</v>
-      </c>
-      <c r="J123" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="K123" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="L123" s="4"/>
-      <c r="M123" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="N123" s="4"/>
-      <c r="O123" s="4"/>
-    </row>
-    <row r="124" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="3">
-        <v>46259</v>
-      </c>
-      <c r="B124" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C124" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="D124" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="E124" s="3">
-        <v>46319</v>
-      </c>
-      <c r="F124" s="5">
-        <v>6265</v>
-      </c>
-      <c r="G124" s="5">
-        <v>6265</v>
-      </c>
-      <c r="H124" s="3"/>
-      <c r="I124" s="6">
-        <v>3</v>
-      </c>
-      <c r="J124" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="K124" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="L124" s="4"/>
-      <c r="M124" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="N124" s="4"/>
-      <c r="O124" s="4"/>
-    </row>
-    <row r="125" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="3">
-        <v>46286</v>
-      </c>
-      <c r="B125" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="C125" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="D125" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="E125" s="3">
-        <v>46321</v>
-      </c>
-      <c r="F125" s="5">
-        <v>5475.86</v>
-      </c>
-      <c r="G125" s="5">
-        <v>5475.86</v>
-      </c>
-      <c r="H125" s="3"/>
-      <c r="I125" s="6">
-        <v>1</v>
-      </c>
-      <c r="J125" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="K125" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="L125" s="4"/>
-      <c r="M125" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="N125" s="4"/>
-      <c r="O125" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
